--- a/Results/Phase 2/Ammonia/ammonia land use results.xlsx
+++ b/Results/Phase 2/Ammonia/ammonia land use results.xlsx
@@ -586,85 +586,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.965429243830839</v>
+        <v>1.965429243830902</v>
       </c>
       <c r="C2" t="n">
-        <v>1.964320871214764</v>
+        <v>1.96432087121485</v>
       </c>
       <c r="D2" t="n">
-        <v>1.931246591717077</v>
+        <v>1.931246591717139</v>
       </c>
       <c r="E2" t="n">
-        <v>1.901082556905407</v>
+        <v>1.901082556905441</v>
       </c>
       <c r="F2" t="n">
-        <v>1.923142687891283</v>
+        <v>1.923142687891357</v>
       </c>
       <c r="G2" t="n">
-        <v>2.043971997410172</v>
+        <v>2.043971997410224</v>
       </c>
       <c r="H2" t="n">
-        <v>1.947334855976385</v>
+        <v>1.947334855976427</v>
       </c>
       <c r="I2" t="n">
-        <v>1.954827391967128</v>
+        <v>1.954827391967184</v>
       </c>
       <c r="J2" t="n">
-        <v>1.993975789721873</v>
+        <v>1.993975789721942</v>
       </c>
       <c r="K2" t="n">
-        <v>1.999374600981757</v>
+        <v>1.999374600981809</v>
       </c>
       <c r="L2" t="n">
-        <v>2.011781953122486</v>
+        <v>2.011781953122546</v>
       </c>
       <c r="M2" t="n">
-        <v>2.044952454269517</v>
+        <v>2.044952454269576</v>
       </c>
       <c r="N2" t="n">
-        <v>1.959795316314341</v>
+        <v>1.959795316314401</v>
       </c>
       <c r="O2" t="n">
-        <v>3.699683215355421</v>
+        <v>3.699683215355555</v>
       </c>
       <c r="P2" t="n">
-        <v>1.984717909653266</v>
+        <v>1.984717909653342</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.948738215850577</v>
+        <v>1.948738215850605</v>
       </c>
       <c r="R2" t="n">
-        <v>1.962415899923232</v>
+        <v>1.962415899923293</v>
       </c>
       <c r="S2" t="n">
-        <v>1.997526398876247</v>
+        <v>1.99752639887629</v>
       </c>
       <c r="T2" t="n">
-        <v>1.958574557036497</v>
+        <v>1.958574557036554</v>
       </c>
       <c r="U2" t="n">
-        <v>1.98467374463173</v>
+        <v>1.984673744631917</v>
       </c>
       <c r="V2" t="n">
-        <v>1.975683433171128</v>
+        <v>1.975683433171187</v>
       </c>
       <c r="W2" t="n">
-        <v>2.039539932181472</v>
+        <v>2.039539932181777</v>
       </c>
       <c r="X2" t="n">
-        <v>1.964048938109803</v>
+        <v>1.964048938109905</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.962921262778762</v>
+        <v>1.962921262778823</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.760472582055876</v>
+        <v>1.760472582055969</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.982801096152069</v>
+        <v>1.98280109615214</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.01976182639464</v>
+        <v>2.019761826394704</v>
       </c>
     </row>
     <row r="3">
@@ -674,85 +674,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.208728488161575</v>
+        <v>2.208728488161634</v>
       </c>
       <c r="C3" t="n">
-        <v>2.087177290051939</v>
+        <v>2.087177290052021</v>
       </c>
       <c r="D3" t="n">
-        <v>1.966086037400081</v>
+        <v>1.966086037400137</v>
       </c>
       <c r="E3" t="n">
-        <v>1.750921156149373</v>
+        <v>1.750921156149444</v>
       </c>
       <c r="F3" t="n">
-        <v>1.908116771178129</v>
+        <v>1.908116771178184</v>
       </c>
       <c r="G3" t="n">
-        <v>2.768263406697269</v>
+        <v>2.768263406697336</v>
       </c>
       <c r="H3" t="n">
-        <v>2.081741381966235</v>
+        <v>2.081741381966299</v>
       </c>
       <c r="I3" t="n">
-        <v>2.135055632310378</v>
+        <v>2.13505563231044</v>
       </c>
       <c r="J3" t="n">
-        <v>2.412901212981834</v>
+        <v>2.412901212981889</v>
       </c>
       <c r="K3" t="n">
-        <v>2.453526899832421</v>
+        <v>2.453526899832474</v>
       </c>
       <c r="L3" t="n">
-        <v>2.540541781603557</v>
+        <v>2.540541781603589</v>
       </c>
       <c r="M3" t="n">
-        <v>2.778928460980596</v>
+        <v>2.778928460980664</v>
       </c>
       <c r="N3" t="n">
-        <v>2.170003338015976</v>
+        <v>2.170003338016018</v>
       </c>
       <c r="O3" t="n">
-        <v>5.135851886108281</v>
+        <v>5.135851886108428</v>
       </c>
       <c r="P3" t="n">
-        <v>2.346142224696009</v>
+        <v>2.346142224696051</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.091080556476185</v>
+        <v>2.091080556476233</v>
       </c>
       <c r="R3" t="n">
-        <v>2.189643956048622</v>
+        <v>2.189643956048679</v>
       </c>
       <c r="S3" t="n">
-        <v>2.437721629364957</v>
+        <v>2.437721629365009</v>
       </c>
       <c r="T3" t="n">
-        <v>2.161779503724641</v>
+        <v>2.161779503724692</v>
       </c>
       <c r="U3" t="n">
-        <v>2.37744772902574</v>
+        <v>2.377447729025938</v>
       </c>
       <c r="V3" t="n">
-        <v>2.281775242559732</v>
+        <v>2.281775242559804</v>
       </c>
       <c r="W3" t="n">
-        <v>2.253994053569912</v>
+        <v>2.253994053570316</v>
       </c>
       <c r="X3" t="n">
-        <v>2.200693952493435</v>
+        <v>2.200693952493503</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.192080408595765</v>
+        <v>2.192080408595809</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.874459164502141</v>
+        <v>1.874459164502224</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.334111892323557</v>
+        <v>2.334111892323633</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.599093253005573</v>
+        <v>2.599093253005619</v>
       </c>
     </row>
     <row r="4">
@@ -762,85 +762,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.706808921488903</v>
+        <v>1.706808921489017</v>
       </c>
       <c r="C4" t="n">
-        <v>1.45995615862838</v>
+        <v>1.459956158628605</v>
       </c>
       <c r="D4" t="n">
-        <v>1.320700141067049</v>
+        <v>1.320700141067189</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9799834917273543</v>
+        <v>0.9799834917274739</v>
       </c>
       <c r="F4" t="n">
-        <v>1.229162819374888</v>
+        <v>1.229162819375038</v>
       </c>
       <c r="G4" t="n">
-        <v>2.593985454619058</v>
+        <v>2.593985454619146</v>
       </c>
       <c r="H4" t="n">
-        <v>1.50242448684291</v>
+        <v>1.502424486843057</v>
       </c>
       <c r="I4" t="n">
-        <v>1.587056127595417</v>
+        <v>1.58705612759546</v>
       </c>
       <c r="J4" t="n">
-        <v>2.028446567233684</v>
+        <v>2.028446567233897</v>
       </c>
       <c r="K4" t="n">
-        <v>2.090237346144118</v>
+        <v>2.090237346144295</v>
       </c>
       <c r="L4" t="n">
-        <v>2.230384096237681</v>
+        <v>2.230384096237897</v>
       </c>
       <c r="M4" t="n">
-        <v>2.601748298108846</v>
+        <v>2.601748298109029</v>
       </c>
       <c r="N4" t="n">
-        <v>1.643171118455246</v>
+        <v>1.643171118455413</v>
       </c>
       <c r="O4" t="n">
-        <v>1.840949880386442</v>
+        <v>1.840949880386531</v>
       </c>
       <c r="P4" t="n">
-        <v>1.924683275177928</v>
+        <v>1.924683275178169</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.518276082199365</v>
+        <v>1.518276082199337</v>
       </c>
       <c r="R4" t="n">
-        <v>1.672771815845726</v>
+        <v>1.67277181584586</v>
       </c>
       <c r="S4" t="n">
-        <v>2.069361053147381</v>
+        <v>2.069361053147447</v>
       </c>
       <c r="T4" t="n">
-        <v>1.62938208083498</v>
+        <v>1.629382080835107</v>
       </c>
       <c r="U4" t="n">
-        <v>1.897996103684423</v>
+        <v>1.897996103684534</v>
       </c>
       <c r="V4" t="n">
-        <v>1.817578136668413</v>
+        <v>1.817578136668488</v>
       </c>
       <c r="W4" t="n">
-        <v>1.545708505374644</v>
+        <v>1.545708505374843</v>
       </c>
       <c r="X4" t="n">
-        <v>1.691217733398157</v>
+        <v>1.691217733398326</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.58879293833837</v>
+        <v>1.58879293833853</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.714395576247573</v>
+        <v>1.71439557624771</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.903031984904073</v>
+        <v>1.903031984904273</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.315967969724783</v>
+        <v>2.315967969724951</v>
       </c>
     </row>
     <row r="5">
@@ -850,85 +850,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>10.65847992630473</v>
+        <v>10.65847992630525</v>
       </c>
       <c r="C5" t="n">
-        <v>6.573456274792221</v>
+        <v>6.573456274792366</v>
       </c>
       <c r="D5" t="n">
-        <v>3.668121319196945</v>
+        <v>3.668121319197134</v>
       </c>
       <c r="E5" t="n">
-        <v>-3.123438771455911</v>
+        <v>-3.123438771455726</v>
       </c>
       <c r="F5" t="n">
-        <v>1.74671806594257</v>
+        <v>1.746718065942753</v>
       </c>
       <c r="G5" t="n">
-        <v>27.91294152409772</v>
+        <v>27.91294152409811</v>
       </c>
       <c r="H5" t="n">
-        <v>7.822514638343309</v>
+        <v>7.822514638343766</v>
       </c>
       <c r="I5" t="n">
-        <v>9.431508359483962</v>
+        <v>9.431508359484184</v>
       </c>
       <c r="J5" t="n">
-        <v>17.40935406770318</v>
+        <v>17.40935406770343</v>
       </c>
       <c r="K5" t="n">
-        <v>19.8828390092999</v>
+        <v>19.88283900930007</v>
       </c>
       <c r="L5" t="n">
-        <v>21.79157226183579</v>
+        <v>21.79157226183617</v>
       </c>
       <c r="M5" t="n">
-        <v>31.31851235281863</v>
+        <v>31.31851235281904</v>
       </c>
       <c r="N5" t="n">
-        <v>16.30048673302501</v>
+        <v>16.30048673302552</v>
       </c>
       <c r="O5" t="n">
-        <v>12.92326556234241</v>
+        <v>12.92326556234266</v>
       </c>
       <c r="P5" t="n">
-        <v>14.89715598136434</v>
+        <v>14.89715598136451</v>
       </c>
       <c r="Q5" t="n">
-        <v>7.73955015895699</v>
+        <v>7.739550158957194</v>
       </c>
       <c r="R5" t="n">
-        <v>11.41247380091206</v>
+        <v>11.41247380091228</v>
       </c>
       <c r="S5" t="n">
-        <v>17.90847245244615</v>
+        <v>17.90847245244646</v>
       </c>
       <c r="T5" t="n">
-        <v>10.2720745824666</v>
+        <v>10.27207458246694</v>
       </c>
       <c r="U5" t="n">
-        <v>16.64499890169322</v>
+        <v>16.64499890169357</v>
       </c>
       <c r="V5" t="n">
-        <v>12.90394109822267</v>
+        <v>12.90394109822297</v>
       </c>
       <c r="W5" t="n">
-        <v>8.116242959831949</v>
+        <v>8.116242959832746</v>
       </c>
       <c r="X5" t="n">
-        <v>11.42430667150904</v>
+        <v>11.42430667150919</v>
       </c>
       <c r="Y5" t="n">
-        <v>10.83183119873878</v>
+        <v>10.83183119873903</v>
       </c>
       <c r="Z5" t="n">
-        <v>11.02773353670071</v>
+        <v>11.02773353670083</v>
       </c>
       <c r="AA5" t="n">
-        <v>15.44185892709181</v>
+        <v>15.44185892709217</v>
       </c>
       <c r="AB5" t="n">
-        <v>25.935336940463</v>
+        <v>25.93533694046389</v>
       </c>
     </row>
     <row r="6">
@@ -938,85 +938,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.037556449307247</v>
+        <v>4.056151605245573</v>
       </c>
       <c r="C6" t="n">
-        <v>3.809298842385036</v>
+        <v>3.809298842385159</v>
       </c>
       <c r="D6" t="n">
-        <v>1.651447668885433</v>
+        <v>1.651447668885506</v>
       </c>
       <c r="E6" t="n">
-        <v>3.329326175483978</v>
+        <v>1.310731019545798</v>
       </c>
       <c r="F6" t="n">
-        <v>1.559910347193273</v>
+        <v>3.578505503131591</v>
       </c>
       <c r="G6" t="n">
-        <v>2.924732982437412</v>
+        <v>4.943328138375701</v>
       </c>
       <c r="H6" t="n">
-        <v>3.851767170599526</v>
+        <v>3.851767170599611</v>
       </c>
       <c r="I6" t="n">
-        <v>3.9363988113519</v>
+        <v>1.917803655413774</v>
       </c>
       <c r="J6" t="n">
-        <v>2.359194095052129</v>
+        <v>4.377789250990457</v>
       </c>
       <c r="K6" t="n">
-        <v>2.420984873962559</v>
+        <v>2.420984873962611</v>
       </c>
       <c r="L6" t="n">
-        <v>4.579726779994305</v>
+        <v>2.561131624056216</v>
       </c>
       <c r="M6" t="n">
-        <v>2.932495825927264</v>
+        <v>2.932495825927339</v>
       </c>
       <c r="N6" t="n">
-        <v>1.979020924995626</v>
+        <v>1.979020924995698</v>
       </c>
       <c r="O6" t="n">
-        <v>4.244694178333003</v>
+        <v>4.244694178333112</v>
       </c>
       <c r="P6" t="n">
-        <v>4.32843588094201</v>
+        <v>4.328435880942211</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.849023610017597</v>
+        <v>1.849023610017654</v>
       </c>
       <c r="R6" t="n">
-        <v>4.022114499602298</v>
+        <v>2.003519343664183</v>
       </c>
       <c r="S6" t="n">
-        <v>4.418703736903858</v>
+        <v>4.418703736904005</v>
       </c>
       <c r="T6" t="n">
-        <v>1.960129608653367</v>
+        <v>1.960129608653426</v>
       </c>
       <c r="U6" t="n">
-        <v>2.31843081494172</v>
+        <v>2.318430814941786</v>
       </c>
       <c r="V6" t="n">
-        <v>4.166920820424918</v>
+        <v>4.166920820425046</v>
       </c>
       <c r="W6" t="n">
-        <v>1.899503510063033</v>
+        <v>3.949457657437285</v>
       </c>
       <c r="X6" t="n">
-        <v>4.040560417154776</v>
+        <v>4.04056041715489</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.029914744597596</v>
+        <v>2.029914744597652</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.045143104065976</v>
+        <v>2.045143104066028</v>
       </c>
       <c r="AA6" t="n">
-        <v>4.252374668660693</v>
+        <v>2.233779512722589</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.655234343620112</v>
+        <v>2.655234343620204</v>
       </c>
     </row>
     <row r="7">
@@ -1026,85 +1026,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.357006766055574</v>
+        <v>2.357006766055675</v>
       </c>
       <c r="C7" t="n">
-        <v>2.110154003195175</v>
+        <v>2.110154003195265</v>
       </c>
       <c r="D7" t="n">
-        <v>1.970897985633787</v>
+        <v>1.970897985633848</v>
       </c>
       <c r="E7" t="n">
-        <v>1.630181336294068</v>
+        <v>1.630181336294139</v>
       </c>
       <c r="F7" t="n">
-        <v>1.879360663941624</v>
+        <v>1.879360663941698</v>
       </c>
       <c r="G7" t="n">
-        <v>3.244183299185743</v>
+        <v>3.244183299185807</v>
       </c>
       <c r="H7" t="n">
-        <v>2.152622331409644</v>
+        <v>2.152622331409717</v>
       </c>
       <c r="I7" t="n">
-        <v>2.237253972162054</v>
+        <v>2.237253972162123</v>
       </c>
       <c r="J7" t="n">
-        <v>2.67864441180047</v>
+        <v>2.678644411800557</v>
       </c>
       <c r="K7" t="n">
-        <v>2.74043519071086</v>
+        <v>2.740435190710957</v>
       </c>
       <c r="L7" t="n">
-        <v>2.880581940804422</v>
+        <v>2.880581940804553</v>
       </c>
       <c r="M7" t="n">
-        <v>3.251946142675606</v>
+        <v>3.251946142675687</v>
       </c>
       <c r="N7" t="n">
-        <v>2.293368963021989</v>
+        <v>2.293368963022073</v>
       </c>
       <c r="O7" t="n">
-        <v>2.491142057914362</v>
+        <v>2.491142057914454</v>
       </c>
       <c r="P7" t="n">
-        <v>2.57487545270605</v>
+        <v>2.574875452706095</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.168473926765923</v>
+        <v>2.168473926765996</v>
       </c>
       <c r="R7" t="n">
-        <v>2.322969660412454</v>
+        <v>2.322969660412523</v>
       </c>
       <c r="S7" t="n">
-        <v>2.719558897714015</v>
+        <v>2.719558897714106</v>
       </c>
       <c r="T7" t="n">
-        <v>2.279579925401697</v>
+        <v>2.279579925401765</v>
       </c>
       <c r="U7" t="n">
-        <v>2.637607823090638</v>
+        <v>2.637607823090719</v>
       </c>
       <c r="V7" t="n">
-        <v>2.467775981235073</v>
+        <v>2.467775981235145</v>
       </c>
       <c r="W7" t="n">
-        <v>2.195906349941409</v>
+        <v>2.195906349941507</v>
       </c>
       <c r="X7" t="n">
-        <v>2.341415577964928</v>
+        <v>2.34141557796498</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.328677966344054</v>
+        <v>2.328677966344129</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.364593420814287</v>
+        <v>2.364593420814372</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.553229829470854</v>
+        <v>2.55322982947093</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.966165814291525</v>
+        <v>2.966165814291613</v>
       </c>
     </row>
     <row r="8">
@@ -1114,85 +1114,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.089748640106249</v>
+        <v>4.089748640106463</v>
       </c>
       <c r="C8" t="n">
-        <v>5.404650807952045</v>
+        <v>5.404650807952397</v>
       </c>
       <c r="D8" t="n">
-        <v>5.2653947903906</v>
+        <v>5.265394790390991</v>
       </c>
       <c r="E8" t="n">
-        <v>4.924678141051028</v>
+        <v>4.093089709328644</v>
       </c>
       <c r="F8" t="n">
-        <v>3.855405703544871</v>
+        <v>3.855405703545096</v>
       </c>
       <c r="G8" t="n">
-        <v>6.538680103942519</v>
+        <v>6.862520162716754</v>
       </c>
       <c r="H8" t="n">
-        <v>5.447119136166584</v>
+        <v>5.447119136166859</v>
       </c>
       <c r="I8" t="n">
-        <v>5.531750776918873</v>
+        <v>5.531750776919262</v>
       </c>
       <c r="J8" t="n">
-        <v>5.973141216557487</v>
+        <v>5.973141216557694</v>
       </c>
       <c r="K8" t="n">
-        <v>6.0349319954677</v>
+        <v>6.034931995468096</v>
       </c>
       <c r="L8" t="n">
-        <v>6.175078745561419</v>
+        <v>6.175078745561697</v>
       </c>
       <c r="M8" t="n">
-        <v>6.54644294743259</v>
+        <v>6.54644294743394</v>
       </c>
       <c r="N8" t="n">
-        <v>4.377244420533017</v>
+        <v>4.377244420533263</v>
       </c>
       <c r="O8" t="n">
-        <v>4.907712440312985</v>
+        <v>4.907712440313227</v>
       </c>
       <c r="P8" t="n">
-        <v>4.909895659108639</v>
+        <v>4.909895659108903</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.594295311588066</v>
+        <v>3.594295311588238</v>
       </c>
       <c r="R8" t="n">
-        <v>5.617466465169387</v>
+        <v>5.61746646516966</v>
       </c>
       <c r="S8" t="n">
-        <v>6.01405570247093</v>
+        <v>6.014055702471252</v>
       </c>
       <c r="T8" t="n">
-        <v>5.574076730158636</v>
+        <v>5.574076730158904</v>
       </c>
       <c r="U8" t="n">
-        <v>4.971160509211787</v>
+        <v>5.169898783593152</v>
       </c>
       <c r="V8" t="n">
-        <v>5.762272785991936</v>
+        <v>5.335192841598114</v>
       </c>
       <c r="W8" t="n">
-        <v>5.490710084220359</v>
+        <v>5.490710084220673</v>
       </c>
       <c r="X8" t="n">
-        <v>3.910374905414197</v>
+        <v>3.910374905414391</v>
       </c>
       <c r="Y8" t="n">
-        <v>7.175637323078005</v>
+        <v>7.17563732307837</v>
       </c>
       <c r="Z8" t="n">
-        <v>5.659090225571211</v>
+        <v>4.068324895189297</v>
       </c>
       <c r="AA8" t="n">
-        <v>5.847726634227835</v>
+        <v>5.847726634228071</v>
       </c>
       <c r="AB8" t="n">
-        <v>7.892046235994533</v>
+        <v>7.892046235994875</v>
       </c>
     </row>
     <row r="9">
@@ -1202,85 +1202,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>92.0341029283849</v>
+        <v>92.03410292838505</v>
       </c>
       <c r="C9" t="n">
-        <v>116.7884670535746</v>
+        <v>116.7884670535747</v>
       </c>
       <c r="D9" t="n">
-        <v>116.6492110360135</v>
+        <v>116.6492110360136</v>
       </c>
       <c r="E9" t="n">
-        <v>116.3084943866737</v>
+        <v>110.5383156212738</v>
       </c>
       <c r="F9" t="n">
-        <v>116.5576737143213</v>
+        <v>58.92304511401836</v>
       </c>
       <c r="G9" t="n">
-        <v>117.9224963495654</v>
+        <v>117.9224964981047</v>
       </c>
       <c r="H9" t="n">
-        <v>116.8309353817891</v>
+        <v>116.8309353817893</v>
       </c>
       <c r="I9" t="n">
-        <v>116.9155670225416</v>
+        <v>116.9155670225417</v>
       </c>
       <c r="J9" t="n">
-        <v>117.35695746218</v>
+        <v>117.3569574621801</v>
       </c>
       <c r="K9" t="n">
-        <v>117.4187482410902</v>
+        <v>117.4187482410904</v>
       </c>
       <c r="L9" t="n">
-        <v>117.5588949911841</v>
+        <v>117.5588949911842</v>
       </c>
       <c r="M9" t="n">
-        <v>117.9302591930553</v>
+        <v>117.9302591930555</v>
       </c>
       <c r="N9" t="n">
-        <v>116.9716820134016</v>
+        <v>116.9716820134017</v>
       </c>
       <c r="O9" t="n">
-        <v>125.4548315134888</v>
+        <v>125.4548315134889</v>
       </c>
       <c r="P9" t="n">
-        <v>127.3404908585073</v>
+        <v>127.3404908585075</v>
       </c>
       <c r="Q9" t="n">
-        <v>116.8467871256848</v>
+        <v>116.8467871256849</v>
       </c>
       <c r="R9" t="n">
-        <v>117.001282710792</v>
+        <v>117.0012827107921</v>
       </c>
       <c r="S9" t="n">
-        <v>117.3978719480937</v>
+        <v>117.3978719480938</v>
       </c>
       <c r="T9" t="n">
-        <v>116.9578929757813</v>
+        <v>116.9578929757815</v>
       </c>
       <c r="U9" t="n">
-        <v>117.3161941820698</v>
+        <v>117.3161941820699</v>
       </c>
       <c r="V9" t="n">
-        <v>117.1460890316148</v>
+        <v>145.9969629990862</v>
       </c>
       <c r="W9" t="n">
-        <v>116.8742194003208</v>
+        <v>116.8742194003209</v>
       </c>
       <c r="X9" t="n">
-        <v>117.0197286283445</v>
+        <v>117.0197286283446</v>
       </c>
       <c r="Y9" t="n">
-        <v>117.0069910167237</v>
+        <v>117.0069910167239</v>
       </c>
       <c r="Z9" t="n">
-        <v>117.042906471194</v>
+        <v>101.9693959416294</v>
       </c>
       <c r="AA9" t="n">
-        <v>117.2315428798505</v>
+        <v>117.2315428798506</v>
       </c>
       <c r="AB9" t="n">
-        <v>117.6444788646713</v>
+        <v>117.6444788646714</v>
       </c>
     </row>
   </sheetData>
@@ -1446,85 +1446,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.307848367242417</v>
+        <v>2.307848367242322</v>
       </c>
       <c r="C2" t="n">
-        <v>2.554679353316879</v>
+        <v>2.554679353316873</v>
       </c>
       <c r="D2" t="n">
-        <v>2.293783463129624</v>
+        <v>2.293783463129559</v>
       </c>
       <c r="E2" t="n">
-        <v>2.298033314826044</v>
+        <v>2.298033314825965</v>
       </c>
       <c r="F2" t="n">
-        <v>2.394552549301783</v>
+        <v>2.3945525493017</v>
       </c>
       <c r="G2" t="n">
-        <v>2.254200998643884</v>
+        <v>2.25420099864382</v>
       </c>
       <c r="H2" t="n">
-        <v>2.227731187305249</v>
+        <v>2.227731187305161</v>
       </c>
       <c r="I2" t="n">
-        <v>2.306763251525883</v>
+        <v>2.306763251525807</v>
       </c>
       <c r="J2" t="n">
-        <v>2.279934467001611</v>
+        <v>2.279934467001532</v>
       </c>
       <c r="K2" t="n">
-        <v>2.300011149294996</v>
+        <v>2.3000111492949</v>
       </c>
       <c r="L2" t="n">
-        <v>2.377218714525104</v>
+        <v>2.377218714525021</v>
       </c>
       <c r="M2" t="n">
-        <v>2.248865025554803</v>
+        <v>2.248865025554795</v>
       </c>
       <c r="N2" t="n">
-        <v>2.263009224009743</v>
+        <v>2.263009224009656</v>
       </c>
       <c r="O2" t="n">
-        <v>4.50619801139441</v>
+        <v>4.506198011394371</v>
       </c>
       <c r="P2" t="n">
-        <v>2.248197286957622</v>
+        <v>2.248197286957524</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.323227520757756</v>
+        <v>2.32322752075765</v>
       </c>
       <c r="R2" t="n">
-        <v>2.522422547767707</v>
+        <v>2.522422547767621</v>
       </c>
       <c r="S2" t="n">
-        <v>2.34238870729919</v>
+        <v>2.342388707299095</v>
       </c>
       <c r="T2" t="n">
-        <v>2.264780938744726</v>
+        <v>2.264780938744713</v>
       </c>
       <c r="U2" t="n">
-        <v>2.582623016918688</v>
+        <v>2.582623016918645</v>
       </c>
       <c r="V2" t="n">
-        <v>2.270309900990936</v>
+        <v>2.270309900990847</v>
       </c>
       <c r="W2" t="n">
-        <v>2.766660774158757</v>
+        <v>2.766660774158667</v>
       </c>
       <c r="X2" t="n">
-        <v>2.287647801178996</v>
+        <v>2.287647801179032</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.265268679766531</v>
+        <v>2.265268679766441</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.501993549163814</v>
+        <v>2.501993549163705</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.259399726000372</v>
+        <v>2.259399726000297</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.275294774158949</v>
+        <v>2.275294774158942</v>
       </c>
     </row>
     <row r="3">
@@ -1534,85 +1534,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.840075752134644</v>
+        <v>2.840075752134562</v>
       </c>
       <c r="C3" t="n">
-        <v>3.403873466248886</v>
+        <v>3.403873466248881</v>
       </c>
       <c r="D3" t="n">
-        <v>2.743149041402397</v>
+        <v>2.743149041402303</v>
       </c>
       <c r="E3" t="n">
-        <v>2.771244325381581</v>
+        <v>2.771244325381503</v>
       </c>
       <c r="F3" t="n">
-        <v>3.464069164008886</v>
+        <v>3.464069164008826</v>
       </c>
       <c r="G3" t="n">
-        <v>2.458723601664014</v>
+        <v>2.458723601663861</v>
       </c>
       <c r="H3" t="n">
-        <v>2.27270240198148</v>
+        <v>2.27270240198141</v>
       </c>
       <c r="I3" t="n">
-        <v>2.837353196290284</v>
+        <v>2.837353196290207</v>
       </c>
       <c r="J3" t="n">
-        <v>2.643049498955428</v>
+        <v>2.643049498955352</v>
       </c>
       <c r="K3" t="n">
-        <v>2.784924326035699</v>
+        <v>2.784924326035602</v>
       </c>
       <c r="L3" t="n">
-        <v>3.332648143861986</v>
+        <v>3.332648143861921</v>
       </c>
       <c r="M3" t="n">
-        <v>2.431543443894864</v>
+        <v>2.43154344389486</v>
       </c>
       <c r="N3" t="n">
-        <v>2.524251324320593</v>
+        <v>2.524251324320505</v>
       </c>
       <c r="O3" t="n">
-        <v>6.058970564426858</v>
+        <v>6.058970564426787</v>
       </c>
       <c r="P3" t="n">
-        <v>2.416203737245887</v>
+        <v>2.416203737245801</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.951660001118622</v>
+        <v>2.951660001118558</v>
       </c>
       <c r="R3" t="n">
-        <v>4.383311860640672</v>
+        <v>4.383311860640583</v>
       </c>
       <c r="S3" t="n">
-        <v>3.084715564500767</v>
+        <v>3.084715564500689</v>
       </c>
       <c r="T3" t="n">
-        <v>2.537387552676624</v>
+        <v>2.537387552676516</v>
       </c>
       <c r="U3" t="n">
-        <v>2.949578662005564</v>
+        <v>2.949578662005532</v>
       </c>
       <c r="V3" t="n">
-        <v>2.573140294599573</v>
+        <v>2.573140294599452</v>
       </c>
       <c r="W3" t="n">
-        <v>3.449468490331711</v>
+        <v>3.44946849033166</v>
       </c>
       <c r="X3" t="n">
-        <v>2.69885954521054</v>
+        <v>2.698859545210422</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.540131427692673</v>
+        <v>2.540131427692575</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.002998615755746</v>
+        <v>3.0029986157557</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.498096529681185</v>
+        <v>2.49809652968111</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.618026714517126</v>
+        <v>2.618026714517132</v>
       </c>
     </row>
     <row r="4">
@@ -1622,85 +1622,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.708009188137409</v>
+        <v>2.70800918813741</v>
       </c>
       <c r="C4" t="n">
-        <v>3.028797647811503</v>
+        <v>3.028797647811496</v>
       </c>
       <c r="D4" t="n">
-        <v>2.549139626008206</v>
+        <v>2.549139626008225</v>
       </c>
       <c r="E4" t="n">
-        <v>2.597143655947467</v>
+        <v>2.597143655947503</v>
       </c>
       <c r="F4" t="n">
-        <v>3.687372810392431</v>
+        <v>3.687372810392429</v>
       </c>
       <c r="G4" t="n">
-        <v>2.102037480808491</v>
+        <v>2.10203748080853</v>
       </c>
       <c r="H4" t="n">
-        <v>1.803048785023511</v>
+        <v>1.803048785023536</v>
       </c>
       <c r="I4" t="n">
-        <v>2.695752306941472</v>
+        <v>2.695752306941495</v>
       </c>
       <c r="J4" t="n">
-        <v>2.391794709641279</v>
+        <v>2.391794709641246</v>
       </c>
       <c r="K4" t="n">
-        <v>2.619484206122896</v>
+        <v>2.619484206122916</v>
       </c>
       <c r="L4" t="n">
-        <v>3.491579172631867</v>
+        <v>3.491579172631899</v>
       </c>
       <c r="M4" t="n">
-        <v>2.057313137037078</v>
+        <v>2.057313137037109</v>
       </c>
       <c r="N4" t="n">
         <v>14.02562870643044</v>
       </c>
       <c r="O4" t="n">
-        <v>1.859020189069</v>
+        <v>1.859020189068998</v>
       </c>
       <c r="P4" t="n">
-        <v>2.034222795467966</v>
+        <v>2.034222795467968</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.881723801853208</v>
+        <v>2.881723801853205</v>
       </c>
       <c r="R4" t="n">
-        <v>5.131723266170453</v>
+        <v>5.131723266170488</v>
       </c>
       <c r="S4" t="n">
-        <v>3.09815821842008</v>
+        <v>3.098158218420089</v>
       </c>
       <c r="T4" t="n">
-        <v>2.22154277126099</v>
+        <v>2.221542771260986</v>
       </c>
       <c r="U4" t="n">
         <v>2.134911290031283</v>
       </c>
       <c r="V4" t="n">
-        <v>2.278273134976614</v>
+        <v>2.278273134976631</v>
       </c>
       <c r="W4" t="n">
-        <v>2.396174939053166</v>
+        <v>2.396174939053178</v>
       </c>
       <c r="X4" t="n">
-        <v>2.479834501733019</v>
+        <v>2.479834501733058</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.366716269778106</v>
+        <v>2.366716269778104</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.384424780446737</v>
+        <v>2.384424780446765</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.160759497832669</v>
+        <v>2.16075949783269</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.348529408822686</v>
+        <v>2.348529408822724</v>
       </c>
     </row>
     <row r="5">
@@ -1710,85 +1710,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>20.80970639275008</v>
+        <v>20.80970639275012</v>
       </c>
       <c r="C5" t="n">
-        <v>27.71870002690045</v>
+        <v>27.7187000269005</v>
       </c>
       <c r="D5" t="n">
-        <v>19.79041168183053</v>
+        <v>19.79041168183058</v>
       </c>
       <c r="E5" t="n">
-        <v>19.48062988690595</v>
+        <v>19.48062988690601</v>
       </c>
       <c r="F5" t="n">
-        <v>40.81646749358931</v>
+        <v>40.81646749358928</v>
       </c>
       <c r="G5" t="n">
-        <v>10.88591008350311</v>
+        <v>10.8859100835051</v>
       </c>
       <c r="H5" t="n">
-        <v>7.098146755580862</v>
+        <v>7.098146755580877</v>
       </c>
       <c r="I5" t="n">
-        <v>23.19543155280035</v>
+        <v>23.19543155280033</v>
       </c>
       <c r="J5" t="n">
-        <v>16.37054072136615</v>
+        <v>16.37054072136498</v>
       </c>
       <c r="K5" t="n">
-        <v>19.64986392321438</v>
+        <v>19.64986392321439</v>
       </c>
       <c r="L5" t="n">
-        <v>33.35875897766007</v>
+        <v>33.35875897766006</v>
       </c>
       <c r="M5" t="n">
-        <v>11.36735991169193</v>
+        <v>11.36735991169201</v>
       </c>
       <c r="N5" t="n">
         <v>14.02562870643044</v>
       </c>
       <c r="O5" t="n">
-        <v>7.080373071453542</v>
+        <v>7.08037307145359</v>
       </c>
       <c r="P5" t="n">
-        <v>9.856952617601177</v>
+        <v>9.856952617601138</v>
       </c>
       <c r="Q5" t="n">
-        <v>24.8265816334956</v>
+        <v>24.82658163349564</v>
       </c>
       <c r="R5" t="n">
-        <v>69.79705594785342</v>
+        <v>69.79705594785347</v>
       </c>
       <c r="S5" t="n">
-        <v>26.73778226458261</v>
+        <v>26.73778226458258</v>
       </c>
       <c r="T5" t="n">
-        <v>14.6342416468918</v>
+        <v>14.63424164689182</v>
       </c>
       <c r="U5" t="n">
-        <v>9.330437797455492</v>
+        <v>9.330437797455511</v>
       </c>
       <c r="V5" t="n">
-        <v>13.81164861712615</v>
+        <v>13.81164861712621</v>
       </c>
       <c r="W5" t="n">
-        <v>17.10882626672303</v>
+        <v>17.10882626672304</v>
       </c>
       <c r="X5" t="n">
-        <v>18.30605712309002</v>
+        <v>18.30605712309004</v>
       </c>
       <c r="Y5" t="n">
-        <v>14.34966905326965</v>
+        <v>14.34966905326968</v>
       </c>
       <c r="Z5" t="n">
-        <v>14.88980297337624</v>
+        <v>14.88980297337625</v>
       </c>
       <c r="AA5" t="n">
-        <v>13.1005399111636</v>
+        <v>13.10053991116361</v>
       </c>
       <c r="AB5" t="n">
-        <v>17.4662912803968</v>
+        <v>17.46629128039693</v>
       </c>
     </row>
     <row r="6">
@@ -1798,85 +1798,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.198211036719943</v>
+        <v>3.206578516650866</v>
       </c>
       <c r="C6" t="n">
-        <v>5.518999496394063</v>
+        <v>3.527366976324979</v>
       </c>
       <c r="D6" t="n">
-        <v>5.039341474590763</v>
+        <v>5.039341474590826</v>
       </c>
       <c r="E6" t="n">
-        <v>5.087345504530061</v>
+        <v>3.095712984460957</v>
       </c>
       <c r="F6" t="n">
-        <v>6.177574658974985</v>
+        <v>4.185942138905896</v>
       </c>
       <c r="G6" t="n">
-        <v>2.600606809321953</v>
+        <v>4.592239329391088</v>
       </c>
       <c r="H6" t="n">
-        <v>2.301618113536994</v>
+        <v>4.293250633606081</v>
       </c>
       <c r="I6" t="n">
-        <v>3.194321635454939</v>
+        <v>5.185954155524098</v>
       </c>
       <c r="J6" t="n">
-        <v>2.890364038154737</v>
+        <v>4.881996558223836</v>
       </c>
       <c r="K6" t="n">
-        <v>5.109686054705479</v>
+        <v>3.11805353463638</v>
       </c>
       <c r="L6" t="n">
-        <v>3.990148501145345</v>
+        <v>5.981781021214491</v>
       </c>
       <c r="M6" t="n">
-        <v>2.555882465550557</v>
+        <v>4.547514985619708</v>
       </c>
       <c r="N6" t="n">
         <v>14.02562870643044</v>
       </c>
       <c r="O6" t="n">
-        <v>4.322865138521376</v>
+        <v>4.322865138521428</v>
       </c>
       <c r="P6" t="n">
-        <v>2.518870133026013</v>
+        <v>4.505018949460315</v>
       </c>
       <c r="Q6" t="n">
-        <v>5.371925650435749</v>
+        <v>5.371925650435809</v>
       </c>
       <c r="R6" t="n">
-        <v>5.63029259468394</v>
+        <v>7.621925114753092</v>
       </c>
       <c r="S6" t="n">
-        <v>3.596727546933548</v>
+        <v>5.588360067002681</v>
       </c>
       <c r="T6" t="n">
-        <v>4.711744619843556</v>
+        <v>2.720112099774429</v>
       </c>
       <c r="U6" t="n">
-        <v>2.493816379240036</v>
+        <v>4.485448899309147</v>
       </c>
       <c r="V6" t="n">
-        <v>2.776842463490096</v>
+        <v>4.768474983559203</v>
       </c>
       <c r="W6" t="n">
-        <v>2.921897224898933</v>
+        <v>2.921897224898943</v>
       </c>
       <c r="X6" t="n">
-        <v>2.978403830246505</v>
+        <v>2.978403830246535</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.749390911400732</v>
+        <v>2.749390911400753</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.874626629029323</v>
+        <v>2.882994108960215</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.659328826346123</v>
+        <v>2.659328826346152</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.84285775625909</v>
+        <v>2.842857756259113</v>
       </c>
     </row>
     <row r="7">
@@ -1886,85 +1886,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.418630869718393</v>
+        <v>3.418630869718406</v>
       </c>
       <c r="C7" t="n">
-        <v>3.739419329392493</v>
+        <v>3.739419329392482</v>
       </c>
       <c r="D7" t="n">
-        <v>3.259761307589191</v>
+        <v>3.259761307589216</v>
       </c>
       <c r="E7" t="n">
-        <v>3.307765337528457</v>
+        <v>3.30776533752848</v>
       </c>
       <c r="F7" t="n">
-        <v>4.397994491973407</v>
+        <v>4.397994491973426</v>
       </c>
       <c r="G7" t="n">
-        <v>2.812659162389489</v>
+        <v>2.812659162389513</v>
       </c>
       <c r="H7" t="n">
-        <v>2.513670466604502</v>
+        <v>2.51367046660452</v>
       </c>
       <c r="I7" t="n">
-        <v>3.406373988522454</v>
+        <v>3.406373988522471</v>
       </c>
       <c r="J7" t="n">
-        <v>3.102416391222232</v>
+        <v>3.102416391222223</v>
       </c>
       <c r="K7" t="n">
-        <v>3.330105887703871</v>
+        <v>3.330105887703906</v>
       </c>
       <c r="L7" t="n">
-        <v>4.202200854212846</v>
+        <v>4.202200854212873</v>
       </c>
       <c r="M7" t="n">
-        <v>2.767934818618066</v>
+        <v>2.767934818618081</v>
       </c>
       <c r="N7" t="n">
         <v>14.02562870643044</v>
       </c>
       <c r="O7" t="n">
-        <v>2.569600290850003</v>
+        <v>2.569600290850004</v>
       </c>
       <c r="P7" t="n">
-        <v>2.744802897248967</v>
+        <v>2.744802897248991</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.592345483434188</v>
+        <v>3.592345483434185</v>
       </c>
       <c r="R7" t="n">
-        <v>5.842344947751442</v>
+        <v>5.842344947751464</v>
       </c>
       <c r="S7" t="n">
-        <v>3.808779900001054</v>
+        <v>3.808779900001058</v>
       </c>
       <c r="T7" t="n">
-        <v>2.932164452841965</v>
+        <v>2.932164452841963</v>
       </c>
       <c r="U7" t="n">
-        <v>2.765918096077535</v>
+        <v>2.765918096077554</v>
       </c>
       <c r="V7" t="n">
-        <v>2.988894816557604</v>
+        <v>2.988894816557602</v>
       </c>
       <c r="W7" t="n">
-        <v>3.106796620634132</v>
+        <v>3.106796620634162</v>
       </c>
       <c r="X7" t="n">
-        <v>3.190456183314013</v>
+        <v>3.190456183314033</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.937673712054353</v>
+        <v>2.937673712054351</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.095046462027723</v>
+        <v>3.095046462027736</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.87138117941364</v>
+        <v>2.871381179413668</v>
       </c>
       <c r="AB7" t="n">
-        <v>3.059151090403649</v>
+        <v>3.059151090403704</v>
       </c>
     </row>
     <row r="8">
@@ -1974,40 +1974,40 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.046083580369942</v>
+        <v>5.046083580370013</v>
       </c>
       <c r="C8" t="n">
-        <v>6.946371672502699</v>
+        <v>6.946371672502738</v>
       </c>
       <c r="D8" t="n">
-        <v>6.466713650699356</v>
+        <v>6.466713650699464</v>
       </c>
       <c r="E8" t="n">
-        <v>6.514717680638644</v>
+        <v>5.673680719010266</v>
       </c>
       <c r="F8" t="n">
-        <v>6.271514785193069</v>
+        <v>6.271514785193078</v>
       </c>
       <c r="G8" t="n">
-        <v>6.019611505499717</v>
+        <v>6.347131043770373</v>
       </c>
       <c r="H8" t="n">
-        <v>5.720622809714665</v>
+        <v>5.720622809714735</v>
       </c>
       <c r="I8" t="n">
-        <v>6.613326331632629</v>
+        <v>6.613326331632744</v>
       </c>
       <c r="J8" t="n">
-        <v>6.309368734332445</v>
+        <v>6.30936873433247</v>
       </c>
       <c r="K8" t="n">
-        <v>6.537058230814056</v>
+        <v>6.537058230814133</v>
       </c>
       <c r="L8" t="n">
-        <v>7.40915319732304</v>
+        <v>7.409153197323098</v>
       </c>
       <c r="M8" t="n">
-        <v>5.974887161728259</v>
+        <v>5.974887161738502</v>
       </c>
       <c r="N8" t="n">
         <v>14.02562870643044</v>
@@ -2016,43 +2016,43 @@
         <v>4.888687035349935</v>
       </c>
       <c r="P8" t="n">
-        <v>4.981412890688508</v>
+        <v>4.981412890688572</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.90939046634017</v>
+        <v>4.909390466340233</v>
       </c>
       <c r="R8" t="n">
-        <v>9.049297290861631</v>
+        <v>9.04929729086172</v>
       </c>
       <c r="S8" t="n">
-        <v>7.015732243111269</v>
+        <v>7.015732243111299</v>
       </c>
       <c r="T8" t="n">
-        <v>6.139116795952141</v>
+        <v>6.139116795952217</v>
       </c>
       <c r="U8" t="n">
-        <v>4.984606864165084</v>
+        <v>5.188457391499666</v>
       </c>
       <c r="V8" t="n">
-        <v>6.195847159667753</v>
+        <v>5.815510344254115</v>
       </c>
       <c r="W8" t="n">
-        <v>6.3140593793546</v>
+        <v>6.314059379354657</v>
       </c>
       <c r="X8" t="n">
-        <v>4.652265445234296</v>
+        <v>4.652265445234332</v>
       </c>
       <c r="Y8" t="n">
-        <v>7.794752608075511</v>
+        <v>7.794752608075605</v>
       </c>
       <c r="Z8" t="n">
-        <v>6.301998805137895</v>
+        <v>4.693159156195478</v>
       </c>
       <c r="AA8" t="n">
-        <v>6.078333522523828</v>
+        <v>6.078333522523903</v>
       </c>
       <c r="AB8" t="n">
-        <v>7.916022874016958</v>
+        <v>7.916022874017031</v>
       </c>
     </row>
     <row r="9">
@@ -2062,55 +2062,55 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>81.21704201771423</v>
+        <v>81.21704201771419</v>
       </c>
       <c r="C9" t="n">
         <v>103.290778171179</v>
       </c>
       <c r="D9" t="n">
-        <v>102.8111201493757</v>
+        <v>102.8111201493758</v>
       </c>
       <c r="E9" t="n">
-        <v>102.859124179315</v>
+        <v>97.8386328836208</v>
       </c>
       <c r="F9" t="n">
-        <v>103.94935333376</v>
+        <v>53.8028714420797</v>
       </c>
       <c r="G9" t="n">
-        <v>102.3640180041761</v>
+        <v>102.3640183985786</v>
       </c>
       <c r="H9" t="n">
-        <v>102.065029308391</v>
+        <v>102.0650293083911</v>
       </c>
       <c r="I9" t="n">
-        <v>102.957732830309</v>
+        <v>102.9577328303091</v>
       </c>
       <c r="J9" t="n">
-        <v>102.653775233009</v>
+        <v>102.6537752330089</v>
       </c>
       <c r="K9" t="n">
         <v>102.8814647294904</v>
       </c>
       <c r="L9" t="n">
-        <v>103.7535596959995</v>
+        <v>103.7535596959996</v>
       </c>
       <c r="M9" t="n">
-        <v>102.3192936604046</v>
+        <v>102.3192936604047</v>
       </c>
       <c r="N9" t="n">
         <v>14.02562870643044</v>
       </c>
       <c r="O9" t="n">
-        <v>109.3298996202038</v>
+        <v>109.3298996202039</v>
       </c>
       <c r="P9" t="n">
         <v>111.0729139693947</v>
       </c>
       <c r="Q9" t="n">
-        <v>103.1437047196233</v>
+        <v>103.1437047196234</v>
       </c>
       <c r="R9" t="n">
-        <v>105.393703789538</v>
+        <v>105.3937037895381</v>
       </c>
       <c r="S9" t="n">
         <v>103.3601387417877</v>
@@ -2122,22 +2122,22 @@
         <v>102.2572275740941</v>
       </c>
       <c r="V9" t="n">
-        <v>102.5402536583442</v>
+        <v>127.6426941395065</v>
       </c>
       <c r="W9" t="n">
-        <v>102.6581554624207</v>
+        <v>102.6581554624208</v>
       </c>
       <c r="X9" t="n">
-        <v>102.7418150251006</v>
+        <v>102.7418150251007</v>
       </c>
       <c r="Y9" t="n">
-        <v>102.4890325538408</v>
+        <v>102.4890325538409</v>
       </c>
       <c r="Z9" t="n">
-        <v>102.6464053038142</v>
+        <v>89.53131234865128</v>
       </c>
       <c r="AA9" t="n">
-        <v>102.4227400212002</v>
+        <v>102.4227400212003</v>
       </c>
       <c r="AB9" t="n">
         <v>102.6105099321902</v>
@@ -2306,82 +2306,82 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.999096585379066</v>
+        <v>1.999096585379075</v>
       </c>
       <c r="C2" t="n">
         <v>2.008840796981491</v>
       </c>
       <c r="D2" t="n">
-        <v>1.986339274419447</v>
+        <v>1.986339274419458</v>
       </c>
       <c r="E2" t="n">
-        <v>1.961672893025503</v>
+        <v>1.961672893025512</v>
       </c>
       <c r="F2" t="n">
-        <v>1.957625411292003</v>
+        <v>1.957625411292011</v>
       </c>
       <c r="G2" t="n">
-        <v>2.096168730861443</v>
+        <v>2.096168730861452</v>
       </c>
       <c r="H2" t="n">
-        <v>1.970902810232908</v>
+        <v>1.970902810232917</v>
       </c>
       <c r="I2" t="n">
-        <v>2.003108992680529</v>
+        <v>2.003108992680538</v>
       </c>
       <c r="J2" t="n">
-        <v>2.042200433066078</v>
+        <v>2.042200433066091</v>
       </c>
       <c r="K2" t="n">
-        <v>2.023076269063306</v>
+        <v>2.023076269063311</v>
       </c>
       <c r="L2" t="n">
-        <v>2.050697501648335</v>
+        <v>2.050697501648349</v>
       </c>
       <c r="M2" t="n">
         <v>2.070865852341769</v>
       </c>
       <c r="N2" t="n">
-        <v>1.99594779604901</v>
+        <v>1.995947796049023</v>
       </c>
       <c r="O2" t="n">
-        <v>3.75590480552756</v>
+        <v>3.755904805527563</v>
       </c>
       <c r="P2" t="n">
-        <v>2.037005129045083</v>
+        <v>2.037005129045092</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.993749919243962</v>
+        <v>1.993749919243974</v>
       </c>
       <c r="R2" t="n">
-        <v>1.986162216183626</v>
+        <v>1.986162216183637</v>
       </c>
       <c r="S2" t="n">
-        <v>2.040890711086676</v>
+        <v>2.040890711086687</v>
       </c>
       <c r="T2" t="n">
-        <v>2.001061102959511</v>
+        <v>2.00106110295952</v>
       </c>
       <c r="U2" t="n">
-        <v>2.056691843430817</v>
+        <v>2.056691843430822</v>
       </c>
       <c r="V2" t="n">
-        <v>2.012655947935196</v>
+        <v>2.012655947935206</v>
       </c>
       <c r="W2" t="n">
-        <v>2.114730744973529</v>
+        <v>2.114730744973531</v>
       </c>
       <c r="X2" t="n">
-        <v>2.01970907781336</v>
+        <v>2.019709077813373</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.013633739532384</v>
+        <v>2.013633739532402</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.827119622688627</v>
+        <v>1.827119622688645</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.006323133118229</v>
+        <v>2.006323133118244</v>
       </c>
       <c r="AB2" t="n">
         <v>2.057320849759277</v>
@@ -2394,85 +2394,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.202703552051148</v>
+        <v>2.202703552051165</v>
       </c>
       <c r="C3" t="n">
-        <v>2.144419667839427</v>
+        <v>2.144419667839428</v>
       </c>
       <c r="D3" t="n">
-        <v>2.113239337763166</v>
+        <v>2.113239337763181</v>
       </c>
       <c r="E3" t="n">
-        <v>1.936953596641112</v>
+        <v>1.93695359664112</v>
       </c>
       <c r="F3" t="n">
-        <v>1.907791434528029</v>
+        <v>1.907791434528036</v>
       </c>
       <c r="G3" t="n">
-        <v>2.893718251393216</v>
+        <v>2.89371825139323</v>
       </c>
       <c r="H3" t="n">
-        <v>2.002953881607655</v>
+        <v>2.002953881607668</v>
       </c>
       <c r="I3" t="n">
-        <v>2.23349647187055</v>
+        <v>2.233496471870569</v>
       </c>
       <c r="J3" t="n">
-        <v>2.510390301883504</v>
+        <v>2.510390301883518</v>
       </c>
       <c r="K3" t="n">
-        <v>2.374615199295664</v>
+        <v>2.374615199295678</v>
       </c>
       <c r="L3" t="n">
-        <v>2.571888615278683</v>
+        <v>2.571888615278699</v>
       </c>
       <c r="M3" t="n">
-        <v>2.718608785663014</v>
+        <v>2.718608785663013</v>
       </c>
       <c r="N3" t="n">
-        <v>2.181601280922792</v>
+        <v>2.181601280922802</v>
       </c>
       <c r="O3" t="n">
-        <v>5.167119815284488</v>
+        <v>5.1671198152845</v>
       </c>
       <c r="P3" t="n">
-        <v>2.472564227409093</v>
+        <v>2.47256422740911</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.165955855173612</v>
+        <v>2.165955855173622</v>
       </c>
       <c r="R3" t="n">
-        <v>2.112239410752593</v>
+        <v>2.112239410752598</v>
       </c>
       <c r="S3" t="n">
-        <v>2.500485905632231</v>
+        <v>2.500485905632246</v>
       </c>
       <c r="T3" t="n">
-        <v>2.218628839372967</v>
+        <v>2.218628839372981</v>
       </c>
       <c r="U3" t="n">
-        <v>2.488025099377323</v>
+        <v>2.488025099377337</v>
       </c>
       <c r="V3" t="n">
-        <v>2.298766030225873</v>
+        <v>2.298766030225887</v>
       </c>
       <c r="W3" t="n">
         <v>2.3691630263602</v>
       </c>
       <c r="X3" t="n">
-        <v>2.351710580607235</v>
+        <v>2.351710580607251</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.307467137071223</v>
+        <v>2.307467137071235</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.991311653042742</v>
+        <v>1.991311653042754</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.255409687027311</v>
+        <v>2.255409687027313</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.621702149518893</v>
+        <v>2.62170214951889</v>
       </c>
     </row>
     <row r="4">
@@ -2482,85 +2482,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.700918874536356</v>
+        <v>1.700918874536357</v>
       </c>
       <c r="C4" t="n">
-        <v>1.547728648378505</v>
+        <v>1.5477286483785</v>
       </c>
       <c r="D4" t="n">
-        <v>1.556819178594492</v>
+        <v>1.556819178594489</v>
       </c>
       <c r="E4" t="n">
-        <v>1.278201053653859</v>
+        <v>1.278201053653858</v>
       </c>
       <c r="F4" t="n">
-        <v>1.232482885540359</v>
+        <v>1.232482885540355</v>
       </c>
       <c r="G4" t="n">
-        <v>2.797393413152936</v>
+        <v>2.797393413152931</v>
       </c>
       <c r="H4" t="n">
-        <v>1.382457214483139</v>
+        <v>1.382457214483136</v>
       </c>
       <c r="I4" t="n">
-        <v>1.74624086080493</v>
+        <v>1.746240860804919</v>
       </c>
       <c r="J4" t="n">
-        <v>2.187016021098417</v>
+        <v>2.187016021098413</v>
       </c>
       <c r="K4" t="n">
-        <v>1.971780432949394</v>
+        <v>1.971780432949382</v>
       </c>
       <c r="L4" t="n">
-        <v>2.28377496139204</v>
+        <v>2.283774961392033</v>
       </c>
       <c r="M4" t="n">
-        <v>2.511384347025883</v>
+        <v>2.511384347025868</v>
       </c>
       <c r="N4" t="n">
-        <v>1.665351850538753</v>
+        <v>1.665351850538743</v>
       </c>
       <c r="O4" t="n">
-        <v>1.835217352973163</v>
+        <v>1.835217352973159</v>
       </c>
       <c r="P4" t="n">
-        <v>2.129113314035686</v>
+        <v>2.129113314035681</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.640525820952423</v>
+        <v>1.640525820952417</v>
       </c>
       <c r="R4" t="n">
-        <v>1.554819224370077</v>
+        <v>1.554819224370078</v>
       </c>
       <c r="S4" t="n">
-        <v>2.173002750651543</v>
+        <v>2.17300275065154</v>
       </c>
       <c r="T4" t="n">
-        <v>1.723109004330238</v>
+        <v>1.723109004330226</v>
       </c>
       <c r="U4" t="n">
-        <v>2.003291633294561</v>
+        <v>2.003291633294575</v>
       </c>
       <c r="V4" t="n">
-        <v>1.849206237594638</v>
+        <v>1.849206237594639</v>
       </c>
       <c r="W4" t="n">
-        <v>1.64837637109809</v>
+        <v>1.648376371098079</v>
       </c>
       <c r="X4" t="n">
-        <v>1.933746458796723</v>
+        <v>1.933746458796722</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.776517572149513</v>
+        <v>1.776517572149517</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.850100465742666</v>
+        <v>1.850100465742663</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.782546055626463</v>
+        <v>1.782546055626461</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.355803084045807</v>
+        <v>2.355803084045788</v>
       </c>
     </row>
     <row r="5">
@@ -2570,85 +2570,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9.047489059473358</v>
+        <v>9.047489059473348</v>
       </c>
       <c r="C5" t="n">
         <v>6.884368162195812</v>
       </c>
       <c r="D5" t="n">
-        <v>7.20456174582583</v>
+        <v>7.204561745825844</v>
       </c>
       <c r="E5" t="n">
-        <v>1.802695841774857</v>
+        <v>1.802695841774885</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7852729403025289</v>
+        <v>0.7852729403025358</v>
       </c>
       <c r="G5" t="n">
-        <v>28.78176431926864</v>
+        <v>28.78176431926865</v>
       </c>
       <c r="H5" t="n">
-        <v>3.843984129057462</v>
+        <v>3.843984129057473</v>
       </c>
       <c r="I5" t="n">
-        <v>11.1035910271547</v>
+        <v>11.10359102715468</v>
       </c>
       <c r="J5" t="n">
-        <v>18.28171181472402</v>
+        <v>18.28171181472407</v>
       </c>
       <c r="K5" t="n">
-        <v>14.59573222793544</v>
+        <v>14.59573222793547</v>
       </c>
       <c r="L5" t="n">
-        <v>20.57236812780998</v>
+        <v>20.57236812781001</v>
       </c>
       <c r="M5" t="n">
-        <v>26.48163956646715</v>
+        <v>26.4816395664672</v>
       </c>
       <c r="N5" t="n">
-        <v>16.22262830283649</v>
+        <v>16.22262830283648</v>
       </c>
       <c r="O5" t="n">
-        <v>11.17077979600106</v>
+        <v>11.17077979600105</v>
       </c>
       <c r="P5" t="n">
-        <v>16.75750611998512</v>
+        <v>16.75750611998516</v>
       </c>
       <c r="Q5" t="n">
-        <v>8.690717491211183</v>
+        <v>8.69071749121119</v>
       </c>
       <c r="R5" t="n">
-        <v>7.313429981722988</v>
+        <v>7.313429981723006</v>
       </c>
       <c r="S5" t="n">
-        <v>17.69307986878515</v>
+        <v>17.69307986878521</v>
       </c>
       <c r="T5" t="n">
-        <v>10.52620950991221</v>
+        <v>10.52620950991219</v>
       </c>
       <c r="U5" t="n">
-        <v>16.64917323156225</v>
+        <v>16.64917323156224</v>
       </c>
       <c r="V5" t="n">
-        <v>11.54290832836475</v>
+        <v>11.54290832836468</v>
       </c>
       <c r="W5" t="n">
-        <v>8.668441599324874</v>
+        <v>8.668441599324863</v>
       </c>
       <c r="X5" t="n">
-        <v>14.50348047049756</v>
+        <v>14.50348047049761</v>
       </c>
       <c r="Y5" t="n">
-        <v>12.71461587320643</v>
+        <v>12.71461587320647</v>
       </c>
       <c r="Z5" t="n">
-        <v>11.88373106622562</v>
+        <v>11.88373106622561</v>
       </c>
       <c r="AA5" t="n">
-        <v>11.21928638283624</v>
+        <v>11.21928638283628</v>
       </c>
       <c r="AB5" t="n">
-        <v>24.18994647862616</v>
+        <v>24.18994647862608</v>
       </c>
     </row>
     <row r="6">
@@ -2658,85 +2658,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.938003047020432</v>
+        <v>2.017416058102059</v>
       </c>
       <c r="C6" t="n">
-        <v>3.784812820862582</v>
+        <v>3.784812820862591</v>
       </c>
       <c r="D6" t="n">
-        <v>1.873316362160197</v>
+        <v>3.793903351078572</v>
       </c>
       <c r="E6" t="n">
-        <v>1.59469823721956</v>
+        <v>1.594698237219558</v>
       </c>
       <c r="F6" t="n">
-        <v>3.469567058024436</v>
+        <v>1.548980069106059</v>
       </c>
       <c r="G6" t="n">
-        <v>5.034477585637009</v>
+        <v>3.113890596718635</v>
       </c>
       <c r="H6" t="n">
-        <v>1.698954398048843</v>
+        <v>3.61954138696722</v>
       </c>
       <c r="I6" t="n">
-        <v>2.062738044370633</v>
+        <v>2.062738044370634</v>
       </c>
       <c r="J6" t="n">
-        <v>4.424100193582492</v>
+        <v>4.424100193582493</v>
       </c>
       <c r="K6" t="n">
-        <v>2.288277616515094</v>
+        <v>4.208864605433466</v>
       </c>
       <c r="L6" t="n">
-        <v>2.600272144957741</v>
+        <v>2.600272144957747</v>
       </c>
       <c r="M6" t="n">
-        <v>2.82788153059158</v>
+        <v>2.827881530591577</v>
       </c>
       <c r="N6" t="n">
-        <v>1.985103502242789</v>
+        <v>1.985103502242803</v>
       </c>
       <c r="O6" t="n">
-        <v>4.13214611939566</v>
+        <v>4.132146119395667</v>
       </c>
       <c r="P6" t="n">
-        <v>4.426817922457597</v>
+        <v>4.426817922457612</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.957023004518128</v>
+        <v>3.877609993436504</v>
       </c>
       <c r="R6" t="n">
-        <v>1.87131640793578</v>
+        <v>3.791903396854152</v>
       </c>
       <c r="S6" t="n">
-        <v>2.489499934217248</v>
+        <v>4.410086923135627</v>
       </c>
       <c r="T6" t="n">
-        <v>3.960193176814312</v>
+        <v>2.039606187895941</v>
       </c>
       <c r="U6" t="n">
-        <v>4.328980951748585</v>
+        <v>2.408393962830214</v>
       </c>
       <c r="V6" t="n">
-        <v>4.086290410078714</v>
+        <v>4.086290410078724</v>
       </c>
       <c r="W6" t="n">
-        <v>3.945073911325967</v>
+        <v>3.945073911325971</v>
       </c>
       <c r="X6" t="n">
-        <v>2.250243642362429</v>
+        <v>4.170830631280806</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.200039204182681</v>
+        <v>2.200039204182686</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.166597649308371</v>
+        <v>4.087184638226747</v>
       </c>
       <c r="AA6" t="n">
-        <v>4.01963022811054</v>
+        <v>2.099043239192164</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.678753334601908</v>
+        <v>2.678753334601905</v>
       </c>
     </row>
     <row r="7">
@@ -2746,82 +2746,82 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.345207326105559</v>
+        <v>2.345207326105553</v>
       </c>
       <c r="C7" t="n">
-        <v>2.19201709994771</v>
+        <v>2.192017099947712</v>
       </c>
       <c r="D7" t="n">
         <v>2.201107630163698</v>
       </c>
       <c r="E7" t="n">
-        <v>1.92248950522306</v>
+        <v>1.922489505223061</v>
       </c>
       <c r="F7" t="n">
         <v>1.87677133710956</v>
       </c>
       <c r="G7" t="n">
-        <v>3.441681864722137</v>
+        <v>3.441681864722132</v>
       </c>
       <c r="H7" t="n">
         <v>2.026745666052346</v>
       </c>
       <c r="I7" t="n">
-        <v>2.390529312374132</v>
+        <v>2.390529312374133</v>
       </c>
       <c r="J7" t="n">
-        <v>2.83130447266762</v>
+        <v>2.831304472667616</v>
       </c>
       <c r="K7" t="n">
-        <v>2.616068884518595</v>
+        <v>2.616068884518598</v>
       </c>
       <c r="L7" t="n">
-        <v>2.928063412961244</v>
+        <v>2.928063412961241</v>
       </c>
       <c r="M7" t="n">
         <v>3.155672798595083</v>
       </c>
       <c r="N7" t="n">
-        <v>2.309640302107953</v>
+        <v>2.309640302107954</v>
       </c>
       <c r="O7" t="n">
-        <v>2.47949951513559</v>
+        <v>2.479499515135591</v>
       </c>
       <c r="P7" t="n">
-        <v>2.773395476198115</v>
+        <v>2.773395476198113</v>
       </c>
       <c r="Q7" t="n">
         <v>2.284814272521625</v>
       </c>
       <c r="R7" t="n">
-        <v>2.199107675939284</v>
+        <v>2.199107675939286</v>
       </c>
       <c r="S7" t="n">
-        <v>2.817291202220745</v>
+        <v>2.817291202220751</v>
       </c>
       <c r="T7" t="n">
-        <v>2.36739745589944</v>
+        <v>2.367397455899441</v>
       </c>
       <c r="U7" t="n">
-        <v>2.738401878176751</v>
+        <v>2.738401878176755</v>
       </c>
       <c r="V7" t="n">
-        <v>2.493494689163842</v>
+        <v>2.493494689163838</v>
       </c>
       <c r="W7" t="n">
-        <v>2.292664822667288</v>
+        <v>2.292664822667294</v>
       </c>
       <c r="X7" t="n">
         <v>2.57803491036593</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.509411169688666</v>
+        <v>2.509411169688667</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.494388917311871</v>
+        <v>2.494388917311868</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.426834507195664</v>
+        <v>2.42683450719566</v>
       </c>
       <c r="AB7" t="n">
         <v>3.000091535615006</v>
@@ -2834,85 +2834,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.989225813858658</v>
+        <v>3.989225813858649</v>
       </c>
       <c r="C8" t="n">
-        <v>5.344366666079483</v>
+        <v>5.344366666079473</v>
       </c>
       <c r="D8" t="n">
-        <v>5.35345719629546</v>
+        <v>5.35345719629548</v>
       </c>
       <c r="E8" t="n">
-        <v>5.074839071354829</v>
+        <v>4.27169726511648</v>
       </c>
       <c r="F8" t="n">
-        <v>3.755770178598596</v>
+        <v>3.755770178598592</v>
       </c>
       <c r="G8" t="n">
-        <v>6.594031430853904</v>
+        <v>6.906793705866869</v>
       </c>
       <c r="H8" t="n">
         <v>5.179095232184113</v>
       </c>
       <c r="I8" t="n">
-        <v>5.542878878505899</v>
+        <v>5.542878878505909</v>
       </c>
       <c r="J8" t="n">
-        <v>5.983654038799387</v>
+        <v>5.983654038799378</v>
       </c>
       <c r="K8" t="n">
-        <v>5.768418450650363</v>
+        <v>5.768418450650359</v>
       </c>
       <c r="L8" t="n">
-        <v>6.080412979093008</v>
+        <v>6.080412979093009</v>
       </c>
       <c r="M8" t="n">
-        <v>6.30802236472685</v>
+        <v>6.308022364729106</v>
       </c>
       <c r="N8" t="n">
-        <v>4.292780944173394</v>
+        <v>4.29278094417338</v>
       </c>
       <c r="O8" t="n">
-        <v>4.783955210958116</v>
+        <v>4.783955210958117</v>
       </c>
       <c r="P8" t="n">
-        <v>4.999090629978824</v>
+        <v>4.999090629978817</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.632411277383246</v>
+        <v>3.632411277383237</v>
       </c>
       <c r="R8" t="n">
-        <v>5.351457242071056</v>
+        <v>5.351457242071043</v>
       </c>
       <c r="S8" t="n">
-        <v>5.969640768352514</v>
+        <v>5.969640768352528</v>
       </c>
       <c r="T8" t="n">
-        <v>5.519747022031211</v>
+        <v>5.519747022031202</v>
       </c>
       <c r="U8" t="n">
-        <v>4.962003997478962</v>
+        <v>5.154061250422773</v>
       </c>
       <c r="V8" t="n">
-        <v>5.645844255295623</v>
+        <v>5.23549473993549</v>
       </c>
       <c r="W8" t="n">
-        <v>5.445310818965614</v>
+        <v>5.445310818965615</v>
       </c>
       <c r="X8" t="n">
-        <v>4.063873455612006</v>
+        <v>4.063873455612005</v>
       </c>
       <c r="Y8" t="n">
-        <v>7.164407070347272</v>
+        <v>7.164407070347317</v>
       </c>
       <c r="Z8" t="n">
-        <v>5.64673848344364</v>
+        <v>4.110389380881022</v>
       </c>
       <c r="AA8" t="n">
-        <v>5.579184073327437</v>
+        <v>5.579184073327419</v>
       </c>
       <c r="AB8" t="n">
-        <v>7.728019037664817</v>
+        <v>7.728019037664797</v>
       </c>
     </row>
     <row r="9">
@@ -2931,13 +2931,13 @@
         <v>109.3664285774787</v>
       </c>
       <c r="E9" t="n">
-        <v>109.087810452538</v>
+        <v>103.6930494251431</v>
       </c>
       <c r="F9" t="n">
-        <v>109.0420922844245</v>
+        <v>55.15727058708097</v>
       </c>
       <c r="G9" t="n">
-        <v>110.6070028120369</v>
+        <v>110.6070030614712</v>
       </c>
       <c r="H9" t="n">
         <v>109.1920666133672</v>
@@ -2955,7 +2955,7 @@
         <v>110.0933843602761</v>
       </c>
       <c r="M9" t="n">
-        <v>110.32099374591</v>
+        <v>110.3209937459101</v>
       </c>
       <c r="N9" t="n">
         <v>109.4749612494228</v>
@@ -2964,10 +2964,10 @@
         <v>117.391137312929</v>
       </c>
       <c r="P9" t="n">
-        <v>119.3697228624747</v>
+        <v>119.3697228624748</v>
       </c>
       <c r="Q9" t="n">
-        <v>109.4501354692709</v>
+        <v>109.4501354692708</v>
       </c>
       <c r="R9" t="n">
         <v>109.3644286232544</v>
@@ -2979,13 +2979,13 @@
         <v>109.5327184032144</v>
       </c>
       <c r="U9" t="n">
-        <v>109.9015061781486</v>
+        <v>109.9015061781487</v>
       </c>
       <c r="V9" t="n">
-        <v>109.6588156364788</v>
+        <v>136.63260279255</v>
       </c>
       <c r="W9" t="n">
-        <v>109.4579857699821</v>
+        <v>109.4579857699822</v>
       </c>
       <c r="X9" t="n">
         <v>109.7433558576806</v>
@@ -2994,7 +2994,7 @@
         <v>109.6747321170036</v>
       </c>
       <c r="Z9" t="n">
-        <v>109.659709864627</v>
+        <v>95.56690763342043</v>
       </c>
       <c r="AA9" t="n">
         <v>109.5921554545106</v>
@@ -3166,10 +3166,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.046799980738987</v>
+        <v>2.046799980738992</v>
       </c>
       <c r="C2" t="n">
-        <v>2.0682493268491</v>
+        <v>2.068249326849102</v>
       </c>
       <c r="D2" t="n">
         <v>2.045267579821104</v>
@@ -3181,70 +3181,70 @@
         <v>2.028434343294394</v>
       </c>
       <c r="G2" t="n">
-        <v>2.140336513931363</v>
+        <v>2.140336513931357</v>
       </c>
       <c r="H2" t="n">
-        <v>2.011245868267694</v>
+        <v>2.011245868267692</v>
       </c>
       <c r="I2" t="n">
-        <v>2.157781969373596</v>
+        <v>2.157781969373599</v>
       </c>
       <c r="J2" t="n">
         <v>2.091247051398959</v>
       </c>
       <c r="K2" t="n">
-        <v>2.077122383170597</v>
+        <v>2.077122383170598</v>
       </c>
       <c r="L2" t="n">
-        <v>2.084363719600353</v>
+        <v>2.084363719600352</v>
       </c>
       <c r="M2" t="n">
-        <v>2.110032066780836</v>
+        <v>2.110032066780837</v>
       </c>
       <c r="N2" t="n">
         <v>2.047670710887969</v>
       </c>
       <c r="O2" t="n">
-        <v>3.871771922435455</v>
+        <v>3.871771922435446</v>
       </c>
       <c r="P2" t="n">
-        <v>2.081929928973144</v>
+        <v>2.081929928973148</v>
       </c>
       <c r="Q2" t="n">
         <v>2.11692904109167</v>
       </c>
       <c r="R2" t="n">
-        <v>2.021194895179046</v>
+        <v>2.021194895179045</v>
       </c>
       <c r="S2" t="n">
-        <v>2.083691300841075</v>
+        <v>2.083691300841076</v>
       </c>
       <c r="T2" t="n">
-        <v>2.037782560622875</v>
+        <v>2.037782560622874</v>
       </c>
       <c r="U2" t="n">
-        <v>2.168947939094571</v>
+        <v>2.168947939094566</v>
       </c>
       <c r="V2" t="n">
         <v>2.052835149438754</v>
       </c>
       <c r="W2" t="n">
-        <v>2.237926157616337</v>
+        <v>2.237926157616331</v>
       </c>
       <c r="X2" t="n">
         <v>2.071369374808068</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.084174001408035</v>
+        <v>2.084174001408037</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.983120697473833</v>
+        <v>1.983120697473826</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.050474799098771</v>
+        <v>2.050474799098772</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.09544096491658</v>
+        <v>2.095440964916582</v>
       </c>
     </row>
     <row r="3">
@@ -3254,85 +3254,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.257006270612901</v>
+        <v>2.257006270612895</v>
       </c>
       <c r="C3" t="n">
-        <v>2.243500650343096</v>
+        <v>2.243500650343102</v>
       </c>
       <c r="D3" t="n">
-        <v>2.247811615607801</v>
+        <v>2.2478116156078</v>
       </c>
       <c r="E3" t="n">
-        <v>2.11992339057162</v>
+        <v>2.119923390571614</v>
       </c>
       <c r="F3" t="n">
-        <v>2.127434808290242</v>
+        <v>2.127434808290241</v>
       </c>
       <c r="G3" t="n">
-        <v>2.921955389115569</v>
+        <v>2.92195538911557</v>
       </c>
       <c r="H3" t="n">
-        <v>2.004539434429329</v>
+        <v>2.004539434429335</v>
       </c>
       <c r="I3" t="n">
-        <v>3.053886129871661</v>
+        <v>3.053886129871662</v>
       </c>
       <c r="J3" t="n">
-        <v>2.573964245778038</v>
+        <v>2.573964245778047</v>
       </c>
       <c r="K3" t="n">
-        <v>2.472931121557985</v>
+        <v>2.472931121557983</v>
       </c>
       <c r="L3" t="n">
-        <v>2.525818904896605</v>
+        <v>2.525818904896608</v>
       </c>
       <c r="M3" t="n">
-        <v>2.713848636470484</v>
+        <v>2.713848636470486</v>
       </c>
       <c r="N3" t="n">
-        <v>2.264633570692937</v>
+        <v>2.264633570692933</v>
       </c>
       <c r="O3" t="n">
-        <v>5.294779005115539</v>
+        <v>5.294779005115553</v>
       </c>
       <c r="P3" t="n">
         <v>2.506627045927116</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.758791251097808</v>
+        <v>2.75879125109781</v>
       </c>
       <c r="R3" t="n">
-        <v>2.075783777872524</v>
+        <v>2.075783777872522</v>
       </c>
       <c r="S3" t="n">
-        <v>2.519509705144165</v>
+        <v>2.519509705144169</v>
       </c>
       <c r="T3" t="n">
-        <v>2.194374275819727</v>
+        <v>2.194374275819729</v>
       </c>
       <c r="U3" t="n">
-        <v>2.624834564615992</v>
+        <v>2.624834564616</v>
       </c>
       <c r="V3" t="n">
-        <v>2.29924346335826</v>
+        <v>2.299243463358262</v>
       </c>
       <c r="W3" t="n">
         <v>2.540470177505335</v>
       </c>
       <c r="X3" t="n">
-        <v>2.434190551100599</v>
+        <v>2.434190551100597</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.524701832070637</v>
+        <v>2.524701832070638</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.288416511148653</v>
+        <v>2.28841651114865</v>
       </c>
       <c r="AA3" t="n">
         <v>2.28433829873428</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.609634218426882</v>
+        <v>2.609634218426885</v>
       </c>
     </row>
     <row r="4">
@@ -3342,85 +3342,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.815362231803751</v>
+        <v>1.815362231803763</v>
       </c>
       <c r="C4" t="n">
-        <v>1.715034444698311</v>
+        <v>1.715034444698307</v>
       </c>
       <c r="D4" t="n">
-        <v>1.798053058496977</v>
+        <v>1.798053058496981</v>
       </c>
       <c r="E4" t="n">
-        <v>1.596440825575594</v>
+        <v>1.596440825575606</v>
       </c>
       <c r="F4" t="n">
-        <v>1.60791390825641</v>
+        <v>1.607913908256417</v>
       </c>
       <c r="G4" t="n">
-        <v>2.871900403142695</v>
+        <v>2.871900403142699</v>
       </c>
       <c r="H4" t="n">
-        <v>1.413762175740628</v>
+        <v>1.413762175740636</v>
       </c>
       <c r="I4" t="n">
-        <v>3.068954847668784</v>
+        <v>3.068954847668783</v>
       </c>
       <c r="J4" t="n">
-        <v>2.31647041205368</v>
+        <v>2.31647041205369</v>
       </c>
       <c r="K4" t="n">
-        <v>2.15786771626302</v>
+        <v>2.157867716263031</v>
       </c>
       <c r="L4" t="n">
-        <v>2.239661942416432</v>
+        <v>2.239661942416443</v>
       </c>
       <c r="M4" t="n">
-        <v>2.532990016360877</v>
+        <v>2.532990016360884</v>
       </c>
       <c r="N4" t="n">
-        <v>1.825197529392121</v>
+        <v>1.825197529392126</v>
       </c>
       <c r="O4" t="n">
-        <v>1.86920979225468</v>
+        <v>1.869209792254689</v>
       </c>
       <c r="P4" t="n">
-        <v>2.212171157683151</v>
+        <v>2.212171157683164</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.607502229448908</v>
+        <v>2.607502229448917</v>
       </c>
       <c r="R4" t="n">
-        <v>1.526141011482852</v>
+        <v>1.526141011482865</v>
       </c>
       <c r="S4" t="n">
-        <v>2.232066663202517</v>
+        <v>2.232066663202506</v>
       </c>
       <c r="T4" t="n">
-        <v>1.71350632337402</v>
+        <v>1.713506323374024</v>
       </c>
       <c r="U4" t="n">
-        <v>2.085645805540183</v>
+        <v>2.085645805540191</v>
       </c>
       <c r="V4" t="n">
-        <v>1.877511749281752</v>
+        <v>1.877511749281793</v>
       </c>
       <c r="W4" t="n">
-        <v>1.747266740160288</v>
+        <v>1.747266740160285</v>
       </c>
       <c r="X4" t="n">
-        <v>2.092884840293657</v>
+        <v>2.092884840293662</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.165615998654704</v>
+        <v>2.165615998654722</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.09995627246044</v>
+        <v>2.099956272460437</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.856870995677468</v>
+        <v>1.856870995677472</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.36595170968816</v>
+        <v>2.365951709688169</v>
       </c>
     </row>
     <row r="5">
@@ -3430,85 +3430,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9.534956124400773</v>
+        <v>9.534956124400823</v>
       </c>
       <c r="C5" t="n">
-        <v>8.288810327243031</v>
+        <v>8.288810327243043</v>
       </c>
       <c r="D5" t="n">
-        <v>10.13164862927882</v>
+        <v>10.13164862927886</v>
       </c>
       <c r="E5" t="n">
-        <v>6.307056180006184</v>
+        <v>6.307056180006204</v>
       </c>
       <c r="F5" t="n">
-        <v>6.645822327096748</v>
+        <v>6.645822327096763</v>
       </c>
       <c r="G5" t="n">
-        <v>26.86083214641676</v>
+        <v>26.86083214641671</v>
       </c>
       <c r="H5" t="n">
-        <v>3.097727018411126</v>
+        <v>3.09772701841114</v>
       </c>
       <c r="I5" t="n">
-        <v>34.19215023320774</v>
+        <v>34.19215023320779</v>
       </c>
       <c r="J5" t="n">
-        <v>18.27731408309753</v>
+        <v>18.27731408309756</v>
       </c>
       <c r="K5" t="n">
-        <v>15.34002016905386</v>
+        <v>15.34002016905388</v>
       </c>
       <c r="L5" t="n">
-        <v>17.41166719098763</v>
+        <v>17.41166719098765</v>
       </c>
       <c r="M5" t="n">
-        <v>24.14933756739238</v>
+        <v>24.1493375673924</v>
       </c>
       <c r="N5" t="n">
-        <v>15.26894467243491</v>
+        <v>15.26894467243501</v>
       </c>
       <c r="O5" t="n">
-        <v>10.05613232749951</v>
+        <v>10.05613232749954</v>
       </c>
       <c r="P5" t="n">
-        <v>15.98135908947318</v>
+        <v>15.9813590894733</v>
       </c>
       <c r="Q5" t="n">
-        <v>24.20360173434295</v>
+        <v>24.20360173434301</v>
       </c>
       <c r="R5" t="n">
-        <v>5.208484323637483</v>
+        <v>5.208484323637502</v>
       </c>
       <c r="S5" t="n">
-        <v>16.49475403885685</v>
+        <v>16.49475403885689</v>
       </c>
       <c r="T5" t="n">
-        <v>8.627809187194583</v>
+        <v>8.627809187194627</v>
       </c>
       <c r="U5" t="n">
-        <v>15.6012959380878</v>
+        <v>15.60129593808792</v>
       </c>
       <c r="V5" t="n">
-        <v>10.30134335730283</v>
+        <v>10.30134335730254</v>
       </c>
       <c r="W5" t="n">
-        <v>8.874772306829808</v>
+        <v>8.874772306829824</v>
       </c>
       <c r="X5" t="n">
-        <v>15.39242117002671</v>
+        <v>15.39242117002679</v>
       </c>
       <c r="Y5" t="n">
-        <v>17.49656162930996</v>
+        <v>17.49656162931004</v>
       </c>
       <c r="Z5" t="n">
-        <v>13.68394055998397</v>
+        <v>13.68394055998398</v>
       </c>
       <c r="AA5" t="n">
         <v>10.84157244110034</v>
       </c>
       <c r="AB5" t="n">
-        <v>21.78159088675732</v>
+        <v>21.78159088675729</v>
       </c>
     </row>
     <row r="6">
@@ -3518,85 +3518,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.941277156011449</v>
+        <v>2.121976841278748</v>
       </c>
       <c r="C6" t="n">
-        <v>2.021649054173287</v>
+        <v>2.021649054173299</v>
       </c>
       <c r="D6" t="n">
-        <v>3.923967982704668</v>
+        <v>3.923967982704671</v>
       </c>
       <c r="E6" t="n">
-        <v>1.903055435050581</v>
+        <v>1.903055435050593</v>
       </c>
       <c r="F6" t="n">
-        <v>1.914528517731392</v>
+        <v>3.733828832464106</v>
       </c>
       <c r="G6" t="n">
-        <v>4.997815327350386</v>
+        <v>3.178515012617683</v>
       </c>
       <c r="H6" t="n">
-        <v>1.720376785215616</v>
+        <v>1.720376785215622</v>
       </c>
       <c r="I6" t="n">
-        <v>5.194869771876471</v>
+        <v>3.37556945714377</v>
       </c>
       <c r="J6" t="n">
-        <v>4.442385336261369</v>
+        <v>4.442385336261378</v>
       </c>
       <c r="K6" t="n">
-        <v>2.464482325738004</v>
+        <v>4.283782640470716</v>
       </c>
       <c r="L6" t="n">
-        <v>4.365576866624136</v>
+        <v>2.54627655189143</v>
       </c>
       <c r="M6" t="n">
-        <v>4.658904940568576</v>
+        <v>4.658904940568574</v>
       </c>
       <c r="N6" t="n">
-        <v>2.133625724203848</v>
+        <v>2.133625724203851</v>
       </c>
       <c r="O6" t="n">
-        <v>4.042971182599512</v>
+        <v>2.177637987066414</v>
       </c>
       <c r="P6" t="n">
-        <v>4.387443941956702</v>
+        <v>4.387443941956726</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.733417153656595</v>
+        <v>4.733417153656603</v>
       </c>
       <c r="R6" t="n">
-        <v>3.652055935690559</v>
+        <v>3.652055935690549</v>
       </c>
       <c r="S6" t="n">
-        <v>2.538681272677481</v>
+        <v>2.538681272677494</v>
       </c>
       <c r="T6" t="n">
-        <v>2.020120932848993</v>
+        <v>2.020120932849008</v>
       </c>
       <c r="U6" t="n">
-        <v>4.28346371925272</v>
+        <v>2.464163404520022</v>
       </c>
       <c r="V6" t="n">
-        <v>4.003426673489432</v>
+        <v>4.003426673489477</v>
       </c>
       <c r="W6" t="n">
-        <v>3.920750541184107</v>
+        <v>2.07358104874517</v>
       </c>
       <c r="X6" t="n">
-        <v>2.399499449768646</v>
+        <v>2.39949944976865</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.561383095270978</v>
+        <v>2.56138309527098</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.225871196668135</v>
+        <v>2.406570881935423</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.163485605152457</v>
+        <v>3.982785919885159</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.676886256783656</v>
+        <v>2.676886256783663</v>
       </c>
     </row>
     <row r="7">
@@ -3606,85 +3606,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.438494590324905</v>
+        <v>2.438494590324903</v>
       </c>
       <c r="C7" t="n">
-        <v>2.338166803219443</v>
+        <v>2.338166803219453</v>
       </c>
       <c r="D7" t="n">
-        <v>2.421185417018118</v>
+        <v>2.421185417018126</v>
       </c>
       <c r="E7" t="n">
-        <v>2.219573184096736</v>
+        <v>2.219573184096744</v>
       </c>
       <c r="F7" t="n">
-        <v>2.23104626677755</v>
+        <v>2.231046266777556</v>
       </c>
       <c r="G7" t="n">
-        <v>3.495032761663823</v>
+        <v>3.495032761663838</v>
       </c>
       <c r="H7" t="n">
-        <v>2.036894534261759</v>
+        <v>2.036894534261774</v>
       </c>
       <c r="I7" t="n">
-        <v>3.692087206189919</v>
+        <v>3.692087206189922</v>
       </c>
       <c r="J7" t="n">
-        <v>2.939602770574838</v>
+        <v>2.939602770574826</v>
       </c>
       <c r="K7" t="n">
-        <v>2.781000074784164</v>
+        <v>2.781000074784171</v>
       </c>
       <c r="L7" t="n">
-        <v>2.862794300937578</v>
+        <v>2.862794300937582</v>
       </c>
       <c r="M7" t="n">
-        <v>3.156122374882024</v>
+        <v>3.156122374882027</v>
       </c>
       <c r="N7" t="n">
-        <v>2.448329887913264</v>
+        <v>2.448329887913266</v>
       </c>
       <c r="O7" t="n">
-        <v>2.492319823220186</v>
+        <v>2.492319823220202</v>
       </c>
       <c r="P7" t="n">
-        <v>2.835281188648661</v>
+        <v>2.835281188648675</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.230634587970045</v>
+        <v>3.230634587970055</v>
       </c>
       <c r="R7" t="n">
-        <v>2.149273370004002</v>
+        <v>2.149273370004006</v>
       </c>
       <c r="S7" t="n">
-        <v>2.855199021723634</v>
+        <v>2.855199021723646</v>
       </c>
       <c r="T7" t="n">
-        <v>2.336638681895145</v>
+        <v>2.336638681895161</v>
       </c>
       <c r="U7" t="n">
-        <v>2.810501587336667</v>
+        <v>2.810501587336676</v>
       </c>
       <c r="V7" t="n">
-        <v>2.500644107802942</v>
+        <v>2.500644107802929</v>
       </c>
       <c r="W7" t="n">
-        <v>2.370399098681424</v>
+        <v>2.370399098681429</v>
       </c>
       <c r="X7" t="n">
-        <v>2.716017198814798</v>
+        <v>2.716017198814801</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.860651346680699</v>
+        <v>2.860651346680707</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.723088630981574</v>
+        <v>2.723088630981579</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.48000335419861</v>
+        <v>2.480003354198612</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.989084068209293</v>
+        <v>2.989084068209308</v>
       </c>
     </row>
     <row r="8">
@@ -3694,85 +3694,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.969727068590263</v>
+        <v>3.969727068590255</v>
       </c>
       <c r="C8" t="n">
-        <v>5.293310860092328</v>
+        <v>5.293310860092344</v>
       </c>
       <c r="D8" t="n">
-        <v>5.376329473891013</v>
+        <v>5.376329473891009</v>
       </c>
       <c r="E8" t="n">
-        <v>5.174717240969624</v>
+        <v>4.41652632816898</v>
       </c>
       <c r="F8" t="n">
-        <v>3.984107527338615</v>
+        <v>3.984107527338617</v>
       </c>
       <c r="G8" t="n">
-        <v>6.450176818536704</v>
+        <v>6.745434160318908</v>
       </c>
       <c r="H8" t="n">
-        <v>4.992038591134654</v>
+        <v>4.992038591134665</v>
       </c>
       <c r="I8" t="n">
-        <v>6.647231263062817</v>
+        <v>6.647231263062812</v>
       </c>
       <c r="J8" t="n">
-        <v>5.89474682744769</v>
+        <v>5.894746827447722</v>
       </c>
       <c r="K8" t="n">
-        <v>5.736144131657056</v>
+        <v>5.736144131657068</v>
       </c>
       <c r="L8" t="n">
-        <v>5.817938357810462</v>
+        <v>5.817938357810476</v>
       </c>
       <c r="M8" t="n">
-        <v>6.111266431754908</v>
+        <v>6.111266431756888</v>
       </c>
       <c r="N8" t="n">
-        <v>4.299704256093059</v>
+        <v>4.29970425609308</v>
       </c>
       <c r="O8" t="n">
-        <v>4.647042013174127</v>
+        <v>4.647042013174133</v>
       </c>
       <c r="P8" t="n">
-        <v>4.915650970620541</v>
+        <v>4.915650970620572</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.482035941872438</v>
+        <v>4.482035941872446</v>
       </c>
       <c r="R8" t="n">
-        <v>5.104417426876881</v>
+        <v>5.104417426876893</v>
       </c>
       <c r="S8" t="n">
-        <v>5.810343078596519</v>
+        <v>5.810343078596544</v>
       </c>
       <c r="T8" t="n">
-        <v>5.291782738768029</v>
+        <v>5.291782738768056</v>
       </c>
       <c r="U8" t="n">
-        <v>4.881340465358252</v>
+        <v>5.063960380966261</v>
       </c>
       <c r="V8" t="n">
-        <v>5.455788164675783</v>
+        <v>5.092120513697576</v>
       </c>
       <c r="W8" t="n">
-        <v>5.325822994771535</v>
+        <v>5.325822994771547</v>
       </c>
       <c r="X8" t="n">
-        <v>4.097922878131308</v>
+        <v>4.097922878131314</v>
       </c>
       <c r="Y8" t="n">
-        <v>7.271122541125486</v>
+        <v>7.271122541125506</v>
       </c>
       <c r="Z8" t="n">
-        <v>5.678232687854472</v>
+        <v>4.227871220626502</v>
       </c>
       <c r="AA8" t="n">
-        <v>5.435147411071512</v>
+        <v>5.435147411071515</v>
       </c>
       <c r="AB8" t="n">
-        <v>7.431622834343063</v>
+        <v>7.431622834343067</v>
       </c>
     </row>
     <row r="9">
@@ -3791,13 +3791,13 @@
         <v>102.1762719965961</v>
       </c>
       <c r="E9" t="n">
-        <v>101.9746597636747</v>
+        <v>96.95141452180988</v>
       </c>
       <c r="F9" t="n">
-        <v>101.9861328463556</v>
+        <v>51.81214434844668</v>
       </c>
       <c r="G9" t="n">
-        <v>103.2501193412417</v>
+        <v>103.2501196464526</v>
       </c>
       <c r="H9" t="n">
         <v>101.7919811138398</v>
@@ -3824,7 +3824,7 @@
         <v>109.4602817981752</v>
       </c>
       <c r="P9" t="n">
-        <v>111.3719148877632</v>
+        <v>111.3719148877633</v>
       </c>
       <c r="Q9" t="n">
         <v>102.9857214727588</v>
@@ -3833,16 +3833,16 @@
         <v>101.904359949582</v>
       </c>
       <c r="S9" t="n">
-        <v>102.6102856013017</v>
+        <v>102.6102856013016</v>
       </c>
       <c r="T9" t="n">
         <v>102.0917252614731</v>
       </c>
       <c r="U9" t="n">
-        <v>102.5357677331441</v>
+        <v>102.5357677331442</v>
       </c>
       <c r="V9" t="n">
-        <v>102.2557306873808</v>
+        <v>127.3719404674919</v>
       </c>
       <c r="W9" t="n">
         <v>102.1254856782594</v>
@@ -3854,7 +3854,7 @@
         <v>102.6157379262586</v>
       </c>
       <c r="Z9" t="n">
-        <v>102.4781752105595</v>
+        <v>89.35588823111286</v>
       </c>
       <c r="AA9" t="n">
         <v>102.2350899337766</v>
@@ -4026,85 +4026,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.103532809552758</v>
+        <v>2.103532809552746</v>
       </c>
       <c r="C2" t="n">
-        <v>2.112033052571958</v>
+        <v>2.112033052571954</v>
       </c>
       <c r="D2" t="n">
-        <v>2.096524149892757</v>
+        <v>2.096524149892752</v>
       </c>
       <c r="E2" t="n">
-        <v>2.064439256710438</v>
+        <v>2.064439256710437</v>
       </c>
       <c r="F2" t="n">
-        <v>2.106342885014902</v>
+        <v>2.106342885014898</v>
       </c>
       <c r="G2" t="n">
-        <v>2.186570647843096</v>
+        <v>2.186570647843087</v>
       </c>
       <c r="H2" t="n">
-        <v>2.069581104098259</v>
+        <v>2.069581104098249</v>
       </c>
       <c r="I2" t="n">
-        <v>2.169772849262714</v>
+        <v>2.169772849262711</v>
       </c>
       <c r="J2" t="n">
-        <v>2.144267422982003</v>
+        <v>2.144267422981989</v>
       </c>
       <c r="K2" t="n">
-        <v>2.142616195370961</v>
+        <v>2.142616195370939</v>
       </c>
       <c r="L2" t="n">
-        <v>2.139206297249411</v>
+        <v>2.139206297249409</v>
       </c>
       <c r="M2" t="n">
-        <v>2.155954622248265</v>
+        <v>2.155954622248256</v>
       </c>
       <c r="N2" t="n">
         <v>2.10351390103813</v>
       </c>
       <c r="O2" t="n">
-        <v>4.041090899649229</v>
+        <v>4.041090899649209</v>
       </c>
       <c r="P2" t="n">
-        <v>2.141205714962686</v>
+        <v>2.141205714962687</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.143822245675286</v>
+        <v>2.143822245675283</v>
       </c>
       <c r="R2" t="n">
-        <v>2.13259280606995</v>
+        <v>2.132592806069944</v>
       </c>
       <c r="S2" t="n">
-        <v>2.146715648281952</v>
+        <v>2.146715648281954</v>
       </c>
       <c r="T2" t="n">
-        <v>2.116616470894638</v>
+        <v>2.116616470894639</v>
       </c>
       <c r="U2" t="n">
-        <v>2.361020384025001</v>
+        <v>2.361020384024986</v>
       </c>
       <c r="V2" t="n">
-        <v>2.119771499918145</v>
+        <v>2.119771499918144</v>
       </c>
       <c r="W2" t="n">
-        <v>2.442393950804044</v>
+        <v>2.442393950804061</v>
       </c>
       <c r="X2" t="n">
-        <v>2.142478418256017</v>
+        <v>2.142478418256013</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.183873462500661</v>
+        <v>2.183873462500655</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.206670607902469</v>
+        <v>2.206670607902456</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.115424307540149</v>
+        <v>2.115424307540148</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.152696821400242</v>
+        <v>2.152696821400232</v>
       </c>
     </row>
     <row r="3">
@@ -4114,85 +4114,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.28657755796039</v>
+        <v>2.286577557960392</v>
       </c>
       <c r="C3" t="n">
-        <v>2.142733478341268</v>
+        <v>2.142733478341259</v>
       </c>
       <c r="D3" t="n">
-        <v>2.238195023939503</v>
+        <v>2.238195023939511</v>
       </c>
       <c r="E3" t="n">
-        <v>2.009392528943147</v>
+        <v>2.00939252894314</v>
       </c>
       <c r="F3" t="n">
-        <v>2.308741489466196</v>
+        <v>2.308741489466201</v>
       </c>
       <c r="G3" t="n">
-        <v>2.875873326783774</v>
+        <v>2.875873326783761</v>
       </c>
       <c r="H3" t="n">
-        <v>2.046020597323567</v>
+        <v>2.04602059732356</v>
       </c>
       <c r="I3" t="n">
-        <v>2.762681852831587</v>
+        <v>2.762681852831582</v>
       </c>
       <c r="J3" t="n">
-        <v>2.576892384061054</v>
+        <v>2.576892384061047</v>
       </c>
       <c r="K3" t="n">
-        <v>2.565221337900366</v>
+        <v>2.565221337900363</v>
       </c>
       <c r="L3" t="n">
-        <v>2.541289856806463</v>
+        <v>2.541289856806456</v>
       </c>
       <c r="M3" t="n">
-        <v>2.665737088260575</v>
+        <v>2.665737088260558</v>
       </c>
       <c r="N3" t="n">
-        <v>2.288290553000985</v>
+        <v>2.288290553000965</v>
       </c>
       <c r="O3" t="n">
-        <v>5.480970979903699</v>
+        <v>5.480970979903709</v>
       </c>
       <c r="P3" t="n">
-        <v>2.553789886472853</v>
+        <v>2.553789886472857</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.574986530232666</v>
+        <v>2.574986530232663</v>
       </c>
       <c r="R3" t="n">
-        <v>2.497667897450903</v>
+        <v>2.497667897450896</v>
       </c>
       <c r="S3" t="n">
         <v>2.593834642824057</v>
       </c>
       <c r="T3" t="n">
-        <v>2.382595180610755</v>
+        <v>2.382595180610757</v>
       </c>
       <c r="U3" t="n">
-        <v>2.898381791053228</v>
+        <v>2.89838179105322</v>
       </c>
       <c r="V3" t="n">
-        <v>2.401412018677438</v>
+        <v>2.401412018677435</v>
       </c>
       <c r="W3" t="n">
-        <v>2.829042109429816</v>
+        <v>2.829042109429798</v>
       </c>
       <c r="X3" t="n">
-        <v>2.566026962933248</v>
+        <v>2.566026962933244</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.862148633919676</v>
+        <v>2.862148633919666</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.603218602971266</v>
+        <v>2.60321860297127</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.373067506245059</v>
+        <v>2.373067506245056</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.642770148155634</v>
+        <v>2.642770148155625</v>
       </c>
     </row>
     <row r="4">
@@ -4202,85 +4202,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.916180838103174</v>
+        <v>1.91618083810317</v>
       </c>
       <c r="C4" t="n">
-        <v>1.590194577005117</v>
+        <v>1.590194577005109</v>
       </c>
       <c r="D4" t="n">
-        <v>1.837014803100775</v>
+        <v>1.837014803100769</v>
       </c>
       <c r="E4" t="n">
-        <v>1.474601174826401</v>
+        <v>1.474601174826397</v>
       </c>
       <c r="F4" t="n">
-        <v>1.947921933146734</v>
+        <v>1.947921933146727</v>
       </c>
       <c r="G4" t="n">
-        <v>2.854131420885439</v>
+        <v>2.854131420885417</v>
       </c>
       <c r="H4" t="n">
-        <v>1.532680706438488</v>
+        <v>1.532680706438474</v>
       </c>
       <c r="I4" t="n">
-        <v>2.664392558550945</v>
+        <v>2.664392558550936</v>
       </c>
       <c r="J4" t="n">
-        <v>2.375354565636168</v>
+        <v>2.375354565636163</v>
       </c>
       <c r="K4" t="n">
-        <v>2.357645660165416</v>
+        <v>2.357645660165406</v>
       </c>
       <c r="L4" t="n">
-        <v>2.319129292252054</v>
+        <v>2.319129292252047</v>
       </c>
       <c r="M4" t="n">
-        <v>2.513188761663427</v>
+        <v>2.513188761663409</v>
       </c>
       <c r="N4" t="n">
-        <v>1.915967257732145</v>
+        <v>1.915967257732143</v>
       </c>
       <c r="O4" t="n">
-        <v>1.908538603603601</v>
+        <v>1.908538603603597</v>
       </c>
       <c r="P4" t="n">
-        <v>2.341713635101078</v>
+        <v>2.341713635101077</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.371268553163465</v>
+        <v>2.371268553163453</v>
       </c>
       <c r="R4" t="n">
-        <v>2.244426867023767</v>
+        <v>2.244426867023758</v>
       </c>
       <c r="S4" t="n">
-        <v>2.403950866636738</v>
+        <v>2.403950866636734</v>
       </c>
       <c r="T4" t="n">
-        <v>2.06396681174132</v>
+        <v>2.063966811741315</v>
       </c>
       <c r="U4" t="n">
-        <v>2.252606470299192</v>
+        <v>2.252606470299185</v>
       </c>
       <c r="V4" t="n">
-        <v>2.093487145981471</v>
+        <v>2.09348714598147</v>
       </c>
       <c r="W4" t="n">
-        <v>1.878382539602097</v>
+        <v>1.878382539602071</v>
       </c>
       <c r="X4" t="n">
-        <v>2.356089404271598</v>
+        <v>2.356089404271597</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.774408612759102</v>
+        <v>2.774408612759098</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.222849809226295</v>
+        <v>2.222849809226317</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.050500778230168</v>
+        <v>2.050500778230162</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.472538045152251</v>
+        <v>2.472538045152235</v>
       </c>
     </row>
     <row r="5">
@@ -4290,85 +4290,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9.496849031373067</v>
+        <v>9.496849031373083</v>
       </c>
       <c r="C5" t="n">
-        <v>4.545557568364388</v>
+        <v>4.545557568364403</v>
       </c>
       <c r="D5" t="n">
-        <v>8.94584006220852</v>
+        <v>8.945840062208573</v>
       </c>
       <c r="E5" t="n">
-        <v>2.63389481640106</v>
+        <v>2.633894816401043</v>
       </c>
       <c r="F5" t="n">
-        <v>11.15080687229831</v>
+        <v>11.15080687229829</v>
       </c>
       <c r="G5" t="n">
-        <v>24.3502993530435</v>
+        <v>24.3502993530434</v>
       </c>
       <c r="H5" t="n">
-        <v>3.625083216364597</v>
+        <v>3.625083216364531</v>
       </c>
       <c r="I5" t="n">
-        <v>24.46409924805321</v>
+        <v>24.46409924805323</v>
       </c>
       <c r="J5" t="n">
-        <v>17.42127576336859</v>
+        <v>17.4212757633685</v>
       </c>
       <c r="K5" t="n">
-        <v>17.15133652529089</v>
+        <v>17.15133652529087</v>
       </c>
       <c r="L5" t="n">
-        <v>16.68006029287293</v>
+        <v>16.68006029287284</v>
       </c>
       <c r="M5" t="n">
-        <v>21.28480905499503</v>
+        <v>21.28480905499505</v>
       </c>
       <c r="N5" t="n">
-        <v>15.6657388530359</v>
+        <v>15.66573885303574</v>
       </c>
       <c r="O5" t="n">
-        <v>9.263753685667105</v>
+        <v>9.263753685667057</v>
       </c>
       <c r="P5" t="n">
-        <v>16.16228843247404</v>
+        <v>16.16228843247405</v>
       </c>
       <c r="Q5" t="n">
-        <v>17.99215145818436</v>
+        <v>17.99215145818431</v>
       </c>
       <c r="R5" t="n">
-        <v>17.21347659188526</v>
+        <v>17.21347659188512</v>
       </c>
       <c r="S5" t="n">
-        <v>17.63622372110943</v>
+        <v>17.63622372110947</v>
       </c>
       <c r="T5" t="n">
-        <v>13.47822027216972</v>
+        <v>13.47822027216981</v>
       </c>
       <c r="U5" t="n">
-        <v>16.05163492451984</v>
+        <v>16.05163492451967</v>
       </c>
       <c r="V5" t="n">
-        <v>12.1845853168123</v>
+        <v>12.18458531681229</v>
       </c>
       <c r="W5" t="n">
-        <v>9.590827986656011</v>
+        <v>9.590827986655981</v>
       </c>
       <c r="X5" t="n">
-        <v>18.05088814308816</v>
+        <v>18.05088814308821</v>
       </c>
       <c r="Y5" t="n">
-        <v>26.6747814242054</v>
+        <v>26.67478142420534</v>
       </c>
       <c r="Z5" t="n">
-        <v>13.5939924233286</v>
+        <v>13.5939924233298</v>
       </c>
       <c r="AA5" t="n">
-        <v>12.71190512158289</v>
+        <v>12.71190512158307</v>
       </c>
       <c r="AB5" t="n">
-        <v>21.79776287994404</v>
+        <v>21.79776287994393</v>
       </c>
     </row>
     <row r="6">
@@ -4378,85 +4378,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.231663450606931</v>
+        <v>4.077461392742768</v>
       </c>
       <c r="C6" t="n">
-        <v>1.905677189508864</v>
+        <v>1.905677189508837</v>
       </c>
       <c r="D6" t="n">
-        <v>2.152497415604523</v>
+        <v>2.152497415604504</v>
       </c>
       <c r="E6" t="n">
-        <v>1.790083787330155</v>
+        <v>3.635881729465839</v>
       </c>
       <c r="F6" t="n">
-        <v>2.263404545650487</v>
+        <v>2.263404545650457</v>
       </c>
       <c r="G6" t="n">
-        <v>3.169614033389201</v>
+        <v>5.015411975524925</v>
       </c>
       <c r="H6" t="n">
-        <v>3.693961261077922</v>
+        <v>1.848163318942212</v>
       </c>
       <c r="I6" t="n">
-        <v>2.979875171054696</v>
+        <v>2.979875171054662</v>
       </c>
       <c r="J6" t="n">
-        <v>2.69083717813993</v>
+        <v>4.536635120275536</v>
       </c>
       <c r="K6" t="n">
-        <v>4.518926214804859</v>
+        <v>4.518926214804955</v>
       </c>
       <c r="L6" t="n">
-        <v>2.634611904755805</v>
+        <v>4.480409846891515</v>
       </c>
       <c r="M6" t="n">
-        <v>2.82867137416718</v>
+        <v>2.828671374167158</v>
       </c>
       <c r="N6" t="n">
-        <v>2.235058842549627</v>
+        <v>2.235058842549618</v>
       </c>
       <c r="O6" t="n">
-        <v>2.227630188421084</v>
+        <v>4.11166356133621</v>
       </c>
       <c r="P6" t="n">
-        <v>4.546773042332272</v>
+        <v>2.638241454063559</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.532549107802921</v>
+        <v>4.532549107802891</v>
       </c>
       <c r="R6" t="n">
-        <v>4.405707421663182</v>
+        <v>4.405707421663243</v>
       </c>
       <c r="S6" t="n">
-        <v>4.565231421276196</v>
+        <v>4.565231421276195</v>
       </c>
       <c r="T6" t="n">
-        <v>2.37944942424507</v>
+        <v>4.225247366380831</v>
       </c>
       <c r="U6" t="n">
-        <v>4.463143883855646</v>
+        <v>2.617345941719884</v>
       </c>
       <c r="V6" t="n">
-        <v>4.254767700620942</v>
+        <v>2.408969758485199</v>
       </c>
       <c r="W6" t="n">
-        <v>4.081224448268163</v>
+        <v>4.081224448268143</v>
       </c>
       <c r="X6" t="n">
-        <v>2.671572016775345</v>
+        <v>2.671572016775329</v>
       </c>
       <c r="Y6" t="n">
-        <v>3.161210092917589</v>
+        <v>3.161210092917554</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.384130363865756</v>
+        <v>4.384130363865889</v>
       </c>
       <c r="AA6" t="n">
-        <v>4.211781332869574</v>
+        <v>4.211781332869676</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.793585211573679</v>
+        <v>2.793585211573645</v>
       </c>
     </row>
     <row r="7">
@@ -4466,85 +4466,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.58127044519054</v>
+        <v>2.581270445190523</v>
       </c>
       <c r="C7" t="n">
-        <v>2.255284184092474</v>
+        <v>2.255284184092462</v>
       </c>
       <c r="D7" t="n">
-        <v>2.502104410188138</v>
+        <v>2.502104410188123</v>
       </c>
       <c r="E7" t="n">
-        <v>2.139690781913769</v>
+        <v>2.139690781913745</v>
       </c>
       <c r="F7" t="n">
-        <v>2.613011540234096</v>
+        <v>2.613011540234075</v>
       </c>
       <c r="G7" t="n">
-        <v>3.519221027972804</v>
+        <v>3.51922102797278</v>
       </c>
       <c r="H7" t="n">
-        <v>2.197770313525814</v>
+        <v>2.197770313525825</v>
       </c>
       <c r="I7" t="n">
-        <v>3.329482165638317</v>
+        <v>3.329482165638292</v>
       </c>
       <c r="J7" t="n">
-        <v>3.040444172723532</v>
+        <v>3.040444172723522</v>
       </c>
       <c r="K7" t="n">
-        <v>3.022735267252784</v>
+        <v>3.022735267252761</v>
       </c>
       <c r="L7" t="n">
-        <v>2.984218899339411</v>
+        <v>2.984218899339395</v>
       </c>
       <c r="M7" t="n">
-        <v>3.178278368750786</v>
+        <v>3.178278368750766</v>
       </c>
       <c r="N7" t="n">
-        <v>2.581056864819513</v>
+        <v>2.581056864819496</v>
       </c>
       <c r="O7" t="n">
-        <v>2.573577918362665</v>
+        <v>2.573577918362654</v>
       </c>
       <c r="P7" t="n">
-        <v>3.006752949860143</v>
+        <v>3.006752949860137</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.036358160250836</v>
+        <v>3.03635816025081</v>
       </c>
       <c r="R7" t="n">
-        <v>2.90951647411113</v>
+        <v>2.909516474111122</v>
       </c>
       <c r="S7" t="n">
-        <v>3.069040473724111</v>
+        <v>3.069040473724095</v>
       </c>
       <c r="T7" t="n">
-        <v>2.729056418828693</v>
+        <v>2.729056418828675</v>
       </c>
       <c r="U7" t="n">
-        <v>3.047185989152152</v>
+        <v>3.04718598915215</v>
       </c>
       <c r="V7" t="n">
-        <v>2.758576753068825</v>
+        <v>2.75857675306882</v>
       </c>
       <c r="W7" t="n">
-        <v>2.543472146689445</v>
+        <v>2.543472146689429</v>
       </c>
       <c r="X7" t="n">
-        <v>3.02117901135895</v>
+        <v>3.021179011358947</v>
       </c>
       <c r="Y7" t="n">
-        <v>3.488755078763426</v>
+        <v>3.488755078763402</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.887939416313644</v>
+        <v>2.887939416313598</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.715590385317523</v>
+        <v>2.715590385317518</v>
       </c>
       <c r="AB7" t="n">
-        <v>3.137627652239604</v>
+        <v>3.137627652239584</v>
       </c>
     </row>
     <row r="8">
@@ -4554,85 +4554,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.112360383055998</v>
+        <v>4.112360383056016</v>
       </c>
       <c r="C8" t="n">
-        <v>5.24487128277902</v>
+        <v>5.244871282779002</v>
       </c>
       <c r="D8" t="n">
-        <v>5.491691508874699</v>
+        <v>5.491691508874659</v>
       </c>
       <c r="E8" t="n">
-        <v>5.129277880600315</v>
+        <v>4.352671165511008</v>
       </c>
       <c r="F8" t="n">
-        <v>4.371318289878255</v>
+        <v>4.371318289878234</v>
       </c>
       <c r="G8" t="n">
-        <v>6.508808126659341</v>
+        <v>6.811237014211597</v>
       </c>
       <c r="H8" t="n">
-        <v>5.187357412212388</v>
+        <v>5.187357412212366</v>
       </c>
       <c r="I8" t="n">
-        <v>6.319069264324829</v>
+        <v>6.319069264324839</v>
       </c>
       <c r="J8" t="n">
-        <v>6.030031271410087</v>
+        <v>6.030031271410075</v>
       </c>
       <c r="K8" t="n">
-        <v>6.012322365939303</v>
+        <v>6.012322365939308</v>
       </c>
       <c r="L8" t="n">
-        <v>5.973805998025966</v>
+        <v>5.973805998025942</v>
       </c>
       <c r="M8" t="n">
-        <v>6.167865467437322</v>
+        <v>6.167865467440719</v>
       </c>
       <c r="N8" t="n">
-        <v>4.440064662515009</v>
+        <v>4.440064662515018</v>
       </c>
       <c r="O8" t="n">
-        <v>4.743329016775649</v>
+        <v>4.743329016775639</v>
       </c>
       <c r="P8" t="n">
-        <v>5.100345684557271</v>
+        <v>5.100345684557264</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.280820117516487</v>
+        <v>4.280820117516493</v>
       </c>
       <c r="R8" t="n">
-        <v>5.899103572797672</v>
+        <v>5.89910357279767</v>
       </c>
       <c r="S8" t="n">
-        <v>6.05862757241066</v>
+        <v>6.058627572410631</v>
       </c>
       <c r="T8" t="n">
-        <v>5.718643517515245</v>
+        <v>5.718643517515214</v>
       </c>
       <c r="U8" t="n">
-        <v>5.117478267782896</v>
+        <v>5.306884658616918</v>
       </c>
       <c r="V8" t="n">
-        <v>5.748163851755369</v>
+        <v>5.418158801897745</v>
       </c>
       <c r="W8" t="n">
-        <v>5.533345881506042</v>
+        <v>5.53334588150603</v>
       </c>
       <c r="X8" t="n">
-        <v>4.399315131278733</v>
+        <v>4.399315131278724</v>
       </c>
       <c r="Y8" t="n">
-        <v>8.034928955612076</v>
+        <v>8.034928955612049</v>
       </c>
       <c r="Z8" t="n">
-        <v>5.877526515000212</v>
+        <v>4.391937020628299</v>
       </c>
       <c r="AA8" t="n">
-        <v>5.705177484004077</v>
+        <v>5.705177484004062</v>
       </c>
       <c r="AB8" t="n">
-        <v>7.650736992668274</v>
+        <v>7.650736992668256</v>
       </c>
     </row>
     <row r="9">
@@ -4642,31 +4642,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>80.48581555610905</v>
+        <v>80.48581555610897</v>
       </c>
       <c r="C9" t="n">
-        <v>101.9161118467355</v>
+        <v>101.9161118467354</v>
       </c>
       <c r="D9" t="n">
         <v>102.1629320728311</v>
       </c>
       <c r="E9" t="n">
-        <v>101.8005184445568</v>
+        <v>96.77925738973735</v>
       </c>
       <c r="F9" t="n">
-        <v>102.2738392028772</v>
+        <v>52.11966970199764</v>
       </c>
       <c r="G9" t="n">
-        <v>103.1800486906157</v>
+        <v>103.1800489712429</v>
       </c>
       <c r="H9" t="n">
-        <v>101.8585979761689</v>
+        <v>101.8585979761688</v>
       </c>
       <c r="I9" t="n">
-        <v>102.9903098282812</v>
+        <v>102.9903098282811</v>
       </c>
       <c r="J9" t="n">
-        <v>102.7012718353665</v>
+        <v>102.7012718353664</v>
       </c>
       <c r="K9" t="n">
         <v>102.6835629298957</v>
@@ -4678,19 +4678,19 @@
         <v>102.8391060313937</v>
       </c>
       <c r="N9" t="n">
-        <v>102.2418845274625</v>
+        <v>102.2418845274624</v>
       </c>
       <c r="O9" t="n">
-        <v>109.4444597971736</v>
+        <v>109.4444597971735</v>
       </c>
       <c r="P9" t="n">
-        <v>111.4456869182443</v>
+        <v>111.4456869182441</v>
       </c>
       <c r="Q9" t="n">
-        <v>102.6971861035211</v>
+        <v>102.697186103521</v>
       </c>
       <c r="R9" t="n">
-        <v>102.5703441367541</v>
+        <v>102.570344136754</v>
       </c>
       <c r="S9" t="n">
         <v>102.7298681363669</v>
@@ -4699,10 +4699,10 @@
         <v>102.3898840814716</v>
       </c>
       <c r="U9" t="n">
-        <v>102.6277805989463</v>
+        <v>102.6277805989464</v>
       </c>
       <c r="V9" t="n">
-        <v>102.4194044157117</v>
+        <v>127.525693140891</v>
       </c>
       <c r="W9" t="n">
         <v>102.2042998093324</v>
@@ -4711,16 +4711,16 @@
         <v>102.6820066740019</v>
       </c>
       <c r="Y9" t="n">
-        <v>103.1495827414063</v>
+        <v>103.1495827414062</v>
       </c>
       <c r="Z9" t="n">
-        <v>102.5487670789565</v>
+        <v>89.43166345582763</v>
       </c>
       <c r="AA9" t="n">
         <v>102.3764180479603</v>
       </c>
       <c r="AB9" t="n">
-        <v>102.7984553148825</v>
+        <v>102.7984553148824</v>
       </c>
     </row>
   </sheetData>
@@ -4886,85 +4886,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.023637633290832</v>
+        <v>2.023637633290857</v>
       </c>
       <c r="C2" t="n">
-        <v>2.078740578885065</v>
+        <v>2.078740578885059</v>
       </c>
       <c r="D2" t="n">
-        <v>2.000186933343386</v>
+        <v>2.000186933343397</v>
       </c>
       <c r="E2" t="n">
-        <v>2.155076456016938</v>
+        <v>2.155076456016952</v>
       </c>
       <c r="F2" t="n">
-        <v>2.093837288244896</v>
+        <v>2.0938372882449</v>
       </c>
       <c r="G2" t="n">
-        <v>2.043856812457799</v>
+        <v>2.043856812457818</v>
       </c>
       <c r="H2" t="n">
-        <v>2.02362976810309</v>
+        <v>2.023629768103107</v>
       </c>
       <c r="I2" t="n">
-        <v>2.083967434939089</v>
+        <v>2.083967434939108</v>
       </c>
       <c r="J2" t="n">
-        <v>2.045522789454843</v>
+        <v>2.045522789454865</v>
       </c>
       <c r="K2" t="n">
-        <v>2.089752056064458</v>
+        <v>2.089752056064469</v>
       </c>
       <c r="L2" t="n">
-        <v>2.206260368509495</v>
+        <v>2.206260368509503</v>
       </c>
       <c r="M2" t="n">
-        <v>2.047467818794771</v>
+        <v>2.047467818794765</v>
       </c>
       <c r="N2" t="n">
-        <v>2.031909033642478</v>
+        <v>2.03190903364249</v>
       </c>
       <c r="O2" t="n">
-        <v>3.894691530786895</v>
+        <v>3.894691530786908</v>
       </c>
       <c r="P2" t="n">
-        <v>2.01656459911033</v>
+        <v>2.016564599110338</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.074920094347884</v>
+        <v>2.0749200943479</v>
       </c>
       <c r="R2" t="n">
-        <v>2.092581568279884</v>
+        <v>2.092581568279925</v>
       </c>
       <c r="S2" t="n">
-        <v>2.115641605981445</v>
+        <v>2.115641605981499</v>
       </c>
       <c r="T2" t="n">
-        <v>2.02518736180356</v>
+        <v>2.025187361803572</v>
       </c>
       <c r="U2" t="n">
-        <v>2.157088765411635</v>
+        <v>2.157088765411674</v>
       </c>
       <c r="V2" t="n">
-        <v>2.024700456373119</v>
+        <v>2.024700456373131</v>
       </c>
       <c r="W2" t="n">
-        <v>2.262336122419391</v>
+        <v>2.262336122419425</v>
       </c>
       <c r="X2" t="n">
-        <v>2.077945424224364</v>
+        <v>2.077945424224405</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.013026786079033</v>
+        <v>2.013026786079044</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.969462557961927</v>
+        <v>1.969462557961938</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.008895290028248</v>
+        <v>2.008895290028258</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.01663566327583</v>
+        <v>2.016635663275832</v>
       </c>
     </row>
     <row r="3">
@@ -4974,85 +4974,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.227166993626152</v>
+        <v>2.227166993626182</v>
       </c>
       <c r="C3" t="n">
-        <v>2.396975158218025</v>
+        <v>2.396975158218021</v>
       </c>
       <c r="D3" t="n">
-        <v>2.061386450796713</v>
+        <v>2.061386450796745</v>
       </c>
       <c r="E3" t="n">
-        <v>3.166384692846669</v>
+        <v>3.166384692846691</v>
       </c>
       <c r="F3" t="n">
-        <v>2.731031681509163</v>
+        <v>2.731031681509192</v>
       </c>
       <c r="G3" t="n">
-        <v>2.369805084937731</v>
+        <v>2.369805084937761</v>
       </c>
       <c r="H3" t="n">
-        <v>2.229891484515205</v>
+        <v>2.229891484515225</v>
       </c>
       <c r="I3" t="n">
-        <v>2.661193775597571</v>
+        <v>2.66119377559758</v>
       </c>
       <c r="J3" t="n">
-        <v>2.382914540758381</v>
+        <v>2.382914540758394</v>
       </c>
       <c r="K3" t="n">
-        <v>2.698326759269428</v>
+        <v>2.698326759269483</v>
       </c>
       <c r="L3" t="n">
-        <v>3.521691920225531</v>
+        <v>3.521691920225567</v>
       </c>
       <c r="M3" t="n">
-        <v>2.401910427827324</v>
+        <v>2.401910427827322</v>
       </c>
       <c r="N3" t="n">
-        <v>2.287383545898098</v>
+        <v>2.287383545898132</v>
       </c>
       <c r="O3" t="n">
-        <v>5.194518460792956</v>
+        <v>5.194518460792963</v>
       </c>
       <c r="P3" t="n">
-        <v>2.177092101888154</v>
+        <v>2.177092101888191</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.593763979737872</v>
+        <v>2.59376397973791</v>
       </c>
       <c r="R3" t="n">
-        <v>2.723999457087068</v>
+        <v>2.723999457087086</v>
       </c>
       <c r="S3" t="n">
-        <v>2.876453103861102</v>
+        <v>2.876453103861131</v>
       </c>
       <c r="T3" t="n">
-        <v>2.239720801676223</v>
+        <v>2.239720801676256</v>
       </c>
       <c r="U3" t="n">
-        <v>2.456211018698344</v>
+        <v>2.456211018698363</v>
       </c>
       <c r="V3" t="n">
-        <v>2.234587670846985</v>
+        <v>2.234587670847042</v>
       </c>
       <c r="W3" t="n">
-        <v>2.579787433050151</v>
+        <v>2.579787433050193</v>
       </c>
       <c r="X3" t="n">
-        <v>2.616996012299178</v>
+        <v>2.616996012299205</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.152699344455636</v>
+        <v>2.152699344455673</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.183571681958314</v>
+        <v>2.183571681958315</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.123261773102474</v>
+        <v>2.123261773102512</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.184048780792474</v>
+        <v>2.184048780792468</v>
       </c>
     </row>
     <row r="4">
@@ -5065,82 +5065,82 @@
         <v>1.789228844427275</v>
       </c>
       <c r="C4" t="n">
-        <v>1.951357746009845</v>
+        <v>1.951357746009844</v>
       </c>
       <c r="D4" t="n">
-        <v>1.524342400665814</v>
+        <v>1.524342400665809</v>
       </c>
       <c r="E4" t="n">
-        <v>3.273890811964274</v>
+        <v>3.27389081196427</v>
       </c>
       <c r="F4" t="n">
-        <v>2.582166240569999</v>
+        <v>2.582166240569995</v>
       </c>
       <c r="G4" t="n">
-        <v>2.017613774400093</v>
+        <v>2.017613774400087</v>
       </c>
       <c r="H4" t="n">
-        <v>1.789140003513558</v>
+        <v>1.789140003513548</v>
       </c>
       <c r="I4" t="n">
-        <v>2.470681707124296</v>
+        <v>2.470681707124285</v>
       </c>
       <c r="J4" t="n">
         <v>2.035708613982208</v>
       </c>
       <c r="K4" t="n">
-        <v>2.536021663792426</v>
+        <v>2.536021663792415</v>
       </c>
       <c r="L4" t="n">
-        <v>3.852036649330698</v>
+        <v>3.852036649330689</v>
       </c>
       <c r="M4" t="n">
-        <v>2.065684584666354</v>
+        <v>2.065684584666355</v>
       </c>
       <c r="N4" t="n">
-        <v>1.88265811643118</v>
+        <v>1.882658116431175</v>
       </c>
       <c r="O4" t="n">
-        <v>1.538308512013894</v>
+        <v>1.538308512013897</v>
       </c>
       <c r="P4" t="n">
-        <v>1.709335669601898</v>
+        <v>1.709335669601894</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.368487833164223</v>
+        <v>2.368487833164218</v>
       </c>
       <c r="R4" t="n">
-        <v>2.567982305905882</v>
+        <v>2.567982305905871</v>
       </c>
       <c r="S4" t="n">
-        <v>2.82845603988658</v>
+        <v>2.828456039886586</v>
       </c>
       <c r="T4" t="n">
-        <v>1.806733740888782</v>
+        <v>1.806733740888768</v>
       </c>
       <c r="U4" t="n">
-        <v>1.739679502968091</v>
+        <v>1.739679502968094</v>
       </c>
       <c r="V4" t="n">
-        <v>1.796684066540967</v>
+        <v>1.79668406654096</v>
       </c>
       <c r="W4" t="n">
-        <v>1.701301216332825</v>
+        <v>1.701301216332822</v>
       </c>
       <c r="X4" t="n">
-        <v>2.402660325839736</v>
+        <v>2.402660325839737</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.602906816343131</v>
+        <v>1.602906816343128</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.884932019730831</v>
+        <v>1.884932019730812</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.622707295463296</v>
+        <v>1.622707295463304</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.718639730485973</v>
+        <v>1.718639730485967</v>
       </c>
     </row>
     <row r="5">
@@ -5150,85 +5150,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9.535729965016309</v>
+        <v>9.535729965016312</v>
       </c>
       <c r="C5" t="n">
-        <v>13.46748997099377</v>
+        <v>13.46748997099376</v>
       </c>
       <c r="D5" t="n">
-        <v>5.410603296369644</v>
+        <v>5.410603296369655</v>
       </c>
       <c r="E5" t="n">
-        <v>38.23729059371339</v>
+        <v>38.23729059371342</v>
       </c>
       <c r="F5" t="n">
-        <v>26.11146337045819</v>
+        <v>26.11146337045822</v>
       </c>
       <c r="G5" t="n">
-        <v>12.92679428478612</v>
+        <v>12.92679428478617</v>
       </c>
       <c r="H5" t="n">
-        <v>11.0805010947588</v>
+        <v>11.08050109475878</v>
       </c>
       <c r="I5" t="n">
-        <v>24.33928979172563</v>
+        <v>24.33928979172565</v>
       </c>
       <c r="J5" t="n">
-        <v>13.95999327853716</v>
+        <v>13.95999327853717</v>
       </c>
       <c r="K5" t="n">
-        <v>23.26550628623574</v>
+        <v>23.26550628623571</v>
       </c>
       <c r="L5" t="n">
-        <v>43.61012645452811</v>
+        <v>43.61012645452817</v>
       </c>
       <c r="M5" t="n">
-        <v>15.15740936788246</v>
+        <v>15.15740936788243</v>
       </c>
       <c r="N5" t="n">
-        <v>10.25123486928964</v>
+        <v>10.25123486928962</v>
       </c>
       <c r="O5" t="n">
-        <v>5.186262816344493</v>
+        <v>5.186262816344492</v>
       </c>
       <c r="P5" t="n">
-        <v>8.25075164609823</v>
+        <v>8.250751646098234</v>
       </c>
       <c r="Q5" t="n">
         <v>20.81727045565924</v>
       </c>
       <c r="R5" t="n">
-        <v>26.91659955261821</v>
+        <v>26.9165995526182</v>
       </c>
       <c r="S5" t="n">
-        <v>25.09715819407011</v>
+        <v>25.09715819407012</v>
       </c>
       <c r="T5" t="n">
-        <v>10.69722326529355</v>
+        <v>10.69722326529354</v>
       </c>
       <c r="U5" t="n">
-        <v>10.17472388342244</v>
+        <v>10.17472388342243</v>
       </c>
       <c r="V5" t="n">
-        <v>9.666548143385514</v>
+        <v>9.666548143385373</v>
       </c>
       <c r="W5" t="n">
-        <v>8.603204563608665</v>
+        <v>8.603204563608747</v>
       </c>
       <c r="X5" t="n">
-        <v>22.37554733471601</v>
+        <v>22.37554733471603</v>
       </c>
       <c r="Y5" t="n">
-        <v>7.971674594725649</v>
+        <v>7.971674594725641</v>
       </c>
       <c r="Z5" t="n">
-        <v>10.98164435118565</v>
+        <v>10.98164435118563</v>
       </c>
       <c r="AA5" t="n">
-        <v>7.116615876649939</v>
+        <v>7.116615876649937</v>
       </c>
       <c r="AB5" t="n">
-        <v>9.444726410790578</v>
+        <v>9.444726410790546</v>
       </c>
     </row>
     <row r="6">
@@ -5238,85 +5238,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.128331103131436</v>
+        <v>2.128331103131431</v>
       </c>
       <c r="C6" t="n">
-        <v>4.239983641405688</v>
+        <v>4.239983641405684</v>
       </c>
       <c r="D6" t="n">
-        <v>3.812968296061655</v>
+        <v>1.863444659369965</v>
       </c>
       <c r="E6" t="n">
-        <v>5.562516707360112</v>
+        <v>3.612993070668422</v>
       </c>
       <c r="F6" t="n">
-        <v>4.870792135965829</v>
+        <v>4.870792135965837</v>
       </c>
       <c r="G6" t="n">
-        <v>2.356716033104252</v>
+        <v>4.306239669795929</v>
       </c>
       <c r="H6" t="n">
-        <v>2.128242262217711</v>
+        <v>2.128242262217704</v>
       </c>
       <c r="I6" t="n">
-        <v>4.759307602520125</v>
+        <v>2.809783965828443</v>
       </c>
       <c r="J6" t="n">
-        <v>2.374810872686365</v>
+        <v>2.374810872686364</v>
       </c>
       <c r="K6" t="n">
-        <v>4.82464755918826</v>
+        <v>2.875123922496571</v>
       </c>
       <c r="L6" t="n">
-        <v>6.140662544726533</v>
+        <v>4.191138908034845</v>
       </c>
       <c r="M6" t="n">
-        <v>2.40478684337052</v>
+        <v>4.354310480062195</v>
       </c>
       <c r="N6" t="n">
-        <v>2.213373426755093</v>
+        <v>2.213373426755095</v>
       </c>
       <c r="O6" t="n">
-        <v>3.861661903639383</v>
+        <v>3.861661903639385</v>
       </c>
       <c r="P6" t="n">
-        <v>4.033431979423571</v>
+        <v>2.016760977927615</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.657113728560058</v>
+        <v>4.657113728560057</v>
       </c>
       <c r="R6" t="n">
-        <v>4.856608201301713</v>
+        <v>2.907084564610031</v>
       </c>
       <c r="S6" t="n">
-        <v>5.117081935282421</v>
+        <v>3.167558298590742</v>
       </c>
       <c r="T6" t="n">
-        <v>2.145835999592929</v>
+        <v>4.095359636284612</v>
       </c>
       <c r="U6" t="n">
-        <v>4.094773025959814</v>
+        <v>2.145249389268137</v>
       </c>
       <c r="V6" t="n">
-        <v>2.135786325245133</v>
+        <v>4.085309961936804</v>
       </c>
       <c r="W6" t="n">
-        <v>2.051847938899396</v>
+        <v>2.051847938899399</v>
       </c>
       <c r="X6" t="n">
-        <v>2.741762584543897</v>
+        <v>2.741762584543892</v>
       </c>
       <c r="Y6" t="n">
         <v>2.018287004383613</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.224034278434974</v>
+        <v>4.17355791512665</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.961809554167459</v>
+        <v>3.911333190859137</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.048691257505575</v>
+        <v>2.048691257505571</v>
       </c>
     </row>
     <row r="7">
@@ -5326,82 +5326,82 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.468404273715795</v>
+        <v>2.468404273715793</v>
       </c>
       <c r="C7" t="n">
-        <v>2.630533175298364</v>
+        <v>2.630533175298361</v>
       </c>
       <c r="D7" t="n">
-        <v>2.203517829954329</v>
+        <v>2.203517829954333</v>
       </c>
       <c r="E7" t="n">
-        <v>3.953066241252786</v>
+        <v>3.953066241252784</v>
       </c>
       <c r="F7" t="n">
-        <v>3.261341669858514</v>
+        <v>3.261341669858513</v>
       </c>
       <c r="G7" t="n">
         <v>2.696789203688609</v>
       </c>
       <c r="H7" t="n">
-        <v>2.468315432802069</v>
+        <v>2.468315432802066</v>
       </c>
       <c r="I7" t="n">
         <v>3.149857136412809</v>
       </c>
       <c r="J7" t="n">
-        <v>2.714884043270726</v>
+        <v>2.714884043270725</v>
       </c>
       <c r="K7" t="n">
-        <v>3.215197093080936</v>
+        <v>3.215197093080932</v>
       </c>
       <c r="L7" t="n">
-        <v>4.531212078619206</v>
+        <v>4.531212078619208</v>
       </c>
       <c r="M7" t="n">
-        <v>2.744860013954876</v>
+        <v>2.744860013954872</v>
       </c>
       <c r="N7" t="n">
-        <v>2.561833545719695</v>
+        <v>2.561833545719693</v>
       </c>
       <c r="O7" t="n">
-        <v>2.217445683956668</v>
+        <v>2.217445683956661</v>
       </c>
       <c r="P7" t="n">
-        <v>2.388472841544667</v>
+        <v>2.388472841544666</v>
       </c>
       <c r="Q7" t="n">
         <v>3.047663262452737</v>
       </c>
       <c r="R7" t="n">
-        <v>3.2471577351944</v>
+        <v>3.247157735194393</v>
       </c>
       <c r="S7" t="n">
-        <v>3.507631469175101</v>
+        <v>3.507631469175099</v>
       </c>
       <c r="T7" t="n">
-        <v>2.485909170177289</v>
+        <v>2.485909170177288</v>
       </c>
       <c r="U7" t="n">
-        <v>2.524943828105826</v>
+        <v>2.524943828105825</v>
       </c>
       <c r="V7" t="n">
-        <v>2.47585949582948</v>
+        <v>2.475859495829478</v>
       </c>
       <c r="W7" t="n">
-        <v>2.380476645621337</v>
+        <v>2.380476645621343</v>
       </c>
       <c r="X7" t="n">
-        <v>3.081835755128258</v>
+        <v>3.081835755128251</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.348549873227535</v>
+        <v>2.348549873227536</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.56410744901933</v>
+        <v>2.564107449019335</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.30188272475182</v>
+        <v>2.301882724751815</v>
       </c>
       <c r="AB7" t="n">
         <v>2.397815159774485</v>
@@ -5414,43 +5414,43 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.13092845745792</v>
+        <v>4.130928457457922</v>
       </c>
       <c r="C8" t="n">
-        <v>5.845219562551919</v>
+        <v>5.845219562551939</v>
       </c>
       <c r="D8" t="n">
-        <v>5.418204217207897</v>
+        <v>5.418204217207865</v>
       </c>
       <c r="E8" t="n">
-        <v>7.167752628506346</v>
+        <v>6.341272041137922</v>
       </c>
       <c r="F8" t="n">
         <v>5.165674584343993</v>
       </c>
       <c r="G8" t="n">
-        <v>5.911475590942169</v>
+        <v>6.233326535288002</v>
       </c>
       <c r="H8" t="n">
-        <v>5.683001820055622</v>
+        <v>5.68300182005561</v>
       </c>
       <c r="I8" t="n">
-        <v>6.364543523666367</v>
+        <v>6.364543523666368</v>
       </c>
       <c r="J8" t="n">
         <v>5.929570430524285</v>
       </c>
       <c r="K8" t="n">
-        <v>6.4298834803345</v>
+        <v>6.429883480334476</v>
       </c>
       <c r="L8" t="n">
-        <v>7.74589846587277</v>
+        <v>7.745898465872783</v>
       </c>
       <c r="M8" t="n">
-        <v>5.95954640120843</v>
+        <v>5.959546401214111</v>
       </c>
       <c r="N8" t="n">
-        <v>4.5733345540947</v>
+        <v>4.573334554094695</v>
       </c>
       <c r="O8" t="n">
         <v>4.559630738699373</v>
@@ -5459,40 +5459,40 @@
         <v>4.649608623894537</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.405152146896943</v>
+        <v>4.405152146896935</v>
       </c>
       <c r="R8" t="n">
-        <v>6.461844122447943</v>
+        <v>6.461844122447959</v>
       </c>
       <c r="S8" t="n">
-        <v>6.722317856428665</v>
+        <v>6.722317856428644</v>
       </c>
       <c r="T8" t="n">
-        <v>5.70059555743085</v>
+        <v>5.700595557430843</v>
       </c>
       <c r="U8" t="n">
-        <v>4.773749013366087</v>
+        <v>4.973154450610081</v>
       </c>
       <c r="V8" t="n">
-        <v>5.690545883083054</v>
+        <v>5.300216529531711</v>
       </c>
       <c r="W8" t="n">
-        <v>5.595468076887147</v>
+        <v>5.595468076887132</v>
       </c>
       <c r="X8" t="n">
-        <v>4.581583389520037</v>
+        <v>4.581583389520024</v>
       </c>
       <c r="Y8" t="n">
-        <v>7.159094724264132</v>
+        <v>7.159094724264126</v>
       </c>
       <c r="Z8" t="n">
-        <v>5.778793836272905</v>
+        <v>4.197799422952682</v>
       </c>
       <c r="AA8" t="n">
-        <v>5.516569112005382</v>
+        <v>5.516569112005365</v>
       </c>
       <c r="AB8" t="n">
-        <v>7.233864758027667</v>
+        <v>7.233864758027618</v>
       </c>
     </row>
     <row r="9">
@@ -5502,67 +5502,67 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>86.13763555256162</v>
+        <v>86.13763555256163</v>
       </c>
       <c r="C9" t="n">
-        <v>109.6547193952427</v>
+        <v>109.6547193952428</v>
       </c>
       <c r="D9" t="n">
-        <v>109.2277040498986</v>
+        <v>109.2277040498987</v>
       </c>
       <c r="E9" t="n">
-        <v>110.977252461197</v>
+        <v>105.5870243945015</v>
       </c>
       <c r="F9" t="n">
-        <v>110.2855278898029</v>
+        <v>56.44598211946212</v>
       </c>
       <c r="G9" t="n">
-        <v>109.7209754236329</v>
+        <v>109.7209757754055</v>
       </c>
       <c r="H9" t="n">
-        <v>109.4925016527464</v>
+        <v>109.4925016527466</v>
       </c>
       <c r="I9" t="n">
-        <v>110.1740433563572</v>
+        <v>110.1740433563571</v>
       </c>
       <c r="J9" t="n">
-        <v>109.739070263215</v>
+        <v>109.7390702632149</v>
       </c>
       <c r="K9" t="n">
         <v>110.2393833130251</v>
       </c>
       <c r="L9" t="n">
-        <v>111.5553982985633</v>
+        <v>111.5553982985635</v>
       </c>
       <c r="M9" t="n">
-        <v>109.7690462338993</v>
+        <v>109.7690462338994</v>
       </c>
       <c r="N9" t="n">
-        <v>109.5860197656638</v>
+        <v>109.5860197656639</v>
       </c>
       <c r="O9" t="n">
-        <v>116.9814721163641</v>
+        <v>116.9814721163643</v>
       </c>
       <c r="P9" t="n">
-        <v>118.8357733300519</v>
+        <v>118.835773330052</v>
       </c>
       <c r="Q9" t="n">
         <v>110.0718498341696</v>
       </c>
       <c r="R9" t="n">
-        <v>110.2713439551387</v>
+        <v>110.2713439551388</v>
       </c>
       <c r="S9" t="n">
-        <v>110.5318176891194</v>
+        <v>110.5318176891193</v>
       </c>
       <c r="T9" t="n">
-        <v>109.5100953901216</v>
+        <v>109.5100953901217</v>
       </c>
       <c r="U9" t="n">
         <v>109.509508779797</v>
       </c>
       <c r="V9" t="n">
-        <v>109.5000457157738</v>
+        <v>136.4511686150771</v>
       </c>
       <c r="W9" t="n">
         <v>109.4046628655657</v>
@@ -5571,16 +5571,16 @@
         <v>110.1060219750727</v>
       </c>
       <c r="Y9" t="n">
-        <v>109.3727360931717</v>
+        <v>109.3727360931718</v>
       </c>
       <c r="Z9" t="n">
-        <v>109.5882936689636</v>
+        <v>95.50733278278888</v>
       </c>
       <c r="AA9" t="n">
-        <v>109.3260689446962</v>
+        <v>109.3260689446963</v>
       </c>
       <c r="AB9" t="n">
-        <v>109.4220013797188</v>
+        <v>109.4220013797189</v>
       </c>
     </row>
   </sheetData>
@@ -5746,85 +5746,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.39004631599523</v>
+        <v>2.39004631599522</v>
       </c>
       <c r="C2" t="n">
-        <v>2.352679256034609</v>
+        <v>2.352679256034604</v>
       </c>
       <c r="D2" t="n">
-        <v>2.190376893873991</v>
+        <v>2.19037689387399</v>
       </c>
       <c r="E2" t="n">
-        <v>2.511765641946948</v>
+        <v>2.511765641946954</v>
       </c>
       <c r="F2" t="n">
-        <v>2.422005119482583</v>
+        <v>2.42200511948259</v>
       </c>
       <c r="G2" t="n">
-        <v>2.216699417292735</v>
+        <v>2.216699417292742</v>
       </c>
       <c r="H2" t="n">
-        <v>2.22256317071131</v>
+        <v>2.222563170711298</v>
       </c>
       <c r="I2" t="n">
-        <v>2.350627214003421</v>
+        <v>2.350627214003437</v>
       </c>
       <c r="J2" t="n">
-        <v>2.267567398011976</v>
+        <v>2.267567398012003</v>
       </c>
       <c r="K2" t="n">
-        <v>2.274033713921657</v>
+        <v>2.274033713921665</v>
       </c>
       <c r="L2" t="n">
-        <v>2.350533580511037</v>
+        <v>2.350533580511029</v>
       </c>
       <c r="M2" t="n">
-        <v>2.213621113897545</v>
+        <v>2.213621113897547</v>
       </c>
       <c r="N2" t="n">
-        <v>2.292627252953004</v>
+        <v>2.292627252953007</v>
       </c>
       <c r="O2" t="n">
-        <v>4.386452093117168</v>
+        <v>4.386452093117184</v>
       </c>
       <c r="P2" t="n">
-        <v>2.202189766539821</v>
+        <v>2.202189766539829</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.289242477521524</v>
+        <v>2.289242477521528</v>
       </c>
       <c r="R2" t="n">
-        <v>2.431973982456113</v>
+        <v>2.431973982456122</v>
       </c>
       <c r="S2" t="n">
-        <v>2.306783059947787</v>
+        <v>2.306783059947794</v>
       </c>
       <c r="T2" t="n">
-        <v>2.240208200009438</v>
+        <v>2.240208200009443</v>
       </c>
       <c r="U2" t="n">
-        <v>2.53172529767942</v>
+        <v>2.531725297679419</v>
       </c>
       <c r="V2" t="n">
-        <v>2.248619088149742</v>
+        <v>2.248619088149751</v>
       </c>
       <c r="W2" t="n">
-        <v>2.731177590300836</v>
+        <v>2.731177590300824</v>
       </c>
       <c r="X2" t="n">
-        <v>2.271663879546756</v>
+        <v>2.271663879546767</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.216810216528307</v>
+        <v>2.216810216528315</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.44331597775345</v>
+        <v>2.443315977753454</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.201028333982749</v>
+        <v>2.201028333982753</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.214283593368801</v>
+        <v>2.214283593368799</v>
       </c>
     </row>
     <row r="3">
@@ -5834,85 +5834,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.617404681465719</v>
+        <v>3.617404681465723</v>
       </c>
       <c r="C3" t="n">
-        <v>2.981736751613495</v>
+        <v>2.981736751613494</v>
       </c>
       <c r="D3" t="n">
-        <v>2.198772782337667</v>
+        <v>2.198772782337652</v>
       </c>
       <c r="E3" t="n">
-        <v>4.490983731414308</v>
+        <v>4.490983731414305</v>
       </c>
       <c r="F3" t="n">
-        <v>3.852472178492927</v>
+        <v>3.852472178492922</v>
       </c>
       <c r="G3" t="n">
-        <v>2.384235446019554</v>
+        <v>2.384235446019545</v>
       </c>
       <c r="H3" t="n">
-        <v>2.429852161192838</v>
+        <v>2.429852161192841</v>
       </c>
       <c r="I3" t="n">
-        <v>3.344004821018561</v>
+        <v>3.344004821018558</v>
       </c>
       <c r="J3" t="n">
-        <v>2.746694082923452</v>
+        <v>2.746694082923465</v>
       </c>
       <c r="K3" t="n">
-        <v>2.792954648351944</v>
+        <v>2.792954648351936</v>
       </c>
       <c r="L3" t="n">
-        <v>3.328205271424118</v>
+        <v>3.328205271424115</v>
       </c>
       <c r="M3" t="n">
-        <v>2.37776670295088</v>
+        <v>2.377766702950877</v>
       </c>
       <c r="N3" t="n">
-        <v>2.927102554167271</v>
+        <v>2.927102554167259</v>
       </c>
       <c r="O3" t="n">
-        <v>6.378654709746904</v>
+        <v>6.378654709746895</v>
       </c>
       <c r="P3" t="n">
-        <v>2.28204421177498</v>
+        <v>2.282044211774978</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.899782969382632</v>
+        <v>2.899782969382622</v>
       </c>
       <c r="R3" t="n">
-        <v>3.927754105699094</v>
+        <v>3.927754105699095</v>
       </c>
       <c r="S3" t="n">
-        <v>3.021252686065803</v>
+        <v>3.021252686065815</v>
       </c>
       <c r="T3" t="n">
-        <v>2.553853439718465</v>
+        <v>2.553853439718454</v>
       </c>
       <c r="U3" t="n">
-        <v>2.836182209134492</v>
+        <v>2.836182209134479</v>
       </c>
       <c r="V3" t="n">
-        <v>2.610887378310266</v>
+        <v>2.610887378310262</v>
       </c>
       <c r="W3" t="n">
-        <v>3.498618996605309</v>
+        <v>3.498618996605292</v>
       </c>
       <c r="X3" t="n">
-        <v>2.777633161681179</v>
+        <v>2.777633161681172</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.387312135943538</v>
+        <v>2.387312135943534</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.339532743917631</v>
+        <v>3.339532743917625</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.274618294886774</v>
+        <v>2.274618294886765</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.382522863765572</v>
+        <v>2.382522863765568</v>
       </c>
     </row>
     <row r="4">
@@ -5922,85 +5922,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.986781619807017</v>
+        <v>3.986781619807035</v>
       </c>
       <c r="C4" t="n">
-        <v>2.796156375954443</v>
+        <v>2.796156375954371</v>
       </c>
       <c r="D4" t="n">
-        <v>1.731423644475435</v>
+        <v>1.731423644475433</v>
       </c>
       <c r="E4" t="n">
-        <v>5.361657400088016</v>
+        <v>5.361657400087832</v>
       </c>
       <c r="F4" t="n">
-        <v>4.347771006972644</v>
+        <v>4.347771006972737</v>
       </c>
       <c r="G4" t="n">
-        <v>2.028748655449181</v>
+        <v>2.028748655449071</v>
       </c>
       <c r="H4" t="n">
-        <v>2.094982447771818</v>
+        <v>2.094982447771737</v>
       </c>
       <c r="I4" t="n">
-        <v>3.54152472912676</v>
+        <v>3.541524729126814</v>
       </c>
       <c r="J4" t="n">
-        <v>2.60254962404288</v>
+        <v>2.60254962404286</v>
       </c>
       <c r="K4" t="n">
-        <v>2.676365910952426</v>
+        <v>2.676365910952306</v>
       </c>
       <c r="L4" t="n">
-        <v>3.540467095756707</v>
+        <v>3.540467095756796</v>
       </c>
       <c r="M4" t="n">
-        <v>2.02010373822039</v>
+        <v>2.020103738220203</v>
       </c>
       <c r="N4" t="n">
-        <v>2.886388487761979</v>
+        <v>2.886388487762063</v>
       </c>
       <c r="O4" t="n">
-        <v>2.885356674560652</v>
+        <v>2.885356674560737</v>
       </c>
       <c r="P4" t="n">
-        <v>1.864855475425908</v>
+        <v>1.864855475425989</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.848155892189797</v>
+        <v>2.848155892189884</v>
       </c>
       <c r="R4" t="n">
-        <v>4.460373900162173</v>
+        <v>4.460373900161997</v>
       </c>
       <c r="S4" t="n">
-        <v>3.046284839760999</v>
+        <v>3.046284839760809</v>
       </c>
       <c r="T4" t="n">
-        <v>2.294291170808706</v>
+        <v>2.294291170808521</v>
       </c>
       <c r="U4" t="n">
-        <v>1.831872758115016</v>
+        <v>1.831872758114942</v>
       </c>
       <c r="V4" t="n">
-        <v>2.384453570887856</v>
+        <v>2.384453570887866</v>
       </c>
       <c r="W4" t="n">
-        <v>2.573677604678961</v>
+        <v>2.573677604678926</v>
       </c>
       <c r="X4" t="n">
-        <v>2.649597541510217</v>
+        <v>2.649597541510302</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.975259423481443</v>
+        <v>1.975259423481421</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.235314096114337</v>
+        <v>3.235314096114146</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.851736560408381</v>
+        <v>1.851736560408189</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.025021102503941</v>
+        <v>2.025021102503876</v>
       </c>
     </row>
     <row r="5">
@@ -6010,85 +6010,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>41.68999509505817</v>
+        <v>41.68999509505814</v>
       </c>
       <c r="C5" t="n">
-        <v>23.39428422748282</v>
+        <v>23.39428422748275</v>
       </c>
       <c r="D5" t="n">
-        <v>5.126607010430639</v>
+        <v>5.126607010430621</v>
       </c>
       <c r="E5" t="n">
-        <v>68.52662950285249</v>
+        <v>68.52662950285261</v>
       </c>
       <c r="F5" t="n">
-        <v>51.68978370704333</v>
+        <v>51.68978370704312</v>
       </c>
       <c r="G5" t="n">
-        <v>9.140256605469995</v>
+        <v>9.140256605469872</v>
       </c>
       <c r="H5" t="n">
-        <v>12.26376685452108</v>
+        <v>12.26376685452101</v>
       </c>
       <c r="I5" t="n">
         <v>37.92764538261454</v>
       </c>
       <c r="J5" t="n">
-        <v>18.99675986109786</v>
+        <v>18.99675986109781</v>
       </c>
       <c r="K5" t="n">
-        <v>20.34644988237159</v>
+        <v>20.34644988237149</v>
       </c>
       <c r="L5" t="n">
-        <v>30.06753529209511</v>
+        <v>30.06753529209517</v>
       </c>
       <c r="M5" t="n">
-        <v>9.664426406946896</v>
+        <v>9.664426406946628</v>
       </c>
       <c r="N5" t="n">
-        <v>8.149086027931904</v>
+        <v>8.149086027931801</v>
       </c>
       <c r="O5" t="n">
-        <v>22.62130488320393</v>
+        <v>22.62130488320372</v>
       </c>
       <c r="P5" t="n">
-        <v>6.948842780931653</v>
+        <v>6.948842780931477</v>
       </c>
       <c r="Q5" t="n">
-        <v>22.4948489409349</v>
+        <v>22.49484894093474</v>
       </c>
       <c r="R5" t="n">
-        <v>55.82351381551901</v>
+        <v>55.82351381551914</v>
       </c>
       <c r="S5" t="n">
         <v>24.07217433456565</v>
       </c>
       <c r="T5" t="n">
-        <v>14.78756962872192</v>
+        <v>14.78756962872168</v>
       </c>
       <c r="U5" t="n">
-        <v>7.149311058588609</v>
+        <v>7.14931105858851</v>
       </c>
       <c r="V5" t="n">
-        <v>14.91096734584533</v>
+        <v>14.91096734584546</v>
       </c>
       <c r="W5" t="n">
-        <v>19.01833941336078</v>
+        <v>19.01833941336083</v>
       </c>
       <c r="X5" t="n">
-        <v>20.69809302720116</v>
+        <v>20.698093027201</v>
       </c>
       <c r="Y5" t="n">
-        <v>10.34700705550343</v>
+        <v>10.34700705550328</v>
       </c>
       <c r="Z5" t="n">
-        <v>27.98202482412752</v>
+        <v>27.98202482412737</v>
       </c>
       <c r="AA5" t="n">
-        <v>7.16418880077102</v>
+        <v>7.164188800771051</v>
       </c>
       <c r="AB5" t="n">
-        <v>10.48830259236143</v>
+        <v>10.48830259236125</v>
       </c>
     </row>
     <row r="6">
@@ -6098,85 +6098,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.393277165234784</v>
+        <v>4.393277165234707</v>
       </c>
       <c r="C6" t="n">
-        <v>5.096220677483911</v>
+        <v>3.202651921382204</v>
       </c>
       <c r="D6" t="n">
-        <v>2.137919189903203</v>
+        <v>2.137919189902992</v>
       </c>
       <c r="E6" t="n">
-        <v>7.661721701617473</v>
+        <v>7.661721701617378</v>
       </c>
       <c r="F6" t="n">
-        <v>6.647835308502104</v>
+        <v>6.647835308502015</v>
       </c>
       <c r="G6" t="n">
-        <v>4.32881295697864</v>
+        <v>2.435244200876814</v>
       </c>
       <c r="H6" t="n">
-        <v>4.395046749301281</v>
+        <v>2.501477993199536</v>
       </c>
       <c r="I6" t="n">
-        <v>3.948020274554531</v>
+        <v>3.948020274554395</v>
       </c>
       <c r="J6" t="n">
-        <v>4.902613925572341</v>
+        <v>3.009045169470686</v>
       </c>
       <c r="K6" t="n">
-        <v>3.082861456380187</v>
+        <v>3.082861456380096</v>
       </c>
       <c r="L6" t="n">
-        <v>5.840531397286158</v>
+        <v>5.840531397285968</v>
       </c>
       <c r="M6" t="n">
-        <v>2.426599283648154</v>
+        <v>4.320168039749747</v>
       </c>
       <c r="N6" t="n">
-        <v>3.277126603926117</v>
+        <v>3.27712660392595</v>
       </c>
       <c r="O6" t="n">
-        <v>3.276094790724805</v>
+        <v>3.276094790724741</v>
       </c>
       <c r="P6" t="n">
-        <v>4.213890859250383</v>
+        <v>2.225627852044993</v>
       </c>
       <c r="Q6" t="n">
-        <v>5.148220193719255</v>
+        <v>3.254651437617527</v>
       </c>
       <c r="R6" t="n">
-        <v>6.760438201691632</v>
+        <v>6.760438201691529</v>
       </c>
       <c r="S6" t="n">
-        <v>5.346349141290461</v>
+        <v>3.452780385188729</v>
       </c>
       <c r="T6" t="n">
-        <v>4.594355472338171</v>
+        <v>4.594355472338067</v>
       </c>
       <c r="U6" t="n">
-        <v>2.293109063846456</v>
+        <v>2.293109063846417</v>
       </c>
       <c r="V6" t="n">
-        <v>2.79094911631563</v>
+        <v>4.684517872417342</v>
       </c>
       <c r="W6" t="n">
-        <v>2.991465701324296</v>
+        <v>2.991465701324377</v>
       </c>
       <c r="X6" t="n">
-        <v>3.056093086937983</v>
+        <v>3.056093086937943</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.444508793617999</v>
+        <v>2.444508793617876</v>
       </c>
       <c r="Z6" t="n">
-        <v>5.535378397643792</v>
+        <v>5.535378397643691</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.258232105836144</v>
+        <v>4.151800861937729</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.413329968780862</v>
+        <v>2.413329968780732</v>
       </c>
     </row>
     <row r="7">
@@ -6186,85 +6186,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.677399874156816</v>
+        <v>4.67739987415669</v>
       </c>
       <c r="C7" t="n">
-        <v>3.48677463030424</v>
+        <v>3.486774630304306</v>
       </c>
       <c r="D7" t="n">
-        <v>2.422041898825234</v>
+        <v>2.422041898825216</v>
       </c>
       <c r="E7" t="n">
-        <v>6.052275654437805</v>
+        <v>6.052275654437728</v>
       </c>
       <c r="F7" t="n">
-        <v>5.038389261322441</v>
+        <v>5.038389261322364</v>
       </c>
       <c r="G7" t="n">
-        <v>2.719366909798974</v>
+        <v>2.719366909798798</v>
       </c>
       <c r="H7" t="n">
-        <v>2.785600702121617</v>
+        <v>2.785600702121477</v>
       </c>
       <c r="I7" t="n">
-        <v>4.23214298347656</v>
+        <v>4.232142983476384</v>
       </c>
       <c r="J7" t="n">
-        <v>3.293167878392675</v>
+        <v>3.293167878392634</v>
       </c>
       <c r="K7" t="n">
-        <v>3.366984165302218</v>
+        <v>3.36698416530212</v>
       </c>
       <c r="L7" t="n">
-        <v>4.231085350106495</v>
+        <v>4.231085350106605</v>
       </c>
       <c r="M7" t="n">
-        <v>2.710721992570185</v>
+        <v>2.710721992570105</v>
       </c>
       <c r="N7" t="n">
-        <v>3.577006742111779</v>
+        <v>3.577006742111691</v>
       </c>
       <c r="O7" t="n">
-        <v>3.575936545294632</v>
+        <v>3.575936545294501</v>
       </c>
       <c r="P7" t="n">
-        <v>2.555435346159882</v>
+        <v>2.555435346159747</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.538774146539593</v>
+        <v>3.538774146539512</v>
       </c>
       <c r="R7" t="n">
-        <v>5.15099215451197</v>
+        <v>5.150992154511894</v>
       </c>
       <c r="S7" t="n">
-        <v>3.736903094110793</v>
+        <v>3.736903094110711</v>
       </c>
       <c r="T7" t="n">
-        <v>2.984909425158505</v>
+        <v>2.984909425158417</v>
       </c>
       <c r="U7" t="n">
-        <v>2.632584824845572</v>
+        <v>2.632584824845378</v>
       </c>
       <c r="V7" t="n">
-        <v>3.07507182523766</v>
+        <v>3.075071825237652</v>
       </c>
       <c r="W7" t="n">
-        <v>3.26429585902876</v>
+        <v>3.264295859028746</v>
       </c>
       <c r="X7" t="n">
-        <v>3.340215795860012</v>
+        <v>3.340215795859931</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.720618438134913</v>
+        <v>2.720618438135034</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.925932350464131</v>
+        <v>3.925932350464045</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.542354814758176</v>
+        <v>2.542354814758093</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.715639356853739</v>
+        <v>2.715639356853705</v>
       </c>
     </row>
     <row r="8">
@@ -6274,85 +6274,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6.289967418251291</v>
+        <v>6.289967418251214</v>
       </c>
       <c r="C8" t="n">
-        <v>6.663441563289796</v>
+        <v>6.663441563289819</v>
       </c>
       <c r="D8" t="n">
-        <v>5.598708831810782</v>
+        <v>5.598708831810651</v>
       </c>
       <c r="E8" t="n">
-        <v>9.228942587423354</v>
+        <v>8.396105801153888</v>
       </c>
       <c r="F8" t="n">
-        <v>6.894625210031776</v>
+        <v>6.894625210031703</v>
       </c>
       <c r="G8" t="n">
-        <v>5.896033842784523</v>
+        <v>6.22036004019094</v>
       </c>
       <c r="H8" t="n">
-        <v>5.962267635107164</v>
+        <v>5.962267635107104</v>
       </c>
       <c r="I8" t="n">
-        <v>7.40880991646211</v>
+        <v>7.408809916462055</v>
       </c>
       <c r="J8" t="n">
-        <v>6.469834811378227</v>
+        <v>6.469834811378177</v>
       </c>
       <c r="K8" t="n">
-        <v>6.54365109828777</v>
+        <v>6.543651098287715</v>
       </c>
       <c r="L8" t="n">
-        <v>7.407752283092048</v>
+        <v>7.407752283091999</v>
       </c>
       <c r="M8" t="n">
-        <v>5.887388925555736</v>
+        <v>5.887388925567155</v>
       </c>
       <c r="N8" t="n">
-        <v>5.541234980265524</v>
+        <v>5.541234980265509</v>
       </c>
       <c r="O8" t="n">
-        <v>5.873391847174442</v>
+        <v>5.87339184717438</v>
       </c>
       <c r="P8" t="n">
-        <v>4.771218051647925</v>
+        <v>4.77121805164782</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.843960462216916</v>
+        <v>4.843960462216883</v>
       </c>
       <c r="R8" t="n">
-        <v>8.327659087497514</v>
+        <v>8.327659087497523</v>
       </c>
       <c r="S8" t="n">
-        <v>6.913570027096343</v>
+        <v>6.913570027096352</v>
       </c>
       <c r="T8" t="n">
-        <v>6.161576358144053</v>
+        <v>6.161576358144056</v>
       </c>
       <c r="U8" t="n">
-        <v>4.831741214312011</v>
+        <v>5.033409671972271</v>
       </c>
       <c r="V8" t="n">
-        <v>6.251738758223205</v>
+        <v>5.871594038637108</v>
       </c>
       <c r="W8" t="n">
-        <v>6.441270181098655</v>
+        <v>6.441270181098534</v>
       </c>
       <c r="X8" t="n">
-        <v>4.788754927673573</v>
+        <v>4.788754927673378</v>
       </c>
       <c r="Y8" t="n">
-        <v>7.525869404481258</v>
+        <v>7.525869404481231</v>
       </c>
       <c r="Z8" t="n">
-        <v>7.102599283449676</v>
+        <v>5.509445945499927</v>
       </c>
       <c r="AA8" t="n">
-        <v>5.719021747743724</v>
+        <v>5.719021747743726</v>
       </c>
       <c r="AB8" t="n">
-        <v>7.526138888245528</v>
+        <v>7.526138888245286</v>
       </c>
     </row>
     <row r="9">
@@ -6362,85 +6362,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>82.68553554592819</v>
+        <v>82.68553554592802</v>
       </c>
       <c r="C9" t="n">
-        <v>103.3032715443615</v>
+        <v>103.3032715443613</v>
       </c>
       <c r="D9" t="n">
         <v>102.2385388128825</v>
       </c>
       <c r="E9" t="n">
-        <v>105.8687725684952</v>
+        <v>100.8354923524829</v>
       </c>
       <c r="F9" t="n">
-        <v>104.8548861753798</v>
+        <v>54.58066042045287</v>
       </c>
       <c r="G9" t="n">
-        <v>102.5358638238563</v>
+        <v>102.5358646091137</v>
       </c>
       <c r="H9" t="n">
-        <v>102.6020976161789</v>
+        <v>102.6020976161787</v>
       </c>
       <c r="I9" t="n">
-        <v>104.0486398975339</v>
+        <v>104.0486398975337</v>
       </c>
       <c r="J9" t="n">
-        <v>103.1096647924501</v>
+        <v>103.10966479245</v>
       </c>
       <c r="K9" t="n">
-        <v>103.1834810793596</v>
+        <v>103.1834810793594</v>
       </c>
       <c r="L9" t="n">
-        <v>104.0475822641639</v>
+        <v>104.047582264164</v>
       </c>
       <c r="M9" t="n">
-        <v>102.5272189066276</v>
+        <v>102.5272189066273</v>
       </c>
       <c r="N9" t="n">
-        <v>103.393503656169</v>
+        <v>103.3935036561687</v>
       </c>
       <c r="O9" t="n">
-        <v>110.6197352485321</v>
+        <v>110.619735248532</v>
       </c>
       <c r="P9" t="n">
-        <v>111.1710396703741</v>
+        <v>111.1710396703739</v>
       </c>
       <c r="Q9" t="n">
-        <v>103.3552718458544</v>
+        <v>103.355271845854</v>
       </c>
       <c r="R9" t="n">
-        <v>104.9674890685692</v>
+        <v>104.967489068569</v>
       </c>
       <c r="S9" t="n">
-        <v>103.5534000081682</v>
+        <v>103.5534000081679</v>
       </c>
       <c r="T9" t="n">
-        <v>102.8014063392159</v>
+        <v>102.8014063392156</v>
       </c>
       <c r="U9" t="n">
-        <v>102.3937286868258</v>
+        <v>102.3937286868255</v>
       </c>
       <c r="V9" t="n">
-        <v>102.8915687392951</v>
+        <v>128.0579557645337</v>
       </c>
       <c r="W9" t="n">
         <v>103.0807927730861</v>
       </c>
       <c r="X9" t="n">
-        <v>103.1567127099174</v>
+        <v>103.1567127099171</v>
       </c>
       <c r="Y9" t="n">
         <v>102.5371153521923</v>
       </c>
       <c r="Z9" t="n">
-        <v>103.7424292645214</v>
+        <v>90.59392702238475</v>
       </c>
       <c r="AA9" t="n">
-        <v>102.3588517288155</v>
+        <v>102.3588517288152</v>
       </c>
       <c r="AB9" t="n">
-        <v>102.5321362709111</v>
+        <v>102.5321362709108</v>
       </c>
     </row>
   </sheetData>
@@ -6606,85 +6606,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.650589221523077</v>
+        <v>2.650589221523078</v>
       </c>
       <c r="C2" t="n">
-        <v>2.578624935182016</v>
+        <v>2.578624935182021</v>
       </c>
       <c r="D2" t="n">
-        <v>2.433993485177948</v>
+        <v>2.433993485177947</v>
       </c>
       <c r="E2" t="n">
-        <v>2.624646245860826</v>
+        <v>2.624646245860828</v>
       </c>
       <c r="F2" t="n">
-        <v>2.504745385364048</v>
+        <v>2.504745385364054</v>
       </c>
       <c r="G2" t="n">
-        <v>2.372640720913896</v>
+        <v>2.372640720913905</v>
       </c>
       <c r="H2" t="n">
-        <v>2.344803977998789</v>
+        <v>2.344803977998792</v>
       </c>
       <c r="I2" t="n">
-        <v>2.403554592298565</v>
+        <v>2.403554592298577</v>
       </c>
       <c r="J2" t="n">
-        <v>2.407138524509064</v>
+        <v>2.407138524509073</v>
       </c>
       <c r="K2" t="n">
-        <v>2.376063456187079</v>
+        <v>2.37606345618708</v>
       </c>
       <c r="L2" t="n">
-        <v>2.460322117285981</v>
+        <v>2.460322117285985</v>
       </c>
       <c r="M2" t="n">
-        <v>2.341752602581927</v>
+        <v>2.341752602581931</v>
       </c>
       <c r="N2" t="n">
-        <v>2.398026834163373</v>
+        <v>2.39802683416338</v>
       </c>
       <c r="O2" t="n">
-        <v>4.666220336154651</v>
+        <v>4.66622033615466</v>
       </c>
       <c r="P2" t="n">
-        <v>2.356973831976486</v>
+        <v>2.356973831976495</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.445751060159645</v>
+        <v>2.445751060159657</v>
       </c>
       <c r="R2" t="n">
-        <v>2.611179584465334</v>
+        <v>2.611179584465339</v>
       </c>
       <c r="S2" t="n">
-        <v>2.429765670346122</v>
+        <v>2.429765670346125</v>
       </c>
       <c r="T2" t="n">
-        <v>2.352983926271685</v>
+        <v>2.352983926271687</v>
       </c>
       <c r="U2" t="n">
-        <v>2.86628861721349</v>
+        <v>2.866288617213477</v>
       </c>
       <c r="V2" t="n">
-        <v>2.401967024606848</v>
+        <v>2.401967024606849</v>
       </c>
       <c r="W2" t="n">
-        <v>3.11163260454202</v>
+        <v>3.111632604542029</v>
       </c>
       <c r="X2" t="n">
-        <v>2.409515243584911</v>
+        <v>2.409515243584918</v>
       </c>
       <c r="Y2" t="n">
         <v>2.37550215456802</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.666183431121758</v>
+        <v>2.666183431121764</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.346082150195892</v>
+        <v>2.346082150195894</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.372224881947642</v>
+        <v>2.372224881947637</v>
       </c>
     </row>
     <row r="3">
@@ -6694,85 +6694,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.59617934913711</v>
+        <v>4.596179349137104</v>
       </c>
       <c r="C3" t="n">
-        <v>3.487274839848317</v>
+        <v>3.48727483984832</v>
       </c>
       <c r="D3" t="n">
-        <v>3.061311181367039</v>
+        <v>3.061311181367033</v>
       </c>
       <c r="E3" t="n">
-        <v>4.413708326270243</v>
+        <v>4.413708326270241</v>
       </c>
       <c r="F3" t="n">
-        <v>3.568842146000944</v>
+        <v>3.568842146000949</v>
       </c>
       <c r="G3" t="n">
-        <v>2.620931209549402</v>
+        <v>2.620931209549405</v>
       </c>
       <c r="H3" t="n">
-        <v>2.425734631101078</v>
+        <v>2.425734631101073</v>
       </c>
       <c r="I3" t="n">
-        <v>2.845428026074766</v>
+        <v>2.845428026074763</v>
       </c>
       <c r="J3" t="n">
-        <v>2.867351365378469</v>
+        <v>2.867351365378472</v>
       </c>
       <c r="K3" t="n">
-        <v>2.647215234274383</v>
+        <v>2.64721523427438</v>
       </c>
       <c r="L3" t="n">
-        <v>3.241339690768554</v>
+        <v>3.241339690768557</v>
       </c>
       <c r="M3" t="n">
-        <v>2.418799105545972</v>
+        <v>2.418799105545976</v>
       </c>
       <c r="N3" t="n">
-        <v>2.804448876183949</v>
+        <v>2.804448876183952</v>
       </c>
       <c r="O3" t="n">
-        <v>6.718961623221252</v>
+        <v>6.718961623221246</v>
       </c>
       <c r="P3" t="n">
-        <v>2.509926303576424</v>
+        <v>2.509926303576422</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.142854004537598</v>
+        <v>3.142854004537601</v>
       </c>
       <c r="R3" t="n">
-        <v>4.332986528934074</v>
+        <v>4.332986528934073</v>
       </c>
       <c r="S3" t="n">
         <v>3.02637587011671</v>
       </c>
       <c r="T3" t="n">
-        <v>2.483494186554846</v>
+        <v>2.48349418655485</v>
       </c>
       <c r="U3" t="n">
-        <v>3.283411346698322</v>
+        <v>3.283411346698305</v>
       </c>
       <c r="V3" t="n">
-        <v>2.829332333745962</v>
+        <v>2.829332333745964</v>
       </c>
       <c r="W3" t="n">
-        <v>4.136269408129407</v>
+        <v>4.136269408129377</v>
       </c>
       <c r="X3" t="n">
-        <v>2.885032053521995</v>
+        <v>2.885032053521993</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.644205882332988</v>
+        <v>2.644205882332994</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.534021530998823</v>
+        <v>3.534021530998835</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.433923359361958</v>
+        <v>2.433923359361955</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.633774070760414</v>
+        <v>2.633774070760418</v>
       </c>
     </row>
     <row r="4">
@@ -6782,85 +6782,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.524632404391246</v>
+        <v>5.524632404391266</v>
       </c>
       <c r="C4" t="n">
-        <v>3.467747976738909</v>
+        <v>3.467747976738896</v>
       </c>
       <c r="D4" t="n">
-        <v>3.078083923411625</v>
+        <v>3.078083923411613</v>
       </c>
       <c r="E4" t="n">
-        <v>5.23159455992772</v>
+        <v>5.231594559927739</v>
       </c>
       <c r="F4" t="n">
-        <v>3.877259183495732</v>
+        <v>3.877259183495737</v>
       </c>
       <c r="G4" t="n">
-        <v>2.385076227383193</v>
+        <v>2.385076227383213</v>
       </c>
       <c r="H4" t="n">
-        <v>2.07064741062263</v>
+        <v>2.070647410622652</v>
       </c>
       <c r="I4" t="n">
-        <v>2.734262625756509</v>
+        <v>2.734262625756513</v>
       </c>
       <c r="J4" t="n">
-        <v>2.7740299872316</v>
+        <v>2.774029987231662</v>
       </c>
       <c r="K4" t="n">
-        <v>2.423737596829767</v>
+        <v>2.423737596829797</v>
       </c>
       <c r="L4" t="n">
-        <v>3.375477934841003</v>
+        <v>3.375477934840996</v>
       </c>
       <c r="M4" t="n">
-        <v>2.064914042874881</v>
+        <v>2.064914042874912</v>
       </c>
       <c r="N4" t="n">
-        <v>2.671824054725068</v>
+        <v>2.671824054725108</v>
       </c>
       <c r="O4" t="n">
-        <v>3.032944481459931</v>
+        <v>3.032944481459957</v>
       </c>
       <c r="P4" t="n">
-        <v>2.208111509710158</v>
+        <v>2.208111509710177</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.210891141581611</v>
+        <v>3.210891141581619</v>
       </c>
       <c r="R4" t="n">
-        <v>5.079482424495332</v>
+        <v>5.079482424495326</v>
       </c>
       <c r="S4" t="n">
-        <v>3.030328809995266</v>
+        <v>3.030328809995237</v>
       </c>
       <c r="T4" t="n">
-        <v>2.163043689327075</v>
+        <v>2.163043689327099</v>
       </c>
       <c r="U4" t="n">
-        <v>2.017156271564223</v>
+        <v>2.01715627156422</v>
       </c>
       <c r="V4" t="n">
-        <v>2.711955292826182</v>
+        <v>2.71195529282622</v>
       </c>
       <c r="W4" t="n">
-        <v>2.991409839150101</v>
+        <v>2.991409839150156</v>
       </c>
       <c r="X4" t="n">
-        <v>2.801590924070771</v>
+        <v>2.801590924070741</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.366146490883408</v>
+        <v>2.366146490883414</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.277548673809609</v>
+        <v>3.277548673809618</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.085084953577178</v>
+        <v>2.085084953577148</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.402059264149773</v>
+        <v>2.402059264149829</v>
       </c>
     </row>
     <row r="5">
@@ -6870,85 +6870,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>63.59281412519803</v>
+        <v>63.59281412519798</v>
       </c>
       <c r="C5" t="n">
-        <v>32.53767737842997</v>
+        <v>32.5376773784301</v>
       </c>
       <c r="D5" t="n">
-        <v>26.01499084361966</v>
+        <v>26.01499084361965</v>
       </c>
       <c r="E5" t="n">
-        <v>59.80153867070242</v>
+        <v>59.80153867070246</v>
       </c>
       <c r="F5" t="n">
-        <v>41.48214494540355</v>
+        <v>41.48214494540356</v>
       </c>
       <c r="G5" t="n">
-        <v>12.46128640963282</v>
+        <v>12.46128640963275</v>
       </c>
       <c r="H5" t="n">
-        <v>8.70125814552048</v>
+        <v>8.701258145520468</v>
       </c>
       <c r="I5" t="n">
-        <v>20.63911321728364</v>
+        <v>20.63911321728362</v>
       </c>
       <c r="J5" t="n">
-        <v>19.46009267177326</v>
+        <v>19.46009267177329</v>
       </c>
       <c r="K5" t="n">
-        <v>14.10679396939642</v>
+        <v>14.10679396939643</v>
       </c>
       <c r="L5" t="n">
-        <v>27.19115440406166</v>
+        <v>27.1911544040616</v>
       </c>
       <c r="M5" t="n">
-        <v>8.20128928312656</v>
+        <v>8.201289283126524</v>
       </c>
       <c r="N5" t="n">
-        <v>8.226112978231102</v>
+        <v>8.22611297823109</v>
       </c>
       <c r="O5" t="n">
-        <v>22.56136866507778</v>
+        <v>22.56136866507777</v>
       </c>
       <c r="P5" t="n">
-        <v>9.751374459820902</v>
+        <v>9.751374459820893</v>
       </c>
       <c r="Q5" t="n">
-        <v>27.13489663857446</v>
+        <v>27.13489663857451</v>
       </c>
       <c r="R5" t="n">
-        <v>65.08688848810837</v>
+        <v>65.08688848810847</v>
       </c>
       <c r="S5" t="n">
-        <v>22.70299876342376</v>
+        <v>22.70299876342373</v>
       </c>
       <c r="T5" t="n">
-        <v>10.0135470882213</v>
+        <v>10.01354708822131</v>
       </c>
       <c r="U5" t="n">
-        <v>7.622696141017879</v>
+        <v>7.622696141017859</v>
       </c>
       <c r="V5" t="n">
         <v>17.84816128300949</v>
       </c>
       <c r="W5" t="n">
-        <v>23.69931573985128</v>
+        <v>23.69931573985117</v>
       </c>
       <c r="X5" t="n">
-        <v>20.30767244649843</v>
+        <v>20.30767244649837</v>
       </c>
       <c r="Y5" t="n">
-        <v>14.51116490141012</v>
+        <v>14.51116490141009</v>
       </c>
       <c r="Z5" t="n">
-        <v>25.68490431401877</v>
+        <v>25.68490431401876</v>
       </c>
       <c r="AA5" t="n">
         <v>8.472769223547211</v>
       </c>
       <c r="AB5" t="n">
-        <v>14.85086972372423</v>
+        <v>14.85086972372427</v>
       </c>
     </row>
     <row r="6">
@@ -6958,85 +6958,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7.977694846359458</v>
+        <v>7.977694846359491</v>
       </c>
       <c r="C6" t="n">
-        <v>5.920810418707076</v>
+        <v>5.920810418707053</v>
       </c>
       <c r="D6" t="n">
-        <v>5.531146365379807</v>
+        <v>5.531146365379798</v>
       </c>
       <c r="E6" t="n">
-        <v>7.68465700189594</v>
+        <v>7.684657001895929</v>
       </c>
       <c r="F6" t="n">
-        <v>4.350578670018227</v>
+        <v>6.330321625463944</v>
       </c>
       <c r="G6" t="n">
-        <v>2.858395713905696</v>
+        <v>4.838138669351438</v>
       </c>
       <c r="H6" t="n">
-        <v>2.543966897145141</v>
+        <v>2.543966897145126</v>
       </c>
       <c r="I6" t="n">
-        <v>5.187325067724709</v>
+        <v>3.207582112279023</v>
       </c>
       <c r="J6" t="n">
-        <v>5.227092429199867</v>
+        <v>3.24734947375415</v>
       </c>
       <c r="K6" t="n">
-        <v>2.897057083352294</v>
+        <v>4.876800038798022</v>
       </c>
       <c r="L6" t="n">
-        <v>5.828540376809188</v>
+        <v>5.828540376809143</v>
       </c>
       <c r="M6" t="n">
-        <v>4.517976484843105</v>
+        <v>4.517976484843166</v>
       </c>
       <c r="N6" t="n">
-        <v>3.132285554028919</v>
+        <v>3.132285554028915</v>
       </c>
       <c r="O6" t="n">
-        <v>3.493405980763783</v>
+        <v>5.549863471261485</v>
       </c>
       <c r="P6" t="n">
-        <v>4.725737986107869</v>
+        <v>4.725737986107858</v>
       </c>
       <c r="Q6" t="n">
-        <v>5.663953583549807</v>
+        <v>5.663953583549817</v>
       </c>
       <c r="R6" t="n">
-        <v>7.53254486646351</v>
+        <v>5.552801911017797</v>
       </c>
       <c r="S6" t="n">
-        <v>3.503648296517747</v>
+        <v>3.503648296517729</v>
       </c>
       <c r="T6" t="n">
-        <v>4.616106131295292</v>
+        <v>4.616106131295276</v>
       </c>
       <c r="U6" t="n">
-        <v>4.521469659480051</v>
+        <v>4.521469659480098</v>
       </c>
       <c r="V6" t="n">
-        <v>3.185274779348716</v>
+        <v>3.185274779348704</v>
       </c>
       <c r="W6" t="n">
-        <v>5.507590359427728</v>
+        <v>5.507590359427716</v>
       </c>
       <c r="X6" t="n">
-        <v>5.254653366038946</v>
+        <v>3.27491041059325</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.908191280816306</v>
+        <v>2.908191280816296</v>
       </c>
       <c r="Z6" t="n">
-        <v>5.730611115777795</v>
+        <v>3.750868160332102</v>
       </c>
       <c r="AA6" t="n">
-        <v>4.538147395545334</v>
+        <v>2.558404440099635</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.859969242441064</v>
+        <v>2.859969242441051</v>
       </c>
     </row>
     <row r="7">
@@ -7046,85 +7046,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6.254362628447961</v>
+        <v>6.254362628447939</v>
       </c>
       <c r="C7" t="n">
-        <v>4.197478200795583</v>
+        <v>4.197478200795564</v>
       </c>
       <c r="D7" t="n">
-        <v>3.807814147468315</v>
+        <v>3.807814147468294</v>
       </c>
       <c r="E7" t="n">
-        <v>5.96132478398444</v>
+        <v>5.961324783984442</v>
       </c>
       <c r="F7" t="n">
-        <v>4.60698940755242</v>
+        <v>4.60698940755243</v>
       </c>
       <c r="G7" t="n">
-        <v>3.114806451439886</v>
+        <v>3.114806451439882</v>
       </c>
       <c r="H7" t="n">
-        <v>2.800377634679335</v>
+        <v>2.800377634679324</v>
       </c>
       <c r="I7" t="n">
-        <v>3.46399284981321</v>
+        <v>3.463992849813199</v>
       </c>
       <c r="J7" t="n">
-        <v>3.503760211288371</v>
+        <v>3.503760211288368</v>
       </c>
       <c r="K7" t="n">
-        <v>3.153467820886487</v>
+        <v>3.153467820886497</v>
       </c>
       <c r="L7" t="n">
-        <v>4.105208158897699</v>
+        <v>4.105208158897697</v>
       </c>
       <c r="M7" t="n">
-        <v>2.794644266931612</v>
+        <v>2.794644266931609</v>
       </c>
       <c r="N7" t="n">
-        <v>3.401554278781787</v>
+        <v>3.401554278781765</v>
       </c>
       <c r="O7" t="n">
-        <v>3.762637269624944</v>
+        <v>3.762637269624935</v>
       </c>
       <c r="P7" t="n">
-        <v>2.937804297875172</v>
+        <v>2.937804297875159</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.940621365638314</v>
+        <v>3.940621365638302</v>
       </c>
       <c r="R7" t="n">
-        <v>5.809212648552004</v>
+        <v>5.809212648552</v>
       </c>
       <c r="S7" t="n">
-        <v>3.760059034051942</v>
+        <v>3.760059034051903</v>
       </c>
       <c r="T7" t="n">
-        <v>2.892773913383798</v>
+        <v>2.892773913383793</v>
       </c>
       <c r="U7" t="n">
-        <v>2.854327825542873</v>
+        <v>2.854327825542864</v>
       </c>
       <c r="V7" t="n">
-        <v>3.441685516882904</v>
+        <v>3.441685516882881</v>
       </c>
       <c r="W7" t="n">
-        <v>3.721140063206848</v>
+        <v>3.721140063206819</v>
       </c>
       <c r="X7" t="n">
-        <v>3.531321148127436</v>
+        <v>3.531321148127419</v>
       </c>
       <c r="Y7" t="n">
-        <v>3.147127660887737</v>
+        <v>3.147127660887727</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.007278897866297</v>
+        <v>4.007278897866291</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.814815177633847</v>
+        <v>2.814815177633838</v>
       </c>
       <c r="AB7" t="n">
-        <v>3.131789488206524</v>
+        <v>3.131789488206513</v>
       </c>
     </row>
     <row r="8">
@@ -7134,85 +7134,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7.924299262156531</v>
+        <v>7.924299262156331</v>
       </c>
       <c r="C8" t="n">
-        <v>7.543069154884455</v>
+        <v>7.543069154884293</v>
       </c>
       <c r="D8" t="n">
-        <v>7.153405101557142</v>
+        <v>7.153405101557065</v>
       </c>
       <c r="E8" t="n">
-        <v>9.306915738073322</v>
+        <v>8.414679241716874</v>
       </c>
       <c r="F8" t="n">
-        <v>6.537973400297216</v>
+        <v>6.537973400297121</v>
       </c>
       <c r="G8" t="n">
-        <v>6.46039740552873</v>
+        <v>6.807855244582824</v>
       </c>
       <c r="H8" t="n">
-        <v>6.145968588768266</v>
+        <v>6.145968588768057</v>
       </c>
       <c r="I8" t="n">
-        <v>6.809583803902053</v>
+        <v>6.809583803901933</v>
       </c>
       <c r="J8" t="n">
-        <v>6.849351165377353</v>
+        <v>6.849351165377102</v>
       </c>
       <c r="K8" t="n">
-        <v>6.499058774975423</v>
+        <v>6.499058774975198</v>
       </c>
       <c r="L8" t="n">
-        <v>7.450799112986478</v>
+        <v>7.450799112986454</v>
       </c>
       <c r="M8" t="n">
-        <v>6.140235221020479</v>
+        <v>6.14023522103518</v>
       </c>
       <c r="N8" t="n">
-        <v>5.448232803080422</v>
+        <v>5.448232803080275</v>
       </c>
       <c r="O8" t="n">
-        <v>6.166305642457326</v>
+        <v>6.166305642457167</v>
       </c>
       <c r="P8" t="n">
-        <v>5.253975009333006</v>
+        <v>5.253975009332916</v>
       </c>
       <c r="Q8" t="n">
-        <v>5.2812536811459</v>
+        <v>5.281253681145831</v>
       </c>
       <c r="R8" t="n">
-        <v>9.154803602640776</v>
+        <v>9.154803602640726</v>
       </c>
       <c r="S8" t="n">
-        <v>7.105649988140826</v>
+        <v>7.105649988140701</v>
       </c>
       <c r="T8" t="n">
-        <v>6.238364867472586</v>
+        <v>6.238364867472557</v>
       </c>
       <c r="U8" t="n">
-        <v>5.153534436500472</v>
+        <v>5.369439065157617</v>
       </c>
       <c r="V8" t="n">
-        <v>6.787276470971825</v>
+        <v>6.377357026289527</v>
       </c>
       <c r="W8" t="n">
-        <v>7.067060328826869</v>
+        <v>7.06706032882681</v>
       </c>
       <c r="X8" t="n">
-        <v>5.025530510106853</v>
+        <v>5.025530510106757</v>
       </c>
       <c r="Y8" t="n">
-        <v>8.23332801977682</v>
+        <v>8.233328019776431</v>
       </c>
       <c r="Z8" t="n">
-        <v>7.352869851955189</v>
+        <v>5.646089392521524</v>
       </c>
       <c r="AA8" t="n">
-        <v>6.160406131722693</v>
+        <v>6.160406131722551</v>
       </c>
       <c r="AB8" t="n">
-        <v>8.227741493467867</v>
+        <v>8.227741493467564</v>
       </c>
     </row>
     <row r="9">
@@ -7222,22 +7222,22 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>84.21149488583879</v>
+        <v>84.21149488583885</v>
       </c>
       <c r="C9" t="n">
         <v>103.9815553552297</v>
       </c>
       <c r="D9" t="n">
-        <v>103.5918913019026</v>
+        <v>103.5918913019025</v>
       </c>
       <c r="E9" t="n">
-        <v>105.7454019384187</v>
+        <v>100.7078327366174</v>
       </c>
       <c r="F9" t="n">
-        <v>104.3910665619865</v>
+        <v>54.07400033294844</v>
       </c>
       <c r="G9" t="n">
-        <v>102.898883605874</v>
+        <v>102.8988844508396</v>
       </c>
       <c r="H9" t="n">
         <v>102.5844547891136</v>
@@ -7255,7 +7255,7 @@
         <v>103.8892853133317</v>
       </c>
       <c r="M9" t="n">
-        <v>102.5787214213658</v>
+        <v>102.5787214213659</v>
       </c>
       <c r="N9" t="n">
         <v>103.185631433216</v>
@@ -7264,7 +7264,7 @@
         <v>110.7801739438636</v>
       </c>
       <c r="P9" t="n">
-        <v>111.5284859869812</v>
+        <v>111.5284859869813</v>
       </c>
       <c r="Q9" t="n">
         <v>103.7246993650378</v>
@@ -7282,10 +7282,10 @@
         <v>102.5822145960027</v>
       </c>
       <c r="V9" t="n">
-        <v>103.225762671317</v>
+        <v>128.4135949275972</v>
       </c>
       <c r="W9" t="n">
-        <v>103.505217217641</v>
+        <v>103.5052172176411</v>
       </c>
       <c r="X9" t="n">
         <v>103.3153983025615</v>
@@ -7294,13 +7294,13 @@
         <v>102.931204815322</v>
       </c>
       <c r="Z9" t="n">
-        <v>103.7913560523004</v>
+        <v>90.63164954257763</v>
       </c>
       <c r="AA9" t="n">
-        <v>102.598892332068</v>
+        <v>102.5988923320681</v>
       </c>
       <c r="AB9" t="n">
-        <v>102.9158666426409</v>
+        <v>102.915866642641</v>
       </c>
     </row>
   </sheetData>
@@ -7466,85 +7466,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.037577912700886</v>
+        <v>2.03757791270089</v>
       </c>
       <c r="C2" t="n">
-        <v>2.051035913546635</v>
+        <v>2.051035913546658</v>
       </c>
       <c r="D2" t="n">
-        <v>1.990298494011219</v>
+        <v>1.990298494011227</v>
       </c>
       <c r="E2" t="n">
-        <v>2.079001449700344</v>
+        <v>2.079001449700356</v>
       </c>
       <c r="F2" t="n">
-        <v>2.065143550140277</v>
+        <v>2.065143550140285</v>
       </c>
       <c r="G2" t="n">
-        <v>2.110625717689917</v>
+        <v>2.11062571768993</v>
       </c>
       <c r="H2" t="n">
-        <v>1.998446451334846</v>
+        <v>1.998446451334855</v>
       </c>
       <c r="I2" t="n">
-        <v>2.093303972311619</v>
+        <v>2.093303972311629</v>
       </c>
       <c r="J2" t="n">
-        <v>2.06507000686146</v>
+        <v>2.06507000686147</v>
       </c>
       <c r="K2" t="n">
-        <v>2.100050027558154</v>
+        <v>2.100050027558162</v>
       </c>
       <c r="L2" t="n">
-        <v>2.121539190491628</v>
+        <v>2.121539190491636</v>
       </c>
       <c r="M2" t="n">
-        <v>2.118658891374253</v>
+        <v>2.118658891374261</v>
       </c>
       <c r="N2" t="n">
-        <v>2.01911942844828</v>
+        <v>2.019119428448289</v>
       </c>
       <c r="O2" t="n">
-        <v>3.765533482809092</v>
+        <v>3.765533482809097</v>
       </c>
       <c r="P2" t="n">
-        <v>2.036308061873501</v>
+        <v>2.036308061873514</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.068789955436086</v>
+        <v>2.068789955436093</v>
       </c>
       <c r="R2" t="n">
-        <v>2.067129225849696</v>
+        <v>2.067129225849703</v>
       </c>
       <c r="S2" t="n">
-        <v>2.087533202675914</v>
+        <v>2.087533202675923</v>
       </c>
       <c r="T2" t="n">
-        <v>2.02761736406133</v>
+        <v>2.027617364061339</v>
       </c>
       <c r="U2" t="n">
-        <v>2.08653778828179</v>
+        <v>2.086537788281818</v>
       </c>
       <c r="V2" t="n">
-        <v>2.018754040858604</v>
+        <v>2.018754040858612</v>
       </c>
       <c r="W2" t="n">
-        <v>2.143916036232167</v>
+        <v>2.143916036232193</v>
       </c>
       <c r="X2" t="n">
-        <v>2.083100666581022</v>
+        <v>2.083100666581031</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.026314616528684</v>
+        <v>2.026314616528694</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.848696594074505</v>
+        <v>1.848696594074517</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.016228940178268</v>
+        <v>2.016228940178275</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.060114601461069</v>
+        <v>2.060114601461079</v>
       </c>
     </row>
     <row r="3">
@@ -7554,85 +7554,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.377155967619092</v>
+        <v>2.377155967619095</v>
       </c>
       <c r="C3" t="n">
-        <v>2.333726664003256</v>
+        <v>2.333726664003285</v>
       </c>
       <c r="D3" t="n">
-        <v>2.041909847195258</v>
+        <v>2.041909847195263</v>
       </c>
       <c r="E3" t="n">
-        <v>2.674743263929062</v>
+        <v>2.674743263929068</v>
       </c>
       <c r="F3" t="n">
-        <v>2.577399095246955</v>
+        <v>2.577399095246963</v>
       </c>
       <c r="G3" t="n">
-        <v>2.895572881316167</v>
+        <v>2.895572881316179</v>
       </c>
       <c r="H3" t="n">
-        <v>2.100644568236684</v>
+        <v>2.100644568236691</v>
       </c>
       <c r="I3" t="n">
-        <v>2.779323567534995</v>
+        <v>2.779323567534998</v>
       </c>
       <c r="J3" t="n">
-        <v>2.573285555259062</v>
+        <v>2.573285555259073</v>
       </c>
       <c r="K3" t="n">
-        <v>2.82243255295802</v>
+        <v>2.822432552958025</v>
       </c>
       <c r="L3" t="n">
-        <v>2.97616858478015</v>
+        <v>2.976168584780161</v>
       </c>
       <c r="M3" t="n">
-        <v>2.955409601720075</v>
+        <v>2.955409601720088</v>
       </c>
       <c r="N3" t="n">
-        <v>2.247693016525358</v>
+        <v>2.247693016525365</v>
       </c>
       <c r="O3" t="n">
-        <v>5.075308592845168</v>
+        <v>5.075308592845193</v>
       </c>
       <c r="P3" t="n">
-        <v>2.36858919621394</v>
+        <v>2.368589196213943</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.601940122594856</v>
+        <v>2.601940122594863</v>
       </c>
       <c r="R3" t="n">
-        <v>2.592874229911169</v>
+        <v>2.592874229911176</v>
       </c>
       <c r="S3" t="n">
-        <v>2.730950151315487</v>
+        <v>2.730950151315496</v>
       </c>
       <c r="T3" t="n">
-        <v>2.309038691550107</v>
+        <v>2.309038691550116</v>
       </c>
       <c r="U3" t="n">
-        <v>2.485430125566619</v>
+        <v>2.485430125566632</v>
       </c>
       <c r="V3" t="n">
-        <v>2.243264804836977</v>
+        <v>2.243264804836986</v>
       </c>
       <c r="W3" t="n">
-        <v>2.349432269206925</v>
+        <v>2.349432269206965</v>
       </c>
       <c r="X3" t="n">
-        <v>2.705423861748479</v>
+        <v>2.705423861748488</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.298587080162579</v>
+        <v>2.298587080162587</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.934053044083737</v>
+        <v>1.934053044083752</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.226742770317738</v>
+        <v>2.226742770317741</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.543707981650732</v>
+        <v>2.543707981650743</v>
       </c>
     </row>
     <row r="4">
@@ -7642,82 +7642,82 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.000292367139457</v>
+        <v>2.000292367139468</v>
       </c>
       <c r="C4" t="n">
-        <v>1.863358983772317</v>
+        <v>1.863358983772321</v>
       </c>
       <c r="D4" t="n">
-        <v>1.466249583432532</v>
+        <v>1.466249583432528</v>
       </c>
       <c r="E4" t="n">
-        <v>2.468190273316818</v>
+        <v>2.468190273316821</v>
       </c>
       <c r="F4" t="n">
-        <v>2.31165892283709</v>
+        <v>2.311658922837098</v>
       </c>
       <c r="G4" t="n">
-        <v>2.825400928141028</v>
+        <v>2.825400928141035</v>
       </c>
       <c r="H4" t="n">
-        <v>1.558284509648417</v>
+        <v>1.55828450964843</v>
       </c>
       <c r="I4" t="n">
-        <v>2.629743845696633</v>
+        <v>2.629743845696638</v>
       </c>
       <c r="J4" t="n">
-        <v>2.309847496562002</v>
+        <v>2.309847496562007</v>
       </c>
       <c r="K4" t="n">
-        <v>2.705943643044942</v>
+        <v>2.705943643044946</v>
       </c>
       <c r="L4" t="n">
-        <v>2.948673623881902</v>
+        <v>2.948673623881903</v>
       </c>
       <c r="M4" t="n">
-        <v>2.913329478416008</v>
+        <v>2.913329478416012</v>
       </c>
       <c r="N4" t="n">
-        <v>1.79179529618399</v>
+        <v>1.791795296183999</v>
       </c>
       <c r="O4" t="n">
-        <v>1.681406435895064</v>
+        <v>1.681406435895072</v>
       </c>
       <c r="P4" t="n">
-        <v>1.985948817883887</v>
+        <v>1.985948817883895</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.352846748082559</v>
+        <v>2.352846748082566</v>
       </c>
       <c r="R4" t="n">
-        <v>2.334088043430941</v>
+        <v>2.334088043430942</v>
       </c>
       <c r="S4" t="n">
-        <v>2.56456034797612</v>
+        <v>2.564560347976129</v>
       </c>
       <c r="T4" t="n">
-        <v>1.887783388176897</v>
+        <v>1.887783388176904</v>
       </c>
       <c r="U4" t="n">
-        <v>1.968040664556321</v>
+        <v>1.968040664556332</v>
       </c>
       <c r="V4" t="n">
-        <v>1.78144379992344</v>
+        <v>1.78144379992341</v>
       </c>
       <c r="W4" t="n">
-        <v>1.577849903742705</v>
+        <v>1.577849903742717</v>
       </c>
       <c r="X4" t="n">
-        <v>2.51449281371697</v>
+        <v>2.514492813716974</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.786585133255778</v>
+        <v>1.786585133255789</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.72805744180519</v>
+        <v>1.728057441805193</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.759145901483857</v>
+        <v>1.759145901483872</v>
       </c>
       <c r="AB4" t="n">
         <v>2.255792168687929</v>
@@ -7730,85 +7730,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>13.58636307449131</v>
+        <v>13.58636307449132</v>
       </c>
       <c r="C5" t="n">
-        <v>12.23408381916859</v>
+        <v>12.23408381916858</v>
       </c>
       <c r="D5" t="n">
-        <v>4.706399406108279</v>
+        <v>4.706399406108281</v>
       </c>
       <c r="E5" t="n">
-        <v>23.51529712278078</v>
+        <v>23.51529712278084</v>
       </c>
       <c r="F5" t="n">
         <v>21.42341019664516</v>
       </c>
       <c r="G5" t="n">
-        <v>27.55851590190531</v>
+        <v>27.55851590190533</v>
       </c>
       <c r="H5" t="n">
-        <v>6.77045861281494</v>
+        <v>6.770458612814984</v>
       </c>
       <c r="I5" t="n">
         <v>27.96170026677659</v>
       </c>
       <c r="J5" t="n">
-        <v>19.41088238694677</v>
+        <v>19.41088238694682</v>
       </c>
       <c r="K5" t="n">
-        <v>26.60061309237806</v>
+        <v>26.60061309237804</v>
       </c>
       <c r="L5" t="n">
-        <v>31.39412764478612</v>
+        <v>31.39412764478618</v>
       </c>
       <c r="M5" t="n">
-        <v>31.46246689376264</v>
+        <v>31.46246689376263</v>
       </c>
       <c r="N5" t="n">
-        <v>14.98584746390331</v>
+        <v>14.98584746390333</v>
       </c>
       <c r="O5" t="n">
-        <v>7.964605733009274</v>
+        <v>7.964605733009294</v>
       </c>
       <c r="P5" t="n">
-        <v>13.59112895832249</v>
+        <v>13.5911289583225</v>
       </c>
       <c r="Q5" t="n">
-        <v>21.37710653025082</v>
+        <v>21.37710653025084</v>
       </c>
       <c r="R5" t="n">
-        <v>22.57231337568148</v>
+        <v>22.57231337568145</v>
       </c>
       <c r="S5" t="n">
-        <v>22.73206968184126</v>
+        <v>22.73206968184125</v>
       </c>
       <c r="T5" t="n">
-        <v>13.11174728924908</v>
+        <v>13.11174728924906</v>
       </c>
       <c r="U5" t="n">
-        <v>15.24857595452201</v>
+        <v>15.24857595452207</v>
       </c>
       <c r="V5" t="n">
-        <v>9.813324817229985</v>
+        <v>9.813324817229988</v>
       </c>
       <c r="W5" t="n">
-        <v>6.673413587476897</v>
+        <v>6.673413587476995</v>
       </c>
       <c r="X5" t="n">
-        <v>25.18289910362824</v>
+        <v>25.18289910362833</v>
       </c>
       <c r="Y5" t="n">
-        <v>12.19180575183186</v>
+        <v>12.19180575183188</v>
       </c>
       <c r="Z5" t="n">
-        <v>8.944332951114863</v>
+        <v>8.944332951114861</v>
       </c>
       <c r="AA5" t="n">
-        <v>10.11433549330859</v>
+        <v>10.11433549330864</v>
       </c>
       <c r="AB5" t="n">
-        <v>21.3077419968625</v>
+        <v>21.30774199686251</v>
       </c>
     </row>
     <row r="6">
@@ -7818,85 +7818,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.239442089128833</v>
+        <v>4.239442089128914</v>
       </c>
       <c r="C6" t="n">
-        <v>2.182569127890414</v>
+        <v>2.18256912789044</v>
       </c>
       <c r="D6" t="n">
-        <v>3.705399305421903</v>
+        <v>3.70539930542199</v>
       </c>
       <c r="E6" t="n">
-        <v>4.707339995306277</v>
+        <v>4.707339995306278</v>
       </c>
       <c r="F6" t="n">
-        <v>4.550808644826525</v>
+        <v>4.550808644826552</v>
       </c>
       <c r="G6" t="n">
-        <v>3.144611072259141</v>
+        <v>3.144611072259149</v>
       </c>
       <c r="H6" t="n">
-        <v>3.797434231637822</v>
+        <v>3.79743423163788</v>
       </c>
       <c r="I6" t="n">
-        <v>2.948953989814739</v>
+        <v>2.94895398981476</v>
       </c>
       <c r="J6" t="n">
-        <v>4.548997218551425</v>
+        <v>2.629057640680119</v>
       </c>
       <c r="K6" t="n">
-        <v>3.025153787163051</v>
+        <v>3.025153787163077</v>
       </c>
       <c r="L6" t="n">
-        <v>3.267883768000007</v>
+        <v>5.187823345871362</v>
       </c>
       <c r="M6" t="n">
-        <v>5.15247920040546</v>
+        <v>5.15247920040547</v>
       </c>
       <c r="N6" t="n">
-        <v>2.107589407247507</v>
+        <v>2.107589407247525</v>
       </c>
       <c r="O6" t="n">
-        <v>1.997200546958581</v>
+        <v>1.997200546958617</v>
       </c>
       <c r="P6" t="n">
-        <v>4.288934533703999</v>
+        <v>4.288934533704013</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.672056892200671</v>
+        <v>4.591996470072005</v>
       </c>
       <c r="R6" t="n">
-        <v>4.573237765420375</v>
+        <v>4.5732377654204</v>
       </c>
       <c r="S6" t="n">
-        <v>4.803710069965551</v>
+        <v>4.803710069965589</v>
       </c>
       <c r="T6" t="n">
-        <v>4.126933110166363</v>
+        <v>2.206993532295018</v>
       </c>
       <c r="U6" t="n">
-        <v>4.293673508792131</v>
+        <v>4.293673508792184</v>
       </c>
       <c r="V6" t="n">
-        <v>2.100653944041524</v>
+        <v>4.020593521912852</v>
       </c>
       <c r="W6" t="n">
-        <v>1.911276599201204</v>
+        <v>1.911276599201239</v>
       </c>
       <c r="X6" t="n">
-        <v>4.753642535706447</v>
+        <v>2.833702957835105</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.204003001090854</v>
+        <v>2.204003001090896</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.047267585923294</v>
+        <v>2.047267585923316</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.998295623473227</v>
+        <v>3.998295623473316</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.573871796305425</v>
+        <v>2.573871796305447</v>
       </c>
     </row>
     <row r="7">
@@ -7906,85 +7906,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.648739665106354</v>
+        <v>2.648739665106364</v>
       </c>
       <c r="C7" t="n">
-        <v>2.511806281739206</v>
+        <v>2.511806281739225</v>
       </c>
       <c r="D7" t="n">
-        <v>2.114696881399416</v>
+        <v>2.114696881399435</v>
       </c>
       <c r="E7" t="n">
-        <v>3.116637571283717</v>
+        <v>3.116637571283753</v>
       </c>
       <c r="F7" t="n">
-        <v>2.960106220803984</v>
+        <v>2.960106220803993</v>
       </c>
       <c r="G7" t="n">
-        <v>3.473848226107925</v>
+        <v>3.473848226107952</v>
       </c>
       <c r="H7" t="n">
-        <v>2.206731807615306</v>
+        <v>2.206731807615335</v>
       </c>
       <c r="I7" t="n">
-        <v>3.278191143663522</v>
+        <v>3.278191143663534</v>
       </c>
       <c r="J7" t="n">
-        <v>2.95829479452888</v>
+        <v>2.958294794528927</v>
       </c>
       <c r="K7" t="n">
-        <v>3.354390941011835</v>
+        <v>3.354390941011856</v>
       </c>
       <c r="L7" t="n">
-        <v>3.597120921848793</v>
+        <v>3.59712092184882</v>
       </c>
       <c r="M7" t="n">
-        <v>3.561776776382895</v>
+        <v>3.561776776382922</v>
       </c>
       <c r="N7" t="n">
-        <v>2.440242594150882</v>
+        <v>2.440242594150903</v>
       </c>
       <c r="O7" t="n">
-        <v>2.32983832822242</v>
+        <v>2.329838328222438</v>
       </c>
       <c r="P7" t="n">
-        <v>2.63438071021125</v>
+        <v>2.634380710211277</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.001294046049452</v>
+        <v>3.001294046049467</v>
       </c>
       <c r="R7" t="n">
-        <v>2.982535341397831</v>
+        <v>2.982535341397853</v>
       </c>
       <c r="S7" t="n">
-        <v>3.213007645943005</v>
+        <v>3.213007645943045</v>
       </c>
       <c r="T7" t="n">
-        <v>2.53623068614379</v>
+        <v>2.536230686143817</v>
       </c>
       <c r="U7" t="n">
-        <v>2.715581056246517</v>
+        <v>2.715581056246543</v>
       </c>
       <c r="V7" t="n">
-        <v>2.429891097890274</v>
+        <v>2.42989109789032</v>
       </c>
       <c r="W7" t="n">
-        <v>2.226297201709594</v>
+        <v>2.22629720170962</v>
       </c>
       <c r="X7" t="n">
-        <v>3.162940111683864</v>
+        <v>3.162940111683887</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.521515553469071</v>
+        <v>2.521515553469097</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.37650473977208</v>
+        <v>2.376504739772099</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.407593199450755</v>
+        <v>2.407593199450774</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.904239466654816</v>
+        <v>2.904239466654837</v>
       </c>
     </row>
     <row r="8">
@@ -7994,85 +7994,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.308805993155983</v>
+        <v>4.308805993156014</v>
       </c>
       <c r="C8" t="n">
-        <v>5.697234895371903</v>
+        <v>5.69723489537194</v>
       </c>
       <c r="D8" t="n">
-        <v>5.300125495032097</v>
+        <v>5.300125495032125</v>
       </c>
       <c r="E8" t="n">
-        <v>6.302066184916419</v>
+        <v>5.489855763258594</v>
       </c>
       <c r="F8" t="n">
-        <v>4.857806165617632</v>
+        <v>4.857806165617678</v>
       </c>
       <c r="G8" t="n">
-        <v>6.659276839740643</v>
+        <v>6.975570646522372</v>
       </c>
       <c r="H8" t="n">
-        <v>5.392160421248009</v>
+        <v>5.392160421248039</v>
       </c>
       <c r="I8" t="n">
-        <v>6.463619757296232</v>
+        <v>6.463619757296273</v>
       </c>
       <c r="J8" t="n">
-        <v>6.143723408161633</v>
+        <v>6.143723408161623</v>
       </c>
       <c r="K8" t="n">
-        <v>6.539819554644533</v>
+        <v>6.539819554644599</v>
       </c>
       <c r="L8" t="n">
-        <v>6.78254953548151</v>
+        <v>6.782549535481549</v>
       </c>
       <c r="M8" t="n">
-        <v>6.747205390015601</v>
+        <v>6.747205390020293</v>
       </c>
       <c r="N8" t="n">
-        <v>4.443260248860082</v>
+        <v>4.443260248860146</v>
       </c>
       <c r="O8" t="n">
-        <v>4.657808186700597</v>
+        <v>4.657808186700635</v>
       </c>
       <c r="P8" t="n">
-        <v>4.882700707905768</v>
+        <v>4.882700707905796</v>
       </c>
       <c r="Q8" t="n">
         <v>4.361591870290917</v>
       </c>
       <c r="R8" t="n">
-        <v>6.167963955030524</v>
+        <v>6.167963955030631</v>
       </c>
       <c r="S8" t="n">
-        <v>6.398436259575696</v>
+        <v>6.398436259575694</v>
       </c>
       <c r="T8" t="n">
-        <v>5.721659299776497</v>
+        <v>5.721659299776568</v>
       </c>
       <c r="U8" t="n">
-        <v>4.958958540008312</v>
+        <v>5.15367508282028</v>
       </c>
       <c r="V8" t="n">
-        <v>5.615319711523033</v>
+        <v>5.20920705889205</v>
       </c>
       <c r="W8" t="n">
-        <v>5.412025592568773</v>
+        <v>5.412025592568765</v>
       </c>
       <c r="X8" t="n">
-        <v>4.663040420256246</v>
+        <v>4.663040420256273</v>
       </c>
       <c r="Y8" t="n">
-        <v>7.240315356841813</v>
+        <v>7.240315356841895</v>
       </c>
       <c r="Z8" t="n">
-        <v>5.561933353404787</v>
+        <v>4.008236680227212</v>
       </c>
       <c r="AA8" t="n">
-        <v>5.593021813083435</v>
+        <v>5.59302181308349</v>
       </c>
       <c r="AB8" t="n">
-        <v>7.683036536198731</v>
+        <v>7.683036536198743</v>
       </c>
     </row>
     <row r="9">
@@ -8082,7 +8082,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>86.45463025096554</v>
+        <v>86.45463025096561</v>
       </c>
       <c r="C9" t="n">
         <v>109.6994607822102</v>
@@ -8091,13 +8091,13 @@
         <v>109.3023513818705</v>
       </c>
       <c r="E9" t="n">
-        <v>110.3042920717546</v>
+        <v>104.9078764683267</v>
       </c>
       <c r="F9" t="n">
-        <v>110.147760721275</v>
+        <v>56.24641317920189</v>
       </c>
       <c r="G9" t="n">
-        <v>110.6615027265789</v>
+        <v>110.6615029028488</v>
       </c>
       <c r="H9" t="n">
         <v>109.3943863080864</v>
@@ -8106,10 +8106,10 @@
         <v>110.4658456441343</v>
       </c>
       <c r="J9" t="n">
-        <v>110.1459492949998</v>
+        <v>110.145949295</v>
       </c>
       <c r="K9" t="n">
-        <v>110.5420454414829</v>
+        <v>110.542045441483</v>
       </c>
       <c r="L9" t="n">
         <v>110.7847754223198</v>
@@ -8121,7 +8121,7 @@
         <v>109.6278970946219</v>
       </c>
       <c r="O9" t="n">
-        <v>117.2661944145053</v>
+        <v>117.2661944145055</v>
       </c>
       <c r="P9" t="n">
         <v>119.2559430572846</v>
@@ -8136,13 +8136,13 @@
         <v>110.400662146414</v>
       </c>
       <c r="T9" t="n">
-        <v>109.7238851866147</v>
+        <v>109.7238851866148</v>
       </c>
       <c r="U9" t="n">
         <v>109.8906255852405</v>
       </c>
       <c r="V9" t="n">
-        <v>109.6175455983614</v>
+        <v>136.5996050945097</v>
       </c>
       <c r="W9" t="n">
         <v>109.4139517021805</v>
@@ -8154,13 +8154,13 @@
         <v>109.7091700539401</v>
       </c>
       <c r="Z9" t="n">
-        <v>109.5641592402431</v>
+        <v>95.46703485729647</v>
       </c>
       <c r="AA9" t="n">
         <v>109.5952476999216</v>
       </c>
       <c r="AB9" t="n">
-        <v>110.0918939671257</v>
+        <v>110.0918939671259</v>
       </c>
     </row>
   </sheetData>
@@ -8326,85 +8326,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.145556870461711</v>
+        <v>2.145556870461697</v>
       </c>
       <c r="C2" t="n">
-        <v>2.215258740931256</v>
+        <v>2.215258740931241</v>
       </c>
       <c r="D2" t="n">
-        <v>2.095803952567214</v>
+        <v>2.095803952567168</v>
       </c>
       <c r="E2" t="n">
-        <v>2.212558395812233</v>
+        <v>2.212558395812228</v>
       </c>
       <c r="F2" t="n">
-        <v>2.235418156048416</v>
+        <v>2.2354181560484</v>
       </c>
       <c r="G2" t="n">
-        <v>2.150365651755607</v>
+        <v>2.150365651755552</v>
       </c>
       <c r="H2" t="n">
-        <v>2.053232308369632</v>
+        <v>2.053232308369611</v>
       </c>
       <c r="I2" t="n">
-        <v>2.175449485456223</v>
+        <v>2.175449485456235</v>
       </c>
       <c r="J2" t="n">
-        <v>2.127742907537732</v>
+        <v>2.127742907537764</v>
       </c>
       <c r="K2" t="n">
-        <v>2.162182117857948</v>
+        <v>2.162182117857906</v>
       </c>
       <c r="L2" t="n">
-        <v>2.263869050954845</v>
+        <v>2.263869050954803</v>
       </c>
       <c r="M2" t="n">
-        <v>2.094898071527803</v>
+        <v>2.094898071527828</v>
       </c>
       <c r="N2" t="n">
-        <v>2.079856775799908</v>
+        <v>2.079856775799925</v>
       </c>
       <c r="O2" t="n">
-        <v>3.938264198637079</v>
+        <v>3.938264198637071</v>
       </c>
       <c r="P2" t="n">
-        <v>2.083515945303354</v>
+        <v>2.083515945303362</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.177509055757371</v>
+        <v>2.177509055757369</v>
       </c>
       <c r="R2" t="n">
-        <v>2.237901295242515</v>
+        <v>2.237901295242498</v>
       </c>
       <c r="S2" t="n">
-        <v>2.175244203758958</v>
+        <v>2.175244203758914</v>
       </c>
       <c r="T2" t="n">
-        <v>2.111217597612741</v>
+        <v>2.111217597612727</v>
       </c>
       <c r="U2" t="n">
-        <v>2.205178293438165</v>
+        <v>2.205178293438157</v>
       </c>
       <c r="V2" t="n">
-        <v>2.080324645696415</v>
+        <v>2.080324645696405</v>
       </c>
       <c r="W2" t="n">
-        <v>2.356815412335771</v>
+        <v>2.356815412335786</v>
       </c>
       <c r="X2" t="n">
-        <v>2.134558065557156</v>
+        <v>2.134558065557103</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.119984790819574</v>
+        <v>2.119984790819573</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.037998648872778</v>
+        <v>2.037998648872772</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.080714573923901</v>
+        <v>2.080714573923904</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.124052448799265</v>
+        <v>2.124052448799242</v>
       </c>
     </row>
     <row r="3">
@@ -8414,85 +8414,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.755071681046382</v>
+        <v>2.755071681046359</v>
       </c>
       <c r="C3" t="n">
-        <v>2.989717310730816</v>
+        <v>2.989717310730801</v>
       </c>
       <c r="D3" t="n">
-        <v>2.403606522982355</v>
+        <v>2.403606522982318</v>
       </c>
       <c r="E3" t="n">
-        <v>3.236218664837497</v>
+        <v>3.236218664837451</v>
       </c>
       <c r="F3" t="n">
-        <v>3.401081140091607</v>
+        <v>3.401081140091584</v>
       </c>
       <c r="G3" t="n">
-        <v>2.786898485323668</v>
+        <v>2.786898485323576</v>
       </c>
       <c r="H3" t="n">
-        <v>2.099916456871258</v>
+        <v>2.099916456871242</v>
       </c>
       <c r="I3" t="n">
-        <v>2.974648428690322</v>
+        <v>2.974648428690311</v>
       </c>
       <c r="J3" t="n">
-        <v>2.628551307849161</v>
+        <v>2.628551307849115</v>
       </c>
       <c r="K3" t="n">
-        <v>2.873017201128378</v>
+        <v>2.873017201128365</v>
       </c>
       <c r="L3" t="n">
-        <v>3.594182751912467</v>
+        <v>3.594182751912447</v>
       </c>
       <c r="M3" t="n">
-        <v>2.403394282595404</v>
+        <v>2.403394282595365</v>
       </c>
       <c r="N3" t="n">
-        <v>2.289647907177475</v>
+        <v>2.289647907177458</v>
       </c>
       <c r="O3" t="n">
-        <v>5.235727094960356</v>
+        <v>5.235727094960311</v>
       </c>
       <c r="P3" t="n">
-        <v>2.313892847499992</v>
+        <v>2.313892847499975</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.982591094708987</v>
+        <v>2.982591094708951</v>
       </c>
       <c r="R3" t="n">
-        <v>3.423255731531767</v>
+        <v>3.423255731531783</v>
       </c>
       <c r="S3" t="n">
-        <v>2.963743230419625</v>
+        <v>2.963743230419631</v>
       </c>
       <c r="T3" t="n">
-        <v>2.51427086552313</v>
+        <v>2.51427086552311</v>
       </c>
       <c r="U3" t="n">
-        <v>2.450148304480921</v>
+        <v>2.450148304480923</v>
       </c>
       <c r="V3" t="n">
-        <v>2.290862983207316</v>
+        <v>2.29086298320727</v>
       </c>
       <c r="W3" t="n">
-        <v>2.898284599320832</v>
+        <v>2.898284599320825</v>
       </c>
       <c r="X3" t="n">
-        <v>2.679802415808489</v>
+        <v>2.679802415808462</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.57548501282444</v>
+        <v>2.575485012824427</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.29536166464277</v>
+        <v>2.29536166464274</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.29545020132759</v>
+        <v>2.29545020132756</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.610496751205473</v>
+        <v>2.610496751205515</v>
       </c>
     </row>
     <row r="4">
@@ -8502,85 +8502,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.613015356333343</v>
+        <v>2.613015356333304</v>
       </c>
       <c r="C4" t="n">
-        <v>2.858556467878532</v>
+        <v>2.858556467878527</v>
       </c>
       <c r="D4" t="n">
-        <v>2.051033261241792</v>
+        <v>2.051033261241733</v>
       </c>
       <c r="E4" t="n">
-        <v>3.36982840739197</v>
+        <v>3.369828407391924</v>
       </c>
       <c r="F4" t="n">
-        <v>3.628039915268815</v>
+        <v>3.628039915268765</v>
       </c>
       <c r="G4" t="n">
-        <v>2.667332753196466</v>
+        <v>2.667332753196179</v>
       </c>
       <c r="H4" t="n">
-        <v>1.570166956106392</v>
+        <v>1.570166956106406</v>
       </c>
       <c r="I4" t="n">
-        <v>2.950666193978941</v>
+        <v>2.950666193978962</v>
       </c>
       <c r="J4" t="n">
-        <v>2.41065973541572</v>
+        <v>2.410659735415662</v>
       </c>
       <c r="K4" t="n">
-        <v>2.800805173665247</v>
+        <v>2.800805173665184</v>
       </c>
       <c r="L4" t="n">
-        <v>3.949405861294846</v>
+        <v>3.949405861294774</v>
       </c>
       <c r="M4" t="n">
-        <v>2.054213423974881</v>
+        <v>2.054213423974886</v>
       </c>
       <c r="N4" t="n">
-        <v>1.870902563591704</v>
+        <v>1.870902563591652</v>
       </c>
       <c r="O4" t="n">
-        <v>1.62296965048217</v>
+        <v>1.622969650482145</v>
       </c>
       <c r="P4" t="n">
-        <v>1.912234566434285</v>
+        <v>1.912234566434226</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.973929987979324</v>
+        <v>2.97392998797931</v>
       </c>
       <c r="R4" t="n">
-        <v>3.656088114766575</v>
+        <v>3.656088114766545</v>
       </c>
       <c r="S4" t="n">
-        <v>2.948347442773402</v>
+        <v>2.948347442773333</v>
       </c>
       <c r="T4" t="n">
-        <v>2.225137472658253</v>
+        <v>2.225137472658207</v>
       </c>
       <c r="U4" t="n">
-        <v>1.706800937932313</v>
+        <v>1.706800937932286</v>
       </c>
       <c r="V4" t="n">
-        <v>1.868873473597044</v>
+        <v>1.868873473597055</v>
       </c>
       <c r="W4" t="n">
-        <v>2.183340050406219</v>
+        <v>2.183340050406176</v>
       </c>
       <c r="X4" t="n">
-        <v>2.488778795235641</v>
+        <v>2.488778795235661</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.252784506815214</v>
+        <v>2.252784506815191</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.03087995063798</v>
+        <v>2.030879950637915</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.880591788008771</v>
+        <v>1.880591788008668</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.375963574989856</v>
+        <v>2.375963574989824</v>
       </c>
     </row>
     <row r="5">
@@ -8590,85 +8590,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>21.87643299718264</v>
+        <v>21.87643299718257</v>
       </c>
       <c r="C5" t="n">
-        <v>27.24840567027755</v>
+        <v>27.24840567027747</v>
       </c>
       <c r="D5" t="n">
-        <v>13.814845276149</v>
+        <v>13.81484527614889</v>
       </c>
       <c r="E5" t="n">
-        <v>36.79263052289922</v>
+        <v>36.79263052289928</v>
       </c>
       <c r="F5" t="n">
-        <v>42.24632710287527</v>
+        <v>42.24632710287531</v>
       </c>
       <c r="G5" t="n">
-        <v>21.54482500259088</v>
+        <v>21.54482500258252</v>
       </c>
       <c r="H5" t="n">
-        <v>5.385530211677717</v>
+        <v>5.385530211677703</v>
       </c>
       <c r="I5" t="n">
-        <v>31.07774741349914</v>
+        <v>31.077747413499</v>
       </c>
       <c r="J5" t="n">
-        <v>18.63710224256335</v>
+        <v>18.63710224256294</v>
       </c>
       <c r="K5" t="n">
-        <v>24.83002205876186</v>
+        <v>24.83002205876187</v>
       </c>
       <c r="L5" t="n">
-        <v>42.77188683369215</v>
+        <v>42.77188683369204</v>
       </c>
       <c r="M5" t="n">
-        <v>13.33514088547392</v>
+        <v>13.33514088547387</v>
       </c>
       <c r="N5" t="n">
-        <v>8.334705156924985</v>
+        <v>8.334705156924818</v>
       </c>
       <c r="O5" t="n">
-        <v>5.580125970660771</v>
+        <v>5.580125970660745</v>
       </c>
       <c r="P5" t="n">
-        <v>10.31648740047323</v>
+        <v>10.31648740047312</v>
       </c>
       <c r="Q5" t="n">
-        <v>27.98777437705704</v>
+        <v>27.98777437705689</v>
       </c>
       <c r="R5" t="n">
-        <v>45.0496991976567</v>
+        <v>45.04969919765657</v>
       </c>
       <c r="S5" t="n">
-        <v>26.14464754422935</v>
+        <v>26.14464754422931</v>
       </c>
       <c r="T5" t="n">
-        <v>17.23432276122377</v>
+        <v>17.23432276122348</v>
       </c>
       <c r="U5" t="n">
-        <v>8.241985977487891</v>
+        <v>8.241985977487838</v>
       </c>
       <c r="V5" t="n">
-        <v>9.540301268169783</v>
+        <v>9.540301268169785</v>
       </c>
       <c r="W5" t="n">
-        <v>15.93081603732574</v>
+        <v>15.93081603732568</v>
       </c>
       <c r="X5" t="n">
-        <v>21.35284246720446</v>
+        <v>21.35284246720455</v>
       </c>
       <c r="Y5" t="n">
-        <v>18.28220418039664</v>
+        <v>18.28220418039652</v>
       </c>
       <c r="Z5" t="n">
-        <v>11.8841012900949</v>
+        <v>11.88410129009483</v>
       </c>
       <c r="AA5" t="n">
-        <v>10.56053746464267</v>
+        <v>10.56053746464138</v>
       </c>
       <c r="AB5" t="n">
-        <v>20.65034602398012</v>
+        <v>20.65034602398016</v>
       </c>
     </row>
     <row r="6">
@@ -8678,85 +8678,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.768369140241633</v>
+        <v>2.941295360716676</v>
       </c>
       <c r="C6" t="n">
-        <v>5.013910251786995</v>
+        <v>5.013910251786803</v>
       </c>
       <c r="D6" t="n">
-        <v>2.379313265625183</v>
+        <v>2.379313265625094</v>
       </c>
       <c r="E6" t="n">
-        <v>3.698108411775286</v>
+        <v>5.525182191300187</v>
       </c>
       <c r="F6" t="n">
-        <v>3.956319919652092</v>
+        <v>5.783393699177029</v>
       </c>
       <c r="G6" t="n">
-        <v>4.822686537104004</v>
+        <v>2.995612757579518</v>
       </c>
       <c r="H6" t="n">
-        <v>1.898446960489792</v>
+        <v>3.725520740014641</v>
       </c>
       <c r="I6" t="n">
-        <v>3.278946198362365</v>
+        <v>5.106019977887225</v>
       </c>
       <c r="J6" t="n">
-        <v>4.566013519324123</v>
+        <v>2.738939739798996</v>
       </c>
       <c r="K6" t="n">
-        <v>3.129085178048587</v>
+        <v>4.95615895757347</v>
       </c>
       <c r="L6" t="n">
-        <v>6.104759645202999</v>
+        <v>4.27768586567813</v>
       </c>
       <c r="M6" t="n">
-        <v>2.382493428358414</v>
+        <v>4.209567207883156</v>
       </c>
       <c r="N6" t="n">
-        <v>2.19183862888291</v>
+        <v>2.19183862888286</v>
       </c>
       <c r="O6" t="n">
-        <v>3.820436640185274</v>
+        <v>1.943905715773337</v>
       </c>
       <c r="P6" t="n">
-        <v>2.210295239187436</v>
+        <v>2.210295239187419</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.302209992362703</v>
+        <v>5.129283771887569</v>
       </c>
       <c r="R6" t="n">
-        <v>5.811441898674902</v>
+        <v>5.811441898674802</v>
       </c>
       <c r="S6" t="n">
-        <v>3.276627447156774</v>
+        <v>3.276627447156685</v>
       </c>
       <c r="T6" t="n">
-        <v>2.553417477041569</v>
+        <v>2.553417477041562</v>
       </c>
       <c r="U6" t="n">
-        <v>3.933537168063039</v>
+        <v>2.106463388538037</v>
       </c>
       <c r="V6" t="n">
-        <v>4.024227257505404</v>
+        <v>4.024227257505285</v>
       </c>
       <c r="W6" t="n">
-        <v>2.525425665172153</v>
+        <v>2.525425665172198</v>
       </c>
       <c r="X6" t="n">
-        <v>4.644132579143968</v>
+        <v>2.817058799619022</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.661799379901678</v>
+        <v>2.661799379901654</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.35915995502133</v>
+        <v>2.359159955021268</v>
       </c>
       <c r="AA6" t="n">
-        <v>4.035945571916916</v>
+        <v>4.035945571916915</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.698911418885884</v>
+        <v>2.698911418885894</v>
       </c>
     </row>
     <row r="7">
@@ -8766,85 +8766,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.241150103558568</v>
+        <v>3.241150103558592</v>
       </c>
       <c r="C7" t="n">
-        <v>3.486691215103823</v>
+        <v>3.486691215103801</v>
       </c>
       <c r="D7" t="n">
-        <v>2.679168008466968</v>
+        <v>2.679168008466983</v>
       </c>
       <c r="E7" t="n">
-        <v>3.997963154617203</v>
+        <v>3.997963154617186</v>
       </c>
       <c r="F7" t="n">
-        <v>4.256174662494049</v>
+        <v>4.256174662494016</v>
       </c>
       <c r="G7" t="n">
-        <v>3.2954675004219</v>
+        <v>3.295467500421451</v>
       </c>
       <c r="H7" t="n">
-        <v>2.198301703331706</v>
+        <v>2.198301703331651</v>
       </c>
       <c r="I7" t="n">
-        <v>3.578800941204211</v>
+        <v>3.578800941204225</v>
       </c>
       <c r="J7" t="n">
-        <v>3.038794482640994</v>
+        <v>3.038794482640895</v>
       </c>
       <c r="K7" t="n">
-        <v>3.428939920890477</v>
+        <v>3.428939920890465</v>
       </c>
       <c r="L7" t="n">
-        <v>4.577540608520036</v>
+        <v>4.577540608520027</v>
       </c>
       <c r="M7" t="n">
-        <v>2.682348171200139</v>
+        <v>2.68234817120016</v>
       </c>
       <c r="N7" t="n">
-        <v>2.499037310816937</v>
+        <v>2.499037310816917</v>
       </c>
       <c r="O7" t="n">
-        <v>2.251075900537469</v>
+        <v>2.25107590053747</v>
       </c>
       <c r="P7" t="n">
-        <v>2.540340816489593</v>
+        <v>2.540340816489556</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.602064735204612</v>
+        <v>3.602064735204584</v>
       </c>
       <c r="R7" t="n">
-        <v>4.284222861991835</v>
+        <v>4.284222861991804</v>
       </c>
       <c r="S7" t="n">
-        <v>3.576482189998626</v>
+        <v>3.5764821899986</v>
       </c>
       <c r="T7" t="n">
-        <v>2.853272219883479</v>
+        <v>2.853272219883472</v>
       </c>
       <c r="U7" t="n">
-        <v>2.445834880694033</v>
+        <v>2.445834880693987</v>
       </c>
       <c r="V7" t="n">
-        <v>2.497008220822319</v>
+        <v>2.497008220822292</v>
       </c>
       <c r="W7" t="n">
-        <v>2.811474797631488</v>
+        <v>2.8114747976314</v>
       </c>
       <c r="X7" t="n">
-        <v>3.116913542460949</v>
+        <v>3.116913542460932</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.952301700262874</v>
+        <v>2.952301700262837</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.659014697863212</v>
+        <v>2.65901469786318</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.508726535233993</v>
+        <v>2.508726535233923</v>
       </c>
       <c r="AB7" t="n">
-        <v>3.004098322215143</v>
+        <v>3.004098322215112</v>
       </c>
     </row>
     <row r="8">
@@ -8854,85 +8854,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.803776919661881</v>
+        <v>4.803776919661798</v>
       </c>
       <c r="C8" t="n">
-        <v>6.506462951446388</v>
+        <v>6.506462951446399</v>
       </c>
       <c r="D8" t="n">
-        <v>5.698939744809715</v>
+        <v>5.698939744809599</v>
       </c>
       <c r="E8" t="n">
-        <v>7.017734890959846</v>
+        <v>6.241848204105718</v>
       </c>
       <c r="F8" t="n">
-        <v>6.045807627089754</v>
+        <v>6.045807627089775</v>
       </c>
       <c r="G8" t="n">
-        <v>6.315239236763831</v>
+        <v>6.617387728418331</v>
       </c>
       <c r="H8" t="n">
-        <v>5.21807343967429</v>
+        <v>5.218073439674268</v>
       </c>
       <c r="I8" t="n">
-        <v>6.598572677546944</v>
+        <v>6.598572677546819</v>
       </c>
       <c r="J8" t="n">
-        <v>6.058566218983574</v>
+        <v>6.058566218983506</v>
       </c>
       <c r="K8" t="n">
-        <v>6.448711657233157</v>
+        <v>6.448711657233051</v>
       </c>
       <c r="L8" t="n">
-        <v>7.597312344862762</v>
+        <v>7.597312344862647</v>
       </c>
       <c r="M8" t="n">
-        <v>5.702119907542778</v>
+        <v>5.70211990754795</v>
       </c>
       <c r="N8" t="n">
-        <v>4.389277958838395</v>
+        <v>4.389277958838361</v>
       </c>
       <c r="O8" t="n">
-        <v>4.451749996144395</v>
+        <v>4.451749996144369</v>
       </c>
       <c r="P8" t="n">
-        <v>4.664927158344366</v>
+        <v>4.664927158344224</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.8783293168556</v>
+        <v>4.878329316855568</v>
       </c>
       <c r="R8" t="n">
-        <v>7.30399459833439</v>
+        <v>7.303994598334409</v>
       </c>
       <c r="S8" t="n">
-        <v>6.596253926341321</v>
+        <v>6.5962539263412</v>
       </c>
       <c r="T8" t="n">
-        <v>5.873043956226174</v>
+        <v>5.873043956226077</v>
       </c>
       <c r="U8" t="n">
-        <v>4.558215462881695</v>
+        <v>4.745523475458703</v>
       </c>
       <c r="V8" t="n">
-        <v>5.516779957165015</v>
+        <v>5.152322576813066</v>
       </c>
       <c r="W8" t="n">
-        <v>5.831532904299618</v>
+        <v>5.83153290429963</v>
       </c>
       <c r="X8" t="n">
-        <v>4.526728351201159</v>
+        <v>4.526728351201133</v>
       </c>
       <c r="Y8" t="n">
-        <v>7.473306871945947</v>
+        <v>7.473306871945865</v>
       </c>
       <c r="Z8" t="n">
-        <v>5.67878643420584</v>
+        <v>4.194574298983103</v>
       </c>
       <c r="AA8" t="n">
         <v>5.528498271576547</v>
       </c>
       <c r="AB8" t="n">
-        <v>7.545979771894307</v>
+        <v>7.54597977189428</v>
       </c>
     </row>
     <row r="9">
@@ -8942,31 +8942,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>81.2466640766398</v>
+        <v>81.24666407663983</v>
       </c>
       <c r="C9" t="n">
-        <v>103.2671007544495</v>
+        <v>103.2671007544493</v>
       </c>
       <c r="D9" t="n">
-        <v>102.4595775478128</v>
+        <v>102.4595775478126</v>
       </c>
       <c r="E9" t="n">
-        <v>103.7783726939629</v>
+        <v>98.75281597405314</v>
       </c>
       <c r="F9" t="n">
-        <v>104.0365842018395</v>
+        <v>53.83950638024739</v>
       </c>
       <c r="G9" t="n">
-        <v>103.075877039767</v>
+        <v>103.0758775059684</v>
       </c>
       <c r="H9" t="n">
-        <v>101.9787112426775</v>
+        <v>101.9787112426774</v>
       </c>
       <c r="I9" t="n">
-        <v>103.3592104805497</v>
+        <v>103.3592104805496</v>
       </c>
       <c r="J9" t="n">
-        <v>102.8192040219864</v>
+        <v>102.8192040219865</v>
       </c>
       <c r="K9" t="n">
         <v>103.2093494602361</v>
@@ -8975,52 +8975,52 @@
         <v>104.3579501478655</v>
       </c>
       <c r="M9" t="n">
-        <v>102.462757710546</v>
+        <v>102.4627577105457</v>
       </c>
       <c r="N9" t="n">
-        <v>102.2794468501624</v>
+        <v>102.2794468501625</v>
       </c>
       <c r="O9" t="n">
         <v>109.2476864366125</v>
       </c>
       <c r="P9" t="n">
-        <v>111.1063449611628</v>
+        <v>111.1063449611629</v>
       </c>
       <c r="Q9" t="n">
-        <v>103.3824747407517</v>
+        <v>103.3824747407515</v>
       </c>
       <c r="R9" t="n">
         <v>104.0646324013373</v>
       </c>
       <c r="S9" t="n">
-        <v>103.3568917293442</v>
+        <v>103.3568917293441</v>
       </c>
       <c r="T9" t="n">
         <v>102.633681759229</v>
       </c>
       <c r="U9" t="n">
-        <v>102.1867276707256</v>
+        <v>102.1867276707255</v>
       </c>
       <c r="V9" t="n">
-        <v>102.2774177601681</v>
+        <v>127.4051857208768</v>
       </c>
       <c r="W9" t="n">
-        <v>102.5918843369773</v>
+        <v>102.591884336977</v>
       </c>
       <c r="X9" t="n">
-        <v>102.8973230818067</v>
+        <v>102.8973230818065</v>
       </c>
       <c r="Y9" t="n">
-        <v>102.7327112396085</v>
+        <v>102.7327112396084</v>
       </c>
       <c r="Z9" t="n">
-        <v>102.4394242372088</v>
+        <v>89.3110986951356</v>
       </c>
       <c r="AA9" t="n">
-        <v>102.2891360745798</v>
+        <v>102.2891360745795</v>
       </c>
       <c r="AB9" t="n">
-        <v>102.784507861561</v>
+        <v>102.7845078615607</v>
       </c>
     </row>
   </sheetData>

--- a/Results/Phase 2/Ammonia/ammonia land use results.xlsx
+++ b/Results/Phase 2/Ammonia/ammonia land use results.xlsx
@@ -586,85 +586,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.965429243830902</v>
+        <v>1.951431572540947</v>
       </c>
       <c r="C2" t="n">
-        <v>1.96432087121485</v>
+        <v>1.972617201936157</v>
       </c>
       <c r="D2" t="n">
-        <v>1.931246591717139</v>
+        <v>1.940709170041142</v>
       </c>
       <c r="E2" t="n">
-        <v>1.901082556905441</v>
+        <v>1.891854521477512</v>
       </c>
       <c r="F2" t="n">
-        <v>1.923142687891357</v>
+        <v>1.929905264664319</v>
       </c>
       <c r="G2" t="n">
-        <v>2.043971997410224</v>
+        <v>2.025426521060638</v>
       </c>
       <c r="H2" t="n">
-        <v>1.947334855976427</v>
+        <v>1.950196310658897</v>
       </c>
       <c r="I2" t="n">
-        <v>1.954827391967184</v>
+        <v>1.958286368086906</v>
       </c>
       <c r="J2" t="n">
-        <v>1.993975789721942</v>
+        <v>1.987309063957829</v>
       </c>
       <c r="K2" t="n">
-        <v>1.999374600981809</v>
+        <v>2.003688483017605</v>
       </c>
       <c r="L2" t="n">
-        <v>2.011781953122546</v>
+        <v>1.94216820908669</v>
       </c>
       <c r="M2" t="n">
-        <v>2.044952454269576</v>
+        <v>2.051916283667521</v>
       </c>
       <c r="N2" t="n">
-        <v>1.959795316314401</v>
+        <v>1.966201862542891</v>
       </c>
       <c r="O2" t="n">
-        <v>3.699683215355555</v>
+        <v>3.719587879210501</v>
       </c>
       <c r="P2" t="n">
-        <v>1.984717909653342</v>
+        <v>1.978029055634911</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.948738215850605</v>
+        <v>1.946166859905627</v>
       </c>
       <c r="R2" t="n">
-        <v>1.962415899923293</v>
+        <v>1.966259195436216</v>
       </c>
       <c r="S2" t="n">
-        <v>1.99752639887629</v>
+        <v>1.989761327606155</v>
       </c>
       <c r="T2" t="n">
-        <v>1.958574557036554</v>
+        <v>1.95979370747216</v>
       </c>
       <c r="U2" t="n">
-        <v>1.984673744631917</v>
+        <v>2.027084533806829</v>
       </c>
       <c r="V2" t="n">
-        <v>1.975683433171187</v>
+        <v>1.977789852687648</v>
       </c>
       <c r="W2" t="n">
-        <v>2.039539932181777</v>
+        <v>2.102527618151945</v>
       </c>
       <c r="X2" t="n">
-        <v>1.964048938109905</v>
+        <v>1.949002327546852</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.962921262778823</v>
+        <v>1.96162693392031</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.760472582055969</v>
+        <v>1.752733561134763</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.98280109615214</v>
+        <v>1.988026565672755</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.019761826394704</v>
+        <v>2.046719325993284</v>
       </c>
     </row>
     <row r="3">
@@ -674,85 +674,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.208728488161634</v>
+        <v>2.074651729313636</v>
       </c>
       <c r="C3" t="n">
-        <v>2.087177290052021</v>
+        <v>2.09413460356083</v>
       </c>
       <c r="D3" t="n">
-        <v>1.966086037400137</v>
+        <v>1.998917962004387</v>
       </c>
       <c r="E3" t="n">
-        <v>1.750921156149444</v>
+        <v>1.650312226703391</v>
       </c>
       <c r="F3" t="n">
-        <v>1.908116771178184</v>
+        <v>1.921621610330813</v>
       </c>
       <c r="G3" t="n">
-        <v>2.768263406697336</v>
+        <v>2.601588633187063</v>
       </c>
       <c r="H3" t="n">
-        <v>2.081741381966299</v>
+        <v>2.067252147159454</v>
       </c>
       <c r="I3" t="n">
-        <v>2.13505563231044</v>
+        <v>2.124894243500339</v>
       </c>
       <c r="J3" t="n">
-        <v>2.412901212981889</v>
+        <v>2.330767805191697</v>
       </c>
       <c r="K3" t="n">
-        <v>2.453526899832474</v>
+        <v>2.449508858897623</v>
       </c>
       <c r="L3" t="n">
-        <v>2.540541781603589</v>
+        <v>2.009045437669644</v>
       </c>
       <c r="M3" t="n">
-        <v>2.778928460980664</v>
+        <v>2.792689580721756</v>
       </c>
       <c r="N3" t="n">
-        <v>2.170003338016018</v>
+        <v>2.180960610040218</v>
       </c>
       <c r="O3" t="n">
-        <v>5.135851886108428</v>
+        <v>5.162434740754759</v>
       </c>
       <c r="P3" t="n">
-        <v>2.346142224696051</v>
+        <v>2.26393158469704</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.091080556476233</v>
+        <v>2.037848516062044</v>
       </c>
       <c r="R3" t="n">
-        <v>2.189643956048679</v>
+        <v>2.182220196022666</v>
       </c>
       <c r="S3" t="n">
-        <v>2.437721629365009</v>
+        <v>2.347779543321996</v>
       </c>
       <c r="T3" t="n">
-        <v>2.161779503724692</v>
+        <v>2.135590405611325</v>
       </c>
       <c r="U3" t="n">
-        <v>2.377447729025938</v>
+        <v>2.374268890449881</v>
       </c>
       <c r="V3" t="n">
-        <v>2.281775242559804</v>
+        <v>2.262156441505533</v>
       </c>
       <c r="W3" t="n">
-        <v>2.253994053570316</v>
+        <v>2.366873218633295</v>
       </c>
       <c r="X3" t="n">
-        <v>2.200693952493503</v>
+        <v>2.058196992250772</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.192080408595809</v>
+        <v>2.148063462869347</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.874459164502224</v>
+        <v>1.776158473308683</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.334111892323633</v>
+        <v>2.336635275819066</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.599093253005619</v>
+        <v>2.75435606817728</v>
       </c>
     </row>
     <row r="4">
@@ -762,85 +762,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.706808921489017</v>
+        <v>1.347650623308595</v>
       </c>
       <c r="C4" t="n">
-        <v>1.459956158628605</v>
+        <v>1.31694630119881</v>
       </c>
       <c r="D4" t="n">
-        <v>1.320700141067189</v>
+        <v>1.226536154524469</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9799834917274739</v>
+        <v>0.6747004247495831</v>
       </c>
       <c r="F4" t="n">
-        <v>1.229162819375038</v>
+        <v>1.104501073251321</v>
       </c>
       <c r="G4" t="n">
-        <v>2.593985454619146</v>
+        <v>2.183457606196623</v>
       </c>
       <c r="H4" t="n">
-        <v>1.502424486843057</v>
+        <v>1.333697772102358</v>
       </c>
       <c r="I4" t="n">
-        <v>1.58705612759546</v>
+        <v>1.425078692361956</v>
       </c>
       <c r="J4" t="n">
-        <v>2.028446567233897</v>
+        <v>1.752186678656816</v>
       </c>
       <c r="K4" t="n">
-        <v>2.090237346144295</v>
+        <v>1.937916466509011</v>
       </c>
       <c r="L4" t="n">
-        <v>2.230384096237897</v>
+        <v>1.243016671735028</v>
       </c>
       <c r="M4" t="n">
-        <v>2.601748298109029</v>
+        <v>2.477188918774697</v>
       </c>
       <c r="N4" t="n">
-        <v>1.643171118455413</v>
+        <v>10.07018886758688</v>
       </c>
       <c r="O4" t="n">
-        <v>1.840949880386531</v>
+        <v>1.69845312362696</v>
       </c>
       <c r="P4" t="n">
-        <v>1.924683275178169</v>
+        <v>1.648081430301739</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.518276082199337</v>
+        <v>1.288183272205244</v>
       </c>
       <c r="R4" t="n">
-        <v>1.67277181584586</v>
+        <v>1.515135444954236</v>
       </c>
       <c r="S4" t="n">
-        <v>2.069361053147447</v>
+        <v>1.780602839328738</v>
       </c>
       <c r="T4" t="n">
-        <v>1.629382080835107</v>
+        <v>1.442104784128799</v>
       </c>
       <c r="U4" t="n">
-        <v>1.897996103684534</v>
+        <v>1.605872651256625</v>
       </c>
       <c r="V4" t="n">
-        <v>1.817578136668488</v>
+        <v>1.640985178831222</v>
       </c>
       <c r="W4" t="n">
-        <v>1.545708505374843</v>
+        <v>1.434566307392051</v>
       </c>
       <c r="X4" t="n">
-        <v>1.691217733398326</v>
+        <v>1.32021118359239</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.58879293833853</v>
+        <v>1.361409555580023</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.71439557624771</v>
+        <v>1.408251609085547</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.903031984904273</v>
+        <v>1.761007905260932</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.315967969724951</v>
+        <v>2.413605046636127</v>
       </c>
     </row>
     <row r="5">
@@ -850,85 +850,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>10.65847992630525</v>
+        <v>6.179938679840494</v>
       </c>
       <c r="C5" t="n">
-        <v>6.573456274792366</v>
+        <v>6.083613081913717</v>
       </c>
       <c r="D5" t="n">
-        <v>3.668121319197134</v>
+        <v>4.212007948906155</v>
       </c>
       <c r="E5" t="n">
-        <v>-3.123438771455726</v>
+        <v>-6.857789148252518</v>
       </c>
       <c r="F5" t="n">
-        <v>1.746718065942753</v>
+        <v>1.64254383924977</v>
       </c>
       <c r="G5" t="n">
-        <v>27.91294152409811</v>
+        <v>22.31665771216294</v>
       </c>
       <c r="H5" t="n">
-        <v>7.822514638343766</v>
+        <v>6.740880473427985</v>
       </c>
       <c r="I5" t="n">
-        <v>9.431508359484184</v>
+        <v>8.523415897706906</v>
       </c>
       <c r="J5" t="n">
-        <v>17.40935406770343</v>
+        <v>14.3737997367639</v>
       </c>
       <c r="K5" t="n">
-        <v>19.88283900930007</v>
+        <v>19.19407742867345</v>
       </c>
       <c r="L5" t="n">
-        <v>21.79157226183617</v>
+        <v>4.374049493356805</v>
       </c>
       <c r="M5" t="n">
-        <v>31.31851235281904</v>
+        <v>31.21604892744288</v>
       </c>
       <c r="N5" t="n">
-        <v>16.30048673302552</v>
+        <v>10.07018886758688</v>
       </c>
       <c r="O5" t="n">
-        <v>12.92326556234266</v>
+        <v>12.48805427623221</v>
       </c>
       <c r="P5" t="n">
-        <v>14.89715598136451</v>
+        <v>11.90443919024092</v>
       </c>
       <c r="Q5" t="n">
-        <v>7.739550158957194</v>
+        <v>5.440818022125251</v>
       </c>
       <c r="R5" t="n">
-        <v>11.41247380091228</v>
+        <v>10.58866412859638</v>
       </c>
       <c r="S5" t="n">
-        <v>17.90847245244646</v>
+        <v>14.64097956167135</v>
       </c>
       <c r="T5" t="n">
-        <v>10.27207458246694</v>
+        <v>8.829557383705978</v>
       </c>
       <c r="U5" t="n">
-        <v>16.64499890169357</v>
+        <v>13.47589459118197</v>
       </c>
       <c r="V5" t="n">
-        <v>12.90394109822297</v>
+        <v>11.80525423683808</v>
       </c>
       <c r="W5" t="n">
-        <v>8.116242959832746</v>
+        <v>8.283046570782787</v>
       </c>
       <c r="X5" t="n">
-        <v>11.42430667150919</v>
+        <v>6.152122049592714</v>
       </c>
       <c r="Y5" t="n">
-        <v>10.83183119873903</v>
+        <v>8.883542823636054</v>
       </c>
       <c r="Z5" t="n">
-        <v>11.02773353670083</v>
+        <v>7.435628648135514</v>
       </c>
       <c r="AA5" t="n">
-        <v>15.44185892709217</v>
+        <v>14.9814803122032</v>
       </c>
       <c r="AB5" t="n">
-        <v>25.93533694046389</v>
+        <v>30.77354297217592</v>
       </c>
     </row>
     <row r="6">
@@ -938,85 +938,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.056151605245573</v>
+        <v>1.702436571950863</v>
       </c>
       <c r="C6" t="n">
-        <v>3.809298842385159</v>
+        <v>3.689340068091489</v>
       </c>
       <c r="D6" t="n">
-        <v>1.651447668885506</v>
+        <v>3.598929921417282</v>
       </c>
       <c r="E6" t="n">
-        <v>1.310731019545798</v>
+        <v>3.04709419164226</v>
       </c>
       <c r="F6" t="n">
-        <v>3.578505503131591</v>
+        <v>1.459287021893489</v>
       </c>
       <c r="G6" t="n">
-        <v>4.943328138375701</v>
+        <v>4.555851373089322</v>
       </c>
       <c r="H6" t="n">
-        <v>3.851767170599611</v>
+        <v>3.706091538995103</v>
       </c>
       <c r="I6" t="n">
-        <v>1.917803655413774</v>
+        <v>1.779864641004162</v>
       </c>
       <c r="J6" t="n">
-        <v>4.377789250990457</v>
+        <v>2.106972627299001</v>
       </c>
       <c r="K6" t="n">
-        <v>2.420984873962611</v>
+        <v>4.310310233401708</v>
       </c>
       <c r="L6" t="n">
-        <v>2.561131624056216</v>
+        <v>3.61541043862783</v>
       </c>
       <c r="M6" t="n">
-        <v>2.932495825927339</v>
+        <v>4.849582685667438</v>
       </c>
       <c r="N6" t="n">
-        <v>1.979020924995698</v>
+        <v>10.07018886758688</v>
       </c>
       <c r="O6" t="n">
-        <v>4.244694178333112</v>
+        <v>2.057410088281883</v>
       </c>
       <c r="P6" t="n">
-        <v>4.328435880942211</v>
+        <v>4.089644685492654</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.849023610017654</v>
+        <v>3.660577039098054</v>
       </c>
       <c r="R6" t="n">
-        <v>2.003519343664183</v>
+        <v>3.887529211846944</v>
       </c>
       <c r="S6" t="n">
-        <v>4.418703736904005</v>
+        <v>2.135388787970841</v>
       </c>
       <c r="T6" t="n">
-        <v>1.960129608653426</v>
+        <v>1.796890732770932</v>
       </c>
       <c r="U6" t="n">
-        <v>2.318430814941786</v>
+        <v>2.062060964505329</v>
       </c>
       <c r="V6" t="n">
-        <v>4.166920820425046</v>
+        <v>4.013378945723941</v>
       </c>
       <c r="W6" t="n">
-        <v>3.949457657437285</v>
+        <v>3.876126052280985</v>
       </c>
       <c r="X6" t="n">
-        <v>4.04056041715489</v>
+        <v>3.692604950485237</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.029914744597652</v>
+        <v>1.839270744140501</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.045143104066028</v>
+        <v>1.763037557727712</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.233779512722589</v>
+        <v>4.133401672153678</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.655234343620204</v>
+        <v>2.777962745078249</v>
       </c>
     </row>
     <row r="7">
@@ -1026,85 +1026,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.357006766055675</v>
+        <v>1.995428453226588</v>
       </c>
       <c r="C7" t="n">
-        <v>2.110154003195265</v>
+        <v>1.964724131116748</v>
       </c>
       <c r="D7" t="n">
-        <v>1.970897985633848</v>
+        <v>1.874313984442409</v>
       </c>
       <c r="E7" t="n">
-        <v>1.630181336294139</v>
+        <v>1.322478254667579</v>
       </c>
       <c r="F7" t="n">
-        <v>1.879360663941698</v>
+        <v>1.752278903169115</v>
       </c>
       <c r="G7" t="n">
-        <v>3.244183299185807</v>
+        <v>2.831235436114556</v>
       </c>
       <c r="H7" t="n">
-        <v>2.152622331409717</v>
+        <v>1.981475602020295</v>
       </c>
       <c r="I7" t="n">
-        <v>2.237253972162123</v>
+        <v>2.072856522279961</v>
       </c>
       <c r="J7" t="n">
-        <v>2.678644411800557</v>
+        <v>2.399964508574774</v>
       </c>
       <c r="K7" t="n">
-        <v>2.740435190710957</v>
+        <v>2.585694296426984</v>
       </c>
       <c r="L7" t="n">
-        <v>2.880581940804553</v>
+        <v>1.890794501653029</v>
       </c>
       <c r="M7" t="n">
-        <v>3.251946142675687</v>
+        <v>3.124966748692664</v>
       </c>
       <c r="N7" t="n">
-        <v>2.293368963022073</v>
+        <v>10.07018886758688</v>
       </c>
       <c r="O7" t="n">
-        <v>2.491142057914454</v>
+        <v>2.346230359438765</v>
       </c>
       <c r="P7" t="n">
-        <v>2.574875452706095</v>
+        <v>2.295858666113482</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.168473926765996</v>
+        <v>1.93596110212311</v>
       </c>
       <c r="R7" t="n">
-        <v>2.322969660412523</v>
+        <v>2.162913274872202</v>
       </c>
       <c r="S7" t="n">
-        <v>2.719558897714106</v>
+        <v>2.428380669246539</v>
       </c>
       <c r="T7" t="n">
-        <v>2.279579925401765</v>
+        <v>2.089882614046729</v>
       </c>
       <c r="U7" t="n">
-        <v>2.637607823090719</v>
+        <v>2.346851656501513</v>
       </c>
       <c r="V7" t="n">
-        <v>2.467775981235145</v>
+        <v>2.288763008749155</v>
       </c>
       <c r="W7" t="n">
-        <v>2.195906349941507</v>
+        <v>2.082344137309851</v>
       </c>
       <c r="X7" t="n">
-        <v>2.34141557796498</v>
+        <v>1.967989013510362</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.328677966344129</v>
+        <v>2.11058975010447</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.364593420814372</v>
+        <v>2.056029439003517</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.55322982947093</v>
+        <v>2.408785735178836</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.966165814291613</v>
+        <v>3.061382876554031</v>
       </c>
     </row>
     <row r="8">
@@ -1114,85 +1114,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.089748640106463</v>
+        <v>3.744823649788991</v>
       </c>
       <c r="C8" t="n">
-        <v>5.404650807952397</v>
+        <v>5.294801624748196</v>
       </c>
       <c r="D8" t="n">
-        <v>5.265394790390991</v>
+        <v>5.204391478073911</v>
       </c>
       <c r="E8" t="n">
-        <v>4.093089709328644</v>
+        <v>3.810889052429096</v>
       </c>
       <c r="F8" t="n">
-        <v>3.855405703545096</v>
+        <v>3.747925927693685</v>
       </c>
       <c r="G8" t="n">
-        <v>6.862520162716754</v>
+        <v>6.489077701184924</v>
       </c>
       <c r="H8" t="n">
-        <v>5.447119136166859</v>
+        <v>5.311553095651711</v>
       </c>
       <c r="I8" t="n">
-        <v>5.531750776919262</v>
+        <v>5.402934015911308</v>
       </c>
       <c r="J8" t="n">
-        <v>5.973141216557694</v>
+        <v>5.730042002206195</v>
       </c>
       <c r="K8" t="n">
-        <v>6.034931995468096</v>
+        <v>5.915771790058367</v>
       </c>
       <c r="L8" t="n">
-        <v>6.175078745561697</v>
+        <v>5.220871995284593</v>
       </c>
       <c r="M8" t="n">
-        <v>6.54644294743394</v>
+        <v>6.455044242322407</v>
       </c>
       <c r="N8" t="n">
-        <v>4.377244420533263</v>
+        <v>10.07018886758688</v>
       </c>
       <c r="O8" t="n">
-        <v>4.907712440313227</v>
+        <v>4.787736440721995</v>
       </c>
       <c r="P8" t="n">
-        <v>4.909895659108903</v>
+        <v>4.654826240979707</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.594295311588238</v>
+        <v>3.37471615013648</v>
       </c>
       <c r="R8" t="n">
-        <v>5.61746646516966</v>
+        <v>5.492990768503612</v>
       </c>
       <c r="S8" t="n">
-        <v>6.014055702471252</v>
+        <v>5.758458162878102</v>
       </c>
       <c r="T8" t="n">
-        <v>5.574076730158904</v>
+        <v>5.419960107678317</v>
       </c>
       <c r="U8" t="n">
-        <v>5.169898783593152</v>
+        <v>4.907265147007153</v>
       </c>
       <c r="V8" t="n">
-        <v>5.335192841598114</v>
+        <v>5.179806530680773</v>
       </c>
       <c r="W8" t="n">
-        <v>5.490710084220673</v>
+        <v>5.412732279657233</v>
       </c>
       <c r="X8" t="n">
-        <v>3.910374905414391</v>
+        <v>3.551616734532737</v>
       </c>
       <c r="Y8" t="n">
-        <v>7.17563732307837</v>
+        <v>7.001431672168098</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.068324895189297</v>
+        <v>3.776062650400469</v>
       </c>
       <c r="AA8" t="n">
-        <v>5.847726634228071</v>
+        <v>5.738863228810372</v>
       </c>
       <c r="AB8" t="n">
-        <v>7.892046235994875</v>
+        <v>8.042615203418933</v>
       </c>
     </row>
     <row r="9">
@@ -1202,85 +1202,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>92.03410292838505</v>
+        <v>91.59761529184001</v>
       </c>
       <c r="C9" t="n">
-        <v>116.7884670535747</v>
+        <v>116.5510440193439</v>
       </c>
       <c r="D9" t="n">
-        <v>116.6492110360136</v>
+        <v>116.4606338726697</v>
       </c>
       <c r="E9" t="n">
-        <v>110.5383156212738</v>
+        <v>110.1425622017699</v>
       </c>
       <c r="F9" t="n">
-        <v>58.92304511401836</v>
+        <v>58.74335319625791</v>
       </c>
       <c r="G9" t="n">
-        <v>117.9224964981047</v>
+        <v>117.4175554001404</v>
       </c>
       <c r="H9" t="n">
-        <v>116.8309353817893</v>
+        <v>116.5677954902477</v>
       </c>
       <c r="I9" t="n">
-        <v>116.9155670225417</v>
+        <v>116.659176410507</v>
       </c>
       <c r="J9" t="n">
-        <v>117.3569574621801</v>
+        <v>116.986284396802</v>
       </c>
       <c r="K9" t="n">
-        <v>117.4187482410904</v>
+        <v>117.1720141846543</v>
       </c>
       <c r="L9" t="n">
-        <v>117.5588949911842</v>
+        <v>116.4771143898804</v>
       </c>
       <c r="M9" t="n">
-        <v>117.9302591930555</v>
+        <v>117.7112866369198</v>
       </c>
       <c r="N9" t="n">
-        <v>116.9716820134017</v>
+        <v>10.07018886758688</v>
       </c>
       <c r="O9" t="n">
-        <v>125.4548315134889</v>
+        <v>125.212259921393</v>
       </c>
       <c r="P9" t="n">
-        <v>127.3404908585075</v>
+        <v>126.9625828805208</v>
       </c>
       <c r="Q9" t="n">
-        <v>116.8467871256849</v>
+        <v>116.5222810661489</v>
       </c>
       <c r="R9" t="n">
-        <v>117.0012827107921</v>
+        <v>116.7492331630993</v>
       </c>
       <c r="S9" t="n">
-        <v>117.3978719480938</v>
+        <v>117.0147005574739</v>
       </c>
       <c r="T9" t="n">
-        <v>116.9578929757815</v>
+        <v>116.676202502274</v>
       </c>
       <c r="U9" t="n">
-        <v>117.3161941820699</v>
+        <v>116.9413727340082</v>
       </c>
       <c r="V9" t="n">
-        <v>145.9969629990862</v>
+        <v>145.7062423945572</v>
       </c>
       <c r="W9" t="n">
-        <v>116.8742194003209</v>
+        <v>116.6686640255371</v>
       </c>
       <c r="X9" t="n">
-        <v>117.0197286283446</v>
+        <v>116.5543089017375</v>
       </c>
       <c r="Y9" t="n">
-        <v>117.0069910167239</v>
+        <v>116.6969096383317</v>
       </c>
       <c r="Z9" t="n">
-        <v>101.9693959416294</v>
+        <v>101.5791388042047</v>
       </c>
       <c r="AA9" t="n">
-        <v>117.2315428798506</v>
+        <v>116.9951056234061</v>
       </c>
       <c r="AB9" t="n">
-        <v>117.6444788646714</v>
+        <v>117.6477027647814</v>
       </c>
     </row>
   </sheetData>
@@ -1446,85 +1446,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.307848367242322</v>
+        <v>2.809041943515195</v>
       </c>
       <c r="C2" t="n">
-        <v>2.554679353316873</v>
+        <v>3.152241722889551</v>
       </c>
       <c r="D2" t="n">
-        <v>2.293783463129559</v>
+        <v>2.796148741812398</v>
       </c>
       <c r="E2" t="n">
-        <v>2.298033314825965</v>
+        <v>2.800216012872772</v>
       </c>
       <c r="F2" t="n">
-        <v>2.3945525493017</v>
+        <v>2.89928367254974</v>
       </c>
       <c r="G2" t="n">
-        <v>2.25420099864382</v>
+        <v>2.756360069512183</v>
       </c>
       <c r="H2" t="n">
-        <v>2.227731187305161</v>
+        <v>2.731359753714071</v>
       </c>
       <c r="I2" t="n">
-        <v>2.306763251525807</v>
+        <v>2.809548778643343</v>
       </c>
       <c r="J2" t="n">
-        <v>2.279934467001532</v>
+        <v>2.783492858527127</v>
       </c>
       <c r="K2" t="n">
-        <v>2.3000111492949</v>
+        <v>2.804449678018212</v>
       </c>
       <c r="L2" t="n">
-        <v>2.377218714525021</v>
+        <v>2.881680784806703</v>
       </c>
       <c r="M2" t="n">
-        <v>2.248865025554795</v>
+        <v>2.751818917689244</v>
       </c>
       <c r="N2" t="n">
-        <v>2.263009224009656</v>
+        <v>2.766444046033673</v>
       </c>
       <c r="O2" t="n">
-        <v>4.506198011394371</v>
+        <v>5.471662348216652</v>
       </c>
       <c r="P2" t="n">
-        <v>2.248197286957524</v>
+        <v>2.752159567879108</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.32322752075765</v>
+        <v>2.824727114000233</v>
       </c>
       <c r="R2" t="n">
-        <v>2.522422547767621</v>
+        <v>3.0337574589307</v>
       </c>
       <c r="S2" t="n">
-        <v>2.342388707299095</v>
+        <v>2.845831693083122</v>
       </c>
       <c r="T2" t="n">
-        <v>2.264780938744713</v>
+        <v>2.767782319687004</v>
       </c>
       <c r="U2" t="n">
-        <v>2.582623016918645</v>
+        <v>3.745279812023359</v>
       </c>
       <c r="V2" t="n">
-        <v>2.270309900990847</v>
+        <v>2.774746036875109</v>
       </c>
       <c r="W2" t="n">
-        <v>2.766660774158667</v>
+        <v>4.025840966947647</v>
       </c>
       <c r="X2" t="n">
-        <v>2.287647801179032</v>
+        <v>2.793536330536034</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.265268679766441</v>
+        <v>2.774898819358032</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.501993549163705</v>
+        <v>3.164657445322198</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.259399726000297</v>
+        <v>2.765886257304916</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.275294774158942</v>
+        <v>2.777996010680378</v>
       </c>
     </row>
     <row r="3">
@@ -1534,85 +1534,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.840075752134562</v>
+        <v>3.317776959414795</v>
       </c>
       <c r="C3" t="n">
-        <v>3.403873466248881</v>
+        <v>4.048005587285722</v>
       </c>
       <c r="D3" t="n">
-        <v>2.743149041402303</v>
+        <v>3.229325506185035</v>
       </c>
       <c r="E3" t="n">
-        <v>2.771244325381503</v>
+        <v>3.255991667162872</v>
       </c>
       <c r="F3" t="n">
-        <v>3.464069164008826</v>
+        <v>3.967176549187474</v>
       </c>
       <c r="G3" t="n">
-        <v>2.458723601663861</v>
+        <v>2.943280047072128</v>
       </c>
       <c r="H3" t="n">
-        <v>2.27270240198141</v>
+        <v>2.768039130696609</v>
       </c>
       <c r="I3" t="n">
-        <v>2.837353196290207</v>
+        <v>3.326575761297418</v>
       </c>
       <c r="J3" t="n">
-        <v>2.643049498955352</v>
+        <v>3.137651421751841</v>
       </c>
       <c r="K3" t="n">
-        <v>2.784924326035602</v>
+        <v>3.2857640918014</v>
       </c>
       <c r="L3" t="n">
-        <v>3.332648143861921</v>
+        <v>3.833600072352799</v>
       </c>
       <c r="M3" t="n">
-        <v>2.43154344389486</v>
+        <v>2.925766563035486</v>
       </c>
       <c r="N3" t="n">
-        <v>2.524251324320505</v>
+        <v>3.018073155479077</v>
       </c>
       <c r="O3" t="n">
-        <v>6.058970564426787</v>
+        <v>7.324004420822305</v>
       </c>
       <c r="P3" t="n">
-        <v>2.416203737245801</v>
+        <v>2.913537688757799</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.951660001118558</v>
+        <v>3.431607472131176</v>
       </c>
       <c r="R3" t="n">
-        <v>4.383311860640583</v>
+        <v>4.933812642227076</v>
       </c>
       <c r="S3" t="n">
-        <v>3.084715564500689</v>
+        <v>3.578381820347384</v>
       </c>
       <c r="T3" t="n">
-        <v>2.537387552676516</v>
+        <v>3.028156624036592</v>
       </c>
       <c r="U3" t="n">
-        <v>2.949578662005532</v>
+        <v>4.513143528582212</v>
       </c>
       <c r="V3" t="n">
-        <v>2.573140294599452</v>
+        <v>3.073845879937239</v>
       </c>
       <c r="W3" t="n">
-        <v>3.44946849033166</v>
+        <v>5.242922410175809</v>
       </c>
       <c r="X3" t="n">
-        <v>2.698859545210422</v>
+        <v>3.210111194193686</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.540131427692575</v>
+        <v>3.078187213670618</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.0029986157557</v>
+        <v>3.752376763358754</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.49809652968111</v>
+        <v>3.013679550442526</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.618026714517132</v>
+        <v>3.109230515717361</v>
       </c>
     </row>
     <row r="4">
@@ -1622,85 +1622,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.70800918813741</v>
+        <v>3.176491067301426</v>
       </c>
       <c r="C4" t="n">
-        <v>3.028797647811496</v>
+        <v>3.512306231748476</v>
       </c>
       <c r="D4" t="n">
-        <v>2.549139626008225</v>
+        <v>3.030856422902626</v>
       </c>
       <c r="E4" t="n">
-        <v>2.597143655947503</v>
+        <v>3.076798120566651</v>
       </c>
       <c r="F4" t="n">
-        <v>3.687372810392429</v>
+        <v>4.195812909992911</v>
       </c>
       <c r="G4" t="n">
-        <v>2.10203748080853</v>
+        <v>2.581425065578173</v>
       </c>
       <c r="H4" t="n">
-        <v>1.803048785023536</v>
+        <v>2.299034997925073</v>
       </c>
       <c r="I4" t="n">
-        <v>2.695752306941495</v>
+        <v>3.182216003229695</v>
       </c>
       <c r="J4" t="n">
-        <v>2.391794709641246</v>
+        <v>2.886944105307483</v>
       </c>
       <c r="K4" t="n">
-        <v>2.619484206122916</v>
+        <v>3.124619315966492</v>
       </c>
       <c r="L4" t="n">
-        <v>3.491579172631899</v>
+        <v>3.996980195207051</v>
       </c>
       <c r="M4" t="n">
-        <v>2.057313137037109</v>
+        <v>2.552689142395347</v>
       </c>
       <c r="N4" t="n">
-        <v>14.02562870643044</v>
+        <v>15.20076458153757</v>
       </c>
       <c r="O4" t="n">
-        <v>1.859020189068998</v>
+        <v>2.371048131003984</v>
       </c>
       <c r="P4" t="n">
-        <v>2.034222795467968</v>
+        <v>2.533978467306139</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.881723801853205</v>
+        <v>3.353662283464772</v>
       </c>
       <c r="R4" t="n">
-        <v>5.131723266170488</v>
+        <v>5.714756188164024</v>
       </c>
       <c r="S4" t="n">
-        <v>3.098158218420089</v>
+        <v>3.592048212792113</v>
       </c>
       <c r="T4" t="n">
-        <v>2.221542771260986</v>
+        <v>2.710444635797293</v>
       </c>
       <c r="U4" t="n">
-        <v>2.134911290031283</v>
+        <v>2.34057131353277</v>
       </c>
       <c r="V4" t="n">
-        <v>2.278273134976631</v>
+        <v>2.783424530268543</v>
       </c>
       <c r="W4" t="n">
-        <v>2.396174939053178</v>
+        <v>2.997443433423884</v>
       </c>
       <c r="X4" t="n">
-        <v>2.479834501733058</v>
+        <v>3.001348035767339</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.366716269778104</v>
+        <v>2.6801901066164</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.384424780446765</v>
+        <v>2.863648443521898</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.16075949783269</v>
+        <v>2.689027738959851</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.348529408822724</v>
+        <v>2.838647957008925</v>
       </c>
     </row>
     <row r="5">
@@ -1710,85 +1710,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>20.80970639275012</v>
+        <v>21.47244479071007</v>
       </c>
       <c r="C5" t="n">
-        <v>27.7187000269005</v>
+        <v>28.69473844305295</v>
       </c>
       <c r="D5" t="n">
-        <v>19.79041168183058</v>
+        <v>20.7456659309608</v>
       </c>
       <c r="E5" t="n">
-        <v>19.48062988690601</v>
+        <v>20.33409347293477</v>
       </c>
       <c r="F5" t="n">
-        <v>40.81646749358928</v>
+        <v>42.2680864837731</v>
       </c>
       <c r="G5" t="n">
-        <v>10.8859100835051</v>
+        <v>11.7231136201221</v>
       </c>
       <c r="H5" t="n">
-        <v>7.098146755580877</v>
+        <v>8.380463876203017</v>
       </c>
       <c r="I5" t="n">
-        <v>23.19543155280033</v>
+        <v>24.25887794747432</v>
       </c>
       <c r="J5" t="n">
-        <v>16.37054072136498</v>
+        <v>17.51754816221369</v>
       </c>
       <c r="K5" t="n">
-        <v>19.64986392321439</v>
+        <v>20.9500811278148</v>
       </c>
       <c r="L5" t="n">
-        <v>33.35875897766006</v>
+        <v>34.63473408118438</v>
       </c>
       <c r="M5" t="n">
-        <v>11.36735991169201</v>
+        <v>12.58322856856416</v>
       </c>
       <c r="N5" t="n">
-        <v>14.02562870643044</v>
+        <v>15.20076458153757</v>
       </c>
       <c r="O5" t="n">
-        <v>7.08037307145359</v>
+        <v>8.41888430603502</v>
       </c>
       <c r="P5" t="n">
-        <v>9.856952617601138</v>
+        <v>11.00667403182578</v>
       </c>
       <c r="Q5" t="n">
-        <v>24.82658163349564</v>
+        <v>25.58269210432838</v>
       </c>
       <c r="R5" t="n">
-        <v>69.79705594785347</v>
+        <v>72.70366033248808</v>
       </c>
       <c r="S5" t="n">
-        <v>26.73778226458258</v>
+        <v>27.80373167549025</v>
       </c>
       <c r="T5" t="n">
-        <v>14.63424164689182</v>
+        <v>15.7438928721052</v>
       </c>
       <c r="U5" t="n">
-        <v>9.330437797455511</v>
+        <v>9.814887401668051</v>
       </c>
       <c r="V5" t="n">
-        <v>13.81164861712621</v>
+        <v>15.0507456405452</v>
       </c>
       <c r="W5" t="n">
-        <v>17.10882626672304</v>
+        <v>20.15155872856502</v>
       </c>
       <c r="X5" t="n">
-        <v>18.30605712309004</v>
+        <v>19.92868299595072</v>
       </c>
       <c r="Y5" t="n">
-        <v>14.34966905326968</v>
+        <v>16.77165251938766</v>
       </c>
       <c r="Z5" t="n">
-        <v>14.88980297337625</v>
+        <v>15.70271680902771</v>
       </c>
       <c r="AA5" t="n">
-        <v>13.10053991116361</v>
+        <v>14.87549044058911</v>
       </c>
       <c r="AB5" t="n">
-        <v>17.46629128039693</v>
+        <v>18.63571983479731</v>
       </c>
     </row>
     <row r="6">
@@ -1798,85 +1798,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.206578516650866</v>
+        <v>3.869159146182673</v>
       </c>
       <c r="C6" t="n">
-        <v>3.527366976324979</v>
+        <v>6.481755487484106</v>
       </c>
       <c r="D6" t="n">
-        <v>5.039341474590826</v>
+        <v>3.72352450178367</v>
       </c>
       <c r="E6" t="n">
-        <v>3.095712984460957</v>
+        <v>6.046247376302222</v>
       </c>
       <c r="F6" t="n">
-        <v>4.185942138905896</v>
+        <v>7.165262165728577</v>
       </c>
       <c r="G6" t="n">
-        <v>4.592239329391088</v>
+        <v>3.274093144459311</v>
       </c>
       <c r="H6" t="n">
-        <v>4.293250633606081</v>
+        <v>2.991703076806175</v>
       </c>
       <c r="I6" t="n">
-        <v>5.185954155524098</v>
+        <v>3.874884082110825</v>
       </c>
       <c r="J6" t="n">
-        <v>4.881996558223836</v>
+        <v>5.856393361043127</v>
       </c>
       <c r="K6" t="n">
-        <v>3.11805353463638</v>
+        <v>3.817287394847653</v>
       </c>
       <c r="L6" t="n">
-        <v>5.981781021214491</v>
+        <v>6.966429450942561</v>
       </c>
       <c r="M6" t="n">
-        <v>4.547514985619708</v>
+        <v>3.245357221276602</v>
       </c>
       <c r="N6" t="n">
-        <v>14.02562870643044</v>
+        <v>15.20076458153757</v>
       </c>
       <c r="O6" t="n">
-        <v>4.322865138521428</v>
+        <v>5.443729009579789</v>
       </c>
       <c r="P6" t="n">
-        <v>4.505018949460315</v>
+        <v>3.169329241890495</v>
       </c>
       <c r="Q6" t="n">
-        <v>5.371925650435809</v>
+        <v>4.046330362346149</v>
       </c>
       <c r="R6" t="n">
-        <v>7.621925114753092</v>
+        <v>6.407424267045156</v>
       </c>
       <c r="S6" t="n">
-        <v>5.588360067002681</v>
+        <v>6.561497468527808</v>
       </c>
       <c r="T6" t="n">
-        <v>2.720112099774429</v>
+        <v>3.403112714678462</v>
       </c>
       <c r="U6" t="n">
-        <v>4.485448899309147</v>
+        <v>5.420659235985129</v>
       </c>
       <c r="V6" t="n">
-        <v>4.768474983559203</v>
+        <v>3.476092609149694</v>
       </c>
       <c r="W6" t="n">
-        <v>2.921897224898943</v>
+        <v>3.730747678532007</v>
       </c>
       <c r="X6" t="n">
-        <v>2.978403830246535</v>
+        <v>5.970797291503157</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.749390911400753</v>
+        <v>3.513770027859336</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.882994108960215</v>
+        <v>3.556316522403186</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.659328826346152</v>
+        <v>5.658476994695574</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.842857756259113</v>
+        <v>3.512279893757289</v>
       </c>
     </row>
     <row r="7">
@@ -1886,85 +1886,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.418630869718406</v>
+        <v>3.990725233357601</v>
       </c>
       <c r="C7" t="n">
-        <v>3.739419329392482</v>
+        <v>4.326540397804594</v>
       </c>
       <c r="D7" t="n">
-        <v>3.259761307589216</v>
+        <v>3.845090588958684</v>
       </c>
       <c r="E7" t="n">
-        <v>3.30776533752848</v>
+        <v>3.89103228662274</v>
       </c>
       <c r="F7" t="n">
-        <v>4.397994491973426</v>
+        <v>5.010047076049004</v>
       </c>
       <c r="G7" t="n">
-        <v>2.812659162389513</v>
+        <v>3.395659231634267</v>
       </c>
       <c r="H7" t="n">
-        <v>2.51367046660452</v>
+        <v>3.113269163980942</v>
       </c>
       <c r="I7" t="n">
-        <v>3.406373988522471</v>
+        <v>3.996450169285594</v>
       </c>
       <c r="J7" t="n">
-        <v>3.102416391222223</v>
+        <v>3.701178271363522</v>
       </c>
       <c r="K7" t="n">
-        <v>3.330105887703906</v>
+        <v>3.938853482022456</v>
       </c>
       <c r="L7" t="n">
-        <v>4.202200854212873</v>
+        <v>4.811214361263011</v>
       </c>
       <c r="M7" t="n">
-        <v>2.767934818618081</v>
+        <v>3.366923308451403</v>
       </c>
       <c r="N7" t="n">
-        <v>14.02562870643044</v>
+        <v>15.20076458153757</v>
       </c>
       <c r="O7" t="n">
-        <v>2.569600290850004</v>
+        <v>3.185281466702098</v>
       </c>
       <c r="P7" t="n">
-        <v>2.744802897248991</v>
+        <v>3.348211803004288</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.592345483434185</v>
+        <v>4.167896449520918</v>
       </c>
       <c r="R7" t="n">
-        <v>5.842344947751464</v>
+        <v>6.528990354219928</v>
       </c>
       <c r="S7" t="n">
-        <v>3.808779900001058</v>
+        <v>4.406282378848146</v>
       </c>
       <c r="T7" t="n">
-        <v>2.932164452841963</v>
+        <v>3.524678801853352</v>
       </c>
       <c r="U7" t="n">
-        <v>2.765918096077554</v>
+        <v>3.252667162081594</v>
       </c>
       <c r="V7" t="n">
-        <v>2.988894816557602</v>
+        <v>3.59765869632459</v>
       </c>
       <c r="W7" t="n">
-        <v>3.106796620634162</v>
+        <v>3.811677599480038</v>
       </c>
       <c r="X7" t="n">
-        <v>3.190456183314033</v>
+        <v>3.81558220182352</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.937673712054351</v>
+        <v>3.60506293938931</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.095046462027736</v>
+        <v>3.677882609577858</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.871381179413668</v>
+        <v>3.50326190501594</v>
       </c>
       <c r="AB7" t="n">
-        <v>3.059151090403704</v>
+        <v>3.652882123065014</v>
       </c>
     </row>
     <row r="8">
@@ -1974,85 +1974,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.046083580370013</v>
+        <v>5.893239328900029</v>
       </c>
       <c r="C8" t="n">
-        <v>6.946371672502738</v>
+        <v>8.284925264030239</v>
       </c>
       <c r="D8" t="n">
-        <v>6.466713650699464</v>
+        <v>7.803475455184202</v>
       </c>
       <c r="E8" t="n">
-        <v>5.673680719010266</v>
+        <v>6.754726613427803</v>
       </c>
       <c r="F8" t="n">
-        <v>6.271514785193078</v>
+        <v>7.232841809394575</v>
       </c>
       <c r="G8" t="n">
-        <v>6.347131043770373</v>
+        <v>7.780342294418055</v>
       </c>
       <c r="H8" t="n">
-        <v>5.720622809714735</v>
+        <v>7.071654030206687</v>
       </c>
       <c r="I8" t="n">
-        <v>6.613326331632744</v>
+        <v>7.954835035511359</v>
       </c>
       <c r="J8" t="n">
-        <v>6.30936873433247</v>
+        <v>7.659563137589265</v>
       </c>
       <c r="K8" t="n">
-        <v>6.537058230814133</v>
+        <v>7.89723834824802</v>
       </c>
       <c r="L8" t="n">
-        <v>7.409153197323098</v>
+        <v>8.769599227488644</v>
       </c>
       <c r="M8" t="n">
-        <v>5.974887161738502</v>
+        <v>7.325308174659528</v>
       </c>
       <c r="N8" t="n">
-        <v>14.02562870643044</v>
+        <v>15.20076458153757</v>
       </c>
       <c r="O8" t="n">
-        <v>4.888687035349935</v>
+        <v>5.987970521253543</v>
       </c>
       <c r="P8" t="n">
-        <v>4.981412890688572</v>
+        <v>6.043549430031432</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.909390466340233</v>
+        <v>5.666385017722085</v>
       </c>
       <c r="R8" t="n">
-        <v>9.04929729086172</v>
+        <v>10.48737522044568</v>
       </c>
       <c r="S8" t="n">
-        <v>7.015732243111299</v>
+        <v>8.36466724507371</v>
       </c>
       <c r="T8" t="n">
-        <v>6.139116795952217</v>
+        <v>7.48306366807895</v>
       </c>
       <c r="U8" t="n">
-        <v>5.188457391499666</v>
+        <v>6.210484718822253</v>
       </c>
       <c r="V8" t="n">
-        <v>5.815510344254115</v>
+        <v>6.983222337851759</v>
       </c>
       <c r="W8" t="n">
-        <v>6.314059379354657</v>
+        <v>7.77046649593724</v>
       </c>
       <c r="X8" t="n">
-        <v>4.652265445234332</v>
+        <v>5.502495406748055</v>
       </c>
       <c r="Y8" t="n">
-        <v>7.794752608075605</v>
+        <v>9.590615233994351</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.693159156195478</v>
+        <v>5.54220785077194</v>
       </c>
       <c r="AA8" t="n">
-        <v>6.078333522523903</v>
+        <v>7.461646771241617</v>
       </c>
       <c r="AB8" t="n">
-        <v>7.916022874017031</v>
+        <v>9.758795911426462</v>
       </c>
     </row>
     <row r="9">
@@ -2062,85 +2062,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>81.21704201771419</v>
+        <v>81.90574602773842</v>
       </c>
       <c r="C9" t="n">
-        <v>103.290778171179</v>
+        <v>104.1580300639979</v>
       </c>
       <c r="D9" t="n">
-        <v>102.8111201493758</v>
+        <v>103.6765802551521</v>
       </c>
       <c r="E9" t="n">
-        <v>97.8386328836208</v>
+        <v>98.66429096015668</v>
       </c>
       <c r="F9" t="n">
-        <v>53.8028714420797</v>
+        <v>54.31809335637372</v>
       </c>
       <c r="G9" t="n">
-        <v>102.3640183985786</v>
+        <v>103.2271497133558</v>
       </c>
       <c r="H9" t="n">
-        <v>102.0650293083911</v>
+        <v>102.9447588301746</v>
       </c>
       <c r="I9" t="n">
-        <v>102.9577328303091</v>
+        <v>103.8279398354792</v>
       </c>
       <c r="J9" t="n">
-        <v>102.6537752330089</v>
+        <v>103.5326679375572</v>
       </c>
       <c r="K9" t="n">
-        <v>102.8814647294904</v>
+        <v>103.770343148216</v>
       </c>
       <c r="L9" t="n">
-        <v>103.7535596959996</v>
+        <v>104.6427040274565</v>
       </c>
       <c r="M9" t="n">
-        <v>102.3192936604047</v>
+        <v>103.1984129746447</v>
       </c>
       <c r="N9" t="n">
-        <v>14.02562870643044</v>
+        <v>15.20076458153757</v>
       </c>
       <c r="O9" t="n">
-        <v>109.3298996202039</v>
+        <v>110.2798621359907</v>
       </c>
       <c r="P9" t="n">
-        <v>111.0729139693947</v>
+        <v>112.0223897938624</v>
       </c>
       <c r="Q9" t="n">
-        <v>103.1437047196234</v>
+        <v>103.9993869312424</v>
       </c>
       <c r="R9" t="n">
-        <v>105.3937037895381</v>
+        <v>106.3604800204135</v>
       </c>
       <c r="S9" t="n">
-        <v>103.3601387417877</v>
+        <v>104.2377720450416</v>
       </c>
       <c r="T9" t="n">
-        <v>102.4835232946285</v>
+        <v>103.3561684680468</v>
       </c>
       <c r="U9" t="n">
-        <v>102.2572275740941</v>
+        <v>103.0969338124991</v>
       </c>
       <c r="V9" t="n">
-        <v>127.6426941395065</v>
+        <v>128.7202893546561</v>
       </c>
       <c r="W9" t="n">
-        <v>102.6581554624208</v>
+        <v>103.6431672656736</v>
       </c>
       <c r="X9" t="n">
-        <v>102.7418150251007</v>
+        <v>103.647071868017</v>
       </c>
       <c r="Y9" t="n">
-        <v>102.4890325538409</v>
+        <v>103.4365526055828</v>
       </c>
       <c r="Z9" t="n">
-        <v>89.53131234865128</v>
+        <v>90.29569075835599</v>
       </c>
       <c r="AA9" t="n">
-        <v>102.4227400212003</v>
+        <v>103.3347515712094</v>
       </c>
       <c r="AB9" t="n">
-        <v>102.6105099321902</v>
+        <v>103.4843717892585</v>
       </c>
     </row>
   </sheetData>
@@ -2306,85 +2306,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.999096585379075</v>
+        <v>2.168082108945144</v>
       </c>
       <c r="C2" t="n">
-        <v>2.008840796981491</v>
+        <v>2.216901382946137</v>
       </c>
       <c r="D2" t="n">
-        <v>1.986339274419458</v>
+        <v>2.177873119840965</v>
       </c>
       <c r="E2" t="n">
-        <v>1.961672893025512</v>
+        <v>2.135461476627222</v>
       </c>
       <c r="F2" t="n">
-        <v>1.957625411292011</v>
+        <v>2.1432049801101</v>
       </c>
       <c r="G2" t="n">
-        <v>2.096168730861452</v>
+        <v>2.268673688960418</v>
       </c>
       <c r="H2" t="n">
-        <v>1.970902810232917</v>
+        <v>2.156964212361835</v>
       </c>
       <c r="I2" t="n">
-        <v>2.003108992680538</v>
+        <v>2.18820558098718</v>
       </c>
       <c r="J2" t="n">
-        <v>2.042200433066091</v>
+        <v>2.219119337695812</v>
       </c>
       <c r="K2" t="n">
-        <v>2.023076269063311</v>
+        <v>2.210639059734772</v>
       </c>
       <c r="L2" t="n">
-        <v>2.050697501648349</v>
+        <v>2.160046274026537</v>
       </c>
       <c r="M2" t="n">
-        <v>2.070865852341769</v>
+        <v>2.258182091709591</v>
       </c>
       <c r="N2" t="n">
-        <v>1.995947796049023</v>
+        <v>2.183343543941915</v>
       </c>
       <c r="O2" t="n">
-        <v>3.755904805527563</v>
+        <v>4.092762901710411</v>
       </c>
       <c r="P2" t="n">
-        <v>2.037005129045092</v>
+        <v>2.205792506311462</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.993749919243974</v>
+        <v>2.171077853634222</v>
       </c>
       <c r="R2" t="n">
-        <v>1.986162216183637</v>
+        <v>2.169855274664966</v>
       </c>
       <c r="S2" t="n">
-        <v>2.040890711086687</v>
+        <v>2.211998136785232</v>
       </c>
       <c r="T2" t="n">
-        <v>2.00106110295952</v>
+        <v>2.180477957889689</v>
       </c>
       <c r="U2" t="n">
-        <v>2.056691843430822</v>
+        <v>2.481065290279762</v>
       </c>
       <c r="V2" t="n">
-        <v>2.012655947935206</v>
+        <v>2.196543452865878</v>
       </c>
       <c r="W2" t="n">
-        <v>2.114730744973531</v>
+        <v>2.591814920829963</v>
       </c>
       <c r="X2" t="n">
-        <v>2.019709077813373</v>
+        <v>2.183744697927139</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.013633739532402</v>
+        <v>2.195230021544365</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.827119622688645</v>
+        <v>2.049726918380394</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.006323133118244</v>
+        <v>2.187512278840144</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.057320849759277</v>
+        <v>2.262601079795424</v>
       </c>
     </row>
     <row r="3">
@@ -2394,85 +2394,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.202703552051165</v>
+        <v>2.269555486621395</v>
       </c>
       <c r="C3" t="n">
-        <v>2.144419667839428</v>
+        <v>2.362080076896108</v>
       </c>
       <c r="D3" t="n">
-        <v>2.113239337763181</v>
+        <v>2.340692698789418</v>
       </c>
       <c r="E3" t="n">
-        <v>1.93695359664112</v>
+        <v>2.037642634297543</v>
       </c>
       <c r="F3" t="n">
-        <v>1.907791434528036</v>
+        <v>2.092630591083693</v>
       </c>
       <c r="G3" t="n">
-        <v>2.89371825139323</v>
+        <v>2.985462046842675</v>
       </c>
       <c r="H3" t="n">
-        <v>2.002953881607668</v>
+        <v>2.191267171685162</v>
       </c>
       <c r="I3" t="n">
-        <v>2.233496471870569</v>
+        <v>2.414872181611513</v>
       </c>
       <c r="J3" t="n">
-        <v>2.510390301883518</v>
+        <v>2.633535989607565</v>
       </c>
       <c r="K3" t="n">
-        <v>2.374615199295678</v>
+        <v>2.573568951534607</v>
       </c>
       <c r="L3" t="n">
-        <v>2.571888615278699</v>
+        <v>2.212726677663932</v>
       </c>
       <c r="M3" t="n">
-        <v>2.718608785663013</v>
+        <v>2.916190145650626</v>
       </c>
       <c r="N3" t="n">
-        <v>2.181601280922802</v>
+        <v>2.379392647446862</v>
       </c>
       <c r="O3" t="n">
-        <v>5.1671198152845</v>
+        <v>5.600827847991666</v>
       </c>
       <c r="P3" t="n">
-        <v>2.47256422740911</v>
+        <v>2.537872602265523</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.165955855173622</v>
+        <v>2.291794964455014</v>
       </c>
       <c r="R3" t="n">
-        <v>2.112239410752598</v>
+        <v>2.283558208074835</v>
       </c>
       <c r="S3" t="n">
-        <v>2.500485905632246</v>
+        <v>2.582274411775789</v>
       </c>
       <c r="T3" t="n">
-        <v>2.218628839372981</v>
+        <v>2.35934697232421</v>
       </c>
       <c r="U3" t="n">
-        <v>2.488025099377337</v>
+        <v>2.981709243371733</v>
       </c>
       <c r="V3" t="n">
-        <v>2.298766030225887</v>
+        <v>2.471519093964826</v>
       </c>
       <c r="W3" t="n">
-        <v>2.3691630263602</v>
+        <v>3.072334556313607</v>
       </c>
       <c r="X3" t="n">
-        <v>2.351710580607251</v>
+        <v>2.382475090123267</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.307467137071235</v>
+        <v>2.463854353042939</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.991311653042754</v>
+        <v>2.167681015316982</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.255409687027313</v>
+        <v>2.408873783331863</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.62170214951889</v>
+        <v>2.946066158122954</v>
       </c>
     </row>
     <row r="4">
@@ -2482,85 +2482,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.700918874536357</v>
+        <v>1.57634022076185</v>
       </c>
       <c r="C4" t="n">
-        <v>1.5477286483785</v>
+        <v>1.602084107421983</v>
       </c>
       <c r="D4" t="n">
-        <v>1.556819178594489</v>
+        <v>1.686934192917683</v>
       </c>
       <c r="E4" t="n">
-        <v>1.278201053653858</v>
+        <v>1.207875172498648</v>
       </c>
       <c r="F4" t="n">
-        <v>1.232482885540355</v>
+        <v>1.295341606525345</v>
       </c>
       <c r="G4" t="n">
-        <v>2.797393413152931</v>
+        <v>2.712568391447358</v>
       </c>
       <c r="H4" t="n">
-        <v>1.382457214483136</v>
+        <v>1.450758464368243</v>
       </c>
       <c r="I4" t="n">
-        <v>1.746240860804919</v>
+        <v>1.803644094731138</v>
       </c>
       <c r="J4" t="n">
-        <v>2.187016021098413</v>
+        <v>2.151934513654954</v>
       </c>
       <c r="K4" t="n">
-        <v>1.971780432949382</v>
+        <v>2.057040557095286</v>
       </c>
       <c r="L4" t="n">
-        <v>2.283774961392033</v>
+        <v>1.485571768689467</v>
       </c>
       <c r="M4" t="n">
-        <v>2.511384347025868</v>
+        <v>2.594415229968675</v>
       </c>
       <c r="N4" t="n">
-        <v>1.665351850538743</v>
+        <v>9.771603527381753</v>
       </c>
       <c r="O4" t="n">
-        <v>1.835217352973159</v>
+        <v>1.896475583259466</v>
       </c>
       <c r="P4" t="n">
-        <v>2.129113314035681</v>
+        <v>2.002296506654262</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.640525820952417</v>
+        <v>1.610178535135609</v>
       </c>
       <c r="R4" t="n">
-        <v>1.554819224370078</v>
+        <v>1.596368943263753</v>
       </c>
       <c r="S4" t="n">
-        <v>2.17300275065154</v>
+        <v>2.07239195758654</v>
       </c>
       <c r="T4" t="n">
-        <v>1.723109004330226</v>
+        <v>1.716357036962706</v>
       </c>
       <c r="U4" t="n">
-        <v>2.003291633294575</v>
+        <v>1.817330530855734</v>
       </c>
       <c r="V4" t="n">
-        <v>1.849206237594639</v>
+        <v>1.89236847594569</v>
       </c>
       <c r="W4" t="n">
-        <v>1.648376371098079</v>
+        <v>1.787772652481693</v>
       </c>
       <c r="X4" t="n">
-        <v>1.933746458796722</v>
+        <v>1.753256368460361</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.776517572149517</v>
+        <v>1.721458868093043</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.850100465742663</v>
+        <v>1.769269603090141</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.782546055626461</v>
+        <v>1.795812928045607</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.355803084045788</v>
+        <v>2.637730460924446</v>
       </c>
     </row>
     <row r="5">
@@ -2570,85 +2570,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9.047489059473348</v>
+        <v>6.002986987782032</v>
       </c>
       <c r="C5" t="n">
-        <v>6.884368162195812</v>
+        <v>6.964043697320839</v>
       </c>
       <c r="D5" t="n">
-        <v>7.204561745825844</v>
+        <v>8.7938821203582</v>
       </c>
       <c r="E5" t="n">
-        <v>1.802695841774885</v>
+        <v>-0.46213953050052</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7852729403025358</v>
+        <v>1.037160792433367</v>
       </c>
       <c r="G5" t="n">
-        <v>28.78176431926865</v>
+        <v>26.36294116762158</v>
       </c>
       <c r="H5" t="n">
-        <v>3.843984129057473</v>
+        <v>4.218391597220759</v>
       </c>
       <c r="I5" t="n">
-        <v>11.10359102715468</v>
+        <v>11.24321125559396</v>
       </c>
       <c r="J5" t="n">
-        <v>18.28171181472407</v>
+        <v>16.74949194066296</v>
       </c>
       <c r="K5" t="n">
-        <v>14.59573222793547</v>
+        <v>15.24907241994685</v>
       </c>
       <c r="L5" t="n">
-        <v>20.57236812781001</v>
+        <v>4.577805519112711</v>
       </c>
       <c r="M5" t="n">
-        <v>26.4816395664672</v>
+        <v>27.14029734250866</v>
       </c>
       <c r="N5" t="n">
-        <v>16.22262830283648</v>
+        <v>9.771603527381753</v>
       </c>
       <c r="O5" t="n">
-        <v>11.17077979600105</v>
+        <v>11.35534008838202</v>
       </c>
       <c r="P5" t="n">
-        <v>16.75750611998516</v>
+        <v>13.59873044498278</v>
       </c>
       <c r="Q5" t="n">
-        <v>8.69071749121119</v>
+        <v>7.120365789075819</v>
       </c>
       <c r="R5" t="n">
-        <v>7.313429981723006</v>
+        <v>7.131130746349735</v>
       </c>
       <c r="S5" t="n">
-        <v>17.69307986878521</v>
+        <v>14.98633057051932</v>
       </c>
       <c r="T5" t="n">
-        <v>10.52620950991219</v>
+        <v>9.385474576635724</v>
       </c>
       <c r="U5" t="n">
-        <v>16.64917323156224</v>
+        <v>13.6359337024102</v>
       </c>
       <c r="V5" t="n">
-        <v>11.54290832836468</v>
+        <v>11.42741071877093</v>
       </c>
       <c r="W5" t="n">
-        <v>8.668441599324863</v>
+        <v>10.35373733200568</v>
       </c>
       <c r="X5" t="n">
-        <v>14.50348047049761</v>
+        <v>9.979291778996409</v>
       </c>
       <c r="Y5" t="n">
-        <v>12.71461587320647</v>
+        <v>12.10297441181771</v>
       </c>
       <c r="Z5" t="n">
-        <v>11.88373106622561</v>
+        <v>9.530677579835931</v>
       </c>
       <c r="AA5" t="n">
-        <v>11.21928638283628</v>
+        <v>10.51103233945868</v>
       </c>
       <c r="AB5" t="n">
-        <v>24.18994647862608</v>
+        <v>29.02877344504801</v>
       </c>
     </row>
     <row r="6">
@@ -2658,85 +2658,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.017416058102059</v>
+        <v>1.962281233513149</v>
       </c>
       <c r="C6" t="n">
-        <v>3.784812820862591</v>
+        <v>4.017401565220974</v>
       </c>
       <c r="D6" t="n">
-        <v>3.793903351078572</v>
+        <v>2.072875205668986</v>
       </c>
       <c r="E6" t="n">
-        <v>1.594698237219558</v>
+        <v>3.623192630297641</v>
       </c>
       <c r="F6" t="n">
-        <v>1.548980069106059</v>
+        <v>1.681282619276649</v>
       </c>
       <c r="G6" t="n">
-        <v>3.113890596718635</v>
+        <v>5.127885849246345</v>
       </c>
       <c r="H6" t="n">
-        <v>3.61954138696722</v>
+        <v>3.866075922167237</v>
       </c>
       <c r="I6" t="n">
-        <v>2.062738044370634</v>
+        <v>4.218961552530127</v>
       </c>
       <c r="J6" t="n">
-        <v>4.424100193582493</v>
+        <v>4.567251971453947</v>
       </c>
       <c r="K6" t="n">
-        <v>4.208864605433466</v>
+        <v>2.442981569846591</v>
       </c>
       <c r="L6" t="n">
-        <v>2.600272144957747</v>
+        <v>3.900889226488458</v>
       </c>
       <c r="M6" t="n">
-        <v>2.827881530591577</v>
+        <v>5.009732687767665</v>
       </c>
       <c r="N6" t="n">
-        <v>1.985103502242803</v>
+        <v>9.771603527381753</v>
       </c>
       <c r="O6" t="n">
-        <v>4.132146119395667</v>
+        <v>2.284078706151775</v>
       </c>
       <c r="P6" t="n">
-        <v>4.426817922457612</v>
+        <v>4.537781734475918</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.877609993436504</v>
+        <v>1.996119547886913</v>
       </c>
       <c r="R6" t="n">
-        <v>3.791903396854152</v>
+        <v>4.011686401062749</v>
       </c>
       <c r="S6" t="n">
-        <v>4.410086923135627</v>
+        <v>2.458332970337847</v>
       </c>
       <c r="T6" t="n">
-        <v>2.039606187895941</v>
+        <v>2.10229804971401</v>
       </c>
       <c r="U6" t="n">
-        <v>2.408393962830214</v>
+        <v>2.364801057740833</v>
       </c>
       <c r="V6" t="n">
-        <v>4.086290410078724</v>
+        <v>2.278309488696995</v>
       </c>
       <c r="W6" t="n">
-        <v>3.945073911325971</v>
+        <v>2.200559852662648</v>
       </c>
       <c r="X6" t="n">
-        <v>4.170830631280806</v>
+        <v>4.168573826259354</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.200039204182686</v>
+        <v>2.289829995539265</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.087184638226747</v>
+        <v>2.155210615841448</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.099043239192164</v>
+        <v>4.211130385844601</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.678753334601905</v>
+        <v>3.02644403488889</v>
       </c>
     </row>
     <row r="7">
@@ -2746,85 +2746,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.345207326105553</v>
+        <v>2.273877158399645</v>
       </c>
       <c r="C7" t="n">
-        <v>2.192017099947712</v>
+        <v>2.299621045059779</v>
       </c>
       <c r="D7" t="n">
-        <v>2.201107630163698</v>
+        <v>2.384471130555482</v>
       </c>
       <c r="E7" t="n">
-        <v>1.922489505223061</v>
+        <v>1.905412110136443</v>
       </c>
       <c r="F7" t="n">
-        <v>1.87677133710956</v>
+        <v>1.99287854416314</v>
       </c>
       <c r="G7" t="n">
-        <v>3.441681864722132</v>
+        <v>3.410105329085152</v>
       </c>
       <c r="H7" t="n">
-        <v>2.026745666052346</v>
+        <v>2.148295402006037</v>
       </c>
       <c r="I7" t="n">
-        <v>2.390529312374133</v>
+        <v>2.501181032368933</v>
       </c>
       <c r="J7" t="n">
-        <v>2.831304472667616</v>
+        <v>2.849471451292751</v>
       </c>
       <c r="K7" t="n">
-        <v>2.616068884518598</v>
+        <v>2.754577494733081</v>
       </c>
       <c r="L7" t="n">
-        <v>2.928063412961241</v>
+        <v>2.183108706327268</v>
       </c>
       <c r="M7" t="n">
-        <v>3.155672798595083</v>
+        <v>3.29195216760647</v>
       </c>
       <c r="N7" t="n">
-        <v>2.309640302107954</v>
+        <v>9.771603527381753</v>
       </c>
       <c r="O7" t="n">
-        <v>2.479499515135591</v>
+        <v>2.594026344927076</v>
       </c>
       <c r="P7" t="n">
-        <v>2.773395476198113</v>
+        <v>2.699847268321875</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.284814272521625</v>
+        <v>2.307715472773404</v>
       </c>
       <c r="R7" t="n">
-        <v>2.199107675939286</v>
+        <v>2.293905880901551</v>
       </c>
       <c r="S7" t="n">
-        <v>2.817291202220751</v>
+        <v>2.769928895224339</v>
       </c>
       <c r="T7" t="n">
-        <v>2.367397455899441</v>
+        <v>2.413893974600505</v>
       </c>
       <c r="U7" t="n">
-        <v>2.738401878176755</v>
+        <v>2.650870069989817</v>
       </c>
       <c r="V7" t="n">
-        <v>2.493494689163838</v>
+        <v>2.589905413583486</v>
       </c>
       <c r="W7" t="n">
-        <v>2.292664822667294</v>
+        <v>2.485309590119489</v>
       </c>
       <c r="X7" t="n">
-        <v>2.57803491036593</v>
+        <v>2.450793306098159</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.509411169688667</v>
+        <v>2.580525319864633</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.494388917311868</v>
+        <v>2.466806540727938</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.42683450719566</v>
+        <v>2.493349865683403</v>
       </c>
       <c r="AB7" t="n">
-        <v>3.000091535615006</v>
+        <v>3.335267398562243</v>
       </c>
     </row>
     <row r="8">
@@ -2834,85 +2834,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.989225813858649</v>
+        <v>4.03553055897158</v>
       </c>
       <c r="C8" t="n">
-        <v>5.344366666079473</v>
+        <v>5.762586117804624</v>
       </c>
       <c r="D8" t="n">
-        <v>5.35345719629548</v>
+        <v>5.847436203300328</v>
       </c>
       <c r="E8" t="n">
-        <v>4.27169726511648</v>
+        <v>4.462478903547982</v>
       </c>
       <c r="F8" t="n">
-        <v>3.755770178598592</v>
+        <v>4.019576419333249</v>
       </c>
       <c r="G8" t="n">
-        <v>6.906793705866869</v>
+        <v>7.225848459988313</v>
       </c>
       <c r="H8" t="n">
-        <v>5.179095232184113</v>
+        <v>5.611260474750888</v>
       </c>
       <c r="I8" t="n">
-        <v>5.542878878505909</v>
+        <v>5.964146105113796</v>
       </c>
       <c r="J8" t="n">
-        <v>5.983654038799378</v>
+        <v>6.312436524037602</v>
       </c>
       <c r="K8" t="n">
-        <v>5.768418450650359</v>
+        <v>6.217542567477937</v>
       </c>
       <c r="L8" t="n">
-        <v>6.080412979093009</v>
+        <v>5.646073779072125</v>
       </c>
       <c r="M8" t="n">
-        <v>6.308022364729106</v>
+        <v>6.754917240339745</v>
       </c>
       <c r="N8" t="n">
-        <v>4.29278094417338</v>
+        <v>9.771603527381753</v>
       </c>
       <c r="O8" t="n">
-        <v>4.783955210958117</v>
+        <v>5.100594435062149</v>
       </c>
       <c r="P8" t="n">
-        <v>4.999090629978817</v>
+        <v>5.117577946818516</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.632411277383237</v>
+        <v>3.735022299857597</v>
       </c>
       <c r="R8" t="n">
-        <v>5.351457242071043</v>
+        <v>5.756870953646401</v>
       </c>
       <c r="S8" t="n">
-        <v>5.969640768352528</v>
+        <v>6.232893967969198</v>
       </c>
       <c r="T8" t="n">
-        <v>5.519747022031202</v>
+        <v>5.876859047345349</v>
       </c>
       <c r="U8" t="n">
-        <v>5.154061250422773</v>
+        <v>5.289181089999607</v>
       </c>
       <c r="V8" t="n">
-        <v>5.23549473993549</v>
+        <v>5.566044762877068</v>
       </c>
       <c r="W8" t="n">
-        <v>5.445310818965615</v>
+        <v>5.948609016987405</v>
       </c>
       <c r="X8" t="n">
-        <v>4.063873455612005</v>
+        <v>4.034028727060011</v>
       </c>
       <c r="Y8" t="n">
-        <v>7.164407070347317</v>
+        <v>7.701205039445014</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.110389380881022</v>
+        <v>4.196857203738488</v>
       </c>
       <c r="AA8" t="n">
-        <v>5.579184073327419</v>
+        <v>5.956314938428269</v>
       </c>
       <c r="AB8" t="n">
-        <v>7.728019037664797</v>
+        <v>8.575394772026483</v>
       </c>
     </row>
     <row r="9">
@@ -2922,85 +2922,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>86.13593311529009</v>
+        <v>86.09660874291033</v>
       </c>
       <c r="C9" t="n">
-        <v>109.3573380472625</v>
+        <v>109.5572620330949</v>
       </c>
       <c r="D9" t="n">
-        <v>109.3664285774787</v>
+        <v>109.6421121185906</v>
       </c>
       <c r="E9" t="n">
-        <v>103.6930494251431</v>
+        <v>103.7543718482869</v>
       </c>
       <c r="F9" t="n">
-        <v>55.15727058708097</v>
+        <v>55.22665693722494</v>
       </c>
       <c r="G9" t="n">
-        <v>110.6070030614712</v>
+        <v>110.6677466436856</v>
       </c>
       <c r="H9" t="n">
-        <v>109.1920666133672</v>
+        <v>109.4059363900413</v>
       </c>
       <c r="I9" t="n">
-        <v>109.5558502596891</v>
+        <v>109.7588220204041</v>
       </c>
       <c r="J9" t="n">
-        <v>109.9966254199824</v>
+        <v>110.1071124393279</v>
       </c>
       <c r="K9" t="n">
-        <v>109.7813898318332</v>
+        <v>110.0122184827684</v>
       </c>
       <c r="L9" t="n">
-        <v>110.0933843602761</v>
+        <v>109.4407496943624</v>
       </c>
       <c r="M9" t="n">
-        <v>110.3209937459101</v>
+        <v>110.5495931556417</v>
       </c>
       <c r="N9" t="n">
-        <v>109.4749612494228</v>
+        <v>9.771603527381753</v>
       </c>
       <c r="O9" t="n">
-        <v>117.391137312929</v>
+        <v>117.6179522346455</v>
       </c>
       <c r="P9" t="n">
-        <v>119.3697228624748</v>
+        <v>119.4128098126191</v>
       </c>
       <c r="Q9" t="n">
-        <v>109.4501354692708</v>
+        <v>109.565356787374</v>
       </c>
       <c r="R9" t="n">
-        <v>109.3644286232544</v>
+        <v>109.5515468689368</v>
       </c>
       <c r="S9" t="n">
-        <v>109.9826121495355</v>
+        <v>110.0275698832595</v>
       </c>
       <c r="T9" t="n">
-        <v>109.5327184032144</v>
+        <v>109.6715349626359</v>
       </c>
       <c r="U9" t="n">
-        <v>109.9015061781487</v>
+        <v>109.9340379706625</v>
       </c>
       <c r="V9" t="n">
-        <v>136.63260279255</v>
+        <v>136.8909350037817</v>
       </c>
       <c r="W9" t="n">
-        <v>109.4579857699822</v>
+        <v>109.7429505781547</v>
       </c>
       <c r="X9" t="n">
-        <v>109.7433558576806</v>
+        <v>109.7084342941332</v>
       </c>
       <c r="Y9" t="n">
-        <v>109.6747321170036</v>
+        <v>109.8381663078999</v>
       </c>
       <c r="Z9" t="n">
-        <v>95.56690763342043</v>
+        <v>95.59528120156402</v>
       </c>
       <c r="AA9" t="n">
-        <v>109.5921554545106</v>
+        <v>109.7509908537184</v>
       </c>
       <c r="AB9" t="n">
-        <v>110.1654124829299</v>
+        <v>110.5929083865975</v>
       </c>
     </row>
   </sheetData>
@@ -3166,85 +3166,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.046799980738992</v>
+        <v>2.453419964662399</v>
       </c>
       <c r="C2" t="n">
-        <v>2.068249326849102</v>
+        <v>2.626995143814099</v>
       </c>
       <c r="D2" t="n">
-        <v>2.045267579821104</v>
+        <v>2.473989551268938</v>
       </c>
       <c r="E2" t="n">
-        <v>2.02741861815724</v>
+        <v>2.438692898553359</v>
       </c>
       <c r="F2" t="n">
-        <v>2.028434343294394</v>
+        <v>2.448843060475876</v>
       </c>
       <c r="G2" t="n">
-        <v>2.140336513931357</v>
+        <v>2.548900167041879</v>
       </c>
       <c r="H2" t="n">
-        <v>2.011245868267692</v>
+        <v>2.432364444275142</v>
       </c>
       <c r="I2" t="n">
-        <v>2.157781969373599</v>
+        <v>2.574970772112164</v>
       </c>
       <c r="J2" t="n">
-        <v>2.091247051398959</v>
+        <v>2.503404569586984</v>
       </c>
       <c r="K2" t="n">
-        <v>2.077122383170598</v>
+        <v>2.487437928382289</v>
       </c>
       <c r="L2" t="n">
-        <v>2.084363719600352</v>
+        <v>2.438968534113629</v>
       </c>
       <c r="M2" t="n">
-        <v>2.110032066780837</v>
+        <v>2.532400950915512</v>
       </c>
       <c r="N2" t="n">
-        <v>2.047670710887969</v>
+        <v>2.466242149191703</v>
       </c>
       <c r="O2" t="n">
-        <v>3.871771922435446</v>
+        <v>4.782909179304438</v>
       </c>
       <c r="P2" t="n">
-        <v>2.081929928973148</v>
+        <v>2.483998430156811</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.11692904109167</v>
+        <v>2.531301236892554</v>
       </c>
       <c r="R2" t="n">
-        <v>2.021194895179045</v>
+        <v>2.440044987221151</v>
       </c>
       <c r="S2" t="n">
-        <v>2.083691300841076</v>
+        <v>2.489698541232653</v>
       </c>
       <c r="T2" t="n">
-        <v>2.037782560622874</v>
+        <v>2.450842071293221</v>
       </c>
       <c r="U2" t="n">
-        <v>2.168947939094566</v>
+        <v>3.101879905228493</v>
       </c>
       <c r="V2" t="n">
-        <v>2.052835149438754</v>
+        <v>2.472144400491752</v>
       </c>
       <c r="W2" t="n">
-        <v>2.237926157616331</v>
+        <v>3.287952029158691</v>
       </c>
       <c r="X2" t="n">
-        <v>2.071369374808068</v>
+        <v>2.470711563775543</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.084174001408037</v>
+        <v>2.507428412867814</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.983120697473826</v>
+        <v>2.539968668909796</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.050474799098772</v>
+        <v>2.461506003044012</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.095440964916582</v>
+        <v>2.533299561763502</v>
       </c>
     </row>
     <row r="3">
@@ -3254,85 +3254,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.257006270612895</v>
+        <v>2.565006189611183</v>
       </c>
       <c r="C3" t="n">
-        <v>2.243500650343102</v>
+        <v>2.876435259531383</v>
       </c>
       <c r="D3" t="n">
-        <v>2.2478116156078</v>
+        <v>2.713509697857538</v>
       </c>
       <c r="E3" t="n">
-        <v>2.119923390571614</v>
+        <v>2.46088952666591</v>
       </c>
       <c r="F3" t="n">
-        <v>2.127434808290241</v>
+        <v>2.533666230928137</v>
       </c>
       <c r="G3" t="n">
-        <v>2.92195538911557</v>
+        <v>3.24381828237401</v>
       </c>
       <c r="H3" t="n">
-        <v>2.004539434429335</v>
+        <v>2.415933460000839</v>
       </c>
       <c r="I3" t="n">
-        <v>3.053886129871662</v>
+        <v>3.437067559473979</v>
       </c>
       <c r="J3" t="n">
-        <v>2.573964245778047</v>
+        <v>2.921406060571584</v>
       </c>
       <c r="K3" t="n">
-        <v>2.472931121557983</v>
+        <v>2.807322418228539</v>
       </c>
       <c r="L3" t="n">
-        <v>2.525818904896608</v>
+        <v>2.462535468701746</v>
       </c>
       <c r="M3" t="n">
-        <v>2.713848636470486</v>
+        <v>3.136205710164297</v>
       </c>
       <c r="N3" t="n">
-        <v>2.264633570692933</v>
+        <v>2.657687199998338</v>
       </c>
       <c r="O3" t="n">
-        <v>5.294779005115553</v>
+        <v>6.509654523850386</v>
       </c>
       <c r="P3" t="n">
-        <v>2.506627045927116</v>
+        <v>2.782298083281689</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.75879125109781</v>
+        <v>3.121869630901979</v>
       </c>
       <c r="R3" t="n">
-        <v>2.075783777872522</v>
+        <v>2.470874883229779</v>
       </c>
       <c r="S3" t="n">
-        <v>2.519509705144169</v>
+        <v>2.823151563675808</v>
       </c>
       <c r="T3" t="n">
-        <v>2.194374275819729</v>
+        <v>2.547992024665126</v>
       </c>
       <c r="U3" t="n">
-        <v>2.624834564616</v>
+        <v>3.690534903240696</v>
       </c>
       <c r="V3" t="n">
-        <v>2.299243463358262</v>
+        <v>2.697488746482846</v>
       </c>
       <c r="W3" t="n">
-        <v>2.540470177505335</v>
+        <v>4.036602007655721</v>
       </c>
       <c r="X3" t="n">
-        <v>2.434190551100597</v>
+        <v>2.689790128955986</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.524701832070638</v>
+        <v>2.951166947576497</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.28841651114865</v>
+        <v>2.854215898722316</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.28433829873428</v>
+        <v>2.623548638416302</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.609634218426885</v>
+        <v>3.14066368690597</v>
       </c>
     </row>
     <row r="4">
@@ -3342,85 +3342,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.815362231803763</v>
+        <v>2.00271771784218</v>
       </c>
       <c r="C4" t="n">
-        <v>1.715034444698307</v>
+        <v>2.055219505038207</v>
       </c>
       <c r="D4" t="n">
-        <v>1.798053058496981</v>
+        <v>2.235060661040157</v>
       </c>
       <c r="E4" t="n">
-        <v>1.596440825575606</v>
+        <v>1.836368731355301</v>
       </c>
       <c r="F4" t="n">
-        <v>1.607913908256417</v>
+        <v>1.951019479575386</v>
       </c>
       <c r="G4" t="n">
-        <v>2.871900403142699</v>
+        <v>3.081210526781254</v>
       </c>
       <c r="H4" t="n">
-        <v>1.413762175740636</v>
+        <v>1.764885929049999</v>
       </c>
       <c r="I4" t="n">
-        <v>3.068954847668783</v>
+        <v>3.375690004121171</v>
       </c>
       <c r="J4" t="n">
-        <v>2.31647041205369</v>
+        <v>2.566269005068594</v>
       </c>
       <c r="K4" t="n">
-        <v>2.157867716263031</v>
+        <v>2.386966267094611</v>
       </c>
       <c r="L4" t="n">
-        <v>2.239661942416443</v>
+        <v>1.839482161807239</v>
       </c>
       <c r="M4" t="n">
-        <v>2.532990016360884</v>
+        <v>2.902021137689739</v>
       </c>
       <c r="N4" t="n">
-        <v>1.825197529392126</v>
+        <v>10.87359888260983</v>
       </c>
       <c r="O4" t="n">
-        <v>1.869209792254689</v>
+        <v>2.209824810043359</v>
       </c>
       <c r="P4" t="n">
-        <v>2.212171157683164</v>
+        <v>2.348115552390574</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.607502229448917</v>
+        <v>2.882422514836837</v>
       </c>
       <c r="R4" t="n">
-        <v>1.526141011482865</v>
+        <v>1.851641194849599</v>
       </c>
       <c r="S4" t="n">
-        <v>2.232066663202506</v>
+        <v>2.412500929172896</v>
       </c>
       <c r="T4" t="n">
-        <v>1.713506323374024</v>
+        <v>1.973599226347299</v>
       </c>
       <c r="U4" t="n">
-        <v>2.085645805540191</v>
+        <v>1.989169598146435</v>
       </c>
       <c r="V4" t="n">
-        <v>1.877511749281793</v>
+        <v>2.207766217166752</v>
       </c>
       <c r="W4" t="n">
-        <v>1.747266740160285</v>
+        <v>2.194671579938396</v>
       </c>
       <c r="X4" t="n">
-        <v>2.092884840293662</v>
+        <v>2.198034284353628</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.165615998654722</v>
+        <v>2.486122450575887</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.099956272460437</v>
+        <v>2.307222394845276</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.856870995677472</v>
+        <v>2.094053241123599</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.365951709688169</v>
+        <v>2.905159014872803</v>
       </c>
     </row>
     <row r="5">
@@ -3430,85 +3430,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9.534956124400823</v>
+        <v>7.706483068032184</v>
       </c>
       <c r="C5" t="n">
-        <v>8.288810327243043</v>
+        <v>9.043075537234849</v>
       </c>
       <c r="D5" t="n">
-        <v>10.13164862927886</v>
+        <v>12.69545654857541</v>
       </c>
       <c r="E5" t="n">
-        <v>6.307056180006204</v>
+        <v>5.277961013070909</v>
       </c>
       <c r="F5" t="n">
-        <v>6.645822327096763</v>
+        <v>7.479091012128158</v>
       </c>
       <c r="G5" t="n">
-        <v>26.86083214641671</v>
+        <v>25.41595261665271</v>
       </c>
       <c r="H5" t="n">
-        <v>3.09772701841114</v>
+        <v>4.122718164939124</v>
       </c>
       <c r="I5" t="n">
-        <v>34.19215023320779</v>
+        <v>34.34623351929267</v>
       </c>
       <c r="J5" t="n">
-        <v>18.27731408309756</v>
+        <v>17.51368256469364</v>
       </c>
       <c r="K5" t="n">
-        <v>15.34002016905388</v>
+        <v>14.25811945266239</v>
       </c>
       <c r="L5" t="n">
-        <v>17.41166719098765</v>
+        <v>5.166530545066858</v>
       </c>
       <c r="M5" t="n">
-        <v>24.1493375673924</v>
+        <v>25.48239985553506</v>
       </c>
       <c r="N5" t="n">
-        <v>15.26894467243501</v>
+        <v>10.87359888260983</v>
       </c>
       <c r="O5" t="n">
-        <v>10.05613232749954</v>
+        <v>10.75025785744794</v>
       </c>
       <c r="P5" t="n">
-        <v>15.9813590894733</v>
+        <v>13.32406471668429</v>
       </c>
       <c r="Q5" t="n">
-        <v>24.20360173434301</v>
+        <v>23.79457937315809</v>
       </c>
       <c r="R5" t="n">
-        <v>5.208484323637502</v>
+        <v>5.721909046613063</v>
       </c>
       <c r="S5" t="n">
-        <v>16.49475403885689</v>
+        <v>14.55170368717905</v>
       </c>
       <c r="T5" t="n">
-        <v>8.627809187194627</v>
+        <v>7.908898803432825</v>
       </c>
       <c r="U5" t="n">
-        <v>15.60129593808792</v>
+        <v>9.828097057081775</v>
       </c>
       <c r="V5" t="n">
-        <v>10.30134335730254</v>
+        <v>10.84239558637378</v>
       </c>
       <c r="W5" t="n">
-        <v>8.874772306829824</v>
+        <v>11.5228861062119</v>
       </c>
       <c r="X5" t="n">
-        <v>15.39242117002679</v>
+        <v>11.87246735999257</v>
       </c>
       <c r="Y5" t="n">
-        <v>17.49656162931004</v>
+        <v>18.85886715687191</v>
       </c>
       <c r="Z5" t="n">
-        <v>13.68394055998398</v>
+        <v>12.28524565611864</v>
       </c>
       <c r="AA5" t="n">
-        <v>10.84157244110034</v>
+        <v>9.75306014383241</v>
       </c>
       <c r="AB5" t="n">
-        <v>21.78159088675729</v>
+        <v>26.49894311323549</v>
       </c>
     </row>
     <row r="6">
@@ -3518,85 +3518,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.121976841278748</v>
+        <v>4.562384751932971</v>
       </c>
       <c r="C6" t="n">
-        <v>2.021649054173299</v>
+        <v>2.518027408524032</v>
       </c>
       <c r="D6" t="n">
-        <v>3.923967982704671</v>
+        <v>4.794727695130942</v>
       </c>
       <c r="E6" t="n">
-        <v>1.903055435050593</v>
+        <v>4.396035765446253</v>
       </c>
       <c r="F6" t="n">
-        <v>3.733828832464106</v>
+        <v>2.413827383061278</v>
       </c>
       <c r="G6" t="n">
-        <v>3.178515012617683</v>
+        <v>3.544018430267029</v>
       </c>
       <c r="H6" t="n">
-        <v>1.720376785215622</v>
+        <v>2.22769383253593</v>
       </c>
       <c r="I6" t="n">
-        <v>3.37556945714377</v>
+        <v>3.838497907607106</v>
       </c>
       <c r="J6" t="n">
-        <v>4.442385336261378</v>
+        <v>5.12593603915944</v>
       </c>
       <c r="K6" t="n">
-        <v>4.283782640470716</v>
+        <v>4.946633301185539</v>
       </c>
       <c r="L6" t="n">
-        <v>2.54627655189143</v>
+        <v>4.399149195898109</v>
       </c>
       <c r="M6" t="n">
-        <v>4.658904940568574</v>
+        <v>3.36482904117566</v>
       </c>
       <c r="N6" t="n">
-        <v>2.133625724203851</v>
+        <v>10.87359888260983</v>
       </c>
       <c r="O6" t="n">
-        <v>2.177637987066414</v>
+        <v>4.879678268324521</v>
       </c>
       <c r="P6" t="n">
-        <v>4.387443941956726</v>
+        <v>5.025063179480593</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.733417153656603</v>
+        <v>5.442089548927699</v>
       </c>
       <c r="R6" t="n">
-        <v>3.652055935690549</v>
+        <v>2.314449098335527</v>
       </c>
       <c r="S6" t="n">
-        <v>2.538681272677494</v>
+        <v>4.972167963263757</v>
       </c>
       <c r="T6" t="n">
-        <v>2.020120932849008</v>
+        <v>2.436407129833306</v>
       </c>
       <c r="U6" t="n">
-        <v>2.464163404520022</v>
+        <v>2.578623036492282</v>
       </c>
       <c r="V6" t="n">
-        <v>4.003426673489477</v>
+        <v>4.767433251257635</v>
       </c>
       <c r="W6" t="n">
-        <v>2.07358104874517</v>
+        <v>4.862445042456422</v>
       </c>
       <c r="X6" t="n">
-        <v>2.39949944976865</v>
+        <v>2.66084218783951</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.56138309527098</v>
+        <v>3.097890376561263</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.406570881935423</v>
+        <v>4.866889428936173</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.982785919885159</v>
+        <v>4.653720275214501</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.676886256783663</v>
+        <v>3.362118058581214</v>
       </c>
     </row>
     <row r="7">
@@ -3606,85 +3606,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.438494590324903</v>
+        <v>2.736131633239183</v>
       </c>
       <c r="C7" t="n">
-        <v>2.338166803219453</v>
+        <v>2.788633420435234</v>
       </c>
       <c r="D7" t="n">
-        <v>2.421185417018126</v>
+        <v>2.968474576437267</v>
       </c>
       <c r="E7" t="n">
-        <v>2.219573184096744</v>
+        <v>2.569782646752437</v>
       </c>
       <c r="F7" t="n">
-        <v>2.231046266777556</v>
+        <v>2.684433394972468</v>
       </c>
       <c r="G7" t="n">
-        <v>3.495032761663838</v>
+        <v>3.814624442178578</v>
       </c>
       <c r="H7" t="n">
-        <v>2.036894534261774</v>
+        <v>2.498299844447089</v>
       </c>
       <c r="I7" t="n">
-        <v>3.692087206189922</v>
+        <v>4.109103919518327</v>
       </c>
       <c r="J7" t="n">
-        <v>2.939602770574826</v>
+        <v>3.299682920465773</v>
       </c>
       <c r="K7" t="n">
-        <v>2.781000074784171</v>
+        <v>3.120380182491729</v>
       </c>
       <c r="L7" t="n">
-        <v>2.862794300937582</v>
+        <v>2.57289607720437</v>
       </c>
       <c r="M7" t="n">
-        <v>3.156122374882027</v>
+        <v>3.635435053086844</v>
       </c>
       <c r="N7" t="n">
-        <v>2.448329887913266</v>
+        <v>10.87359888260983</v>
       </c>
       <c r="O7" t="n">
-        <v>2.492319823220202</v>
+        <v>2.94324001894797</v>
       </c>
       <c r="P7" t="n">
-        <v>2.835281188648675</v>
+        <v>3.081530761295268</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.230634587970055</v>
+        <v>3.615836430233928</v>
       </c>
       <c r="R7" t="n">
-        <v>2.149273370004006</v>
+        <v>2.585055110246672</v>
       </c>
       <c r="S7" t="n">
-        <v>2.855199021723646</v>
+        <v>3.145914844570033</v>
       </c>
       <c r="T7" t="n">
-        <v>2.336638681895161</v>
+        <v>2.707013141744458</v>
       </c>
       <c r="U7" t="n">
-        <v>2.810501587336676</v>
+        <v>2.832425433680407</v>
       </c>
       <c r="V7" t="n">
-        <v>2.500644107802929</v>
+        <v>2.941180132563891</v>
       </c>
       <c r="W7" t="n">
-        <v>2.370399098681429</v>
+        <v>2.928085495335518</v>
       </c>
       <c r="X7" t="n">
-        <v>2.716017198814801</v>
+        <v>2.931448199750736</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.860651346680707</v>
+        <v>3.346181900832875</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.723088630981579</v>
+        <v>3.040636310242435</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.480003354198612</v>
+        <v>2.827467156520718</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.989084068209308</v>
+        <v>3.638572930269835</v>
       </c>
     </row>
     <row r="8">
@@ -3694,85 +3694,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.969727068590255</v>
+        <v>4.494327761473631</v>
       </c>
       <c r="C8" t="n">
-        <v>5.293310860092344</v>
+        <v>6.360745990543156</v>
       </c>
       <c r="D8" t="n">
-        <v>5.376329473891009</v>
+        <v>6.540587146545196</v>
       </c>
       <c r="E8" t="n">
-        <v>4.41652632816898</v>
+        <v>5.176038219812154</v>
       </c>
       <c r="F8" t="n">
-        <v>3.984107527338617</v>
+        <v>4.725216504630237</v>
       </c>
       <c r="G8" t="n">
-        <v>6.745434160318908</v>
+        <v>7.762864402777922</v>
       </c>
       <c r="H8" t="n">
-        <v>4.992038591134665</v>
+        <v>6.070412414554817</v>
       </c>
       <c r="I8" t="n">
-        <v>6.647231263062812</v>
+        <v>7.681216489626252</v>
       </c>
       <c r="J8" t="n">
-        <v>5.894746827447722</v>
+        <v>6.871795490573266</v>
       </c>
       <c r="K8" t="n">
-        <v>5.736144131657068</v>
+        <v>6.692492752599707</v>
       </c>
       <c r="L8" t="n">
-        <v>5.817938357810476</v>
+        <v>6.145008647312165</v>
       </c>
       <c r="M8" t="n">
-        <v>6.111266431756888</v>
+        <v>7.207547623172118</v>
       </c>
       <c r="N8" t="n">
-        <v>4.29970425609308</v>
+        <v>10.87359888260983</v>
       </c>
       <c r="O8" t="n">
-        <v>4.647042013174133</v>
+        <v>5.495667972870701</v>
       </c>
       <c r="P8" t="n">
-        <v>4.915650970620572</v>
+        <v>5.539241419381853</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.482035941872446</v>
+        <v>5.017556578378416</v>
       </c>
       <c r="R8" t="n">
-        <v>5.104417426876893</v>
+        <v>6.157167680354402</v>
       </c>
       <c r="S8" t="n">
-        <v>5.810343078596544</v>
+        <v>6.718027414677914</v>
       </c>
       <c r="T8" t="n">
-        <v>5.291782738768056</v>
+        <v>6.27912571185254</v>
       </c>
       <c r="U8" t="n">
-        <v>5.063960380966261</v>
+        <v>5.52296981911639</v>
       </c>
       <c r="V8" t="n">
-        <v>5.092120513697576</v>
+        <v>6.003157566238403</v>
       </c>
       <c r="W8" t="n">
-        <v>5.325822994771547</v>
+        <v>6.500554547202908</v>
       </c>
       <c r="X8" t="n">
-        <v>4.097922878131314</v>
+        <v>4.499417391141654</v>
       </c>
       <c r="Y8" t="n">
-        <v>7.271122541125506</v>
+        <v>8.699551066760723</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.227871220626502</v>
+        <v>4.765138009755434</v>
       </c>
       <c r="AA8" t="n">
-        <v>5.435147411071515</v>
+        <v>6.399579726628415</v>
       </c>
       <c r="AB8" t="n">
-        <v>7.431622834343067</v>
+        <v>9.105472896561508</v>
       </c>
     </row>
     <row r="9">
@@ -3782,85 +3782,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>80.42870138671005</v>
+        <v>80.77810665781855</v>
       </c>
       <c r="C9" t="n">
-        <v>102.0932533827974</v>
+        <v>102.7167878466588</v>
       </c>
       <c r="D9" t="n">
-        <v>102.1762719965961</v>
+        <v>102.8966290026607</v>
       </c>
       <c r="E9" t="n">
-        <v>96.95141452180988</v>
+        <v>97.44669652919009</v>
       </c>
       <c r="F9" t="n">
-        <v>51.81214434844668</v>
+        <v>52.15897033351156</v>
       </c>
       <c r="G9" t="n">
-        <v>103.2501196464526</v>
+        <v>103.742779375439</v>
       </c>
       <c r="H9" t="n">
-        <v>101.7919811138398</v>
+        <v>102.4264542706705</v>
       </c>
       <c r="I9" t="n">
-        <v>103.4471737857679</v>
+        <v>104.0372583457416</v>
       </c>
       <c r="J9" t="n">
-        <v>102.6946893501527</v>
+        <v>103.2278373466891</v>
       </c>
       <c r="K9" t="n">
-        <v>102.5360866543621</v>
+        <v>103.0485346087152</v>
       </c>
       <c r="L9" t="n">
-        <v>102.6178808805156</v>
+        <v>102.5010505034278</v>
       </c>
       <c r="M9" t="n">
-        <v>102.91120895446</v>
+        <v>103.5635894793103</v>
       </c>
       <c r="N9" t="n">
-        <v>102.2034164674911</v>
+        <v>10.87359888260983</v>
       </c>
       <c r="O9" t="n">
-        <v>109.4602817981752</v>
+        <v>110.1244450229228</v>
       </c>
       <c r="P9" t="n">
-        <v>111.3719148877633</v>
+        <v>111.8401499955883</v>
       </c>
       <c r="Q9" t="n">
-        <v>102.9857214727588</v>
+        <v>103.5439913634943</v>
       </c>
       <c r="R9" t="n">
-        <v>101.904359949582</v>
+        <v>102.5132095364701</v>
       </c>
       <c r="S9" t="n">
-        <v>102.6102856013016</v>
+        <v>103.0740692707935</v>
       </c>
       <c r="T9" t="n">
-        <v>102.0917252614731</v>
+        <v>102.6351675679676</v>
       </c>
       <c r="U9" t="n">
-        <v>102.5357677331442</v>
+        <v>102.777383474627</v>
       </c>
       <c r="V9" t="n">
-        <v>127.3719404674919</v>
+        <v>128.1255217375783</v>
       </c>
       <c r="W9" t="n">
-        <v>102.1254856782594</v>
+        <v>102.856239921559</v>
       </c>
       <c r="X9" t="n">
-        <v>102.4711037783928</v>
+        <v>102.859602625974</v>
       </c>
       <c r="Y9" t="n">
-        <v>102.6157379262586</v>
+        <v>103.2743363270564</v>
       </c>
       <c r="Z9" t="n">
-        <v>89.35588823111286</v>
+        <v>89.77337095361889</v>
       </c>
       <c r="AA9" t="n">
-        <v>102.2350899337766</v>
+        <v>102.7556215827442</v>
       </c>
       <c r="AB9" t="n">
-        <v>102.7441706477872</v>
+        <v>103.5667273564933</v>
       </c>
     </row>
   </sheetData>
@@ -4026,85 +4026,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.103532809552746</v>
+        <v>2.62422502594185</v>
       </c>
       <c r="C2" t="n">
-        <v>2.112033052571954</v>
+        <v>2.860397404555671</v>
       </c>
       <c r="D2" t="n">
-        <v>2.096524149892752</v>
+        <v>2.634502045743093</v>
       </c>
       <c r="E2" t="n">
-        <v>2.064439256710437</v>
+        <v>2.588068434377308</v>
       </c>
       <c r="F2" t="n">
-        <v>2.106342885014898</v>
+        <v>2.639318086138652</v>
       </c>
       <c r="G2" t="n">
-        <v>2.186570647843087</v>
+        <v>2.711580456204373</v>
       </c>
       <c r="H2" t="n">
-        <v>2.069581104098249</v>
+        <v>2.603549694586645</v>
       </c>
       <c r="I2" t="n">
-        <v>2.169772849262711</v>
+        <v>2.696665086155855</v>
       </c>
       <c r="J2" t="n">
-        <v>2.144267422981989</v>
+        <v>2.670158609974452</v>
       </c>
       <c r="K2" t="n">
-        <v>2.142616195370939</v>
+        <v>2.660542181682984</v>
       </c>
       <c r="L2" t="n">
-        <v>2.139206297249409</v>
+        <v>2.619581387210956</v>
       </c>
       <c r="M2" t="n">
-        <v>2.155954622248256</v>
+        <v>2.691632131174362</v>
       </c>
       <c r="N2" t="n">
-        <v>2.10351390103813</v>
+        <v>2.632566002170837</v>
       </c>
       <c r="O2" t="n">
-        <v>4.041090899649209</v>
+        <v>5.227341239579896</v>
       </c>
       <c r="P2" t="n">
-        <v>2.141205714962687</v>
+        <v>2.654300172730635</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.143822245675283</v>
+        <v>2.664129818984105</v>
       </c>
       <c r="R2" t="n">
-        <v>2.132592806069944</v>
+        <v>2.663473747242632</v>
       </c>
       <c r="S2" t="n">
-        <v>2.146715648281954</v>
+        <v>2.664040195116291</v>
       </c>
       <c r="T2" t="n">
-        <v>2.116616470894639</v>
+        <v>2.644222141417561</v>
       </c>
       <c r="U2" t="n">
-        <v>2.361020384024986</v>
+        <v>3.509893580658892</v>
       </c>
       <c r="V2" t="n">
-        <v>2.119771499918144</v>
+        <v>2.647938410047465</v>
       </c>
       <c r="W2" t="n">
-        <v>2.442393950804061</v>
+        <v>3.739751588442426</v>
       </c>
       <c r="X2" t="n">
-        <v>2.142478418256013</v>
+        <v>2.652874296946361</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.183873462500655</v>
+        <v>2.724785681622179</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.206670607902456</v>
+        <v>2.893745594073673</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.115424307540148</v>
+        <v>2.636651771100202</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.152696821400232</v>
+        <v>2.700875133405165</v>
       </c>
     </row>
     <row r="3">
@@ -4114,85 +4114,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.286577557960392</v>
+        <v>2.71821541528959</v>
       </c>
       <c r="C3" t="n">
-        <v>2.142733478341259</v>
+        <v>3.009080157012053</v>
       </c>
       <c r="D3" t="n">
-        <v>2.238195023939511</v>
+        <v>2.792958375165513</v>
       </c>
       <c r="E3" t="n">
-        <v>2.00939252894314</v>
+        <v>2.46184233459396</v>
       </c>
       <c r="F3" t="n">
-        <v>2.308741489466201</v>
+        <v>2.827843325197714</v>
       </c>
       <c r="G3" t="n">
-        <v>2.875873326783761</v>
+        <v>3.338203105008404</v>
       </c>
       <c r="H3" t="n">
-        <v>2.04602059732356</v>
+        <v>2.572373292192077</v>
       </c>
       <c r="I3" t="n">
-        <v>2.762681852831582</v>
+        <v>3.238278714574765</v>
       </c>
       <c r="J3" t="n">
-        <v>2.576892384061047</v>
+        <v>3.045540506553649</v>
       </c>
       <c r="K3" t="n">
-        <v>2.565221337900363</v>
+        <v>2.97719448228061</v>
       </c>
       <c r="L3" t="n">
-        <v>2.541289856806456</v>
+        <v>2.685811067044779</v>
       </c>
       <c r="M3" t="n">
-        <v>2.665737088260558</v>
+        <v>3.206974777593735</v>
       </c>
       <c r="N3" t="n">
-        <v>2.288290553000965</v>
+        <v>2.779308073237586</v>
       </c>
       <c r="O3" t="n">
-        <v>5.480970979903709</v>
+        <v>7.07841661981518</v>
       </c>
       <c r="P3" t="n">
-        <v>2.553789886472857</v>
+        <v>2.931539518492208</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.574986530232663</v>
+        <v>3.00367788931891</v>
       </c>
       <c r="R3" t="n">
-        <v>2.497667897450896</v>
+        <v>3.00182412324242</v>
       </c>
       <c r="S3" t="n">
-        <v>2.593834642824057</v>
+        <v>3.001474998467732</v>
       </c>
       <c r="T3" t="n">
-        <v>2.382595180610757</v>
+        <v>2.863273811669968</v>
       </c>
       <c r="U3" t="n">
-        <v>2.89838179105322</v>
+        <v>4.18347400629466</v>
       </c>
       <c r="V3" t="n">
-        <v>2.401412018677435</v>
+        <v>2.886156680177414</v>
       </c>
       <c r="W3" t="n">
-        <v>2.829042109429798</v>
+        <v>4.665951768024379</v>
       </c>
       <c r="X3" t="n">
-        <v>2.566026962933244</v>
+        <v>2.923925684595092</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.862148633919666</v>
+        <v>3.437884207104372</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.60321860297127</v>
+        <v>3.313762545724393</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.373067506245056</v>
+        <v>2.808195137412473</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.642770148155625</v>
+        <v>3.271313112408909</v>
       </c>
     </row>
     <row r="4">
@@ -4202,85 +4202,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.91618083810317</v>
+        <v>2.271619454046292</v>
       </c>
       <c r="C4" t="n">
-        <v>1.590194577005109</v>
+        <v>2.067819274200209</v>
       </c>
       <c r="D4" t="n">
-        <v>1.837014803100769</v>
+        <v>2.387703120364008</v>
       </c>
       <c r="E4" t="n">
-        <v>1.474601174826397</v>
+        <v>1.863214119470879</v>
       </c>
       <c r="F4" t="n">
-        <v>1.947921933146727</v>
+        <v>2.442102512119833</v>
       </c>
       <c r="G4" t="n">
-        <v>2.854131420885417</v>
+        <v>3.258339224344422</v>
       </c>
       <c r="H4" t="n">
-        <v>1.532680706438474</v>
+        <v>2.038082075267083</v>
       </c>
       <c r="I4" t="n">
-        <v>2.664392558550936</v>
+        <v>3.089863258237525</v>
       </c>
       <c r="J4" t="n">
-        <v>2.375354565636163</v>
+        <v>2.789315870024089</v>
       </c>
       <c r="K4" t="n">
-        <v>2.357645660165406</v>
+        <v>2.68183843485936</v>
       </c>
       <c r="L4" t="n">
-        <v>2.319129292252047</v>
+        <v>2.219167418401353</v>
       </c>
       <c r="M4" t="n">
-        <v>2.513188761663409</v>
+        <v>3.043096255995662</v>
       </c>
       <c r="N4" t="n">
-        <v>1.915967257732143</v>
+        <v>10.83050639163236</v>
       </c>
       <c r="O4" t="n">
-        <v>1.908538603603597</v>
+        <v>2.40325918115258</v>
       </c>
       <c r="P4" t="n">
-        <v>2.341713635101077</v>
+        <v>2.611332072276666</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.371268553163453</v>
+        <v>2.722362448570223</v>
       </c>
       <c r="R4" t="n">
-        <v>2.244426867023758</v>
+        <v>2.71495181644255</v>
       </c>
       <c r="S4" t="n">
-        <v>2.403950866636734</v>
+        <v>2.72135010575438</v>
       </c>
       <c r="T4" t="n">
-        <v>2.063966811741315</v>
+        <v>2.497496072472023</v>
       </c>
       <c r="U4" t="n">
-        <v>2.252606470299185</v>
+        <v>2.22801514937862</v>
       </c>
       <c r="V4" t="n">
-        <v>2.09348714598147</v>
+        <v>2.532372603141346</v>
       </c>
       <c r="W4" t="n">
-        <v>1.878382539602071</v>
+        <v>2.488088795830678</v>
       </c>
       <c r="X4" t="n">
-        <v>2.356089404271597</v>
+        <v>2.595226149358064</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.774408612759098</v>
+        <v>3.357771714212979</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.222849809226317</v>
+        <v>2.586674396010397</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.050500778230162</v>
+        <v>2.411985257195127</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.472538045152235</v>
+        <v>3.138976623326687</v>
       </c>
     </row>
     <row r="5">
@@ -4290,85 +4290,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9.496849031373083</v>
+        <v>8.354328753969678</v>
       </c>
       <c r="C5" t="n">
-        <v>4.545557568364403</v>
+        <v>5.42558647754165</v>
       </c>
       <c r="D5" t="n">
-        <v>8.945840062208573</v>
+        <v>11.13056849443723</v>
       </c>
       <c r="E5" t="n">
-        <v>2.633894816401043</v>
+        <v>2.000751142991024</v>
       </c>
       <c r="F5" t="n">
-        <v>11.15080687229829</v>
+        <v>12.35836883384906</v>
       </c>
       <c r="G5" t="n">
-        <v>24.3502993530434</v>
+        <v>24.00662781505358</v>
       </c>
       <c r="H5" t="n">
-        <v>3.625083216364531</v>
+        <v>5.11453220763414</v>
       </c>
       <c r="I5" t="n">
-        <v>24.46409924805323</v>
+        <v>24.40948576456641</v>
       </c>
       <c r="J5" t="n">
-        <v>17.4212757633685</v>
+        <v>17.26794196477793</v>
       </c>
       <c r="K5" t="n">
-        <v>17.15133652529087</v>
+        <v>15.49660818132428</v>
       </c>
       <c r="L5" t="n">
-        <v>16.68006029287284</v>
+        <v>7.808835685967373</v>
       </c>
       <c r="M5" t="n">
-        <v>21.28480905499505</v>
+        <v>23.13586690105995</v>
       </c>
       <c r="N5" t="n">
-        <v>15.66573885303574</v>
+        <v>10.83050639163236</v>
       </c>
       <c r="O5" t="n">
-        <v>9.263753685667057</v>
+        <v>10.34162330191747</v>
       </c>
       <c r="P5" t="n">
-        <v>16.16228843247405</v>
+        <v>13.67672326305236</v>
       </c>
       <c r="Q5" t="n">
-        <v>17.99215145818431</v>
+        <v>16.66847863809715</v>
       </c>
       <c r="R5" t="n">
-        <v>17.21347659188512</v>
+        <v>18.00328595182103</v>
       </c>
       <c r="S5" t="n">
-        <v>17.63622372110947</v>
+        <v>15.84046370477228</v>
       </c>
       <c r="T5" t="n">
-        <v>13.47822027216981</v>
+        <v>13.56093169205977</v>
       </c>
       <c r="U5" t="n">
-        <v>16.05163492451967</v>
+        <v>8.666516449532295</v>
       </c>
       <c r="V5" t="n">
-        <v>12.18458531681229</v>
+        <v>12.40975639362042</v>
       </c>
       <c r="W5" t="n">
-        <v>9.590827986655981</v>
+        <v>12.81169834271109</v>
       </c>
       <c r="X5" t="n">
-        <v>18.05088814308821</v>
+        <v>14.71992438111992</v>
       </c>
       <c r="Y5" t="n">
-        <v>26.67478142420534</v>
+        <v>29.46117411541059</v>
       </c>
       <c r="Z5" t="n">
-        <v>13.5939924233298</v>
+        <v>12.6970512525077</v>
       </c>
       <c r="AA5" t="n">
-        <v>12.71190512158307</v>
+        <v>11.50514012813357</v>
       </c>
       <c r="AB5" t="n">
-        <v>21.79776287994393</v>
+        <v>26.38717626251981</v>
       </c>
     </row>
     <row r="6">
@@ -4378,85 +4378,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.077461392742768</v>
+        <v>2.808071650474086</v>
       </c>
       <c r="C6" t="n">
-        <v>1.905677189508837</v>
+        <v>2.604271470628093</v>
       </c>
       <c r="D6" t="n">
-        <v>2.152497415604504</v>
+        <v>5.141670904220919</v>
       </c>
       <c r="E6" t="n">
-        <v>3.635881729465839</v>
+        <v>4.617181903327855</v>
       </c>
       <c r="F6" t="n">
-        <v>2.263404545650457</v>
+        <v>2.978554708547689</v>
       </c>
       <c r="G6" t="n">
-        <v>5.015411975524925</v>
+        <v>3.794791420772606</v>
       </c>
       <c r="H6" t="n">
-        <v>1.848163318942212</v>
+        <v>4.792049859123834</v>
       </c>
       <c r="I6" t="n">
-        <v>2.979875171054662</v>
+        <v>3.626315454665351</v>
       </c>
       <c r="J6" t="n">
-        <v>4.536635120275536</v>
+        <v>5.543283653881094</v>
       </c>
       <c r="K6" t="n">
-        <v>4.518926214804955</v>
+        <v>5.435806218716353</v>
       </c>
       <c r="L6" t="n">
-        <v>4.480409846891515</v>
+        <v>2.755619614829331</v>
       </c>
       <c r="M6" t="n">
-        <v>2.828671374167158</v>
+        <v>3.579548452423435</v>
       </c>
       <c r="N6" t="n">
-        <v>2.235058842549618</v>
+        <v>10.83050639163236</v>
       </c>
       <c r="O6" t="n">
-        <v>4.11166356133621</v>
+        <v>2.934256560137761</v>
       </c>
       <c r="P6" t="n">
-        <v>2.638241454063559</v>
+        <v>5.47482048127701</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.532549107802891</v>
+        <v>5.476330232427066</v>
       </c>
       <c r="R6" t="n">
-        <v>4.405707421663243</v>
+        <v>5.468919600299422</v>
       </c>
       <c r="S6" t="n">
-        <v>4.565231421276195</v>
+        <v>3.257802302182073</v>
       </c>
       <c r="T6" t="n">
-        <v>4.225247366380831</v>
+        <v>5.251463856329178</v>
       </c>
       <c r="U6" t="n">
-        <v>2.617345941719884</v>
+        <v>5.031709539165282</v>
       </c>
       <c r="V6" t="n">
-        <v>2.408969758485199</v>
+        <v>3.068824799569131</v>
       </c>
       <c r="W6" t="n">
-        <v>4.081224448268143</v>
+        <v>3.060720923169481</v>
       </c>
       <c r="X6" t="n">
-        <v>2.671572016775329</v>
+        <v>3.131678345785705</v>
       </c>
       <c r="Y6" t="n">
-        <v>3.161210092917554</v>
+        <v>3.972171163375724</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.384130363865889</v>
+        <v>3.123126592438247</v>
       </c>
       <c r="AA6" t="n">
-        <v>4.211781332869676</v>
+        <v>5.165953041051885</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.793585211573645</v>
+        <v>3.667123869023014</v>
       </c>
     </row>
     <row r="7">
@@ -4466,85 +4466,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.581270445190523</v>
+        <v>3.067749813720309</v>
       </c>
       <c r="C7" t="n">
-        <v>2.255284184092462</v>
+        <v>2.863949633874187</v>
       </c>
       <c r="D7" t="n">
-        <v>2.502104410188123</v>
+        <v>3.183833480037995</v>
       </c>
       <c r="E7" t="n">
-        <v>2.139690781913745</v>
+        <v>2.659344479144896</v>
       </c>
       <c r="F7" t="n">
-        <v>2.613011540234075</v>
+        <v>3.238232871793797</v>
       </c>
       <c r="G7" t="n">
-        <v>3.51922102797278</v>
+        <v>4.054469584018481</v>
       </c>
       <c r="H7" t="n">
-        <v>2.197770313525825</v>
+        <v>2.834212434941068</v>
       </c>
       <c r="I7" t="n">
-        <v>3.329482165638292</v>
+        <v>3.885993617911463</v>
       </c>
       <c r="J7" t="n">
-        <v>3.040444172723522</v>
+        <v>3.585446229698069</v>
       </c>
       <c r="K7" t="n">
-        <v>3.022735267252761</v>
+        <v>3.477968794533379</v>
       </c>
       <c r="L7" t="n">
-        <v>2.984218899339395</v>
+        <v>3.015297778075333</v>
       </c>
       <c r="M7" t="n">
-        <v>3.178278368750766</v>
+        <v>3.839226615669642</v>
       </c>
       <c r="N7" t="n">
-        <v>2.581056864819496</v>
+        <v>10.83050639163236</v>
       </c>
       <c r="O7" t="n">
-        <v>2.573577918362654</v>
+        <v>3.199374985873793</v>
       </c>
       <c r="P7" t="n">
-        <v>3.006752949860137</v>
+        <v>3.407447876997822</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.03635816025081</v>
+        <v>3.518492808244241</v>
       </c>
       <c r="R7" t="n">
-        <v>2.909516474111122</v>
+        <v>3.511082176116526</v>
       </c>
       <c r="S7" t="n">
-        <v>3.069040473724095</v>
+        <v>3.517480465428385</v>
       </c>
       <c r="T7" t="n">
-        <v>2.729056418828675</v>
+        <v>3.293626432146032</v>
       </c>
       <c r="U7" t="n">
-        <v>3.04718598915215</v>
+        <v>3.079433926056615</v>
       </c>
       <c r="V7" t="n">
-        <v>2.75857675306882</v>
+        <v>3.328502962815354</v>
       </c>
       <c r="W7" t="n">
-        <v>2.543472146689429</v>
+        <v>3.284219155504698</v>
       </c>
       <c r="X7" t="n">
-        <v>3.021179011358947</v>
+        <v>3.391356509032001</v>
       </c>
       <c r="Y7" t="n">
-        <v>3.488755078763402</v>
+        <v>4.203628679816676</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.887939416313598</v>
+        <v>3.382804755684405</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.715590385317518</v>
+        <v>3.208115616869135</v>
       </c>
       <c r="AB7" t="n">
-        <v>3.137627652239584</v>
+        <v>3.935106983000736</v>
       </c>
     </row>
     <row r="8">
@@ -4554,85 +4554,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.112360383056016</v>
+        <v>4.893726193320748</v>
       </c>
       <c r="C8" t="n">
-        <v>5.244871282779002</v>
+        <v>6.644294352343102</v>
       </c>
       <c r="D8" t="n">
-        <v>5.491691508874659</v>
+        <v>6.964178198506955</v>
       </c>
       <c r="E8" t="n">
-        <v>4.352671165511008</v>
+        <v>5.399045708782073</v>
       </c>
       <c r="F8" t="n">
-        <v>4.371318289878234</v>
+        <v>5.368676996719278</v>
       </c>
       <c r="G8" t="n">
-        <v>6.811237014211597</v>
+        <v>8.240065308665081</v>
       </c>
       <c r="H8" t="n">
-        <v>5.187357412212366</v>
+        <v>6.614557153410087</v>
       </c>
       <c r="I8" t="n">
-        <v>6.319069264324839</v>
+        <v>7.66633833638044</v>
       </c>
       <c r="J8" t="n">
-        <v>6.030031271410075</v>
+        <v>7.365790948167136</v>
       </c>
       <c r="K8" t="n">
-        <v>6.012322365939308</v>
+        <v>7.258313513002288</v>
       </c>
       <c r="L8" t="n">
-        <v>5.973805998025942</v>
+        <v>6.795642496544239</v>
       </c>
       <c r="M8" t="n">
-        <v>6.167865467440719</v>
+        <v>7.619571334114962</v>
       </c>
       <c r="N8" t="n">
-        <v>4.440064662515018</v>
+        <v>10.83050639163236</v>
       </c>
       <c r="O8" t="n">
-        <v>4.743329016775639</v>
+        <v>5.881096661182423</v>
       </c>
       <c r="P8" t="n">
-        <v>5.100345684557264</v>
+        <v>5.987118278320439</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.280820117516493</v>
+        <v>4.960391204753435</v>
       </c>
       <c r="R8" t="n">
-        <v>5.89910357279767</v>
+        <v>7.291426894585408</v>
       </c>
       <c r="S8" t="n">
-        <v>6.058627572410631</v>
+        <v>7.297825183897332</v>
       </c>
       <c r="T8" t="n">
-        <v>5.718643517515214</v>
+        <v>7.073971150615045</v>
       </c>
       <c r="U8" t="n">
-        <v>5.306884658616918</v>
+        <v>5.904637275012469</v>
       </c>
       <c r="V8" t="n">
-        <v>5.418158801897745</v>
+        <v>6.57945588193852</v>
       </c>
       <c r="W8" t="n">
-        <v>5.53334588150603</v>
+        <v>7.064947957114622</v>
       </c>
       <c r="X8" t="n">
-        <v>4.399315131278724</v>
+        <v>5.012376643338345</v>
       </c>
       <c r="Y8" t="n">
-        <v>8.034928955612049</v>
+        <v>9.934550260659263</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.391937020628299</v>
+        <v>5.172477740615513</v>
       </c>
       <c r="AA8" t="n">
-        <v>5.705177484004062</v>
+        <v>6.988460335338193</v>
       </c>
       <c r="AB8" t="n">
-        <v>7.650736992668256</v>
+        <v>9.756952847072172</v>
       </c>
     </row>
     <row r="9">
@@ -4642,85 +4642,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>80.48581555610897</v>
+        <v>81.01562922457934</v>
       </c>
       <c r="C9" t="n">
-        <v>101.9161118467354</v>
+        <v>102.7143729995563</v>
       </c>
       <c r="D9" t="n">
-        <v>102.1629320728311</v>
+        <v>103.03425684572</v>
       </c>
       <c r="E9" t="n">
-        <v>96.77925738973735</v>
+        <v>97.45475046135488</v>
       </c>
       <c r="F9" t="n">
-        <v>52.11966970199764</v>
+        <v>52.59731393336054</v>
       </c>
       <c r="G9" t="n">
-        <v>103.1800489712429</v>
+        <v>103.9048934989073</v>
       </c>
       <c r="H9" t="n">
-        <v>101.8585979761688</v>
+        <v>102.6846358006232</v>
       </c>
       <c r="I9" t="n">
-        <v>102.9903098282811</v>
+        <v>103.7364169835936</v>
       </c>
       <c r="J9" t="n">
-        <v>102.7012718353664</v>
+        <v>103.4358695953804</v>
       </c>
       <c r="K9" t="n">
-        <v>102.6835629298957</v>
+        <v>103.3283921602153</v>
       </c>
       <c r="L9" t="n">
-        <v>102.6450465619822</v>
+        <v>102.8657211437576</v>
       </c>
       <c r="M9" t="n">
-        <v>102.8391060313937</v>
+        <v>103.6896499813518</v>
       </c>
       <c r="N9" t="n">
-        <v>102.2418845274624</v>
+        <v>10.83050639163236</v>
       </c>
       <c r="O9" t="n">
-        <v>109.4444597971735</v>
+        <v>110.3082880254093</v>
       </c>
       <c r="P9" t="n">
-        <v>111.4456869182441</v>
+        <v>112.0949546009948</v>
       </c>
       <c r="Q9" t="n">
-        <v>102.697186103521</v>
+        <v>103.3689167231333</v>
       </c>
       <c r="R9" t="n">
-        <v>102.570344136754</v>
+        <v>103.3615055417983</v>
       </c>
       <c r="S9" t="n">
-        <v>102.7298681363669</v>
+        <v>103.3679038311104</v>
       </c>
       <c r="T9" t="n">
-        <v>102.3898840814716</v>
+        <v>103.1440497978282</v>
       </c>
       <c r="U9" t="n">
-        <v>102.6277805989464</v>
+        <v>102.9242954806643</v>
       </c>
       <c r="V9" t="n">
-        <v>127.525693140891</v>
+        <v>128.453997883289</v>
       </c>
       <c r="W9" t="n">
-        <v>102.2042998093324</v>
+        <v>103.1346425211867</v>
       </c>
       <c r="X9" t="n">
-        <v>102.6820066740019</v>
+        <v>103.2417798747143</v>
       </c>
       <c r="Y9" t="n">
-        <v>103.1495827414062</v>
+        <v>104.0540520454987</v>
       </c>
       <c r="Z9" t="n">
-        <v>89.43166345582763</v>
+        <v>90.0279419848907</v>
       </c>
       <c r="AA9" t="n">
-        <v>102.3764180479603</v>
+        <v>103.0585389825509</v>
       </c>
       <c r="AB9" t="n">
-        <v>102.7984553148824</v>
+        <v>103.7855303486826</v>
       </c>
     </row>
   </sheetData>
@@ -4886,85 +4886,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.023637633290857</v>
+        <v>2.468012033060575</v>
       </c>
       <c r="C2" t="n">
-        <v>2.078740578885059</v>
+        <v>2.727788715105641</v>
       </c>
       <c r="D2" t="n">
-        <v>2.000186933343397</v>
+        <v>2.449965102443522</v>
       </c>
       <c r="E2" t="n">
-        <v>2.155076456016952</v>
+        <v>2.619827979225541</v>
       </c>
       <c r="F2" t="n">
-        <v>2.0938372882449</v>
+        <v>2.540641095793224</v>
       </c>
       <c r="G2" t="n">
-        <v>2.043856812457818</v>
+        <v>2.487998365600217</v>
       </c>
       <c r="H2" t="n">
-        <v>2.023629768103107</v>
+        <v>2.471100502908711</v>
       </c>
       <c r="I2" t="n">
-        <v>2.083967434939108</v>
+        <v>2.532486017215209</v>
       </c>
       <c r="J2" t="n">
-        <v>2.045522789454865</v>
+        <v>2.493746652002202</v>
       </c>
       <c r="K2" t="n">
-        <v>2.089752056064469</v>
+        <v>2.540531406389088</v>
       </c>
       <c r="L2" t="n">
-        <v>2.206260368509503</v>
+        <v>2.641546948816828</v>
       </c>
       <c r="M2" t="n">
-        <v>2.047467818794765</v>
+        <v>2.496834065715524</v>
       </c>
       <c r="N2" t="n">
-        <v>2.03190903364249</v>
+        <v>2.487754795549558</v>
       </c>
       <c r="O2" t="n">
-        <v>3.894691530786908</v>
+        <v>4.97757216500754</v>
       </c>
       <c r="P2" t="n">
-        <v>2.016564599110338</v>
+        <v>2.466270651884423</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.0749200943479</v>
+        <v>2.525463128747114</v>
       </c>
       <c r="R2" t="n">
-        <v>2.092581568279925</v>
+        <v>2.541312075397371</v>
       </c>
       <c r="S2" t="n">
-        <v>2.115641605981499</v>
+        <v>2.569943724849044</v>
       </c>
       <c r="T2" t="n">
-        <v>2.025187361803572</v>
+        <v>2.471517568177217</v>
       </c>
       <c r="U2" t="n">
-        <v>2.157088765411674</v>
+        <v>3.123400692636082</v>
       </c>
       <c r="V2" t="n">
-        <v>2.024700456373131</v>
+        <v>2.47369821200787</v>
       </c>
       <c r="W2" t="n">
-        <v>2.262336122419425</v>
+        <v>3.329357451091784</v>
       </c>
       <c r="X2" t="n">
-        <v>2.077945424224405</v>
+        <v>2.525639864863219</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.013026786079044</v>
+        <v>2.460935268609961</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.969462557961938</v>
+        <v>2.641404139920456</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.008895290028258</v>
+        <v>2.453475256600053</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.016635663275832</v>
+        <v>2.467498178887845</v>
       </c>
     </row>
     <row r="3">
@@ -4974,85 +4974,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.227166993626182</v>
+        <v>2.623594484423121</v>
       </c>
       <c r="C3" t="n">
-        <v>2.396975158218021</v>
+        <v>3.142841165802742</v>
       </c>
       <c r="D3" t="n">
-        <v>2.061386450796745</v>
+        <v>2.49650814948996</v>
       </c>
       <c r="E3" t="n">
-        <v>3.166384692846691</v>
+        <v>3.708219115857563</v>
       </c>
       <c r="F3" t="n">
-        <v>2.731031681509192</v>
+        <v>3.144892282478271</v>
       </c>
       <c r="G3" t="n">
-        <v>2.369805084937761</v>
+        <v>2.764631051765924</v>
       </c>
       <c r="H3" t="n">
-        <v>2.229891484515225</v>
+        <v>2.648603253662948</v>
       </c>
       <c r="I3" t="n">
-        <v>2.66119377559758</v>
+        <v>3.087338257127953</v>
       </c>
       <c r="J3" t="n">
-        <v>2.382914540758394</v>
+        <v>2.806779977528669</v>
       </c>
       <c r="K3" t="n">
-        <v>2.698326759269483</v>
+        <v>3.140405295779853</v>
       </c>
       <c r="L3" t="n">
-        <v>3.521691920225567</v>
+        <v>3.853760935482633</v>
       </c>
       <c r="M3" t="n">
-        <v>2.401910427827322</v>
+        <v>2.836894778281755</v>
       </c>
       <c r="N3" t="n">
-        <v>2.287383545898132</v>
+        <v>2.765668321062993</v>
       </c>
       <c r="O3" t="n">
-        <v>5.194518460792963</v>
+        <v>6.667245021044055</v>
       </c>
       <c r="P3" t="n">
-        <v>2.177092101888191</v>
+        <v>2.611412998678098</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.59376397973791</v>
+        <v>3.034196348015481</v>
       </c>
       <c r="R3" t="n">
-        <v>2.723999457087086</v>
+        <v>3.151710339837245</v>
       </c>
       <c r="S3" t="n">
-        <v>2.876453103861131</v>
+        <v>3.343081411983578</v>
       </c>
       <c r="T3" t="n">
-        <v>2.239720801676256</v>
+        <v>2.65017592001165</v>
       </c>
       <c r="U3" t="n">
-        <v>2.456211018698363</v>
+        <v>3.666123325338882</v>
       </c>
       <c r="V3" t="n">
-        <v>2.234587670847042</v>
+        <v>2.663834195261727</v>
       </c>
       <c r="W3" t="n">
-        <v>2.579787433050193</v>
+        <v>4.076003205672846</v>
       </c>
       <c r="X3" t="n">
-        <v>2.616996012299205</v>
+        <v>3.037189898265195</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.152699344455673</v>
+        <v>2.574367002978229</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.183571681958315</v>
+        <v>2.990892276028218</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.123261773102512</v>
+        <v>2.521175613693546</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.184048780792468</v>
+        <v>2.628812925621478</v>
       </c>
     </row>
     <row r="4">
@@ -5062,85 +5062,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.789228844427275</v>
+        <v>2.193855478981984</v>
       </c>
       <c r="C4" t="n">
-        <v>1.951357746009844</v>
+        <v>2.379989488802262</v>
       </c>
       <c r="D4" t="n">
-        <v>1.524342400665809</v>
+        <v>1.99000709566401</v>
       </c>
       <c r="E4" t="n">
-        <v>3.27389081196427</v>
+        <v>3.908686429700819</v>
       </c>
       <c r="F4" t="n">
-        <v>2.582166240569995</v>
+        <v>3.014234153566613</v>
       </c>
       <c r="G4" t="n">
-        <v>2.017613774400087</v>
+        <v>2.419610299184216</v>
       </c>
       <c r="H4" t="n">
-        <v>1.789140003513548</v>
+        <v>2.228741166682928</v>
       </c>
       <c r="I4" t="n">
-        <v>2.470681707124285</v>
+        <v>2.922118789506488</v>
       </c>
       <c r="J4" t="n">
-        <v>2.035708613982208</v>
+        <v>2.483616679498459</v>
       </c>
       <c r="K4" t="n">
-        <v>2.536021663792415</v>
+        <v>3.01299516128735</v>
       </c>
       <c r="L4" t="n">
-        <v>3.852036649330689</v>
+        <v>4.15401218245402</v>
       </c>
       <c r="M4" t="n">
-        <v>2.065684584666355</v>
+        <v>2.532055659299039</v>
       </c>
       <c r="N4" t="n">
-        <v>1.882658116431175</v>
+        <v>14.837759495947</v>
       </c>
       <c r="O4" t="n">
-        <v>1.538308512013897</v>
+        <v>1.989271578587187</v>
       </c>
       <c r="P4" t="n">
-        <v>1.709335669601894</v>
+        <v>2.174185777522416</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.368487833164218</v>
+        <v>2.842792033571169</v>
       </c>
       <c r="R4" t="n">
-        <v>2.567982305905871</v>
+        <v>3.021813176861394</v>
       </c>
       <c r="S4" t="n">
-        <v>2.828456039886586</v>
+        <v>3.345220828627526</v>
       </c>
       <c r="T4" t="n">
-        <v>1.806733740888768</v>
+        <v>2.233452110750086</v>
       </c>
       <c r="U4" t="n">
-        <v>1.739679502968094</v>
+        <v>2.028604890788954</v>
       </c>
       <c r="V4" t="n">
-        <v>1.79668406654096</v>
+        <v>2.252506526057085</v>
       </c>
       <c r="W4" t="n">
-        <v>1.701301216332822</v>
+        <v>2.254082631950247</v>
       </c>
       <c r="X4" t="n">
-        <v>2.402660325839737</v>
+        <v>2.84478834930521</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.602906816343128</v>
+        <v>2.031122908414112</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.884932019730812</v>
+        <v>2.362712945357151</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.622707295463304</v>
+        <v>2.029655901612786</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.718639730485967</v>
+        <v>2.199854423362734</v>
       </c>
     </row>
     <row r="5">
@@ -5150,85 +5150,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9.535729965016312</v>
+        <v>9.971222434938991</v>
       </c>
       <c r="C5" t="n">
-        <v>13.46748997099376</v>
+        <v>14.38981424628213</v>
       </c>
       <c r="D5" t="n">
-        <v>5.410603296369655</v>
+        <v>7.070960615451734</v>
       </c>
       <c r="E5" t="n">
-        <v>38.23729059371342</v>
+        <v>43.01055115187621</v>
       </c>
       <c r="F5" t="n">
-        <v>26.11146337045822</v>
+        <v>27.11826126545104</v>
       </c>
       <c r="G5" t="n">
-        <v>12.92679428478617</v>
+        <v>13.34610066741707</v>
       </c>
       <c r="H5" t="n">
-        <v>11.08050109475878</v>
+        <v>12.28049981470961</v>
       </c>
       <c r="I5" t="n">
-        <v>24.33928979172565</v>
+        <v>25.73759401277868</v>
       </c>
       <c r="J5" t="n">
-        <v>13.95999327853717</v>
+        <v>15.19748427978871</v>
       </c>
       <c r="K5" t="n">
-        <v>23.26550628623571</v>
+        <v>25.03477541581857</v>
       </c>
       <c r="L5" t="n">
-        <v>43.61012645452817</v>
+        <v>42.38374831756386</v>
       </c>
       <c r="M5" t="n">
-        <v>15.15740936788243</v>
+        <v>16.77038196867709</v>
       </c>
       <c r="N5" t="n">
-        <v>10.25123486928962</v>
+        <v>14.837759495947</v>
       </c>
       <c r="O5" t="n">
-        <v>5.186262816344492</v>
+        <v>6.398534185404317</v>
       </c>
       <c r="P5" t="n">
-        <v>8.250751646098234</v>
+        <v>9.736589397038301</v>
       </c>
       <c r="Q5" t="n">
-        <v>20.81727045565924</v>
+        <v>22.55855417740191</v>
       </c>
       <c r="R5" t="n">
-        <v>26.9165995526182</v>
+        <v>28.39013248581418</v>
       </c>
       <c r="S5" t="n">
-        <v>25.09715819407012</v>
+        <v>27.28933094307287</v>
       </c>
       <c r="T5" t="n">
-        <v>10.69722326529354</v>
+        <v>11.58876435060932</v>
       </c>
       <c r="U5" t="n">
-        <v>10.17472388342243</v>
+        <v>8.845975399369561</v>
       </c>
       <c r="V5" t="n">
-        <v>9.666548143385373</v>
+        <v>10.98939585068664</v>
       </c>
       <c r="W5" t="n">
-        <v>8.603204563608747</v>
+        <v>11.85925730441417</v>
       </c>
       <c r="X5" t="n">
-        <v>22.37554733471603</v>
+        <v>23.55965378434567</v>
       </c>
       <c r="Y5" t="n">
-        <v>7.971674594725641</v>
+        <v>9.171543082142641</v>
       </c>
       <c r="Z5" t="n">
-        <v>10.98164435118563</v>
+        <v>12.64445335571956</v>
       </c>
       <c r="AA5" t="n">
-        <v>7.116615876649937</v>
+        <v>7.60669524796017</v>
       </c>
       <c r="AB5" t="n">
-        <v>9.444726410790546</v>
+        <v>11.45998585602297</v>
       </c>
     </row>
     <row r="6">
@@ -5238,85 +5238,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.128331103131431</v>
+        <v>2.73844021645594</v>
       </c>
       <c r="C6" t="n">
-        <v>4.239983641405684</v>
+        <v>2.924574226276345</v>
       </c>
       <c r="D6" t="n">
-        <v>1.863444659369965</v>
+        <v>4.845992456411701</v>
       </c>
       <c r="E6" t="n">
-        <v>3.612993070668422</v>
+        <v>6.764671790448554</v>
       </c>
       <c r="F6" t="n">
-        <v>4.870792135965837</v>
+        <v>3.55881889104064</v>
       </c>
       <c r="G6" t="n">
-        <v>4.306239669795929</v>
+        <v>2.964195036658362</v>
       </c>
       <c r="H6" t="n">
-        <v>2.128242262217704</v>
+        <v>5.084726527430538</v>
       </c>
       <c r="I6" t="n">
-        <v>2.809783965828443</v>
+        <v>5.778104150254236</v>
       </c>
       <c r="J6" t="n">
-        <v>2.374810872686364</v>
+        <v>3.02820141697227</v>
       </c>
       <c r="K6" t="n">
-        <v>2.875123922496571</v>
+        <v>5.868980522035093</v>
       </c>
       <c r="L6" t="n">
-        <v>4.191138908034845</v>
+        <v>4.698596919928148</v>
       </c>
       <c r="M6" t="n">
-        <v>4.354310480062195</v>
+        <v>5.388041020046656</v>
       </c>
       <c r="N6" t="n">
-        <v>2.213373426755095</v>
+        <v>14.837759495947</v>
       </c>
       <c r="O6" t="n">
-        <v>3.861661903639385</v>
+        <v>4.908489188270447</v>
       </c>
       <c r="P6" t="n">
-        <v>2.016760977927615</v>
+        <v>5.097305827929778</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.657113728560057</v>
+        <v>5.698777394318721</v>
       </c>
       <c r="R6" t="n">
-        <v>2.907084564610031</v>
+        <v>5.877798537609091</v>
       </c>
       <c r="S6" t="n">
-        <v>3.167558298590742</v>
+        <v>3.889805566101516</v>
       </c>
       <c r="T6" t="n">
-        <v>4.095359636284612</v>
+        <v>2.778036848224219</v>
       </c>
       <c r="U6" t="n">
-        <v>2.145249389268137</v>
+        <v>2.655986888888465</v>
       </c>
       <c r="V6" t="n">
-        <v>4.085309961936804</v>
+        <v>5.108491886804749</v>
       </c>
       <c r="W6" t="n">
-        <v>2.051847938899399</v>
+        <v>5.171161108232221</v>
       </c>
       <c r="X6" t="n">
-        <v>2.741762584543892</v>
+        <v>3.389373086779166</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.018287004383613</v>
+        <v>2.674659548331483</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.17355791512665</v>
+        <v>2.9072976828312</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.911333190859137</v>
+        <v>4.885641262360418</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.048691257505571</v>
+        <v>2.722909803491794</v>
       </c>
     </row>
     <row r="7">
@@ -5326,85 +5326,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.468404273715793</v>
+        <v>3.027411770222843</v>
       </c>
       <c r="C7" t="n">
-        <v>2.630533175298361</v>
+        <v>3.213545780043279</v>
       </c>
       <c r="D7" t="n">
-        <v>2.203517829954333</v>
+        <v>2.823563386904996</v>
       </c>
       <c r="E7" t="n">
-        <v>3.953066241252784</v>
+        <v>4.742242720941833</v>
       </c>
       <c r="F7" t="n">
-        <v>3.261341669858513</v>
+        <v>3.847790444807713</v>
       </c>
       <c r="G7" t="n">
-        <v>2.696789203688609</v>
+        <v>3.253166590425328</v>
       </c>
       <c r="H7" t="n">
-        <v>2.468315432802066</v>
+        <v>3.062297457923943</v>
       </c>
       <c r="I7" t="n">
-        <v>3.149857136412809</v>
+        <v>3.755675080747504</v>
       </c>
       <c r="J7" t="n">
-        <v>2.714884043270725</v>
+        <v>3.31717297073944</v>
       </c>
       <c r="K7" t="n">
-        <v>3.215197093080932</v>
+        <v>3.846551452528329</v>
       </c>
       <c r="L7" t="n">
-        <v>4.531212078619208</v>
+        <v>4.98756847369505</v>
       </c>
       <c r="M7" t="n">
-        <v>2.744860013954872</v>
+        <v>3.365611950540037</v>
       </c>
       <c r="N7" t="n">
-        <v>2.561833545719693</v>
+        <v>14.837759495947</v>
       </c>
       <c r="O7" t="n">
-        <v>2.217445683956661</v>
+        <v>2.822816705118538</v>
       </c>
       <c r="P7" t="n">
-        <v>2.388472841544666</v>
+        <v>3.00773090405374</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.047663262452737</v>
+        <v>3.67634832481206</v>
       </c>
       <c r="R7" t="n">
-        <v>3.247157735194393</v>
+        <v>3.855369468102344</v>
       </c>
       <c r="S7" t="n">
-        <v>3.507631469175099</v>
+        <v>4.178777119868503</v>
       </c>
       <c r="T7" t="n">
-        <v>2.485909170177288</v>
+        <v>3.067008401991244</v>
       </c>
       <c r="U7" t="n">
-        <v>2.524943828105825</v>
+        <v>2.942151572537236</v>
       </c>
       <c r="V7" t="n">
-        <v>2.475859495829478</v>
+        <v>3.086062817298182</v>
       </c>
       <c r="W7" t="n">
-        <v>2.380476645621343</v>
+        <v>3.087638923191141</v>
       </c>
       <c r="X7" t="n">
-        <v>3.081835755128251</v>
+        <v>3.678344640546102</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.348549873227536</v>
+        <v>2.947476460280677</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.564107449019335</v>
+        <v>3.196269236598134</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.301882724751815</v>
+        <v>2.863212192853721</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.397815159774485</v>
+        <v>3.033410714603656</v>
       </c>
     </row>
     <row r="8">
@@ -5414,85 +5414,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.130928457457922</v>
+        <v>4.967407485716032</v>
       </c>
       <c r="C8" t="n">
-        <v>5.845219562551939</v>
+        <v>7.161287166008734</v>
       </c>
       <c r="D8" t="n">
-        <v>5.418204217207865</v>
+        <v>6.771304772870453</v>
       </c>
       <c r="E8" t="n">
-        <v>6.341272041137922</v>
+        <v>7.620918763271196</v>
       </c>
       <c r="F8" t="n">
-        <v>5.165674584343993</v>
+        <v>6.100569470214076</v>
       </c>
       <c r="G8" t="n">
-        <v>6.233326535288002</v>
+        <v>7.61722712014925</v>
       </c>
       <c r="H8" t="n">
-        <v>5.68300182005561</v>
+        <v>7.010038843889305</v>
       </c>
       <c r="I8" t="n">
-        <v>6.364543523666368</v>
+        <v>7.703416466712948</v>
       </c>
       <c r="J8" t="n">
-        <v>5.929570430524285</v>
+        <v>7.264914356704732</v>
       </c>
       <c r="K8" t="n">
-        <v>6.429883480334476</v>
+        <v>7.794292838493791</v>
       </c>
       <c r="L8" t="n">
-        <v>7.745898465872783</v>
+        <v>8.935309859660537</v>
       </c>
       <c r="M8" t="n">
-        <v>5.959546401214111</v>
+        <v>7.313353336489266</v>
       </c>
       <c r="N8" t="n">
-        <v>4.573334554094695</v>
+        <v>14.837759495947</v>
       </c>
       <c r="O8" t="n">
-        <v>4.559630738699373</v>
+        <v>5.641925880388073</v>
       </c>
       <c r="P8" t="n">
-        <v>4.649608623894537</v>
+        <v>5.72200160030763</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.405152146896935</v>
+        <v>5.221776192860321</v>
       </c>
       <c r="R8" t="n">
-        <v>6.461844122447959</v>
+        <v>7.803110854067795</v>
       </c>
       <c r="S8" t="n">
-        <v>6.722317856428644</v>
+        <v>8.126518505833952</v>
       </c>
       <c r="T8" t="n">
-        <v>5.700595557430843</v>
+        <v>7.014749787956603</v>
       </c>
       <c r="U8" t="n">
-        <v>4.973154450610081</v>
+        <v>5.910579358061204</v>
       </c>
       <c r="V8" t="n">
-        <v>5.300216529531711</v>
+        <v>6.482667335833413</v>
       </c>
       <c r="W8" t="n">
-        <v>5.595468076887132</v>
+        <v>7.03577488394007</v>
       </c>
       <c r="X8" t="n">
-        <v>4.581583389520024</v>
+        <v>5.407786385810758</v>
       </c>
       <c r="Y8" t="n">
-        <v>7.159094724264126</v>
+        <v>8.887767238234252</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.197799422952682</v>
+        <v>5.098970045945756</v>
       </c>
       <c r="AA8" t="n">
-        <v>5.516569112005365</v>
+        <v>6.810953578819131</v>
       </c>
       <c r="AB8" t="n">
-        <v>7.233864758027618</v>
+        <v>9.078410333779416</v>
       </c>
     </row>
     <row r="9">
@@ -5502,85 +5502,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>86.13763555256163</v>
+        <v>86.81732714828389</v>
       </c>
       <c r="C9" t="n">
-        <v>109.6547193952428</v>
+        <v>110.5133497795431</v>
       </c>
       <c r="D9" t="n">
-        <v>109.2277040498987</v>
+        <v>110.123367386405</v>
       </c>
       <c r="E9" t="n">
-        <v>105.5870243945015</v>
+        <v>106.6160608102509</v>
       </c>
       <c r="F9" t="n">
-        <v>56.44598211946212</v>
+        <v>56.95088388550231</v>
       </c>
       <c r="G9" t="n">
-        <v>109.7209757754055</v>
+        <v>110.5529712250615</v>
       </c>
       <c r="H9" t="n">
-        <v>109.4925016527466</v>
+        <v>110.3621014574238</v>
       </c>
       <c r="I9" t="n">
-        <v>110.1740433563571</v>
+        <v>111.0554790802476</v>
       </c>
       <c r="J9" t="n">
-        <v>109.7390702632149</v>
+        <v>110.6169769702394</v>
       </c>
       <c r="K9" t="n">
-        <v>110.2393833130251</v>
+        <v>111.1463554520281</v>
       </c>
       <c r="L9" t="n">
-        <v>111.5553982985635</v>
+        <v>112.287372473195</v>
       </c>
       <c r="M9" t="n">
-        <v>109.7690462338994</v>
+        <v>110.66541595004</v>
       </c>
       <c r="N9" t="n">
-        <v>109.5860197656639</v>
+        <v>14.837759495947</v>
       </c>
       <c r="O9" t="n">
-        <v>116.9814721163643</v>
+        <v>117.9137790205117</v>
       </c>
       <c r="P9" t="n">
-        <v>118.835773330052</v>
+        <v>119.7931339131292</v>
       </c>
       <c r="Q9" t="n">
-        <v>110.0718498341696</v>
+        <v>110.9761529594479</v>
       </c>
       <c r="R9" t="n">
-        <v>110.2713439551388</v>
+        <v>111.1551734676021</v>
       </c>
       <c r="S9" t="n">
-        <v>110.5318176891193</v>
+        <v>111.4785811193686</v>
       </c>
       <c r="T9" t="n">
-        <v>109.5100953901217</v>
+        <v>110.3668124014912</v>
       </c>
       <c r="U9" t="n">
-        <v>109.509508779797</v>
+        <v>110.2447624421554</v>
       </c>
       <c r="V9" t="n">
-        <v>136.4511686150771</v>
+        <v>137.5157801946275</v>
       </c>
       <c r="W9" t="n">
-        <v>109.4046628655657</v>
+        <v>110.3874429226909</v>
       </c>
       <c r="X9" t="n">
-        <v>110.1060219750727</v>
+        <v>110.9781486400457</v>
       </c>
       <c r="Y9" t="n">
-        <v>109.3727360931718</v>
+        <v>110.2472804597806</v>
       </c>
       <c r="Z9" t="n">
-        <v>95.50733278278888</v>
+        <v>96.32170123043905</v>
       </c>
       <c r="AA9" t="n">
-        <v>109.3260689446963</v>
+        <v>110.1630161923537</v>
       </c>
       <c r="AB9" t="n">
-        <v>109.4220013797189</v>
+        <v>110.3332147141033</v>
       </c>
     </row>
   </sheetData>
@@ -5746,85 +5746,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.39004631599522</v>
+        <v>3.032053663854787</v>
       </c>
       <c r="C2" t="n">
-        <v>2.352679256034604</v>
+        <v>3.230147467090333</v>
       </c>
       <c r="D2" t="n">
-        <v>2.19037689387399</v>
+        <v>2.831832061046188</v>
       </c>
       <c r="E2" t="n">
-        <v>2.511765641946954</v>
+        <v>3.210938212272282</v>
       </c>
       <c r="F2" t="n">
-        <v>2.42200511948259</v>
+        <v>3.068833602710846</v>
       </c>
       <c r="G2" t="n">
-        <v>2.216699417292742</v>
+        <v>2.860855207287281</v>
       </c>
       <c r="H2" t="n">
-        <v>2.222563170711298</v>
+        <v>2.869460709605487</v>
       </c>
       <c r="I2" t="n">
-        <v>2.350627214003437</v>
+        <v>2.995834342311721</v>
       </c>
       <c r="J2" t="n">
-        <v>2.267567398012003</v>
+        <v>2.915214904270052</v>
       </c>
       <c r="K2" t="n">
-        <v>2.274033713921665</v>
+        <v>2.916828394301786</v>
       </c>
       <c r="L2" t="n">
-        <v>2.350533580511029</v>
+        <v>2.997122340267324</v>
       </c>
       <c r="M2" t="n">
-        <v>2.213621113897547</v>
+        <v>2.855942416981295</v>
       </c>
       <c r="N2" t="n">
-        <v>2.292627252953007</v>
+        <v>2.939978342837283</v>
       </c>
       <c r="O2" t="n">
-        <v>4.386452093117184</v>
+        <v>5.7805712816699</v>
       </c>
       <c r="P2" t="n">
-        <v>2.202189766539829</v>
+        <v>2.854575872635603</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.289242477521528</v>
+        <v>2.929802497627136</v>
       </c>
       <c r="R2" t="n">
-        <v>2.431973982456122</v>
+        <v>3.087931873729723</v>
       </c>
       <c r="S2" t="n">
-        <v>2.306783059947794</v>
+        <v>2.958272348504189</v>
       </c>
       <c r="T2" t="n">
-        <v>2.240208200009443</v>
+        <v>2.888675618010112</v>
       </c>
       <c r="U2" t="n">
-        <v>2.531725297679419</v>
+        <v>3.883195011566139</v>
       </c>
       <c r="V2" t="n">
-        <v>2.248619088149751</v>
+        <v>2.895274731583911</v>
       </c>
       <c r="W2" t="n">
-        <v>2.731177590300824</v>
+        <v>4.193108661498727</v>
       </c>
       <c r="X2" t="n">
-        <v>2.271663879546767</v>
+        <v>2.917861077988707</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.216810216528315</v>
+        <v>2.862968468789653</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.443315977753454</v>
+        <v>3.458539673838075</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.201028333982753</v>
+        <v>2.847015085160677</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.214283593368799</v>
+        <v>2.855687367121358</v>
       </c>
     </row>
     <row r="3">
@@ -5834,85 +5834,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.617404681465723</v>
+        <v>4.206284287266378</v>
       </c>
       <c r="C3" t="n">
-        <v>2.981736751613494</v>
+        <v>3.963974491255271</v>
       </c>
       <c r="D3" t="n">
-        <v>2.198772782337652</v>
+        <v>2.783895188149871</v>
       </c>
       <c r="E3" t="n">
-        <v>4.490983731414305</v>
+        <v>5.487688501021072</v>
       </c>
       <c r="F3" t="n">
-        <v>3.852472178492922</v>
+        <v>4.475982880420335</v>
       </c>
       <c r="G3" t="n">
-        <v>2.384235446019545</v>
+        <v>2.988239121534499</v>
       </c>
       <c r="H3" t="n">
-        <v>2.429852161192841</v>
+        <v>3.05411829532338</v>
       </c>
       <c r="I3" t="n">
-        <v>3.344004821018558</v>
+        <v>3.95598934565355</v>
       </c>
       <c r="J3" t="n">
-        <v>2.746694082923465</v>
+        <v>3.375670120903186</v>
       </c>
       <c r="K3" t="n">
-        <v>2.792954648351936</v>
+        <v>3.387542366376876</v>
       </c>
       <c r="L3" t="n">
-        <v>3.328205271424115</v>
+        <v>3.949349162779686</v>
       </c>
       <c r="M3" t="n">
-        <v>2.377766702950877</v>
+        <v>2.973656390286579</v>
       </c>
       <c r="N3" t="n">
-        <v>2.927102554167259</v>
+        <v>3.55416972235126</v>
       </c>
       <c r="O3" t="n">
-        <v>6.378654709746895</v>
+        <v>8.2394604644693</v>
       </c>
       <c r="P3" t="n">
-        <v>2.282044211774978</v>
+        <v>2.944632392935393</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.899782969382622</v>
+        <v>3.478405893014124</v>
       </c>
       <c r="R3" t="n">
-        <v>3.927754105699095</v>
+        <v>4.616738338748286</v>
       </c>
       <c r="S3" t="n">
-        <v>3.021252686065815</v>
+        <v>3.677092021518443</v>
       </c>
       <c r="T3" t="n">
-        <v>2.553853439718454</v>
+        <v>3.188944103464725</v>
       </c>
       <c r="U3" t="n">
-        <v>2.836182209134479</v>
+        <v>4.591716333117468</v>
       </c>
       <c r="V3" t="n">
-        <v>2.610887378310262</v>
+        <v>3.232662303648772</v>
       </c>
       <c r="W3" t="n">
-        <v>3.498618996605292</v>
+        <v>5.494376954591847</v>
       </c>
       <c r="X3" t="n">
-        <v>2.777633161681172</v>
+        <v>3.396489326526507</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.387312135943534</v>
+        <v>3.005978405643623</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.339532743917625</v>
+        <v>4.60175569357239</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.274618294886765</v>
+        <v>2.892048439966317</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.382522863765568</v>
+        <v>2.97112928249991</v>
       </c>
     </row>
     <row r="4">
@@ -5922,85 +5922,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.986781619807035</v>
+        <v>4.544969496345785</v>
       </c>
       <c r="C4" t="n">
-        <v>2.796156375954371</v>
+        <v>3.363816649710006</v>
       </c>
       <c r="D4" t="n">
-        <v>1.731423644475433</v>
+        <v>2.283374386134946</v>
       </c>
       <c r="E4" t="n">
-        <v>5.361657400087832</v>
+        <v>6.565552761679298</v>
       </c>
       <c r="F4" t="n">
-        <v>4.347771006972737</v>
+        <v>4.960415825332774</v>
       </c>
       <c r="G4" t="n">
-        <v>2.028748655449071</v>
+        <v>2.611204174234973</v>
       </c>
       <c r="H4" t="n">
-        <v>2.094982447771737</v>
+        <v>2.708407281645747</v>
       </c>
       <c r="I4" t="n">
-        <v>3.541524729126814</v>
+        <v>4.135855597805871</v>
       </c>
       <c r="J4" t="n">
-        <v>2.60254962404286</v>
+        <v>3.22410879612052</v>
       </c>
       <c r="K4" t="n">
-        <v>2.676365910952306</v>
+        <v>3.243447070501966</v>
       </c>
       <c r="L4" t="n">
-        <v>3.540467095756796</v>
+        <v>4.150404127222747</v>
       </c>
       <c r="M4" t="n">
-        <v>2.020103738220203</v>
+        <v>2.590456693117607</v>
       </c>
       <c r="N4" t="n">
-        <v>2.886388487762063</v>
+        <v>27.12432858592459</v>
       </c>
       <c r="O4" t="n">
-        <v>2.885356674560737</v>
+        <v>3.506851096390652</v>
       </c>
       <c r="P4" t="n">
-        <v>1.864855475425989</v>
+        <v>2.540276200707505</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.848155892189884</v>
+        <v>3.389995535944078</v>
       </c>
       <c r="R4" t="n">
-        <v>4.460373900161997</v>
+        <v>5.176139582129838</v>
       </c>
       <c r="S4" t="n">
-        <v>3.046284839760809</v>
+        <v>3.711575598378851</v>
       </c>
       <c r="T4" t="n">
-        <v>2.294291170808521</v>
+        <v>2.925448511370592</v>
       </c>
       <c r="U4" t="n">
-        <v>1.831872758114942</v>
+        <v>2.301570024299467</v>
       </c>
       <c r="V4" t="n">
-        <v>2.384453570887866</v>
+        <v>2.993337269437866</v>
       </c>
       <c r="W4" t="n">
-        <v>2.573677604678926</v>
+        <v>3.242160478767404</v>
       </c>
       <c r="X4" t="n">
-        <v>2.649597541510302</v>
+        <v>3.255111707803633</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.975259423481421</v>
+        <v>2.501011969150265</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.235314096114146</v>
+        <v>3.912619075942746</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.851736560408189</v>
+        <v>2.454873628044294</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.025021102503876</v>
+        <v>2.583360926368699</v>
       </c>
     </row>
     <row r="5">
@@ -6010,85 +6010,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>41.68999509505814</v>
+        <v>42.91153549279137</v>
       </c>
       <c r="C5" t="n">
-        <v>23.39428422748275</v>
+        <v>24.86531174285755</v>
       </c>
       <c r="D5" t="n">
-        <v>5.126607010430621</v>
+        <v>6.3330525604473</v>
       </c>
       <c r="E5" t="n">
-        <v>68.52662950285261</v>
+        <v>81.082609823824</v>
       </c>
       <c r="F5" t="n">
-        <v>51.68978370704312</v>
+        <v>53.98974470963311</v>
       </c>
       <c r="G5" t="n">
-        <v>9.140256605469872</v>
+        <v>10.68245834417837</v>
       </c>
       <c r="H5" t="n">
-        <v>12.26376685452101</v>
+        <v>14.71359836316736</v>
       </c>
       <c r="I5" t="n">
-        <v>37.92764538261454</v>
+        <v>39.92728023492237</v>
       </c>
       <c r="J5" t="n">
-        <v>18.99675986109781</v>
+        <v>21.26304469108349</v>
       </c>
       <c r="K5" t="n">
-        <v>20.34644988237149</v>
+        <v>21.77134287618586</v>
       </c>
       <c r="L5" t="n">
-        <v>30.06753529209517</v>
+        <v>31.97970509031294</v>
       </c>
       <c r="M5" t="n">
-        <v>9.664426406946628</v>
+        <v>11.14600215505916</v>
       </c>
       <c r="N5" t="n">
-        <v>8.149086027931801</v>
+        <v>27.12432858592459</v>
       </c>
       <c r="O5" t="n">
-        <v>22.62130488320372</v>
+        <v>24.79616063589708</v>
       </c>
       <c r="P5" t="n">
-        <v>6.948842780931477</v>
+        <v>10.05461522028183</v>
       </c>
       <c r="Q5" t="n">
-        <v>22.49484894093474</v>
+        <v>23.46505776786229</v>
       </c>
       <c r="R5" t="n">
-        <v>55.82351381551914</v>
+        <v>60.11135078813276</v>
       </c>
       <c r="S5" t="n">
-        <v>24.07217433456565</v>
+        <v>26.81832839512394</v>
       </c>
       <c r="T5" t="n">
-        <v>14.78756962872168</v>
+        <v>17.35422057248883</v>
       </c>
       <c r="U5" t="n">
-        <v>7.14931105858851</v>
+        <v>8.21972692618729</v>
       </c>
       <c r="V5" t="n">
-        <v>14.91096734584546</v>
+        <v>16.91433200394376</v>
       </c>
       <c r="W5" t="n">
-        <v>19.01833941336083</v>
+        <v>22.12444257817218</v>
       </c>
       <c r="X5" t="n">
-        <v>20.698093027201</v>
+        <v>22.79470768327029</v>
       </c>
       <c r="Y5" t="n">
-        <v>10.34700705550328</v>
+        <v>12.48147890085066</v>
       </c>
       <c r="Z5" t="n">
-        <v>27.98202482412737</v>
+        <v>31.01213667314778</v>
       </c>
       <c r="AA5" t="n">
-        <v>7.164188800771051</v>
+        <v>9.258121185129992</v>
       </c>
       <c r="AB5" t="n">
-        <v>10.48830259236125</v>
+        <v>11.84096257599798</v>
       </c>
     </row>
     <row r="6">
@@ -6098,85 +6098,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.393277165234707</v>
+        <v>7.659941974734918</v>
       </c>
       <c r="C6" t="n">
-        <v>3.202651921382204</v>
+        <v>4.136154386922028</v>
       </c>
       <c r="D6" t="n">
-        <v>2.137919189902992</v>
+        <v>3.055712123346928</v>
       </c>
       <c r="E6" t="n">
-        <v>7.661721701617378</v>
+        <v>7.337890498891473</v>
       </c>
       <c r="F6" t="n">
-        <v>6.647835308502015</v>
+        <v>8.075388303721876</v>
       </c>
       <c r="G6" t="n">
-        <v>2.435244200876814</v>
+        <v>5.726176652623917</v>
       </c>
       <c r="H6" t="n">
-        <v>2.501477993199536</v>
+        <v>5.823379760034722</v>
       </c>
       <c r="I6" t="n">
-        <v>3.948020274554395</v>
+        <v>7.250828076194818</v>
       </c>
       <c r="J6" t="n">
-        <v>3.009045169470686</v>
+        <v>6.339081274509484</v>
       </c>
       <c r="K6" t="n">
-        <v>3.082861456380096</v>
+        <v>6.35841954889094</v>
       </c>
       <c r="L6" t="n">
-        <v>5.840531397285968</v>
+        <v>4.922741864434733</v>
       </c>
       <c r="M6" t="n">
-        <v>4.320168039749747</v>
+        <v>5.705429171506675</v>
       </c>
       <c r="N6" t="n">
-        <v>3.27712660392595</v>
+        <v>27.12432858592459</v>
       </c>
       <c r="O6" t="n">
-        <v>3.276094790724741</v>
+        <v>6.727572883443766</v>
       </c>
       <c r="P6" t="n">
-        <v>2.225627852044993</v>
+        <v>3.22179201059351</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.254651437617527</v>
+        <v>6.504968014333183</v>
       </c>
       <c r="R6" t="n">
-        <v>6.760438201691529</v>
+        <v>5.948477319341792</v>
       </c>
       <c r="S6" t="n">
-        <v>3.452780385188729</v>
+        <v>6.826548076768017</v>
       </c>
       <c r="T6" t="n">
-        <v>4.594355472338067</v>
+        <v>3.697786248582644</v>
       </c>
       <c r="U6" t="n">
-        <v>2.293109063846417</v>
+        <v>3.207970227413738</v>
       </c>
       <c r="V6" t="n">
-        <v>4.684517872417342</v>
+        <v>3.765675006649986</v>
       </c>
       <c r="W6" t="n">
-        <v>2.991465701324377</v>
+        <v>4.041529941787124</v>
       </c>
       <c r="X6" t="n">
-        <v>3.056093086937943</v>
+        <v>6.370084186192678</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.444508793617876</v>
+        <v>3.422747880558282</v>
       </c>
       <c r="Z6" t="n">
-        <v>5.535378397643691</v>
+        <v>4.684956813154922</v>
       </c>
       <c r="AA6" t="n">
-        <v>4.151800861937729</v>
+        <v>5.569846106433268</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.413329968780732</v>
+        <v>3.315907661825044</v>
       </c>
     </row>
     <row r="7">
@@ -6186,85 +6186,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.67739987415669</v>
+        <v>5.402427007544466</v>
       </c>
       <c r="C7" t="n">
-        <v>3.486774630304306</v>
+        <v>4.221274160908559</v>
       </c>
       <c r="D7" t="n">
-        <v>2.422041898825216</v>
+        <v>3.140831897333467</v>
       </c>
       <c r="E7" t="n">
-        <v>6.052275654437728</v>
+        <v>7.423010272878017</v>
       </c>
       <c r="F7" t="n">
-        <v>5.038389261322364</v>
+        <v>5.817873336531484</v>
       </c>
       <c r="G7" t="n">
-        <v>2.719366909798798</v>
+        <v>3.468661685433494</v>
       </c>
       <c r="H7" t="n">
-        <v>2.785600702121477</v>
+        <v>3.565864792844299</v>
       </c>
       <c r="I7" t="n">
-        <v>4.232142983476384</v>
+        <v>4.993313109004391</v>
       </c>
       <c r="J7" t="n">
-        <v>3.293167878392634</v>
+        <v>4.081566307319076</v>
       </c>
       <c r="K7" t="n">
-        <v>3.36698416530212</v>
+        <v>4.100904581700515</v>
       </c>
       <c r="L7" t="n">
-        <v>4.231085350106605</v>
+        <v>5.007861638421298</v>
       </c>
       <c r="M7" t="n">
-        <v>2.710721992570105</v>
+        <v>3.447914204316349</v>
       </c>
       <c r="N7" t="n">
-        <v>3.577006742111691</v>
+        <v>27.12432858592459</v>
       </c>
       <c r="O7" t="n">
-        <v>3.575936545294501</v>
+        <v>4.364312445657445</v>
       </c>
       <c r="P7" t="n">
-        <v>2.555435346159747</v>
+        <v>3.397737549974329</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.538774146539512</v>
+        <v>4.247453047142753</v>
       </c>
       <c r="R7" t="n">
-        <v>5.150992154511894</v>
+        <v>6.033597093328358</v>
       </c>
       <c r="S7" t="n">
-        <v>3.736903094110711</v>
+        <v>4.569033109577533</v>
       </c>
       <c r="T7" t="n">
-        <v>2.984909425158417</v>
+        <v>3.782906022569118</v>
       </c>
       <c r="U7" t="n">
-        <v>2.632584824845378</v>
+        <v>3.273824329430913</v>
       </c>
       <c r="V7" t="n">
-        <v>3.075071825237652</v>
+        <v>3.850794780636517</v>
       </c>
       <c r="W7" t="n">
-        <v>3.264295859028746</v>
+        <v>4.09961798996602</v>
       </c>
       <c r="X7" t="n">
-        <v>3.340215795859931</v>
+        <v>4.112569219002285</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.720618438135034</v>
+        <v>3.492531946251103</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.925932350464045</v>
+        <v>4.770076587141367</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.542354814758093</v>
+        <v>3.312331139242818</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.715639356853705</v>
+        <v>3.440818437567319</v>
       </c>
     </row>
     <row r="8">
@@ -6274,85 +6274,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6.289967418251214</v>
+        <v>7.360823246355128</v>
       </c>
       <c r="C8" t="n">
-        <v>6.663441563289819</v>
+        <v>8.31645765154631</v>
       </c>
       <c r="D8" t="n">
-        <v>5.598708831810651</v>
+        <v>7.236015387971215</v>
       </c>
       <c r="E8" t="n">
-        <v>8.396105801153888</v>
+        <v>10.38041758483426</v>
       </c>
       <c r="F8" t="n">
-        <v>6.894625210031703</v>
+        <v>8.109156055189406</v>
       </c>
       <c r="G8" t="n">
-        <v>6.22036004019094</v>
+        <v>8.006921932102129</v>
       </c>
       <c r="H8" t="n">
-        <v>5.962267635107104</v>
+        <v>7.661048283482046</v>
       </c>
       <c r="I8" t="n">
-        <v>7.408809916462055</v>
+        <v>9.088496599642145</v>
       </c>
       <c r="J8" t="n">
-        <v>6.469834811378177</v>
+        <v>8.176749797956786</v>
       </c>
       <c r="K8" t="n">
-        <v>6.543651098287715</v>
+        <v>8.196088072338259</v>
       </c>
       <c r="L8" t="n">
-        <v>7.407752283091999</v>
+        <v>9.103045129059019</v>
       </c>
       <c r="M8" t="n">
-        <v>5.887388925567155</v>
+        <v>7.543097694955136</v>
       </c>
       <c r="N8" t="n">
-        <v>5.541234980265509</v>
+        <v>27.12432858592459</v>
       </c>
       <c r="O8" t="n">
-        <v>5.87339184717438</v>
+        <v>7.258308693697121</v>
       </c>
       <c r="P8" t="n">
-        <v>4.77121805164782</v>
+        <v>6.180157153643719</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.843960462216883</v>
+        <v>5.785921823295207</v>
       </c>
       <c r="R8" t="n">
-        <v>8.327659087497523</v>
+        <v>10.12878058396608</v>
       </c>
       <c r="S8" t="n">
-        <v>6.913570027096352</v>
+        <v>8.664216600215088</v>
       </c>
       <c r="T8" t="n">
-        <v>6.161576358144056</v>
+        <v>7.878089513206841</v>
       </c>
       <c r="U8" t="n">
-        <v>5.033409671972271</v>
+        <v>6.330402752090024</v>
       </c>
       <c r="V8" t="n">
-        <v>5.871594038637108</v>
+        <v>7.345490991971459</v>
       </c>
       <c r="W8" t="n">
-        <v>6.441270181098534</v>
+        <v>8.195221413010083</v>
       </c>
       <c r="X8" t="n">
-        <v>4.788754927673378</v>
+        <v>5.846878788019461</v>
       </c>
       <c r="Y8" t="n">
-        <v>7.525869404481231</v>
+        <v>9.686727664837644</v>
       </c>
       <c r="Z8" t="n">
-        <v>5.509445945499927</v>
+        <v>6.68878090644571</v>
       </c>
       <c r="AA8" t="n">
-        <v>5.719021747743726</v>
+        <v>7.407514629880526</v>
       </c>
       <c r="AB8" t="n">
-        <v>7.526138888245286</v>
+        <v>9.768054880806217</v>
       </c>
     </row>
     <row r="9">
@@ -6362,85 +6362,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>82.68553554592802</v>
+        <v>83.52986685770969</v>
       </c>
       <c r="C9" t="n">
-        <v>103.3032715443613</v>
+        <v>104.3436927403425</v>
       </c>
       <c r="D9" t="n">
-        <v>102.2385388128825</v>
+        <v>103.2632504767674</v>
       </c>
       <c r="E9" t="n">
-        <v>100.8354923524829</v>
+        <v>102.4690784175719</v>
       </c>
       <c r="F9" t="n">
-        <v>54.58066042045287</v>
+        <v>55.23586135051903</v>
       </c>
       <c r="G9" t="n">
-        <v>102.5358646091137</v>
+        <v>103.5910814870297</v>
       </c>
       <c r="H9" t="n">
-        <v>102.6020976161787</v>
+        <v>103.6882833722783</v>
       </c>
       <c r="I9" t="n">
-        <v>104.0486398975337</v>
+        <v>105.1157316884383</v>
       </c>
       <c r="J9" t="n">
-        <v>103.10966479245</v>
+        <v>104.2039848867533</v>
       </c>
       <c r="K9" t="n">
-        <v>103.1834810793594</v>
+        <v>104.2233231611345</v>
       </c>
       <c r="L9" t="n">
-        <v>104.047582264164</v>
+        <v>105.1302802178552</v>
       </c>
       <c r="M9" t="n">
-        <v>102.5272189066273</v>
+        <v>103.5703327837502</v>
       </c>
       <c r="N9" t="n">
-        <v>103.3935036561687</v>
+        <v>27.12432858592459</v>
       </c>
       <c r="O9" t="n">
-        <v>110.619735248532</v>
+        <v>111.7758359651136</v>
       </c>
       <c r="P9" t="n">
-        <v>111.1710396703739</v>
+        <v>112.3945169028243</v>
       </c>
       <c r="Q9" t="n">
-        <v>103.355271845854</v>
+        <v>104.3698728487389</v>
       </c>
       <c r="R9" t="n">
-        <v>104.967489068569</v>
+        <v>106.1560156727623</v>
       </c>
       <c r="S9" t="n">
-        <v>103.5534000081679</v>
+        <v>104.6914516890116</v>
       </c>
       <c r="T9" t="n">
-        <v>102.8014063392156</v>
+        <v>103.9053246020031</v>
       </c>
       <c r="U9" t="n">
-        <v>102.3937286868255</v>
+        <v>103.4155085808342</v>
       </c>
       <c r="V9" t="n">
-        <v>128.0579557645337</v>
+        <v>129.3549534938589</v>
       </c>
       <c r="W9" t="n">
-        <v>103.0807927730861</v>
+        <v>104.2220365694</v>
       </c>
       <c r="X9" t="n">
-        <v>103.1567127099171</v>
+        <v>104.2349877984363</v>
       </c>
       <c r="Y9" t="n">
-        <v>102.5371153521923</v>
+        <v>103.6149505256851</v>
       </c>
       <c r="Z9" t="n">
-        <v>90.59392702238475</v>
+        <v>91.63147934795282</v>
       </c>
       <c r="AA9" t="n">
-        <v>102.3588517288152</v>
+        <v>103.4347497186767</v>
       </c>
       <c r="AB9" t="n">
-        <v>102.5321362709108</v>
+        <v>103.5632370170012</v>
       </c>
     </row>
   </sheetData>
@@ -6606,85 +6606,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.650589221523078</v>
+        <v>3.289717205110761</v>
       </c>
       <c r="C2" t="n">
-        <v>2.578624935182021</v>
+        <v>3.45283308636466</v>
       </c>
       <c r="D2" t="n">
-        <v>2.433993485177947</v>
+        <v>3.071776491331234</v>
       </c>
       <c r="E2" t="n">
-        <v>2.624646245860828</v>
+        <v>3.320744564775182</v>
       </c>
       <c r="F2" t="n">
-        <v>2.504745385364054</v>
+        <v>3.147561436439771</v>
       </c>
       <c r="G2" t="n">
-        <v>2.372640720913905</v>
+        <v>3.011139727644716</v>
       </c>
       <c r="H2" t="n">
-        <v>2.344803977998792</v>
+        <v>2.984352829577822</v>
       </c>
       <c r="I2" t="n">
-        <v>2.403554592298577</v>
+        <v>3.041401879416969</v>
       </c>
       <c r="J2" t="n">
-        <v>2.407138524509073</v>
+        <v>3.049464253972549</v>
       </c>
       <c r="K2" t="n">
-        <v>2.37606345618708</v>
+        <v>3.012644953319922</v>
       </c>
       <c r="L2" t="n">
-        <v>2.460322117285985</v>
+        <v>3.102428559899532</v>
       </c>
       <c r="M2" t="n">
-        <v>2.341752602581931</v>
+        <v>2.978473653760973</v>
       </c>
       <c r="N2" t="n">
-        <v>2.39802683416338</v>
+        <v>3.037322726020564</v>
       </c>
       <c r="O2" t="n">
-        <v>4.66622033615466</v>
+        <v>6.043936008986202</v>
       </c>
       <c r="P2" t="n">
-        <v>2.356973831976495</v>
+        <v>3.008163221724061</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.445751060159657</v>
+        <v>3.081611066061608</v>
       </c>
       <c r="R2" t="n">
-        <v>2.611179584465339</v>
+        <v>3.272028140796353</v>
       </c>
       <c r="S2" t="n">
-        <v>2.429765670346125</v>
+        <v>3.077358101811107</v>
       </c>
       <c r="T2" t="n">
-        <v>2.352983926271687</v>
+        <v>2.994955834638783</v>
       </c>
       <c r="U2" t="n">
-        <v>2.866288617213477</v>
+        <v>4.194003425772692</v>
       </c>
       <c r="V2" t="n">
-        <v>2.401967024606849</v>
+        <v>3.042384385776159</v>
       </c>
       <c r="W2" t="n">
-        <v>3.111632604542029</v>
+        <v>4.545934196652236</v>
       </c>
       <c r="X2" t="n">
-        <v>2.409515243584918</v>
+        <v>3.050905523920061</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.37550215456802</v>
+        <v>3.016254973668923</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.666183431121764</v>
+        <v>3.650499389283862</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.346082150195894</v>
+        <v>2.988111646959944</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.372224881947637</v>
+        <v>3.009527721494161</v>
       </c>
     </row>
     <row r="3">
@@ -6694,85 +6694,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.596179349137104</v>
+        <v>5.197899365788602</v>
       </c>
       <c r="C3" t="n">
-        <v>3.48727483984832</v>
+        <v>4.481263302994123</v>
       </c>
       <c r="D3" t="n">
-        <v>3.061311181367033</v>
+        <v>3.653697722990397</v>
       </c>
       <c r="E3" t="n">
-        <v>4.413708326270241</v>
+        <v>5.420472822573493</v>
       </c>
       <c r="F3" t="n">
-        <v>3.568842146000949</v>
+        <v>4.197274581962657</v>
       </c>
       <c r="G3" t="n">
-        <v>2.620931209549405</v>
+        <v>3.218144406955536</v>
       </c>
       <c r="H3" t="n">
-        <v>2.425734631101073</v>
+        <v>3.030915085224303</v>
       </c>
       <c r="I3" t="n">
-        <v>2.845428026074763</v>
+        <v>3.438337584677256</v>
       </c>
       <c r="J3" t="n">
-        <v>2.867351365378472</v>
+        <v>3.491876428371059</v>
       </c>
       <c r="K3" t="n">
-        <v>2.64721523427438</v>
+        <v>3.230992513685412</v>
       </c>
       <c r="L3" t="n">
-        <v>3.241339690768557</v>
+        <v>3.864094164305444</v>
       </c>
       <c r="M3" t="n">
-        <v>2.418799105545976</v>
+        <v>3.008219345670884</v>
       </c>
       <c r="N3" t="n">
-        <v>2.804448876183952</v>
+        <v>3.40757742115645</v>
       </c>
       <c r="O3" t="n">
-        <v>6.718961623221246</v>
+        <v>8.576343510882102</v>
       </c>
       <c r="P3" t="n">
-        <v>2.509926303576422</v>
+        <v>3.197154563266038</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.142854004537601</v>
+        <v>3.721439973493786</v>
       </c>
       <c r="R3" t="n">
-        <v>4.332986528934073</v>
+        <v>5.090647383284414</v>
       </c>
       <c r="S3" t="n">
-        <v>3.02637587011671</v>
+        <v>3.688102976463906</v>
       </c>
       <c r="T3" t="n">
-        <v>2.48349418655485</v>
+        <v>3.105816507074024</v>
       </c>
       <c r="U3" t="n">
-        <v>3.283411346698305</v>
+        <v>5.009076422942927</v>
       </c>
       <c r="V3" t="n">
-        <v>2.829332333745964</v>
+        <v>3.440168338952648</v>
       </c>
       <c r="W3" t="n">
-        <v>4.136269408129377</v>
+        <v>6.089701117119567</v>
       </c>
       <c r="X3" t="n">
-        <v>2.885032053521993</v>
+        <v>3.502999136628425</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.644205882332994</v>
+        <v>3.257785763758861</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.534021530998835</v>
+        <v>4.752780506040195</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.433923359361955</v>
+        <v>3.056584240136559</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.633774070760418</v>
+        <v>3.226592582869135</v>
       </c>
     </row>
     <row r="4">
@@ -6782,85 +6782,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.524632404391266</v>
+        <v>6.085564332464038</v>
       </c>
       <c r="C4" t="n">
-        <v>3.467747976738896</v>
+        <v>4.037051225794204</v>
       </c>
       <c r="D4" t="n">
-        <v>3.078083923411613</v>
+        <v>3.623823712642789</v>
       </c>
       <c r="E4" t="n">
-        <v>5.231594559927739</v>
+        <v>6.436032633164338</v>
       </c>
       <c r="F4" t="n">
-        <v>3.877259183495737</v>
+        <v>4.479849530440766</v>
       </c>
       <c r="G4" t="n">
-        <v>2.385076227383213</v>
+        <v>2.938903572514018</v>
       </c>
       <c r="H4" t="n">
-        <v>2.070647410622652</v>
+        <v>2.636333236266583</v>
       </c>
       <c r="I4" t="n">
-        <v>2.734262625756513</v>
+        <v>3.280728498059345</v>
       </c>
       <c r="J4" t="n">
-        <v>2.774029987231662</v>
+        <v>3.370703454333192</v>
       </c>
       <c r="K4" t="n">
-        <v>2.423737596829797</v>
+        <v>2.955905788953524</v>
       </c>
       <c r="L4" t="n">
-        <v>3.375477934840996</v>
+        <v>3.970052927769806</v>
       </c>
       <c r="M4" t="n">
-        <v>2.064914042874912</v>
+        <v>2.607121539718747</v>
       </c>
       <c r="N4" t="n">
-        <v>2.671824054725108</v>
+        <v>20.40478683821665</v>
       </c>
       <c r="O4" t="n">
-        <v>3.032944481459957</v>
+        <v>3.669760390924519</v>
       </c>
       <c r="P4" t="n">
-        <v>2.208111509710177</v>
+        <v>2.905282568879894</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.210891141581619</v>
+        <v>3.734909758350145</v>
       </c>
       <c r="R4" t="n">
-        <v>5.079482424495326</v>
+        <v>5.885758213661264</v>
       </c>
       <c r="S4" t="n">
-        <v>3.030328809995237</v>
+        <v>3.686870570680592</v>
       </c>
       <c r="T4" t="n">
-        <v>2.163043689327099</v>
+        <v>2.756099056053434</v>
       </c>
       <c r="U4" t="n">
-        <v>2.01715627156422</v>
+        <v>2.440145443213641</v>
       </c>
       <c r="V4" t="n">
-        <v>2.71195529282622</v>
+        <v>3.285371345014326</v>
       </c>
       <c r="W4" t="n">
-        <v>2.991409839150156</v>
+        <v>3.632819735701069</v>
       </c>
       <c r="X4" t="n">
-        <v>2.801590924070741</v>
+        <v>3.388076534614168</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.366146490883414</v>
+        <v>2.833777969520669</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.277548673809618</v>
+        <v>3.936997075505811</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.085084953577148</v>
+        <v>2.678790807739047</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.402059264149829</v>
+        <v>2.949240782933377</v>
       </c>
     </row>
     <row r="5">
@@ -6870,85 +6870,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>63.59281412519798</v>
+        <v>65.1118291558416</v>
       </c>
       <c r="C5" t="n">
-        <v>32.5376773784301</v>
+        <v>34.32422296420146</v>
       </c>
       <c r="D5" t="n">
-        <v>26.01499084361965</v>
+        <v>27.40299803876711</v>
       </c>
       <c r="E5" t="n">
-        <v>59.80153867070246</v>
+        <v>71.89584881445381</v>
       </c>
       <c r="F5" t="n">
-        <v>41.48214494540356</v>
+        <v>43.94032344743562</v>
       </c>
       <c r="G5" t="n">
-        <v>12.46128640963275</v>
+        <v>13.84543110045678</v>
       </c>
       <c r="H5" t="n">
-        <v>8.701258145520468</v>
+        <v>10.5410173931668</v>
       </c>
       <c r="I5" t="n">
-        <v>20.63911321728362</v>
+        <v>22.07325341588406</v>
       </c>
       <c r="J5" t="n">
-        <v>19.46009267177329</v>
+        <v>21.60854095645568</v>
       </c>
       <c r="K5" t="n">
-        <v>14.10679396939643</v>
+        <v>15.23712862669227</v>
       </c>
       <c r="L5" t="n">
-        <v>27.1911544040616</v>
+        <v>29.18966246128461</v>
       </c>
       <c r="M5" t="n">
-        <v>8.201289283126524</v>
+        <v>9.534501493285704</v>
       </c>
       <c r="N5" t="n">
-        <v>8.22611297823109</v>
+        <v>20.40478683821664</v>
       </c>
       <c r="O5" t="n">
-        <v>22.56136866507777</v>
+        <v>25.2306390378361</v>
       </c>
       <c r="P5" t="n">
-        <v>9.751374459820893</v>
+        <v>13.38222417616187</v>
       </c>
       <c r="Q5" t="n">
-        <v>27.13489663857451</v>
+        <v>28.09933153881808</v>
       </c>
       <c r="R5" t="n">
-        <v>65.08688848810847</v>
+        <v>71.42199535956254</v>
       </c>
       <c r="S5" t="n">
-        <v>22.70299876342373</v>
+        <v>25.70361853201441</v>
       </c>
       <c r="T5" t="n">
-        <v>10.01354708822131</v>
+        <v>12.25881342984594</v>
       </c>
       <c r="U5" t="n">
-        <v>7.622696141017859</v>
+        <v>8.724416309908056</v>
       </c>
       <c r="V5" t="n">
-        <v>17.84816128300949</v>
+        <v>19.57793099534462</v>
       </c>
       <c r="W5" t="n">
-        <v>23.69931573985117</v>
+        <v>26.66388433238836</v>
       </c>
       <c r="X5" t="n">
-        <v>20.30767244649837</v>
+        <v>22.33095704427158</v>
       </c>
       <c r="Y5" t="n">
-        <v>14.51116490141009</v>
+        <v>16.49125321305124</v>
       </c>
       <c r="Z5" t="n">
-        <v>25.68490431401876</v>
+        <v>28.63134284440373</v>
       </c>
       <c r="AA5" t="n">
-        <v>8.472769223547211</v>
+        <v>10.69199461036785</v>
       </c>
       <c r="AB5" t="n">
-        <v>14.85086972372427</v>
+        <v>16.33113218792017</v>
       </c>
     </row>
     <row r="6">
@@ -6958,85 +6958,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7.977694846359491</v>
+        <v>9.348776175394557</v>
       </c>
       <c r="C6" t="n">
-        <v>5.920810418707053</v>
+        <v>7.300263068724725</v>
       </c>
       <c r="D6" t="n">
-        <v>5.531146365379798</v>
+        <v>6.887035555573192</v>
       </c>
       <c r="E6" t="n">
-        <v>7.684657001895929</v>
+        <v>7.275486890337284</v>
       </c>
       <c r="F6" t="n">
-        <v>6.330321625463944</v>
+        <v>7.743061373371288</v>
       </c>
       <c r="G6" t="n">
-        <v>4.838138669351438</v>
+        <v>6.202115415444547</v>
       </c>
       <c r="H6" t="n">
-        <v>2.543966897145126</v>
+        <v>5.899545079197006</v>
       </c>
       <c r="I6" t="n">
-        <v>3.207582112279023</v>
+        <v>6.543940340989677</v>
       </c>
       <c r="J6" t="n">
-        <v>3.24734947375415</v>
+        <v>4.210157711506187</v>
       </c>
       <c r="K6" t="n">
-        <v>4.876800038798022</v>
+        <v>3.795360046126499</v>
       </c>
       <c r="L6" t="n">
-        <v>5.828540376809143</v>
+        <v>7.233264770700329</v>
       </c>
       <c r="M6" t="n">
-        <v>4.517976484843166</v>
+        <v>5.87033338264927</v>
       </c>
       <c r="N6" t="n">
-        <v>3.132285554028915</v>
+        <v>20.40478683821664</v>
       </c>
       <c r="O6" t="n">
-        <v>5.549863471261485</v>
+        <v>4.486164010661235</v>
       </c>
       <c r="P6" t="n">
-        <v>4.725737986107858</v>
+        <v>6.296548801097863</v>
       </c>
       <c r="Q6" t="n">
-        <v>5.663953583549817</v>
+        <v>6.9981216012807</v>
       </c>
       <c r="R6" t="n">
-        <v>5.552801911017797</v>
+        <v>9.148970056591748</v>
       </c>
       <c r="S6" t="n">
-        <v>3.503648296517729</v>
+        <v>6.950082413611115</v>
       </c>
       <c r="T6" t="n">
-        <v>4.616106131295276</v>
+        <v>3.595553313226473</v>
       </c>
       <c r="U6" t="n">
-        <v>4.521469659480098</v>
+        <v>5.866261946110321</v>
       </c>
       <c r="V6" t="n">
-        <v>3.185274779348704</v>
+        <v>4.124825602187284</v>
       </c>
       <c r="W6" t="n">
-        <v>5.507590359427716</v>
+        <v>7.016197340652296</v>
       </c>
       <c r="X6" t="n">
-        <v>3.27491041059325</v>
+        <v>4.227530791787117</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.908191280816296</v>
+        <v>3.856796571892457</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.750868160332102</v>
+        <v>4.776451332678817</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.558404440099635</v>
+        <v>5.942002650669537</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.859969242441051</v>
+        <v>3.749663004295965</v>
       </c>
     </row>
     <row r="7">
@@ -7046,85 +7046,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6.254362628447939</v>
+        <v>6.972914963501511</v>
       </c>
       <c r="C7" t="n">
-        <v>4.197478200795564</v>
+        <v>4.924401856831751</v>
       </c>
       <c r="D7" t="n">
-        <v>3.807814147468294</v>
+        <v>4.511174343680275</v>
       </c>
       <c r="E7" t="n">
-        <v>5.961324783984442</v>
+        <v>7.323383264201816</v>
       </c>
       <c r="F7" t="n">
-        <v>4.60698940755243</v>
+        <v>5.367200161478275</v>
       </c>
       <c r="G7" t="n">
-        <v>3.114806451439882</v>
+        <v>3.826254203551559</v>
       </c>
       <c r="H7" t="n">
-        <v>2.800377634679324</v>
+        <v>3.523683867304064</v>
       </c>
       <c r="I7" t="n">
-        <v>3.463992849813199</v>
+        <v>4.168079129096794</v>
       </c>
       <c r="J7" t="n">
-        <v>3.503760211288368</v>
+        <v>4.258054085370701</v>
       </c>
       <c r="K7" t="n">
-        <v>3.153467820886497</v>
+        <v>3.843256419991098</v>
       </c>
       <c r="L7" t="n">
-        <v>4.105208158897697</v>
+        <v>4.857403558807349</v>
       </c>
       <c r="M7" t="n">
-        <v>2.794644266931609</v>
+        <v>3.494472170756286</v>
       </c>
       <c r="N7" t="n">
-        <v>3.401554278781765</v>
+        <v>20.40478683821664</v>
       </c>
       <c r="O7" t="n">
-        <v>3.762637269624935</v>
+        <v>4.557119590659822</v>
       </c>
       <c r="P7" t="n">
-        <v>2.937804297875159</v>
+        <v>3.792641768615196</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.940621365638302</v>
+        <v>4.622260389387689</v>
       </c>
       <c r="R7" t="n">
-        <v>5.809212648552</v>
+        <v>6.773108844698833</v>
       </c>
       <c r="S7" t="n">
-        <v>3.760059034051903</v>
+        <v>4.574221201718131</v>
       </c>
       <c r="T7" t="n">
-        <v>2.892773913383793</v>
+        <v>3.643449687091039</v>
       </c>
       <c r="U7" t="n">
-        <v>2.854327825542864</v>
+        <v>3.462719161891451</v>
       </c>
       <c r="V7" t="n">
-        <v>3.441685516882881</v>
+        <v>4.172721976051831</v>
       </c>
       <c r="W7" t="n">
-        <v>3.721140063206819</v>
+        <v>4.520170366738519</v>
       </c>
       <c r="X7" t="n">
-        <v>3.531321148127419</v>
+        <v>4.275427165651806</v>
       </c>
       <c r="Y7" t="n">
-        <v>3.147127660887727</v>
+        <v>3.884033260524431</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.007278897866291</v>
+        <v>4.824347706543318</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.814815177633838</v>
+        <v>3.566141438776585</v>
       </c>
       <c r="AB7" t="n">
-        <v>3.131789488206513</v>
+        <v>3.836591413970827</v>
       </c>
     </row>
     <row r="8">
@@ -7134,85 +7134,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7.924299262156331</v>
+        <v>8.988928278444657</v>
       </c>
       <c r="C8" t="n">
-        <v>7.543069154884293</v>
+        <v>9.187148725604546</v>
       </c>
       <c r="D8" t="n">
-        <v>7.153405101557065</v>
+        <v>8.773921212453208</v>
       </c>
       <c r="E8" t="n">
-        <v>8.414679241716874</v>
+        <v>10.38981079197581</v>
       </c>
       <c r="F8" t="n">
-        <v>6.537973400297121</v>
+        <v>7.733228305000692</v>
       </c>
       <c r="G8" t="n">
-        <v>6.807855244582824</v>
+        <v>8.554875910190088</v>
       </c>
       <c r="H8" t="n">
-        <v>6.145968588768057</v>
+        <v>7.78643073607696</v>
       </c>
       <c r="I8" t="n">
-        <v>6.809583803901933</v>
+        <v>8.430825997869656</v>
       </c>
       <c r="J8" t="n">
-        <v>6.849351165377102</v>
+        <v>8.520800954143528</v>
       </c>
       <c r="K8" t="n">
-        <v>6.499058774975198</v>
+        <v>8.106003288763812</v>
       </c>
       <c r="L8" t="n">
-        <v>7.450799112986454</v>
+        <v>9.120150427580157</v>
       </c>
       <c r="M8" t="n">
-        <v>6.14023522103518</v>
+        <v>7.757219039541186</v>
       </c>
       <c r="N8" t="n">
-        <v>5.448232803080275</v>
+        <v>20.40478683821664</v>
       </c>
       <c r="O8" t="n">
-        <v>6.166305642457167</v>
+        <v>7.556868766053143</v>
       </c>
       <c r="P8" t="n">
-        <v>5.253975009332916</v>
+        <v>6.675073232500785</v>
       </c>
       <c r="Q8" t="n">
-        <v>5.281253681145831</v>
+        <v>6.19673928432584</v>
       </c>
       <c r="R8" t="n">
-        <v>9.154803602640726</v>
+        <v>11.03585571347165</v>
       </c>
       <c r="S8" t="n">
-        <v>7.105649988140701</v>
+        <v>8.836968070491013</v>
       </c>
       <c r="T8" t="n">
-        <v>6.238364867472557</v>
+        <v>7.906196555863819</v>
       </c>
       <c r="U8" t="n">
-        <v>5.369439065157617</v>
+        <v>6.635087757327189</v>
       </c>
       <c r="V8" t="n">
-        <v>6.377357026289527</v>
+        <v>7.797733835660466</v>
       </c>
       <c r="W8" t="n">
-        <v>7.06706032882681</v>
+        <v>8.783358774093376</v>
       </c>
       <c r="X8" t="n">
-        <v>5.025530510106757</v>
+        <v>6.055823649621563</v>
       </c>
       <c r="Y8" t="n">
-        <v>8.233328019776431</v>
+        <v>10.34394574749267</v>
       </c>
       <c r="Z8" t="n">
-        <v>5.646089392521524</v>
+        <v>6.798626793108876</v>
       </c>
       <c r="AA8" t="n">
-        <v>6.160406131722551</v>
+        <v>7.828888307549399</v>
       </c>
       <c r="AB8" t="n">
-        <v>8.227741493467564</v>
+        <v>10.44623933999174</v>
       </c>
     </row>
     <row r="9">
@@ -7222,85 +7222,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>84.21149488583885</v>
+        <v>85.00767314614951</v>
       </c>
       <c r="C9" t="n">
-        <v>103.9815553552297</v>
+        <v>104.9604273252745</v>
       </c>
       <c r="D9" t="n">
-        <v>103.5918913019025</v>
+        <v>104.5471998121232</v>
       </c>
       <c r="E9" t="n">
-        <v>100.7078327366174</v>
+        <v>102.2816069876303</v>
       </c>
       <c r="F9" t="n">
-        <v>54.07400033294844</v>
+        <v>54.68429811860008</v>
       </c>
       <c r="G9" t="n">
-        <v>102.8988844508396</v>
+        <v>103.8622809759568</v>
       </c>
       <c r="H9" t="n">
-        <v>102.5844547891136</v>
+        <v>103.5597093357469</v>
       </c>
       <c r="I9" t="n">
-        <v>103.2480700042474</v>
+        <v>104.2041045975396</v>
       </c>
       <c r="J9" t="n">
-        <v>103.2878373657225</v>
+        <v>104.2940795538136</v>
       </c>
       <c r="K9" t="n">
-        <v>102.9375449753207</v>
+        <v>103.879281888434</v>
       </c>
       <c r="L9" t="n">
-        <v>103.8892853133317</v>
+        <v>104.8934290272503</v>
       </c>
       <c r="M9" t="n">
-        <v>102.5787214213659</v>
+        <v>103.5304976391992</v>
       </c>
       <c r="N9" t="n">
-        <v>103.185631433216</v>
+        <v>20.40478683821664</v>
       </c>
       <c r="O9" t="n">
-        <v>110.7801739438636</v>
+        <v>111.8843293968026</v>
       </c>
       <c r="P9" t="n">
-        <v>111.5284859869813</v>
+        <v>112.7055606525112</v>
       </c>
       <c r="Q9" t="n">
-        <v>103.7246993650378</v>
+        <v>104.658287161793</v>
       </c>
       <c r="R9" t="n">
-        <v>105.5932898029861</v>
+        <v>106.8091343131417</v>
       </c>
       <c r="S9" t="n">
-        <v>103.5441361884862</v>
+        <v>104.6102466701609</v>
       </c>
       <c r="T9" t="n">
-        <v>102.676851067818</v>
+        <v>103.6794751555336</v>
       </c>
       <c r="U9" t="n">
-        <v>102.5822145960027</v>
+        <v>103.5264262026603</v>
       </c>
       <c r="V9" t="n">
-        <v>128.4135949275972</v>
+        <v>129.597744568313</v>
       </c>
       <c r="W9" t="n">
-        <v>103.5052172176411</v>
+        <v>104.5561958351815</v>
       </c>
       <c r="X9" t="n">
-        <v>103.3153983025615</v>
+        <v>104.3114526340945</v>
       </c>
       <c r="Y9" t="n">
-        <v>102.931204815322</v>
+        <v>103.9200587289673</v>
       </c>
       <c r="Z9" t="n">
-        <v>90.63164954257763</v>
+        <v>91.59556594846052</v>
       </c>
       <c r="AA9" t="n">
-        <v>102.5988923320681</v>
+        <v>103.6021669072194</v>
       </c>
       <c r="AB9" t="n">
-        <v>102.915866642641</v>
+        <v>103.8726168824136</v>
       </c>
     </row>
   </sheetData>
@@ -7466,85 +7466,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.03757791270089</v>
+        <v>2.296974047046325</v>
       </c>
       <c r="C2" t="n">
-        <v>2.051035913546658</v>
+        <v>2.348894663363299</v>
       </c>
       <c r="D2" t="n">
-        <v>1.990298494011227</v>
+        <v>2.262336912219033</v>
       </c>
       <c r="E2" t="n">
-        <v>2.079001449700356</v>
+        <v>2.350843158358721</v>
       </c>
       <c r="F2" t="n">
-        <v>2.065143550140285</v>
+        <v>2.33374295871989</v>
       </c>
       <c r="G2" t="n">
-        <v>2.11062571768993</v>
+        <v>2.367977575825368</v>
       </c>
       <c r="H2" t="n">
-        <v>1.998446451334855</v>
+        <v>2.267355694162637</v>
       </c>
       <c r="I2" t="n">
-        <v>2.093303972311629</v>
+        <v>2.364311013827875</v>
       </c>
       <c r="J2" t="n">
-        <v>2.06507000686147</v>
+        <v>2.32858076683651</v>
       </c>
       <c r="K2" t="n">
-        <v>2.100050027558162</v>
+        <v>2.371923535264024</v>
       </c>
       <c r="L2" t="n">
-        <v>2.121539190491636</v>
+        <v>2.324545505482345</v>
       </c>
       <c r="M2" t="n">
-        <v>2.118658891374261</v>
+        <v>2.3919767403412</v>
       </c>
       <c r="N2" t="n">
-        <v>2.019119428448289</v>
+        <v>2.299583070746583</v>
       </c>
       <c r="O2" t="n">
-        <v>3.765533482809097</v>
+        <v>4.245885709121339</v>
       </c>
       <c r="P2" t="n">
-        <v>2.036308061873514</v>
+        <v>2.297933541402521</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.068789955436093</v>
+        <v>2.333936224417935</v>
       </c>
       <c r="R2" t="n">
-        <v>2.067129225849703</v>
+        <v>2.334870188047368</v>
       </c>
       <c r="S2" t="n">
-        <v>2.087533202675923</v>
+        <v>2.355348922852984</v>
       </c>
       <c r="T2" t="n">
-        <v>2.027617364061339</v>
+        <v>2.294379641524253</v>
       </c>
       <c r="U2" t="n">
-        <v>2.086537788281818</v>
+        <v>2.677755071062309</v>
       </c>
       <c r="V2" t="n">
-        <v>2.018754040858612</v>
+        <v>2.28722030185991</v>
       </c>
       <c r="W2" t="n">
-        <v>2.143916036232193</v>
+        <v>2.801052559733495</v>
       </c>
       <c r="X2" t="n">
-        <v>2.083100666581031</v>
+        <v>2.336793714404096</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.026314616528694</v>
+        <v>2.293661830048227</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.848696594074517</v>
+        <v>2.217088971164569</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.016228940178275</v>
+        <v>2.280756173812253</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.060114601461079</v>
+        <v>2.345661968121422</v>
       </c>
     </row>
     <row r="3">
@@ -7554,85 +7554,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.377155967619095</v>
+        <v>2.572598310496395</v>
       </c>
       <c r="C3" t="n">
-        <v>2.333726664003285</v>
+        <v>2.63662137748303</v>
       </c>
       <c r="D3" t="n">
-        <v>2.041909847195263</v>
+        <v>2.327451874502726</v>
       </c>
       <c r="E3" t="n">
-        <v>2.674743263929068</v>
+        <v>2.958775934764759</v>
       </c>
       <c r="F3" t="n">
-        <v>2.577399095246963</v>
+        <v>2.838331580014116</v>
       </c>
       <c r="G3" t="n">
-        <v>2.895572881316179</v>
+        <v>3.076553650435982</v>
       </c>
       <c r="H3" t="n">
-        <v>2.100644568236691</v>
+        <v>2.363836132368519</v>
       </c>
       <c r="I3" t="n">
-        <v>2.779323567534998</v>
+        <v>3.057490496471345</v>
       </c>
       <c r="J3" t="n">
-        <v>2.573285555259073</v>
+        <v>2.798015623181571</v>
       </c>
       <c r="K3" t="n">
-        <v>2.822432552958025</v>
+        <v>3.10661300013589</v>
       </c>
       <c r="L3" t="n">
-        <v>2.976168584780161</v>
+        <v>2.769918710146106</v>
       </c>
       <c r="M3" t="n">
-        <v>2.955409601720088</v>
+        <v>3.25086908500765</v>
       </c>
       <c r="N3" t="n">
-        <v>2.247693016525365</v>
+        <v>2.593367646320614</v>
       </c>
       <c r="O3" t="n">
-        <v>5.075308592845193</v>
+        <v>5.692123924809483</v>
       </c>
       <c r="P3" t="n">
-        <v>2.368589196213943</v>
+        <v>2.579799958954037</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.601940122594863</v>
+        <v>2.838183664531467</v>
       </c>
       <c r="R3" t="n">
-        <v>2.592874229911176</v>
+        <v>2.847668407532754</v>
       </c>
       <c r="S3" t="n">
-        <v>2.730950151315496</v>
+        <v>2.986206229185968</v>
       </c>
       <c r="T3" t="n">
-        <v>2.309038691550116</v>
+        <v>2.556815153005821</v>
       </c>
       <c r="U3" t="n">
-        <v>2.485430125566632</v>
+        <v>3.165967752974291</v>
       </c>
       <c r="V3" t="n">
-        <v>2.243264804836986</v>
+        <v>2.503134544712687</v>
       </c>
       <c r="W3" t="n">
-        <v>2.349432269206965</v>
+        <v>3.284034712963791</v>
       </c>
       <c r="X3" t="n">
-        <v>2.705423861748488</v>
+        <v>2.859747574787682</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.298587080162587</v>
+        <v>2.55053672668643</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.934053044083752</v>
+        <v>2.323227012592789</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.226742770317741</v>
+        <v>2.458557282294555</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.543707981650743</v>
+        <v>2.925415807854112</v>
       </c>
     </row>
     <row r="4">
@@ -7642,85 +7642,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.000292367139468</v>
+        <v>2.059087429556583</v>
       </c>
       <c r="C4" t="n">
-        <v>1.863358983772321</v>
+        <v>2.013326869072522</v>
       </c>
       <c r="D4" t="n">
-        <v>1.466249583432528</v>
+        <v>1.66784505781294</v>
       </c>
       <c r="E4" t="n">
-        <v>2.468190273316821</v>
+        <v>2.66756382284561</v>
       </c>
       <c r="F4" t="n">
-        <v>2.311658922837098</v>
+        <v>2.474409201444528</v>
       </c>
       <c r="G4" t="n">
-        <v>2.825400928141035</v>
+        <v>2.861104950352935</v>
       </c>
       <c r="H4" t="n">
-        <v>1.55828450964843</v>
+        <v>1.724534508619941</v>
       </c>
       <c r="I4" t="n">
-        <v>2.629743845696638</v>
+        <v>2.819689445889205</v>
       </c>
       <c r="J4" t="n">
-        <v>2.309847496562007</v>
+        <v>2.415008934397937</v>
       </c>
       <c r="K4" t="n">
-        <v>2.705943643044946</v>
+        <v>2.905676377443575</v>
       </c>
       <c r="L4" t="n">
-        <v>2.948673623881903</v>
+        <v>2.370519736088788</v>
       </c>
       <c r="M4" t="n">
-        <v>2.913329478416012</v>
+        <v>3.131039336090281</v>
       </c>
       <c r="N4" t="n">
-        <v>1.791795296183999</v>
+        <v>14.00383852928701</v>
       </c>
       <c r="O4" t="n">
-        <v>1.681406435895072</v>
+        <v>1.857579459276364</v>
       </c>
       <c r="P4" t="n">
-        <v>1.985948817883895</v>
+        <v>2.069925359699046</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.352846748082566</v>
+        <v>2.476592226410497</v>
       </c>
       <c r="R4" t="n">
-        <v>2.334088043430942</v>
+        <v>2.487141775249516</v>
       </c>
       <c r="S4" t="n">
-        <v>2.564560347976129</v>
+        <v>2.718458505562406</v>
       </c>
       <c r="T4" t="n">
-        <v>1.887783388176904</v>
+        <v>2.029782425699193</v>
       </c>
       <c r="U4" t="n">
-        <v>1.968040664556332</v>
+        <v>1.85394687555402</v>
       </c>
       <c r="V4" t="n">
-        <v>1.78144379992341</v>
+        <v>1.942160916964028</v>
       </c>
       <c r="W4" t="n">
-        <v>1.577849903742717</v>
+        <v>1.807230503286222</v>
       </c>
       <c r="X4" t="n">
-        <v>2.514492813716974</v>
+        <v>2.508868890314484</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.786585133255789</v>
+        <v>1.891245767361997</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.728057441805193</v>
+        <v>1.815502936263407</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.759145901483872</v>
+        <v>1.875899090787462</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.255792168687929</v>
+        <v>2.60837456544885</v>
       </c>
     </row>
     <row r="5">
@@ -7730,85 +7730,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>13.58636307449132</v>
+        <v>12.25166952336325</v>
       </c>
       <c r="C5" t="n">
-        <v>12.23408381916858</v>
+        <v>12.49966065377071</v>
       </c>
       <c r="D5" t="n">
-        <v>4.706399406108281</v>
+        <v>6.000060068376128</v>
       </c>
       <c r="E5" t="n">
-        <v>23.51529712278084</v>
+        <v>24.70831037029462</v>
       </c>
       <c r="F5" t="n">
-        <v>21.42341019664516</v>
+        <v>21.94635106933207</v>
       </c>
       <c r="G5" t="n">
-        <v>27.55851590190533</v>
+        <v>25.85870000630263</v>
       </c>
       <c r="H5" t="n">
-        <v>6.770458612814984</v>
+        <v>7.386143088669983</v>
       </c>
       <c r="I5" t="n">
-        <v>27.96170026677659</v>
+        <v>29.02723807378222</v>
       </c>
       <c r="J5" t="n">
-        <v>19.41088238694682</v>
+        <v>18.9111604363394</v>
       </c>
       <c r="K5" t="n">
-        <v>26.60061309237804</v>
+        <v>27.75638439353323</v>
       </c>
       <c r="L5" t="n">
-        <v>31.39412764478618</v>
+        <v>18.44137290719141</v>
       </c>
       <c r="M5" t="n">
-        <v>31.46246689376263</v>
+        <v>32.99561224001796</v>
       </c>
       <c r="N5" t="n">
-        <v>14.98584746390333</v>
+        <v>14.00383852928701</v>
       </c>
       <c r="O5" t="n">
-        <v>7.964605733009294</v>
+        <v>8.644814835465292</v>
       </c>
       <c r="P5" t="n">
-        <v>13.5911289583225</v>
+        <v>12.65329723047179</v>
       </c>
       <c r="Q5" t="n">
-        <v>21.37710653025084</v>
+        <v>21.13823707174754</v>
       </c>
       <c r="R5" t="n">
-        <v>22.57231337568145</v>
+        <v>22.90549902930837</v>
       </c>
       <c r="S5" t="n">
-        <v>22.73206968184125</v>
+        <v>23.04137269386008</v>
       </c>
       <c r="T5" t="n">
-        <v>13.11174728924906</v>
+        <v>13.2176731457118</v>
       </c>
       <c r="U5" t="n">
-        <v>15.24857595452207</v>
+        <v>11.47247589018786</v>
       </c>
       <c r="V5" t="n">
-        <v>9.813324817229988</v>
+        <v>10.24475260288635</v>
       </c>
       <c r="W5" t="n">
-        <v>6.673413587476995</v>
+        <v>8.431178319390936</v>
       </c>
       <c r="X5" t="n">
-        <v>25.18289910362833</v>
+        <v>22.39914241025882</v>
       </c>
       <c r="Y5" t="n">
-        <v>12.19180575183188</v>
+        <v>12.42180600694493</v>
       </c>
       <c r="Z5" t="n">
-        <v>8.944332951114861</v>
+        <v>8.094324325905504</v>
       </c>
       <c r="AA5" t="n">
-        <v>10.11433549330864</v>
+        <v>9.737170070372775</v>
       </c>
       <c r="AB5" t="n">
-        <v>21.30774199686251</v>
+        <v>25.80252544859538</v>
       </c>
     </row>
     <row r="6">
@@ -7818,85 +7818,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.239442089128914</v>
+        <v>2.484631979492976</v>
       </c>
       <c r="C6" t="n">
-        <v>2.18256912789044</v>
+        <v>2.438871419008759</v>
       </c>
       <c r="D6" t="n">
-        <v>3.70539930542199</v>
+        <v>2.093389607749194</v>
       </c>
       <c r="E6" t="n">
-        <v>4.707339995306278</v>
+        <v>5.180011130897102</v>
       </c>
       <c r="F6" t="n">
-        <v>4.550808644826552</v>
+        <v>2.899953751380699</v>
       </c>
       <c r="G6" t="n">
-        <v>3.144611072259149</v>
+        <v>5.373552258404066</v>
       </c>
       <c r="H6" t="n">
-        <v>3.79743423163788</v>
+        <v>2.150079058556106</v>
       </c>
       <c r="I6" t="n">
-        <v>2.94895398981476</v>
+        <v>3.245233995825422</v>
       </c>
       <c r="J6" t="n">
-        <v>2.629057640680119</v>
+        <v>2.840553484334121</v>
       </c>
       <c r="K6" t="n">
-        <v>3.025153787163077</v>
+        <v>5.418123685494905</v>
       </c>
       <c r="L6" t="n">
-        <v>5.187823345871362</v>
+        <v>4.882967044139875</v>
       </c>
       <c r="M6" t="n">
-        <v>5.15247920040547</v>
+        <v>3.556583886026523</v>
       </c>
       <c r="N6" t="n">
-        <v>2.107589407247525</v>
+        <v>14.00383852928701</v>
       </c>
       <c r="O6" t="n">
-        <v>1.997200546958617</v>
+        <v>4.495499590618625</v>
       </c>
       <c r="P6" t="n">
-        <v>4.288934533704013</v>
+        <v>4.711818376105716</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.591996470072005</v>
+        <v>2.902136776346737</v>
       </c>
       <c r="R6" t="n">
-        <v>4.5732377654204</v>
+        <v>4.999589083300625</v>
       </c>
       <c r="S6" t="n">
-        <v>4.803710069965589</v>
+        <v>3.14400305549869</v>
       </c>
       <c r="T6" t="n">
-        <v>2.206993532295018</v>
+        <v>2.455326975635403</v>
       </c>
       <c r="U6" t="n">
-        <v>4.293673508792184</v>
+        <v>4.496822831111379</v>
       </c>
       <c r="V6" t="n">
-        <v>4.020593521912852</v>
+        <v>2.367705466900307</v>
       </c>
       <c r="W6" t="n">
-        <v>1.911276599201239</v>
+        <v>2.253458067386498</v>
       </c>
       <c r="X6" t="n">
-        <v>2.833702957835105</v>
+        <v>5.021316198365753</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.204003001090896</v>
+        <v>2.462000474827251</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.047267585923316</v>
+        <v>4.327950244314848</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.998295623473316</v>
+        <v>4.388346398838738</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.573871796305447</v>
+        <v>3.026274713785592</v>
       </c>
     </row>
     <row r="7">
@@ -7906,85 +7906,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.648739665106364</v>
+        <v>2.786277254864392</v>
       </c>
       <c r="C7" t="n">
-        <v>2.511806281739225</v>
+        <v>2.740516694380255</v>
       </c>
       <c r="D7" t="n">
-        <v>2.114696881399435</v>
+        <v>2.395034883120735</v>
       </c>
       <c r="E7" t="n">
-        <v>3.116637571283753</v>
+        <v>3.394753648153372</v>
       </c>
       <c r="F7" t="n">
-        <v>2.960106220803993</v>
+        <v>3.20159902675227</v>
       </c>
       <c r="G7" t="n">
-        <v>3.473848226107952</v>
+        <v>3.588294775660734</v>
       </c>
       <c r="H7" t="n">
-        <v>2.206731807615335</v>
+        <v>2.451724333927681</v>
       </c>
       <c r="I7" t="n">
-        <v>3.278191143663534</v>
+        <v>3.546879271196948</v>
       </c>
       <c r="J7" t="n">
-        <v>2.958294794528927</v>
+        <v>3.142198759705693</v>
       </c>
       <c r="K7" t="n">
-        <v>3.354390941011856</v>
+        <v>3.63286620275135</v>
       </c>
       <c r="L7" t="n">
-        <v>3.59712092184882</v>
+        <v>3.097709561396577</v>
       </c>
       <c r="M7" t="n">
-        <v>3.561776776382922</v>
+        <v>3.858229161398047</v>
       </c>
       <c r="N7" t="n">
-        <v>2.440242594150903</v>
+        <v>14.00383852928701</v>
       </c>
       <c r="O7" t="n">
-        <v>2.329838328222438</v>
+        <v>2.584772640374423</v>
       </c>
       <c r="P7" t="n">
-        <v>2.634380710211277</v>
+        <v>2.797118540797092</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.001294046049467</v>
+        <v>3.203782051718186</v>
       </c>
       <c r="R7" t="n">
-        <v>2.982535341397853</v>
+        <v>3.214331600557253</v>
       </c>
       <c r="S7" t="n">
-        <v>3.213007645943045</v>
+        <v>3.445648330870166</v>
       </c>
       <c r="T7" t="n">
-        <v>2.536230686143817</v>
+        <v>2.756972251006903</v>
       </c>
       <c r="U7" t="n">
-        <v>2.715581056246543</v>
+        <v>2.695601343264647</v>
       </c>
       <c r="V7" t="n">
-        <v>2.42989109789032</v>
+        <v>2.669350742271792</v>
       </c>
       <c r="W7" t="n">
-        <v>2.22629720170962</v>
+        <v>2.534420328593998</v>
       </c>
       <c r="X7" t="n">
-        <v>3.162940111683887</v>
+        <v>3.236058715622213</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.521515553469097</v>
+        <v>2.74886424017566</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.376504739772099</v>
+        <v>2.542692761571159</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.407593199450774</v>
+        <v>2.60308891609524</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.904239466654837</v>
+        <v>3.335564390756548</v>
       </c>
     </row>
     <row r="8">
@@ -7994,85 +7994,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.308805993156014</v>
+        <v>4.604381100905834</v>
       </c>
       <c r="C8" t="n">
-        <v>5.69723489537194</v>
+        <v>6.346762708136849</v>
       </c>
       <c r="D8" t="n">
-        <v>5.300125495032125</v>
+        <v>6.001280896877004</v>
       </c>
       <c r="E8" t="n">
-        <v>5.489855763258594</v>
+        <v>6.048866705233904</v>
       </c>
       <c r="F8" t="n">
-        <v>4.857806165617678</v>
+        <v>5.298274523713542</v>
       </c>
       <c r="G8" t="n">
-        <v>6.975570646522372</v>
+        <v>7.565323716429947</v>
       </c>
       <c r="H8" t="n">
-        <v>5.392160421248039</v>
+        <v>6.057970347683959</v>
       </c>
       <c r="I8" t="n">
-        <v>6.463619757296273</v>
+        <v>7.153125284953477</v>
       </c>
       <c r="J8" t="n">
-        <v>6.143723408161623</v>
+        <v>6.748444773461862</v>
       </c>
       <c r="K8" t="n">
-        <v>6.539819554644599</v>
+        <v>7.239112216507758</v>
       </c>
       <c r="L8" t="n">
-        <v>6.782549535481549</v>
+        <v>6.703955575153008</v>
       </c>
       <c r="M8" t="n">
-        <v>6.747205390020293</v>
+        <v>7.464475175146144</v>
       </c>
       <c r="N8" t="n">
-        <v>4.443260248860146</v>
+        <v>14.00383852928701</v>
       </c>
       <c r="O8" t="n">
-        <v>4.657808186700635</v>
+        <v>5.185820845724457</v>
       </c>
       <c r="P8" t="n">
-        <v>4.882700707905796</v>
+        <v>5.304795305593922</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.361591870290917</v>
+        <v>4.670475150290764</v>
       </c>
       <c r="R8" t="n">
-        <v>6.167963955030631</v>
+        <v>6.82057761431375</v>
       </c>
       <c r="S8" t="n">
-        <v>6.398436259575694</v>
+        <v>7.051894344626636</v>
       </c>
       <c r="T8" t="n">
-        <v>5.721659299776568</v>
+        <v>6.363218264763418</v>
       </c>
       <c r="U8" t="n">
-        <v>5.15367508282028</v>
+        <v>5.432668721585808</v>
       </c>
       <c r="V8" t="n">
-        <v>5.20920705889205</v>
+        <v>5.773222033094308</v>
       </c>
       <c r="W8" t="n">
-        <v>5.412025592568765</v>
+        <v>6.141017760451474</v>
       </c>
       <c r="X8" t="n">
-        <v>4.663040420256273</v>
+        <v>4.866638595096475</v>
       </c>
       <c r="Y8" t="n">
-        <v>7.240315356841895</v>
+        <v>8.111850460820131</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.008236680227212</v>
+        <v>4.327580949092179</v>
       </c>
       <c r="AA8" t="n">
-        <v>5.59302181308349</v>
+        <v>6.209334929851618</v>
       </c>
       <c r="AB8" t="n">
-        <v>7.683036536198743</v>
+        <v>8.809674417793914</v>
       </c>
     </row>
     <row r="9">
@@ -8082,85 +8082,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>86.45463025096561</v>
+        <v>86.65696519725397</v>
       </c>
       <c r="C9" t="n">
-        <v>109.6994607822102</v>
+        <v>110.0815582769805</v>
       </c>
       <c r="D9" t="n">
-        <v>109.3023513818705</v>
+        <v>109.7360764657208</v>
       </c>
       <c r="E9" t="n">
-        <v>104.9078764683267</v>
+        <v>105.3189335665829</v>
       </c>
       <c r="F9" t="n">
-        <v>56.24641317920189</v>
+        <v>56.43706942443487</v>
       </c>
       <c r="G9" t="n">
-        <v>110.6615029028488</v>
+        <v>110.9293366470819</v>
       </c>
       <c r="H9" t="n">
-        <v>109.3943863080864</v>
+        <v>109.792765916528</v>
       </c>
       <c r="I9" t="n">
-        <v>110.4658456441343</v>
+        <v>110.8879208537972</v>
       </c>
       <c r="J9" t="n">
-        <v>110.145949295</v>
+        <v>110.483240342306</v>
       </c>
       <c r="K9" t="n">
-        <v>110.542045441483</v>
+        <v>110.9739077853517</v>
       </c>
       <c r="L9" t="n">
-        <v>110.7847754223198</v>
+        <v>110.4387511439971</v>
       </c>
       <c r="M9" t="n">
-        <v>110.749431276854</v>
+        <v>111.1992707439983</v>
       </c>
       <c r="N9" t="n">
-        <v>109.6278970946219</v>
+        <v>14.00383852928701</v>
       </c>
       <c r="O9" t="n">
-        <v>117.2661944145055</v>
+        <v>117.7038557162718</v>
       </c>
       <c r="P9" t="n">
-        <v>119.2559430572846</v>
+        <v>119.6077928597866</v>
       </c>
       <c r="Q9" t="n">
-        <v>110.1889487227903</v>
+        <v>110.5448239231391</v>
       </c>
       <c r="R9" t="n">
-        <v>110.1701898418688</v>
+        <v>110.5553731831577</v>
       </c>
       <c r="S9" t="n">
-        <v>110.400662146414</v>
+        <v>110.7866899134705</v>
       </c>
       <c r="T9" t="n">
-        <v>109.7238851866148</v>
+        <v>110.0980138336073</v>
       </c>
       <c r="U9" t="n">
-        <v>109.8906255852405</v>
+        <v>110.0526069309682</v>
       </c>
       <c r="V9" t="n">
-        <v>136.5996050945097</v>
+        <v>137.0946825765068</v>
       </c>
       <c r="W9" t="n">
-        <v>109.4139517021805</v>
+        <v>109.8754619111942</v>
       </c>
       <c r="X9" t="n">
-        <v>110.3505946121549</v>
+        <v>110.5771002982223</v>
       </c>
       <c r="Y9" t="n">
-        <v>109.7091700539401</v>
+        <v>110.089905822776</v>
       </c>
       <c r="Z9" t="n">
-        <v>95.46703485729647</v>
+        <v>95.73319827908726</v>
       </c>
       <c r="AA9" t="n">
-        <v>109.5952476999216</v>
+        <v>109.9441304986956</v>
       </c>
       <c r="AB9" t="n">
-        <v>110.0918939671259</v>
+        <v>110.676605973357</v>
       </c>
     </row>
   </sheetData>
@@ -8326,85 +8326,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.145556870461697</v>
+        <v>2.685194862619022</v>
       </c>
       <c r="C2" t="n">
-        <v>2.215258740931241</v>
+        <v>2.973924393219739</v>
       </c>
       <c r="D2" t="n">
-        <v>2.095803952567168</v>
+        <v>2.636765089679431</v>
       </c>
       <c r="E2" t="n">
-        <v>2.212558395812228</v>
+        <v>2.773495957116592</v>
       </c>
       <c r="F2" t="n">
-        <v>2.2354181560484</v>
+        <v>2.778166847320292</v>
       </c>
       <c r="G2" t="n">
-        <v>2.150365651755552</v>
+        <v>2.68685234503575</v>
       </c>
       <c r="H2" t="n">
-        <v>2.053232308369611</v>
+        <v>2.595027360888671</v>
       </c>
       <c r="I2" t="n">
-        <v>2.175449485456235</v>
+        <v>2.71892351697796</v>
       </c>
       <c r="J2" t="n">
-        <v>2.127742907537764</v>
+        <v>2.670821355591098</v>
       </c>
       <c r="K2" t="n">
-        <v>2.162182117857906</v>
+        <v>2.70580057655602</v>
       </c>
       <c r="L2" t="n">
-        <v>2.263869050954803</v>
+        <v>2.789994437735348</v>
       </c>
       <c r="M2" t="n">
-        <v>2.094898071527828</v>
+        <v>2.637816505163736</v>
       </c>
       <c r="N2" t="n">
-        <v>2.079856775799925</v>
+        <v>2.634621703553871</v>
       </c>
       <c r="O2" t="n">
-        <v>3.938264198637071</v>
+        <v>5.15874226782507</v>
       </c>
       <c r="P2" t="n">
-        <v>2.083515945303362</v>
+        <v>2.628421504678209</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.177509055757369</v>
+        <v>2.720820988170416</v>
       </c>
       <c r="R2" t="n">
-        <v>2.237901295242498</v>
+        <v>2.787486030753161</v>
       </c>
       <c r="S2" t="n">
-        <v>2.175244203758914</v>
+        <v>2.736733996487086</v>
       </c>
       <c r="T2" t="n">
-        <v>2.111217597612727</v>
+        <v>2.665857743226745</v>
       </c>
       <c r="U2" t="n">
-        <v>2.205178293438157</v>
+        <v>3.400841047859718</v>
       </c>
       <c r="V2" t="n">
-        <v>2.080324645696405</v>
+        <v>2.623853867053732</v>
       </c>
       <c r="W2" t="n">
-        <v>2.356815412335786</v>
+        <v>3.658524646153395</v>
       </c>
       <c r="X2" t="n">
-        <v>2.134558065557103</v>
+        <v>2.676574892565697</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.119984790819573</v>
+        <v>2.672291550386388</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.037998648872772</v>
+        <v>2.827436974069589</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.080714573923904</v>
+        <v>2.621688924945463</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.124052448799242</v>
+        <v>2.67436340320566</v>
       </c>
     </row>
     <row r="3">
@@ -8414,85 +8414,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.755071681046359</v>
+        <v>3.254195695907292</v>
       </c>
       <c r="C3" t="n">
-        <v>2.989717310730801</v>
+        <v>3.869696704321305</v>
       </c>
       <c r="D3" t="n">
-        <v>2.403606522982318</v>
+        <v>2.912326845850276</v>
       </c>
       <c r="E3" t="n">
-        <v>3.236218664837451</v>
+        <v>3.887380205209123</v>
       </c>
       <c r="F3" t="n">
-        <v>3.401081140091584</v>
+        <v>3.922581804792487</v>
       </c>
       <c r="G3" t="n">
-        <v>2.786898485323576</v>
+        <v>3.263707617281419</v>
       </c>
       <c r="H3" t="n">
-        <v>2.099916456871242</v>
+        <v>2.614746666657052</v>
       </c>
       <c r="I3" t="n">
-        <v>2.974648428690311</v>
+        <v>3.501403887374877</v>
       </c>
       <c r="J3" t="n">
-        <v>2.628551307849115</v>
+        <v>3.152279006735557</v>
       </c>
       <c r="K3" t="n">
-        <v>2.873017201128365</v>
+        <v>3.400526334341739</v>
       </c>
       <c r="L3" t="n">
-        <v>3.594182751912447</v>
+        <v>3.997440865483627</v>
       </c>
       <c r="M3" t="n">
-        <v>2.403394282595365</v>
+        <v>2.929582758333244</v>
       </c>
       <c r="N3" t="n">
-        <v>2.289647907177458</v>
+        <v>2.896990153699226</v>
       </c>
       <c r="O3" t="n">
-        <v>5.235727094960311</v>
+        <v>6.884815553395065</v>
       </c>
       <c r="P3" t="n">
-        <v>2.313892847499975</v>
+        <v>2.850426762809411</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.982591094708951</v>
+        <v>3.507892378943714</v>
       </c>
       <c r="R3" t="n">
-        <v>3.423255731531783</v>
+        <v>3.993856368947656</v>
       </c>
       <c r="S3" t="n">
-        <v>2.963743230419631</v>
+        <v>3.617779938952931</v>
       </c>
       <c r="T3" t="n">
-        <v>2.51427086552311</v>
+        <v>3.120845345282417</v>
       </c>
       <c r="U3" t="n">
-        <v>2.450148304480923</v>
+        <v>4.024058446305276</v>
       </c>
       <c r="V3" t="n">
-        <v>2.29086298320727</v>
+        <v>2.817577085881953</v>
       </c>
       <c r="W3" t="n">
-        <v>2.898284599320825</v>
+        <v>4.721466791025285</v>
       </c>
       <c r="X3" t="n">
-        <v>2.679802415808462</v>
+        <v>3.196021054869767</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.575485012824427</v>
+        <v>3.165083133559884</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.29536166464274</v>
+        <v>3.219534034171907</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.29545020132756</v>
+        <v>2.80420194228279</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.610496751205515</v>
+        <v>3.188004382260226</v>
       </c>
     </row>
     <row r="4">
@@ -8502,85 +8502,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.613015356333304</v>
+        <v>3.059547088843514</v>
       </c>
       <c r="C4" t="n">
-        <v>2.858556467878527</v>
+        <v>3.344941225863073</v>
       </c>
       <c r="D4" t="n">
-        <v>2.051033261241733</v>
+        <v>2.512510524694609</v>
       </c>
       <c r="E4" t="n">
-        <v>3.369828407391924</v>
+        <v>4.056948571703929</v>
       </c>
       <c r="F4" t="n">
-        <v>3.628039915268765</v>
+        <v>4.109708425270279</v>
       </c>
       <c r="G4" t="n">
-        <v>2.667332753196179</v>
+        <v>3.078269115219995</v>
       </c>
       <c r="H4" t="n">
-        <v>1.570166956106406</v>
+        <v>2.041063677699048</v>
       </c>
       <c r="I4" t="n">
-        <v>2.950666193978962</v>
+        <v>3.440527755775201</v>
       </c>
       <c r="J4" t="n">
-        <v>2.410659735415662</v>
+        <v>2.895861899351965</v>
       </c>
       <c r="K4" t="n">
-        <v>2.800805173665184</v>
+        <v>3.292298106858708</v>
       </c>
       <c r="L4" t="n">
-        <v>3.949405861294774</v>
+        <v>4.243306499968892</v>
       </c>
       <c r="M4" t="n">
-        <v>2.054213423974886</v>
+        <v>2.544342725765739</v>
       </c>
       <c r="N4" t="n">
-        <v>1.870902563591652</v>
+        <v>14.50806095784715</v>
       </c>
       <c r="O4" t="n">
-        <v>1.622969650482145</v>
+        <v>2.123760229046396</v>
       </c>
       <c r="P4" t="n">
-        <v>1.912234566434226</v>
+        <v>2.418265893867185</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.97392998797931</v>
+        <v>3.46196056577393</v>
       </c>
       <c r="R4" t="n">
-        <v>3.656088114766545</v>
+        <v>4.214972889180835</v>
       </c>
       <c r="S4" t="n">
-        <v>2.948347442773333</v>
+        <v>3.641705315056212</v>
       </c>
       <c r="T4" t="n">
-        <v>2.225137472658207</v>
+        <v>2.841125429793385</v>
       </c>
       <c r="U4" t="n">
-        <v>1.706800937932286</v>
+        <v>2.070185810497419</v>
       </c>
       <c r="V4" t="n">
-        <v>1.868873473597055</v>
+        <v>2.358435110135439</v>
       </c>
       <c r="W4" t="n">
-        <v>2.183340050406176</v>
+        <v>2.765785571086552</v>
       </c>
       <c r="X4" t="n">
-        <v>2.488778795235661</v>
+        <v>2.962180561709129</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.252784506815191</v>
+        <v>2.776131487990855</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.030879950637915</v>
+        <v>2.503842993717833</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.880591788008668</v>
+        <v>2.34221830864592</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.375963574989824</v>
+        <v>2.946151112141048</v>
       </c>
     </row>
     <row r="5">
@@ -8590,85 +8590,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>21.87643299718257</v>
+        <v>22.6745840519627</v>
       </c>
       <c r="C5" t="n">
-        <v>27.24840567027747</v>
+        <v>28.79747250653999</v>
       </c>
       <c r="D5" t="n">
-        <v>13.81484527614889</v>
+        <v>14.95659854188484</v>
       </c>
       <c r="E5" t="n">
-        <v>36.79263052289928</v>
+        <v>41.85709505105191</v>
       </c>
       <c r="F5" t="n">
-        <v>42.24632710287531</v>
+        <v>43.75684489003857</v>
       </c>
       <c r="G5" t="n">
-        <v>21.54482500258252</v>
+        <v>21.8046695956031</v>
       </c>
       <c r="H5" t="n">
-        <v>5.385530211677703</v>
+        <v>6.77586066319313</v>
       </c>
       <c r="I5" t="n">
-        <v>31.077747413499</v>
+        <v>32.77359667797558</v>
       </c>
       <c r="J5" t="n">
-        <v>18.63710224256294</v>
+        <v>20.14777453098147</v>
       </c>
       <c r="K5" t="n">
-        <v>24.83002205876187</v>
+        <v>26.41111987369269</v>
       </c>
       <c r="L5" t="n">
-        <v>42.77188683369204</v>
+        <v>41.16808887255243</v>
       </c>
       <c r="M5" t="n">
-        <v>13.33514088547387</v>
+        <v>14.95444018436257</v>
       </c>
       <c r="N5" t="n">
-        <v>8.334705156924818</v>
+        <v>14.50806095784715</v>
       </c>
       <c r="O5" t="n">
-        <v>5.580125970660745</v>
+        <v>7.213019328956163</v>
       </c>
       <c r="P5" t="n">
-        <v>10.31648740047312</v>
+        <v>12.07112091087398</v>
       </c>
       <c r="Q5" t="n">
-        <v>27.98777437705689</v>
+        <v>29.49718959351134</v>
       </c>
       <c r="R5" t="n">
-        <v>45.04969919765657</v>
+        <v>48.08697007599766</v>
       </c>
       <c r="S5" t="n">
-        <v>26.14464754422931</v>
+        <v>30.76693874323563</v>
       </c>
       <c r="T5" t="n">
-        <v>17.23432276122348</v>
+        <v>21.22617416031663</v>
       </c>
       <c r="U5" t="n">
-        <v>8.241985977487838</v>
+        <v>8.791831754516378</v>
       </c>
       <c r="V5" t="n">
-        <v>9.540301268169785</v>
+        <v>11.02069640650693</v>
       </c>
       <c r="W5" t="n">
-        <v>15.93081603732568</v>
+        <v>19.18713962009827</v>
       </c>
       <c r="X5" t="n">
-        <v>21.35284246720455</v>
+        <v>22.68674298699446</v>
       </c>
       <c r="Y5" t="n">
-        <v>18.28220418039652</v>
+        <v>21.64057702138255</v>
       </c>
       <c r="Z5" t="n">
-        <v>11.88410129009483</v>
+        <v>13.08190210273064</v>
       </c>
       <c r="AA5" t="n">
-        <v>10.56053746464138</v>
+        <v>11.67233931446258</v>
       </c>
       <c r="AB5" t="n">
-        <v>20.65034602398016</v>
+        <v>23.90812806423045</v>
       </c>
     </row>
     <row r="6">
@@ -8678,85 +8678,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.941295360716676</v>
+        <v>5.836235962907016</v>
       </c>
       <c r="C6" t="n">
-        <v>5.013910251786803</v>
+        <v>6.121630099926599</v>
       </c>
       <c r="D6" t="n">
-        <v>2.379313265625094</v>
+        <v>5.289199398758078</v>
       </c>
       <c r="E6" t="n">
-        <v>5.525182191300187</v>
+        <v>4.635290083945503</v>
       </c>
       <c r="F6" t="n">
-        <v>5.783393699177029</v>
+        <v>4.688049937511856</v>
       </c>
       <c r="G6" t="n">
-        <v>2.995612757579518</v>
+        <v>3.656610627461566</v>
       </c>
       <c r="H6" t="n">
-        <v>3.725520740014641</v>
+        <v>2.619405189940607</v>
       </c>
       <c r="I6" t="n">
-        <v>5.106019977887225</v>
+        <v>6.217216629838664</v>
       </c>
       <c r="J6" t="n">
-        <v>2.738939739798996</v>
+        <v>5.672550773415411</v>
       </c>
       <c r="K6" t="n">
-        <v>4.95615895757347</v>
+        <v>3.870639619100289</v>
       </c>
       <c r="L6" t="n">
-        <v>4.27768586567813</v>
+        <v>7.019995374032357</v>
       </c>
       <c r="M6" t="n">
-        <v>4.209567207883156</v>
+        <v>3.122684238007297</v>
       </c>
       <c r="N6" t="n">
-        <v>2.19183862888286</v>
+        <v>14.50806095784715</v>
       </c>
       <c r="O6" t="n">
-        <v>1.943905715773337</v>
+        <v>5.000802039504914</v>
       </c>
       <c r="P6" t="n">
-        <v>2.210295239187419</v>
+        <v>2.941963199864942</v>
       </c>
       <c r="Q6" t="n">
-        <v>5.129283771887569</v>
+        <v>4.040302078015501</v>
       </c>
       <c r="R6" t="n">
-        <v>5.811441898674802</v>
+        <v>6.991661763244302</v>
       </c>
       <c r="S6" t="n">
-        <v>3.276627447156685</v>
+        <v>4.220046827297772</v>
       </c>
       <c r="T6" t="n">
-        <v>2.553417477041562</v>
+        <v>3.419466942034975</v>
       </c>
       <c r="U6" t="n">
-        <v>2.106463388538037</v>
+        <v>4.984541437929066</v>
       </c>
       <c r="V6" t="n">
-        <v>4.024227257505285</v>
+        <v>2.936776622376999</v>
       </c>
       <c r="W6" t="n">
-        <v>2.525425665172198</v>
+        <v>3.371428733548853</v>
       </c>
       <c r="X6" t="n">
-        <v>2.817058799619022</v>
+        <v>5.738869435772628</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.661799379901654</v>
+        <v>3.508511567001395</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.359159955021268</v>
+        <v>5.280531867781315</v>
       </c>
       <c r="AA6" t="n">
-        <v>4.035945571916915</v>
+        <v>2.92055982088749</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.698911418885894</v>
+        <v>3.504107528407195</v>
       </c>
     </row>
     <row r="7">
@@ -8766,85 +8766,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.241150103558592</v>
+        <v>3.833707851286795</v>
       </c>
       <c r="C7" t="n">
-        <v>3.486691215103801</v>
+        <v>4.119101988306332</v>
       </c>
       <c r="D7" t="n">
-        <v>2.679168008466983</v>
+        <v>3.286671287137848</v>
       </c>
       <c r="E7" t="n">
-        <v>3.997963154617186</v>
+        <v>4.83110933414719</v>
       </c>
       <c r="F7" t="n">
-        <v>4.256174662494016</v>
+        <v>4.883869187713544</v>
       </c>
       <c r="G7" t="n">
-        <v>3.295467500421451</v>
+        <v>3.85242987766324</v>
       </c>
       <c r="H7" t="n">
-        <v>2.198301703331651</v>
+        <v>2.8152244401423</v>
       </c>
       <c r="I7" t="n">
-        <v>3.578800941204225</v>
+        <v>4.214688518218426</v>
       </c>
       <c r="J7" t="n">
-        <v>3.038794482640895</v>
+        <v>3.670022661795186</v>
       </c>
       <c r="K7" t="n">
-        <v>3.428939920890465</v>
+        <v>4.066458869301969</v>
       </c>
       <c r="L7" t="n">
-        <v>4.577540608520027</v>
+        <v>5.017467262412143</v>
       </c>
       <c r="M7" t="n">
-        <v>2.68234817120016</v>
+        <v>3.318503488208997</v>
       </c>
       <c r="N7" t="n">
-        <v>2.499037310816917</v>
+        <v>14.50806095784715</v>
       </c>
       <c r="O7" t="n">
-        <v>2.25107590053747</v>
+        <v>2.897923563691941</v>
       </c>
       <c r="P7" t="n">
-        <v>2.540340816489556</v>
+        <v>3.192429228512748</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.602064735204584</v>
+        <v>4.236121328217194</v>
       </c>
       <c r="R7" t="n">
-        <v>4.284222861991804</v>
+        <v>4.98913365162408</v>
       </c>
       <c r="S7" t="n">
-        <v>3.5764821899986</v>
+        <v>4.415866077499468</v>
       </c>
       <c r="T7" t="n">
-        <v>2.853272219883472</v>
+        <v>3.615286192236661</v>
       </c>
       <c r="U7" t="n">
-        <v>2.445834880693987</v>
+        <v>2.963081815067132</v>
       </c>
       <c r="V7" t="n">
-        <v>2.497008220822292</v>
+        <v>3.132595872578671</v>
       </c>
       <c r="W7" t="n">
-        <v>2.8114747976314</v>
+        <v>3.539946333529789</v>
       </c>
       <c r="X7" t="n">
-        <v>3.116913542460932</v>
+        <v>3.73634132415237</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.952301700262837</v>
+        <v>3.687959003802276</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.65901469786318</v>
+        <v>3.278003756161076</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.508726535233923</v>
+        <v>3.116379071089178</v>
       </c>
       <c r="AB7" t="n">
-        <v>3.004098322215112</v>
+        <v>3.720311874584288</v>
       </c>
     </row>
     <row r="8">
@@ -8854,85 +8854,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.803776919661798</v>
+        <v>5.687400303421683</v>
       </c>
       <c r="C8" t="n">
-        <v>6.506462951446399</v>
+        <v>7.92057024562828</v>
       </c>
       <c r="D8" t="n">
-        <v>5.698939744809599</v>
+        <v>7.088139544459861</v>
       </c>
       <c r="E8" t="n">
-        <v>6.241848204105718</v>
+        <v>7.595444432292273</v>
       </c>
       <c r="F8" t="n">
-        <v>6.045807627089775</v>
+        <v>7.041002345504705</v>
       </c>
       <c r="G8" t="n">
-        <v>6.617387728418331</v>
+        <v>8.057782136389026</v>
       </c>
       <c r="H8" t="n">
-        <v>5.218073439674268</v>
+        <v>6.61669269746426</v>
       </c>
       <c r="I8" t="n">
-        <v>6.598572677546819</v>
+        <v>8.016156775540427</v>
       </c>
       <c r="J8" t="n">
-        <v>6.058566218983506</v>
+        <v>7.471490919117094</v>
       </c>
       <c r="K8" t="n">
-        <v>6.448711657233051</v>
+        <v>7.867927126623946</v>
       </c>
       <c r="L8" t="n">
-        <v>7.597312344862647</v>
+        <v>8.818935519734142</v>
       </c>
       <c r="M8" t="n">
-        <v>5.70211990754795</v>
+        <v>7.119971745514952</v>
       </c>
       <c r="N8" t="n">
-        <v>4.389277958838361</v>
+        <v>14.50806095784715</v>
       </c>
       <c r="O8" t="n">
-        <v>4.451749996144369</v>
+        <v>5.604457608106015</v>
       </c>
       <c r="P8" t="n">
-        <v>4.664927158344224</v>
+        <v>5.797256241281114</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.878329316855568</v>
+        <v>5.707031380485108</v>
       </c>
       <c r="R8" t="n">
-        <v>7.303994598334409</v>
+        <v>8.790601908946075</v>
       </c>
       <c r="S8" t="n">
-        <v>6.5962539263412</v>
+        <v>8.217334334821476</v>
       </c>
       <c r="T8" t="n">
-        <v>5.873043956226077</v>
+        <v>7.416754449558685</v>
       </c>
       <c r="U8" t="n">
-        <v>4.745523475458703</v>
+        <v>5.818124756428226</v>
       </c>
       <c r="V8" t="n">
-        <v>5.152322576813066</v>
+        <v>6.385523244217323</v>
       </c>
       <c r="W8" t="n">
-        <v>5.83153290429963</v>
+        <v>7.341797378720821</v>
       </c>
       <c r="X8" t="n">
-        <v>4.526728351201133</v>
+        <v>5.38576889562603</v>
       </c>
       <c r="Y8" t="n">
-        <v>7.473306871945865</v>
+        <v>9.400954404670639</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.194574298983103</v>
+        <v>5.095515273286414</v>
       </c>
       <c r="AA8" t="n">
-        <v>5.528498271576547</v>
+        <v>6.917847328411169</v>
       </c>
       <c r="AB8" t="n">
-        <v>7.54597977189428</v>
+        <v>9.556394825166041</v>
       </c>
     </row>
     <row r="9">
@@ -8942,85 +8942,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>81.24666407663983</v>
+        <v>81.93133926328163</v>
       </c>
       <c r="C9" t="n">
-        <v>103.2671007544493</v>
+        <v>104.1501573447852</v>
       </c>
       <c r="D9" t="n">
-        <v>102.4595775478126</v>
+        <v>103.3177266436169</v>
       </c>
       <c r="E9" t="n">
-        <v>98.75281597405314</v>
+        <v>99.80002051783168</v>
       </c>
       <c r="F9" t="n">
-        <v>53.83950638024739</v>
+        <v>54.35239511976607</v>
       </c>
       <c r="G9" t="n">
-        <v>103.0758775059684</v>
+        <v>103.8834860255925</v>
       </c>
       <c r="H9" t="n">
-        <v>101.9787112426774</v>
+        <v>102.8462797966213</v>
       </c>
       <c r="I9" t="n">
-        <v>103.3592104805496</v>
+        <v>104.2457438746974</v>
       </c>
       <c r="J9" t="n">
-        <v>102.8192040219865</v>
+        <v>103.7010780182741</v>
       </c>
       <c r="K9" t="n">
-        <v>103.2093494602361</v>
+        <v>104.0975142257808</v>
       </c>
       <c r="L9" t="n">
-        <v>104.3579501478655</v>
+        <v>105.0485226188912</v>
       </c>
       <c r="M9" t="n">
-        <v>102.4627577105457</v>
+        <v>103.3495588446879</v>
       </c>
       <c r="N9" t="n">
-        <v>102.2794468501625</v>
+        <v>14.50806095784715</v>
       </c>
       <c r="O9" t="n">
-        <v>109.2476864366125</v>
+        <v>110.1976853775308</v>
       </c>
       <c r="P9" t="n">
-        <v>111.1063449611629</v>
+        <v>112.0730103741142</v>
       </c>
       <c r="Q9" t="n">
-        <v>103.3824747407515</v>
+        <v>104.2671774761465</v>
       </c>
       <c r="R9" t="n">
-        <v>104.0646324013373</v>
+        <v>105.0201890081031</v>
       </c>
       <c r="S9" t="n">
-        <v>103.3568917293441</v>
+        <v>104.4469214339784</v>
       </c>
       <c r="T9" t="n">
-        <v>102.633681759229</v>
+        <v>103.6463415487157</v>
       </c>
       <c r="U9" t="n">
-        <v>102.1867276707255</v>
+        <v>103.0130686827877</v>
       </c>
       <c r="V9" t="n">
-        <v>127.4051857208768</v>
+        <v>128.4743579279231</v>
       </c>
       <c r="W9" t="n">
-        <v>102.591884336977</v>
+        <v>103.5710016900087</v>
       </c>
       <c r="X9" t="n">
-        <v>102.8973230818065</v>
+        <v>103.7673966806314</v>
       </c>
       <c r="Y9" t="n">
-        <v>102.7327112396084</v>
+        <v>103.7190143602812</v>
       </c>
       <c r="Z9" t="n">
-        <v>89.3110986951356</v>
+        <v>90.08515518454672</v>
       </c>
       <c r="AA9" t="n">
-        <v>102.2891360745795</v>
+        <v>103.1474344275681</v>
       </c>
       <c r="AB9" t="n">
-        <v>102.7845078615607</v>
+        <v>103.7513672310632</v>
       </c>
     </row>
   </sheetData>

--- a/Results/Phase 2/Ammonia/ammonia land use results.xlsx
+++ b/Results/Phase 2/Ammonia/ammonia land use results.xlsx
@@ -798,7 +798,7 @@
         <v>2.477188918774697</v>
       </c>
       <c r="N4" t="n">
-        <v>10.07018886758688</v>
+        <v>1.514487843549658</v>
       </c>
       <c r="O4" t="n">
         <v>1.69845312362696</v>
@@ -974,7 +974,7 @@
         <v>4.849582685667438</v>
       </c>
       <c r="N6" t="n">
-        <v>10.07018886758688</v>
+        <v>1.873444361252026</v>
       </c>
       <c r="O6" t="n">
         <v>2.057410088281883</v>
@@ -1062,7 +1062,7 @@
         <v>3.124966748692664</v>
       </c>
       <c r="N7" t="n">
-        <v>10.07018886758688</v>
+        <v>2.162265673467694</v>
       </c>
       <c r="O7" t="n">
         <v>2.346230359438765</v>
@@ -1150,7 +1150,7 @@
         <v>6.455044242322407</v>
       </c>
       <c r="N8" t="n">
-        <v>10.07018886758688</v>
+        <v>4.267049944300641</v>
       </c>
       <c r="O8" t="n">
         <v>4.787736440721995</v>
@@ -1238,7 +1238,7 @@
         <v>117.7112866369198</v>
       </c>
       <c r="N9" t="n">
-        <v>10.07018886758688</v>
+        <v>116.7485855616948</v>
       </c>
       <c r="O9" t="n">
         <v>125.212259921393</v>
@@ -1658,7 +1658,7 @@
         <v>2.552689142395347</v>
       </c>
       <c r="N4" t="n">
-        <v>15.20076458153757</v>
+        <v>2.695328219246667</v>
       </c>
       <c r="O4" t="n">
         <v>2.371048131003984</v>
@@ -1670,7 +1670,7 @@
         <v>3.353662283464772</v>
       </c>
       <c r="R4" t="n">
-        <v>5.714756188164024</v>
+        <v>5.714756188164023</v>
       </c>
       <c r="S4" t="n">
         <v>3.592048212792113</v>
@@ -1834,7 +1834,7 @@
         <v>3.245357221276602</v>
       </c>
       <c r="N6" t="n">
-        <v>15.20076458153757</v>
+        <v>3.399629820812907</v>
       </c>
       <c r="O6" t="n">
         <v>5.443729009579789</v>
@@ -1873,7 +1873,7 @@
         <v>3.556316522403186</v>
       </c>
       <c r="AA6" t="n">
-        <v>5.658476994695574</v>
+        <v>5.658476994695575</v>
       </c>
       <c r="AB6" t="n">
         <v>3.512279893757289</v>
@@ -1922,7 +1922,7 @@
         <v>3.366923308451403</v>
       </c>
       <c r="N7" t="n">
-        <v>15.20076458153757</v>
+        <v>3.509562385302631</v>
       </c>
       <c r="O7" t="n">
         <v>3.185281466702098</v>
@@ -2010,7 +2010,7 @@
         <v>7.325308174659528</v>
       </c>
       <c r="N8" t="n">
-        <v>15.20076458153757</v>
+        <v>5.874303462769506</v>
       </c>
       <c r="O8" t="n">
         <v>5.987970521253543</v>
@@ -2098,7 +2098,7 @@
         <v>103.1984129746447</v>
       </c>
       <c r="N9" t="n">
-        <v>15.20076458153757</v>
+        <v>103.3410520514962</v>
       </c>
       <c r="O9" t="n">
         <v>110.2798621359907</v>
@@ -2518,7 +2518,7 @@
         <v>2.594415229968675</v>
       </c>
       <c r="N4" t="n">
-        <v>9.771603527381753</v>
+        <v>1.748725149657322</v>
       </c>
       <c r="O4" t="n">
         <v>1.896475583259466</v>
@@ -2694,7 +2694,7 @@
         <v>5.009732687767665</v>
       </c>
       <c r="N6" t="n">
-        <v>9.771603527381753</v>
+        <v>2.156337256721684</v>
       </c>
       <c r="O6" t="n">
         <v>2.284078706151775</v>
@@ -2782,7 +2782,7 @@
         <v>3.29195216760647</v>
       </c>
       <c r="N7" t="n">
-        <v>9.771603527381753</v>
+        <v>2.446262087295117</v>
       </c>
       <c r="O7" t="n">
         <v>2.594026344927076</v>
@@ -2870,7 +2870,7 @@
         <v>6.754917240339745</v>
       </c>
       <c r="N8" t="n">
-        <v>9.771603527381753</v>
+        <v>4.590425990302834</v>
       </c>
       <c r="O8" t="n">
         <v>5.100594435062149</v>
@@ -2958,7 +2958,7 @@
         <v>110.5495931556417</v>
       </c>
       <c r="N9" t="n">
-        <v>9.771603527381753</v>
+        <v>109.7039030753304</v>
       </c>
       <c r="O9" t="n">
         <v>117.6179522346455</v>
@@ -3166,85 +3166,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.453419964662399</v>
+        <v>2.453419964662416</v>
       </c>
       <c r="C2" t="n">
-        <v>2.626995143814099</v>
+        <v>2.626995143814092</v>
       </c>
       <c r="D2" t="n">
-        <v>2.473989551268938</v>
+        <v>2.473989551268937</v>
       </c>
       <c r="E2" t="n">
-        <v>2.438692898553359</v>
+        <v>2.438692898553376</v>
       </c>
       <c r="F2" t="n">
-        <v>2.448843060475876</v>
+        <v>2.448843060475884</v>
       </c>
       <c r="G2" t="n">
-        <v>2.548900167041879</v>
+        <v>2.548900167041889</v>
       </c>
       <c r="H2" t="n">
-        <v>2.432364444275142</v>
+        <v>2.432364444275146</v>
       </c>
       <c r="I2" t="n">
-        <v>2.574970772112164</v>
+        <v>2.574970772112184</v>
       </c>
       <c r="J2" t="n">
         <v>2.503404569586984</v>
       </c>
       <c r="K2" t="n">
-        <v>2.487437928382289</v>
+        <v>2.487437928382304</v>
       </c>
       <c r="L2" t="n">
-        <v>2.438968534113629</v>
+        <v>2.438968534113647</v>
       </c>
       <c r="M2" t="n">
-        <v>2.532400950915512</v>
+        <v>2.532400950915515</v>
       </c>
       <c r="N2" t="n">
-        <v>2.466242149191703</v>
+        <v>2.466242149191717</v>
       </c>
       <c r="O2" t="n">
-        <v>4.782909179304438</v>
+        <v>4.782909179304437</v>
       </c>
       <c r="P2" t="n">
-        <v>2.483998430156811</v>
+        <v>2.483998430156825</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.531301236892554</v>
+        <v>2.531301236892553</v>
       </c>
       <c r="R2" t="n">
-        <v>2.440044987221151</v>
+        <v>2.440044987221174</v>
       </c>
       <c r="S2" t="n">
-        <v>2.489698541232653</v>
+        <v>2.489698541232685</v>
       </c>
       <c r="T2" t="n">
-        <v>2.450842071293221</v>
+        <v>2.450842071293208</v>
       </c>
       <c r="U2" t="n">
-        <v>3.101879905228493</v>
+        <v>3.101879905228496</v>
       </c>
       <c r="V2" t="n">
-        <v>2.472144400491752</v>
+        <v>2.472144400491767</v>
       </c>
       <c r="W2" t="n">
-        <v>3.287952029158691</v>
+        <v>3.287952029158704</v>
       </c>
       <c r="X2" t="n">
-        <v>2.470711563775543</v>
+        <v>2.470711563775557</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.507428412867814</v>
+        <v>2.507428412867821</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.539968668909796</v>
+        <v>2.539968668909805</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.461506003044012</v>
+        <v>2.461506003044015</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.533299561763502</v>
+        <v>2.533299561763501</v>
       </c>
     </row>
     <row r="3">
@@ -3254,85 +3254,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.565006189611183</v>
+        <v>2.565006189611169</v>
       </c>
       <c r="C3" t="n">
-        <v>2.876435259531383</v>
+        <v>2.876435259531389</v>
       </c>
       <c r="D3" t="n">
-        <v>2.713509697857538</v>
+        <v>2.713509697857539</v>
       </c>
       <c r="E3" t="n">
-        <v>2.46088952666591</v>
+        <v>2.460889526665913</v>
       </c>
       <c r="F3" t="n">
-        <v>2.533666230928137</v>
+        <v>2.53366623092814</v>
       </c>
       <c r="G3" t="n">
-        <v>3.24381828237401</v>
+        <v>3.243818282374086</v>
       </c>
       <c r="H3" t="n">
-        <v>2.415933460000839</v>
+        <v>2.415933460000844</v>
       </c>
       <c r="I3" t="n">
-        <v>3.437067559473979</v>
+        <v>3.437067559473986</v>
       </c>
       <c r="J3" t="n">
-        <v>2.921406060571584</v>
+        <v>2.921406060571524</v>
       </c>
       <c r="K3" t="n">
-        <v>2.807322418228539</v>
+        <v>2.807322418228535</v>
       </c>
       <c r="L3" t="n">
-        <v>2.462535468701746</v>
+        <v>2.462535468701751</v>
       </c>
       <c r="M3" t="n">
-        <v>3.136205710164297</v>
+        <v>3.136205710164303</v>
       </c>
       <c r="N3" t="n">
-        <v>2.657687199998338</v>
+        <v>2.657687199998333</v>
       </c>
       <c r="O3" t="n">
         <v>6.509654523850386</v>
       </c>
       <c r="P3" t="n">
-        <v>2.782298083281689</v>
+        <v>2.782298083281682</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.121869630901979</v>
+        <v>3.121869630901965</v>
       </c>
       <c r="R3" t="n">
-        <v>2.470874883229779</v>
+        <v>2.470874883229782</v>
       </c>
       <c r="S3" t="n">
-        <v>2.823151563675808</v>
+        <v>2.823151563675806</v>
       </c>
       <c r="T3" t="n">
-        <v>2.547992024665126</v>
+        <v>2.547992024665115</v>
       </c>
       <c r="U3" t="n">
-        <v>3.690534903240696</v>
+        <v>3.690534903240704</v>
       </c>
       <c r="V3" t="n">
-        <v>2.697488746482846</v>
+        <v>2.697488746482838</v>
       </c>
       <c r="W3" t="n">
-        <v>4.036602007655721</v>
+        <v>4.036602007655728</v>
       </c>
       <c r="X3" t="n">
-        <v>2.689790128955986</v>
+        <v>2.689790128955983</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.951166947576497</v>
+        <v>2.951166947576512</v>
       </c>
       <c r="Z3" t="n">
         <v>2.854215898722316</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.623548638416302</v>
+        <v>2.623548638416294</v>
       </c>
       <c r="AB3" t="n">
-        <v>3.14066368690597</v>
+        <v>3.140663686905979</v>
       </c>
     </row>
     <row r="4">
@@ -3342,85 +3342,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.00271771784218</v>
+        <v>2.002717717841945</v>
       </c>
       <c r="C4" t="n">
-        <v>2.055219505038207</v>
+        <v>2.055219505038089</v>
       </c>
       <c r="D4" t="n">
-        <v>2.235060661040157</v>
+        <v>2.23506066104001</v>
       </c>
       <c r="E4" t="n">
-        <v>1.836368731355301</v>
+        <v>1.836368731355141</v>
       </c>
       <c r="F4" t="n">
-        <v>1.951019479575386</v>
+        <v>1.951019479575219</v>
       </c>
       <c r="G4" t="n">
-        <v>3.081210526781254</v>
+        <v>3.081210526781109</v>
       </c>
       <c r="H4" t="n">
-        <v>1.764885929049999</v>
+        <v>1.764885929049863</v>
       </c>
       <c r="I4" t="n">
-        <v>3.375690004121171</v>
+        <v>3.375690004120959</v>
       </c>
       <c r="J4" t="n">
-        <v>2.566269005068594</v>
+        <v>2.566269005068436</v>
       </c>
       <c r="K4" t="n">
-        <v>2.386966267094611</v>
+        <v>2.386966267094508</v>
       </c>
       <c r="L4" t="n">
-        <v>1.839482161807239</v>
+        <v>1.839482161807046</v>
       </c>
       <c r="M4" t="n">
-        <v>2.902021137689739</v>
+        <v>2.902021137689511</v>
       </c>
       <c r="N4" t="n">
-        <v>10.87359888260983</v>
+        <v>2.147550190596721</v>
       </c>
       <c r="O4" t="n">
-        <v>2.209824810043359</v>
+        <v>2.209824810043137</v>
       </c>
       <c r="P4" t="n">
-        <v>2.348115552390574</v>
+        <v>2.34811555239045</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.882422514836837</v>
+        <v>2.882422514836704</v>
       </c>
       <c r="R4" t="n">
-        <v>1.851641194849599</v>
+        <v>1.851641194849468</v>
       </c>
       <c r="S4" t="n">
-        <v>2.412500929172896</v>
+        <v>2.412500929172737</v>
       </c>
       <c r="T4" t="n">
-        <v>1.973599226347299</v>
+        <v>1.97359922634713</v>
       </c>
       <c r="U4" t="n">
-        <v>1.989169598146435</v>
+        <v>1.989169598146258</v>
       </c>
       <c r="V4" t="n">
-        <v>2.207766217166752</v>
+        <v>2.207766217166742</v>
       </c>
       <c r="W4" t="n">
-        <v>2.194671579938396</v>
+        <v>2.194671579938301</v>
       </c>
       <c r="X4" t="n">
-        <v>2.198034284353628</v>
+        <v>2.198034284353468</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.486122450575887</v>
+        <v>2.48612245057579</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.307222394845276</v>
+        <v>2.307222394845091</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.094053241123599</v>
+        <v>2.094053241123401</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.905159014872803</v>
+        <v>2.905159014872639</v>
       </c>
     </row>
     <row r="5">
@@ -3430,85 +3430,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7.706483068032184</v>
+        <v>7.706483068032112</v>
       </c>
       <c r="C5" t="n">
-        <v>9.043075537234849</v>
+        <v>9.043075537234602</v>
       </c>
       <c r="D5" t="n">
-        <v>12.69545654857541</v>
+        <v>12.69545654857521</v>
       </c>
       <c r="E5" t="n">
-        <v>5.277961013070909</v>
+        <v>5.277961013070643</v>
       </c>
       <c r="F5" t="n">
-        <v>7.479091012128158</v>
+        <v>7.479091012128017</v>
       </c>
       <c r="G5" t="n">
-        <v>25.41595261665271</v>
+        <v>25.41595261665468</v>
       </c>
       <c r="H5" t="n">
-        <v>4.122718164939124</v>
+        <v>4.122718164939069</v>
       </c>
       <c r="I5" t="n">
-        <v>34.34623351929267</v>
+        <v>34.34623351929242</v>
       </c>
       <c r="J5" t="n">
-        <v>17.51368256469364</v>
+        <v>17.51368256469455</v>
       </c>
       <c r="K5" t="n">
-        <v>14.25811945266239</v>
+        <v>14.25811945266216</v>
       </c>
       <c r="L5" t="n">
-        <v>5.166530545066858</v>
+        <v>5.166530545066538</v>
       </c>
       <c r="M5" t="n">
-        <v>25.48239985553506</v>
+        <v>25.48239985553471</v>
       </c>
       <c r="N5" t="n">
-        <v>10.87359888260983</v>
+        <v>10.87359888260971</v>
       </c>
       <c r="O5" t="n">
-        <v>10.75025785744794</v>
+        <v>10.75025785744783</v>
       </c>
       <c r="P5" t="n">
-        <v>13.32406471668429</v>
+        <v>13.32406471668432</v>
       </c>
       <c r="Q5" t="n">
-        <v>23.79457937315809</v>
+        <v>23.79457937315783</v>
       </c>
       <c r="R5" t="n">
-        <v>5.721909046613063</v>
+        <v>5.721909046612894</v>
       </c>
       <c r="S5" t="n">
-        <v>14.55170368717905</v>
+        <v>14.55170368717884</v>
       </c>
       <c r="T5" t="n">
-        <v>7.908898803432825</v>
+        <v>7.908898803432757</v>
       </c>
       <c r="U5" t="n">
-        <v>9.828097057081775</v>
+        <v>9.828097057082172</v>
       </c>
       <c r="V5" t="n">
-        <v>10.84239558637378</v>
+        <v>10.84239558637383</v>
       </c>
       <c r="W5" t="n">
-        <v>11.5228861062119</v>
+        <v>11.52288610621166</v>
       </c>
       <c r="X5" t="n">
-        <v>11.87246735999257</v>
+        <v>11.87246735999241</v>
       </c>
       <c r="Y5" t="n">
-        <v>18.85886715687191</v>
+        <v>18.85886715687176</v>
       </c>
       <c r="Z5" t="n">
-        <v>12.28524565611864</v>
+        <v>12.28524565611837</v>
       </c>
       <c r="AA5" t="n">
-        <v>9.75306014383241</v>
+        <v>9.753060143832187</v>
       </c>
       <c r="AB5" t="n">
-        <v>26.49894311323549</v>
+        <v>26.49894311323532</v>
       </c>
     </row>
     <row r="6">
@@ -3518,85 +3518,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.562384751932971</v>
+        <v>4.562384751932892</v>
       </c>
       <c r="C6" t="n">
-        <v>2.518027408524032</v>
+        <v>2.518027408523976</v>
       </c>
       <c r="D6" t="n">
-        <v>4.794727695130942</v>
+        <v>4.794727695130802</v>
       </c>
       <c r="E6" t="n">
-        <v>4.396035765446253</v>
+        <v>4.396035765446141</v>
       </c>
       <c r="F6" t="n">
-        <v>2.413827383061278</v>
+        <v>2.413827383061142</v>
       </c>
       <c r="G6" t="n">
-        <v>3.544018430267029</v>
+        <v>3.544018430267128</v>
       </c>
       <c r="H6" t="n">
-        <v>2.22769383253593</v>
+        <v>2.227693832535817</v>
       </c>
       <c r="I6" t="n">
-        <v>3.838497907607106</v>
+        <v>3.838497907606975</v>
       </c>
       <c r="J6" t="n">
-        <v>5.12593603915944</v>
+        <v>5.125936039159252</v>
       </c>
       <c r="K6" t="n">
-        <v>4.946633301185539</v>
+        <v>4.946633301185297</v>
       </c>
       <c r="L6" t="n">
-        <v>4.399149195898109</v>
+        <v>4.399149195897949</v>
       </c>
       <c r="M6" t="n">
-        <v>3.36482904117566</v>
+        <v>3.36482904117555</v>
       </c>
       <c r="N6" t="n">
-        <v>10.87359888260983</v>
+        <v>2.627138950205301</v>
       </c>
       <c r="O6" t="n">
-        <v>4.879678268324521</v>
+        <v>4.87967826832426</v>
       </c>
       <c r="P6" t="n">
-        <v>5.025063179480593</v>
+        <v>5.025063179480311</v>
       </c>
       <c r="Q6" t="n">
-        <v>5.442089548927699</v>
+        <v>5.442089548927489</v>
       </c>
       <c r="R6" t="n">
-        <v>2.314449098335527</v>
+        <v>2.314449098335393</v>
       </c>
       <c r="S6" t="n">
-        <v>4.972167963263757</v>
+        <v>4.97216796326359</v>
       </c>
       <c r="T6" t="n">
-        <v>2.436407129833306</v>
+        <v>2.436407129833205</v>
       </c>
       <c r="U6" t="n">
-        <v>2.578623036492282</v>
+        <v>2.578623036492193</v>
       </c>
       <c r="V6" t="n">
-        <v>4.767433251257635</v>
+        <v>4.767433251257589</v>
       </c>
       <c r="W6" t="n">
-        <v>4.862445042456422</v>
+        <v>4.862445042456263</v>
       </c>
       <c r="X6" t="n">
-        <v>2.66084218783951</v>
+        <v>2.660842187839483</v>
       </c>
       <c r="Y6" t="n">
-        <v>3.097890376561263</v>
+        <v>3.097890376561188</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.866889428936173</v>
+        <v>4.866889428936062</v>
       </c>
       <c r="AA6" t="n">
-        <v>4.653720275214501</v>
+        <v>4.653720275214336</v>
       </c>
       <c r="AB6" t="n">
-        <v>3.362118058581214</v>
+        <v>3.362118058580961</v>
       </c>
     </row>
     <row r="7">
@@ -3606,85 +3606,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.736131633239183</v>
+        <v>2.736131633239067</v>
       </c>
       <c r="C7" t="n">
-        <v>2.788633420435234</v>
+        <v>2.788633420435167</v>
       </c>
       <c r="D7" t="n">
-        <v>2.968474576437267</v>
+        <v>2.968474576437154</v>
       </c>
       <c r="E7" t="n">
-        <v>2.569782646752437</v>
+        <v>2.569782646752242</v>
       </c>
       <c r="F7" t="n">
-        <v>2.684433394972468</v>
+        <v>2.684433394972328</v>
       </c>
       <c r="G7" t="n">
-        <v>3.814624442178578</v>
+        <v>3.81462444217827</v>
       </c>
       <c r="H7" t="n">
-        <v>2.498299844447089</v>
+        <v>2.49829984444702</v>
       </c>
       <c r="I7" t="n">
-        <v>4.109103919518327</v>
+        <v>4.109103919518134</v>
       </c>
       <c r="J7" t="n">
-        <v>3.299682920465773</v>
+        <v>3.299682920465535</v>
       </c>
       <c r="K7" t="n">
-        <v>3.120380182491729</v>
+        <v>3.120380182491689</v>
       </c>
       <c r="L7" t="n">
-        <v>2.57289607720437</v>
+        <v>2.572896077204187</v>
       </c>
       <c r="M7" t="n">
-        <v>3.635435053086844</v>
+        <v>3.635435053086656</v>
       </c>
       <c r="N7" t="n">
-        <v>10.87359888260983</v>
+        <v>2.880964105993679</v>
       </c>
       <c r="O7" t="n">
-        <v>2.94324001894797</v>
+        <v>2.943240018947852</v>
       </c>
       <c r="P7" t="n">
-        <v>3.081530761295268</v>
+        <v>3.081530761295124</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.615836430233928</v>
+        <v>3.615836430233693</v>
       </c>
       <c r="R7" t="n">
-        <v>2.585055110246672</v>
+        <v>2.58505511024659</v>
       </c>
       <c r="S7" t="n">
-        <v>3.145914844570033</v>
+        <v>3.145914844569887</v>
       </c>
       <c r="T7" t="n">
-        <v>2.707013141744458</v>
+        <v>2.707013141744278</v>
       </c>
       <c r="U7" t="n">
-        <v>2.832425433680407</v>
+        <v>2.8324254336803</v>
       </c>
       <c r="V7" t="n">
-        <v>2.941180132563891</v>
+        <v>2.941180132563868</v>
       </c>
       <c r="W7" t="n">
-        <v>2.928085495335518</v>
+        <v>2.92808549533541</v>
       </c>
       <c r="X7" t="n">
-        <v>2.931448199750736</v>
+        <v>2.931448199750485</v>
       </c>
       <c r="Y7" t="n">
-        <v>3.346181900832875</v>
+        <v>3.346181900832761</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.040636310242435</v>
+        <v>3.040636310242203</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.827467156520718</v>
+        <v>2.827467156520532</v>
       </c>
       <c r="AB7" t="n">
-        <v>3.638572930269835</v>
+        <v>3.638572930269627</v>
       </c>
     </row>
     <row r="8">
@@ -3694,85 +3694,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.494327761473631</v>
+        <v>4.494327761473546</v>
       </c>
       <c r="C8" t="n">
-        <v>6.360745990543156</v>
+        <v>6.360745990543149</v>
       </c>
       <c r="D8" t="n">
-        <v>6.540587146545196</v>
+        <v>6.540587146545024</v>
       </c>
       <c r="E8" t="n">
-        <v>5.176038219812154</v>
+        <v>5.176038219812226</v>
       </c>
       <c r="F8" t="n">
-        <v>4.725216504630237</v>
+        <v>4.7252165046302</v>
       </c>
       <c r="G8" t="n">
-        <v>7.762864402777922</v>
+        <v>7.762864402777572</v>
       </c>
       <c r="H8" t="n">
-        <v>6.070412414554817</v>
+        <v>6.070412414554852</v>
       </c>
       <c r="I8" t="n">
-        <v>7.681216489626252</v>
+        <v>7.681216489626096</v>
       </c>
       <c r="J8" t="n">
-        <v>6.871795490573266</v>
+        <v>6.871795490573534</v>
       </c>
       <c r="K8" t="n">
-        <v>6.692492752599707</v>
+        <v>6.692492752599616</v>
       </c>
       <c r="L8" t="n">
-        <v>6.145008647312165</v>
+        <v>6.145008647312224</v>
       </c>
       <c r="M8" t="n">
-        <v>7.207547623172118</v>
+        <v>7.207547623172009</v>
       </c>
       <c r="N8" t="n">
-        <v>10.87359888260983</v>
+        <v>5.046987970872051</v>
       </c>
       <c r="O8" t="n">
-        <v>5.495667972870701</v>
+        <v>5.495667972870578</v>
       </c>
       <c r="P8" t="n">
-        <v>5.539241419381853</v>
+        <v>5.539241419381748</v>
       </c>
       <c r="Q8" t="n">
-        <v>5.017556578378416</v>
+        <v>5.017556578378327</v>
       </c>
       <c r="R8" t="n">
-        <v>6.157167680354402</v>
+        <v>6.157167680354473</v>
       </c>
       <c r="S8" t="n">
-        <v>6.718027414677914</v>
+        <v>6.718027414677808</v>
       </c>
       <c r="T8" t="n">
-        <v>6.27912571185254</v>
+        <v>6.279125711852282</v>
       </c>
       <c r="U8" t="n">
-        <v>5.52296981911639</v>
+        <v>5.522969819116281</v>
       </c>
       <c r="V8" t="n">
-        <v>6.003157566238403</v>
+        <v>6.003157566238492</v>
       </c>
       <c r="W8" t="n">
-        <v>6.500554547202908</v>
+        <v>6.50055454720287</v>
       </c>
       <c r="X8" t="n">
-        <v>4.499417391141654</v>
+        <v>4.499417391141456</v>
       </c>
       <c r="Y8" t="n">
-        <v>8.699551066760723</v>
+        <v>8.699551066760513</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.765138009755434</v>
+        <v>4.765138009755445</v>
       </c>
       <c r="AA8" t="n">
-        <v>6.399579726628415</v>
+        <v>6.399579726628602</v>
       </c>
       <c r="AB8" t="n">
-        <v>9.105472896561508</v>
+        <v>9.105472896561462</v>
       </c>
     </row>
     <row r="9">
@@ -3782,85 +3782,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>80.77810665781855</v>
+        <v>80.77810665781844</v>
       </c>
       <c r="C9" t="n">
-        <v>102.7167878466588</v>
+        <v>102.7167878466587</v>
       </c>
       <c r="D9" t="n">
-        <v>102.8966290026607</v>
+        <v>102.8966290026606</v>
       </c>
       <c r="E9" t="n">
-        <v>97.44669652919009</v>
+        <v>97.44669652919004</v>
       </c>
       <c r="F9" t="n">
-        <v>52.15897033351156</v>
+        <v>52.15897033351153</v>
       </c>
       <c r="G9" t="n">
-        <v>103.742779375439</v>
+        <v>103.7427793754388</v>
       </c>
       <c r="H9" t="n">
-        <v>102.4264542706705</v>
+        <v>102.4264542706703</v>
       </c>
       <c r="I9" t="n">
         <v>104.0372583457416</v>
       </c>
       <c r="J9" t="n">
-        <v>103.2278373466891</v>
+        <v>103.2278373466889</v>
       </c>
       <c r="K9" t="n">
-        <v>103.0485346087152</v>
+        <v>103.0485346087151</v>
       </c>
       <c r="L9" t="n">
-        <v>102.5010505034278</v>
+        <v>102.5010505034277</v>
       </c>
       <c r="M9" t="n">
-        <v>103.5635894793103</v>
+        <v>103.5635894793102</v>
       </c>
       <c r="N9" t="n">
-        <v>10.87359888260983</v>
+        <v>102.8091185322172</v>
       </c>
       <c r="O9" t="n">
-        <v>110.1244450229228</v>
+        <v>110.124445022923</v>
       </c>
       <c r="P9" t="n">
-        <v>111.8401499955883</v>
+        <v>111.8401499955882</v>
       </c>
       <c r="Q9" t="n">
-        <v>103.5439913634943</v>
+        <v>103.5439913634942</v>
       </c>
       <c r="R9" t="n">
         <v>102.5132095364701</v>
       </c>
       <c r="S9" t="n">
-        <v>103.0740692707935</v>
+        <v>103.0740692707934</v>
       </c>
       <c r="T9" t="n">
         <v>102.6351675679676</v>
       </c>
       <c r="U9" t="n">
-        <v>102.777383474627</v>
+        <v>102.7773834746269</v>
       </c>
       <c r="V9" t="n">
-        <v>128.1255217375783</v>
+        <v>128.1255217375784</v>
       </c>
       <c r="W9" t="n">
-        <v>102.856239921559</v>
+        <v>102.8562399215588</v>
       </c>
       <c r="X9" t="n">
-        <v>102.859602625974</v>
+        <v>102.8596026259739</v>
       </c>
       <c r="Y9" t="n">
-        <v>103.2743363270564</v>
+        <v>103.2743363270562</v>
       </c>
       <c r="Z9" t="n">
-        <v>89.77337095361889</v>
+        <v>89.77337095361878</v>
       </c>
       <c r="AA9" t="n">
-        <v>102.7556215827442</v>
+        <v>102.7556215827441</v>
       </c>
       <c r="AB9" t="n">
-        <v>103.5667273564933</v>
+        <v>103.5667273564931</v>
       </c>
     </row>
   </sheetData>
@@ -4026,85 +4026,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.62422502594185</v>
+        <v>2.6242250259418</v>
       </c>
       <c r="C2" t="n">
-        <v>2.860397404555671</v>
+        <v>2.860397404555679</v>
       </c>
       <c r="D2" t="n">
-        <v>2.634502045743093</v>
+        <v>2.63450204574311</v>
       </c>
       <c r="E2" t="n">
-        <v>2.588068434377308</v>
+        <v>2.588068434377272</v>
       </c>
       <c r="F2" t="n">
-        <v>2.639318086138652</v>
+        <v>2.639318086138606</v>
       </c>
       <c r="G2" t="n">
-        <v>2.711580456204373</v>
+        <v>2.711580456204302</v>
       </c>
       <c r="H2" t="n">
-        <v>2.603549694586645</v>
+        <v>2.603549694586624</v>
       </c>
       <c r="I2" t="n">
-        <v>2.696665086155855</v>
+        <v>2.696665086155826</v>
       </c>
       <c r="J2" t="n">
-        <v>2.670158609974452</v>
+        <v>2.670158609974424</v>
       </c>
       <c r="K2" t="n">
-        <v>2.660542181682984</v>
+        <v>2.660542181682935</v>
       </c>
       <c r="L2" t="n">
-        <v>2.619581387210956</v>
+        <v>2.61958138721091</v>
       </c>
       <c r="M2" t="n">
-        <v>2.691632131174362</v>
+        <v>2.69163213117432</v>
       </c>
       <c r="N2" t="n">
-        <v>2.632566002170837</v>
+        <v>2.632566002170807</v>
       </c>
       <c r="O2" t="n">
-        <v>5.227341239579896</v>
+        <v>5.227341239579862</v>
       </c>
       <c r="P2" t="n">
-        <v>2.654300172730635</v>
+        <v>2.654300172730601</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.664129818984105</v>
+        <v>2.664129818984076</v>
       </c>
       <c r="R2" t="n">
-        <v>2.663473747242632</v>
+        <v>2.663473747242601</v>
       </c>
       <c r="S2" t="n">
-        <v>2.664040195116291</v>
+        <v>2.66404019511626</v>
       </c>
       <c r="T2" t="n">
-        <v>2.644222141417561</v>
+        <v>2.644222141417545</v>
       </c>
       <c r="U2" t="n">
-        <v>3.509893580658892</v>
+        <v>3.509893580658846</v>
       </c>
       <c r="V2" t="n">
-        <v>2.647938410047465</v>
+        <v>2.647938410047423</v>
       </c>
       <c r="W2" t="n">
-        <v>3.739751588442426</v>
+        <v>3.73975158844237</v>
       </c>
       <c r="X2" t="n">
-        <v>2.652874296946361</v>
+        <v>2.652874296946335</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.724785681622179</v>
+        <v>2.724785681622108</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.893745594073673</v>
+        <v>2.893745594073646</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.636651771100202</v>
+        <v>2.636651771100166</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.700875133405165</v>
+        <v>2.70087513340515</v>
       </c>
     </row>
     <row r="3">
@@ -4114,85 +4114,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.71821541528959</v>
+        <v>2.718215415289546</v>
       </c>
       <c r="C3" t="n">
-        <v>3.009080157012053</v>
+        <v>3.009080157012021</v>
       </c>
       <c r="D3" t="n">
-        <v>2.792958375165513</v>
+        <v>2.792958375165346</v>
       </c>
       <c r="E3" t="n">
-        <v>2.46184233459396</v>
+        <v>2.461842334593929</v>
       </c>
       <c r="F3" t="n">
-        <v>2.827843325197714</v>
+        <v>2.827843325197672</v>
       </c>
       <c r="G3" t="n">
-        <v>3.338203105008404</v>
+        <v>3.338203105008355</v>
       </c>
       <c r="H3" t="n">
-        <v>2.572373292192077</v>
+        <v>2.57237329219206</v>
       </c>
       <c r="I3" t="n">
-        <v>3.238278714574765</v>
+        <v>3.238278714574719</v>
       </c>
       <c r="J3" t="n">
-        <v>3.045540506553649</v>
+        <v>3.045540506553534</v>
       </c>
       <c r="K3" t="n">
-        <v>2.97719448228061</v>
+        <v>2.977194482280554</v>
       </c>
       <c r="L3" t="n">
-        <v>2.685811067044779</v>
+        <v>2.685811067044731</v>
       </c>
       <c r="M3" t="n">
-        <v>3.206974777593735</v>
+        <v>3.206974777593672</v>
       </c>
       <c r="N3" t="n">
-        <v>2.779308073237586</v>
+        <v>2.779308073237547</v>
       </c>
       <c r="O3" t="n">
-        <v>7.07841661981518</v>
+        <v>7.078416619815192</v>
       </c>
       <c r="P3" t="n">
-        <v>2.931539518492208</v>
+        <v>2.931539518492202</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.00367788931891</v>
+        <v>3.003677889318899</v>
       </c>
       <c r="R3" t="n">
-        <v>3.00182412324242</v>
+        <v>3.001824123242381</v>
       </c>
       <c r="S3" t="n">
-        <v>3.001474998467732</v>
+        <v>3.001474998467608</v>
       </c>
       <c r="T3" t="n">
-        <v>2.863273811669968</v>
+        <v>2.863273811669939</v>
       </c>
       <c r="U3" t="n">
-        <v>4.18347400629466</v>
+        <v>4.183474006294586</v>
       </c>
       <c r="V3" t="n">
-        <v>2.886156680177414</v>
+        <v>2.886156680177344</v>
       </c>
       <c r="W3" t="n">
-        <v>4.665951768024379</v>
+        <v>4.66595176802436</v>
       </c>
       <c r="X3" t="n">
-        <v>2.923925684595092</v>
+        <v>2.923925684595077</v>
       </c>
       <c r="Y3" t="n">
-        <v>3.437884207104372</v>
+        <v>3.437884207104027</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.313762545724393</v>
+        <v>3.313762545724324</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.808195137412473</v>
+        <v>2.808195137412439</v>
       </c>
       <c r="AB3" t="n">
-        <v>3.271313112408909</v>
+        <v>3.271313112408867</v>
       </c>
     </row>
     <row r="4">
@@ -4202,85 +4202,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.271619454046292</v>
+        <v>2.271619454046469</v>
       </c>
       <c r="C4" t="n">
-        <v>2.067819274200209</v>
+        <v>2.067819274200434</v>
       </c>
       <c r="D4" t="n">
-        <v>2.387703120364008</v>
+        <v>2.387703120364233</v>
       </c>
       <c r="E4" t="n">
-        <v>1.863214119470879</v>
+        <v>1.863214119471154</v>
       </c>
       <c r="F4" t="n">
-        <v>2.442102512119833</v>
+        <v>2.442102512120094</v>
       </c>
       <c r="G4" t="n">
-        <v>3.258339224344422</v>
+        <v>3.258339224344546</v>
       </c>
       <c r="H4" t="n">
-        <v>2.038082075267083</v>
+        <v>2.038082075267223</v>
       </c>
       <c r="I4" t="n">
-        <v>3.089863258237525</v>
+        <v>3.089863258237687</v>
       </c>
       <c r="J4" t="n">
-        <v>2.789315870024089</v>
+        <v>2.789315870024172</v>
       </c>
       <c r="K4" t="n">
-        <v>2.68183843485936</v>
+        <v>2.681838434859507</v>
       </c>
       <c r="L4" t="n">
-        <v>2.219167418401353</v>
+        <v>2.219167418401605</v>
       </c>
       <c r="M4" t="n">
-        <v>3.043096255995662</v>
+        <v>3.043096255995815</v>
       </c>
       <c r="N4" t="n">
-        <v>10.83050639163236</v>
+        <v>2.365834617591257</v>
       </c>
       <c r="O4" t="n">
-        <v>2.40325918115258</v>
+        <v>2.40325918115266</v>
       </c>
       <c r="P4" t="n">
-        <v>2.611332072276666</v>
+        <v>2.611332072276817</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.722362448570223</v>
+        <v>2.722362448570382</v>
       </c>
       <c r="R4" t="n">
-        <v>2.71495181644255</v>
+        <v>2.714951816442485</v>
       </c>
       <c r="S4" t="n">
-        <v>2.72135010575438</v>
+        <v>2.721350105754561</v>
       </c>
       <c r="T4" t="n">
-        <v>2.497496072472023</v>
+        <v>2.497496072472265</v>
       </c>
       <c r="U4" t="n">
-        <v>2.22801514937862</v>
+        <v>2.228015149378962</v>
       </c>
       <c r="V4" t="n">
-        <v>2.532372603141346</v>
+        <v>2.532372603141271</v>
       </c>
       <c r="W4" t="n">
-        <v>2.488088795830678</v>
+        <v>2.488088795830709</v>
       </c>
       <c r="X4" t="n">
-        <v>2.595226149358064</v>
+        <v>2.59522614935799</v>
       </c>
       <c r="Y4" t="n">
-        <v>3.357771714212979</v>
+        <v>3.357771714213129</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.586674396010397</v>
+        <v>2.586674396010579</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.411985257195127</v>
+        <v>2.411985257195177</v>
       </c>
       <c r="AB4" t="n">
-        <v>3.138976623326687</v>
+        <v>3.138976623326767</v>
       </c>
     </row>
     <row r="5">
@@ -4290,85 +4290,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8.354328753969678</v>
+        <v>8.354328753969828</v>
       </c>
       <c r="C5" t="n">
-        <v>5.42558647754165</v>
+        <v>5.425586477542002</v>
       </c>
       <c r="D5" t="n">
-        <v>11.13056849443723</v>
+        <v>11.13056849443406</v>
       </c>
       <c r="E5" t="n">
-        <v>2.000751142991024</v>
+        <v>2.000751142991071</v>
       </c>
       <c r="F5" t="n">
-        <v>12.35836883384906</v>
+        <v>12.358368833848</v>
       </c>
       <c r="G5" t="n">
-        <v>24.00662781505358</v>
+        <v>24.00662781504915</v>
       </c>
       <c r="H5" t="n">
-        <v>5.11453220763414</v>
+        <v>5.114532207634145</v>
       </c>
       <c r="I5" t="n">
-        <v>24.40948576456641</v>
+        <v>24.40948576456635</v>
       </c>
       <c r="J5" t="n">
-        <v>17.26794196477793</v>
+        <v>17.26794196477593</v>
       </c>
       <c r="K5" t="n">
-        <v>15.49660818132428</v>
+        <v>15.49660818132329</v>
       </c>
       <c r="L5" t="n">
-        <v>7.808835685967373</v>
+        <v>7.808835685967433</v>
       </c>
       <c r="M5" t="n">
-        <v>23.13586690105995</v>
+        <v>23.13586690105952</v>
       </c>
       <c r="N5" t="n">
-        <v>10.83050639163236</v>
+        <v>10.83050639163243</v>
       </c>
       <c r="O5" t="n">
-        <v>10.34162330191747</v>
+        <v>10.34162330191427</v>
       </c>
       <c r="P5" t="n">
-        <v>13.67672326305236</v>
+        <v>13.67672326304721</v>
       </c>
       <c r="Q5" t="n">
-        <v>16.66847863809715</v>
+        <v>16.66847863809731</v>
       </c>
       <c r="R5" t="n">
-        <v>18.00328595182103</v>
+        <v>18.00328595182078</v>
       </c>
       <c r="S5" t="n">
-        <v>15.84046370477228</v>
+        <v>15.84046370477145</v>
       </c>
       <c r="T5" t="n">
-        <v>13.56093169205977</v>
+        <v>13.56093169205996</v>
       </c>
       <c r="U5" t="n">
-        <v>8.666516449532295</v>
+        <v>8.666516449531507</v>
       </c>
       <c r="V5" t="n">
-        <v>12.40975639362042</v>
+        <v>12.40975639362189</v>
       </c>
       <c r="W5" t="n">
-        <v>12.81169834271109</v>
+        <v>12.81169834271113</v>
       </c>
       <c r="X5" t="n">
-        <v>14.71992438111992</v>
+        <v>14.71992438111757</v>
       </c>
       <c r="Y5" t="n">
-        <v>29.46117411541059</v>
+        <v>29.46117411540508</v>
       </c>
       <c r="Z5" t="n">
-        <v>12.6970512525077</v>
+        <v>12.6970512525078</v>
       </c>
       <c r="AA5" t="n">
-        <v>11.50514012813357</v>
+        <v>11.50514012813355</v>
       </c>
       <c r="AB5" t="n">
-        <v>26.38717626251981</v>
+        <v>26.38717626251987</v>
       </c>
     </row>
     <row r="6">
@@ -4378,85 +4378,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.808071650474086</v>
+        <v>2.808071650474357</v>
       </c>
       <c r="C6" t="n">
-        <v>2.604271470628093</v>
+        <v>2.604271470628333</v>
       </c>
       <c r="D6" t="n">
-        <v>5.141670904220919</v>
+        <v>5.141670904221057</v>
       </c>
       <c r="E6" t="n">
-        <v>4.617181903327855</v>
+        <v>4.617181903328127</v>
       </c>
       <c r="F6" t="n">
-        <v>2.978554708547689</v>
+        <v>2.978554708547782</v>
       </c>
       <c r="G6" t="n">
-        <v>3.794791420772606</v>
+        <v>3.794791420772333</v>
       </c>
       <c r="H6" t="n">
-        <v>4.792049859123834</v>
+        <v>4.792049859124227</v>
       </c>
       <c r="I6" t="n">
-        <v>3.626315454665351</v>
+        <v>3.626315454665654</v>
       </c>
       <c r="J6" t="n">
-        <v>5.543283653881094</v>
+        <v>5.543283653881095</v>
       </c>
       <c r="K6" t="n">
-        <v>5.435806218716353</v>
+        <v>5.435806218716576</v>
       </c>
       <c r="L6" t="n">
-        <v>2.755619614829331</v>
+        <v>2.755619614829429</v>
       </c>
       <c r="M6" t="n">
-        <v>3.579548452423435</v>
+        <v>3.579548452423686</v>
       </c>
       <c r="N6" t="n">
-        <v>10.83050639163236</v>
+        <v>2.912678971137336</v>
       </c>
       <c r="O6" t="n">
-        <v>2.934256560137761</v>
+        <v>2.934256560137823</v>
       </c>
       <c r="P6" t="n">
-        <v>5.47482048127701</v>
+        <v>5.474820481277236</v>
       </c>
       <c r="Q6" t="n">
-        <v>5.476330232427066</v>
+        <v>5.476330232427397</v>
       </c>
       <c r="R6" t="n">
-        <v>5.468919600299422</v>
+        <v>5.468919600299857</v>
       </c>
       <c r="S6" t="n">
-        <v>3.257802302182073</v>
+        <v>3.257802302182344</v>
       </c>
       <c r="T6" t="n">
-        <v>5.251463856329178</v>
+        <v>5.251463856329165</v>
       </c>
       <c r="U6" t="n">
-        <v>5.031709539165282</v>
+        <v>5.031709539165673</v>
       </c>
       <c r="V6" t="n">
-        <v>3.068824799569131</v>
+        <v>3.068824799569019</v>
       </c>
       <c r="W6" t="n">
-        <v>3.060720923169481</v>
+        <v>3.060720923169623</v>
       </c>
       <c r="X6" t="n">
-        <v>3.131678345785705</v>
+        <v>3.131678345785769</v>
       </c>
       <c r="Y6" t="n">
-        <v>3.972171163375724</v>
+        <v>3.972171163375916</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.123126592438247</v>
+        <v>3.123126592438477</v>
       </c>
       <c r="AA6" t="n">
-        <v>5.165953041051885</v>
+        <v>5.165953041051943</v>
       </c>
       <c r="AB6" t="n">
-        <v>3.667123869023014</v>
+        <v>3.667123869023263</v>
       </c>
     </row>
     <row r="7">
@@ -4466,85 +4466,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.067749813720309</v>
+        <v>3.067749813720426</v>
       </c>
       <c r="C7" t="n">
-        <v>2.863949633874187</v>
+        <v>2.863949633874399</v>
       </c>
       <c r="D7" t="n">
-        <v>3.183833480037995</v>
+        <v>3.18383348003815</v>
       </c>
       <c r="E7" t="n">
-        <v>2.659344479144896</v>
+        <v>2.659344479145065</v>
       </c>
       <c r="F7" t="n">
-        <v>3.238232871793797</v>
+        <v>3.238232871794216</v>
       </c>
       <c r="G7" t="n">
-        <v>4.054469584018481</v>
+        <v>4.05446958401849</v>
       </c>
       <c r="H7" t="n">
-        <v>2.834212434941068</v>
+        <v>2.834212434941077</v>
       </c>
       <c r="I7" t="n">
-        <v>3.885993617911463</v>
+        <v>3.885993617911622</v>
       </c>
       <c r="J7" t="n">
-        <v>3.585446229698069</v>
+        <v>3.585446229697988</v>
       </c>
       <c r="K7" t="n">
-        <v>3.477968794533379</v>
+        <v>3.477968794533487</v>
       </c>
       <c r="L7" t="n">
-        <v>3.015297778075333</v>
+        <v>3.015297778075524</v>
       </c>
       <c r="M7" t="n">
-        <v>3.839226615669642</v>
+        <v>3.839226615669781</v>
       </c>
       <c r="N7" t="n">
-        <v>10.83050639163236</v>
+        <v>3.161964977265438</v>
       </c>
       <c r="O7" t="n">
-        <v>3.199374985873793</v>
+        <v>3.199374985874051</v>
       </c>
       <c r="P7" t="n">
-        <v>3.407447876997822</v>
+        <v>3.407447876997805</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.518492808244241</v>
+        <v>3.51849280824437</v>
       </c>
       <c r="R7" t="n">
-        <v>3.511082176116526</v>
+        <v>3.511082176116424</v>
       </c>
       <c r="S7" t="n">
-        <v>3.517480465428385</v>
+        <v>3.517480465428456</v>
       </c>
       <c r="T7" t="n">
-        <v>3.293626432146032</v>
+        <v>3.293626432146214</v>
       </c>
       <c r="U7" t="n">
-        <v>3.079433926056615</v>
+        <v>3.079433926056752</v>
       </c>
       <c r="V7" t="n">
-        <v>3.328502962815354</v>
+        <v>3.328502962815215</v>
       </c>
       <c r="W7" t="n">
-        <v>3.284219155504698</v>
+        <v>3.28421915550487</v>
       </c>
       <c r="X7" t="n">
-        <v>3.391356509032001</v>
+        <v>3.391356509031764</v>
       </c>
       <c r="Y7" t="n">
-        <v>4.203628679816676</v>
+        <v>4.203628679816392</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.382804755684405</v>
+        <v>3.382804755684537</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.208115616869135</v>
+        <v>3.208115616869089</v>
       </c>
       <c r="AB7" t="n">
-        <v>3.935106983000736</v>
+        <v>3.935106983000991</v>
       </c>
     </row>
     <row r="8">
@@ -4554,85 +4554,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.893726193320748</v>
+        <v>4.893726193320813</v>
       </c>
       <c r="C8" t="n">
-        <v>6.644294352343102</v>
+        <v>6.644294352343303</v>
       </c>
       <c r="D8" t="n">
-        <v>6.964178198506955</v>
+        <v>6.964178198507047</v>
       </c>
       <c r="E8" t="n">
-        <v>5.399045708782073</v>
+        <v>5.399045708782118</v>
       </c>
       <c r="F8" t="n">
-        <v>5.368676996719278</v>
+        <v>5.368676996719329</v>
       </c>
       <c r="G8" t="n">
-        <v>8.240065308665081</v>
+        <v>8.240065308664823</v>
       </c>
       <c r="H8" t="n">
-        <v>6.614557153410087</v>
+        <v>6.614557153409934</v>
       </c>
       <c r="I8" t="n">
-        <v>7.66633833638044</v>
+        <v>7.666338336380357</v>
       </c>
       <c r="J8" t="n">
-        <v>7.365790948167136</v>
+        <v>7.36579094816699</v>
       </c>
       <c r="K8" t="n">
-        <v>7.258313513002288</v>
+        <v>7.25831351300242</v>
       </c>
       <c r="L8" t="n">
-        <v>6.795642496544239</v>
+        <v>6.795642496544507</v>
       </c>
       <c r="M8" t="n">
-        <v>7.619571334114962</v>
+        <v>7.619571334115016</v>
       </c>
       <c r="N8" t="n">
-        <v>10.83050639163236</v>
+        <v>5.427347272878223</v>
       </c>
       <c r="O8" t="n">
-        <v>5.881096661182423</v>
+        <v>5.881096661182448</v>
       </c>
       <c r="P8" t="n">
-        <v>5.987118278320439</v>
+        <v>5.98711827832051</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.960391204753435</v>
+        <v>4.960391204753757</v>
       </c>
       <c r="R8" t="n">
-        <v>7.291426894585408</v>
+        <v>7.291426894585468</v>
       </c>
       <c r="S8" t="n">
-        <v>7.297825183897332</v>
+        <v>7.297825183897439</v>
       </c>
       <c r="T8" t="n">
-        <v>7.073971150615045</v>
+        <v>7.073971150615221</v>
       </c>
       <c r="U8" t="n">
-        <v>5.904637275012469</v>
+        <v>5.904637275012267</v>
       </c>
       <c r="V8" t="n">
-        <v>6.57945588193852</v>
+        <v>6.579455881938379</v>
       </c>
       <c r="W8" t="n">
-        <v>7.064947957114622</v>
+        <v>7.064947957114807</v>
       </c>
       <c r="X8" t="n">
-        <v>5.012376643338345</v>
+        <v>5.012376643338199</v>
       </c>
       <c r="Y8" t="n">
-        <v>9.934550260659263</v>
+        <v>9.934550260658597</v>
       </c>
       <c r="Z8" t="n">
-        <v>5.172477740615513</v>
+        <v>5.172477740615657</v>
       </c>
       <c r="AA8" t="n">
-        <v>6.988460335338193</v>
+        <v>6.988460335337919</v>
       </c>
       <c r="AB8" t="n">
-        <v>9.756952847072172</v>
+        <v>9.756952847072316</v>
       </c>
     </row>
     <row r="9">
@@ -4642,85 +4642,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>81.01562922457934</v>
+        <v>81.01562922457944</v>
       </c>
       <c r="C9" t="n">
         <v>102.7143729995563</v>
       </c>
       <c r="D9" t="n">
-        <v>103.03425684572</v>
+        <v>103.0342568457205</v>
       </c>
       <c r="E9" t="n">
-        <v>97.45475046135488</v>
+        <v>97.45475046135473</v>
       </c>
       <c r="F9" t="n">
-        <v>52.59731393336054</v>
+        <v>52.59731393336077</v>
       </c>
       <c r="G9" t="n">
-        <v>103.9048934989073</v>
+        <v>103.9048934989075</v>
       </c>
       <c r="H9" t="n">
-        <v>102.6846358006232</v>
+        <v>102.6846358006231</v>
       </c>
       <c r="I9" t="n">
         <v>103.7364169835936</v>
       </c>
       <c r="J9" t="n">
-        <v>103.4358695953804</v>
+        <v>103.43586959538</v>
       </c>
       <c r="K9" t="n">
         <v>103.3283921602153</v>
       </c>
       <c r="L9" t="n">
-        <v>102.8657211437576</v>
+        <v>102.8657211437575</v>
       </c>
       <c r="M9" t="n">
-        <v>103.6896499813518</v>
+        <v>103.6896499813517</v>
       </c>
       <c r="N9" t="n">
-        <v>10.83050639163236</v>
+        <v>103.0123883429474</v>
       </c>
       <c r="O9" t="n">
-        <v>110.3082880254093</v>
+        <v>110.308288025409</v>
       </c>
       <c r="P9" t="n">
-        <v>112.0949546009948</v>
+        <v>112.094954600995</v>
       </c>
       <c r="Q9" t="n">
-        <v>103.3689167231333</v>
+        <v>103.3689167231335</v>
       </c>
       <c r="R9" t="n">
         <v>103.3615055417983</v>
       </c>
       <c r="S9" t="n">
-        <v>103.3679038311104</v>
+        <v>103.3679038311105</v>
       </c>
       <c r="T9" t="n">
-        <v>103.1440497978282</v>
+        <v>103.1440497978286</v>
       </c>
       <c r="U9" t="n">
-        <v>102.9242954806643</v>
+        <v>102.9242954806644</v>
       </c>
       <c r="V9" t="n">
-        <v>128.453997883289</v>
+        <v>128.4539978832889</v>
       </c>
       <c r="W9" t="n">
-        <v>103.1346425211867</v>
+        <v>103.1346425211869</v>
       </c>
       <c r="X9" t="n">
-        <v>103.2417798747143</v>
+        <v>103.2417798747142</v>
       </c>
       <c r="Y9" t="n">
-        <v>104.0540520454987</v>
+        <v>104.0540520454993</v>
       </c>
       <c r="Z9" t="n">
-        <v>90.0279419848907</v>
+        <v>90.02794198489072</v>
       </c>
       <c r="AA9" t="n">
-        <v>103.0585389825509</v>
+        <v>103.0585389825513</v>
       </c>
       <c r="AB9" t="n">
-        <v>103.7855303486826</v>
+        <v>103.7855303486828</v>
       </c>
     </row>
   </sheetData>
@@ -5098,7 +5098,7 @@
         <v>2.532055659299039</v>
       </c>
       <c r="N4" t="n">
-        <v>14.837759495947</v>
+        <v>2.416859063414496</v>
       </c>
       <c r="O4" t="n">
         <v>1.989271578587187</v>
@@ -5274,7 +5274,7 @@
         <v>5.388041020046656</v>
       </c>
       <c r="N6" t="n">
-        <v>14.837759495947</v>
+        <v>2.970910102346211</v>
       </c>
       <c r="O6" t="n">
         <v>4.908489188270447</v>
@@ -5362,7 +5362,7 @@
         <v>3.365611950540037</v>
       </c>
       <c r="N7" t="n">
-        <v>14.837759495947</v>
+        <v>3.250415354655428</v>
       </c>
       <c r="O7" t="n">
         <v>2.822816705118538</v>
@@ -5450,7 +5450,7 @@
         <v>7.313353336489266</v>
       </c>
       <c r="N8" t="n">
-        <v>14.837759495947</v>
+        <v>5.641817956332036</v>
       </c>
       <c r="O8" t="n">
         <v>5.641925880388073</v>
@@ -5538,7 +5538,7 @@
         <v>110.66541595004</v>
       </c>
       <c r="N9" t="n">
-        <v>14.837759495947</v>
+        <v>110.5502193541552</v>
       </c>
       <c r="O9" t="n">
         <v>117.9137790205117</v>
@@ -5834,7 +5834,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.206284287266378</v>
+        <v>4.206284287266376</v>
       </c>
       <c r="C3" t="n">
         <v>3.963974491255271</v>
@@ -5843,7 +5843,7 @@
         <v>2.783895188149871</v>
       </c>
       <c r="E3" t="n">
-        <v>5.487688501021072</v>
+        <v>5.487688501021074</v>
       </c>
       <c r="F3" t="n">
         <v>4.475982880420335</v>
@@ -5858,7 +5858,7 @@
         <v>3.95598934565355</v>
       </c>
       <c r="J3" t="n">
-        <v>3.375670120903186</v>
+        <v>3.375670120903185</v>
       </c>
       <c r="K3" t="n">
         <v>3.387542366376876</v>
@@ -5882,7 +5882,7 @@
         <v>3.478405893014124</v>
       </c>
       <c r="R3" t="n">
-        <v>4.616738338748286</v>
+        <v>4.616738338748285</v>
       </c>
       <c r="S3" t="n">
         <v>3.677092021518443</v>
@@ -5958,7 +5958,7 @@
         <v>2.590456693117607</v>
       </c>
       <c r="N4" t="n">
-        <v>27.12432858592459</v>
+        <v>3.504936388712792</v>
       </c>
       <c r="O4" t="n">
         <v>3.506851096390652</v>
@@ -6016,7 +6016,7 @@
         <v>24.86531174285755</v>
       </c>
       <c r="D5" t="n">
-        <v>6.3330525604473</v>
+        <v>6.333052560447299</v>
       </c>
       <c r="E5" t="n">
         <v>81.082609823824</v>
@@ -6055,10 +6055,10 @@
         <v>10.05461522028183</v>
       </c>
       <c r="Q5" t="n">
-        <v>23.46505776786229</v>
+        <v>23.4650577678623</v>
       </c>
       <c r="R5" t="n">
-        <v>60.11135078813276</v>
+        <v>60.11135078813277</v>
       </c>
       <c r="S5" t="n">
         <v>26.81832839512394</v>
@@ -6134,7 +6134,7 @@
         <v>5.705429171506675</v>
       </c>
       <c r="N6" t="n">
-        <v>27.12432858592459</v>
+        <v>4.272581751036259</v>
       </c>
       <c r="O6" t="n">
         <v>6.727572883443766</v>
@@ -6176,7 +6176,7 @@
         <v>5.569846106433268</v>
       </c>
       <c r="AB6" t="n">
-        <v>3.315907661825044</v>
+        <v>3.315907661825043</v>
       </c>
     </row>
     <row r="7">
@@ -6195,10 +6195,10 @@
         <v>3.140831897333467</v>
       </c>
       <c r="E7" t="n">
-        <v>7.423010272878017</v>
+        <v>7.423010272878016</v>
       </c>
       <c r="F7" t="n">
-        <v>5.817873336531484</v>
+        <v>5.817873336531485</v>
       </c>
       <c r="G7" t="n">
         <v>3.468661685433494</v>
@@ -6222,7 +6222,7 @@
         <v>3.447914204316349</v>
       </c>
       <c r="N7" t="n">
-        <v>27.12432858592459</v>
+        <v>4.362393899911406</v>
       </c>
       <c r="O7" t="n">
         <v>4.364312445657445</v>
@@ -6264,7 +6264,7 @@
         <v>3.312331139242818</v>
       </c>
       <c r="AB7" t="n">
-        <v>3.440818437567319</v>
+        <v>3.440818437567318</v>
       </c>
     </row>
     <row r="8">
@@ -6310,7 +6310,7 @@
         <v>7.543097694955136</v>
       </c>
       <c r="N8" t="n">
-        <v>27.12432858592459</v>
+        <v>6.801209791812065</v>
       </c>
       <c r="O8" t="n">
         <v>7.258308693697121</v>
@@ -6398,7 +6398,7 @@
         <v>103.5703327837502</v>
       </c>
       <c r="N9" t="n">
-        <v>27.12432858592459</v>
+        <v>104.4848124793454</v>
       </c>
       <c r="O9" t="n">
         <v>111.7758359651136</v>
@@ -6818,7 +6818,7 @@
         <v>2.607121539718747</v>
       </c>
       <c r="N4" t="n">
-        <v>20.40478683821665</v>
+        <v>3.234652583943517</v>
       </c>
       <c r="O4" t="n">
         <v>3.669760390924519</v>
@@ -6906,7 +6906,7 @@
         <v>9.534501493285704</v>
       </c>
       <c r="N5" t="n">
-        <v>20.40478683821664</v>
+        <v>20.40478683821665</v>
       </c>
       <c r="O5" t="n">
         <v>25.2306390378361</v>
@@ -6994,7 +6994,7 @@
         <v>5.87033338264927</v>
       </c>
       <c r="N6" t="n">
-        <v>20.40478683821664</v>
+        <v>4.069452934234431</v>
       </c>
       <c r="O6" t="n">
         <v>4.486164010661235</v>
@@ -7082,7 +7082,7 @@
         <v>3.494472170756286</v>
       </c>
       <c r="N7" t="n">
-        <v>20.40478683821664</v>
+        <v>4.122003214981086</v>
       </c>
       <c r="O7" t="n">
         <v>4.557119590659822</v>
@@ -7170,7 +7170,7 @@
         <v>7.757219039541186</v>
       </c>
       <c r="N8" t="n">
-        <v>20.40478683821664</v>
+        <v>6.643155706989527</v>
       </c>
       <c r="O8" t="n">
         <v>7.556868766053143</v>
@@ -7258,7 +7258,7 @@
         <v>103.5304976391992</v>
       </c>
       <c r="N9" t="n">
-        <v>20.40478683821664</v>
+        <v>104.158028683424</v>
       </c>
       <c r="O9" t="n">
         <v>111.8843293968026</v>
@@ -7678,7 +7678,7 @@
         <v>3.131039336090281</v>
       </c>
       <c r="N4" t="n">
-        <v>14.00383852928701</v>
+        <v>2.088557552461184</v>
       </c>
       <c r="O4" t="n">
         <v>1.857579459276364</v>
@@ -7854,7 +7854,7 @@
         <v>3.556583886026523</v>
       </c>
       <c r="N6" t="n">
-        <v>14.00383852928701</v>
+        <v>2.526478562207239</v>
       </c>
       <c r="O6" t="n">
         <v>4.495499590618625</v>
@@ -7942,7 +7942,7 @@
         <v>3.858229161398047</v>
       </c>
       <c r="N7" t="n">
-        <v>14.00383852928701</v>
+        <v>2.81574737776902</v>
       </c>
       <c r="O7" t="n">
         <v>2.584772640374423</v>
@@ -8030,7 +8030,7 @@
         <v>7.464475175146144</v>
       </c>
       <c r="N8" t="n">
-        <v>14.00383852928701</v>
+        <v>5.035884061144731</v>
       </c>
       <c r="O8" t="n">
         <v>5.185820845724457</v>
@@ -8118,7 +8118,7 @@
         <v>111.1992707439983</v>
       </c>
       <c r="N9" t="n">
-        <v>14.00383852928701</v>
+        <v>110.1567889603693</v>
       </c>
       <c r="O9" t="n">
         <v>117.7038557162718</v>
@@ -8538,7 +8538,7 @@
         <v>2.544342725765739</v>
       </c>
       <c r="N4" t="n">
-        <v>14.50806095784715</v>
+        <v>2.488299992400071</v>
       </c>
       <c r="O4" t="n">
         <v>2.123760229046396</v>
@@ -8714,7 +8714,7 @@
         <v>3.122684238007297</v>
       </c>
       <c r="N6" t="n">
-        <v>14.50806095784715</v>
+        <v>3.074138561373638</v>
       </c>
       <c r="O6" t="n">
         <v>5.000802039504914</v>
@@ -8802,7 +8802,7 @@
         <v>3.318503488208997</v>
       </c>
       <c r="N7" t="n">
-        <v>14.50806095784715</v>
+        <v>3.262460754843308</v>
       </c>
       <c r="O7" t="n">
         <v>2.897923563691941</v>
@@ -8890,7 +8890,7 @@
         <v>7.119971745514952</v>
       </c>
       <c r="N8" t="n">
-        <v>14.50806095784715</v>
+        <v>5.554076905911566</v>
       </c>
       <c r="O8" t="n">
         <v>5.604457608106015</v>
@@ -8978,7 +8978,7 @@
         <v>103.3495588446879</v>
       </c>
       <c r="N9" t="n">
-        <v>14.50806095784715</v>
+        <v>103.2935161113224</v>
       </c>
       <c r="O9" t="n">
         <v>110.1976853775308</v>

--- a/Results/Phase 2/Ammonia/ammonia land use results.xlsx
+++ b/Results/Phase 2/Ammonia/ammonia land use results.xlsx
@@ -586,34 +586,34 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.951431572540947</v>
+        <v>1.951431572540951</v>
       </c>
       <c r="C2" t="n">
-        <v>1.972617201936157</v>
+        <v>1.972617201936159</v>
       </c>
       <c r="D2" t="n">
-        <v>1.940709170041142</v>
+        <v>1.940709170041143</v>
       </c>
       <c r="E2" t="n">
-        <v>1.891854521477512</v>
+        <v>1.891854521477514</v>
       </c>
       <c r="F2" t="n">
-        <v>1.929905264664319</v>
+        <v>1.929905264664322</v>
       </c>
       <c r="G2" t="n">
         <v>2.025426521060638</v>
       </c>
       <c r="H2" t="n">
-        <v>1.950196310658897</v>
+        <v>1.950196310658898</v>
       </c>
       <c r="I2" t="n">
         <v>1.958286368086906</v>
       </c>
       <c r="J2" t="n">
-        <v>1.987309063957829</v>
+        <v>1.987309063957832</v>
       </c>
       <c r="K2" t="n">
-        <v>2.003688483017605</v>
+        <v>2.003688483017608</v>
       </c>
       <c r="L2" t="n">
         <v>1.94216820908669</v>
@@ -622,49 +622,49 @@
         <v>2.051916283667521</v>
       </c>
       <c r="N2" t="n">
-        <v>1.966201862542891</v>
+        <v>1.966201862542893</v>
       </c>
       <c r="O2" t="n">
-        <v>3.719587879210501</v>
+        <v>3.719587879210499</v>
       </c>
       <c r="P2" t="n">
-        <v>1.978029055634911</v>
+        <v>1.978029055634912</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.946166859905627</v>
+        <v>1.946166859905629</v>
       </c>
       <c r="R2" t="n">
-        <v>1.966259195436216</v>
+        <v>1.966259195436215</v>
       </c>
       <c r="S2" t="n">
-        <v>1.989761327606155</v>
+        <v>1.989761327606157</v>
       </c>
       <c r="T2" t="n">
-        <v>1.95979370747216</v>
+        <v>1.959793707472161</v>
       </c>
       <c r="U2" t="n">
-        <v>2.027084533806829</v>
+        <v>2.027084533806833</v>
       </c>
       <c r="V2" t="n">
-        <v>1.977789852687648</v>
+        <v>1.97778985268765</v>
       </c>
       <c r="W2" t="n">
-        <v>2.102527618151945</v>
+        <v>2.102527618151943</v>
       </c>
       <c r="X2" t="n">
-        <v>1.949002327546852</v>
+        <v>1.949002327546854</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.96162693392031</v>
+        <v>1.961626933920311</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.752733561134763</v>
+        <v>1.752733561134764</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.988026565672755</v>
+        <v>1.988026565672757</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.046719325993284</v>
+        <v>2.046719325993283</v>
       </c>
     </row>
     <row r="3">
@@ -674,85 +674,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.074651729313636</v>
+        <v>2.081419784576804</v>
       </c>
       <c r="C3" t="n">
-        <v>2.09413460356083</v>
+        <v>2.100292043604153</v>
       </c>
       <c r="D3" t="n">
-        <v>1.998917962004387</v>
+        <v>2.003048455824875</v>
       </c>
       <c r="E3" t="n">
-        <v>1.650312226703391</v>
+        <v>1.642023104282536</v>
       </c>
       <c r="F3" t="n">
-        <v>1.921621610330813</v>
+        <v>1.923008921958796</v>
       </c>
       <c r="G3" t="n">
-        <v>2.601588633187063</v>
+        <v>2.626870742968976</v>
       </c>
       <c r="H3" t="n">
-        <v>2.067252147159454</v>
+        <v>2.073827267725814</v>
       </c>
       <c r="I3" t="n">
-        <v>2.124894243500339</v>
+        <v>2.133501912711658</v>
       </c>
       <c r="J3" t="n">
-        <v>2.330767805191697</v>
+        <v>2.34657243678115</v>
       </c>
       <c r="K3" t="n">
-        <v>2.449508858897623</v>
+        <v>2.469605612397065</v>
       </c>
       <c r="L3" t="n">
-        <v>2.009045437669644</v>
+        <v>2.013517194873502</v>
       </c>
       <c r="M3" t="n">
-        <v>2.792689580721756</v>
+        <v>2.825054416068371</v>
       </c>
       <c r="N3" t="n">
-        <v>2.180960610040218</v>
+        <v>2.191525564094397</v>
       </c>
       <c r="O3" t="n">
-        <v>5.162434740754759</v>
+        <v>5.176953490834447</v>
       </c>
       <c r="P3" t="n">
-        <v>2.26393158469704</v>
+        <v>2.277325836932243</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.037848516062044</v>
+        <v>2.043354216773901</v>
       </c>
       <c r="R3" t="n">
-        <v>2.182220196022666</v>
+        <v>2.19287562302837</v>
       </c>
       <c r="S3" t="n">
-        <v>2.347779543321996</v>
+        <v>2.364177628509117</v>
       </c>
       <c r="T3" t="n">
-        <v>2.135590405611325</v>
+        <v>2.144572068113595</v>
       </c>
       <c r="U3" t="n">
-        <v>2.374268890449881</v>
+        <v>2.389068523932562</v>
       </c>
       <c r="V3" t="n">
-        <v>2.262156441505533</v>
+        <v>2.275525166899178</v>
       </c>
       <c r="W3" t="n">
-        <v>2.366873218633295</v>
+        <v>2.37562413456426</v>
       </c>
       <c r="X3" t="n">
-        <v>2.058196992250772</v>
+        <v>2.064428704774381</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.148063462869347</v>
+        <v>2.157457642273628</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.776158473308683</v>
+        <v>1.784275476559986</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.336635275819066</v>
+        <v>2.352681795885045</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.75435606817728</v>
+        <v>2.785180335897828</v>
       </c>
     </row>
     <row r="4">
@@ -762,85 +762,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.347650623308595</v>
+        <v>1.34765062330865</v>
       </c>
       <c r="C4" t="n">
-        <v>1.31694630119881</v>
+        <v>1.316946301198806</v>
       </c>
       <c r="D4" t="n">
-        <v>1.226536154524469</v>
+        <v>1.226536154524534</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6747004247495831</v>
+        <v>0.6747004247496382</v>
       </c>
       <c r="F4" t="n">
-        <v>1.104501073251321</v>
+        <v>1.104501073251269</v>
       </c>
       <c r="G4" t="n">
-        <v>2.183457606196623</v>
+        <v>2.18345760619653</v>
       </c>
       <c r="H4" t="n">
-        <v>1.333697772102358</v>
+        <v>1.333697772102366</v>
       </c>
       <c r="I4" t="n">
-        <v>1.425078692361956</v>
+        <v>1.425078692361985</v>
       </c>
       <c r="J4" t="n">
-        <v>1.752186678656816</v>
+        <v>1.752186678656859</v>
       </c>
       <c r="K4" t="n">
-        <v>1.937916466509011</v>
+        <v>1.937916466509015</v>
       </c>
       <c r="L4" t="n">
-        <v>1.243016671735028</v>
+        <v>1.243016671735099</v>
       </c>
       <c r="M4" t="n">
-        <v>2.477188918774697</v>
+        <v>2.477188918774707</v>
       </c>
       <c r="N4" t="n">
-        <v>1.514487843549658</v>
+        <v>1.514487843549706</v>
       </c>
       <c r="O4" t="n">
-        <v>1.69845312362696</v>
+        <v>1.698453123626899</v>
       </c>
       <c r="P4" t="n">
-        <v>1.648081430301739</v>
+        <v>1.648081430301661</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.288183272205244</v>
+        <v>1.288183272205011</v>
       </c>
       <c r="R4" t="n">
-        <v>1.515135444954236</v>
+        <v>1.515135444954239</v>
       </c>
       <c r="S4" t="n">
-        <v>1.780602839328738</v>
+        <v>1.78060283932857</v>
       </c>
       <c r="T4" t="n">
-        <v>1.442104784128799</v>
+        <v>1.442104784128831</v>
       </c>
       <c r="U4" t="n">
-        <v>1.605872651256625</v>
+        <v>1.605872651256437</v>
       </c>
       <c r="V4" t="n">
-        <v>1.640985178831222</v>
+        <v>1.640985178831219</v>
       </c>
       <c r="W4" t="n">
-        <v>1.434566307392051</v>
+        <v>1.434566307391872</v>
       </c>
       <c r="X4" t="n">
-        <v>1.32021118359239</v>
+        <v>1.32021118359237</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.361409555580023</v>
+        <v>1.361409555579907</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.408251609085547</v>
+        <v>1.408251609085416</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.761007905260932</v>
+        <v>1.761007905260941</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.413605046636127</v>
+        <v>2.413605046636117</v>
       </c>
     </row>
     <row r="5">
@@ -850,85 +850,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.179938679840494</v>
+        <v>6.179938679840317</v>
       </c>
       <c r="C5" t="n">
-        <v>6.083613081913717</v>
+        <v>6.083613081913732</v>
       </c>
       <c r="D5" t="n">
-        <v>4.212007948906155</v>
+        <v>4.212007948906224</v>
       </c>
       <c r="E5" t="n">
-        <v>-6.857789148252518</v>
+        <v>-6.857789148252394</v>
       </c>
       <c r="F5" t="n">
-        <v>1.64254383924977</v>
+        <v>1.642543839249677</v>
       </c>
       <c r="G5" t="n">
-        <v>22.31665771216294</v>
+        <v>22.31665771216291</v>
       </c>
       <c r="H5" t="n">
-        <v>6.740880473427985</v>
+        <v>6.740880473427927</v>
       </c>
       <c r="I5" t="n">
-        <v>8.523415897706906</v>
+        <v>8.523415897706926</v>
       </c>
       <c r="J5" t="n">
-        <v>14.3737997367639</v>
+        <v>14.37379973676394</v>
       </c>
       <c r="K5" t="n">
-        <v>19.19407742867345</v>
+        <v>19.19407742867341</v>
       </c>
       <c r="L5" t="n">
-        <v>4.374049493356805</v>
+        <v>4.374049493356969</v>
       </c>
       <c r="M5" t="n">
-        <v>31.21604892744288</v>
+        <v>31.21604892744264</v>
       </c>
       <c r="N5" t="n">
-        <v>10.07018886758688</v>
+        <v>10.07018886758702</v>
       </c>
       <c r="O5" t="n">
-        <v>12.48805427623221</v>
+        <v>12.48805427623239</v>
       </c>
       <c r="P5" t="n">
-        <v>11.90443919024092</v>
+        <v>11.90443919024089</v>
       </c>
       <c r="Q5" t="n">
-        <v>5.440818022125251</v>
+        <v>5.440818022125349</v>
       </c>
       <c r="R5" t="n">
-        <v>10.58866412859638</v>
+        <v>10.58866412859622</v>
       </c>
       <c r="S5" t="n">
-        <v>14.64097956167135</v>
+        <v>14.6409795616712</v>
       </c>
       <c r="T5" t="n">
-        <v>8.829557383705978</v>
+        <v>8.829557383706007</v>
       </c>
       <c r="U5" t="n">
-        <v>13.47589459118197</v>
+        <v>13.47589459118194</v>
       </c>
       <c r="V5" t="n">
-        <v>11.80525423683808</v>
+        <v>11.8052542368381</v>
       </c>
       <c r="W5" t="n">
-        <v>8.283046570782787</v>
+        <v>8.28304657078262</v>
       </c>
       <c r="X5" t="n">
-        <v>6.152122049592714</v>
+        <v>6.152122049592626</v>
       </c>
       <c r="Y5" t="n">
-        <v>8.883542823636054</v>
+        <v>8.883542823636017</v>
       </c>
       <c r="Z5" t="n">
-        <v>7.435628648135514</v>
+        <v>7.435628648135379</v>
       </c>
       <c r="AA5" t="n">
-        <v>14.9814803122032</v>
+        <v>14.98148031220333</v>
       </c>
       <c r="AB5" t="n">
-        <v>30.77354297217592</v>
+        <v>30.77354297217595</v>
       </c>
     </row>
     <row r="6">
@@ -938,85 +938,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.702436571950863</v>
+        <v>1.70243657195072</v>
       </c>
       <c r="C6" t="n">
-        <v>3.689340068091489</v>
+        <v>3.689340068091447</v>
       </c>
       <c r="D6" t="n">
-        <v>3.598929921417282</v>
+        <v>3.598929921417171</v>
       </c>
       <c r="E6" t="n">
-        <v>3.04709419164226</v>
+        <v>3.047094191642286</v>
       </c>
       <c r="F6" t="n">
-        <v>1.459287021893489</v>
+        <v>1.459287021893397</v>
       </c>
       <c r="G6" t="n">
-        <v>4.555851373089322</v>
+        <v>4.555851373089437</v>
       </c>
       <c r="H6" t="n">
-        <v>3.706091538995103</v>
+        <v>3.706091538995013</v>
       </c>
       <c r="I6" t="n">
-        <v>1.779864641004162</v>
+        <v>1.779864641004082</v>
       </c>
       <c r="J6" t="n">
-        <v>2.106972627299001</v>
+        <v>2.106972627299014</v>
       </c>
       <c r="K6" t="n">
-        <v>4.310310233401708</v>
+        <v>4.310310233401718</v>
       </c>
       <c r="L6" t="n">
-        <v>3.61541043862783</v>
+        <v>3.615410438627637</v>
       </c>
       <c r="M6" t="n">
-        <v>4.849582685667438</v>
+        <v>4.84958268566734</v>
       </c>
       <c r="N6" t="n">
-        <v>1.873444361252026</v>
+        <v>1.873444361252074</v>
       </c>
       <c r="O6" t="n">
-        <v>2.057410088281883</v>
+        <v>2.057410088282066</v>
       </c>
       <c r="P6" t="n">
-        <v>4.089644685492654</v>
+        <v>4.089644685492742</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.660577039098054</v>
+        <v>3.66057703909796</v>
       </c>
       <c r="R6" t="n">
-        <v>3.887529211846944</v>
+        <v>3.887529211846879</v>
       </c>
       <c r="S6" t="n">
-        <v>2.135388787970841</v>
+        <v>2.135388787970695</v>
       </c>
       <c r="T6" t="n">
-        <v>1.796890732770932</v>
+        <v>1.796890732770924</v>
       </c>
       <c r="U6" t="n">
-        <v>2.062060964505329</v>
+        <v>2.062060964505338</v>
       </c>
       <c r="V6" t="n">
-        <v>4.013378945723941</v>
+        <v>4.013378945723895</v>
       </c>
       <c r="W6" t="n">
-        <v>3.876126052280985</v>
+        <v>3.876126052280883</v>
       </c>
       <c r="X6" t="n">
-        <v>3.692604950485237</v>
+        <v>3.692604950485318</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.839270744140501</v>
+        <v>1.83927074414036</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.763037557727712</v>
+        <v>1.763037557727621</v>
       </c>
       <c r="AA6" t="n">
-        <v>4.133401672153678</v>
+        <v>4.133401672153773</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.777962745078249</v>
+        <v>2.777962745078243</v>
       </c>
     </row>
     <row r="7">
@@ -1029,82 +1029,82 @@
         <v>1.995428453226588</v>
       </c>
       <c r="C7" t="n">
-        <v>1.964724131116748</v>
+        <v>1.96472413111675</v>
       </c>
       <c r="D7" t="n">
-        <v>1.874313984442409</v>
+        <v>1.874313984442465</v>
       </c>
       <c r="E7" t="n">
-        <v>1.322478254667579</v>
+        <v>1.322478254667578</v>
       </c>
       <c r="F7" t="n">
-        <v>1.752278903169115</v>
+        <v>1.752278903169238</v>
       </c>
       <c r="G7" t="n">
-        <v>2.831235436114556</v>
+        <v>2.831235436114473</v>
       </c>
       <c r="H7" t="n">
-        <v>1.981475602020295</v>
+        <v>1.981475602020312</v>
       </c>
       <c r="I7" t="n">
-        <v>2.072856522279961</v>
+        <v>2.07285652227993</v>
       </c>
       <c r="J7" t="n">
-        <v>2.399964508574774</v>
+        <v>2.399964508574798</v>
       </c>
       <c r="K7" t="n">
-        <v>2.585694296426984</v>
+        <v>2.58569429642695</v>
       </c>
       <c r="L7" t="n">
-        <v>1.890794501653029</v>
+        <v>1.890794501653033</v>
       </c>
       <c r="M7" t="n">
-        <v>3.124966748692664</v>
+        <v>3.124966748692641</v>
       </c>
       <c r="N7" t="n">
-        <v>2.162265673467694</v>
+        <v>2.162265673467682</v>
       </c>
       <c r="O7" t="n">
-        <v>2.346230359438765</v>
+        <v>2.346230359438613</v>
       </c>
       <c r="P7" t="n">
-        <v>2.295858666113482</v>
+        <v>2.29585866611336</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.93596110212311</v>
+        <v>1.935961102123265</v>
       </c>
       <c r="R7" t="n">
-        <v>2.162913274872202</v>
+        <v>2.162913274872179</v>
       </c>
       <c r="S7" t="n">
-        <v>2.428380669246539</v>
+        <v>2.428380669246504</v>
       </c>
       <c r="T7" t="n">
-        <v>2.089882614046729</v>
+        <v>2.089882614046775</v>
       </c>
       <c r="U7" t="n">
-        <v>2.346851656501513</v>
+        <v>2.346851656501587</v>
       </c>
       <c r="V7" t="n">
-        <v>2.288763008749155</v>
+        <v>2.288763008749159</v>
       </c>
       <c r="W7" t="n">
-        <v>2.082344137309851</v>
+        <v>2.082344137309863</v>
       </c>
       <c r="X7" t="n">
-        <v>1.967989013510362</v>
+        <v>1.967989013510318</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.11058975010447</v>
+        <v>2.110589750104366</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.056029439003517</v>
+        <v>2.056029439003361</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.408785735178836</v>
+        <v>2.408785735178887</v>
       </c>
       <c r="AB7" t="n">
-        <v>3.061382876554031</v>
+        <v>3.061382876554005</v>
       </c>
     </row>
     <row r="8">
@@ -1114,85 +1114,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.744823649788991</v>
+        <v>3.744823649788819</v>
       </c>
       <c r="C8" t="n">
-        <v>5.294801624748196</v>
+        <v>5.294801624748182</v>
       </c>
       <c r="D8" t="n">
-        <v>5.204391478073911</v>
+        <v>5.204391478073921</v>
       </c>
       <c r="E8" t="n">
-        <v>3.810889052429096</v>
+        <v>3.810889052429063</v>
       </c>
       <c r="F8" t="n">
-        <v>3.747925927693685</v>
+        <v>3.747925927693752</v>
       </c>
       <c r="G8" t="n">
-        <v>6.489077701184924</v>
+        <v>6.48907770118501</v>
       </c>
       <c r="H8" t="n">
-        <v>5.311553095651711</v>
+        <v>5.311553095651794</v>
       </c>
       <c r="I8" t="n">
-        <v>5.402934015911308</v>
+        <v>5.4029340159114</v>
       </c>
       <c r="J8" t="n">
-        <v>5.730042002206195</v>
+        <v>5.730042002206262</v>
       </c>
       <c r="K8" t="n">
-        <v>5.915771790058367</v>
+        <v>5.915771790058516</v>
       </c>
       <c r="L8" t="n">
-        <v>5.220871995284593</v>
+        <v>5.220871995284538</v>
       </c>
       <c r="M8" t="n">
-        <v>6.455044242322407</v>
+        <v>6.455044242322458</v>
       </c>
       <c r="N8" t="n">
-        <v>4.267049944300641</v>
+        <v>4.267049944300739</v>
       </c>
       <c r="O8" t="n">
-        <v>4.787736440721995</v>
+        <v>4.787736440721873</v>
       </c>
       <c r="P8" t="n">
-        <v>4.654826240979707</v>
+        <v>4.654826240979594</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.37471615013648</v>
+        <v>3.374716150136602</v>
       </c>
       <c r="R8" t="n">
-        <v>5.492990768503612</v>
+        <v>5.492990768503655</v>
       </c>
       <c r="S8" t="n">
-        <v>5.758458162878102</v>
+        <v>5.758458162878062</v>
       </c>
       <c r="T8" t="n">
-        <v>5.419960107678317</v>
+        <v>5.419960107678223</v>
       </c>
       <c r="U8" t="n">
-        <v>4.907265147007153</v>
+        <v>4.907265147007195</v>
       </c>
       <c r="V8" t="n">
-        <v>5.179806530680773</v>
+        <v>5.179806530680823</v>
       </c>
       <c r="W8" t="n">
-        <v>5.412732279657233</v>
+        <v>5.412732279657096</v>
       </c>
       <c r="X8" t="n">
-        <v>3.551616734532737</v>
+        <v>3.551616734532748</v>
       </c>
       <c r="Y8" t="n">
-        <v>7.001431672168098</v>
+        <v>7.001431672168107</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.776062650400469</v>
+        <v>3.776062650400414</v>
       </c>
       <c r="AA8" t="n">
-        <v>5.738863228810372</v>
+        <v>5.738863228810358</v>
       </c>
       <c r="AB8" t="n">
-        <v>8.042615203418933</v>
+        <v>8.042615203419137</v>
       </c>
     </row>
     <row r="9">
@@ -1202,7 +1202,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>91.59761529184001</v>
+        <v>91.59761529183996</v>
       </c>
       <c r="C9" t="n">
         <v>116.5510440193439</v>
@@ -1211,16 +1211,16 @@
         <v>116.4606338726697</v>
       </c>
       <c r="E9" t="n">
-        <v>110.1425622017699</v>
+        <v>110.1425622017701</v>
       </c>
       <c r="F9" t="n">
-        <v>58.74335319625791</v>
+        <v>58.74335319625797</v>
       </c>
       <c r="G9" t="n">
-        <v>117.4175554001404</v>
+        <v>117.4175554001403</v>
       </c>
       <c r="H9" t="n">
-        <v>116.5677954902477</v>
+        <v>116.5677954902476</v>
       </c>
       <c r="I9" t="n">
         <v>116.659176410507</v>
@@ -1229,13 +1229,13 @@
         <v>116.986284396802</v>
       </c>
       <c r="K9" t="n">
-        <v>117.1720141846543</v>
+        <v>117.1720141846542</v>
       </c>
       <c r="L9" t="n">
-        <v>116.4771143898804</v>
+        <v>116.4771143898805</v>
       </c>
       <c r="M9" t="n">
-        <v>117.7112866369198</v>
+        <v>117.7112866369197</v>
       </c>
       <c r="N9" t="n">
         <v>116.7485855616948</v>
@@ -1247,7 +1247,7 @@
         <v>126.9625828805208</v>
       </c>
       <c r="Q9" t="n">
-        <v>116.5222810661489</v>
+        <v>116.522281066149</v>
       </c>
       <c r="R9" t="n">
         <v>116.7492331630993</v>
@@ -1256,31 +1256,31 @@
         <v>117.0147005574739</v>
       </c>
       <c r="T9" t="n">
-        <v>116.676202502274</v>
+        <v>116.6762025022738</v>
       </c>
       <c r="U9" t="n">
-        <v>116.9413727340082</v>
+        <v>116.9413727340083</v>
       </c>
       <c r="V9" t="n">
         <v>145.7062423945572</v>
       </c>
       <c r="W9" t="n">
-        <v>116.6686640255371</v>
+        <v>116.668664025537</v>
       </c>
       <c r="X9" t="n">
         <v>116.5543089017375</v>
       </c>
       <c r="Y9" t="n">
-        <v>116.6969096383317</v>
+        <v>116.6969096383316</v>
       </c>
       <c r="Z9" t="n">
-        <v>101.5791388042047</v>
+        <v>101.5791388042045</v>
       </c>
       <c r="AA9" t="n">
-        <v>116.9951056234061</v>
+        <v>116.9951056234062</v>
       </c>
       <c r="AB9" t="n">
-        <v>117.6477027647814</v>
+        <v>117.6477027647815</v>
       </c>
     </row>
   </sheetData>
@@ -1446,85 +1446,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.809041943515195</v>
+        <v>2.809041943515213</v>
       </c>
       <c r="C2" t="n">
-        <v>3.152241722889551</v>
+        <v>3.152241722889546</v>
       </c>
       <c r="D2" t="n">
-        <v>2.796148741812398</v>
+        <v>2.7961487418124</v>
       </c>
       <c r="E2" t="n">
-        <v>2.800216012872772</v>
+        <v>2.800216012872783</v>
       </c>
       <c r="F2" t="n">
-        <v>2.89928367254974</v>
+        <v>2.899283672549743</v>
       </c>
       <c r="G2" t="n">
-        <v>2.756360069512183</v>
+        <v>2.756360069512184</v>
       </c>
       <c r="H2" t="n">
-        <v>2.731359753714071</v>
+        <v>2.731359753714066</v>
       </c>
       <c r="I2" t="n">
-        <v>2.809548778643343</v>
+        <v>2.809548778643349</v>
       </c>
       <c r="J2" t="n">
-        <v>2.783492858527127</v>
+        <v>2.783492858527125</v>
       </c>
       <c r="K2" t="n">
-        <v>2.804449678018212</v>
+        <v>2.804449678018202</v>
       </c>
       <c r="L2" t="n">
-        <v>2.881680784806703</v>
+        <v>2.881680784806698</v>
       </c>
       <c r="M2" t="n">
-        <v>2.751818917689244</v>
+        <v>2.751818917689246</v>
       </c>
       <c r="N2" t="n">
-        <v>2.766444046033673</v>
+        <v>2.766444046033679</v>
       </c>
       <c r="O2" t="n">
-        <v>5.471662348216652</v>
+        <v>5.471662348216649</v>
       </c>
       <c r="P2" t="n">
-        <v>2.752159567879108</v>
+        <v>2.752159567879101</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.824727114000233</v>
+        <v>2.82472711400023</v>
       </c>
       <c r="R2" t="n">
-        <v>3.0337574589307</v>
+        <v>3.033757458930695</v>
       </c>
       <c r="S2" t="n">
         <v>2.845831693083122</v>
       </c>
       <c r="T2" t="n">
-        <v>2.767782319687004</v>
+        <v>2.767782319687011</v>
       </c>
       <c r="U2" t="n">
-        <v>3.745279812023359</v>
+        <v>3.745279812023357</v>
       </c>
       <c r="V2" t="n">
-        <v>2.774746036875109</v>
+        <v>2.774746036875105</v>
       </c>
       <c r="W2" t="n">
-        <v>4.025840966947647</v>
+        <v>4.025840966947649</v>
       </c>
       <c r="X2" t="n">
-        <v>2.793536330536034</v>
+        <v>2.793536330536044</v>
       </c>
       <c r="Y2" t="n">
         <v>2.774898819358032</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.164657445322198</v>
+        <v>3.164657445322204</v>
       </c>
       <c r="AA2" t="n">
         <v>2.765886257304916</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.777996010680378</v>
+        <v>2.77799601068038</v>
       </c>
     </row>
     <row r="3">
@@ -1534,85 +1534,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.317776959414795</v>
+        <v>3.350492305783701</v>
       </c>
       <c r="C3" t="n">
-        <v>4.048005587285722</v>
+        <v>4.088648389947265</v>
       </c>
       <c r="D3" t="n">
-        <v>3.229325506185035</v>
+        <v>3.259184779519327</v>
       </c>
       <c r="E3" t="n">
-        <v>3.255991667162872</v>
+        <v>3.286538485570951</v>
       </c>
       <c r="F3" t="n">
-        <v>3.967176549187474</v>
+        <v>4.023471209815138</v>
       </c>
       <c r="G3" t="n">
-        <v>2.943280047072128</v>
+        <v>2.96283104651907</v>
       </c>
       <c r="H3" t="n">
-        <v>2.768039130696609</v>
+        <v>2.781496310759906</v>
       </c>
       <c r="I3" t="n">
-        <v>3.326575761297418</v>
+        <v>3.359888954587603</v>
       </c>
       <c r="J3" t="n">
-        <v>3.137651421751841</v>
+        <v>3.164153435542103</v>
       </c>
       <c r="K3" t="n">
-        <v>3.2857640918014</v>
+        <v>3.317694531192784</v>
       </c>
       <c r="L3" t="n">
-        <v>3.833600072352799</v>
+        <v>3.884760506755328</v>
       </c>
       <c r="M3" t="n">
-        <v>2.925766563035486</v>
+        <v>2.944925878562594</v>
       </c>
       <c r="N3" t="n">
-        <v>3.018073155479077</v>
+        <v>3.040320513834721</v>
       </c>
       <c r="O3" t="n">
-        <v>7.324004420822305</v>
+        <v>7.338881478823013</v>
       </c>
       <c r="P3" t="n">
-        <v>2.913537688757799</v>
+        <v>2.932006239630911</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.431607472131176</v>
+        <v>3.468644525901644</v>
       </c>
       <c r="R3" t="n">
-        <v>4.933812642227076</v>
+        <v>5.024343030901363</v>
       </c>
       <c r="S3" t="n">
-        <v>3.578381820347384</v>
+        <v>3.620406827959743</v>
       </c>
       <c r="T3" t="n">
-        <v>3.028156624036592</v>
+        <v>3.050823152962203</v>
       </c>
       <c r="U3" t="n">
-        <v>4.513143528582212</v>
+        <v>4.529861298033645</v>
       </c>
       <c r="V3" t="n">
-        <v>3.073845879937239</v>
+        <v>3.098004961325551</v>
       </c>
       <c r="W3" t="n">
-        <v>5.242922410175809</v>
+        <v>5.271856473345801</v>
       </c>
       <c r="X3" t="n">
-        <v>3.210111194193686</v>
+        <v>3.239284769146032</v>
       </c>
       <c r="Y3" t="n">
-        <v>3.078187213670618</v>
+        <v>3.102540895211662</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.752376763358754</v>
+        <v>3.778189239352291</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.013679550442526</v>
+        <v>3.035745255290042</v>
       </c>
       <c r="AB3" t="n">
-        <v>3.109230515717361</v>
+        <v>3.134773089010599</v>
       </c>
     </row>
     <row r="4">
@@ -1622,85 +1622,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.176491067301426</v>
+        <v>3.176491067301449</v>
       </c>
       <c r="C4" t="n">
-        <v>3.512306231748476</v>
+        <v>3.512306231748388</v>
       </c>
       <c r="D4" t="n">
-        <v>3.030856422902626</v>
+        <v>3.030856422902517</v>
       </c>
       <c r="E4" t="n">
-        <v>3.076798120566651</v>
+        <v>3.076798120566582</v>
       </c>
       <c r="F4" t="n">
-        <v>4.195812909992911</v>
+        <v>4.195812909992958</v>
       </c>
       <c r="G4" t="n">
-        <v>2.581425065578173</v>
+        <v>2.581425065577989</v>
       </c>
       <c r="H4" t="n">
-        <v>2.299034997925073</v>
+        <v>2.299034997924898</v>
       </c>
       <c r="I4" t="n">
-        <v>3.182216003229695</v>
+        <v>3.18221600322957</v>
       </c>
       <c r="J4" t="n">
-        <v>2.886944105307483</v>
+        <v>2.886944105307427</v>
       </c>
       <c r="K4" t="n">
-        <v>3.124619315966492</v>
+        <v>3.124619315966396</v>
       </c>
       <c r="L4" t="n">
-        <v>3.996980195207051</v>
+        <v>3.99698019520692</v>
       </c>
       <c r="M4" t="n">
-        <v>2.552689142395347</v>
+        <v>2.552689142395328</v>
       </c>
       <c r="N4" t="n">
-        <v>2.695328219246667</v>
+        <v>2.695328219246641</v>
       </c>
       <c r="O4" t="n">
-        <v>2.371048131003984</v>
+        <v>2.371048131003938</v>
       </c>
       <c r="P4" t="n">
-        <v>2.533978467306139</v>
+        <v>2.533978467306222</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.353662283464772</v>
+        <v>3.353662283464855</v>
       </c>
       <c r="R4" t="n">
-        <v>5.714756188164023</v>
+        <v>5.714756188163859</v>
       </c>
       <c r="S4" t="n">
-        <v>3.592048212792113</v>
+        <v>3.592048212792057</v>
       </c>
       <c r="T4" t="n">
-        <v>2.710444635797293</v>
+        <v>2.710444635797244</v>
       </c>
       <c r="U4" t="n">
-        <v>2.34057131353277</v>
+        <v>2.340571313532688</v>
       </c>
       <c r="V4" t="n">
-        <v>2.783424530268543</v>
+        <v>2.783424530268545</v>
       </c>
       <c r="W4" t="n">
-        <v>2.997443433423884</v>
+        <v>2.997443433424006</v>
       </c>
       <c r="X4" t="n">
-        <v>3.001348035767339</v>
+        <v>3.001348035767389</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.6801901066164</v>
+        <v>2.680190106616331</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.863648443521898</v>
+        <v>2.863648443521914</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.689027738959851</v>
+        <v>2.689027738959951</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.838647957008925</v>
+        <v>2.838647957008962</v>
       </c>
     </row>
     <row r="5">
@@ -1710,85 +1710,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>21.47244479071007</v>
+        <v>21.47244479071006</v>
       </c>
       <c r="C5" t="n">
-        <v>28.69473844305295</v>
+        <v>28.69473844305301</v>
       </c>
       <c r="D5" t="n">
-        <v>20.7456659309608</v>
+        <v>20.74566593096063</v>
       </c>
       <c r="E5" t="n">
-        <v>20.33409347293477</v>
+        <v>20.33409347293479</v>
       </c>
       <c r="F5" t="n">
-        <v>42.2680864837731</v>
+        <v>42.26808648377296</v>
       </c>
       <c r="G5" t="n">
-        <v>11.7231136201221</v>
+        <v>11.72311362012149</v>
       </c>
       <c r="H5" t="n">
-        <v>8.380463876203017</v>
+        <v>8.380463876202986</v>
       </c>
       <c r="I5" t="n">
-        <v>24.25887794747432</v>
+        <v>24.25887794747409</v>
       </c>
       <c r="J5" t="n">
-        <v>17.51754816221369</v>
+        <v>17.51754816221367</v>
       </c>
       <c r="K5" t="n">
-        <v>20.9500811278148</v>
+        <v>20.95008112781436</v>
       </c>
       <c r="L5" t="n">
-        <v>34.63473408118438</v>
+        <v>34.63473408118436</v>
       </c>
       <c r="M5" t="n">
-        <v>12.58322856856416</v>
+        <v>12.58322856856396</v>
       </c>
       <c r="N5" t="n">
-        <v>15.20076458153757</v>
+        <v>15.20076458153752</v>
       </c>
       <c r="O5" t="n">
-        <v>8.41888430603502</v>
+        <v>8.41888430603507</v>
       </c>
       <c r="P5" t="n">
-        <v>11.00667403182578</v>
+        <v>11.00667403182588</v>
       </c>
       <c r="Q5" t="n">
-        <v>25.58269210432838</v>
+        <v>25.5826921043283</v>
       </c>
       <c r="R5" t="n">
-        <v>72.70366033248808</v>
+        <v>72.70366033248794</v>
       </c>
       <c r="S5" t="n">
-        <v>27.80373167549025</v>
+        <v>27.80373167549035</v>
       </c>
       <c r="T5" t="n">
-        <v>15.7438928721052</v>
+        <v>15.74389287210505</v>
       </c>
       <c r="U5" t="n">
-        <v>9.814887401668051</v>
+        <v>9.81488740166801</v>
       </c>
       <c r="V5" t="n">
-        <v>15.0507456405452</v>
+        <v>15.05074564054517</v>
       </c>
       <c r="W5" t="n">
-        <v>20.15155872856502</v>
+        <v>20.15155872856491</v>
       </c>
       <c r="X5" t="n">
-        <v>19.92868299595072</v>
+        <v>19.92868299595076</v>
       </c>
       <c r="Y5" t="n">
-        <v>16.77165251938766</v>
+        <v>16.77165251938746</v>
       </c>
       <c r="Z5" t="n">
-        <v>15.70271680902771</v>
+        <v>15.70271680902774</v>
       </c>
       <c r="AA5" t="n">
-        <v>14.87549044058911</v>
+        <v>14.87549044058895</v>
       </c>
       <c r="AB5" t="n">
-        <v>18.63571983479731</v>
+        <v>18.63571983479736</v>
       </c>
     </row>
     <row r="6">
@@ -1798,85 +1798,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.869159146182673</v>
+        <v>3.86915914618258</v>
       </c>
       <c r="C6" t="n">
-        <v>6.481755487484106</v>
+        <v>6.481755487484047</v>
       </c>
       <c r="D6" t="n">
-        <v>3.72352450178367</v>
+        <v>3.723524501783574</v>
       </c>
       <c r="E6" t="n">
-        <v>6.046247376302222</v>
+        <v>6.04624737630223</v>
       </c>
       <c r="F6" t="n">
-        <v>7.165262165728577</v>
+        <v>7.165262165728614</v>
       </c>
       <c r="G6" t="n">
-        <v>3.274093144459311</v>
+        <v>3.274093144459063</v>
       </c>
       <c r="H6" t="n">
-        <v>2.991703076806175</v>
+        <v>2.991703076805952</v>
       </c>
       <c r="I6" t="n">
-        <v>3.874884082110825</v>
+        <v>3.874884082110691</v>
       </c>
       <c r="J6" t="n">
-        <v>5.856393361043127</v>
+        <v>5.856393361043059</v>
       </c>
       <c r="K6" t="n">
-        <v>3.817287394847653</v>
+        <v>3.817287394847507</v>
       </c>
       <c r="L6" t="n">
-        <v>6.966429450942561</v>
+        <v>6.966429450942658</v>
       </c>
       <c r="M6" t="n">
-        <v>3.245357221276602</v>
+        <v>3.245357221276361</v>
       </c>
       <c r="N6" t="n">
-        <v>3.399629820812907</v>
+        <v>3.399629820812703</v>
       </c>
       <c r="O6" t="n">
-        <v>5.443729009579789</v>
+        <v>5.443729009579754</v>
       </c>
       <c r="P6" t="n">
-        <v>3.169329241890495</v>
+        <v>3.169329241890449</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.046330362346149</v>
+        <v>4.046330362346001</v>
       </c>
       <c r="R6" t="n">
-        <v>6.407424267045156</v>
+        <v>6.407424267044982</v>
       </c>
       <c r="S6" t="n">
-        <v>6.561497468527808</v>
+        <v>6.561497468527693</v>
       </c>
       <c r="T6" t="n">
-        <v>3.403112714678462</v>
+        <v>3.403112714678315</v>
       </c>
       <c r="U6" t="n">
-        <v>5.420659235985129</v>
+        <v>5.420659235985164</v>
       </c>
       <c r="V6" t="n">
-        <v>3.476092609149694</v>
+        <v>3.476092609149601</v>
       </c>
       <c r="W6" t="n">
-        <v>3.730747678532007</v>
+        <v>3.730747678531887</v>
       </c>
       <c r="X6" t="n">
-        <v>5.970797291503157</v>
+        <v>5.97079729150304</v>
       </c>
       <c r="Y6" t="n">
-        <v>3.513770027859336</v>
+        <v>3.513770027859278</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.556316522403186</v>
+        <v>3.55631652240297</v>
       </c>
       <c r="AA6" t="n">
-        <v>5.658476994695575</v>
+        <v>5.658476994695516</v>
       </c>
       <c r="AB6" t="n">
-        <v>3.512279893757289</v>
+        <v>3.51227989375728</v>
       </c>
     </row>
     <row r="7">
@@ -1886,85 +1886,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.990725233357601</v>
+        <v>3.990725233357499</v>
       </c>
       <c r="C7" t="n">
-        <v>4.326540397804594</v>
+        <v>4.326540397804435</v>
       </c>
       <c r="D7" t="n">
-        <v>3.845090588958684</v>
+        <v>3.845090588958547</v>
       </c>
       <c r="E7" t="n">
-        <v>3.89103228662274</v>
+        <v>3.891032286622625</v>
       </c>
       <c r="F7" t="n">
-        <v>5.010047076049004</v>
+        <v>5.010047076049007</v>
       </c>
       <c r="G7" t="n">
-        <v>3.395659231634267</v>
+        <v>3.395659231634026</v>
       </c>
       <c r="H7" t="n">
-        <v>3.113269163980942</v>
+        <v>3.113269163980951</v>
       </c>
       <c r="I7" t="n">
-        <v>3.996450169285594</v>
+        <v>3.996450169285601</v>
       </c>
       <c r="J7" t="n">
-        <v>3.701178271363522</v>
+        <v>3.701178271363456</v>
       </c>
       <c r="K7" t="n">
-        <v>3.938853482022456</v>
+        <v>3.938853482022424</v>
       </c>
       <c r="L7" t="n">
-        <v>4.811214361263011</v>
+        <v>4.811214361262923</v>
       </c>
       <c r="M7" t="n">
-        <v>3.366923308451403</v>
+        <v>3.366923308451367</v>
       </c>
       <c r="N7" t="n">
-        <v>3.509562385302631</v>
+        <v>3.509562385302688</v>
       </c>
       <c r="O7" t="n">
-        <v>3.185281466702098</v>
+        <v>3.185281466701944</v>
       </c>
       <c r="P7" t="n">
-        <v>3.348211803004288</v>
+        <v>3.348211803004236</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.167896449520918</v>
+        <v>4.167896449520913</v>
       </c>
       <c r="R7" t="n">
-        <v>6.528990354219928</v>
+        <v>6.528990354219903</v>
       </c>
       <c r="S7" t="n">
-        <v>4.406282378848146</v>
+        <v>4.406282378848097</v>
       </c>
       <c r="T7" t="n">
-        <v>3.524678801853352</v>
+        <v>3.524678801853291</v>
       </c>
       <c r="U7" t="n">
-        <v>3.252667162081594</v>
+        <v>3.252667162081552</v>
       </c>
       <c r="V7" t="n">
-        <v>3.59765869632459</v>
+        <v>3.597658696324585</v>
       </c>
       <c r="W7" t="n">
-        <v>3.811677599480038</v>
+        <v>3.811677599480048</v>
       </c>
       <c r="X7" t="n">
-        <v>3.81558220182352</v>
+        <v>3.815582201823443</v>
       </c>
       <c r="Y7" t="n">
-        <v>3.60506293938931</v>
+        <v>3.605062939389205</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.677882609577858</v>
+        <v>3.677882609577951</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.50326190501594</v>
+        <v>3.503261905015922</v>
       </c>
       <c r="AB7" t="n">
-        <v>3.652882123065014</v>
+        <v>3.652882123065005</v>
       </c>
     </row>
     <row r="8">
@@ -1974,85 +1974,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.893239328900029</v>
+        <v>5.89323932890002</v>
       </c>
       <c r="C8" t="n">
-        <v>8.284925264030239</v>
+        <v>8.284925264030054</v>
       </c>
       <c r="D8" t="n">
-        <v>7.803475455184202</v>
+        <v>7.803475455184165</v>
       </c>
       <c r="E8" t="n">
-        <v>6.754726613427803</v>
+        <v>6.754726613427819</v>
       </c>
       <c r="F8" t="n">
-        <v>7.232841809394575</v>
+        <v>7.232841809394508</v>
       </c>
       <c r="G8" t="n">
-        <v>7.780342294418055</v>
+        <v>7.780342294417848</v>
       </c>
       <c r="H8" t="n">
-        <v>7.071654030206687</v>
+        <v>7.071654030206552</v>
       </c>
       <c r="I8" t="n">
-        <v>7.954835035511359</v>
+        <v>7.954835035511205</v>
       </c>
       <c r="J8" t="n">
-        <v>7.659563137589265</v>
+        <v>7.659563137589119</v>
       </c>
       <c r="K8" t="n">
-        <v>7.89723834824802</v>
+        <v>7.89723834824806</v>
       </c>
       <c r="L8" t="n">
-        <v>8.769599227488644</v>
+        <v>8.769599227488564</v>
       </c>
       <c r="M8" t="n">
-        <v>7.325308174659528</v>
+        <v>7.325308174659462</v>
       </c>
       <c r="N8" t="n">
-        <v>5.874303462769506</v>
+        <v>5.874303462769513</v>
       </c>
       <c r="O8" t="n">
-        <v>5.987970521253543</v>
+        <v>5.987970521253409</v>
       </c>
       <c r="P8" t="n">
-        <v>6.043549430031432</v>
+        <v>6.043549430031278</v>
       </c>
       <c r="Q8" t="n">
-        <v>5.666385017722085</v>
+        <v>5.666385017722082</v>
       </c>
       <c r="R8" t="n">
-        <v>10.48737522044568</v>
+        <v>10.48737522044554</v>
       </c>
       <c r="S8" t="n">
-        <v>8.36466724507371</v>
+        <v>8.364667245073736</v>
       </c>
       <c r="T8" t="n">
-        <v>7.48306366807895</v>
+        <v>7.483063668078888</v>
       </c>
       <c r="U8" t="n">
-        <v>6.210484718822253</v>
+        <v>6.210484718822173</v>
       </c>
       <c r="V8" t="n">
-        <v>6.983222337851759</v>
+        <v>6.98322233785176</v>
       </c>
       <c r="W8" t="n">
-        <v>7.77046649593724</v>
+        <v>7.770466495937122</v>
       </c>
       <c r="X8" t="n">
-        <v>5.502495406748055</v>
+        <v>5.502495406747956</v>
       </c>
       <c r="Y8" t="n">
-        <v>9.590615233994351</v>
+        <v>9.590615233994283</v>
       </c>
       <c r="Z8" t="n">
-        <v>5.54220785077194</v>
+        <v>5.542207850771926</v>
       </c>
       <c r="AA8" t="n">
-        <v>7.461646771241617</v>
+        <v>7.461646771241472</v>
       </c>
       <c r="AB8" t="n">
-        <v>9.758795911426462</v>
+        <v>9.758795911426446</v>
       </c>
     </row>
     <row r="9">
@@ -2062,55 +2062,55 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>81.90574602773842</v>
+        <v>81.90574602773837</v>
       </c>
       <c r="C9" t="n">
-        <v>104.1580300639979</v>
+        <v>104.1580300639977</v>
       </c>
       <c r="D9" t="n">
         <v>103.6765802551521</v>
       </c>
       <c r="E9" t="n">
-        <v>98.66429096015668</v>
+        <v>98.66429096015662</v>
       </c>
       <c r="F9" t="n">
-        <v>54.31809335637372</v>
+        <v>54.31809335637366</v>
       </c>
       <c r="G9" t="n">
-        <v>103.2271497133558</v>
+        <v>103.2271497133556</v>
       </c>
       <c r="H9" t="n">
-        <v>102.9447588301746</v>
+        <v>102.9447588301745</v>
       </c>
       <c r="I9" t="n">
-        <v>103.8279398354792</v>
+        <v>103.827939835479</v>
       </c>
       <c r="J9" t="n">
-        <v>103.5326679375572</v>
+        <v>103.532667937557</v>
       </c>
       <c r="K9" t="n">
-        <v>103.770343148216</v>
+        <v>103.7703431482159</v>
       </c>
       <c r="L9" t="n">
-        <v>104.6427040274565</v>
+        <v>104.6427040274562</v>
       </c>
       <c r="M9" t="n">
-        <v>103.1984129746447</v>
+        <v>103.1984129746448</v>
       </c>
       <c r="N9" t="n">
-        <v>103.3410520514962</v>
+        <v>103.3410520514963</v>
       </c>
       <c r="O9" t="n">
-        <v>110.2798621359907</v>
+        <v>110.2798621359906</v>
       </c>
       <c r="P9" t="n">
-        <v>112.0223897938624</v>
+        <v>112.0223897938625</v>
       </c>
       <c r="Q9" t="n">
-        <v>103.9993869312424</v>
+        <v>103.9993869312422</v>
       </c>
       <c r="R9" t="n">
-        <v>106.3604800204135</v>
+        <v>106.3604800204134</v>
       </c>
       <c r="S9" t="n">
         <v>104.2377720450416</v>
@@ -2122,19 +2122,19 @@
         <v>103.0969338124991</v>
       </c>
       <c r="V9" t="n">
-        <v>128.7202893546561</v>
+        <v>128.720289354656</v>
       </c>
       <c r="W9" t="n">
-        <v>103.6431672656736</v>
+        <v>103.6431672656735</v>
       </c>
       <c r="X9" t="n">
-        <v>103.647071868017</v>
+        <v>103.6470718680169</v>
       </c>
       <c r="Y9" t="n">
-        <v>103.4365526055828</v>
+        <v>103.4365526055827</v>
       </c>
       <c r="Z9" t="n">
-        <v>90.29569075835599</v>
+        <v>90.2956907583559</v>
       </c>
       <c r="AA9" t="n">
         <v>103.3347515712094</v>
@@ -2306,85 +2306,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.168082108945144</v>
+        <v>2.168082108945212</v>
       </c>
       <c r="C2" t="n">
-        <v>2.216901382946137</v>
+        <v>2.216901382946109</v>
       </c>
       <c r="D2" t="n">
-        <v>2.177873119840965</v>
+        <v>2.17787311984098</v>
       </c>
       <c r="E2" t="n">
-        <v>2.135461476627222</v>
+        <v>2.135461476627226</v>
       </c>
       <c r="F2" t="n">
-        <v>2.1432049801101</v>
+        <v>2.143204980110115</v>
       </c>
       <c r="G2" t="n">
-        <v>2.268673688960418</v>
+        <v>2.268673688960445</v>
       </c>
       <c r="H2" t="n">
-        <v>2.156964212361835</v>
+        <v>2.156964212361851</v>
       </c>
       <c r="I2" t="n">
-        <v>2.18820558098718</v>
+        <v>2.188205580987199</v>
       </c>
       <c r="J2" t="n">
-        <v>2.219119337695812</v>
+        <v>2.21911933769582</v>
       </c>
       <c r="K2" t="n">
-        <v>2.210639059734772</v>
+        <v>2.2106390597348</v>
       </c>
       <c r="L2" t="n">
-        <v>2.160046274026537</v>
+        <v>2.160046274026629</v>
       </c>
       <c r="M2" t="n">
-        <v>2.258182091709591</v>
+        <v>2.25818209170962</v>
       </c>
       <c r="N2" t="n">
-        <v>2.183343543941915</v>
+        <v>2.183343543941937</v>
       </c>
       <c r="O2" t="n">
-        <v>4.092762901710411</v>
+        <v>4.092762901710448</v>
       </c>
       <c r="P2" t="n">
-        <v>2.205792506311462</v>
+        <v>2.205792506311483</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.171077853634222</v>
+        <v>2.171077853634239</v>
       </c>
       <c r="R2" t="n">
-        <v>2.169855274664966</v>
+        <v>2.169855274664981</v>
       </c>
       <c r="S2" t="n">
-        <v>2.211998136785232</v>
+        <v>2.211998136785276</v>
       </c>
       <c r="T2" t="n">
-        <v>2.180477957889689</v>
+        <v>2.180477957889715</v>
       </c>
       <c r="U2" t="n">
-        <v>2.481065290279762</v>
+        <v>2.481065290279779</v>
       </c>
       <c r="V2" t="n">
-        <v>2.196543452865878</v>
+        <v>2.196543452865883</v>
       </c>
       <c r="W2" t="n">
-        <v>2.591814920829963</v>
+        <v>2.591814920829989</v>
       </c>
       <c r="X2" t="n">
-        <v>2.183744697927139</v>
+        <v>2.18374469792717</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.195230021544365</v>
+        <v>2.195230021544385</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.049726918380394</v>
+        <v>2.049726918380453</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.187512278840144</v>
+        <v>2.187512278840167</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.262601079795424</v>
+        <v>2.262601079795459</v>
       </c>
     </row>
     <row r="3">
@@ -2394,85 +2394,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.269555486621395</v>
+        <v>2.27675366268736</v>
       </c>
       <c r="C3" t="n">
-        <v>2.362080076896108</v>
+        <v>2.36993553035032</v>
       </c>
       <c r="D3" t="n">
-        <v>2.340692698789418</v>
+        <v>2.35046281080231</v>
       </c>
       <c r="E3" t="n">
-        <v>2.037642634297543</v>
+        <v>2.036561329509842</v>
       </c>
       <c r="F3" t="n">
-        <v>2.092630591083693</v>
+        <v>2.093593409392419</v>
       </c>
       <c r="G3" t="n">
-        <v>2.985462046842675</v>
+        <v>3.01782786249219</v>
       </c>
       <c r="H3" t="n">
-        <v>2.191267171685162</v>
+        <v>2.195746297002375</v>
       </c>
       <c r="I3" t="n">
-        <v>2.414872181611513</v>
+        <v>2.427286112210227</v>
       </c>
       <c r="J3" t="n">
-        <v>2.633535989607565</v>
+        <v>2.653577350258885</v>
       </c>
       <c r="K3" t="n">
-        <v>2.573568951534607</v>
+        <v>2.591636436387613</v>
       </c>
       <c r="L3" t="n">
-        <v>2.212726677663932</v>
+        <v>2.217937550105912</v>
       </c>
       <c r="M3" t="n">
-        <v>2.916190145650626</v>
+        <v>2.946470132729973</v>
       </c>
       <c r="N3" t="n">
-        <v>2.379392647446862</v>
+        <v>2.390512171685016</v>
       </c>
       <c r="O3" t="n">
-        <v>5.600827847991666</v>
+        <v>5.615098610479788</v>
       </c>
       <c r="P3" t="n">
-        <v>2.537872602265523</v>
+        <v>2.554469973148821</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.291794964455014</v>
+        <v>2.299823376606701</v>
       </c>
       <c r="R3" t="n">
-        <v>2.283558208074835</v>
+        <v>2.291316050716622</v>
       </c>
       <c r="S3" t="n">
-        <v>2.582274411775789</v>
+        <v>2.600503731141286</v>
       </c>
       <c r="T3" t="n">
-        <v>2.35934697232421</v>
+        <v>2.369784086219904</v>
       </c>
       <c r="U3" t="n">
-        <v>2.981709243371733</v>
+        <v>2.997893657267003</v>
       </c>
       <c r="V3" t="n">
-        <v>2.471519093964826</v>
+        <v>2.48584314922403</v>
       </c>
       <c r="W3" t="n">
-        <v>3.072334556313607</v>
+        <v>3.084294012091901</v>
       </c>
       <c r="X3" t="n">
-        <v>2.382475090123267</v>
+        <v>2.393727050133465</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.463854353042939</v>
+        <v>2.477958268837163</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.167681015316982</v>
+        <v>2.179160524018045</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.408873783331863</v>
+        <v>2.421021114522905</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.946066158122954</v>
+        <v>2.977218266508773</v>
       </c>
     </row>
     <row r="4">
@@ -2482,85 +2482,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.57634022076185</v>
+        <v>1.576340220761828</v>
       </c>
       <c r="C4" t="n">
-        <v>1.602084107421983</v>
+        <v>1.602084107421846</v>
       </c>
       <c r="D4" t="n">
-        <v>1.686934192917683</v>
+        <v>1.686934192917628</v>
       </c>
       <c r="E4" t="n">
-        <v>1.207875172498648</v>
+        <v>1.207875172498492</v>
       </c>
       <c r="F4" t="n">
-        <v>1.295341606525345</v>
+        <v>1.295341606525202</v>
       </c>
       <c r="G4" t="n">
-        <v>2.712568391447358</v>
+        <v>2.712568391447318</v>
       </c>
       <c r="H4" t="n">
-        <v>1.450758464368243</v>
+        <v>1.450758464368141</v>
       </c>
       <c r="I4" t="n">
-        <v>1.803644094731138</v>
+        <v>1.80364409473108</v>
       </c>
       <c r="J4" t="n">
-        <v>2.151934513654954</v>
+        <v>2.151934513655024</v>
       </c>
       <c r="K4" t="n">
-        <v>2.057040557095286</v>
+        <v>2.057040557095103</v>
       </c>
       <c r="L4" t="n">
-        <v>1.485571768689467</v>
+        <v>1.485571768690377</v>
       </c>
       <c r="M4" t="n">
-        <v>2.594415229968675</v>
+        <v>2.594415229968609</v>
       </c>
       <c r="N4" t="n">
-        <v>1.748725149657322</v>
+        <v>1.748725149657172</v>
       </c>
       <c r="O4" t="n">
-        <v>1.896475583259466</v>
+        <v>1.896475583259319</v>
       </c>
       <c r="P4" t="n">
-        <v>2.002296506654262</v>
+        <v>2.002296506654151</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.610178535135609</v>
+        <v>1.610178535135625</v>
       </c>
       <c r="R4" t="n">
-        <v>1.596368943263753</v>
+        <v>1.596368943263692</v>
       </c>
       <c r="S4" t="n">
-        <v>2.07239195758654</v>
+        <v>2.072391957586402</v>
       </c>
       <c r="T4" t="n">
-        <v>1.716357036962706</v>
+        <v>1.716357036962679</v>
       </c>
       <c r="U4" t="n">
-        <v>1.817330530855734</v>
+        <v>1.817330530855512</v>
       </c>
       <c r="V4" t="n">
-        <v>1.89236847594569</v>
+        <v>1.892368475945701</v>
       </c>
       <c r="W4" t="n">
-        <v>1.787772652481693</v>
+        <v>1.787772652481577</v>
       </c>
       <c r="X4" t="n">
-        <v>1.753256368460361</v>
+        <v>1.753256368460846</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.721458868093043</v>
+        <v>1.721458868092892</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.769269603090141</v>
+        <v>1.769269603089865</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.795812928045607</v>
+        <v>1.795812928045536</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.637730460924446</v>
+        <v>2.637730460924272</v>
       </c>
     </row>
     <row r="5">
@@ -2570,85 +2570,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.002986987782032</v>
+        <v>6.002986987807001</v>
       </c>
       <c r="C5" t="n">
-        <v>6.964043697320839</v>
+        <v>6.964043697320731</v>
       </c>
       <c r="D5" t="n">
-        <v>8.7938821203582</v>
+        <v>8.793882120358401</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.46213953050052</v>
+        <v>-0.4621395304986993</v>
       </c>
       <c r="F5" t="n">
-        <v>1.037160792433367</v>
+        <v>1.037160792433215</v>
       </c>
       <c r="G5" t="n">
-        <v>26.36294116762158</v>
+        <v>26.36294116762153</v>
       </c>
       <c r="H5" t="n">
-        <v>4.218391597220759</v>
+        <v>4.21839159722068</v>
       </c>
       <c r="I5" t="n">
-        <v>11.24321125559396</v>
+        <v>11.24321125559574</v>
       </c>
       <c r="J5" t="n">
-        <v>16.74949194066296</v>
+        <v>16.74949194066504</v>
       </c>
       <c r="K5" t="n">
-        <v>15.24907241994685</v>
+        <v>15.2490724199463</v>
       </c>
       <c r="L5" t="n">
-        <v>4.577805519112711</v>
+        <v>4.577805519147105</v>
       </c>
       <c r="M5" t="n">
-        <v>27.14029734250866</v>
+        <v>27.1402973425086</v>
       </c>
       <c r="N5" t="n">
-        <v>9.771603527381753</v>
+        <v>9.77160352738237</v>
       </c>
       <c r="O5" t="n">
-        <v>11.35534008838202</v>
+        <v>11.35534008838198</v>
       </c>
       <c r="P5" t="n">
-        <v>13.59873044498278</v>
+        <v>13.59873044498314</v>
       </c>
       <c r="Q5" t="n">
-        <v>7.120365789075819</v>
+        <v>7.120365789078404</v>
       </c>
       <c r="R5" t="n">
-        <v>7.131130746349735</v>
+        <v>7.131130746349377</v>
       </c>
       <c r="S5" t="n">
-        <v>14.98633057051932</v>
+        <v>14.98633057051259</v>
       </c>
       <c r="T5" t="n">
-        <v>9.385474576635724</v>
+        <v>9.385474576635616</v>
       </c>
       <c r="U5" t="n">
-        <v>13.6359337024102</v>
+        <v>13.63593370240997</v>
       </c>
       <c r="V5" t="n">
-        <v>11.42741071877093</v>
+        <v>11.42741071877096</v>
       </c>
       <c r="W5" t="n">
-        <v>10.35373733200568</v>
+        <v>10.35373733200685</v>
       </c>
       <c r="X5" t="n">
-        <v>9.979291778996409</v>
+        <v>9.979291779006243</v>
       </c>
       <c r="Y5" t="n">
-        <v>12.10297441181771</v>
+        <v>12.10297441181751</v>
       </c>
       <c r="Z5" t="n">
-        <v>9.530677579835931</v>
+        <v>9.5306775798431</v>
       </c>
       <c r="AA5" t="n">
-        <v>10.51103233945868</v>
+        <v>10.51103233946008</v>
       </c>
       <c r="AB5" t="n">
-        <v>29.02877344504801</v>
+        <v>29.02877344504783</v>
       </c>
     </row>
     <row r="6">
@@ -2658,85 +2658,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.962281233513149</v>
+        <v>1.962281233513555</v>
       </c>
       <c r="C6" t="n">
-        <v>4.017401565220974</v>
+        <v>4.017401565220681</v>
       </c>
       <c r="D6" t="n">
-        <v>2.072875205668986</v>
+        <v>2.072875205668749</v>
       </c>
       <c r="E6" t="n">
-        <v>3.623192630297641</v>
+        <v>3.623192630297701</v>
       </c>
       <c r="F6" t="n">
-        <v>1.681282619276649</v>
+        <v>1.681282619276456</v>
       </c>
       <c r="G6" t="n">
-        <v>5.127885849246345</v>
+        <v>5.127885849246227</v>
       </c>
       <c r="H6" t="n">
-        <v>3.866075922167237</v>
+        <v>3.866075922167135</v>
       </c>
       <c r="I6" t="n">
-        <v>4.218961552530127</v>
+        <v>4.218961552530004</v>
       </c>
       <c r="J6" t="n">
-        <v>4.567251971453947</v>
+        <v>4.567251971454024</v>
       </c>
       <c r="K6" t="n">
-        <v>2.442981569846591</v>
+        <v>2.442981569846516</v>
       </c>
       <c r="L6" t="n">
-        <v>3.900889226488458</v>
+        <v>3.900889226487543</v>
       </c>
       <c r="M6" t="n">
-        <v>5.009732687767665</v>
+        <v>5.009732687767507</v>
       </c>
       <c r="N6" t="n">
-        <v>2.156337256721684</v>
+        <v>2.15633725672155</v>
       </c>
       <c r="O6" t="n">
-        <v>2.284078706151775</v>
+        <v>2.284078706151607</v>
       </c>
       <c r="P6" t="n">
-        <v>4.537781734475918</v>
+        <v>4.537781734475682</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.996119547886913</v>
+        <v>1.99611954788703</v>
       </c>
       <c r="R6" t="n">
-        <v>4.011686401062749</v>
+        <v>4.011686401062705</v>
       </c>
       <c r="S6" t="n">
-        <v>2.458332970337847</v>
+        <v>2.458332970337678</v>
       </c>
       <c r="T6" t="n">
-        <v>2.10229804971401</v>
+        <v>2.102298049713955</v>
       </c>
       <c r="U6" t="n">
-        <v>2.364801057740833</v>
+        <v>2.3648010577406</v>
       </c>
       <c r="V6" t="n">
-        <v>2.278309488696995</v>
+        <v>2.278309488697</v>
       </c>
       <c r="W6" t="n">
         <v>2.200559852662648</v>
       </c>
       <c r="X6" t="n">
-        <v>4.168573826259354</v>
+        <v>4.168573826259308</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.289829995539265</v>
+        <v>2.28982999553899</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.155210615841448</v>
+        <v>2.155210615841289</v>
       </c>
       <c r="AA6" t="n">
-        <v>4.211130385844601</v>
+        <v>4.211130385844525</v>
       </c>
       <c r="AB6" t="n">
-        <v>3.02644403488889</v>
+        <v>3.026444034888786</v>
       </c>
     </row>
     <row r="7">
@@ -2746,85 +2746,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.273877158399645</v>
+        <v>2.273877158399421</v>
       </c>
       <c r="C7" t="n">
-        <v>2.299621045059779</v>
+        <v>2.299621045059727</v>
       </c>
       <c r="D7" t="n">
-        <v>2.384471130555482</v>
+        <v>2.384471130555399</v>
       </c>
       <c r="E7" t="n">
-        <v>1.905412110136443</v>
+        <v>1.905412110136561</v>
       </c>
       <c r="F7" t="n">
-        <v>1.99287854416314</v>
+        <v>1.992878544163062</v>
       </c>
       <c r="G7" t="n">
-        <v>3.410105329085152</v>
+        <v>3.410105329085063</v>
       </c>
       <c r="H7" t="n">
-        <v>2.148295402006037</v>
+        <v>2.148295402005971</v>
       </c>
       <c r="I7" t="n">
-        <v>2.501181032368933</v>
+        <v>2.501181032368815</v>
       </c>
       <c r="J7" t="n">
-        <v>2.849471451292751</v>
+        <v>2.849471451292765</v>
       </c>
       <c r="K7" t="n">
-        <v>2.754577494733081</v>
+        <v>2.754577494732933</v>
       </c>
       <c r="L7" t="n">
-        <v>2.183108706327268</v>
+        <v>2.183108706326578</v>
       </c>
       <c r="M7" t="n">
-        <v>3.29195216760647</v>
+        <v>3.291952167606391</v>
       </c>
       <c r="N7" t="n">
-        <v>2.446262087295117</v>
+        <v>2.446262087295041</v>
       </c>
       <c r="O7" t="n">
-        <v>2.594026344927076</v>
+        <v>2.594026344926962</v>
       </c>
       <c r="P7" t="n">
-        <v>2.699847268321875</v>
+        <v>2.699847268321736</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.307715472773404</v>
+        <v>2.307715472773341</v>
       </c>
       <c r="R7" t="n">
-        <v>2.293905880901551</v>
+        <v>2.293905880901401</v>
       </c>
       <c r="S7" t="n">
-        <v>2.769928895224339</v>
+        <v>2.769928895224511</v>
       </c>
       <c r="T7" t="n">
-        <v>2.413893974600505</v>
+        <v>2.413893974600296</v>
       </c>
       <c r="U7" t="n">
-        <v>2.650870069989817</v>
+        <v>2.650870069989738</v>
       </c>
       <c r="V7" t="n">
-        <v>2.589905413583486</v>
+        <v>2.589905413583502</v>
       </c>
       <c r="W7" t="n">
-        <v>2.485309590119489</v>
+        <v>2.485309590119421</v>
       </c>
       <c r="X7" t="n">
-        <v>2.450793306098159</v>
+        <v>2.450793306098382</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.580525319864633</v>
+        <v>2.580525319864468</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.466806540727938</v>
+        <v>2.466806540727785</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.493349865683403</v>
+        <v>2.493349865683342</v>
       </c>
       <c r="AB7" t="n">
-        <v>3.335267398562243</v>
+        <v>3.335267398562174</v>
       </c>
     </row>
     <row r="8">
@@ -2834,85 +2834,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.03553055897158</v>
+        <v>4.035530558971844</v>
       </c>
       <c r="C8" t="n">
-        <v>5.762586117804624</v>
+        <v>5.762586117804484</v>
       </c>
       <c r="D8" t="n">
-        <v>5.847436203300328</v>
+        <v>5.847436203300181</v>
       </c>
       <c r="E8" t="n">
-        <v>4.462478903547982</v>
+        <v>4.462478903548145</v>
       </c>
       <c r="F8" t="n">
-        <v>4.019576419333249</v>
+        <v>4.019576419333114</v>
       </c>
       <c r="G8" t="n">
-        <v>7.225848459988313</v>
+        <v>7.225848459988226</v>
       </c>
       <c r="H8" t="n">
-        <v>5.611260474750888</v>
+        <v>5.611260474750693</v>
       </c>
       <c r="I8" t="n">
-        <v>5.964146105113796</v>
+        <v>5.964146105113579</v>
       </c>
       <c r="J8" t="n">
-        <v>6.312436524037602</v>
+        <v>6.312436524037621</v>
       </c>
       <c r="K8" t="n">
-        <v>6.217542567477937</v>
+        <v>6.217542567477706</v>
       </c>
       <c r="L8" t="n">
-        <v>5.646073779072125</v>
+        <v>5.646073779072176</v>
       </c>
       <c r="M8" t="n">
-        <v>6.754917240339745</v>
+        <v>6.754917240339561</v>
       </c>
       <c r="N8" t="n">
-        <v>4.590425990302834</v>
+        <v>4.590425990302752</v>
       </c>
       <c r="O8" t="n">
-        <v>5.100594435062149</v>
+        <v>5.100594435062145</v>
       </c>
       <c r="P8" t="n">
-        <v>5.117577946818516</v>
+        <v>5.117577946818452</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.735022299857597</v>
+        <v>3.735022299857529</v>
       </c>
       <c r="R8" t="n">
-        <v>5.756870953646401</v>
+        <v>5.756870953646251</v>
       </c>
       <c r="S8" t="n">
-        <v>6.232893967969198</v>
+        <v>6.232893967969275</v>
       </c>
       <c r="T8" t="n">
-        <v>5.876859047345349</v>
+        <v>5.876859047345189</v>
       </c>
       <c r="U8" t="n">
-        <v>5.289181089999607</v>
+        <v>5.289181089999522</v>
       </c>
       <c r="V8" t="n">
-        <v>5.566044762877068</v>
+        <v>5.566044762877095</v>
       </c>
       <c r="W8" t="n">
-        <v>5.948609016987405</v>
+        <v>5.94860901698731</v>
       </c>
       <c r="X8" t="n">
-        <v>4.034028727060011</v>
+        <v>4.034028727060361</v>
       </c>
       <c r="Y8" t="n">
-        <v>7.701205039445014</v>
+        <v>7.701205039445012</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.196857203738488</v>
+        <v>4.196857203738367</v>
       </c>
       <c r="AA8" t="n">
-        <v>5.956314938428269</v>
+        <v>5.956314938428182</v>
       </c>
       <c r="AB8" t="n">
-        <v>8.575394772026483</v>
+        <v>8.575394772026408</v>
       </c>
     </row>
     <row r="9">
@@ -2922,19 +2922,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>86.09660874291033</v>
+        <v>86.09660874291049</v>
       </c>
       <c r="C9" t="n">
         <v>109.5572620330949</v>
       </c>
       <c r="D9" t="n">
-        <v>109.6421121185906</v>
+        <v>109.6421121185905</v>
       </c>
       <c r="E9" t="n">
         <v>103.7543718482869</v>
       </c>
       <c r="F9" t="n">
-        <v>55.22665693722494</v>
+        <v>55.22665693722486</v>
       </c>
       <c r="G9" t="n">
         <v>110.6677466436856</v>
@@ -2943,64 +2943,64 @@
         <v>109.4059363900413</v>
       </c>
       <c r="I9" t="n">
-        <v>109.7588220204041</v>
+        <v>109.7588220204039</v>
       </c>
       <c r="J9" t="n">
         <v>110.1071124393279</v>
       </c>
       <c r="K9" t="n">
-        <v>110.0122184827684</v>
+        <v>110.0122184827683</v>
       </c>
       <c r="L9" t="n">
-        <v>109.4407496943624</v>
+        <v>109.4407496943619</v>
       </c>
       <c r="M9" t="n">
-        <v>110.5495931556417</v>
+        <v>110.5495931556415</v>
       </c>
       <c r="N9" t="n">
         <v>109.7039030753304</v>
       </c>
       <c r="O9" t="n">
-        <v>117.6179522346455</v>
+        <v>117.6179522346453</v>
       </c>
       <c r="P9" t="n">
-        <v>119.4128098126191</v>
+        <v>119.412809812619</v>
       </c>
       <c r="Q9" t="n">
         <v>109.565356787374</v>
       </c>
       <c r="R9" t="n">
-        <v>109.5515468689368</v>
+        <v>109.5515468689366</v>
       </c>
       <c r="S9" t="n">
-        <v>110.0275698832595</v>
+        <v>110.0275698832597</v>
       </c>
       <c r="T9" t="n">
-        <v>109.6715349626359</v>
+        <v>109.6715349626358</v>
       </c>
       <c r="U9" t="n">
-        <v>109.9340379706625</v>
+        <v>109.9340379706623</v>
       </c>
       <c r="V9" t="n">
-        <v>136.8909350037817</v>
+        <v>136.8909350037818</v>
       </c>
       <c r="W9" t="n">
         <v>109.7429505781547</v>
       </c>
       <c r="X9" t="n">
-        <v>109.7084342941332</v>
+        <v>109.7084342941333</v>
       </c>
       <c r="Y9" t="n">
-        <v>109.8381663078999</v>
+        <v>109.8381663078996</v>
       </c>
       <c r="Z9" t="n">
-        <v>95.59528120156402</v>
+        <v>95.59528120156391</v>
       </c>
       <c r="AA9" t="n">
-        <v>109.7509908537184</v>
+        <v>109.7509908537183</v>
       </c>
       <c r="AB9" t="n">
-        <v>110.5929083865975</v>
+        <v>110.5929083865973</v>
       </c>
     </row>
   </sheetData>
@@ -3166,82 +3166,82 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.453419964662416</v>
+        <v>2.453419964662404</v>
       </c>
       <c r="C2" t="n">
-        <v>2.626995143814092</v>
+        <v>2.626995143814096</v>
       </c>
       <c r="D2" t="n">
-        <v>2.473989551268937</v>
+        <v>2.47398955126893</v>
       </c>
       <c r="E2" t="n">
-        <v>2.438692898553376</v>
+        <v>2.438692898553366</v>
       </c>
       <c r="F2" t="n">
-        <v>2.448843060475884</v>
+        <v>2.44884306047588</v>
       </c>
       <c r="G2" t="n">
-        <v>2.548900167041889</v>
+        <v>2.54890016704188</v>
       </c>
       <c r="H2" t="n">
-        <v>2.432364444275146</v>
+        <v>2.432364444275138</v>
       </c>
       <c r="I2" t="n">
-        <v>2.574970772112184</v>
+        <v>2.574970772112172</v>
       </c>
       <c r="J2" t="n">
-        <v>2.503404569586984</v>
+        <v>2.503404569586976</v>
       </c>
       <c r="K2" t="n">
-        <v>2.487437928382304</v>
+        <v>2.487437928382289</v>
       </c>
       <c r="L2" t="n">
-        <v>2.438968534113647</v>
+        <v>2.438968534113643</v>
       </c>
       <c r="M2" t="n">
-        <v>2.532400950915515</v>
+        <v>2.532400950915513</v>
       </c>
       <c r="N2" t="n">
-        <v>2.466242149191717</v>
+        <v>2.466242149191705</v>
       </c>
       <c r="O2" t="n">
-        <v>4.782909179304437</v>
+        <v>4.782909179304439</v>
       </c>
       <c r="P2" t="n">
-        <v>2.483998430156825</v>
+        <v>2.483998430156817</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.531301236892553</v>
+        <v>2.531301236892542</v>
       </c>
       <c r="R2" t="n">
-        <v>2.440044987221174</v>
+        <v>2.440044987221154</v>
       </c>
       <c r="S2" t="n">
-        <v>2.489698541232685</v>
+        <v>2.489698541232663</v>
       </c>
       <c r="T2" t="n">
-        <v>2.450842071293208</v>
+        <v>2.4508420712932</v>
       </c>
       <c r="U2" t="n">
-        <v>3.101879905228496</v>
+        <v>3.101879905228487</v>
       </c>
       <c r="V2" t="n">
-        <v>2.472144400491767</v>
+        <v>2.472144400491755</v>
       </c>
       <c r="W2" t="n">
-        <v>3.287952029158704</v>
+        <v>3.2879520291587</v>
       </c>
       <c r="X2" t="n">
-        <v>2.470711563775557</v>
+        <v>2.470711563775546</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.507428412867821</v>
+        <v>2.50742841286781</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.539968668909805</v>
+        <v>2.539968668909796</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.461506003044015</v>
+        <v>2.461506003044001</v>
       </c>
       <c r="AB2" t="n">
         <v>2.533299561763501</v>
@@ -3254,85 +3254,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.565006189611169</v>
+        <v>2.576845008931436</v>
       </c>
       <c r="C3" t="n">
-        <v>2.876435259531389</v>
+        <v>2.889566622595992</v>
       </c>
       <c r="D3" t="n">
-        <v>2.713509697857539</v>
+        <v>2.73069475317921</v>
       </c>
       <c r="E3" t="n">
-        <v>2.460889526665913</v>
+        <v>2.468959757292359</v>
       </c>
       <c r="F3" t="n">
-        <v>2.53366623092814</v>
+        <v>2.544499028750407</v>
       </c>
       <c r="G3" t="n">
-        <v>3.243818282374086</v>
+        <v>3.279547371373831</v>
       </c>
       <c r="H3" t="n">
-        <v>2.415933460000844</v>
+        <v>2.422566151071949</v>
       </c>
       <c r="I3" t="n">
-        <v>3.437067559473986</v>
+        <v>3.479968487642152</v>
       </c>
       <c r="J3" t="n">
-        <v>2.921406060571524</v>
+        <v>2.945857205887371</v>
       </c>
       <c r="K3" t="n">
-        <v>2.807322418228535</v>
+        <v>2.827899022066785</v>
       </c>
       <c r="L3" t="n">
-        <v>2.462535468701751</v>
+        <v>2.470787799979373</v>
       </c>
       <c r="M3" t="n">
-        <v>3.136205710164303</v>
+        <v>3.168492411821974</v>
       </c>
       <c r="N3" t="n">
-        <v>2.657687199998333</v>
+        <v>2.672857586024026</v>
       </c>
       <c r="O3" t="n">
-        <v>6.509654523850386</v>
+        <v>6.526064164370408</v>
       </c>
       <c r="P3" t="n">
-        <v>2.782298083281682</v>
+        <v>2.801751748239492</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.121869630901965</v>
+        <v>3.153537556586109</v>
       </c>
       <c r="R3" t="n">
-        <v>2.470874883229782</v>
+        <v>2.479458211195172</v>
       </c>
       <c r="S3" t="n">
-        <v>2.823151563675806</v>
+        <v>2.844113408516741</v>
       </c>
       <c r="T3" t="n">
-        <v>2.547992024665115</v>
+        <v>2.559303692586818</v>
       </c>
       <c r="U3" t="n">
-        <v>3.690534903240704</v>
+        <v>3.704932149248692</v>
       </c>
       <c r="V3" t="n">
-        <v>2.697488746482838</v>
+        <v>2.714018864808797</v>
       </c>
       <c r="W3" t="n">
-        <v>4.036602007655728</v>
+        <v>4.05278651356665</v>
       </c>
       <c r="X3" t="n">
-        <v>2.689790128955983</v>
+        <v>2.706130884752378</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.951166947576512</v>
+        <v>2.97671491302463</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.854215898722316</v>
+        <v>2.872811164798535</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.623548638416294</v>
+        <v>2.637496233460372</v>
       </c>
       <c r="AB3" t="n">
-        <v>3.140663686905979</v>
+        <v>3.172919968308096</v>
       </c>
     </row>
     <row r="4">
@@ -3342,85 +3342,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.002717717841945</v>
+        <v>2.002717717842013</v>
       </c>
       <c r="C4" t="n">
-        <v>2.055219505038089</v>
+        <v>2.055219505038099</v>
       </c>
       <c r="D4" t="n">
-        <v>2.23506066104001</v>
+        <v>2.235060661040031</v>
       </c>
       <c r="E4" t="n">
-        <v>1.836368731355141</v>
+        <v>1.836368731355256</v>
       </c>
       <c r="F4" t="n">
-        <v>1.951019479575219</v>
+        <v>1.951019479575269</v>
       </c>
       <c r="G4" t="n">
-        <v>3.081210526781109</v>
+        <v>3.081210526781279</v>
       </c>
       <c r="H4" t="n">
-        <v>1.764885929049863</v>
+        <v>1.764885929049925</v>
       </c>
       <c r="I4" t="n">
-        <v>3.375690004120959</v>
+        <v>3.37569000412112</v>
       </c>
       <c r="J4" t="n">
-        <v>2.566269005068436</v>
+        <v>2.566269005068424</v>
       </c>
       <c r="K4" t="n">
-        <v>2.386966267094508</v>
+        <v>2.386966267094553</v>
       </c>
       <c r="L4" t="n">
-        <v>1.839482161807046</v>
+        <v>1.839482161807187</v>
       </c>
       <c r="M4" t="n">
-        <v>2.902021137689511</v>
+        <v>2.902021137689664</v>
       </c>
       <c r="N4" t="n">
-        <v>2.147550190596721</v>
+        <v>2.147550190596748</v>
       </c>
       <c r="O4" t="n">
-        <v>2.209824810043137</v>
+        <v>2.209824810043226</v>
       </c>
       <c r="P4" t="n">
-        <v>2.34811555239045</v>
+        <v>2.34811555239051</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.882422514836704</v>
+        <v>2.882422514836705</v>
       </c>
       <c r="R4" t="n">
-        <v>1.851641194849468</v>
+        <v>1.851641194849512</v>
       </c>
       <c r="S4" t="n">
-        <v>2.412500929172737</v>
+        <v>2.412500929172839</v>
       </c>
       <c r="T4" t="n">
-        <v>1.97359922634713</v>
+        <v>1.973599226347285</v>
       </c>
       <c r="U4" t="n">
-        <v>1.989169598146258</v>
+        <v>1.989169598146397</v>
       </c>
       <c r="V4" t="n">
-        <v>2.207766217166742</v>
+        <v>2.207766217166739</v>
       </c>
       <c r="W4" t="n">
-        <v>2.194671579938301</v>
+        <v>2.194671579938325</v>
       </c>
       <c r="X4" t="n">
-        <v>2.198034284353468</v>
+        <v>2.198034284353526</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.48612245057579</v>
+        <v>2.486122450575844</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.307222394845091</v>
+        <v>2.307222394845238</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.094053241123401</v>
+        <v>2.094053241123551</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.905159014872639</v>
+        <v>2.905159014872656</v>
       </c>
     </row>
     <row r="5">
@@ -3430,85 +3430,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7.706483068032112</v>
+        <v>7.706483068032099</v>
       </c>
       <c r="C5" t="n">
-        <v>9.043075537234602</v>
+        <v>9.043075537234753</v>
       </c>
       <c r="D5" t="n">
-        <v>12.69545654857521</v>
+        <v>12.69545654857535</v>
       </c>
       <c r="E5" t="n">
-        <v>5.277961013070643</v>
+        <v>5.277961013070784</v>
       </c>
       <c r="F5" t="n">
-        <v>7.479091012128017</v>
+        <v>7.479091012128073</v>
       </c>
       <c r="G5" t="n">
-        <v>25.41595261665468</v>
+        <v>25.41595261665475</v>
       </c>
       <c r="H5" t="n">
-        <v>4.122718164939069</v>
+        <v>4.122718164939123</v>
       </c>
       <c r="I5" t="n">
-        <v>34.34623351929242</v>
+        <v>34.34623351929259</v>
       </c>
       <c r="J5" t="n">
-        <v>17.51368256469455</v>
+        <v>17.51368256469459</v>
       </c>
       <c r="K5" t="n">
-        <v>14.25811945266216</v>
+        <v>14.25811945266222</v>
       </c>
       <c r="L5" t="n">
-        <v>5.166530545066538</v>
+        <v>5.166530545066746</v>
       </c>
       <c r="M5" t="n">
-        <v>25.48239985553471</v>
+        <v>25.48239985553494</v>
       </c>
       <c r="N5" t="n">
-        <v>10.87359888260971</v>
+        <v>10.87359888260978</v>
       </c>
       <c r="O5" t="n">
-        <v>10.75025785744783</v>
+        <v>10.75025785744791</v>
       </c>
       <c r="P5" t="n">
-        <v>13.32406471668432</v>
+        <v>13.32406471668434</v>
       </c>
       <c r="Q5" t="n">
-        <v>23.79457937315783</v>
+        <v>23.79457937315802</v>
       </c>
       <c r="R5" t="n">
-        <v>5.721909046612894</v>
+        <v>5.721909046612978</v>
       </c>
       <c r="S5" t="n">
-        <v>14.55170368717884</v>
+        <v>14.55170368717896</v>
       </c>
       <c r="T5" t="n">
-        <v>7.908898803432757</v>
+        <v>7.908898803432804</v>
       </c>
       <c r="U5" t="n">
-        <v>9.828097057082172</v>
+        <v>9.828097057081724</v>
       </c>
       <c r="V5" t="n">
-        <v>10.84239558637383</v>
+        <v>10.84239558637377</v>
       </c>
       <c r="W5" t="n">
-        <v>11.52288610621166</v>
+        <v>11.52288610621182</v>
       </c>
       <c r="X5" t="n">
-        <v>11.87246735999241</v>
+        <v>11.87246735999251</v>
       </c>
       <c r="Y5" t="n">
-        <v>18.85886715687176</v>
+        <v>18.85886715687191</v>
       </c>
       <c r="Z5" t="n">
-        <v>12.28524565611837</v>
+        <v>12.28524565611854</v>
       </c>
       <c r="AA5" t="n">
-        <v>9.753060143832187</v>
+        <v>9.753060143832307</v>
       </c>
       <c r="AB5" t="n">
-        <v>26.49894311323532</v>
+        <v>26.4989431132354</v>
       </c>
     </row>
     <row r="6">
@@ -3518,85 +3518,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.562384751932892</v>
+        <v>4.562384751932877</v>
       </c>
       <c r="C6" t="n">
-        <v>2.518027408523976</v>
+        <v>2.518027408524022</v>
       </c>
       <c r="D6" t="n">
-        <v>4.794727695130802</v>
+        <v>4.794727695130898</v>
       </c>
       <c r="E6" t="n">
-        <v>4.396035765446141</v>
+        <v>4.396035765446126</v>
       </c>
       <c r="F6" t="n">
-        <v>2.413827383061142</v>
+        <v>2.413827383061195</v>
       </c>
       <c r="G6" t="n">
-        <v>3.544018430267128</v>
+        <v>3.544018430267196</v>
       </c>
       <c r="H6" t="n">
-        <v>2.227693832535817</v>
+        <v>2.227693832535846</v>
       </c>
       <c r="I6" t="n">
-        <v>3.838497907606975</v>
+        <v>3.838497907607041</v>
       </c>
       <c r="J6" t="n">
-        <v>5.125936039159252</v>
+        <v>5.125936039159295</v>
       </c>
       <c r="K6" t="n">
-        <v>4.946633301185297</v>
+        <v>4.946633301185424</v>
       </c>
       <c r="L6" t="n">
-        <v>4.399149195897949</v>
+        <v>4.399149195898062</v>
       </c>
       <c r="M6" t="n">
-        <v>3.36482904117555</v>
+        <v>3.364829041175589</v>
       </c>
       <c r="N6" t="n">
-        <v>2.627138950205301</v>
+        <v>2.627138950205453</v>
       </c>
       <c r="O6" t="n">
-        <v>4.87967826832426</v>
+        <v>4.879678268324345</v>
       </c>
       <c r="P6" t="n">
-        <v>5.025063179480311</v>
+        <v>5.025063179480384</v>
       </c>
       <c r="Q6" t="n">
-        <v>5.442089548927489</v>
+        <v>5.44208954892757</v>
       </c>
       <c r="R6" t="n">
-        <v>2.314449098335393</v>
+        <v>2.314449098335436</v>
       </c>
       <c r="S6" t="n">
-        <v>4.97216796326359</v>
+        <v>4.972167963263708</v>
       </c>
       <c r="T6" t="n">
-        <v>2.436407129833205</v>
+        <v>2.436407129833212</v>
       </c>
       <c r="U6" t="n">
-        <v>2.578623036492193</v>
+        <v>2.578623036492199</v>
       </c>
       <c r="V6" t="n">
-        <v>4.767433251257589</v>
+        <v>4.76743325125761</v>
       </c>
       <c r="W6" t="n">
-        <v>4.862445042456263</v>
+        <v>4.862445042456342</v>
       </c>
       <c r="X6" t="n">
-        <v>2.660842187839483</v>
+        <v>2.660842187839452</v>
       </c>
       <c r="Y6" t="n">
-        <v>3.097890376561188</v>
+        <v>3.097890376561239</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.866889428936062</v>
+        <v>4.866889428936109</v>
       </c>
       <c r="AA6" t="n">
-        <v>4.653720275214336</v>
+        <v>4.653720275214422</v>
       </c>
       <c r="AB6" t="n">
-        <v>3.362118058580961</v>
+        <v>3.36211805858115</v>
       </c>
     </row>
     <row r="7">
@@ -3606,85 +3606,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.736131633239067</v>
+        <v>2.736131633239161</v>
       </c>
       <c r="C7" t="n">
-        <v>2.788633420435167</v>
+        <v>2.788633420435245</v>
       </c>
       <c r="D7" t="n">
-        <v>2.968474576437154</v>
+        <v>2.968474576437176</v>
       </c>
       <c r="E7" t="n">
-        <v>2.569782646752242</v>
+        <v>2.569782646752401</v>
       </c>
       <c r="F7" t="n">
-        <v>2.684433394972328</v>
+        <v>2.684433394972416</v>
       </c>
       <c r="G7" t="n">
-        <v>3.81462444217827</v>
+        <v>3.814624442178424</v>
       </c>
       <c r="H7" t="n">
-        <v>2.49829984444702</v>
+        <v>2.498299844447069</v>
       </c>
       <c r="I7" t="n">
-        <v>4.109103919518134</v>
+        <v>4.109103919518263</v>
       </c>
       <c r="J7" t="n">
-        <v>3.299682920465535</v>
+        <v>3.299682920465582</v>
       </c>
       <c r="K7" t="n">
-        <v>3.120380182491689</v>
+        <v>3.1203801824917</v>
       </c>
       <c r="L7" t="n">
-        <v>2.572896077204187</v>
+        <v>2.572896077204333</v>
       </c>
       <c r="M7" t="n">
-        <v>3.635435053086656</v>
+        <v>3.635435053086812</v>
       </c>
       <c r="N7" t="n">
-        <v>2.880964105993679</v>
+        <v>2.880964105993896</v>
       </c>
       <c r="O7" t="n">
-        <v>2.943240018947852</v>
+        <v>2.94324001894796</v>
       </c>
       <c r="P7" t="n">
-        <v>3.081530761295124</v>
+        <v>3.081530761295245</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.615836430233693</v>
+        <v>3.615836430233851</v>
       </c>
       <c r="R7" t="n">
-        <v>2.58505511024659</v>
+        <v>2.585055110246659</v>
       </c>
       <c r="S7" t="n">
-        <v>3.145914844569887</v>
+        <v>3.145914844569985</v>
       </c>
       <c r="T7" t="n">
-        <v>2.707013141744278</v>
+        <v>2.707013141744431</v>
       </c>
       <c r="U7" t="n">
-        <v>2.8324254336803</v>
+        <v>2.832425433680374</v>
       </c>
       <c r="V7" t="n">
-        <v>2.941180132563868</v>
+        <v>2.941180132563884</v>
       </c>
       <c r="W7" t="n">
-        <v>2.92808549533541</v>
+        <v>2.92808549533547</v>
       </c>
       <c r="X7" t="n">
-        <v>2.931448199750485</v>
+        <v>2.93144819975067</v>
       </c>
       <c r="Y7" t="n">
-        <v>3.346181900832761</v>
+        <v>3.346181900832867</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.040636310242203</v>
+        <v>3.040636310242387</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.827467156520532</v>
+        <v>2.827467156520696</v>
       </c>
       <c r="AB7" t="n">
-        <v>3.638572930269627</v>
+        <v>3.638572930269809</v>
       </c>
     </row>
     <row r="8">
@@ -3694,85 +3694,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.494327761473546</v>
+        <v>4.494327761473637</v>
       </c>
       <c r="C8" t="n">
-        <v>6.360745990543149</v>
+        <v>6.360745990543154</v>
       </c>
       <c r="D8" t="n">
-        <v>6.540587146545024</v>
+        <v>6.54058714654509</v>
       </c>
       <c r="E8" t="n">
-        <v>5.176038219812226</v>
+        <v>5.176038219812189</v>
       </c>
       <c r="F8" t="n">
-        <v>4.7252165046302</v>
+        <v>4.725216504630235</v>
       </c>
       <c r="G8" t="n">
-        <v>7.762864402777572</v>
+        <v>7.762864402777675</v>
       </c>
       <c r="H8" t="n">
-        <v>6.070412414554852</v>
+        <v>6.070412414554983</v>
       </c>
       <c r="I8" t="n">
-        <v>7.681216489626096</v>
+        <v>7.681216489626178</v>
       </c>
       <c r="J8" t="n">
-        <v>6.871795490573534</v>
+        <v>6.871795490573483</v>
       </c>
       <c r="K8" t="n">
-        <v>6.692492752599616</v>
+        <v>6.692492752599615</v>
       </c>
       <c r="L8" t="n">
-        <v>6.145008647312224</v>
+        <v>6.145008647312244</v>
       </c>
       <c r="M8" t="n">
-        <v>7.207547623172009</v>
+        <v>7.207547623172125</v>
       </c>
       <c r="N8" t="n">
-        <v>5.046987970872051</v>
+        <v>5.046987970872095</v>
       </c>
       <c r="O8" t="n">
-        <v>5.495667972870578</v>
+        <v>5.495667972870698</v>
       </c>
       <c r="P8" t="n">
-        <v>5.539241419381748</v>
+        <v>5.539241419381873</v>
       </c>
       <c r="Q8" t="n">
-        <v>5.017556578378327</v>
+        <v>5.01755657837842</v>
       </c>
       <c r="R8" t="n">
-        <v>6.157167680354473</v>
+        <v>6.157167680354565</v>
       </c>
       <c r="S8" t="n">
-        <v>6.718027414677808</v>
+        <v>6.718027414677895</v>
       </c>
       <c r="T8" t="n">
-        <v>6.279125711852282</v>
+        <v>6.279125711852344</v>
       </c>
       <c r="U8" t="n">
-        <v>5.522969819116281</v>
+        <v>5.522969819116391</v>
       </c>
       <c r="V8" t="n">
-        <v>6.003157566238492</v>
+        <v>6.003157566238491</v>
       </c>
       <c r="W8" t="n">
-        <v>6.50055454720287</v>
+        <v>6.500554547202949</v>
       </c>
       <c r="X8" t="n">
-        <v>4.499417391141456</v>
+        <v>4.499417391141547</v>
       </c>
       <c r="Y8" t="n">
-        <v>8.699551066760513</v>
+        <v>8.699551066760687</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.765138009755445</v>
+        <v>4.765138009755482</v>
       </c>
       <c r="AA8" t="n">
-        <v>6.399579726628602</v>
+        <v>6.39957972662861</v>
       </c>
       <c r="AB8" t="n">
-        <v>9.105472896561462</v>
+        <v>9.105472896561501</v>
       </c>
     </row>
     <row r="9">
@@ -3782,85 +3782,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>80.77810665781844</v>
+        <v>80.77810665781855</v>
       </c>
       <c r="C9" t="n">
-        <v>102.7167878466587</v>
+        <v>102.7167878466588</v>
       </c>
       <c r="D9" t="n">
-        <v>102.8966290026606</v>
+        <v>102.8966290026607</v>
       </c>
       <c r="E9" t="n">
-        <v>97.44669652919004</v>
+        <v>97.44669652919012</v>
       </c>
       <c r="F9" t="n">
-        <v>52.15897033351153</v>
+        <v>52.1589703335116</v>
       </c>
       <c r="G9" t="n">
-        <v>103.7427793754388</v>
+        <v>103.7427793754389</v>
       </c>
       <c r="H9" t="n">
-        <v>102.4264542706703</v>
+        <v>102.4264542706705</v>
       </c>
       <c r="I9" t="n">
-        <v>104.0372583457416</v>
+        <v>104.0372583457417</v>
       </c>
       <c r="J9" t="n">
-        <v>103.2278373466889</v>
+        <v>103.227837346689</v>
       </c>
       <c r="K9" t="n">
-        <v>103.0485346087151</v>
+        <v>103.0485346087152</v>
       </c>
       <c r="L9" t="n">
-        <v>102.5010505034277</v>
+        <v>102.5010505034278</v>
       </c>
       <c r="M9" t="n">
-        <v>103.5635894793102</v>
+        <v>103.5635894793103</v>
       </c>
       <c r="N9" t="n">
-        <v>102.8091185322172</v>
+        <v>102.8091185322174</v>
       </c>
       <c r="O9" t="n">
         <v>110.124445022923</v>
       </c>
       <c r="P9" t="n">
-        <v>111.8401499955882</v>
+        <v>111.8401499955883</v>
       </c>
       <c r="Q9" t="n">
-        <v>103.5439913634942</v>
+        <v>103.5439913634943</v>
       </c>
       <c r="R9" t="n">
-        <v>102.5132095364701</v>
+        <v>102.5132095364702</v>
       </c>
       <c r="S9" t="n">
-        <v>103.0740692707934</v>
+        <v>103.0740692707935</v>
       </c>
       <c r="T9" t="n">
-        <v>102.6351675679676</v>
+        <v>102.6351675679677</v>
       </c>
       <c r="U9" t="n">
-        <v>102.7773834746269</v>
+        <v>102.777383474627</v>
       </c>
       <c r="V9" t="n">
         <v>128.1255217375784</v>
       </c>
       <c r="W9" t="n">
-        <v>102.8562399215588</v>
+        <v>102.856239921559</v>
       </c>
       <c r="X9" t="n">
-        <v>102.8596026259739</v>
+        <v>102.859602625974</v>
       </c>
       <c r="Y9" t="n">
-        <v>103.2743363270562</v>
+        <v>103.2743363270563</v>
       </c>
       <c r="Z9" t="n">
-        <v>89.77337095361878</v>
+        <v>89.77337095361892</v>
       </c>
       <c r="AA9" t="n">
-        <v>102.7556215827441</v>
+        <v>102.7556215827442</v>
       </c>
       <c r="AB9" t="n">
-        <v>103.5667273564931</v>
+        <v>103.5667273564932</v>
       </c>
     </row>
   </sheetData>
@@ -4026,85 +4026,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.6242250259418</v>
+        <v>2.624225025941822</v>
       </c>
       <c r="C2" t="n">
-        <v>2.860397404555679</v>
+        <v>2.860397404555654</v>
       </c>
       <c r="D2" t="n">
-        <v>2.63450204574311</v>
+        <v>2.634502045743064</v>
       </c>
       <c r="E2" t="n">
-        <v>2.588068434377272</v>
+        <v>2.588068434377284</v>
       </c>
       <c r="F2" t="n">
-        <v>2.639318086138606</v>
+        <v>2.639318086138627</v>
       </c>
       <c r="G2" t="n">
-        <v>2.711580456204302</v>
+        <v>2.711580456204307</v>
       </c>
       <c r="H2" t="n">
-        <v>2.603549694586624</v>
+        <v>2.603549694586622</v>
       </c>
       <c r="I2" t="n">
-        <v>2.696665086155826</v>
+        <v>2.696665086155822</v>
       </c>
       <c r="J2" t="n">
-        <v>2.670158609974424</v>
+        <v>2.670158609974426</v>
       </c>
       <c r="K2" t="n">
-        <v>2.660542181682935</v>
+        <v>2.660542181682956</v>
       </c>
       <c r="L2" t="n">
-        <v>2.61958138721091</v>
+        <v>2.619581387210921</v>
       </c>
       <c r="M2" t="n">
-        <v>2.69163213117432</v>
+        <v>2.691632131174337</v>
       </c>
       <c r="N2" t="n">
-        <v>2.632566002170807</v>
+        <v>2.632566002170805</v>
       </c>
       <c r="O2" t="n">
-        <v>5.227341239579862</v>
+        <v>5.227341239579848</v>
       </c>
       <c r="P2" t="n">
-        <v>2.654300172730601</v>
+        <v>2.654300172730609</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.664129818984076</v>
+        <v>2.66412981898407</v>
       </c>
       <c r="R2" t="n">
-        <v>2.663473747242601</v>
+        <v>2.663473747242608</v>
       </c>
       <c r="S2" t="n">
-        <v>2.66404019511626</v>
+        <v>2.664040195116264</v>
       </c>
       <c r="T2" t="n">
         <v>2.644222141417545</v>
       </c>
       <c r="U2" t="n">
-        <v>3.509893580658846</v>
+        <v>3.509893580658853</v>
       </c>
       <c r="V2" t="n">
-        <v>2.647938410047423</v>
+        <v>2.647938410047447</v>
       </c>
       <c r="W2" t="n">
-        <v>3.73975158844237</v>
+        <v>3.739751588442392</v>
       </c>
       <c r="X2" t="n">
-        <v>2.652874296946335</v>
+        <v>2.652874296946325</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.724785681622108</v>
+        <v>2.724785681622162</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.893745594073646</v>
+        <v>2.893745594073639</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.636651771100166</v>
+        <v>2.636651771100175</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.70087513340515</v>
+        <v>2.700875133405151</v>
       </c>
     </row>
     <row r="3">
@@ -4114,85 +4114,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.718215415289546</v>
+        <v>2.733063162295961</v>
       </c>
       <c r="C3" t="n">
-        <v>3.009080157012021</v>
+        <v>3.019477394658608</v>
       </c>
       <c r="D3" t="n">
-        <v>2.792958375165346</v>
+        <v>2.810551998326436</v>
       </c>
       <c r="E3" t="n">
-        <v>2.461842334593929</v>
+        <v>2.467529711137292</v>
       </c>
       <c r="F3" t="n">
-        <v>2.827843325197672</v>
+        <v>2.846722068657655</v>
       </c>
       <c r="G3" t="n">
-        <v>3.338203105008355</v>
+        <v>3.374909053810792</v>
       </c>
       <c r="H3" t="n">
-        <v>2.57237329219206</v>
+        <v>2.582131303096927</v>
       </c>
       <c r="I3" t="n">
-        <v>3.238278714574719</v>
+        <v>3.271709008568683</v>
       </c>
       <c r="J3" t="n">
-        <v>3.045540506553534</v>
+        <v>3.072006716810622</v>
       </c>
       <c r="K3" t="n">
-        <v>2.977194482280554</v>
+        <v>3.001375137105828</v>
       </c>
       <c r="L3" t="n">
-        <v>2.685811067044731</v>
+        <v>2.699545400816556</v>
       </c>
       <c r="M3" t="n">
-        <v>3.206974777593672</v>
+        <v>3.239402343084997</v>
       </c>
       <c r="N3" t="n">
-        <v>2.779308073237547</v>
+        <v>2.796363906620809</v>
       </c>
       <c r="O3" t="n">
-        <v>7.078416619815192</v>
+        <v>7.096165595971883</v>
       </c>
       <c r="P3" t="n">
-        <v>2.931539518492202</v>
+        <v>2.953874835432053</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.003677889318899</v>
+        <v>3.028746758790338</v>
       </c>
       <c r="R3" t="n">
-        <v>3.001824123242381</v>
+        <v>3.026849172239461</v>
       </c>
       <c r="S3" t="n">
-        <v>3.001474998467608</v>
+        <v>3.026335389639147</v>
       </c>
       <c r="T3" t="n">
-        <v>2.863273811669939</v>
+        <v>2.883344585662242</v>
       </c>
       <c r="U3" t="n">
-        <v>4.183474006294586</v>
+        <v>4.198504212819736</v>
       </c>
       <c r="V3" t="n">
-        <v>2.886156680177344</v>
+        <v>2.906947145409518</v>
       </c>
       <c r="W3" t="n">
-        <v>4.66595176802436</v>
+        <v>4.685699004083446</v>
       </c>
       <c r="X3" t="n">
-        <v>2.923925684595077</v>
+        <v>2.946169236252735</v>
       </c>
       <c r="Y3" t="n">
-        <v>3.437884207104027</v>
+        <v>3.478200658006859</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.313762545724324</v>
+        <v>3.33560147465139</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.808195137412439</v>
+        <v>2.82625402947945</v>
       </c>
       <c r="AB3" t="n">
-        <v>3.271313112408867</v>
+        <v>3.305802915140574</v>
       </c>
     </row>
     <row r="4">
@@ -4202,85 +4202,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.271619454046469</v>
+        <v>2.271619454046475</v>
       </c>
       <c r="C4" t="n">
-        <v>2.067819274200434</v>
+        <v>2.067819274200333</v>
       </c>
       <c r="D4" t="n">
-        <v>2.387703120364233</v>
+        <v>2.38770312036417</v>
       </c>
       <c r="E4" t="n">
-        <v>1.863214119471154</v>
+        <v>1.863214119471102</v>
       </c>
       <c r="F4" t="n">
-        <v>2.442102512120094</v>
+        <v>2.442102512120056</v>
       </c>
       <c r="G4" t="n">
-        <v>3.258339224344546</v>
+        <v>3.258339224344375</v>
       </c>
       <c r="H4" t="n">
-        <v>2.038082075267223</v>
+        <v>2.038082075267129</v>
       </c>
       <c r="I4" t="n">
-        <v>3.089863258237687</v>
+        <v>3.089863258237673</v>
       </c>
       <c r="J4" t="n">
-        <v>2.789315870024172</v>
+        <v>2.789315870024156</v>
       </c>
       <c r="K4" t="n">
-        <v>2.681838434859507</v>
+        <v>2.68183843485954</v>
       </c>
       <c r="L4" t="n">
-        <v>2.219167418401605</v>
+        <v>2.219167418401535</v>
       </c>
       <c r="M4" t="n">
-        <v>3.043096255995815</v>
+        <v>3.043096255995862</v>
       </c>
       <c r="N4" t="n">
-        <v>2.365834617591257</v>
+        <v>2.365834617591496</v>
       </c>
       <c r="O4" t="n">
-        <v>2.40325918115266</v>
+        <v>2.403259181152686</v>
       </c>
       <c r="P4" t="n">
-        <v>2.611332072276817</v>
+        <v>2.61133207227683</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.722362448570382</v>
+        <v>2.722362448570385</v>
       </c>
       <c r="R4" t="n">
-        <v>2.714951816442485</v>
+        <v>2.714951816442599</v>
       </c>
       <c r="S4" t="n">
-        <v>2.721350105754561</v>
+        <v>2.721350105754484</v>
       </c>
       <c r="T4" t="n">
-        <v>2.497496072472265</v>
+        <v>2.497496072472238</v>
       </c>
       <c r="U4" t="n">
-        <v>2.228015149378962</v>
+        <v>2.228015149378733</v>
       </c>
       <c r="V4" t="n">
-        <v>2.532372603141271</v>
+        <v>2.532372603141268</v>
       </c>
       <c r="W4" t="n">
-        <v>2.488088795830709</v>
+        <v>2.488088795830932</v>
       </c>
       <c r="X4" t="n">
-        <v>2.59522614935799</v>
+        <v>2.595226149358146</v>
       </c>
       <c r="Y4" t="n">
-        <v>3.357771714213129</v>
+        <v>3.357771714213159</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.586674396010579</v>
+        <v>2.58667439601052</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.411985257195177</v>
+        <v>2.411985257195135</v>
       </c>
       <c r="AB4" t="n">
-        <v>3.138976623326767</v>
+        <v>3.138976623326855</v>
       </c>
     </row>
     <row r="5">
@@ -4290,85 +4290,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8.354328753969828</v>
+        <v>8.354328753969702</v>
       </c>
       <c r="C5" t="n">
-        <v>5.425586477542002</v>
+        <v>5.425586477541907</v>
       </c>
       <c r="D5" t="n">
-        <v>11.13056849443406</v>
+        <v>11.13056849443712</v>
       </c>
       <c r="E5" t="n">
-        <v>2.000751142991071</v>
+        <v>2.000751142991013</v>
       </c>
       <c r="F5" t="n">
-        <v>12.358368833848</v>
+        <v>12.35836883384886</v>
       </c>
       <c r="G5" t="n">
-        <v>24.00662781504915</v>
+        <v>24.00662781504894</v>
       </c>
       <c r="H5" t="n">
-        <v>5.114532207634145</v>
+        <v>5.114532207634185</v>
       </c>
       <c r="I5" t="n">
-        <v>24.40948576456635</v>
+        <v>24.40948576456639</v>
       </c>
       <c r="J5" t="n">
-        <v>17.26794196477593</v>
+        <v>17.26794196477657</v>
       </c>
       <c r="K5" t="n">
-        <v>15.49660818132329</v>
+        <v>15.49660818132431</v>
       </c>
       <c r="L5" t="n">
-        <v>7.808835685967433</v>
+        <v>7.808835685967135</v>
       </c>
       <c r="M5" t="n">
-        <v>23.13586690105952</v>
+        <v>23.13586690105999</v>
       </c>
       <c r="N5" t="n">
-        <v>10.83050639163243</v>
+        <v>10.83050639163239</v>
       </c>
       <c r="O5" t="n">
-        <v>10.34162330191427</v>
+        <v>10.3416233019174</v>
       </c>
       <c r="P5" t="n">
-        <v>13.67672326304721</v>
+        <v>13.67672326305231</v>
       </c>
       <c r="Q5" t="n">
-        <v>16.66847863809731</v>
+        <v>16.6684786380974</v>
       </c>
       <c r="R5" t="n">
-        <v>18.00328595182078</v>
+        <v>18.00328595182102</v>
       </c>
       <c r="S5" t="n">
-        <v>15.84046370477145</v>
+        <v>15.84046370477233</v>
       </c>
       <c r="T5" t="n">
-        <v>13.56093169205996</v>
+        <v>13.56093169205987</v>
       </c>
       <c r="U5" t="n">
-        <v>8.666516449531507</v>
+        <v>8.666516449532535</v>
       </c>
       <c r="V5" t="n">
-        <v>12.40975639362189</v>
+        <v>12.40975639362031</v>
       </c>
       <c r="W5" t="n">
-        <v>12.81169834271113</v>
+        <v>12.81169834271124</v>
       </c>
       <c r="X5" t="n">
-        <v>14.71992438111757</v>
+        <v>14.71992438111961</v>
       </c>
       <c r="Y5" t="n">
-        <v>29.46117411540508</v>
+        <v>29.4611741154108</v>
       </c>
       <c r="Z5" t="n">
-        <v>12.6970512525078</v>
+        <v>12.69705125250781</v>
       </c>
       <c r="AA5" t="n">
-        <v>11.50514012813355</v>
+        <v>11.50514012813343</v>
       </c>
       <c r="AB5" t="n">
-        <v>26.38717626251987</v>
+        <v>26.38717626251999</v>
       </c>
     </row>
     <row r="6">
@@ -4378,85 +4378,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.808071650474357</v>
+        <v>2.80807165047421</v>
       </c>
       <c r="C6" t="n">
-        <v>2.604271470628333</v>
+        <v>2.604271470628141</v>
       </c>
       <c r="D6" t="n">
-        <v>5.141670904221057</v>
+        <v>5.141670904221062</v>
       </c>
       <c r="E6" t="n">
-        <v>4.617181903328127</v>
+        <v>4.617181903327954</v>
       </c>
       <c r="F6" t="n">
-        <v>2.978554708547782</v>
+        <v>2.9785547085479</v>
       </c>
       <c r="G6" t="n">
-        <v>3.794791420772333</v>
+        <v>3.794791420772085</v>
       </c>
       <c r="H6" t="n">
-        <v>4.792049859124227</v>
+        <v>4.792049859124208</v>
       </c>
       <c r="I6" t="n">
-        <v>3.626315454665654</v>
+        <v>3.626315454665427</v>
       </c>
       <c r="J6" t="n">
-        <v>5.543283653881095</v>
+        <v>5.543283653881038</v>
       </c>
       <c r="K6" t="n">
-        <v>5.435806218716576</v>
+        <v>5.435806218716424</v>
       </c>
       <c r="L6" t="n">
-        <v>2.755619614829429</v>
+        <v>2.755619614829329</v>
       </c>
       <c r="M6" t="n">
-        <v>3.579548452423686</v>
+        <v>3.579548452423546</v>
       </c>
       <c r="N6" t="n">
-        <v>2.912678971137336</v>
+        <v>2.912678971137425</v>
       </c>
       <c r="O6" t="n">
-        <v>2.934256560137823</v>
+        <v>2.934256560137785</v>
       </c>
       <c r="P6" t="n">
-        <v>5.474820481277236</v>
+        <v>5.474820481277222</v>
       </c>
       <c r="Q6" t="n">
-        <v>5.476330232427397</v>
+        <v>5.476330232427253</v>
       </c>
       <c r="R6" t="n">
-        <v>5.468919600299857</v>
+        <v>5.468919600299422</v>
       </c>
       <c r="S6" t="n">
-        <v>3.257802302182344</v>
+        <v>3.25780230218227</v>
       </c>
       <c r="T6" t="n">
-        <v>5.251463856329165</v>
+        <v>5.251463856329362</v>
       </c>
       <c r="U6" t="n">
-        <v>5.031709539165673</v>
+        <v>5.031709539165392</v>
       </c>
       <c r="V6" t="n">
-        <v>3.068824799569019</v>
+        <v>3.068824799569049</v>
       </c>
       <c r="W6" t="n">
-        <v>3.060720923169623</v>
+        <v>3.06072092316946</v>
       </c>
       <c r="X6" t="n">
-        <v>3.131678345785769</v>
+        <v>3.131678345785941</v>
       </c>
       <c r="Y6" t="n">
-        <v>3.972171163375916</v>
+        <v>3.972171163375975</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.123126592438477</v>
+        <v>3.12312659243838</v>
       </c>
       <c r="AA6" t="n">
-        <v>5.165953041051943</v>
+        <v>5.165953041052064</v>
       </c>
       <c r="AB6" t="n">
-        <v>3.667123869023263</v>
+        <v>3.66712386902311</v>
       </c>
     </row>
     <row r="7">
@@ -4466,85 +4466,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.067749813720426</v>
+        <v>3.06774981372036</v>
       </c>
       <c r="C7" t="n">
-        <v>2.863949633874399</v>
+        <v>2.863949633874346</v>
       </c>
       <c r="D7" t="n">
-        <v>3.18383348003815</v>
+        <v>3.183833480038157</v>
       </c>
       <c r="E7" t="n">
-        <v>2.659344479145065</v>
+        <v>2.659344479145075</v>
       </c>
       <c r="F7" t="n">
-        <v>3.238232871794216</v>
+        <v>3.238232871794065</v>
       </c>
       <c r="G7" t="n">
-        <v>4.05446958401849</v>
+        <v>4.054469584018431</v>
       </c>
       <c r="H7" t="n">
-        <v>2.834212434941077</v>
+        <v>2.834212434941058</v>
       </c>
       <c r="I7" t="n">
-        <v>3.885993617911622</v>
+        <v>3.885993617911729</v>
       </c>
       <c r="J7" t="n">
-        <v>3.585446229697988</v>
+        <v>3.585446229698141</v>
       </c>
       <c r="K7" t="n">
-        <v>3.477968794533487</v>
+        <v>3.477968794533549</v>
       </c>
       <c r="L7" t="n">
-        <v>3.015297778075524</v>
+        <v>3.015297778075506</v>
       </c>
       <c r="M7" t="n">
-        <v>3.839226615669781</v>
+        <v>3.839226615669952</v>
       </c>
       <c r="N7" t="n">
-        <v>3.161964977265438</v>
+        <v>3.161964977265429</v>
       </c>
       <c r="O7" t="n">
-        <v>3.199374985874051</v>
+        <v>3.19937498587379</v>
       </c>
       <c r="P7" t="n">
-        <v>3.407447876997805</v>
+        <v>3.407447876997819</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.51849280824437</v>
+        <v>3.518492808244358</v>
       </c>
       <c r="R7" t="n">
-        <v>3.511082176116424</v>
+        <v>3.511082176116578</v>
       </c>
       <c r="S7" t="n">
-        <v>3.517480465428456</v>
+        <v>3.517480465428444</v>
       </c>
       <c r="T7" t="n">
-        <v>3.293626432146214</v>
+        <v>3.293626432146307</v>
       </c>
       <c r="U7" t="n">
-        <v>3.079433926056752</v>
+        <v>3.079433926056769</v>
       </c>
       <c r="V7" t="n">
-        <v>3.328502962815215</v>
+        <v>3.328502962815239</v>
       </c>
       <c r="W7" t="n">
-        <v>3.28421915550487</v>
+        <v>3.284219155504811</v>
       </c>
       <c r="X7" t="n">
-        <v>3.391356509031764</v>
+        <v>3.391356509032107</v>
       </c>
       <c r="Y7" t="n">
-        <v>4.203628679816392</v>
+        <v>4.203628679816843</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.382804755684537</v>
+        <v>3.382804755684452</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.208115616869089</v>
+        <v>3.208115616869171</v>
       </c>
       <c r="AB7" t="n">
-        <v>3.935106983000991</v>
+        <v>3.935106983000892</v>
       </c>
     </row>
     <row r="8">
@@ -4554,85 +4554,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.893726193320813</v>
+        <v>4.893726193320927</v>
       </c>
       <c r="C8" t="n">
-        <v>6.644294352343303</v>
+        <v>6.644294352343181</v>
       </c>
       <c r="D8" t="n">
-        <v>6.964178198507047</v>
+        <v>6.964178198507154</v>
       </c>
       <c r="E8" t="n">
-        <v>5.399045708782118</v>
+        <v>5.399045708782231</v>
       </c>
       <c r="F8" t="n">
-        <v>5.368676996719329</v>
+        <v>5.368676996719483</v>
       </c>
       <c r="G8" t="n">
-        <v>8.240065308664823</v>
+        <v>8.240065308664922</v>
       </c>
       <c r="H8" t="n">
-        <v>6.614557153409934</v>
+        <v>6.614557153410044</v>
       </c>
       <c r="I8" t="n">
-        <v>7.666338336380357</v>
+        <v>7.666338336380434</v>
       </c>
       <c r="J8" t="n">
-        <v>7.36579094816699</v>
+        <v>7.365790948167009</v>
       </c>
       <c r="K8" t="n">
-        <v>7.25831351300242</v>
+        <v>7.258313513002483</v>
       </c>
       <c r="L8" t="n">
-        <v>6.795642496544507</v>
+        <v>6.795642496544514</v>
       </c>
       <c r="M8" t="n">
-        <v>7.619571334115016</v>
+        <v>7.619571334114972</v>
       </c>
       <c r="N8" t="n">
-        <v>5.427347272878223</v>
+        <v>5.427347272878277</v>
       </c>
       <c r="O8" t="n">
-        <v>5.881096661182448</v>
+        <v>5.881096661182589</v>
       </c>
       <c r="P8" t="n">
-        <v>5.98711827832051</v>
+        <v>5.987118278320627</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.960391204753757</v>
+        <v>4.960391204753584</v>
       </c>
       <c r="R8" t="n">
-        <v>7.291426894585468</v>
+        <v>7.291426894585443</v>
       </c>
       <c r="S8" t="n">
-        <v>7.297825183897439</v>
+        <v>7.297825183897402</v>
       </c>
       <c r="T8" t="n">
-        <v>7.073971150615221</v>
+        <v>7.073971150615265</v>
       </c>
       <c r="U8" t="n">
-        <v>5.904637275012267</v>
+        <v>5.904637275012392</v>
       </c>
       <c r="V8" t="n">
-        <v>6.579455881938379</v>
+        <v>6.579455881938503</v>
       </c>
       <c r="W8" t="n">
-        <v>7.064947957114807</v>
+        <v>7.064947957114764</v>
       </c>
       <c r="X8" t="n">
-        <v>5.012376643338199</v>
+        <v>5.01237664333843</v>
       </c>
       <c r="Y8" t="n">
-        <v>9.934550260658597</v>
+        <v>9.934550260659202</v>
       </c>
       <c r="Z8" t="n">
-        <v>5.172477740615657</v>
+        <v>5.172477740615582</v>
       </c>
       <c r="AA8" t="n">
-        <v>6.988460335337919</v>
+        <v>6.988460335338099</v>
       </c>
       <c r="AB8" t="n">
-        <v>9.756952847072316</v>
+        <v>9.75695284707222</v>
       </c>
     </row>
     <row r="9">
@@ -4642,43 +4642,43 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>81.01562922457944</v>
+        <v>81.01562922457968</v>
       </c>
       <c r="C9" t="n">
-        <v>102.7143729995563</v>
+        <v>102.7143729995562</v>
       </c>
       <c r="D9" t="n">
-        <v>103.0342568457205</v>
+        <v>103.0342568457201</v>
       </c>
       <c r="E9" t="n">
-        <v>97.45475046135473</v>
+        <v>97.45475046135472</v>
       </c>
       <c r="F9" t="n">
-        <v>52.59731393336077</v>
+        <v>52.59731393336065</v>
       </c>
       <c r="G9" t="n">
-        <v>103.9048934989075</v>
+        <v>103.9048934989073</v>
       </c>
       <c r="H9" t="n">
-        <v>102.6846358006231</v>
+        <v>102.6846358006232</v>
       </c>
       <c r="I9" t="n">
-        <v>103.7364169835936</v>
+        <v>103.7364169835937</v>
       </c>
       <c r="J9" t="n">
-        <v>103.43586959538</v>
+        <v>103.4358695953802</v>
       </c>
       <c r="K9" t="n">
         <v>103.3283921602153</v>
       </c>
       <c r="L9" t="n">
-        <v>102.8657211437575</v>
+        <v>102.8657211437574</v>
       </c>
       <c r="M9" t="n">
-        <v>103.6896499813517</v>
+        <v>103.6896499813519</v>
       </c>
       <c r="N9" t="n">
-        <v>103.0123883429474</v>
+        <v>103.0123883429473</v>
       </c>
       <c r="O9" t="n">
         <v>110.308288025409</v>
@@ -4687,40 +4687,40 @@
         <v>112.094954600995</v>
       </c>
       <c r="Q9" t="n">
-        <v>103.3689167231335</v>
+        <v>103.3689167231334</v>
       </c>
       <c r="R9" t="n">
-        <v>103.3615055417983</v>
+        <v>103.3615055417984</v>
       </c>
       <c r="S9" t="n">
-        <v>103.3679038311105</v>
+        <v>103.3679038311104</v>
       </c>
       <c r="T9" t="n">
-        <v>103.1440497978286</v>
+        <v>103.1440497978283</v>
       </c>
       <c r="U9" t="n">
         <v>102.9242954806644</v>
       </c>
       <c r="V9" t="n">
-        <v>128.4539978832889</v>
+        <v>128.4539978832888</v>
       </c>
       <c r="W9" t="n">
-        <v>103.1346425211869</v>
+        <v>103.1346425211868</v>
       </c>
       <c r="X9" t="n">
-        <v>103.2417798747142</v>
+        <v>103.241779874714</v>
       </c>
       <c r="Y9" t="n">
-        <v>104.0540520454993</v>
+        <v>104.0540520454988</v>
       </c>
       <c r="Z9" t="n">
-        <v>90.02794198489072</v>
+        <v>90.02794198489067</v>
       </c>
       <c r="AA9" t="n">
-        <v>103.0585389825513</v>
+        <v>103.0585389825512</v>
       </c>
       <c r="AB9" t="n">
-        <v>103.7855303486828</v>
+        <v>103.7855303486827</v>
       </c>
     </row>
   </sheetData>
@@ -4886,13 +4886,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.468012033060575</v>
+        <v>2.468012033060576</v>
       </c>
       <c r="C2" t="n">
-        <v>2.727788715105641</v>
+        <v>2.727788715105642</v>
       </c>
       <c r="D2" t="n">
-        <v>2.449965102443522</v>
+        <v>2.449965102443521</v>
       </c>
       <c r="E2" t="n">
         <v>2.619827979225541</v>
@@ -4901,31 +4901,31 @@
         <v>2.540641095793224</v>
       </c>
       <c r="G2" t="n">
-        <v>2.487998365600217</v>
+        <v>2.487998365600218</v>
       </c>
       <c r="H2" t="n">
-        <v>2.471100502908711</v>
+        <v>2.47110050290871</v>
       </c>
       <c r="I2" t="n">
         <v>2.532486017215209</v>
       </c>
       <c r="J2" t="n">
-        <v>2.493746652002202</v>
+        <v>2.4937466520022</v>
       </c>
       <c r="K2" t="n">
         <v>2.540531406389088</v>
       </c>
       <c r="L2" t="n">
-        <v>2.641546948816828</v>
+        <v>2.641546948816827</v>
       </c>
       <c r="M2" t="n">
-        <v>2.496834065715524</v>
+        <v>2.496834065715523</v>
       </c>
       <c r="N2" t="n">
-        <v>2.487754795549558</v>
+        <v>2.48775479554956</v>
       </c>
       <c r="O2" t="n">
-        <v>4.97757216500754</v>
+        <v>4.977572165007544</v>
       </c>
       <c r="P2" t="n">
         <v>2.466270651884423</v>
@@ -4934,37 +4934,37 @@
         <v>2.525463128747114</v>
       </c>
       <c r="R2" t="n">
-        <v>2.541312075397371</v>
+        <v>2.54131207539737</v>
       </c>
       <c r="S2" t="n">
         <v>2.569943724849044</v>
       </c>
       <c r="T2" t="n">
-        <v>2.471517568177217</v>
+        <v>2.471517568177215</v>
       </c>
       <c r="U2" t="n">
-        <v>3.123400692636082</v>
+        <v>3.123400692636081</v>
       </c>
       <c r="V2" t="n">
-        <v>2.47369821200787</v>
+        <v>2.473698212007869</v>
       </c>
       <c r="W2" t="n">
-        <v>3.329357451091784</v>
+        <v>3.329357451091785</v>
       </c>
       <c r="X2" t="n">
-        <v>2.525639864863219</v>
+        <v>2.525639864863218</v>
       </c>
       <c r="Y2" t="n">
         <v>2.460935268609961</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.641404139920456</v>
+        <v>2.641404139920453</v>
       </c>
       <c r="AA2" t="n">
         <v>2.453475256600053</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.467498178887845</v>
+        <v>2.467498178887844</v>
       </c>
     </row>
     <row r="3">
@@ -4974,85 +4974,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.623594484423121</v>
+        <v>2.638315553095173</v>
       </c>
       <c r="C3" t="n">
-        <v>3.142841165802742</v>
+        <v>3.161890486187365</v>
       </c>
       <c r="D3" t="n">
-        <v>2.49650814948996</v>
+        <v>2.506807008503031</v>
       </c>
       <c r="E3" t="n">
-        <v>3.708219115857563</v>
+        <v>3.761098424324601</v>
       </c>
       <c r="F3" t="n">
-        <v>3.144892282478271</v>
+        <v>3.178358850650072</v>
       </c>
       <c r="G3" t="n">
-        <v>2.764631051765924</v>
+        <v>2.784357735295274</v>
       </c>
       <c r="H3" t="n">
-        <v>2.648603253662948</v>
+        <v>2.664345342203886</v>
       </c>
       <c r="I3" t="n">
-        <v>3.087338257127953</v>
+        <v>3.118642621502048</v>
       </c>
       <c r="J3" t="n">
-        <v>2.806779977528669</v>
+        <v>2.828040872743434</v>
       </c>
       <c r="K3" t="n">
-        <v>3.140405295779853</v>
+        <v>3.173661609177018</v>
       </c>
       <c r="L3" t="n">
-        <v>3.853760935482633</v>
+        <v>3.912209235456583</v>
       </c>
       <c r="M3" t="n">
-        <v>2.836894778281755</v>
+        <v>2.85944836885334</v>
       </c>
       <c r="N3" t="n">
-        <v>2.765668321062993</v>
+        <v>2.785498401876483</v>
       </c>
       <c r="O3" t="n">
-        <v>6.667245021044055</v>
+        <v>6.677431346882967</v>
       </c>
       <c r="P3" t="n">
-        <v>2.611412998678098</v>
+        <v>2.625679268159252</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.034196348015481</v>
+        <v>3.063603268296195</v>
       </c>
       <c r="R3" t="n">
-        <v>3.151710339837245</v>
+        <v>3.185320602132325</v>
       </c>
       <c r="S3" t="n">
-        <v>3.343081411983578</v>
+        <v>3.383398868021297</v>
       </c>
       <c r="T3" t="n">
-        <v>2.65017592001165</v>
+        <v>2.665954973663531</v>
       </c>
       <c r="U3" t="n">
-        <v>3.666123325338882</v>
+        <v>3.679064106886611</v>
       </c>
       <c r="V3" t="n">
-        <v>2.663834195261727</v>
+        <v>2.679985144459903</v>
       </c>
       <c r="W3" t="n">
-        <v>4.076003205672846</v>
+        <v>4.09215016124139</v>
       </c>
       <c r="X3" t="n">
-        <v>3.037189898265195</v>
+        <v>3.066681406889747</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.574367002978229</v>
+        <v>2.587400479604082</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.990892276028218</v>
+        <v>3.009366565722193</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.521175613693546</v>
+        <v>2.532320565200753</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.628812925621478</v>
+        <v>2.643831841089916</v>
       </c>
     </row>
     <row r="4">
@@ -5062,82 +5062,82 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.193855478981984</v>
+        <v>2.193855478981958</v>
       </c>
       <c r="C4" t="n">
-        <v>2.379989488802262</v>
+        <v>2.379989488802359</v>
       </c>
       <c r="D4" t="n">
-        <v>1.99000709566401</v>
+        <v>1.990007095664074</v>
       </c>
       <c r="E4" t="n">
-        <v>3.908686429700819</v>
+        <v>3.908686429700899</v>
       </c>
       <c r="F4" t="n">
-        <v>3.014234153566613</v>
+        <v>3.014234153566745</v>
       </c>
       <c r="G4" t="n">
-        <v>2.419610299184216</v>
+        <v>2.419610299184431</v>
       </c>
       <c r="H4" t="n">
-        <v>2.228741166682928</v>
+        <v>2.228741166682979</v>
       </c>
       <c r="I4" t="n">
-        <v>2.922118789506488</v>
+        <v>2.922118789506594</v>
       </c>
       <c r="J4" t="n">
-        <v>2.483616679498459</v>
+        <v>2.483616679498516</v>
       </c>
       <c r="K4" t="n">
-        <v>3.01299516128735</v>
+        <v>3.012995161287416</v>
       </c>
       <c r="L4" t="n">
-        <v>4.15401218245402</v>
+        <v>4.154012182454104</v>
       </c>
       <c r="M4" t="n">
-        <v>2.532055659299039</v>
+        <v>2.532055659299055</v>
       </c>
       <c r="N4" t="n">
-        <v>2.416859063414496</v>
+        <v>2.416859063414475</v>
       </c>
       <c r="O4" t="n">
-        <v>1.989271578587187</v>
+        <v>1.989271578587163</v>
       </c>
       <c r="P4" t="n">
-        <v>2.174185777522416</v>
+        <v>2.174185777522386</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.842792033571169</v>
+        <v>2.842792033571143</v>
       </c>
       <c r="R4" t="n">
-        <v>3.021813176861394</v>
+        <v>3.021813176861448</v>
       </c>
       <c r="S4" t="n">
-        <v>3.345220828627526</v>
+        <v>3.345220828627595</v>
       </c>
       <c r="T4" t="n">
-        <v>2.233452110750086</v>
+        <v>2.233452110750255</v>
       </c>
       <c r="U4" t="n">
-        <v>2.028604890788954</v>
+        <v>2.028604890789025</v>
       </c>
       <c r="V4" t="n">
-        <v>2.252506526057085</v>
+        <v>2.252506526057188</v>
       </c>
       <c r="W4" t="n">
-        <v>2.254082631950247</v>
+        <v>2.254082631950228</v>
       </c>
       <c r="X4" t="n">
-        <v>2.84478834930521</v>
+        <v>2.844788349305183</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.031122908414112</v>
+        <v>2.03112290841422</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.362712945357151</v>
+        <v>2.362712945357237</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.029655901612786</v>
+        <v>2.02965590161282</v>
       </c>
       <c r="AB4" t="n">
         <v>2.199854423362734</v>
@@ -5150,85 +5150,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9.971222434938991</v>
+        <v>9.971222434939056</v>
       </c>
       <c r="C5" t="n">
-        <v>14.38981424628213</v>
+        <v>14.38981424628217</v>
       </c>
       <c r="D5" t="n">
-        <v>7.070960615451734</v>
+        <v>7.070960615451804</v>
       </c>
       <c r="E5" t="n">
-        <v>43.01055115187621</v>
+        <v>43.01055115187635</v>
       </c>
       <c r="F5" t="n">
-        <v>27.11826126545104</v>
+        <v>27.11826126545098</v>
       </c>
       <c r="G5" t="n">
-        <v>13.34610066741707</v>
+        <v>13.34610066741713</v>
       </c>
       <c r="H5" t="n">
-        <v>12.28049981470961</v>
+        <v>12.28049981470977</v>
       </c>
       <c r="I5" t="n">
-        <v>25.73759401277868</v>
+        <v>25.73759401277871</v>
       </c>
       <c r="J5" t="n">
-        <v>15.19748427978871</v>
+        <v>15.19748427978882</v>
       </c>
       <c r="K5" t="n">
-        <v>25.03477541581857</v>
+        <v>25.03477541581865</v>
       </c>
       <c r="L5" t="n">
-        <v>42.38374831756386</v>
+        <v>42.38374831756392</v>
       </c>
       <c r="M5" t="n">
-        <v>16.77038196867709</v>
+        <v>16.77038196867711</v>
       </c>
       <c r="N5" t="n">
-        <v>14.837759495947</v>
+        <v>14.8377594959471</v>
       </c>
       <c r="O5" t="n">
-        <v>6.398534185404317</v>
+        <v>6.39853418540438</v>
       </c>
       <c r="P5" t="n">
-        <v>9.736589397038301</v>
+        <v>9.736589397038415</v>
       </c>
       <c r="Q5" t="n">
-        <v>22.55855417740191</v>
+        <v>22.55855417740199</v>
       </c>
       <c r="R5" t="n">
-        <v>28.39013248581418</v>
+        <v>28.39013248581429</v>
       </c>
       <c r="S5" t="n">
-        <v>27.28933094307287</v>
+        <v>27.28933094307292</v>
       </c>
       <c r="T5" t="n">
-        <v>11.58876435060932</v>
+        <v>11.5887643506095</v>
       </c>
       <c r="U5" t="n">
-        <v>8.845975399369561</v>
+        <v>8.845975399369653</v>
       </c>
       <c r="V5" t="n">
-        <v>10.98939585068664</v>
+        <v>10.98939585068673</v>
       </c>
       <c r="W5" t="n">
-        <v>11.85925730441417</v>
+        <v>11.85925730441439</v>
       </c>
       <c r="X5" t="n">
-        <v>23.55965378434567</v>
+        <v>23.55965378434566</v>
       </c>
       <c r="Y5" t="n">
-        <v>9.171543082142641</v>
+        <v>9.171543082142668</v>
       </c>
       <c r="Z5" t="n">
-        <v>12.64445335571956</v>
+        <v>12.6444533557196</v>
       </c>
       <c r="AA5" t="n">
-        <v>7.60669524796017</v>
+        <v>7.606695247960201</v>
       </c>
       <c r="AB5" t="n">
-        <v>11.45998585602297</v>
+        <v>11.45998585602307</v>
       </c>
     </row>
     <row r="6">
@@ -5238,85 +5238,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.73844021645594</v>
+        <v>2.738440216455923</v>
       </c>
       <c r="C6" t="n">
-        <v>2.924574226276345</v>
+        <v>2.924574226276325</v>
       </c>
       <c r="D6" t="n">
-        <v>4.845992456411701</v>
+        <v>4.845992456411822</v>
       </c>
       <c r="E6" t="n">
-        <v>6.764671790448554</v>
+        <v>6.764671790448644</v>
       </c>
       <c r="F6" t="n">
-        <v>3.55881889104064</v>
+        <v>3.558818891040711</v>
       </c>
       <c r="G6" t="n">
-        <v>2.964195036658362</v>
+        <v>2.964195036658395</v>
       </c>
       <c r="H6" t="n">
-        <v>5.084726527430538</v>
+        <v>5.084726527430725</v>
       </c>
       <c r="I6" t="n">
-        <v>5.778104150254236</v>
+        <v>5.77810415025434</v>
       </c>
       <c r="J6" t="n">
-        <v>3.02820141697227</v>
+        <v>3.02820141697248</v>
       </c>
       <c r="K6" t="n">
-        <v>5.868980522035093</v>
+        <v>5.868980522035167</v>
       </c>
       <c r="L6" t="n">
-        <v>4.698596919928148</v>
+        <v>4.698596919928073</v>
       </c>
       <c r="M6" t="n">
-        <v>5.388041020046656</v>
+        <v>5.388041020046807</v>
       </c>
       <c r="N6" t="n">
-        <v>2.970910102346211</v>
+        <v>2.970910102346271</v>
       </c>
       <c r="O6" t="n">
-        <v>4.908489188270447</v>
+        <v>4.908489188270686</v>
       </c>
       <c r="P6" t="n">
-        <v>5.097305827929778</v>
+        <v>5.097305827929842</v>
       </c>
       <c r="Q6" t="n">
-        <v>5.698777394318721</v>
+        <v>5.698777394318892</v>
       </c>
       <c r="R6" t="n">
-        <v>5.877798537609091</v>
+        <v>5.877798537609193</v>
       </c>
       <c r="S6" t="n">
-        <v>3.889805566101516</v>
+        <v>3.889805566101568</v>
       </c>
       <c r="T6" t="n">
-        <v>2.778036848224219</v>
+        <v>2.778036848224225</v>
       </c>
       <c r="U6" t="n">
-        <v>2.655986888888465</v>
+        <v>2.655986888888541</v>
       </c>
       <c r="V6" t="n">
-        <v>5.108491886804749</v>
+        <v>5.108491886804932</v>
       </c>
       <c r="W6" t="n">
-        <v>5.171161108232221</v>
+        <v>5.171161108232262</v>
       </c>
       <c r="X6" t="n">
-        <v>3.389373086779166</v>
+        <v>3.389373086779153</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.674659548331483</v>
+        <v>2.674659548331453</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.9072976828312</v>
+        <v>2.907297682831199</v>
       </c>
       <c r="AA6" t="n">
-        <v>4.885641262360418</v>
+        <v>4.885641262360561</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.722909803491794</v>
+        <v>2.722909803491951</v>
       </c>
     </row>
     <row r="7">
@@ -5326,85 +5326,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.027411770222843</v>
+        <v>3.027411770222958</v>
       </c>
       <c r="C7" t="n">
-        <v>3.213545780043279</v>
+        <v>3.213545780043358</v>
       </c>
       <c r="D7" t="n">
-        <v>2.823563386904996</v>
+        <v>2.823563386905076</v>
       </c>
       <c r="E7" t="n">
-        <v>4.742242720941833</v>
+        <v>4.7422427209419</v>
       </c>
       <c r="F7" t="n">
-        <v>3.847790444807713</v>
+        <v>3.847790444807742</v>
       </c>
       <c r="G7" t="n">
-        <v>3.253166590425328</v>
+        <v>3.253166590425426</v>
       </c>
       <c r="H7" t="n">
-        <v>3.062297457923943</v>
+        <v>3.062297457923974</v>
       </c>
       <c r="I7" t="n">
-        <v>3.755675080747504</v>
+        <v>3.755675080747595</v>
       </c>
       <c r="J7" t="n">
-        <v>3.31717297073944</v>
+        <v>3.317172970739516</v>
       </c>
       <c r="K7" t="n">
-        <v>3.846551452528329</v>
+        <v>3.84655145252842</v>
       </c>
       <c r="L7" t="n">
-        <v>4.98756847369505</v>
+        <v>4.987568473695102</v>
       </c>
       <c r="M7" t="n">
-        <v>3.365611950540037</v>
+        <v>3.365611950540063</v>
       </c>
       <c r="N7" t="n">
-        <v>3.250415354655428</v>
+        <v>3.25041535465547</v>
       </c>
       <c r="O7" t="n">
-        <v>2.822816705118538</v>
+        <v>2.822816705118617</v>
       </c>
       <c r="P7" t="n">
-        <v>3.00773090405374</v>
+        <v>3.007730904053839</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.67634832481206</v>
+        <v>3.676348324812145</v>
       </c>
       <c r="R7" t="n">
-        <v>3.855369468102344</v>
+        <v>3.855369468102448</v>
       </c>
       <c r="S7" t="n">
-        <v>4.178777119868503</v>
+        <v>4.178777119868597</v>
       </c>
       <c r="T7" t="n">
-        <v>3.067008401991244</v>
+        <v>3.067008401991258</v>
       </c>
       <c r="U7" t="n">
-        <v>2.942151572537236</v>
+        <v>2.942151572537313</v>
       </c>
       <c r="V7" t="n">
-        <v>3.086062817298182</v>
+        <v>3.086062817298189</v>
       </c>
       <c r="W7" t="n">
-        <v>3.087638923191141</v>
+        <v>3.087638923191231</v>
       </c>
       <c r="X7" t="n">
-        <v>3.678344640546102</v>
+        <v>3.678344640546186</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.947476460280677</v>
+        <v>2.94747646028077</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.196269236598134</v>
+        <v>3.196269236598236</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.863212192853721</v>
+        <v>2.86321219285382</v>
       </c>
       <c r="AB7" t="n">
-        <v>3.033410714603656</v>
+        <v>3.033410714603736</v>
       </c>
     </row>
     <row r="8">
@@ -5414,85 +5414,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.967407485716032</v>
+        <v>4.967407485716134</v>
       </c>
       <c r="C8" t="n">
-        <v>7.161287166008734</v>
+        <v>7.161287166008782</v>
       </c>
       <c r="D8" t="n">
-        <v>6.771304772870453</v>
+        <v>6.771304772870494</v>
       </c>
       <c r="E8" t="n">
-        <v>7.620918763271196</v>
+        <v>7.620918763271219</v>
       </c>
       <c r="F8" t="n">
-        <v>6.100569470214076</v>
+        <v>6.100569470214181</v>
       </c>
       <c r="G8" t="n">
-        <v>7.61722712014925</v>
+        <v>7.617227120149344</v>
       </c>
       <c r="H8" t="n">
-        <v>7.010038843889305</v>
+        <v>7.010038843889397</v>
       </c>
       <c r="I8" t="n">
-        <v>7.703416466712948</v>
+        <v>7.703416466712994</v>
       </c>
       <c r="J8" t="n">
-        <v>7.264914356704732</v>
+        <v>7.264914356704931</v>
       </c>
       <c r="K8" t="n">
-        <v>7.794292838493791</v>
+        <v>7.794292838493837</v>
       </c>
       <c r="L8" t="n">
-        <v>8.935309859660537</v>
+        <v>8.935309859660528</v>
       </c>
       <c r="M8" t="n">
-        <v>7.313353336489266</v>
+        <v>7.313353336489332</v>
       </c>
       <c r="N8" t="n">
-        <v>5.641817956332036</v>
+        <v>5.641817956332214</v>
       </c>
       <c r="O8" t="n">
-        <v>5.641925880388073</v>
+        <v>5.641925880388082</v>
       </c>
       <c r="P8" t="n">
-        <v>5.72200160030763</v>
+        <v>5.722001600307672</v>
       </c>
       <c r="Q8" t="n">
-        <v>5.221776192860321</v>
+        <v>5.221776192860454</v>
       </c>
       <c r="R8" t="n">
-        <v>7.803110854067795</v>
+        <v>7.803110854067862</v>
       </c>
       <c r="S8" t="n">
-        <v>8.126518505833952</v>
+        <v>8.126518505834017</v>
       </c>
       <c r="T8" t="n">
-        <v>7.014749787956603</v>
+        <v>7.014749787956686</v>
       </c>
       <c r="U8" t="n">
-        <v>5.910579358061204</v>
+        <v>5.910579358061368</v>
       </c>
       <c r="V8" t="n">
-        <v>6.482667335833413</v>
+        <v>6.482667335833527</v>
       </c>
       <c r="W8" t="n">
-        <v>7.03577488394007</v>
+        <v>7.035774883940149</v>
       </c>
       <c r="X8" t="n">
-        <v>5.407786385810758</v>
+        <v>5.407786385810687</v>
       </c>
       <c r="Y8" t="n">
-        <v>8.887767238234252</v>
+        <v>8.887767238234389</v>
       </c>
       <c r="Z8" t="n">
-        <v>5.098970045945756</v>
+        <v>5.098970045945709</v>
       </c>
       <c r="AA8" t="n">
-        <v>6.810953578819131</v>
+        <v>6.810953578819233</v>
       </c>
       <c r="AB8" t="n">
-        <v>9.078410333779416</v>
+        <v>9.078410333779507</v>
       </c>
     </row>
     <row r="9">
@@ -5502,58 +5502,58 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>86.81732714828389</v>
+        <v>86.81732714828401</v>
       </c>
       <c r="C9" t="n">
-        <v>110.5133497795431</v>
+        <v>110.5133497795432</v>
       </c>
       <c r="D9" t="n">
-        <v>110.123367386405</v>
+        <v>110.1233673864051</v>
       </c>
       <c r="E9" t="n">
         <v>106.6160608102509</v>
       </c>
       <c r="F9" t="n">
-        <v>56.95088388550231</v>
+        <v>56.95088388550236</v>
       </c>
       <c r="G9" t="n">
-        <v>110.5529712250615</v>
+        <v>110.5529712250616</v>
       </c>
       <c r="H9" t="n">
-        <v>110.3621014574238</v>
+        <v>110.3621014574239</v>
       </c>
       <c r="I9" t="n">
-        <v>111.0554790802476</v>
+        <v>111.0554790802477</v>
       </c>
       <c r="J9" t="n">
-        <v>110.6169769702394</v>
+        <v>110.6169769702395</v>
       </c>
       <c r="K9" t="n">
-        <v>111.1463554520281</v>
+        <v>111.1463554520282</v>
       </c>
       <c r="L9" t="n">
-        <v>112.287372473195</v>
+        <v>112.2873724731952</v>
       </c>
       <c r="M9" t="n">
-        <v>110.66541595004</v>
+        <v>110.6654159500401</v>
       </c>
       <c r="N9" t="n">
-        <v>110.5502193541552</v>
+        <v>110.5502193541553</v>
       </c>
       <c r="O9" t="n">
         <v>117.9137790205117</v>
       </c>
       <c r="P9" t="n">
-        <v>119.7931339131292</v>
+        <v>119.7931339131293</v>
       </c>
       <c r="Q9" t="n">
-        <v>110.9761529594479</v>
+        <v>110.976152959448</v>
       </c>
       <c r="R9" t="n">
-        <v>111.1551734676021</v>
+        <v>111.1551734676022</v>
       </c>
       <c r="S9" t="n">
-        <v>111.4785811193686</v>
+        <v>111.4785811193687</v>
       </c>
       <c r="T9" t="n">
         <v>110.3668124014912</v>
@@ -5562,25 +5562,25 @@
         <v>110.2447624421554</v>
       </c>
       <c r="V9" t="n">
-        <v>137.5157801946275</v>
+        <v>137.5157801946276</v>
       </c>
       <c r="W9" t="n">
-        <v>110.3874429226909</v>
+        <v>110.387442922691</v>
       </c>
       <c r="X9" t="n">
-        <v>110.9781486400457</v>
+        <v>110.9781486400458</v>
       </c>
       <c r="Y9" t="n">
-        <v>110.2472804597806</v>
+        <v>110.2472804597805</v>
       </c>
       <c r="Z9" t="n">
-        <v>96.32170123043905</v>
+        <v>96.32170123043903</v>
       </c>
       <c r="AA9" t="n">
         <v>110.1630161923537</v>
       </c>
       <c r="AB9" t="n">
-        <v>110.3332147141033</v>
+        <v>110.3332147141034</v>
       </c>
     </row>
   </sheetData>
@@ -5746,85 +5746,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.032053663854787</v>
+        <v>3.032053663854785</v>
       </c>
       <c r="C2" t="n">
-        <v>3.230147467090333</v>
+        <v>3.230147467090329</v>
       </c>
       <c r="D2" t="n">
-        <v>2.831832061046188</v>
+        <v>2.831832061046187</v>
       </c>
       <c r="E2" t="n">
-        <v>3.210938212272282</v>
+        <v>3.21093821227228</v>
       </c>
       <c r="F2" t="n">
-        <v>3.068833602710846</v>
+        <v>3.068833602710844</v>
       </c>
       <c r="G2" t="n">
-        <v>2.860855207287281</v>
+        <v>2.860855207287277</v>
       </c>
       <c r="H2" t="n">
-        <v>2.869460709605487</v>
+        <v>2.869460709605484</v>
       </c>
       <c r="I2" t="n">
-        <v>2.995834342311721</v>
+        <v>2.995834342311709</v>
       </c>
       <c r="J2" t="n">
-        <v>2.915214904270052</v>
+        <v>2.915214904270043</v>
       </c>
       <c r="K2" t="n">
-        <v>2.916828394301786</v>
+        <v>2.916828394301783</v>
       </c>
       <c r="L2" t="n">
-        <v>2.997122340267324</v>
+        <v>2.997122340267305</v>
       </c>
       <c r="M2" t="n">
-        <v>2.855942416981295</v>
+        <v>2.855942416981294</v>
       </c>
       <c r="N2" t="n">
-        <v>2.939978342837283</v>
+        <v>2.939978342837275</v>
       </c>
       <c r="O2" t="n">
-        <v>5.7805712816699</v>
+        <v>5.780571281669885</v>
       </c>
       <c r="P2" t="n">
-        <v>2.854575872635603</v>
+        <v>2.854575872635599</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.929802497627136</v>
+        <v>2.929802497627132</v>
       </c>
       <c r="R2" t="n">
-        <v>3.087931873729723</v>
+        <v>3.087931873729715</v>
       </c>
       <c r="S2" t="n">
         <v>2.958272348504189</v>
       </c>
       <c r="T2" t="n">
-        <v>2.888675618010112</v>
+        <v>2.888675618010102</v>
       </c>
       <c r="U2" t="n">
-        <v>3.883195011566139</v>
+        <v>3.883195011566122</v>
       </c>
       <c r="V2" t="n">
-        <v>2.895274731583911</v>
+        <v>2.895274731583906</v>
       </c>
       <c r="W2" t="n">
-        <v>4.193108661498727</v>
+        <v>4.193108661498716</v>
       </c>
       <c r="X2" t="n">
-        <v>2.917861077988707</v>
+        <v>2.917861077988705</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.862968468789653</v>
+        <v>2.862968468789648</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.458539673838075</v>
+        <v>3.458539673838065</v>
       </c>
       <c r="AA2" t="n">
         <v>2.847015085160677</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.855687367121358</v>
+        <v>2.855687367121355</v>
       </c>
     </row>
     <row r="3">
@@ -5834,85 +5834,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.206284287266376</v>
+        <v>4.267372572695302</v>
       </c>
       <c r="C3" t="n">
-        <v>3.963974491255271</v>
+        <v>3.999338420561679</v>
       </c>
       <c r="D3" t="n">
-        <v>2.783895188149871</v>
+        <v>2.795003379110147</v>
       </c>
       <c r="E3" t="n">
-        <v>5.487688501021074</v>
+        <v>5.594029238654693</v>
       </c>
       <c r="F3" t="n">
-        <v>4.475982880420335</v>
+        <v>4.547595731730764</v>
       </c>
       <c r="G3" t="n">
-        <v>2.988239121534499</v>
+        <v>3.006530095218411</v>
       </c>
       <c r="H3" t="n">
-        <v>3.05411829532338</v>
+        <v>3.074882320792541</v>
       </c>
       <c r="I3" t="n">
-        <v>3.95598934565355</v>
+        <v>4.00883197856083</v>
       </c>
       <c r="J3" t="n">
-        <v>3.375670120903185</v>
+        <v>3.40773074066638</v>
       </c>
       <c r="K3" t="n">
-        <v>3.387542366376876</v>
+        <v>3.420196439851999</v>
       </c>
       <c r="L3" t="n">
-        <v>3.949349162779686</v>
+        <v>4.001997236012764</v>
       </c>
       <c r="M3" t="n">
-        <v>2.973656390286579</v>
+        <v>2.99171449849622</v>
       </c>
       <c r="N3" t="n">
-        <v>3.55416972235126</v>
+        <v>3.592602669357779</v>
       </c>
       <c r="O3" t="n">
-        <v>8.2394604644693</v>
+        <v>8.277534752470018</v>
       </c>
       <c r="P3" t="n">
-        <v>2.944632392935393</v>
+        <v>2.961325044118845</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.478405893014124</v>
+        <v>3.514315745355008</v>
       </c>
       <c r="R3" t="n">
-        <v>4.616738338748285</v>
+        <v>4.693158151418123</v>
       </c>
       <c r="S3" t="n">
-        <v>3.677092021518443</v>
+        <v>3.719846873190674</v>
       </c>
       <c r="T3" t="n">
-        <v>3.188944103464725</v>
+        <v>3.214499569577183</v>
       </c>
       <c r="U3" t="n">
-        <v>4.591716333117468</v>
+        <v>4.60615938575548</v>
       </c>
       <c r="V3" t="n">
-        <v>3.232662303648772</v>
+        <v>3.259574920846566</v>
       </c>
       <c r="W3" t="n">
-        <v>5.494376954591847</v>
+        <v>5.526838304721407</v>
       </c>
       <c r="X3" t="n">
-        <v>3.396489326526507</v>
+        <v>3.429417565482597</v>
       </c>
       <c r="Y3" t="n">
-        <v>3.005978405643623</v>
+        <v>3.024915441813399</v>
       </c>
       <c r="Z3" t="n">
-        <v>4.60175569357239</v>
+        <v>4.648892512855122</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.892048439966317</v>
+        <v>2.906951052756125</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.97112928249991</v>
+        <v>2.988984314973286</v>
       </c>
     </row>
     <row r="4">
@@ -5922,85 +5922,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.544969496345785</v>
+        <v>4.544969496345893</v>
       </c>
       <c r="C4" t="n">
-        <v>3.363816649710006</v>
+        <v>3.363816649710053</v>
       </c>
       <c r="D4" t="n">
-        <v>2.283374386134946</v>
+        <v>2.283374386134891</v>
       </c>
       <c r="E4" t="n">
-        <v>6.565552761679298</v>
+        <v>6.565552761679383</v>
       </c>
       <c r="F4" t="n">
-        <v>4.960415825332774</v>
+        <v>4.960415825332806</v>
       </c>
       <c r="G4" t="n">
-        <v>2.611204174234973</v>
+        <v>2.611204174234984</v>
       </c>
       <c r="H4" t="n">
-        <v>2.708407281645747</v>
+        <v>2.708407281645724</v>
       </c>
       <c r="I4" t="n">
-        <v>4.135855597805871</v>
+        <v>4.135855597805809</v>
       </c>
       <c r="J4" t="n">
-        <v>3.22410879612052</v>
+        <v>3.224108796120371</v>
       </c>
       <c r="K4" t="n">
-        <v>3.243447070501966</v>
+        <v>3.243447070501914</v>
       </c>
       <c r="L4" t="n">
-        <v>4.150404127222747</v>
+        <v>4.150404127222656</v>
       </c>
       <c r="M4" t="n">
-        <v>2.590456693117607</v>
+        <v>2.59045669311767</v>
       </c>
       <c r="N4" t="n">
-        <v>3.504936388712792</v>
+        <v>3.504936388712692</v>
       </c>
       <c r="O4" t="n">
-        <v>3.506851096390652</v>
+        <v>3.50685109639066</v>
       </c>
       <c r="P4" t="n">
-        <v>2.540276200707505</v>
+        <v>2.540276200707568</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.389995535944078</v>
+        <v>3.389995535944142</v>
       </c>
       <c r="R4" t="n">
-        <v>5.176139582129838</v>
+        <v>5.176139582129722</v>
       </c>
       <c r="S4" t="n">
-        <v>3.711575598378851</v>
+        <v>3.711575598378982</v>
       </c>
       <c r="T4" t="n">
-        <v>2.925448511370592</v>
+        <v>2.9254485113705</v>
       </c>
       <c r="U4" t="n">
-        <v>2.301570024299467</v>
+        <v>2.301570024299495</v>
       </c>
       <c r="V4" t="n">
-        <v>2.993337269437866</v>
+        <v>2.993337269437859</v>
       </c>
       <c r="W4" t="n">
-        <v>3.242160478767404</v>
+        <v>3.242160478767403</v>
       </c>
       <c r="X4" t="n">
-        <v>3.255111707803633</v>
+        <v>3.255111707803661</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.501011969150265</v>
+        <v>2.501011969150317</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.912619075942746</v>
+        <v>3.912619075942875</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.454873628044294</v>
+        <v>2.45487362804428</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.583360926368699</v>
+        <v>2.583360926368722</v>
       </c>
     </row>
     <row r="5">
@@ -6010,85 +6010,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>42.91153549279137</v>
+        <v>42.91153549279159</v>
       </c>
       <c r="C5" t="n">
-        <v>24.86531174285755</v>
+        <v>24.86531174285765</v>
       </c>
       <c r="D5" t="n">
-        <v>6.333052560447299</v>
+        <v>6.333052560447141</v>
       </c>
       <c r="E5" t="n">
-        <v>81.082609823824</v>
+        <v>81.08260982382401</v>
       </c>
       <c r="F5" t="n">
-        <v>53.98974470963311</v>
+        <v>53.98974470963323</v>
       </c>
       <c r="G5" t="n">
-        <v>10.68245834417837</v>
+        <v>10.6824583441783</v>
       </c>
       <c r="H5" t="n">
         <v>14.71359836316736</v>
       </c>
       <c r="I5" t="n">
-        <v>39.92728023492237</v>
+        <v>39.92728023492234</v>
       </c>
       <c r="J5" t="n">
-        <v>21.26304469108349</v>
+        <v>21.26304469108332</v>
       </c>
       <c r="K5" t="n">
-        <v>21.77134287618586</v>
+        <v>21.77134287618578</v>
       </c>
       <c r="L5" t="n">
-        <v>31.97970509031294</v>
+        <v>31.97970509031283</v>
       </c>
       <c r="M5" t="n">
-        <v>11.14600215505916</v>
+        <v>11.14600215505913</v>
       </c>
       <c r="N5" t="n">
-        <v>27.12432858592459</v>
+        <v>27.12432858592462</v>
       </c>
       <c r="O5" t="n">
-        <v>24.79616063589708</v>
+        <v>24.79616063589728</v>
       </c>
       <c r="P5" t="n">
-        <v>10.05461522028183</v>
+        <v>10.05461522028182</v>
       </c>
       <c r="Q5" t="n">
-        <v>23.4650577678623</v>
+        <v>23.46505776786243</v>
       </c>
       <c r="R5" t="n">
-        <v>60.11135078813277</v>
+        <v>60.1113507881327</v>
       </c>
       <c r="S5" t="n">
-        <v>26.81832839512394</v>
+        <v>26.81832839512409</v>
       </c>
       <c r="T5" t="n">
-        <v>17.35422057248883</v>
+        <v>17.35422057248876</v>
       </c>
       <c r="U5" t="n">
-        <v>8.21972692618729</v>
+        <v>8.219726926187107</v>
       </c>
       <c r="V5" t="n">
-        <v>16.91433200394376</v>
+        <v>16.91433200394378</v>
       </c>
       <c r="W5" t="n">
         <v>22.12444257817218</v>
       </c>
       <c r="X5" t="n">
-        <v>22.79470768327029</v>
+        <v>22.79470768327017</v>
       </c>
       <c r="Y5" t="n">
-        <v>12.48147890085066</v>
+        <v>12.48147890085062</v>
       </c>
       <c r="Z5" t="n">
-        <v>31.01213667314778</v>
+        <v>31.01213667314787</v>
       </c>
       <c r="AA5" t="n">
-        <v>9.258121185129992</v>
+        <v>9.258121185129951</v>
       </c>
       <c r="AB5" t="n">
-        <v>11.84096257599798</v>
+        <v>11.8409625759979</v>
       </c>
     </row>
     <row r="6">
@@ -6098,85 +6098,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7.659941974734918</v>
+        <v>7.659941974734881</v>
       </c>
       <c r="C6" t="n">
-        <v>4.136154386922028</v>
+        <v>4.13615438692211</v>
       </c>
       <c r="D6" t="n">
-        <v>3.055712123346928</v>
+        <v>3.055712123346949</v>
       </c>
       <c r="E6" t="n">
-        <v>7.337890498891473</v>
+        <v>7.337890498891503</v>
       </c>
       <c r="F6" t="n">
-        <v>8.075388303721876</v>
+        <v>8.075388303721843</v>
       </c>
       <c r="G6" t="n">
-        <v>5.726176652623917</v>
+        <v>5.72617665262395</v>
       </c>
       <c r="H6" t="n">
-        <v>5.823379760034722</v>
+        <v>5.823379760034748</v>
       </c>
       <c r="I6" t="n">
-        <v>7.250828076194818</v>
+        <v>7.250828076194903</v>
       </c>
       <c r="J6" t="n">
-        <v>6.339081274509484</v>
+        <v>6.339081274509528</v>
       </c>
       <c r="K6" t="n">
-        <v>6.35841954889094</v>
+        <v>6.358419548890983</v>
       </c>
       <c r="L6" t="n">
-        <v>4.922741864434733</v>
+        <v>4.922741864434776</v>
       </c>
       <c r="M6" t="n">
-        <v>5.705429171506675</v>
+        <v>5.705429171506703</v>
       </c>
       <c r="N6" t="n">
-        <v>4.272581751036259</v>
+        <v>4.272581751036184</v>
       </c>
       <c r="O6" t="n">
-        <v>6.727572883443766</v>
+        <v>6.727572883443526</v>
       </c>
       <c r="P6" t="n">
-        <v>3.22179201059351</v>
+        <v>3.221792010593469</v>
       </c>
       <c r="Q6" t="n">
-        <v>6.504968014333183</v>
+        <v>6.504968014333172</v>
       </c>
       <c r="R6" t="n">
-        <v>5.948477319341792</v>
+        <v>5.948477319341901</v>
       </c>
       <c r="S6" t="n">
-        <v>6.826548076768017</v>
+        <v>6.826548076767954</v>
       </c>
       <c r="T6" t="n">
-        <v>3.697786248582644</v>
+        <v>3.697786248582677</v>
       </c>
       <c r="U6" t="n">
-        <v>3.207970227413738</v>
+        <v>3.207970227413832</v>
       </c>
       <c r="V6" t="n">
-        <v>3.765675006649986</v>
+        <v>3.76567500664998</v>
       </c>
       <c r="W6" t="n">
-        <v>4.041529941787124</v>
+        <v>4.041529941787214</v>
       </c>
       <c r="X6" t="n">
-        <v>6.370084186192678</v>
+        <v>6.370084186192846</v>
       </c>
       <c r="Y6" t="n">
-        <v>3.422747880558282</v>
+        <v>3.422747880558247</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.684956813154922</v>
+        <v>4.684956813154959</v>
       </c>
       <c r="AA6" t="n">
-        <v>5.569846106433268</v>
+        <v>5.569846106433186</v>
       </c>
       <c r="AB6" t="n">
-        <v>3.315907661825043</v>
+        <v>3.315907661825045</v>
       </c>
     </row>
     <row r="7">
@@ -6186,85 +6186,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.402427007544466</v>
+        <v>5.402427007544583</v>
       </c>
       <c r="C7" t="n">
-        <v>4.221274160908559</v>
+        <v>4.221274160908665</v>
       </c>
       <c r="D7" t="n">
-        <v>3.140831897333467</v>
+        <v>3.1408318973336</v>
       </c>
       <c r="E7" t="n">
-        <v>7.423010272878016</v>
+        <v>7.423010272877995</v>
       </c>
       <c r="F7" t="n">
-        <v>5.817873336531485</v>
+        <v>5.817873336531572</v>
       </c>
       <c r="G7" t="n">
-        <v>3.468661685433494</v>
+        <v>3.468661685433626</v>
       </c>
       <c r="H7" t="n">
-        <v>3.565864792844299</v>
+        <v>3.565864792844426</v>
       </c>
       <c r="I7" t="n">
-        <v>4.993313109004391</v>
+        <v>4.993313109004454</v>
       </c>
       <c r="J7" t="n">
-        <v>4.081566307319076</v>
+        <v>4.081566307319108</v>
       </c>
       <c r="K7" t="n">
-        <v>4.100904581700515</v>
+        <v>4.100904581700527</v>
       </c>
       <c r="L7" t="n">
-        <v>5.007861638421298</v>
+        <v>5.007861638421327</v>
       </c>
       <c r="M7" t="n">
-        <v>3.447914204316349</v>
+        <v>3.447914204316374</v>
       </c>
       <c r="N7" t="n">
-        <v>4.362393899911406</v>
+        <v>4.362393899911462</v>
       </c>
       <c r="O7" t="n">
-        <v>4.364312445657445</v>
+        <v>4.364312445657487</v>
       </c>
       <c r="P7" t="n">
-        <v>3.397737549974329</v>
+        <v>3.39773754997434</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.247453047142753</v>
+        <v>4.247453047142847</v>
       </c>
       <c r="R7" t="n">
-        <v>6.033597093328358</v>
+        <v>6.033597093328396</v>
       </c>
       <c r="S7" t="n">
-        <v>4.569033109577533</v>
+        <v>4.569033109577655</v>
       </c>
       <c r="T7" t="n">
-        <v>3.782906022569118</v>
+        <v>3.782906022569176</v>
       </c>
       <c r="U7" t="n">
-        <v>3.273824329430913</v>
+        <v>3.273824329430953</v>
       </c>
       <c r="V7" t="n">
-        <v>3.850794780636517</v>
+        <v>3.850794780636512</v>
       </c>
       <c r="W7" t="n">
-        <v>4.09961798996602</v>
+        <v>4.099617989966171</v>
       </c>
       <c r="X7" t="n">
-        <v>4.112569219002285</v>
+        <v>4.112569219002211</v>
       </c>
       <c r="Y7" t="n">
-        <v>3.492531946251103</v>
+        <v>3.49253194625121</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.770076587141367</v>
+        <v>4.770076587141521</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.312331139242818</v>
+        <v>3.31233113924292</v>
       </c>
       <c r="AB7" t="n">
-        <v>3.440818437567318</v>
+        <v>3.44081843756746</v>
       </c>
     </row>
     <row r="8">
@@ -6274,85 +6274,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7.360823246355128</v>
+        <v>7.360823246355261</v>
       </c>
       <c r="C8" t="n">
-        <v>8.31645765154631</v>
+        <v>8.316457651546258</v>
       </c>
       <c r="D8" t="n">
-        <v>7.236015387971215</v>
+        <v>7.236015387971102</v>
       </c>
       <c r="E8" t="n">
-        <v>10.38041758483426</v>
+        <v>10.38041758483428</v>
       </c>
       <c r="F8" t="n">
-        <v>8.109156055189406</v>
+        <v>8.109156055189437</v>
       </c>
       <c r="G8" t="n">
-        <v>8.006921932102129</v>
+        <v>8.006921932102179</v>
       </c>
       <c r="H8" t="n">
-        <v>7.661048283482046</v>
+        <v>7.661048283482016</v>
       </c>
       <c r="I8" t="n">
-        <v>9.088496599642145</v>
+        <v>9.088496599642042</v>
       </c>
       <c r="J8" t="n">
-        <v>8.176749797956786</v>
+        <v>8.176749797956731</v>
       </c>
       <c r="K8" t="n">
-        <v>8.196088072338259</v>
+        <v>8.196088072338208</v>
       </c>
       <c r="L8" t="n">
-        <v>9.103045129059019</v>
+        <v>9.103045129058948</v>
       </c>
       <c r="M8" t="n">
-        <v>7.543097694955136</v>
+        <v>7.543097694955133</v>
       </c>
       <c r="N8" t="n">
-        <v>6.801209791812065</v>
+        <v>6.801209791812052</v>
       </c>
       <c r="O8" t="n">
-        <v>7.258308693697121</v>
+        <v>7.258308693697131</v>
       </c>
       <c r="P8" t="n">
-        <v>6.180157153643719</v>
+        <v>6.180157153643768</v>
       </c>
       <c r="Q8" t="n">
-        <v>5.785921823295207</v>
+        <v>5.785921823295364</v>
       </c>
       <c r="R8" t="n">
-        <v>10.12878058396608</v>
+        <v>10.12878058396602</v>
       </c>
       <c r="S8" t="n">
-        <v>8.664216600215088</v>
+        <v>8.664216600215184</v>
       </c>
       <c r="T8" t="n">
-        <v>7.878089513206841</v>
+        <v>7.878089513206858</v>
       </c>
       <c r="U8" t="n">
-        <v>6.330402752090024</v>
+        <v>6.330402752090126</v>
       </c>
       <c r="V8" t="n">
-        <v>7.345490991971459</v>
+        <v>7.345490991971448</v>
       </c>
       <c r="W8" t="n">
-        <v>8.195221413010083</v>
+        <v>8.195221413010115</v>
       </c>
       <c r="X8" t="n">
-        <v>5.846878788019461</v>
+        <v>5.846878788019382</v>
       </c>
       <c r="Y8" t="n">
-        <v>9.686727664837644</v>
+        <v>9.686727664837647</v>
       </c>
       <c r="Z8" t="n">
-        <v>6.68878090644571</v>
+        <v>6.688780906445738</v>
       </c>
       <c r="AA8" t="n">
-        <v>7.407514629880526</v>
+        <v>7.407514629880482</v>
       </c>
       <c r="AB8" t="n">
-        <v>9.768054880806217</v>
+        <v>9.768054880806069</v>
       </c>
     </row>
     <row r="9">
@@ -6362,10 +6362,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>83.52986685770969</v>
+        <v>83.52986685770972</v>
       </c>
       <c r="C9" t="n">
-        <v>104.3436927403425</v>
+        <v>104.3436927403426</v>
       </c>
       <c r="D9" t="n">
         <v>103.2632504767674</v>
@@ -6374,34 +6374,34 @@
         <v>102.4690784175719</v>
       </c>
       <c r="F9" t="n">
-        <v>55.23586135051903</v>
+        <v>55.23586135051905</v>
       </c>
       <c r="G9" t="n">
-        <v>103.5910814870297</v>
+        <v>103.5910814870296</v>
       </c>
       <c r="H9" t="n">
-        <v>103.6882833722783</v>
+        <v>103.6882833722784</v>
       </c>
       <c r="I9" t="n">
-        <v>105.1157316884383</v>
+        <v>105.1157316884384</v>
       </c>
       <c r="J9" t="n">
-        <v>104.2039848867533</v>
+        <v>104.2039848867532</v>
       </c>
       <c r="K9" t="n">
-        <v>104.2233231611345</v>
+        <v>104.2233231611346</v>
       </c>
       <c r="L9" t="n">
-        <v>105.1302802178552</v>
+        <v>105.1302802178553</v>
       </c>
       <c r="M9" t="n">
         <v>103.5703327837502</v>
       </c>
       <c r="N9" t="n">
-        <v>104.4848124793454</v>
+        <v>104.4848124793455</v>
       </c>
       <c r="O9" t="n">
-        <v>111.7758359651136</v>
+        <v>111.7758359651137</v>
       </c>
       <c r="P9" t="n">
         <v>112.3945169028243</v>
@@ -6410,22 +6410,22 @@
         <v>104.3698728487389</v>
       </c>
       <c r="R9" t="n">
-        <v>106.1560156727623</v>
+        <v>106.1560156727625</v>
       </c>
       <c r="S9" t="n">
-        <v>104.6914516890116</v>
+        <v>104.6914516890117</v>
       </c>
       <c r="T9" t="n">
-        <v>103.9053246020031</v>
+        <v>103.9053246020033</v>
       </c>
       <c r="U9" t="n">
-        <v>103.4155085808342</v>
+        <v>103.4155085808343</v>
       </c>
       <c r="V9" t="n">
         <v>129.3549534938589</v>
       </c>
       <c r="W9" t="n">
-        <v>104.2220365694</v>
+        <v>104.2220365694002</v>
       </c>
       <c r="X9" t="n">
         <v>104.2349877984363</v>
@@ -6434,13 +6434,13 @@
         <v>103.6149505256851</v>
       </c>
       <c r="Z9" t="n">
-        <v>91.63147934795282</v>
+        <v>91.63147934795285</v>
       </c>
       <c r="AA9" t="n">
-        <v>103.4347497186767</v>
+        <v>103.4347497186769</v>
       </c>
       <c r="AB9" t="n">
-        <v>103.5632370170012</v>
+        <v>103.5632370170013</v>
       </c>
     </row>
   </sheetData>
@@ -6606,85 +6606,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.289717205110761</v>
+        <v>3.289717205110751</v>
       </c>
       <c r="C2" t="n">
-        <v>3.45283308636466</v>
+        <v>3.452833086364655</v>
       </c>
       <c r="D2" t="n">
-        <v>3.071776491331234</v>
+        <v>3.071776491331238</v>
       </c>
       <c r="E2" t="n">
-        <v>3.320744564775182</v>
+        <v>3.320744564775173</v>
       </c>
       <c r="F2" t="n">
-        <v>3.147561436439771</v>
+        <v>3.147561436439761</v>
       </c>
       <c r="G2" t="n">
-        <v>3.011139727644716</v>
+        <v>3.011139727644709</v>
       </c>
       <c r="H2" t="n">
-        <v>2.984352829577822</v>
+        <v>2.984352829577812</v>
       </c>
       <c r="I2" t="n">
-        <v>3.041401879416969</v>
+        <v>3.041401879416968</v>
       </c>
       <c r="J2" t="n">
-        <v>3.049464253972549</v>
+        <v>3.049464253972568</v>
       </c>
       <c r="K2" t="n">
-        <v>3.012644953319922</v>
+        <v>3.012644953319918</v>
       </c>
       <c r="L2" t="n">
-        <v>3.102428559899532</v>
+        <v>3.102428559899541</v>
       </c>
       <c r="M2" t="n">
-        <v>2.978473653760973</v>
+        <v>2.978473653760977</v>
       </c>
       <c r="N2" t="n">
-        <v>3.037322726020564</v>
+        <v>3.037322726020559</v>
       </c>
       <c r="O2" t="n">
-        <v>6.043936008986202</v>
+        <v>6.043936008986198</v>
       </c>
       <c r="P2" t="n">
-        <v>3.008163221724061</v>
+        <v>3.008163221724058</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.081611066061608</v>
+        <v>3.081611066061612</v>
       </c>
       <c r="R2" t="n">
-        <v>3.272028140796353</v>
+        <v>3.272028140796352</v>
       </c>
       <c r="S2" t="n">
-        <v>3.077358101811107</v>
+        <v>3.07735810181111</v>
       </c>
       <c r="T2" t="n">
         <v>2.994955834638783</v>
       </c>
       <c r="U2" t="n">
-        <v>4.194003425772692</v>
+        <v>4.194003425772728</v>
       </c>
       <c r="V2" t="n">
-        <v>3.042384385776159</v>
+        <v>3.042384385776163</v>
       </c>
       <c r="W2" t="n">
-        <v>4.545934196652236</v>
+        <v>4.545934196652238</v>
       </c>
       <c r="X2" t="n">
-        <v>3.050905523920061</v>
+        <v>3.05090552392006</v>
       </c>
       <c r="Y2" t="n">
-        <v>3.016254973668923</v>
+        <v>3.016254973668917</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.650499389283862</v>
+        <v>3.650499389283882</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.988111646959944</v>
+        <v>2.988111646959942</v>
       </c>
       <c r="AB2" t="n">
-        <v>3.009527721494161</v>
+        <v>3.00952772149416</v>
       </c>
     </row>
     <row r="3">
@@ -6694,85 +6694,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.197899365788602</v>
+        <v>5.290419975966418</v>
       </c>
       <c r="C3" t="n">
-        <v>4.481263302994123</v>
+        <v>4.529028471371746</v>
       </c>
       <c r="D3" t="n">
-        <v>3.653697722990397</v>
+        <v>3.692220792873634</v>
       </c>
       <c r="E3" t="n">
-        <v>5.420472822573493</v>
+        <v>5.521233979171849</v>
       </c>
       <c r="F3" t="n">
-        <v>4.197274581962657</v>
+        <v>4.255293852601198</v>
       </c>
       <c r="G3" t="n">
-        <v>3.218144406955536</v>
+        <v>3.241022267513811</v>
       </c>
       <c r="H3" t="n">
-        <v>3.030915085224303</v>
+        <v>3.047304724512085</v>
       </c>
       <c r="I3" t="n">
-        <v>3.438337584677256</v>
+        <v>3.46919298502953</v>
       </c>
       <c r="J3" t="n">
-        <v>3.491876428371059</v>
+        <v>3.524516210298397</v>
       </c>
       <c r="K3" t="n">
-        <v>3.230992513685412</v>
+        <v>3.254475709578259</v>
       </c>
       <c r="L3" t="n">
-        <v>3.864094164305444</v>
+        <v>3.910035173212076</v>
       </c>
       <c r="M3" t="n">
-        <v>3.008219345670884</v>
+        <v>3.023920419671568</v>
       </c>
       <c r="N3" t="n">
-        <v>3.40757742115645</v>
+        <v>3.437253244344435</v>
       </c>
       <c r="O3" t="n">
-        <v>8.576343510882102</v>
+        <v>8.615354472709503</v>
       </c>
       <c r="P3" t="n">
-        <v>3.197154563266038</v>
+        <v>3.219248224772575</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.721439973493786</v>
+        <v>3.762372339112354</v>
       </c>
       <c r="R3" t="n">
-        <v>5.090647383284414</v>
+        <v>5.18034997894417</v>
       </c>
       <c r="S3" t="n">
-        <v>3.688102976463906</v>
+        <v>3.727630108010938</v>
       </c>
       <c r="T3" t="n">
-        <v>3.105816507074024</v>
+        <v>3.124839807834469</v>
       </c>
       <c r="U3" t="n">
-        <v>5.009076422942927</v>
+        <v>5.024558524328918</v>
       </c>
       <c r="V3" t="n">
-        <v>3.440168338952648</v>
+        <v>3.470876642093841</v>
       </c>
       <c r="W3" t="n">
-        <v>6.089701117119567</v>
+        <v>6.128183653859335</v>
       </c>
       <c r="X3" t="n">
-        <v>3.502999136628425</v>
+        <v>3.536196554055131</v>
       </c>
       <c r="Y3" t="n">
-        <v>3.257785763758861</v>
+        <v>3.282103487573528</v>
       </c>
       <c r="Z3" t="n">
-        <v>4.752780506040195</v>
+        <v>4.797784889690321</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.056584240136559</v>
+        <v>3.073789029930559</v>
       </c>
       <c r="AB3" t="n">
-        <v>3.226592582869135</v>
+        <v>3.24995385058203</v>
       </c>
     </row>
     <row r="4">
@@ -6782,85 +6782,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.085564332464038</v>
+        <v>6.085564332464105</v>
       </c>
       <c r="C4" t="n">
-        <v>4.037051225794204</v>
+        <v>4.037051225794304</v>
       </c>
       <c r="D4" t="n">
-        <v>3.623823712642789</v>
+        <v>3.623823712642864</v>
       </c>
       <c r="E4" t="n">
-        <v>6.436032633164338</v>
+        <v>6.436032633164233</v>
       </c>
       <c r="F4" t="n">
-        <v>4.479849530440766</v>
+        <v>4.479849530440963</v>
       </c>
       <c r="G4" t="n">
-        <v>2.938903572514018</v>
+        <v>2.93890357251406</v>
       </c>
       <c r="H4" t="n">
-        <v>2.636333236266583</v>
+        <v>2.636333236266562</v>
       </c>
       <c r="I4" t="n">
-        <v>3.280728498059345</v>
+        <v>3.280728498059357</v>
       </c>
       <c r="J4" t="n">
-        <v>3.370703454333192</v>
+        <v>3.37070345433323</v>
       </c>
       <c r="K4" t="n">
-        <v>2.955905788953524</v>
+        <v>2.955905788953555</v>
       </c>
       <c r="L4" t="n">
-        <v>3.970052927769806</v>
+        <v>3.970052927769967</v>
       </c>
       <c r="M4" t="n">
-        <v>2.607121539718747</v>
+        <v>2.607121539718855</v>
       </c>
       <c r="N4" t="n">
-        <v>3.234652583943517</v>
+        <v>3.234652583943737</v>
       </c>
       <c r="O4" t="n">
-        <v>3.669760390924519</v>
+        <v>3.669760390924504</v>
       </c>
       <c r="P4" t="n">
-        <v>2.905282568879894</v>
+        <v>2.905282568879907</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.734909758350145</v>
+        <v>3.734909758350296</v>
       </c>
       <c r="R4" t="n">
-        <v>5.885758213661264</v>
+        <v>5.885758213661325</v>
       </c>
       <c r="S4" t="n">
-        <v>3.686870570680592</v>
+        <v>3.686870570680681</v>
       </c>
       <c r="T4" t="n">
-        <v>2.756099056053434</v>
+        <v>2.756099056053621</v>
       </c>
       <c r="U4" t="n">
-        <v>2.440145443213641</v>
+        <v>2.4401454432137</v>
       </c>
       <c r="V4" t="n">
-        <v>3.285371345014326</v>
+        <v>3.285371345014348</v>
       </c>
       <c r="W4" t="n">
-        <v>3.632819735701069</v>
+        <v>3.632819735701073</v>
       </c>
       <c r="X4" t="n">
-        <v>3.388076534614168</v>
+        <v>3.388076534614202</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.833777969520669</v>
+        <v>2.833777969520824</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.936997075505811</v>
+        <v>3.936997075505906</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.678790807739047</v>
+        <v>2.678790807739196</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.949240782933377</v>
+        <v>2.949240782933326</v>
       </c>
     </row>
     <row r="5">
@@ -6870,19 +6870,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>65.1118291558416</v>
+        <v>65.11182915584175</v>
       </c>
       <c r="C5" t="n">
-        <v>34.32422296420146</v>
+        <v>34.32422296420155</v>
       </c>
       <c r="D5" t="n">
         <v>27.40299803876711</v>
       </c>
       <c r="E5" t="n">
-        <v>71.89584881445381</v>
+        <v>71.89584881445367</v>
       </c>
       <c r="F5" t="n">
-        <v>43.94032344743562</v>
+        <v>43.94032344743593</v>
       </c>
       <c r="G5" t="n">
         <v>13.84543110045678</v>
@@ -6891,64 +6891,64 @@
         <v>10.5410173931668</v>
       </c>
       <c r="I5" t="n">
-        <v>22.07325341588406</v>
+        <v>22.07325341588407</v>
       </c>
       <c r="J5" t="n">
-        <v>21.60854095645568</v>
+        <v>21.60854095645577</v>
       </c>
       <c r="K5" t="n">
-        <v>15.23712862669227</v>
+        <v>15.23712862669234</v>
       </c>
       <c r="L5" t="n">
-        <v>29.18966246128461</v>
+        <v>29.18966246128469</v>
       </c>
       <c r="M5" t="n">
-        <v>9.534501493285704</v>
+        <v>9.534501493285747</v>
       </c>
       <c r="N5" t="n">
-        <v>20.40478683821665</v>
+        <v>20.40478683821657</v>
       </c>
       <c r="O5" t="n">
-        <v>25.2306390378361</v>
+        <v>25.23063903783618</v>
       </c>
       <c r="P5" t="n">
-        <v>13.38222417616187</v>
+        <v>13.38222417616212</v>
       </c>
       <c r="Q5" t="n">
-        <v>28.09933153881808</v>
+        <v>28.09933153881806</v>
       </c>
       <c r="R5" t="n">
-        <v>71.42199535956254</v>
+        <v>71.4219953595627</v>
       </c>
       <c r="S5" t="n">
-        <v>25.70361853201441</v>
+        <v>25.7036185320144</v>
       </c>
       <c r="T5" t="n">
-        <v>12.25881342984594</v>
+        <v>12.25881342984616</v>
       </c>
       <c r="U5" t="n">
-        <v>8.724416309908056</v>
+        <v>8.724416309908131</v>
       </c>
       <c r="V5" t="n">
-        <v>19.57793099534462</v>
+        <v>19.57793099534461</v>
       </c>
       <c r="W5" t="n">
-        <v>26.66388433238836</v>
+        <v>26.66388433238857</v>
       </c>
       <c r="X5" t="n">
-        <v>22.33095704427158</v>
+        <v>22.33095704427159</v>
       </c>
       <c r="Y5" t="n">
-        <v>16.49125321305124</v>
+        <v>16.49125321305112</v>
       </c>
       <c r="Z5" t="n">
-        <v>28.63134284440373</v>
+        <v>28.63134284440391</v>
       </c>
       <c r="AA5" t="n">
-        <v>10.69199461036785</v>
+        <v>10.69199461036802</v>
       </c>
       <c r="AB5" t="n">
-        <v>16.33113218792017</v>
+        <v>16.33113218792016</v>
       </c>
     </row>
     <row r="6">
@@ -6958,85 +6958,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9.348776175394557</v>
+        <v>9.34877617539459</v>
       </c>
       <c r="C6" t="n">
-        <v>7.300263068724725</v>
+        <v>7.300263068724712</v>
       </c>
       <c r="D6" t="n">
-        <v>6.887035555573192</v>
+        <v>6.887035555573283</v>
       </c>
       <c r="E6" t="n">
-        <v>7.275486890337284</v>
+        <v>7.275486890337325</v>
       </c>
       <c r="F6" t="n">
-        <v>7.743061373371288</v>
+        <v>7.743061373371322</v>
       </c>
       <c r="G6" t="n">
-        <v>6.202115415444547</v>
+        <v>6.202115415444548</v>
       </c>
       <c r="H6" t="n">
-        <v>5.899545079197006</v>
+        <v>5.899545079197072</v>
       </c>
       <c r="I6" t="n">
-        <v>6.543940340989677</v>
+        <v>6.543940340989821</v>
       </c>
       <c r="J6" t="n">
-        <v>4.210157711506187</v>
+        <v>4.210157711506207</v>
       </c>
       <c r="K6" t="n">
-        <v>3.795360046126499</v>
+        <v>3.79536004612658</v>
       </c>
       <c r="L6" t="n">
-        <v>7.233264770700329</v>
+        <v>7.233264770700364</v>
       </c>
       <c r="M6" t="n">
-        <v>5.87033338264927</v>
+        <v>5.870333382649292</v>
       </c>
       <c r="N6" t="n">
-        <v>4.069452934234431</v>
+        <v>4.069452934234498</v>
       </c>
       <c r="O6" t="n">
-        <v>4.486164010661235</v>
+        <v>4.486164010661299</v>
       </c>
       <c r="P6" t="n">
-        <v>6.296548801097863</v>
+        <v>6.296548801098164</v>
       </c>
       <c r="Q6" t="n">
-        <v>6.9981216012807</v>
+        <v>6.998121601280756</v>
       </c>
       <c r="R6" t="n">
-        <v>9.148970056591748</v>
+        <v>9.148970056591805</v>
       </c>
       <c r="S6" t="n">
-        <v>6.950082413611115</v>
+        <v>6.950082413611189</v>
       </c>
       <c r="T6" t="n">
-        <v>3.595553313226473</v>
+        <v>3.595553313226457</v>
       </c>
       <c r="U6" t="n">
-        <v>5.866261946110321</v>
+        <v>5.866261946110362</v>
       </c>
       <c r="V6" t="n">
-        <v>4.124825602187284</v>
+        <v>4.124825602187382</v>
       </c>
       <c r="W6" t="n">
-        <v>7.016197340652296</v>
+        <v>7.016197340652623</v>
       </c>
       <c r="X6" t="n">
-        <v>4.227530791787117</v>
+        <v>4.227530791787185</v>
       </c>
       <c r="Y6" t="n">
-        <v>3.856796571892457</v>
+        <v>3.856796571892409</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.776451332678817</v>
+        <v>4.776451332678803</v>
       </c>
       <c r="AA6" t="n">
-        <v>5.942002650669537</v>
+        <v>5.942002650669589</v>
       </c>
       <c r="AB6" t="n">
-        <v>3.749663004295965</v>
+        <v>3.749663004296047</v>
       </c>
     </row>
     <row r="7">
@@ -7046,85 +7046,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6.972914963501511</v>
+        <v>6.972914963501519</v>
       </c>
       <c r="C7" t="n">
-        <v>4.924401856831751</v>
+        <v>4.924401856831678</v>
       </c>
       <c r="D7" t="n">
-        <v>4.511174343680275</v>
+        <v>4.511174343680239</v>
       </c>
       <c r="E7" t="n">
-        <v>7.323383264201816</v>
+        <v>7.323383264202073</v>
       </c>
       <c r="F7" t="n">
-        <v>5.367200161478275</v>
+        <v>5.367200161478421</v>
       </c>
       <c r="G7" t="n">
-        <v>3.826254203551559</v>
+        <v>3.826254203551669</v>
       </c>
       <c r="H7" t="n">
-        <v>3.523683867304064</v>
+        <v>3.523683867304207</v>
       </c>
       <c r="I7" t="n">
-        <v>4.168079129096794</v>
+        <v>4.168079129096719</v>
       </c>
       <c r="J7" t="n">
-        <v>4.258054085370701</v>
+        <v>4.258054085370742</v>
       </c>
       <c r="K7" t="n">
-        <v>3.843256419991098</v>
+        <v>3.843256419991123</v>
       </c>
       <c r="L7" t="n">
-        <v>4.857403558807349</v>
+        <v>4.857403558807305</v>
       </c>
       <c r="M7" t="n">
-        <v>3.494472170756286</v>
+        <v>3.494472170756281</v>
       </c>
       <c r="N7" t="n">
-        <v>4.122003214981086</v>
+        <v>4.122003214981234</v>
       </c>
       <c r="O7" t="n">
-        <v>4.557119590659822</v>
+        <v>4.55711959065995</v>
       </c>
       <c r="P7" t="n">
-        <v>3.792641768615196</v>
+        <v>3.792641768615252</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.622260389387689</v>
+        <v>4.622260389387725</v>
       </c>
       <c r="R7" t="n">
-        <v>6.773108844698833</v>
+        <v>6.77310884469875</v>
       </c>
       <c r="S7" t="n">
-        <v>4.574221201718131</v>
+        <v>4.574221201718077</v>
       </c>
       <c r="T7" t="n">
-        <v>3.643449687091039</v>
+        <v>3.64344968709111</v>
       </c>
       <c r="U7" t="n">
-        <v>3.462719161891451</v>
+        <v>3.462719161891641</v>
       </c>
       <c r="V7" t="n">
-        <v>4.172721976051831</v>
+        <v>4.172721976051892</v>
       </c>
       <c r="W7" t="n">
-        <v>4.520170366738519</v>
+        <v>4.52017036673853</v>
       </c>
       <c r="X7" t="n">
-        <v>4.275427165651806</v>
+        <v>4.275427165651593</v>
       </c>
       <c r="Y7" t="n">
-        <v>3.884033260524431</v>
+        <v>3.884033260524481</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.824347706543318</v>
+        <v>4.824347706543299</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.566141438776585</v>
+        <v>3.566141438776567</v>
       </c>
       <c r="AB7" t="n">
-        <v>3.836591413970827</v>
+        <v>3.836591413970784</v>
       </c>
     </row>
     <row r="8">
@@ -7134,85 +7134,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8.988928278444657</v>
+        <v>8.988928278444721</v>
       </c>
       <c r="C8" t="n">
-        <v>9.187148725604546</v>
+        <v>9.187148725604693</v>
       </c>
       <c r="D8" t="n">
-        <v>8.773921212453208</v>
+        <v>8.773921212453248</v>
       </c>
       <c r="E8" t="n">
-        <v>10.38981079197581</v>
+        <v>10.38981079197593</v>
       </c>
       <c r="F8" t="n">
-        <v>7.733228305000692</v>
+        <v>7.73322830500073</v>
       </c>
       <c r="G8" t="n">
-        <v>8.554875910190088</v>
+        <v>8.554875910190294</v>
       </c>
       <c r="H8" t="n">
-        <v>7.78643073607696</v>
+        <v>7.786430736077044</v>
       </c>
       <c r="I8" t="n">
-        <v>8.430825997869656</v>
+        <v>8.430825997869784</v>
       </c>
       <c r="J8" t="n">
-        <v>8.520800954143528</v>
+        <v>8.52080095414367</v>
       </c>
       <c r="K8" t="n">
-        <v>8.106003288763812</v>
+        <v>8.106003288763905</v>
       </c>
       <c r="L8" t="n">
-        <v>9.120150427580157</v>
+        <v>9.120150427580208</v>
       </c>
       <c r="M8" t="n">
-        <v>7.757219039541186</v>
+        <v>7.757219039541321</v>
       </c>
       <c r="N8" t="n">
-        <v>6.643155706989527</v>
+        <v>6.643155706989633</v>
       </c>
       <c r="O8" t="n">
-        <v>7.556868766053143</v>
+        <v>7.556868766053261</v>
       </c>
       <c r="P8" t="n">
-        <v>6.675073232500785</v>
+        <v>6.675073232500853</v>
       </c>
       <c r="Q8" t="n">
-        <v>6.19673928432584</v>
+        <v>6.196739284325872</v>
       </c>
       <c r="R8" t="n">
-        <v>11.03585571347165</v>
+        <v>11.03585571347174</v>
       </c>
       <c r="S8" t="n">
-        <v>8.836968070491013</v>
+        <v>8.836968070491015</v>
       </c>
       <c r="T8" t="n">
-        <v>7.906196555863819</v>
+        <v>7.906196555863903</v>
       </c>
       <c r="U8" t="n">
-        <v>6.635087757327189</v>
+        <v>6.635087757327269</v>
       </c>
       <c r="V8" t="n">
-        <v>7.797733835660466</v>
+        <v>7.7977338356605</v>
       </c>
       <c r="W8" t="n">
-        <v>8.783358774093376</v>
+        <v>8.78335877409349</v>
       </c>
       <c r="X8" t="n">
-        <v>6.055823649621563</v>
+        <v>6.055823649621732</v>
       </c>
       <c r="Y8" t="n">
-        <v>10.34394574749267</v>
+        <v>10.34394574749274</v>
       </c>
       <c r="Z8" t="n">
-        <v>6.798626793108876</v>
+        <v>6.798626793109036</v>
       </c>
       <c r="AA8" t="n">
-        <v>7.828888307549399</v>
+        <v>7.828888307549579</v>
       </c>
       <c r="AB8" t="n">
-        <v>10.44623933999174</v>
+        <v>10.44623933999191</v>
       </c>
     </row>
     <row r="9">
@@ -7222,7 +7222,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>85.00767314614951</v>
+        <v>85.00767314614964</v>
       </c>
       <c r="C9" t="n">
         <v>104.9604273252745</v>
@@ -7231,70 +7231,70 @@
         <v>104.5471998121232</v>
       </c>
       <c r="E9" t="n">
-        <v>102.2816069876303</v>
+        <v>102.2816069876304</v>
       </c>
       <c r="F9" t="n">
-        <v>54.68429811860008</v>
+        <v>54.68429811860023</v>
       </c>
       <c r="G9" t="n">
         <v>103.8622809759568</v>
       </c>
       <c r="H9" t="n">
-        <v>103.5597093357469</v>
+        <v>103.559709335747</v>
       </c>
       <c r="I9" t="n">
         <v>104.2041045975396</v>
       </c>
       <c r="J9" t="n">
-        <v>104.2940795538136</v>
+        <v>104.2940795538137</v>
       </c>
       <c r="K9" t="n">
-        <v>103.879281888434</v>
+        <v>103.8792818884342</v>
       </c>
       <c r="L9" t="n">
-        <v>104.8934290272503</v>
+        <v>104.8934290272504</v>
       </c>
       <c r="M9" t="n">
-        <v>103.5304976391992</v>
+        <v>103.5304976391991</v>
       </c>
       <c r="N9" t="n">
-        <v>104.158028683424</v>
+        <v>104.1580286834241</v>
       </c>
       <c r="O9" t="n">
         <v>111.8843293968026</v>
       </c>
       <c r="P9" t="n">
-        <v>112.7055606525112</v>
+        <v>112.7055606525114</v>
       </c>
       <c r="Q9" t="n">
-        <v>104.658287161793</v>
+        <v>104.6582871617932</v>
       </c>
       <c r="R9" t="n">
         <v>106.8091343131417</v>
       </c>
       <c r="S9" t="n">
-        <v>104.6102466701609</v>
+        <v>104.610246670161</v>
       </c>
       <c r="T9" t="n">
-        <v>103.6794751555336</v>
+        <v>103.6794751555339</v>
       </c>
       <c r="U9" t="n">
-        <v>103.5264262026603</v>
+        <v>103.5264262026604</v>
       </c>
       <c r="V9" t="n">
-        <v>129.597744568313</v>
+        <v>129.5977445683131</v>
       </c>
       <c r="W9" t="n">
         <v>104.5561958351815</v>
       </c>
       <c r="X9" t="n">
-        <v>104.3114526340945</v>
+        <v>104.3114526340946</v>
       </c>
       <c r="Y9" t="n">
-        <v>103.9200587289673</v>
+        <v>103.9200587289674</v>
       </c>
       <c r="Z9" t="n">
-        <v>91.59556594846052</v>
+        <v>91.59556594846063</v>
       </c>
       <c r="AA9" t="n">
         <v>103.6021669072194</v>
@@ -7466,85 +7466,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.296974047046325</v>
+        <v>2.296974047046344</v>
       </c>
       <c r="C2" t="n">
-        <v>2.348894663363299</v>
+        <v>2.348894663363341</v>
       </c>
       <c r="D2" t="n">
-        <v>2.262336912219033</v>
+        <v>2.262336912219056</v>
       </c>
       <c r="E2" t="n">
-        <v>2.350843158358721</v>
+        <v>2.350843158358732</v>
       </c>
       <c r="F2" t="n">
-        <v>2.33374295871989</v>
+        <v>2.333742958719911</v>
       </c>
       <c r="G2" t="n">
-        <v>2.367977575825368</v>
+        <v>2.367977575825403</v>
       </c>
       <c r="H2" t="n">
-        <v>2.267355694162637</v>
+        <v>2.267355694162676</v>
       </c>
       <c r="I2" t="n">
-        <v>2.364311013827875</v>
+        <v>2.364311013827878</v>
       </c>
       <c r="J2" t="n">
-        <v>2.32858076683651</v>
+        <v>2.328580766836521</v>
       </c>
       <c r="K2" t="n">
-        <v>2.371923535264024</v>
+        <v>2.371923535264078</v>
       </c>
       <c r="L2" t="n">
-        <v>2.324545505482345</v>
+        <v>2.324545505482372</v>
       </c>
       <c r="M2" t="n">
-        <v>2.3919767403412</v>
+        <v>2.391976740341239</v>
       </c>
       <c r="N2" t="n">
-        <v>2.299583070746583</v>
+        <v>2.299583070746621</v>
       </c>
       <c r="O2" t="n">
-        <v>4.245885709121339</v>
+        <v>4.245885709121336</v>
       </c>
       <c r="P2" t="n">
-        <v>2.297933541402521</v>
+        <v>2.297933541402565</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.333936224417935</v>
+        <v>2.33393622441797</v>
       </c>
       <c r="R2" t="n">
-        <v>2.334870188047368</v>
+        <v>2.334870188047416</v>
       </c>
       <c r="S2" t="n">
-        <v>2.355348922852984</v>
+        <v>2.355348922853024</v>
       </c>
       <c r="T2" t="n">
-        <v>2.294379641524253</v>
+        <v>2.29437964152427</v>
       </c>
       <c r="U2" t="n">
-        <v>2.677755071062309</v>
+        <v>2.677755071062405</v>
       </c>
       <c r="V2" t="n">
-        <v>2.28722030185991</v>
+        <v>2.287220301859954</v>
       </c>
       <c r="W2" t="n">
-        <v>2.801052559733495</v>
+        <v>2.801052559733612</v>
       </c>
       <c r="X2" t="n">
-        <v>2.336793714404096</v>
+        <v>2.336793714404115</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.293661830048227</v>
+        <v>2.293661830048234</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.217088971164569</v>
+        <v>2.217088971164619</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.280756173812253</v>
+        <v>2.280756173812293</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.345661968121422</v>
+        <v>2.345661968121469</v>
       </c>
     </row>
     <row r="3">
@@ -7554,85 +7554,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.572598310496395</v>
+        <v>2.588636869183746</v>
       </c>
       <c r="C3" t="n">
-        <v>2.63662137748303</v>
+        <v>2.651826070976084</v>
       </c>
       <c r="D3" t="n">
-        <v>2.327451874502726</v>
+        <v>2.334904180111414</v>
       </c>
       <c r="E3" t="n">
-        <v>2.958775934764759</v>
+        <v>2.988349800975752</v>
       </c>
       <c r="F3" t="n">
-        <v>2.838331580014116</v>
+        <v>2.864029107474721</v>
       </c>
       <c r="G3" t="n">
-        <v>3.076553650435982</v>
+        <v>3.11036232739447</v>
       </c>
       <c r="H3" t="n">
-        <v>2.363836132368519</v>
+        <v>2.372604176301939</v>
       </c>
       <c r="I3" t="n">
-        <v>3.057490496471345</v>
+        <v>3.090895533712259</v>
       </c>
       <c r="J3" t="n">
-        <v>2.798015623181571</v>
+        <v>2.822082886419846</v>
       </c>
       <c r="K3" t="n">
-        <v>3.10661300013589</v>
+        <v>3.141847390174721</v>
       </c>
       <c r="L3" t="n">
-        <v>2.769918710146106</v>
+        <v>2.792978954775599</v>
       </c>
       <c r="M3" t="n">
-        <v>3.25086908500765</v>
+        <v>3.291359757265725</v>
       </c>
       <c r="N3" t="n">
-        <v>2.593367646320614</v>
+        <v>2.610218119014077</v>
       </c>
       <c r="O3" t="n">
-        <v>5.692123924809483</v>
+        <v>5.70369235672242</v>
       </c>
       <c r="P3" t="n">
-        <v>2.579799958954037</v>
+        <v>2.59605151212968</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.838183664531467</v>
+        <v>2.863759179235568</v>
       </c>
       <c r="R3" t="n">
-        <v>2.847668407532754</v>
+        <v>2.873631572217644</v>
       </c>
       <c r="S3" t="n">
-        <v>2.986206229185968</v>
+        <v>3.01692674143817</v>
       </c>
       <c r="T3" t="n">
-        <v>2.556815153005821</v>
+        <v>2.572412566834983</v>
       </c>
       <c r="U3" t="n">
-        <v>3.165967752974291</v>
+        <v>3.180414877006537</v>
       </c>
       <c r="V3" t="n">
-        <v>2.503134544712687</v>
+        <v>2.516741648701077</v>
       </c>
       <c r="W3" t="n">
-        <v>3.284034712963791</v>
+        <v>3.294560851037688</v>
       </c>
       <c r="X3" t="n">
-        <v>2.859747574787682</v>
+        <v>2.886084541700996</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.55053672668643</v>
+        <v>2.565868053843682</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.323227012592789</v>
+        <v>2.333882658090928</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.458557282294555</v>
+        <v>2.47062322796516</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.925415807854112</v>
+        <v>2.954018502906536</v>
       </c>
     </row>
     <row r="4">
@@ -7642,85 +7642,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.059087429556583</v>
+        <v>2.059087429556491</v>
       </c>
       <c r="C4" t="n">
-        <v>2.013326869072522</v>
+        <v>2.013326869072438</v>
       </c>
       <c r="D4" t="n">
-        <v>1.66784505781294</v>
+        <v>1.66784505781286</v>
       </c>
       <c r="E4" t="n">
-        <v>2.66756382284561</v>
+        <v>2.667563822845514</v>
       </c>
       <c r="F4" t="n">
-        <v>2.474409201444528</v>
+        <v>2.47440920144441</v>
       </c>
       <c r="G4" t="n">
-        <v>2.861104950352935</v>
+        <v>2.861104950352938</v>
       </c>
       <c r="H4" t="n">
-        <v>1.724534508619941</v>
+        <v>1.724534508619784</v>
       </c>
       <c r="I4" t="n">
-        <v>2.819689445889205</v>
+        <v>2.819689445889201</v>
       </c>
       <c r="J4" t="n">
-        <v>2.415008934397937</v>
+        <v>2.415008934397834</v>
       </c>
       <c r="K4" t="n">
-        <v>2.905676377443575</v>
+        <v>2.905676377443447</v>
       </c>
       <c r="L4" t="n">
-        <v>2.370519736088788</v>
+        <v>2.370519736088744</v>
       </c>
       <c r="M4" t="n">
-        <v>3.131039336090281</v>
+        <v>3.131039336090171</v>
       </c>
       <c r="N4" t="n">
-        <v>2.088557552461184</v>
+        <v>2.088557552461062</v>
       </c>
       <c r="O4" t="n">
-        <v>1.857579459276364</v>
+        <v>1.857579459276249</v>
       </c>
       <c r="P4" t="n">
-        <v>2.069925359699046</v>
+        <v>2.069925359699192</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.476592226410497</v>
+        <v>2.476592226410376</v>
       </c>
       <c r="R4" t="n">
-        <v>2.487141775249516</v>
+        <v>2.48714177524951</v>
       </c>
       <c r="S4" t="n">
-        <v>2.718458505562406</v>
+        <v>2.71845850556238</v>
       </c>
       <c r="T4" t="n">
-        <v>2.029782425699193</v>
+        <v>2.029782425699156</v>
       </c>
       <c r="U4" t="n">
-        <v>1.85394687555402</v>
+        <v>1.853946875554101</v>
       </c>
       <c r="V4" t="n">
-        <v>1.942160916964028</v>
+        <v>1.942160916964037</v>
       </c>
       <c r="W4" t="n">
-        <v>1.807230503286222</v>
+        <v>1.807230503286174</v>
       </c>
       <c r="X4" t="n">
-        <v>2.508868890314484</v>
+        <v>2.508868890314487</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.891245767361997</v>
+        <v>1.891245767361786</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.815502936263407</v>
+        <v>1.815502936263412</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.875899090787462</v>
+        <v>1.87589909078734</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.60837456544885</v>
+        <v>2.608374565448759</v>
       </c>
     </row>
     <row r="5">
@@ -7730,85 +7730,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>12.25166952336325</v>
+        <v>12.25166952336326</v>
       </c>
       <c r="C5" t="n">
-        <v>12.49966065377071</v>
+        <v>12.49966065377097</v>
       </c>
       <c r="D5" t="n">
-        <v>6.000060068376128</v>
+        <v>6.000060068376286</v>
       </c>
       <c r="E5" t="n">
-        <v>24.70831037029462</v>
+        <v>24.70831037029464</v>
       </c>
       <c r="F5" t="n">
-        <v>21.94635106933207</v>
+        <v>21.94635106933198</v>
       </c>
       <c r="G5" t="n">
-        <v>25.85870000630263</v>
+        <v>25.85870000630252</v>
       </c>
       <c r="H5" t="n">
-        <v>7.386143088669983</v>
+        <v>7.386143088670172</v>
       </c>
       <c r="I5" t="n">
-        <v>29.02723807378222</v>
+        <v>29.02723807378227</v>
       </c>
       <c r="J5" t="n">
-        <v>18.9111604363394</v>
+        <v>18.91116043633926</v>
       </c>
       <c r="K5" t="n">
-        <v>27.75638439353323</v>
+        <v>27.75638439353335</v>
       </c>
       <c r="L5" t="n">
-        <v>18.44137290719141</v>
+        <v>18.44137290719079</v>
       </c>
       <c r="M5" t="n">
-        <v>32.99561224001796</v>
+        <v>32.99561224001779</v>
       </c>
       <c r="N5" t="n">
-        <v>14.00383852928701</v>
+        <v>14.00383852928686</v>
       </c>
       <c r="O5" t="n">
-        <v>8.644814835465292</v>
+        <v>8.644814835465189</v>
       </c>
       <c r="P5" t="n">
-        <v>12.65329723047179</v>
+        <v>12.65329723047174</v>
       </c>
       <c r="Q5" t="n">
-        <v>21.13823707174754</v>
+        <v>21.13823707174751</v>
       </c>
       <c r="R5" t="n">
-        <v>22.90549902930837</v>
+        <v>22.90549902930846</v>
       </c>
       <c r="S5" t="n">
-        <v>23.04137269386008</v>
+        <v>23.04137269385987</v>
       </c>
       <c r="T5" t="n">
-        <v>13.2176731457118</v>
+        <v>13.21767314571185</v>
       </c>
       <c r="U5" t="n">
-        <v>11.47247589018786</v>
+        <v>11.47247589018759</v>
       </c>
       <c r="V5" t="n">
-        <v>10.24475260288635</v>
+        <v>10.24475260288636</v>
       </c>
       <c r="W5" t="n">
-        <v>8.431178319390936</v>
+        <v>8.431178319391098</v>
       </c>
       <c r="X5" t="n">
-        <v>22.39914241025882</v>
+        <v>22.39914241025861</v>
       </c>
       <c r="Y5" t="n">
-        <v>12.42180600694493</v>
+        <v>12.42180600694497</v>
       </c>
       <c r="Z5" t="n">
-        <v>8.094324325905504</v>
+        <v>8.094324325905399</v>
       </c>
       <c r="AA5" t="n">
-        <v>9.737170070372775</v>
+        <v>9.737170070372851</v>
       </c>
       <c r="AB5" t="n">
-        <v>25.80252544859538</v>
+        <v>25.80252544859518</v>
       </c>
     </row>
     <row r="6">
@@ -7818,85 +7818,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.484631979492976</v>
+        <v>2.484631979493034</v>
       </c>
       <c r="C6" t="n">
         <v>2.438871419008759</v>
       </c>
       <c r="D6" t="n">
-        <v>2.093389607749194</v>
+        <v>2.093389607749116</v>
       </c>
       <c r="E6" t="n">
-        <v>5.180011130897102</v>
+        <v>5.180011130896865</v>
       </c>
       <c r="F6" t="n">
-        <v>2.899953751380699</v>
+        <v>2.899953751380978</v>
       </c>
       <c r="G6" t="n">
-        <v>5.373552258404066</v>
+        <v>5.373552258404235</v>
       </c>
       <c r="H6" t="n">
-        <v>2.150079058556106</v>
+        <v>2.150079058556068</v>
       </c>
       <c r="I6" t="n">
-        <v>3.245233995825422</v>
+        <v>3.245233995825358</v>
       </c>
       <c r="J6" t="n">
-        <v>2.840553484334121</v>
+        <v>2.84055348433397</v>
       </c>
       <c r="K6" t="n">
-        <v>5.418123685494905</v>
+        <v>5.418123685494782</v>
       </c>
       <c r="L6" t="n">
-        <v>4.882967044139875</v>
+        <v>4.882967044140035</v>
       </c>
       <c r="M6" t="n">
-        <v>3.556583886026523</v>
+        <v>3.556583886026526</v>
       </c>
       <c r="N6" t="n">
-        <v>2.526478562207239</v>
+        <v>2.526478562207159</v>
       </c>
       <c r="O6" t="n">
-        <v>4.495499590618625</v>
+        <v>4.49549959061855</v>
       </c>
       <c r="P6" t="n">
-        <v>4.711818376105716</v>
+        <v>4.711818376105636</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.902136776346737</v>
+        <v>2.902136776346519</v>
       </c>
       <c r="R6" t="n">
-        <v>4.999589083300625</v>
+        <v>4.999589083300837</v>
       </c>
       <c r="S6" t="n">
-        <v>3.14400305549869</v>
+        <v>3.144003055498613</v>
       </c>
       <c r="T6" t="n">
-        <v>2.455326975635403</v>
+        <v>2.455326975635422</v>
       </c>
       <c r="U6" t="n">
-        <v>4.496822831111379</v>
+        <v>4.496822831111221</v>
       </c>
       <c r="V6" t="n">
-        <v>2.367705466900307</v>
+        <v>2.367705466900311</v>
       </c>
       <c r="W6" t="n">
-        <v>2.253458067386498</v>
+        <v>2.253458067386324</v>
       </c>
       <c r="X6" t="n">
-        <v>5.021316198365753</v>
+        <v>5.021316198365633</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.462000474827251</v>
+        <v>2.462000474827014</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.327950244314848</v>
+        <v>4.327950244314871</v>
       </c>
       <c r="AA6" t="n">
-        <v>4.388346398838738</v>
+        <v>4.388346398838701</v>
       </c>
       <c r="AB6" t="n">
-        <v>3.026274713785592</v>
+        <v>3.026274713785452</v>
       </c>
     </row>
     <row r="7">
@@ -7906,85 +7906,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.786277254864392</v>
+        <v>2.786277254864412</v>
       </c>
       <c r="C7" t="n">
         <v>2.740516694380255</v>
       </c>
       <c r="D7" t="n">
-        <v>2.395034883120735</v>
+        <v>2.395034883120647</v>
       </c>
       <c r="E7" t="n">
-        <v>3.394753648153372</v>
+        <v>3.394753648153296</v>
       </c>
       <c r="F7" t="n">
-        <v>3.20159902675227</v>
+        <v>3.201599026752209</v>
       </c>
       <c r="G7" t="n">
-        <v>3.588294775660734</v>
+        <v>3.588294775660708</v>
       </c>
       <c r="H7" t="n">
-        <v>2.451724333927681</v>
+        <v>2.451724333927618</v>
       </c>
       <c r="I7" t="n">
-        <v>3.546879271196948</v>
+        <v>3.546879271196915</v>
       </c>
       <c r="J7" t="n">
-        <v>3.142198759705693</v>
+        <v>3.142198759705629</v>
       </c>
       <c r="K7" t="n">
-        <v>3.63286620275135</v>
+        <v>3.632866202751197</v>
       </c>
       <c r="L7" t="n">
-        <v>3.097709561396577</v>
+        <v>3.097709561396488</v>
       </c>
       <c r="M7" t="n">
-        <v>3.858229161398047</v>
+        <v>3.858229161398008</v>
       </c>
       <c r="N7" t="n">
-        <v>2.81574737776902</v>
+        <v>2.815747377768886</v>
       </c>
       <c r="O7" t="n">
-        <v>2.584772640374423</v>
+        <v>2.584772640374124</v>
       </c>
       <c r="P7" t="n">
-        <v>2.797118540797092</v>
+        <v>2.797118540796815</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.203782051718186</v>
+        <v>3.203782051718127</v>
       </c>
       <c r="R7" t="n">
-        <v>3.214331600557253</v>
+        <v>3.214331600557328</v>
       </c>
       <c r="S7" t="n">
-        <v>3.445648330870166</v>
+        <v>3.445648330870089</v>
       </c>
       <c r="T7" t="n">
-        <v>2.756972251006903</v>
+        <v>2.756972251006876</v>
       </c>
       <c r="U7" t="n">
-        <v>2.695601343264647</v>
+        <v>2.695601343264515</v>
       </c>
       <c r="V7" t="n">
-        <v>2.669350742271792</v>
+        <v>2.66935074227177</v>
       </c>
       <c r="W7" t="n">
-        <v>2.534420328593998</v>
+        <v>2.534420328593941</v>
       </c>
       <c r="X7" t="n">
-        <v>3.236058715622213</v>
+        <v>3.236058715622308</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.74886424017566</v>
+        <v>2.748864240175593</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.542692761571159</v>
+        <v>2.542692761571117</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.60308891609524</v>
+        <v>2.603088916095091</v>
       </c>
       <c r="AB7" t="n">
-        <v>3.335564390756548</v>
+        <v>3.335564390756554</v>
       </c>
     </row>
     <row r="8">
@@ -7994,85 +7994,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.604381100905834</v>
+        <v>4.604381100905984</v>
       </c>
       <c r="C8" t="n">
-        <v>6.346762708136849</v>
+        <v>6.346762708136711</v>
       </c>
       <c r="D8" t="n">
-        <v>6.001280896877004</v>
+        <v>6.001280896877207</v>
       </c>
       <c r="E8" t="n">
-        <v>6.048866705233904</v>
+        <v>6.048866705233986</v>
       </c>
       <c r="F8" t="n">
-        <v>5.298274523713542</v>
+        <v>5.298274523713465</v>
       </c>
       <c r="G8" t="n">
-        <v>7.565323716429947</v>
+        <v>7.565323716430159</v>
       </c>
       <c r="H8" t="n">
-        <v>6.057970347683959</v>
+        <v>6.05797034768382</v>
       </c>
       <c r="I8" t="n">
-        <v>7.153125284953477</v>
+        <v>7.153125284953511</v>
       </c>
       <c r="J8" t="n">
-        <v>6.748444773461862</v>
+        <v>6.748444773461975</v>
       </c>
       <c r="K8" t="n">
-        <v>7.239112216507758</v>
+        <v>7.239112216507797</v>
       </c>
       <c r="L8" t="n">
-        <v>6.703955575153008</v>
+        <v>6.703955575153136</v>
       </c>
       <c r="M8" t="n">
-        <v>7.464475175146144</v>
+        <v>7.464475175146336</v>
       </c>
       <c r="N8" t="n">
-        <v>5.035884061144731</v>
+        <v>5.035884061144695</v>
       </c>
       <c r="O8" t="n">
-        <v>5.185820845724457</v>
+        <v>5.185820845724407</v>
       </c>
       <c r="P8" t="n">
-        <v>5.304795305593922</v>
+        <v>5.304795305594006</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.670475150290764</v>
+        <v>4.670475150290766</v>
       </c>
       <c r="R8" t="n">
-        <v>6.82057761431375</v>
+        <v>6.820577614313859</v>
       </c>
       <c r="S8" t="n">
-        <v>7.051894344626636</v>
+        <v>7.051894344626827</v>
       </c>
       <c r="T8" t="n">
-        <v>6.363218264763418</v>
+        <v>6.363218264763463</v>
       </c>
       <c r="U8" t="n">
-        <v>5.432668721585808</v>
+        <v>5.432668721585805</v>
       </c>
       <c r="V8" t="n">
-        <v>5.773222033094308</v>
+        <v>5.773222033094323</v>
       </c>
       <c r="W8" t="n">
-        <v>6.141017760451474</v>
+        <v>6.141017760451658</v>
       </c>
       <c r="X8" t="n">
-        <v>4.866638595096475</v>
+        <v>4.866638595096656</v>
       </c>
       <c r="Y8" t="n">
-        <v>8.111850460820131</v>
+        <v>8.11185046082015</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.327580949092179</v>
+        <v>4.327580949092074</v>
       </c>
       <c r="AA8" t="n">
-        <v>6.209334929851618</v>
+        <v>6.20933492985167</v>
       </c>
       <c r="AB8" t="n">
-        <v>8.809674417793914</v>
+        <v>8.809674417793815</v>
       </c>
     </row>
     <row r="9">
@@ -8082,52 +8082,52 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>86.65696519725397</v>
+        <v>86.65696519725408</v>
       </c>
       <c r="C9" t="n">
-        <v>110.0815582769805</v>
+        <v>110.0815582769806</v>
       </c>
       <c r="D9" t="n">
         <v>109.7360764657208</v>
       </c>
       <c r="E9" t="n">
-        <v>105.3189335665829</v>
+        <v>105.318933566583</v>
       </c>
       <c r="F9" t="n">
-        <v>56.43706942443487</v>
+        <v>56.43706942443478</v>
       </c>
       <c r="G9" t="n">
         <v>110.9293366470819</v>
       </c>
       <c r="H9" t="n">
-        <v>109.792765916528</v>
+        <v>109.7927659165282</v>
       </c>
       <c r="I9" t="n">
-        <v>110.8879208537972</v>
+        <v>110.8879208537974</v>
       </c>
       <c r="J9" t="n">
-        <v>110.483240342306</v>
+        <v>110.4832403423058</v>
       </c>
       <c r="K9" t="n">
-        <v>110.9739077853517</v>
+        <v>110.9739077853516</v>
       </c>
       <c r="L9" t="n">
         <v>110.4387511439971</v>
       </c>
       <c r="M9" t="n">
-        <v>111.1992707439983</v>
+        <v>111.1992707439982</v>
       </c>
       <c r="N9" t="n">
         <v>110.1567889603693</v>
       </c>
       <c r="O9" t="n">
-        <v>117.7038557162718</v>
+        <v>117.7038557162717</v>
       </c>
       <c r="P9" t="n">
-        <v>119.6077928597866</v>
+        <v>119.6077928597865</v>
       </c>
       <c r="Q9" t="n">
-        <v>110.5448239231391</v>
+        <v>110.5448239231389</v>
       </c>
       <c r="R9" t="n">
         <v>110.5553731831577</v>
@@ -8148,19 +8148,19 @@
         <v>109.8754619111942</v>
       </c>
       <c r="X9" t="n">
-        <v>110.5771002982223</v>
+        <v>110.5771002982225</v>
       </c>
       <c r="Y9" t="n">
-        <v>110.089905822776</v>
+        <v>110.0899058227761</v>
       </c>
       <c r="Z9" t="n">
-        <v>95.73319827908726</v>
+        <v>95.73319827908729</v>
       </c>
       <c r="AA9" t="n">
         <v>109.9441304986956</v>
       </c>
       <c r="AB9" t="n">
-        <v>110.676605973357</v>
+        <v>110.6766059733569</v>
       </c>
     </row>
   </sheetData>
@@ -8326,85 +8326,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.685194862619022</v>
+        <v>2.685194862619014</v>
       </c>
       <c r="C2" t="n">
-        <v>2.973924393219739</v>
+        <v>2.973924393219718</v>
       </c>
       <c r="D2" t="n">
-        <v>2.636765089679431</v>
+        <v>2.636765089679419</v>
       </c>
       <c r="E2" t="n">
-        <v>2.773495957116592</v>
+        <v>2.773495957116582</v>
       </c>
       <c r="F2" t="n">
-        <v>2.778166847320292</v>
+        <v>2.778166847320284</v>
       </c>
       <c r="G2" t="n">
-        <v>2.68685234503575</v>
+        <v>2.686852345035731</v>
       </c>
       <c r="H2" t="n">
-        <v>2.595027360888671</v>
+        <v>2.595027360888654</v>
       </c>
       <c r="I2" t="n">
-        <v>2.71892351697796</v>
+        <v>2.718923516977935</v>
       </c>
       <c r="J2" t="n">
-        <v>2.670821355591098</v>
+        <v>2.6708213555911</v>
       </c>
       <c r="K2" t="n">
-        <v>2.70580057655602</v>
+        <v>2.705800576556015</v>
       </c>
       <c r="L2" t="n">
-        <v>2.789994437735348</v>
+        <v>2.789994437735338</v>
       </c>
       <c r="M2" t="n">
-        <v>2.637816505163736</v>
+        <v>2.637816505163724</v>
       </c>
       <c r="N2" t="n">
-        <v>2.634621703553871</v>
+        <v>2.63462170355386</v>
       </c>
       <c r="O2" t="n">
-        <v>5.15874226782507</v>
+        <v>5.158742267825068</v>
       </c>
       <c r="P2" t="n">
-        <v>2.628421504678209</v>
+        <v>2.628421504678212</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.720820988170416</v>
+        <v>2.720820988170401</v>
       </c>
       <c r="R2" t="n">
-        <v>2.787486030753161</v>
+        <v>2.787486030753165</v>
       </c>
       <c r="S2" t="n">
-        <v>2.736733996487086</v>
+        <v>2.736733996487072</v>
       </c>
       <c r="T2" t="n">
-        <v>2.665857743226745</v>
+        <v>2.665857743226737</v>
       </c>
       <c r="U2" t="n">
-        <v>3.400841047859718</v>
+        <v>3.400841047859717</v>
       </c>
       <c r="V2" t="n">
-        <v>2.623853867053732</v>
+        <v>2.623853867053724</v>
       </c>
       <c r="W2" t="n">
-        <v>3.658524646153395</v>
+        <v>3.658524646153377</v>
       </c>
       <c r="X2" t="n">
-        <v>2.676574892565697</v>
+        <v>2.676574892565689</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.672291550386388</v>
+        <v>2.672291550386371</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.827436974069589</v>
+        <v>2.827436974069592</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.621688924945463</v>
+        <v>2.621688924945464</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.67436340320566</v>
+        <v>2.674363403205645</v>
       </c>
     </row>
     <row r="3">
@@ -8414,85 +8414,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.254195695907292</v>
+        <v>3.286903749509785</v>
       </c>
       <c r="C3" t="n">
-        <v>3.869696704321305</v>
+        <v>3.909219046202263</v>
       </c>
       <c r="D3" t="n">
-        <v>2.912326845850276</v>
+        <v>2.933175326518735</v>
       </c>
       <c r="E3" t="n">
-        <v>3.887380205209123</v>
+        <v>3.942373963019791</v>
       </c>
       <c r="F3" t="n">
-        <v>3.922581804792487</v>
+        <v>3.979593057653968</v>
       </c>
       <c r="G3" t="n">
-        <v>3.263707617281419</v>
+        <v>3.296845914878994</v>
       </c>
       <c r="H3" t="n">
-        <v>2.614746666657052</v>
+        <v>2.625034215755211</v>
       </c>
       <c r="I3" t="n">
-        <v>3.501403887374877</v>
+        <v>3.543185029270284</v>
       </c>
       <c r="J3" t="n">
-        <v>3.152279006735557</v>
+        <v>3.181558728629976</v>
       </c>
       <c r="K3" t="n">
-        <v>3.400526334341739</v>
+        <v>3.438857875833373</v>
       </c>
       <c r="L3" t="n">
-        <v>3.997440865483627</v>
+        <v>4.056694155200756</v>
       </c>
       <c r="M3" t="n">
-        <v>2.929582758333244</v>
+        <v>2.951211219128791</v>
       </c>
       <c r="N3" t="n">
-        <v>2.896990153699226</v>
+        <v>2.917228496163785</v>
       </c>
       <c r="O3" t="n">
-        <v>6.884815553395065</v>
+        <v>6.896801839469281</v>
       </c>
       <c r="P3" t="n">
-        <v>2.850426762809411</v>
+        <v>2.868912623842921</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.507892378943714</v>
+        <v>3.549990199391959</v>
       </c>
       <c r="R3" t="n">
-        <v>3.993856368947656</v>
+        <v>4.053194114574779</v>
       </c>
       <c r="S3" t="n">
-        <v>3.617779938952931</v>
+        <v>3.663500897205509</v>
       </c>
       <c r="T3" t="n">
-        <v>3.120845345282417</v>
+        <v>3.149096546491846</v>
       </c>
       <c r="U3" t="n">
-        <v>4.024058446305276</v>
+        <v>4.037962873939533</v>
       </c>
       <c r="V3" t="n">
-        <v>2.817577085881953</v>
+        <v>2.834957695297654</v>
       </c>
       <c r="W3" t="n">
-        <v>4.721466791025285</v>
+        <v>4.747844577949635</v>
       </c>
       <c r="X3" t="n">
-        <v>3.196021054869767</v>
+        <v>3.226953509109556</v>
       </c>
       <c r="Y3" t="n">
-        <v>3.165083133559884</v>
+        <v>3.194803854928233</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.219534034171907</v>
+        <v>3.239958936834208</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.80420194228279</v>
+        <v>2.821138996043552</v>
       </c>
       <c r="AB3" t="n">
-        <v>3.188004382260226</v>
+        <v>3.218607633784013</v>
       </c>
     </row>
     <row r="4">
@@ -8502,85 +8502,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.059547088843514</v>
+        <v>3.059547088843537</v>
       </c>
       <c r="C4" t="n">
-        <v>3.344941225863073</v>
+        <v>3.34494122586307</v>
       </c>
       <c r="D4" t="n">
-        <v>2.512510524694609</v>
+        <v>2.512510524694545</v>
       </c>
       <c r="E4" t="n">
-        <v>4.056948571703929</v>
+        <v>4.056948571703955</v>
       </c>
       <c r="F4" t="n">
-        <v>4.109708425270279</v>
+        <v>4.109708425270227</v>
       </c>
       <c r="G4" t="n">
-        <v>3.078269115219995</v>
+        <v>3.078269115220001</v>
       </c>
       <c r="H4" t="n">
-        <v>2.041063677699048</v>
+        <v>2.041063677698994</v>
       </c>
       <c r="I4" t="n">
-        <v>3.440527755775201</v>
+        <v>3.44052775577515</v>
       </c>
       <c r="J4" t="n">
-        <v>2.895861899351965</v>
+        <v>2.895861899351925</v>
       </c>
       <c r="K4" t="n">
-        <v>3.292298106858708</v>
+        <v>3.292298106858709</v>
       </c>
       <c r="L4" t="n">
-        <v>4.243306499968892</v>
+        <v>4.243306499968897</v>
       </c>
       <c r="M4" t="n">
-        <v>2.544342725765739</v>
+        <v>2.544342725765694</v>
       </c>
       <c r="N4" t="n">
-        <v>2.488299992400071</v>
+        <v>2.488299992400017</v>
       </c>
       <c r="O4" t="n">
-        <v>2.123760229046396</v>
+        <v>2.123760229046378</v>
       </c>
       <c r="P4" t="n">
-        <v>2.418265893867185</v>
+        <v>2.418265893867132</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.46196056577393</v>
+        <v>3.461960565773943</v>
       </c>
       <c r="R4" t="n">
-        <v>4.214972889180835</v>
+        <v>4.214972889180869</v>
       </c>
       <c r="S4" t="n">
-        <v>3.641705315056212</v>
+        <v>3.6417053150562</v>
       </c>
       <c r="T4" t="n">
-        <v>2.841125429793385</v>
+        <v>2.841125429793406</v>
       </c>
       <c r="U4" t="n">
         <v>2.070185810497419</v>
       </c>
       <c r="V4" t="n">
-        <v>2.358435110135439</v>
+        <v>2.35843511013543</v>
       </c>
       <c r="W4" t="n">
-        <v>2.765785571086552</v>
+        <v>2.765785571086488</v>
       </c>
       <c r="X4" t="n">
-        <v>2.962180561709129</v>
+        <v>2.962180561709127</v>
       </c>
       <c r="Y4" t="n">
         <v>2.776131487990855</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.503842993717833</v>
+        <v>2.503842993717789</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.34221830864592</v>
+        <v>2.342218308645927</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.946151112141048</v>
+        <v>2.946151112141012</v>
       </c>
     </row>
     <row r="5">
@@ -8590,85 +8590,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>22.6745840519627</v>
+        <v>22.67458405196262</v>
       </c>
       <c r="C5" t="n">
-        <v>28.79747250653999</v>
+        <v>28.79747250653996</v>
       </c>
       <c r="D5" t="n">
-        <v>14.95659854188484</v>
+        <v>14.95659854188479</v>
       </c>
       <c r="E5" t="n">
-        <v>41.85709505105191</v>
+        <v>41.85709505105196</v>
       </c>
       <c r="F5" t="n">
-        <v>43.75684489003857</v>
+        <v>43.7568448900385</v>
       </c>
       <c r="G5" t="n">
-        <v>21.8046695956031</v>
+        <v>21.80466959560292</v>
       </c>
       <c r="H5" t="n">
-        <v>6.77586066319313</v>
+        <v>6.775860663193114</v>
       </c>
       <c r="I5" t="n">
-        <v>32.77359667797558</v>
+        <v>32.77359667797552</v>
       </c>
       <c r="J5" t="n">
-        <v>20.14777453098147</v>
+        <v>20.14777453098136</v>
       </c>
       <c r="K5" t="n">
-        <v>26.41111987369269</v>
+        <v>26.41111987369263</v>
       </c>
       <c r="L5" t="n">
         <v>41.16808887255243</v>
       </c>
       <c r="M5" t="n">
-        <v>14.95444018436257</v>
+        <v>14.95444018436255</v>
       </c>
       <c r="N5" t="n">
-        <v>14.50806095784715</v>
+        <v>14.50806095784711</v>
       </c>
       <c r="O5" t="n">
-        <v>7.213019328956163</v>
+        <v>7.213019328956141</v>
       </c>
       <c r="P5" t="n">
-        <v>12.07112091087398</v>
+        <v>12.07112091087396</v>
       </c>
       <c r="Q5" t="n">
         <v>29.49718959351134</v>
       </c>
       <c r="R5" t="n">
-        <v>48.08697007599766</v>
+        <v>48.08697007599761</v>
       </c>
       <c r="S5" t="n">
-        <v>30.76693874323563</v>
+        <v>30.76693874323562</v>
       </c>
       <c r="T5" t="n">
-        <v>21.22617416031663</v>
+        <v>21.22617416031668</v>
       </c>
       <c r="U5" t="n">
-        <v>8.791831754516378</v>
+        <v>8.791831754516377</v>
       </c>
       <c r="V5" t="n">
-        <v>11.02069640650693</v>
+        <v>11.02069640650691</v>
       </c>
       <c r="W5" t="n">
-        <v>19.18713962009827</v>
+        <v>19.1871396200983</v>
       </c>
       <c r="X5" t="n">
-        <v>22.68674298699446</v>
+        <v>22.68674298699445</v>
       </c>
       <c r="Y5" t="n">
-        <v>21.64057702138255</v>
+        <v>21.64057702138251</v>
       </c>
       <c r="Z5" t="n">
-        <v>13.08190210273064</v>
+        <v>13.08190210273063</v>
       </c>
       <c r="AA5" t="n">
-        <v>11.67233931446258</v>
+        <v>11.67233931446253</v>
       </c>
       <c r="AB5" t="n">
-        <v>23.90812806423045</v>
+        <v>23.90812806423047</v>
       </c>
     </row>
     <row r="6">
@@ -8678,85 +8678,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.836235962907016</v>
+        <v>5.836235962907038</v>
       </c>
       <c r="C6" t="n">
-        <v>6.121630099926599</v>
+        <v>6.121630099926575</v>
       </c>
       <c r="D6" t="n">
-        <v>5.289199398758078</v>
+        <v>5.289199398758096</v>
       </c>
       <c r="E6" t="n">
-        <v>4.635290083945503</v>
+        <v>4.635290083945492</v>
       </c>
       <c r="F6" t="n">
-        <v>4.688049937511856</v>
+        <v>4.688049937511847</v>
       </c>
       <c r="G6" t="n">
-        <v>3.656610627461566</v>
+        <v>3.656610627461554</v>
       </c>
       <c r="H6" t="n">
-        <v>2.619405189940607</v>
+        <v>2.619405189940601</v>
       </c>
       <c r="I6" t="n">
-        <v>6.217216629838664</v>
+        <v>6.217216629838688</v>
       </c>
       <c r="J6" t="n">
-        <v>5.672550773415411</v>
+        <v>5.672550773415439</v>
       </c>
       <c r="K6" t="n">
-        <v>3.870639619100289</v>
+        <v>3.870639619100278</v>
       </c>
       <c r="L6" t="n">
-        <v>7.019995374032357</v>
+        <v>7.019995374032392</v>
       </c>
       <c r="M6" t="n">
-        <v>3.122684238007297</v>
+        <v>3.122684238007302</v>
       </c>
       <c r="N6" t="n">
-        <v>3.074138561373638</v>
+        <v>3.074138561373633</v>
       </c>
       <c r="O6" t="n">
-        <v>5.000802039504914</v>
+        <v>5.000802039504886</v>
       </c>
       <c r="P6" t="n">
-        <v>2.941963199864942</v>
+        <v>2.94196319986495</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.040302078015501</v>
+        <v>4.040302078015499</v>
       </c>
       <c r="R6" t="n">
-        <v>6.991661763244302</v>
+        <v>6.991661763244326</v>
       </c>
       <c r="S6" t="n">
-        <v>4.220046827297772</v>
+        <v>4.220046827297766</v>
       </c>
       <c r="T6" t="n">
-        <v>3.419466942034975</v>
+        <v>3.41946694203497</v>
       </c>
       <c r="U6" t="n">
-        <v>4.984541437929066</v>
+        <v>4.984541437929103</v>
       </c>
       <c r="V6" t="n">
-        <v>2.936776622376999</v>
+        <v>2.936776622377002</v>
       </c>
       <c r="W6" t="n">
-        <v>3.371428733548853</v>
+        <v>3.371428733548816</v>
       </c>
       <c r="X6" t="n">
-        <v>5.738869435772628</v>
+        <v>5.738869435772637</v>
       </c>
       <c r="Y6" t="n">
-        <v>3.508511567001395</v>
+        <v>3.508511567001394</v>
       </c>
       <c r="Z6" t="n">
-        <v>5.280531867781315</v>
+        <v>5.280531867781328</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.92055982088749</v>
+        <v>2.920559820887489</v>
       </c>
       <c r="AB6" t="n">
-        <v>3.504107528407195</v>
+        <v>3.504107528407192</v>
       </c>
     </row>
     <row r="7">
@@ -8766,85 +8766,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.833707851286795</v>
+        <v>3.833707851286782</v>
       </c>
       <c r="C7" t="n">
-        <v>4.119101988306332</v>
+        <v>4.119101988306323</v>
       </c>
       <c r="D7" t="n">
-        <v>3.286671287137848</v>
+        <v>3.286671287137843</v>
       </c>
       <c r="E7" t="n">
-        <v>4.83110933414719</v>
+        <v>4.831109334147181</v>
       </c>
       <c r="F7" t="n">
-        <v>4.883869187713544</v>
+        <v>4.883869187713532</v>
       </c>
       <c r="G7" t="n">
-        <v>3.85242987766324</v>
+        <v>3.852429877663238</v>
       </c>
       <c r="H7" t="n">
-        <v>2.8152244401423</v>
+        <v>2.815224440142291</v>
       </c>
       <c r="I7" t="n">
-        <v>4.214688518218426</v>
+        <v>4.214688518218431</v>
       </c>
       <c r="J7" t="n">
-        <v>3.670022661795186</v>
+        <v>3.670022661795179</v>
       </c>
       <c r="K7" t="n">
-        <v>4.066458869301969</v>
+        <v>4.066458869301965</v>
       </c>
       <c r="L7" t="n">
-        <v>5.017467262412143</v>
+        <v>5.017467262412135</v>
       </c>
       <c r="M7" t="n">
-        <v>3.318503488208997</v>
+        <v>3.318503488208985</v>
       </c>
       <c r="N7" t="n">
-        <v>3.262460754843308</v>
+        <v>3.262460754843301</v>
       </c>
       <c r="O7" t="n">
-        <v>2.897923563691941</v>
+        <v>2.89792356369193</v>
       </c>
       <c r="P7" t="n">
-        <v>3.192429228512748</v>
+        <v>3.192429228512737</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.236121328217194</v>
+        <v>4.236121328217187</v>
       </c>
       <c r="R7" t="n">
-        <v>4.98913365162408</v>
+        <v>4.989133651624074</v>
       </c>
       <c r="S7" t="n">
-        <v>4.415866077499468</v>
+        <v>4.415866077499458</v>
       </c>
       <c r="T7" t="n">
-        <v>3.615286192236661</v>
+        <v>3.615286192236657</v>
       </c>
       <c r="U7" t="n">
-        <v>2.963081815067132</v>
+        <v>2.963081815067127</v>
       </c>
       <c r="V7" t="n">
-        <v>3.132595872578671</v>
+        <v>3.132595872578689</v>
       </c>
       <c r="W7" t="n">
         <v>3.539946333529789</v>
       </c>
       <c r="X7" t="n">
-        <v>3.73634132415237</v>
+        <v>3.736341324152379</v>
       </c>
       <c r="Y7" t="n">
-        <v>3.687959003802276</v>
+        <v>3.687959003802278</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.278003756161076</v>
+        <v>3.278003756161073</v>
       </c>
       <c r="AA7" t="n">
         <v>3.116379071089178</v>
       </c>
       <c r="AB7" t="n">
-        <v>3.720311874584288</v>
+        <v>3.720311874584292</v>
       </c>
     </row>
     <row r="8">
@@ -8854,85 +8854,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.687400303421683</v>
+        <v>5.687400303421673</v>
       </c>
       <c r="C8" t="n">
-        <v>7.92057024562828</v>
+        <v>7.920570245628255</v>
       </c>
       <c r="D8" t="n">
-        <v>7.088139544459861</v>
+        <v>7.088139544459746</v>
       </c>
       <c r="E8" t="n">
-        <v>7.595444432292273</v>
+        <v>7.595444432292256</v>
       </c>
       <c r="F8" t="n">
-        <v>7.041002345504705</v>
+        <v>7.04100234550467</v>
       </c>
       <c r="G8" t="n">
-        <v>8.057782136389026</v>
+        <v>8.057782136388955</v>
       </c>
       <c r="H8" t="n">
-        <v>6.61669269746426</v>
+        <v>6.616692697464169</v>
       </c>
       <c r="I8" t="n">
-        <v>8.016156775540427</v>
+        <v>8.016156775540329</v>
       </c>
       <c r="J8" t="n">
-        <v>7.471490919117094</v>
+        <v>7.471490919117172</v>
       </c>
       <c r="K8" t="n">
-        <v>7.867927126623946</v>
+        <v>7.867927126623905</v>
       </c>
       <c r="L8" t="n">
-        <v>8.818935519734142</v>
+        <v>8.818935519734085</v>
       </c>
       <c r="M8" t="n">
-        <v>7.119971745514952</v>
+        <v>7.119971745514864</v>
       </c>
       <c r="N8" t="n">
-        <v>5.554076905911566</v>
+        <v>5.554076905911522</v>
       </c>
       <c r="O8" t="n">
-        <v>5.604457608106015</v>
+        <v>5.604457608105986</v>
       </c>
       <c r="P8" t="n">
-        <v>5.797256241281114</v>
+        <v>5.797256241281121</v>
       </c>
       <c r="Q8" t="n">
-        <v>5.707031380485108</v>
+        <v>5.707031380485119</v>
       </c>
       <c r="R8" t="n">
-        <v>8.790601908946075</v>
+        <v>8.790601908946003</v>
       </c>
       <c r="S8" t="n">
-        <v>8.217334334821476</v>
+        <v>8.217334334821365</v>
       </c>
       <c r="T8" t="n">
-        <v>7.416754449558685</v>
+        <v>7.4167544495586</v>
       </c>
       <c r="U8" t="n">
-        <v>5.818124756428226</v>
+        <v>5.818124756428161</v>
       </c>
       <c r="V8" t="n">
-        <v>6.385523244217323</v>
+        <v>6.385523244217284</v>
       </c>
       <c r="W8" t="n">
-        <v>7.341797378720821</v>
+        <v>7.341797378720772</v>
       </c>
       <c r="X8" t="n">
-        <v>5.38576889562603</v>
+        <v>5.385768895625944</v>
       </c>
       <c r="Y8" t="n">
-        <v>9.400954404670639</v>
+        <v>9.400954404670498</v>
       </c>
       <c r="Z8" t="n">
-        <v>5.095515273286414</v>
+        <v>5.095515273286375</v>
       </c>
       <c r="AA8" t="n">
-        <v>6.917847328411169</v>
+        <v>6.917847328411117</v>
       </c>
       <c r="AB8" t="n">
-        <v>9.556394825166041</v>
+        <v>9.556394825165901</v>
       </c>
     </row>
     <row r="9">
@@ -8942,7 +8942,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>81.93133926328163</v>
+        <v>81.93133926328164</v>
       </c>
       <c r="C9" t="n">
         <v>104.1501573447852</v>
@@ -8951,10 +8951,10 @@
         <v>103.3177266436169</v>
       </c>
       <c r="E9" t="n">
-        <v>99.80002051783168</v>
+        <v>99.80002051783171</v>
       </c>
       <c r="F9" t="n">
-        <v>54.35239511976607</v>
+        <v>54.35239511976605</v>
       </c>
       <c r="G9" t="n">
         <v>103.8834860255925</v>
@@ -8978,13 +8978,13 @@
         <v>103.3495588446879</v>
       </c>
       <c r="N9" t="n">
-        <v>103.2935161113224</v>
+        <v>103.2935161113223</v>
       </c>
       <c r="O9" t="n">
         <v>110.1976853775308</v>
       </c>
       <c r="P9" t="n">
-        <v>112.0730103741142</v>
+        <v>112.0730103741141</v>
       </c>
       <c r="Q9" t="n">
         <v>104.2671774761465</v>

--- a/Results/Phase 2/Ammonia/ammonia land use results.xlsx
+++ b/Results/Phase 2/Ammonia/ammonia land use results.xlsx
@@ -586,85 +586,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.95143157254096</v>
+        <v>1.951431572540952</v>
       </c>
       <c r="C2" t="n">
-        <v>1.972617201936154</v>
+        <v>1.972617201936155</v>
       </c>
       <c r="D2" t="n">
-        <v>1.940709170041146</v>
+        <v>1.940709170041139</v>
       </c>
       <c r="E2" t="n">
-        <v>1.891854521477517</v>
+        <v>1.891854521477532</v>
       </c>
       <c r="F2" t="n">
-        <v>1.929905264664332</v>
+        <v>1.929905264664338</v>
       </c>
       <c r="G2" t="n">
-        <v>2.025426521060643</v>
+        <v>2.025426521060654</v>
       </c>
       <c r="H2" t="n">
-        <v>1.950196310658899</v>
+        <v>1.950196310658922</v>
       </c>
       <c r="I2" t="n">
-        <v>1.958286368086914</v>
+        <v>1.958286368086924</v>
       </c>
       <c r="J2" t="n">
-        <v>1.987309063957841</v>
+        <v>1.987309063957834</v>
       </c>
       <c r="K2" t="n">
-        <v>2.003688483017619</v>
+        <v>2.003688483017604</v>
       </c>
       <c r="L2" t="n">
-        <v>1.942168209086701</v>
+        <v>1.942168209086683</v>
       </c>
       <c r="M2" t="n">
-        <v>2.051916283667531</v>
+        <v>2.05191628366752</v>
       </c>
       <c r="N2" t="n">
-        <v>1.966201862542902</v>
+        <v>1.966201862542891</v>
       </c>
       <c r="O2" t="n">
-        <v>3.719587879210508</v>
+        <v>3.719587879210522</v>
       </c>
       <c r="P2" t="n">
-        <v>1.978029055634923</v>
+        <v>1.978029055634919</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.94616685990564</v>
+        <v>1.946166859905641</v>
       </c>
       <c r="R2" t="n">
-        <v>1.966259195436223</v>
+        <v>1.966259195436225</v>
       </c>
       <c r="S2" t="n">
-        <v>1.989761327606169</v>
+        <v>1.989761327606153</v>
       </c>
       <c r="T2" t="n">
-        <v>1.95979370747217</v>
+        <v>1.959793707472159</v>
       </c>
       <c r="U2" t="n">
-        <v>2.02708453380685</v>
+        <v>2.027084533806858</v>
       </c>
       <c r="V2" t="n">
-        <v>1.977789852687662</v>
+        <v>1.977789852687671</v>
       </c>
       <c r="W2" t="n">
-        <v>2.10252761815196</v>
+        <v>2.102527618151943</v>
       </c>
       <c r="X2" t="n">
-        <v>1.949002327546863</v>
+        <v>1.949002327546856</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.961626933920324</v>
+        <v>1.961626933920327</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.752733561134759</v>
+        <v>1.752733561134782</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.988026565672769</v>
+        <v>1.988026565672772</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.046719325993287</v>
+        <v>2.046719325993277</v>
       </c>
     </row>
     <row r="3">
@@ -674,85 +674,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.446636600869315</v>
+        <v>2.072621053209123</v>
       </c>
       <c r="C3" t="n">
-        <v>2.413593736000768</v>
+        <v>2.081609215572528</v>
       </c>
       <c r="D3" t="n">
-        <v>2.203271316411629</v>
+        <v>1.993041315758438</v>
       </c>
       <c r="E3" t="n">
-        <v>1.167292095560526</v>
+        <v>1.707297153000729</v>
       </c>
       <c r="F3" t="n">
-        <v>1.951095173399806</v>
+        <v>1.905192586650006</v>
       </c>
       <c r="G3" t="n">
-        <v>4.152193774450883</v>
+        <v>2.655100355671532</v>
       </c>
       <c r="H3" t="n">
-        <v>2.427669092123849</v>
+        <v>2.073738261990507</v>
       </c>
       <c r="I3" t="n">
-        <v>2.614756822652555</v>
+        <v>2.13766985255559</v>
       </c>
       <c r="J3" t="n">
-        <v>3.278398476816241</v>
+        <v>2.359893765170397</v>
       </c>
       <c r="K3" t="n">
-        <v>3.671573343682099</v>
+        <v>2.505149685343644</v>
       </c>
       <c r="L3" t="n">
-        <v>2.234977567419837</v>
+        <v>2.002484940818968</v>
       </c>
       <c r="M3" t="n">
-        <v>4.797747082061421</v>
+        <v>2.902636444667987</v>
       </c>
       <c r="N3" t="n">
-        <v>2.795283119129655</v>
+        <v>2.197639941893498</v>
       </c>
       <c r="O3" t="n">
-        <v>4.897413059852766</v>
+        <v>4.048200019511947</v>
       </c>
       <c r="P3" t="n">
-        <v>3.057570743321037</v>
+        <v>2.280974540905717</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.329808398497268</v>
+        <v>2.036514324851906</v>
       </c>
       <c r="R3" t="n">
-        <v>2.802770667048641</v>
+        <v>2.20470585499455</v>
       </c>
       <c r="S3" t="n">
-        <v>3.333066317790918</v>
+        <v>2.37572177598781</v>
       </c>
       <c r="T3" t="n">
-        <v>2.649242392931968</v>
+        <v>2.149240678494027</v>
       </c>
       <c r="U3" t="n">
-        <v>3.229473133350819</v>
+        <v>2.37169204398644</v>
       </c>
       <c r="V3" t="n">
-        <v>3.05428908698132</v>
+        <v>2.278598463461917</v>
       </c>
       <c r="W3" t="n">
-        <v>2.77213456247199</v>
+        <v>2.282141099503435</v>
       </c>
       <c r="X3" t="n">
-        <v>2.396477425766208</v>
+        <v>2.060053962103164</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.687692669391235</v>
+        <v>2.159160156970789</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.366840758334668</v>
+        <v>1.911901351311014</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.300048506854693</v>
+        <v>2.371422625535363</v>
       </c>
       <c r="AB3" t="n">
-        <v>4.660531014381774</v>
+        <v>2.868626140798887</v>
       </c>
     </row>
     <row r="4">
@@ -762,85 +762,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.179938679840516</v>
+        <v>6.179938679839223</v>
       </c>
       <c r="C4" t="n">
-        <v>6.083613081913717</v>
+        <v>6.083613081913715</v>
       </c>
       <c r="D4" t="n">
-        <v>4.212007948906211</v>
+        <v>4.212007948906195</v>
       </c>
       <c r="E4" t="n">
-        <v>-6.857789148252386</v>
+        <v>-6.857789148251216</v>
       </c>
       <c r="F4" t="n">
-        <v>1.642543839249769</v>
+        <v>1.642543839249763</v>
       </c>
       <c r="G4" t="n">
-        <v>22.31665771216296</v>
+        <v>22.31665771216293</v>
       </c>
       <c r="H4" t="n">
-        <v>6.740880473427954</v>
+        <v>6.740880473427677</v>
       </c>
       <c r="I4" t="n">
-        <v>8.523415897706929</v>
+        <v>8.523415897707046</v>
       </c>
       <c r="J4" t="n">
-        <v>14.37379973676395</v>
+        <v>14.37379973676444</v>
       </c>
       <c r="K4" t="n">
-        <v>19.19407742867352</v>
+        <v>19.19407742867339</v>
       </c>
       <c r="L4" t="n">
-        <v>4.374049493356922</v>
+        <v>4.374049493352713</v>
       </c>
       <c r="M4" t="n">
         <v>31.21604892744283</v>
       </c>
       <c r="N4" t="n">
-        <v>10.07018886758695</v>
+        <v>10.07018886758693</v>
       </c>
       <c r="O4" t="n">
-        <v>12.48805427623219</v>
+        <v>12.48805427623217</v>
       </c>
       <c r="P4" t="n">
-        <v>11.90443919024093</v>
+        <v>11.90443919024097</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.440818022125275</v>
+        <v>5.440818022124873</v>
       </c>
       <c r="R4" t="n">
         <v>10.58866412859639</v>
       </c>
       <c r="S4" t="n">
-        <v>14.6409795616713</v>
+        <v>14.64097956167186</v>
       </c>
       <c r="T4" t="n">
-        <v>8.829557383705982</v>
+        <v>8.829557383705604</v>
       </c>
       <c r="U4" t="n">
-        <v>13.47589459118202</v>
+        <v>13.47589459118205</v>
       </c>
       <c r="V4" t="n">
-        <v>11.80525423683809</v>
+        <v>11.80525423683807</v>
       </c>
       <c r="W4" t="n">
-        <v>8.283046570782728</v>
+        <v>8.283046570782499</v>
       </c>
       <c r="X4" t="n">
-        <v>6.152122049592705</v>
+        <v>6.15212204959094</v>
       </c>
       <c r="Y4" t="n">
-        <v>8.883542823636079</v>
+        <v>8.88354282363605</v>
       </c>
       <c r="Z4" t="n">
-        <v>7.435628648135554</v>
+        <v>7.435628648135366</v>
       </c>
       <c r="AA4" t="n">
-        <v>14.98148031220327</v>
+        <v>14.98148031220317</v>
       </c>
       <c r="AB4" t="n">
-        <v>30.77354297217599</v>
+        <v>30.77354297217597</v>
       </c>
     </row>
     <row r="5">
@@ -850,85 +850,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.744823649788867</v>
+        <v>3.744823649788762</v>
       </c>
       <c r="C5" t="n">
-        <v>5.294801624748212</v>
+        <v>5.294801624748215</v>
       </c>
       <c r="D5" t="n">
-        <v>5.204391478073943</v>
+        <v>5.204391478073955</v>
       </c>
       <c r="E5" t="n">
-        <v>3.810889052429081</v>
+        <v>3.810889052429034</v>
       </c>
       <c r="F5" t="n">
-        <v>3.747925927693691</v>
+        <v>3.747925927693693</v>
       </c>
       <c r="G5" t="n">
-        <v>6.489077701184917</v>
+        <v>6.489077701184922</v>
       </c>
       <c r="H5" t="n">
-        <v>5.311553095651789</v>
+        <v>5.311553095651741</v>
       </c>
       <c r="I5" t="n">
-        <v>5.402934015911444</v>
+        <v>5.40293401591139</v>
       </c>
       <c r="J5" t="n">
-        <v>5.730042002206296</v>
+        <v>5.730042002206283</v>
       </c>
       <c r="K5" t="n">
-        <v>5.915771790058425</v>
+        <v>5.915771790058432</v>
       </c>
       <c r="L5" t="n">
-        <v>5.220871995284527</v>
+        <v>5.220871995284475</v>
       </c>
       <c r="M5" t="n">
-        <v>6.455044242322459</v>
+        <v>6.455044242322424</v>
       </c>
       <c r="N5" t="n">
-        <v>10.07018886758695</v>
+        <v>4.267049944300617</v>
       </c>
       <c r="O5" t="n">
-        <v>4.787736440722093</v>
+        <v>4.787736440722065</v>
       </c>
       <c r="P5" t="n">
-        <v>4.654826240979722</v>
+        <v>4.654826240979687</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.374716150136593</v>
+        <v>3.374716150136594</v>
       </c>
       <c r="R5" t="n">
-        <v>5.492990768503655</v>
+        <v>5.49299076850364</v>
       </c>
       <c r="S5" t="n">
-        <v>5.758458162878106</v>
+        <v>5.7584581628781</v>
       </c>
       <c r="T5" t="n">
-        <v>5.419960107678265</v>
+        <v>5.41996010767823</v>
       </c>
       <c r="U5" t="n">
-        <v>4.907265147007265</v>
+        <v>4.907265147007256</v>
       </c>
       <c r="V5" t="n">
-        <v>5.179806530680805</v>
+        <v>5.179806530680815</v>
       </c>
       <c r="W5" t="n">
-        <v>5.412732279657217</v>
+        <v>5.412732279657189</v>
       </c>
       <c r="X5" t="n">
-        <v>3.551616734532733</v>
+        <v>3.551616734532648</v>
       </c>
       <c r="Y5" t="n">
-        <v>7.001431672168079</v>
+        <v>7.001431672168055</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.776062650400537</v>
+        <v>3.776062650400627</v>
       </c>
       <c r="AA5" t="n">
-        <v>5.738863228810406</v>
+        <v>5.738863228810411</v>
       </c>
       <c r="AB5" t="n">
-        <v>8.042615203418993</v>
+        <v>8.04261520341892</v>
       </c>
     </row>
     <row r="6">
@@ -938,7 +938,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>91.59761529184013</v>
+        <v>91.59761529183999</v>
       </c>
       <c r="C6" t="n">
         <v>116.5510440193439</v>
@@ -947,13 +947,13 @@
         <v>116.4606338726698</v>
       </c>
       <c r="E6" t="n">
-        <v>110.1425622017701</v>
+        <v>110.14256220177</v>
       </c>
       <c r="F6" t="n">
-        <v>58.74335319625796</v>
+        <v>58.74335319625789</v>
       </c>
       <c r="G6" t="n">
-        <v>117.4175554001406</v>
+        <v>117.4175554001405</v>
       </c>
       <c r="H6" t="n">
         <v>116.5677954902476</v>
@@ -962,61 +962,61 @@
         <v>116.6591764105071</v>
       </c>
       <c r="J6" t="n">
-        <v>116.9862843968021</v>
+        <v>116.9862843968019</v>
       </c>
       <c r="K6" t="n">
-        <v>117.1720141846543</v>
+        <v>117.1720141846542</v>
       </c>
       <c r="L6" t="n">
-        <v>116.4771143898805</v>
+        <v>116.4771143898803</v>
       </c>
       <c r="M6" t="n">
         <v>117.7112866369199</v>
       </c>
       <c r="N6" t="n">
-        <v>10.07018886758695</v>
+        <v>116.7485855616948</v>
       </c>
       <c r="O6" t="n">
-        <v>125.2122599213932</v>
+        <v>125.2122599213931</v>
       </c>
       <c r="P6" t="n">
-        <v>126.9625828805209</v>
+        <v>126.9625828805208</v>
       </c>
       <c r="Q6" t="n">
-        <v>116.5222810661492</v>
+        <v>116.5222810661489</v>
       </c>
       <c r="R6" t="n">
-        <v>116.7492331630994</v>
+        <v>116.7492331630993</v>
       </c>
       <c r="S6" t="n">
         <v>117.0147005574739</v>
       </c>
       <c r="T6" t="n">
-        <v>116.676202502274</v>
+        <v>116.6762025022739</v>
       </c>
       <c r="U6" t="n">
         <v>116.9413727340083</v>
       </c>
       <c r="V6" t="n">
-        <v>145.7062423945572</v>
+        <v>145.7062423945571</v>
       </c>
       <c r="W6" t="n">
         <v>116.6686640255371</v>
       </c>
       <c r="X6" t="n">
-        <v>116.5543089017376</v>
+        <v>116.5543089017374</v>
       </c>
       <c r="Y6" t="n">
-        <v>116.6969096383316</v>
+        <v>116.6969096383317</v>
       </c>
       <c r="Z6" t="n">
-        <v>101.5791388042048</v>
+        <v>101.5791388042046</v>
       </c>
       <c r="AA6" t="n">
         <v>116.9951056234061</v>
       </c>
       <c r="AB6" t="n">
-        <v>117.6477027647815</v>
+        <v>117.6477027647814</v>
       </c>
     </row>
   </sheetData>
@@ -1182,85 +1182,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.809041943515195</v>
+        <v>2.809041943515193</v>
       </c>
       <c r="C2" t="n">
-        <v>3.152241722889547</v>
+        <v>3.152241722889557</v>
       </c>
       <c r="D2" t="n">
-        <v>2.796148741812397</v>
+        <v>2.796148741812392</v>
       </c>
       <c r="E2" t="n">
-        <v>2.800216012872776</v>
+        <v>2.800216012872773</v>
       </c>
       <c r="F2" t="n">
-        <v>2.899283672549741</v>
+        <v>2.899283672549731</v>
       </c>
       <c r="G2" t="n">
-        <v>2.756360069512186</v>
+        <v>2.75636006951218</v>
       </c>
       <c r="H2" t="n">
-        <v>2.731359753714077</v>
+        <v>2.731359753714072</v>
       </c>
       <c r="I2" t="n">
-        <v>2.80954877864335</v>
+        <v>2.809548778643351</v>
       </c>
       <c r="J2" t="n">
-        <v>2.783492858527138</v>
+        <v>2.783492858527121</v>
       </c>
       <c r="K2" t="n">
-        <v>2.804449678018202</v>
+        <v>2.804449678018209</v>
       </c>
       <c r="L2" t="n">
         <v>2.881680784806703</v>
       </c>
       <c r="M2" t="n">
-        <v>2.751818917689246</v>
+        <v>2.751818917689245</v>
       </c>
       <c r="N2" t="n">
-        <v>2.766444046033676</v>
+        <v>2.766444046033671</v>
       </c>
       <c r="O2" t="n">
-        <v>5.471662348216655</v>
+        <v>5.471662348216658</v>
       </c>
       <c r="P2" t="n">
-        <v>2.752159567879127</v>
+        <v>2.752159567879111</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.824727114000235</v>
+        <v>2.824727114000231</v>
       </c>
       <c r="R2" t="n">
-        <v>3.033757458930701</v>
+        <v>3.0337574589307</v>
       </c>
       <c r="S2" t="n">
-        <v>2.845831693083119</v>
+        <v>2.845831693083122</v>
       </c>
       <c r="T2" t="n">
-        <v>2.767782319687005</v>
+        <v>2.767782319687004</v>
       </c>
       <c r="U2" t="n">
-        <v>3.745279812023386</v>
+        <v>3.745279812023353</v>
       </c>
       <c r="V2" t="n">
-        <v>2.774746036875113</v>
+        <v>2.774746036875106</v>
       </c>
       <c r="W2" t="n">
-        <v>4.025840966947658</v>
+        <v>4.025840966947638</v>
       </c>
       <c r="X2" t="n">
-        <v>2.793536330536033</v>
+        <v>2.793536330536032</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.774898819358035</v>
+        <v>2.774898819358028</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.164657445322196</v>
+        <v>3.164657445322224</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.765886257304916</v>
+        <v>2.765886257304912</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.777996010680381</v>
+        <v>2.777996010680388</v>
       </c>
     </row>
     <row r="3">
@@ -1270,85 +1270,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.281426019775052</v>
+        <v>3.599777737320917</v>
       </c>
       <c r="C3" t="n">
-        <v>6.317419173500292</v>
+        <v>4.170517019768881</v>
       </c>
       <c r="D3" t="n">
-        <v>5.013429621937196</v>
+        <v>3.524533390321</v>
       </c>
       <c r="E3" t="n">
-        <v>4.996637695924263</v>
+        <v>3.453302540127194</v>
       </c>
       <c r="F3" t="n">
-        <v>7.438063271209706</v>
+        <v>4.363337517766804</v>
       </c>
       <c r="G3" t="n">
-        <v>4.068989918281144</v>
+        <v>3.190166103139096</v>
       </c>
       <c r="H3" t="n">
-        <v>3.506790828047381</v>
+        <v>3.014926830480474</v>
       </c>
       <c r="I3" t="n">
-        <v>5.331182306512908</v>
+        <v>3.644100642460891</v>
       </c>
       <c r="J3" t="n">
-        <v>4.706855788846132</v>
+        <v>3.412795278655226</v>
       </c>
       <c r="K3" t="n">
-        <v>5.201685237810658</v>
+        <v>3.569464100243326</v>
       </c>
       <c r="L3" t="n">
-        <v>6.973146218586685</v>
+        <v>4.16089495244537</v>
       </c>
       <c r="M3" t="n">
-        <v>4.027986853513097</v>
+        <v>3.188366255359542</v>
       </c>
       <c r="N3" t="n">
-        <v>4.316489790101496</v>
+        <v>3.29257302918606</v>
       </c>
       <c r="O3" t="n">
-        <v>6.373148470459806</v>
+        <v>5.781347669386791</v>
       </c>
       <c r="P3" t="n">
-        <v>3.970131872034597</v>
+        <v>3.158351391713428</v>
       </c>
       <c r="Q3" t="n">
-        <v>5.672824489175754</v>
+        <v>3.740143385374397</v>
       </c>
       <c r="R3" t="n">
-        <v>10.58780855713088</v>
+        <v>5.491595897590482</v>
       </c>
       <c r="S3" t="n">
-        <v>6.135337371360102</v>
+        <v>3.878985660162715</v>
       </c>
       <c r="T3" t="n">
-        <v>4.353776891475106</v>
+        <v>3.307461596665085</v>
       </c>
       <c r="U3" t="n">
-        <v>4.807859193971145</v>
+        <v>4.104370397274807</v>
       </c>
       <c r="V3" t="n">
-        <v>4.492784912701934</v>
+        <v>3.332123312939177</v>
       </c>
       <c r="W3" t="n">
-        <v>6.164923343702247</v>
+        <v>4.73320382684487</v>
       </c>
       <c r="X3" t="n">
-        <v>4.950365814145565</v>
+        <v>3.499259477040387</v>
       </c>
       <c r="Y3" t="n">
-        <v>4.510638507062474</v>
+        <v>3.358392368103983</v>
       </c>
       <c r="Z3" t="n">
-        <v>5.027386549751405</v>
+        <v>3.758289497676686</v>
       </c>
       <c r="AA3" t="n">
-        <v>4.300272976340073</v>
+        <v>3.284900608046271</v>
       </c>
       <c r="AB3" t="n">
-        <v>4.617543825902708</v>
+        <v>3.4062870459818</v>
       </c>
     </row>
     <row r="4">
@@ -1358,82 +1358,82 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>21.4724447907103</v>
+        <v>21.47244479071008</v>
       </c>
       <c r="C4" t="n">
-        <v>28.69473844305301</v>
+        <v>28.69473844305308</v>
       </c>
       <c r="D4" t="n">
-        <v>20.74566593096062</v>
+        <v>20.74566593096064</v>
       </c>
       <c r="E4" t="n">
-        <v>20.33409347293483</v>
+        <v>20.3340934729348</v>
       </c>
       <c r="F4" t="n">
-        <v>42.26808648377286</v>
+        <v>42.26808648377309</v>
       </c>
       <c r="G4" t="n">
-        <v>11.72311362012206</v>
+        <v>11.72311362012192</v>
       </c>
       <c r="H4" t="n">
-        <v>8.380463876202976</v>
+        <v>8.380463876202908</v>
       </c>
       <c r="I4" t="n">
-        <v>24.25887794747427</v>
+        <v>24.2588779474742</v>
       </c>
       <c r="J4" t="n">
-        <v>17.51754816221357</v>
+        <v>17.51754816221362</v>
       </c>
       <c r="K4" t="n">
-        <v>20.95008112781478</v>
+        <v>20.95008112781492</v>
       </c>
       <c r="L4" t="n">
-        <v>34.63473408118447</v>
+        <v>34.63473408118445</v>
       </c>
       <c r="M4" t="n">
-        <v>12.58322856856409</v>
+        <v>12.58322856856404</v>
       </c>
       <c r="N4" t="n">
-        <v>15.20076458153769</v>
+        <v>15.20076458153764</v>
       </c>
       <c r="O4" t="n">
-        <v>8.418884306035146</v>
+        <v>8.418884306035197</v>
       </c>
       <c r="P4" t="n">
-        <v>11.00667403182613</v>
+        <v>11.0066740318259</v>
       </c>
       <c r="Q4" t="n">
-        <v>25.58269210432832</v>
+        <v>25.58269210432825</v>
       </c>
       <c r="R4" t="n">
-        <v>72.70366033248793</v>
+        <v>72.70366033248791</v>
       </c>
       <c r="S4" t="n">
         <v>27.80373167549038</v>
       </c>
       <c r="T4" t="n">
-        <v>15.74389287210524</v>
+        <v>15.74389287210512</v>
       </c>
       <c r="U4" t="n">
-        <v>9.814887401668406</v>
+        <v>9.814887401667896</v>
       </c>
       <c r="V4" t="n">
-        <v>15.05074564054518</v>
+        <v>15.05074564054496</v>
       </c>
       <c r="W4" t="n">
-        <v>20.15155872856498</v>
+        <v>20.151558728565</v>
       </c>
       <c r="X4" t="n">
-        <v>19.92868299595075</v>
+        <v>19.92868299595063</v>
       </c>
       <c r="Y4" t="n">
-        <v>16.77165251938758</v>
+        <v>16.77165251938733</v>
       </c>
       <c r="Z4" t="n">
-        <v>15.70271680902756</v>
+        <v>15.70271680902768</v>
       </c>
       <c r="AA4" t="n">
-        <v>14.87549044058916</v>
+        <v>14.87549044058907</v>
       </c>
       <c r="AB4" t="n">
         <v>18.63571983479743</v>
@@ -1446,85 +1446,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.893239328900178</v>
+        <v>5.893239328900038</v>
       </c>
       <c r="C5" t="n">
-        <v>8.28492526403001</v>
+        <v>8.284925264030054</v>
       </c>
       <c r="D5" t="n">
-        <v>7.803475455184128</v>
+        <v>7.803475455184202</v>
       </c>
       <c r="E5" t="n">
-        <v>6.754726613427843</v>
+        <v>6.754726613427919</v>
       </c>
       <c r="F5" t="n">
-        <v>7.232841809394645</v>
+        <v>7.232841809394557</v>
       </c>
       <c r="G5" t="n">
-        <v>7.780342294417824</v>
+        <v>7.780342294417808</v>
       </c>
       <c r="H5" t="n">
-        <v>7.071654030206569</v>
+        <v>7.071654030206692</v>
       </c>
       <c r="I5" t="n">
-        <v>7.954835035511262</v>
+        <v>7.954835035511207</v>
       </c>
       <c r="J5" t="n">
-        <v>7.659563137589211</v>
+        <v>7.659563137589094</v>
       </c>
       <c r="K5" t="n">
-        <v>7.897238348248247</v>
+        <v>7.897238348248188</v>
       </c>
       <c r="L5" t="n">
-        <v>8.76959922748855</v>
+        <v>8.769599227488587</v>
       </c>
       <c r="M5" t="n">
-        <v>7.325308174659432</v>
+        <v>7.325308174659596</v>
       </c>
       <c r="N5" t="n">
-        <v>15.20076458153769</v>
+        <v>5.87430346276956</v>
       </c>
       <c r="O5" t="n">
-        <v>5.987970521253446</v>
+        <v>5.987970521253406</v>
       </c>
       <c r="P5" t="n">
-        <v>6.043549430031338</v>
+        <v>6.043549430031272</v>
       </c>
       <c r="Q5" t="n">
-        <v>5.666385017722087</v>
+        <v>5.666385017722148</v>
       </c>
       <c r="R5" t="n">
-        <v>10.48737522044546</v>
+        <v>10.48737522044564</v>
       </c>
       <c r="S5" t="n">
-        <v>8.364667245073852</v>
+        <v>8.364667245073763</v>
       </c>
       <c r="T5" t="n">
-        <v>7.4830636680789</v>
+        <v>7.483063668078913</v>
       </c>
       <c r="U5" t="n">
-        <v>6.210484718822267</v>
+        <v>6.210484718822054</v>
       </c>
       <c r="V5" t="n">
-        <v>6.983222337851754</v>
+        <v>6.983222337851523</v>
       </c>
       <c r="W5" t="n">
-        <v>7.770466495937227</v>
+        <v>7.770466495937169</v>
       </c>
       <c r="X5" t="n">
-        <v>5.50249540674811</v>
+        <v>5.502495406747968</v>
       </c>
       <c r="Y5" t="n">
-        <v>9.590615233994273</v>
+        <v>9.590615233994395</v>
       </c>
       <c r="Z5" t="n">
-        <v>5.54220785077209</v>
+        <v>5.542207850771917</v>
       </c>
       <c r="AA5" t="n">
-        <v>7.461646771241447</v>
+        <v>7.461646771241431</v>
       </c>
       <c r="AB5" t="n">
-        <v>9.758795911426461</v>
+        <v>9.758795911426489</v>
       </c>
     </row>
     <row r="6">
@@ -1534,49 +1534,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>81.90574602773839</v>
+        <v>81.90574602773833</v>
       </c>
       <c r="C6" t="n">
-        <v>104.158030063998</v>
+        <v>104.1580300639978</v>
       </c>
       <c r="D6" t="n">
-        <v>103.6765802551523</v>
+        <v>103.6765802551521</v>
       </c>
       <c r="E6" t="n">
-        <v>98.66429096015652</v>
+        <v>98.66429096015665</v>
       </c>
       <c r="F6" t="n">
-        <v>54.31809335637375</v>
+        <v>54.31809335637367</v>
       </c>
       <c r="G6" t="n">
         <v>103.2271497133559</v>
       </c>
       <c r="H6" t="n">
-        <v>102.9447588301746</v>
+        <v>102.9447588301745</v>
       </c>
       <c r="I6" t="n">
-        <v>103.8279398354792</v>
+        <v>103.8279398354791</v>
       </c>
       <c r="J6" t="n">
-        <v>103.532667937557</v>
+        <v>103.5326679375571</v>
       </c>
       <c r="K6" t="n">
         <v>103.7703431482159</v>
       </c>
       <c r="L6" t="n">
-        <v>104.6427040274564</v>
+        <v>104.6427040274562</v>
       </c>
       <c r="M6" t="n">
-        <v>103.1984129746448</v>
+        <v>103.1984129746447</v>
       </c>
       <c r="N6" t="n">
-        <v>15.20076458153769</v>
+        <v>103.3410520514962</v>
       </c>
       <c r="O6" t="n">
-        <v>110.2798621359907</v>
+        <v>110.2798621359909</v>
       </c>
       <c r="P6" t="n">
-        <v>112.0223897938627</v>
+        <v>112.0223897938625</v>
       </c>
       <c r="Q6" t="n">
         <v>103.9993869312424</v>
@@ -1585,34 +1585,34 @@
         <v>106.3604800204134</v>
       </c>
       <c r="S6" t="n">
-        <v>104.2377720450416</v>
+        <v>104.2377720450417</v>
       </c>
       <c r="T6" t="n">
-        <v>103.3561684680469</v>
+        <v>103.3561684680468</v>
       </c>
       <c r="U6" t="n">
-        <v>103.0969338124992</v>
+        <v>103.0969338124991</v>
       </c>
       <c r="V6" t="n">
         <v>128.720289354656</v>
       </c>
       <c r="W6" t="n">
-        <v>103.6431672656736</v>
+        <v>103.6431672656735</v>
       </c>
       <c r="X6" t="n">
-        <v>103.6470718680171</v>
+        <v>103.647071868017</v>
       </c>
       <c r="Y6" t="n">
-        <v>103.436552605583</v>
+        <v>103.4365526055828</v>
       </c>
       <c r="Z6" t="n">
-        <v>90.2956907583561</v>
+        <v>90.29569075835592</v>
       </c>
       <c r="AA6" t="n">
-        <v>103.3347515712095</v>
+        <v>103.3347515712093</v>
       </c>
       <c r="AB6" t="n">
-        <v>103.4843717892586</v>
+        <v>103.4843717892585</v>
       </c>
     </row>
   </sheetData>
@@ -1778,85 +1778,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.168082108945147</v>
+        <v>2.168082108945156</v>
       </c>
       <c r="C2" t="n">
-        <v>2.216901382946141</v>
+        <v>2.216901382946185</v>
       </c>
       <c r="D2" t="n">
-        <v>2.177873119840968</v>
+        <v>2.17787311984097</v>
       </c>
       <c r="E2" t="n">
-        <v>2.135461476627226</v>
+        <v>2.135461476627234</v>
       </c>
       <c r="F2" t="n">
-        <v>2.143204980110102</v>
+        <v>2.143204980110101</v>
       </c>
       <c r="G2" t="n">
-        <v>2.268673688960421</v>
+        <v>2.268673688960418</v>
       </c>
       <c r="H2" t="n">
-        <v>2.156964212361838</v>
+        <v>2.156964212361847</v>
       </c>
       <c r="I2" t="n">
-        <v>2.188205580987184</v>
+        <v>2.188205580987189</v>
       </c>
       <c r="J2" t="n">
-        <v>2.219119337695817</v>
+        <v>2.219119337695819</v>
       </c>
       <c r="K2" t="n">
-        <v>2.210639059734776</v>
+        <v>2.210639059734775</v>
       </c>
       <c r="L2" t="n">
-        <v>2.160046274026541</v>
+        <v>2.160046274026555</v>
       </c>
       <c r="M2" t="n">
-        <v>2.258182091709594</v>
+        <v>2.258182091709605</v>
       </c>
       <c r="N2" t="n">
-        <v>2.183343543941919</v>
+        <v>2.183343543941918</v>
       </c>
       <c r="O2" t="n">
-        <v>4.092762901710415</v>
+        <v>4.092762901710437</v>
       </c>
       <c r="P2" t="n">
-        <v>2.205792506311465</v>
+        <v>2.205792506311468</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.171077853634226</v>
+        <v>2.171077853634225</v>
       </c>
       <c r="R2" t="n">
-        <v>2.169855274664969</v>
+        <v>2.169855274664975</v>
       </c>
       <c r="S2" t="n">
-        <v>2.211998136785236</v>
+        <v>2.211998136785246</v>
       </c>
       <c r="T2" t="n">
-        <v>2.180477957889691</v>
+        <v>2.180477957889694</v>
       </c>
       <c r="U2" t="n">
-        <v>2.481065290279765</v>
+        <v>2.48106529027978</v>
       </c>
       <c r="V2" t="n">
-        <v>2.196543452865883</v>
+        <v>2.196543452865882</v>
       </c>
       <c r="W2" t="n">
-        <v>2.591814920829969</v>
+        <v>2.591814920829988</v>
       </c>
       <c r="X2" t="n">
-        <v>2.183744697927142</v>
+        <v>2.183744697927148</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.195230021544368</v>
+        <v>2.19523002154437</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.049726918380397</v>
+        <v>2.049726918380407</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.187512278840148</v>
+        <v>2.187512278840149</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.262601079795446</v>
+        <v>2.262601079795454</v>
       </c>
     </row>
     <row r="3">
@@ -1866,85 +1866,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.689435109431892</v>
+        <v>2.310246958649935</v>
       </c>
       <c r="C3" t="n">
-        <v>2.795347863353606</v>
+        <v>2.381646076767074</v>
       </c>
       <c r="D3" t="n">
-        <v>2.925056030704315</v>
+        <v>2.398292386136929</v>
       </c>
       <c r="E3" t="n">
-        <v>2.000222643934807</v>
+        <v>2.126732813261405</v>
       </c>
       <c r="F3" t="n">
-        <v>2.115493503156315</v>
+        <v>2.11616603161831</v>
       </c>
       <c r="G3" t="n">
-        <v>5.007569677323803</v>
+        <v>3.098796218562608</v>
       </c>
       <c r="H3" t="n">
-        <v>2.438435037411777</v>
+        <v>2.229579261290259</v>
       </c>
       <c r="I3" t="n">
-        <v>3.167904113613498</v>
+        <v>2.484293334595829</v>
       </c>
       <c r="J3" t="n">
-        <v>3.871477409591159</v>
+        <v>2.716175262304382</v>
       </c>
       <c r="K3" t="n">
-        <v>3.686761563984726</v>
+        <v>2.652881038931255</v>
       </c>
       <c r="L3" t="n">
-        <v>2.506235904393202</v>
+        <v>2.250050911495745</v>
       </c>
       <c r="M3" t="n">
-        <v>4.808739706459139</v>
+        <v>3.057308807657052</v>
       </c>
       <c r="N3" t="n">
-        <v>3.049542093992645</v>
+        <v>2.439368841246363</v>
       </c>
       <c r="O3" t="n">
-        <v>5.236924782799727</v>
+        <v>4.423463372427768</v>
       </c>
       <c r="P3" t="n">
-        <v>3.555892164282187</v>
+        <v>2.605300332088122</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.765024659965036</v>
+        <v>2.340868267357719</v>
       </c>
       <c r="R3" t="n">
-        <v>2.739780510143548</v>
+        <v>2.334882094730485</v>
       </c>
       <c r="S3" t="n">
-        <v>3.704673150665119</v>
+        <v>2.655876706074814</v>
       </c>
       <c r="T3" t="n">
-        <v>2.986266193224941</v>
+        <v>2.419619058003049</v>
       </c>
       <c r="U3" t="n">
-        <v>3.793659136297376</v>
+        <v>2.8728212765994</v>
       </c>
       <c r="V3" t="n">
-        <v>3.344769525707983</v>
+        <v>2.528829340491017</v>
       </c>
       <c r="W3" t="n">
-        <v>3.53226499296751</v>
+        <v>2.869830594204347</v>
       </c>
       <c r="X3" t="n">
-        <v>3.061252805721224</v>
+        <v>2.444299238779087</v>
       </c>
       <c r="Y3" t="n">
-        <v>3.324056772772493</v>
+        <v>2.531543109402734</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.948277987727951</v>
+        <v>2.309686734004697</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.144360752643758</v>
+        <v>2.470592918359408</v>
       </c>
       <c r="AB3" t="n">
-        <v>4.89346215439287</v>
+        <v>3.103075030306191</v>
       </c>
     </row>
     <row r="4">
@@ -1954,85 +1954,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.002986987782024</v>
+        <v>6.002986987783071</v>
       </c>
       <c r="C4" t="n">
-        <v>6.964043697320839</v>
+        <v>6.964043697320869</v>
       </c>
       <c r="D4" t="n">
-        <v>8.793882120358218</v>
+        <v>8.793882120358338</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.4621395305004703</v>
+        <v>-0.4621395304993565</v>
       </c>
       <c r="F4" t="n">
-        <v>1.037160792433365</v>
+        <v>1.037160792433466</v>
       </c>
       <c r="G4" t="n">
         <v>26.36294116762156</v>
       </c>
       <c r="H4" t="n">
-        <v>4.218391597220776</v>
+        <v>4.218391597220909</v>
       </c>
       <c r="I4" t="n">
-        <v>11.24321125559396</v>
+        <v>11.24321125559406</v>
       </c>
       <c r="J4" t="n">
-        <v>16.74949194066301</v>
+        <v>16.74949194066307</v>
       </c>
       <c r="K4" t="n">
-        <v>15.24907241994681</v>
+        <v>15.24907241994712</v>
       </c>
       <c r="L4" t="n">
-        <v>4.577805519112644</v>
+        <v>4.577805519118603</v>
       </c>
       <c r="M4" t="n">
-        <v>27.14029734250864</v>
+        <v>27.14029734250876</v>
       </c>
       <c r="N4" t="n">
-        <v>9.771603527381732</v>
+        <v>9.771603527381789</v>
       </c>
       <c r="O4" t="n">
-        <v>11.35534008838203</v>
+        <v>11.35534008838204</v>
       </c>
       <c r="P4" t="n">
-        <v>13.5987304449828</v>
+        <v>13.59873044498284</v>
       </c>
       <c r="Q4" t="n">
-        <v>7.120365789075827</v>
+        <v>7.120365789076259</v>
       </c>
       <c r="R4" t="n">
-        <v>7.13113074634976</v>
+        <v>7.131130746349914</v>
       </c>
       <c r="S4" t="n">
-        <v>14.98633057051932</v>
+        <v>14.98633057051957</v>
       </c>
       <c r="T4" t="n">
-        <v>9.385474576635717</v>
+        <v>9.385474576635772</v>
       </c>
       <c r="U4" t="n">
-        <v>13.63593370241021</v>
+        <v>13.63593370241025</v>
       </c>
       <c r="V4" t="n">
-        <v>11.42741071877096</v>
+        <v>11.42741071877093</v>
       </c>
       <c r="W4" t="n">
-        <v>10.35373733200564</v>
+        <v>10.35373733200558</v>
       </c>
       <c r="X4" t="n">
-        <v>9.979291778996394</v>
+        <v>9.979291778997048</v>
       </c>
       <c r="Y4" t="n">
-        <v>12.10297441181771</v>
+        <v>12.10297441181777</v>
       </c>
       <c r="Z4" t="n">
-        <v>9.530677579835942</v>
+        <v>9.530677579836759</v>
       </c>
       <c r="AA4" t="n">
-        <v>10.5110323394587</v>
+        <v>10.51103233945895</v>
       </c>
       <c r="AB4" t="n">
-        <v>29.02877344504788</v>
+        <v>29.02877344504812</v>
       </c>
     </row>
     <row r="5">
@@ -2042,85 +2042,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.035530558971602</v>
+        <v>4.035530558971733</v>
       </c>
       <c r="C5" t="n">
-        <v>5.762586117804669</v>
+        <v>5.762586117804809</v>
       </c>
       <c r="D5" t="n">
-        <v>5.847436203300377</v>
+        <v>5.847436203300492</v>
       </c>
       <c r="E5" t="n">
-        <v>4.462478903548007</v>
+        <v>4.462478903548094</v>
       </c>
       <c r="F5" t="n">
-        <v>4.019576419333277</v>
+        <v>4.019576419333333</v>
       </c>
       <c r="G5" t="n">
-        <v>7.225848459988345</v>
+        <v>7.22584845998839</v>
       </c>
       <c r="H5" t="n">
-        <v>5.61126047475092</v>
+        <v>5.611260474751076</v>
       </c>
       <c r="I5" t="n">
-        <v>5.96414610511381</v>
+        <v>5.964146105113954</v>
       </c>
       <c r="J5" t="n">
-        <v>6.312436524037643</v>
+        <v>6.312436524037699</v>
       </c>
       <c r="K5" t="n">
-        <v>6.217542567477953</v>
+        <v>6.217542567478118</v>
       </c>
       <c r="L5" t="n">
-        <v>5.646073779072146</v>
+        <v>5.646073779072559</v>
       </c>
       <c r="M5" t="n">
-        <v>6.754917240339807</v>
+        <v>6.754917240339871</v>
       </c>
       <c r="N5" t="n">
-        <v>9.771603527381732</v>
+        <v>4.590425990302984</v>
       </c>
       <c r="O5" t="n">
-        <v>5.100594435062191</v>
+        <v>5.100594435062318</v>
       </c>
       <c r="P5" t="n">
-        <v>5.117577946818528</v>
+        <v>5.117577946818665</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.735022299857608</v>
+        <v>3.735022299857733</v>
       </c>
       <c r="R5" t="n">
-        <v>5.756870953646454</v>
+        <v>5.756870953646546</v>
       </c>
       <c r="S5" t="n">
-        <v>6.232893967969231</v>
+        <v>6.232893967969403</v>
       </c>
       <c r="T5" t="n">
-        <v>5.87685904734537</v>
+        <v>5.876859047345508</v>
       </c>
       <c r="U5" t="n">
-        <v>5.289181089999635</v>
+        <v>5.289181089999753</v>
       </c>
       <c r="V5" t="n">
-        <v>5.566044762877102</v>
+        <v>5.566044762877118</v>
       </c>
       <c r="W5" t="n">
-        <v>5.948609016987456</v>
+        <v>5.948609016987642</v>
       </c>
       <c r="X5" t="n">
-        <v>4.034028727060018</v>
+        <v>4.034028727060202</v>
       </c>
       <c r="Y5" t="n">
-        <v>7.70120503944505</v>
+        <v>7.701205039445183</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.196857203738517</v>
+        <v>4.196857203738628</v>
       </c>
       <c r="AA5" t="n">
-        <v>5.956314938428303</v>
+        <v>5.956314938428459</v>
       </c>
       <c r="AB5" t="n">
-        <v>8.575394772026558</v>
+        <v>8.575394772026721</v>
       </c>
     </row>
     <row r="6">
@@ -2130,85 +2130,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>86.09660874291033</v>
+        <v>86.09660874291045</v>
       </c>
       <c r="C6" t="n">
-        <v>109.557262033095</v>
+        <v>109.5572620330951</v>
       </c>
       <c r="D6" t="n">
         <v>109.6421121185906</v>
       </c>
       <c r="E6" t="n">
-        <v>103.7543718482869</v>
+        <v>103.7543718482871</v>
       </c>
       <c r="F6" t="n">
-        <v>55.22665693722493</v>
+        <v>55.22665693722497</v>
       </c>
       <c r="G6" t="n">
-        <v>110.6677466436856</v>
+        <v>110.6677466436858</v>
       </c>
       <c r="H6" t="n">
-        <v>109.4059363900413</v>
+        <v>109.4059363900412</v>
       </c>
       <c r="I6" t="n">
-        <v>109.7588220204041</v>
+        <v>109.7588220204042</v>
       </c>
       <c r="J6" t="n">
-        <v>110.1071124393279</v>
+        <v>110.107112439328</v>
       </c>
       <c r="K6" t="n">
-        <v>110.0122184827684</v>
+        <v>110.0122184827685</v>
       </c>
       <c r="L6" t="n">
-        <v>109.4407496943624</v>
+        <v>109.4407496943625</v>
       </c>
       <c r="M6" t="n">
         <v>110.5495931556417</v>
       </c>
       <c r="N6" t="n">
-        <v>9.771603527381732</v>
+        <v>109.7039030753305</v>
       </c>
       <c r="O6" t="n">
         <v>117.6179522346455</v>
       </c>
       <c r="P6" t="n">
-        <v>119.4128098126191</v>
+        <v>119.4128098126192</v>
       </c>
       <c r="Q6" t="n">
-        <v>109.565356787374</v>
+        <v>109.5653567873741</v>
       </c>
       <c r="R6" t="n">
-        <v>109.5515468689368</v>
+        <v>109.5515468689369</v>
       </c>
       <c r="S6" t="n">
-        <v>110.0275698832595</v>
+        <v>110.0275698832596</v>
       </c>
       <c r="T6" t="n">
-        <v>109.6715349626359</v>
+        <v>109.671534962636</v>
       </c>
       <c r="U6" t="n">
         <v>109.9340379706625</v>
       </c>
       <c r="V6" t="n">
-        <v>136.8909350037817</v>
+        <v>136.8909350037818</v>
       </c>
       <c r="W6" t="n">
-        <v>109.7429505781547</v>
+        <v>109.7429505781548</v>
       </c>
       <c r="X6" t="n">
-        <v>109.7084342941332</v>
+        <v>109.7084342941334</v>
       </c>
       <c r="Y6" t="n">
-        <v>109.8381663078999</v>
+        <v>109.8381663079</v>
       </c>
       <c r="Z6" t="n">
-        <v>95.59528120156402</v>
+        <v>95.59528120156411</v>
       </c>
       <c r="AA6" t="n">
-        <v>109.7509908537184</v>
+        <v>109.7509908537185</v>
       </c>
       <c r="AB6" t="n">
-        <v>110.5929083865975</v>
+        <v>110.5929083865976</v>
       </c>
     </row>
   </sheetData>
@@ -2374,85 +2374,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.45341996466241</v>
+        <v>2.453419964662421</v>
       </c>
       <c r="C2" t="n">
-        <v>2.626995143814096</v>
+        <v>2.626995143814098</v>
       </c>
       <c r="D2" t="n">
-        <v>2.473989551268934</v>
+        <v>2.473989551268944</v>
       </c>
       <c r="E2" t="n">
-        <v>2.438692898553366</v>
+        <v>2.438692898553377</v>
       </c>
       <c r="F2" t="n">
-        <v>2.448843060475886</v>
+        <v>2.448843060475895</v>
       </c>
       <c r="G2" t="n">
-        <v>2.548900167041884</v>
+        <v>2.548900167041891</v>
       </c>
       <c r="H2" t="n">
-        <v>2.432364444275144</v>
+        <v>2.432364444275154</v>
       </c>
       <c r="I2" t="n">
-        <v>2.574970772112178</v>
+        <v>2.574970772112187</v>
       </c>
       <c r="J2" t="n">
-        <v>2.503404569586982</v>
+        <v>2.503404569586988</v>
       </c>
       <c r="K2" t="n">
-        <v>2.487437928382292</v>
+        <v>2.487437928382303</v>
       </c>
       <c r="L2" t="n">
-        <v>2.438968534113644</v>
+        <v>2.438968534113653</v>
       </c>
       <c r="M2" t="n">
-        <v>2.532400950915509</v>
+        <v>2.532400950915515</v>
       </c>
       <c r="N2" t="n">
-        <v>2.466242149191709</v>
+        <v>2.46624214919172</v>
       </c>
       <c r="O2" t="n">
-        <v>4.782909179304437</v>
+        <v>4.782909179304449</v>
       </c>
       <c r="P2" t="n">
-        <v>2.483998430156824</v>
+        <v>2.48399843015683</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.531301236892546</v>
+        <v>2.531301236892557</v>
       </c>
       <c r="R2" t="n">
-        <v>2.44004498722116</v>
+        <v>2.440044987221171</v>
       </c>
       <c r="S2" t="n">
-        <v>2.48969854123267</v>
+        <v>2.489698541232678</v>
       </c>
       <c r="T2" t="n">
-        <v>2.450842071293204</v>
+        <v>2.450842071293214</v>
       </c>
       <c r="U2" t="n">
-        <v>3.101879905228489</v>
+        <v>3.101879905228498</v>
       </c>
       <c r="V2" t="n">
-        <v>2.472144400491759</v>
+        <v>2.47214440049177</v>
       </c>
       <c r="W2" t="n">
-        <v>3.287952029158697</v>
+        <v>3.287952029158712</v>
       </c>
       <c r="X2" t="n">
-        <v>2.470711563775549</v>
+        <v>2.470711563775561</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.507428412867819</v>
+        <v>2.507428412867827</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.539968668909799</v>
+        <v>2.539968668909807</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.461506003044004</v>
+        <v>2.461506003044014</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.533299561763502</v>
+        <v>2.533299561763499</v>
       </c>
     </row>
     <row r="3">
@@ -2462,85 +2462,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.222501034583955</v>
+        <v>2.698135662515218</v>
       </c>
       <c r="C3" t="n">
-        <v>3.50846204056777</v>
+        <v>2.91042237678143</v>
       </c>
       <c r="D3" t="n">
-        <v>3.712579475217053</v>
+        <v>2.875799159684057</v>
       </c>
       <c r="E3" t="n">
-        <v>2.875154659333031</v>
+        <v>2.585059053932982</v>
       </c>
       <c r="F3" t="n">
-        <v>3.127972777899028</v>
+        <v>2.671887880472695</v>
       </c>
       <c r="G3" t="n">
-        <v>5.422221872398489</v>
+        <v>3.44114859838785</v>
       </c>
       <c r="H3" t="n">
-        <v>2.742382774778155</v>
+        <v>2.539116694304716</v>
       </c>
       <c r="I3" t="n">
-        <v>6.076003539871983</v>
+        <v>3.705329445805729</v>
       </c>
       <c r="J3" t="n">
-        <v>4.38246604201739</v>
+        <v>3.095183388549368</v>
       </c>
       <c r="K3" t="n">
-        <v>4.022465856211396</v>
+        <v>2.966777937279722</v>
       </c>
       <c r="L3" t="n">
-        <v>2.891891315701258</v>
+        <v>2.587791028995821</v>
       </c>
       <c r="M3" t="n">
-        <v>5.098651384014191</v>
+        <v>3.362188086537846</v>
       </c>
       <c r="N3" t="n">
-        <v>3.528032097814141</v>
+        <v>2.809723890274045</v>
       </c>
       <c r="O3" t="n">
-        <v>5.954200505605054</v>
+        <v>5.146690151053741</v>
       </c>
       <c r="P3" t="n">
-        <v>3.924339982596737</v>
+        <v>2.935240036678071</v>
       </c>
       <c r="Q3" t="n">
-        <v>5.043814601491752</v>
+        <v>3.328920684182589</v>
       </c>
       <c r="R3" t="n">
-        <v>2.921681682107688</v>
+        <v>2.601501719442382</v>
       </c>
       <c r="S3" t="n">
-        <v>4.061710108361468</v>
+        <v>2.982234990015366</v>
       </c>
       <c r="T3" t="n">
-        <v>3.172652929472072</v>
+        <v>2.688279442602208</v>
       </c>
       <c r="U3" t="n">
-        <v>4.095842551064542</v>
+        <v>3.418477305160851</v>
       </c>
       <c r="V3" t="n">
-        <v>3.653456432690154</v>
+        <v>2.838989221059754</v>
       </c>
       <c r="W3" t="n">
-        <v>4.439366062266824</v>
+        <v>3.657846493253714</v>
       </c>
       <c r="X3" t="n">
-        <v>3.634962485013938</v>
+        <v>2.847087289778041</v>
       </c>
       <c r="Y3" t="n">
-        <v>4.482605527532596</v>
+        <v>3.135438745868365</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.903113403636685</v>
+        <v>2.96132479865585</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.415816969224984</v>
+        <v>2.769244501349066</v>
       </c>
       <c r="AB3" t="n">
-        <v>5.100198710359426</v>
+        <v>3.379020043746556</v>
       </c>
     </row>
     <row r="4">
@@ -2550,85 +2550,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.706483068031921</v>
+        <v>7.706483068032136</v>
       </c>
       <c r="C4" t="n">
-        <v>9.04307553723469</v>
+        <v>9.043075537234747</v>
       </c>
       <c r="D4" t="n">
-        <v>12.69545654857536</v>
+        <v>12.69545654857532</v>
       </c>
       <c r="E4" t="n">
-        <v>5.277961013070687</v>
+        <v>5.277961013070787</v>
       </c>
       <c r="F4" t="n">
-        <v>7.479091012127979</v>
+        <v>7.479091012128078</v>
       </c>
       <c r="G4" t="n">
-        <v>25.41595261665475</v>
+        <v>25.41595261665488</v>
       </c>
       <c r="H4" t="n">
-        <v>4.122718164939036</v>
+        <v>4.122718164939131</v>
       </c>
       <c r="I4" t="n">
-        <v>34.34623351929242</v>
+        <v>34.34623351929258</v>
       </c>
       <c r="J4" t="n">
-        <v>17.51368256469451</v>
+        <v>17.51368256469462</v>
       </c>
       <c r="K4" t="n">
-        <v>14.25811945266213</v>
+        <v>14.25811945266222</v>
       </c>
       <c r="L4" t="n">
-        <v>5.166530545066695</v>
+        <v>5.166530545066776</v>
       </c>
       <c r="M4" t="n">
-        <v>25.4823998555349</v>
+        <v>25.48239985553497</v>
       </c>
       <c r="N4" t="n">
-        <v>10.87359888260973</v>
+        <v>10.87359888260979</v>
       </c>
       <c r="O4" t="n">
-        <v>10.7502578574478</v>
+        <v>10.75025785744793</v>
       </c>
       <c r="P4" t="n">
-        <v>13.32406471668425</v>
+        <v>13.32406471668434</v>
       </c>
       <c r="Q4" t="n">
-        <v>23.79457937315792</v>
+        <v>23.79457937315795</v>
       </c>
       <c r="R4" t="n">
-        <v>5.721909046612907</v>
+        <v>5.72190904661298</v>
       </c>
       <c r="S4" t="n">
-        <v>14.55170368717891</v>
+        <v>14.55170368717898</v>
       </c>
       <c r="T4" t="n">
-        <v>7.908898803432671</v>
+        <v>7.908898803432816</v>
       </c>
       <c r="U4" t="n">
-        <v>9.828097057081738</v>
+        <v>9.828097057081699</v>
       </c>
       <c r="V4" t="n">
-        <v>10.84239558637369</v>
+        <v>10.84239558637374</v>
       </c>
       <c r="W4" t="n">
-        <v>11.52288610621176</v>
+        <v>11.52288610621177</v>
       </c>
       <c r="X4" t="n">
-        <v>11.87246735999234</v>
+        <v>11.87246735999252</v>
       </c>
       <c r="Y4" t="n">
-        <v>18.85886715687174</v>
+        <v>18.85886715687189</v>
       </c>
       <c r="Z4" t="n">
-        <v>12.28524565611849</v>
+        <v>12.28524565611851</v>
       </c>
       <c r="AA4" t="n">
-        <v>9.753060143832347</v>
+        <v>9.753060143832384</v>
       </c>
       <c r="AB4" t="n">
-        <v>26.49894311323546</v>
+        <v>26.4989431132356</v>
       </c>
     </row>
     <row r="5">
@@ -2638,85 +2638,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.494327761473562</v>
+        <v>4.494327761473635</v>
       </c>
       <c r="C5" t="n">
-        <v>6.360745990543014</v>
+        <v>6.360745990543168</v>
       </c>
       <c r="D5" t="n">
-        <v>6.540587146544925</v>
+        <v>6.54058714654506</v>
       </c>
       <c r="E5" t="n">
-        <v>5.17603821981203</v>
+        <v>5.176038219812199</v>
       </c>
       <c r="F5" t="n">
-        <v>4.725216504630134</v>
+        <v>4.725216504630232</v>
       </c>
       <c r="G5" t="n">
-        <v>7.762864402777655</v>
+        <v>7.762864402777728</v>
       </c>
       <c r="H5" t="n">
-        <v>6.070412414554946</v>
+        <v>6.070412414554998</v>
       </c>
       <c r="I5" t="n">
-        <v>7.681216489626081</v>
+        <v>7.681216489626203</v>
       </c>
       <c r="J5" t="n">
-        <v>6.871795490573379</v>
+        <v>6.871795490573478</v>
       </c>
       <c r="K5" t="n">
-        <v>6.692492752599536</v>
+        <v>6.692492752599629</v>
       </c>
       <c r="L5" t="n">
-        <v>6.145008647312044</v>
+        <v>6.145008647312243</v>
       </c>
       <c r="M5" t="n">
-        <v>7.207547623171923</v>
+        <v>7.207547623172124</v>
       </c>
       <c r="N5" t="n">
-        <v>10.87359888260973</v>
+        <v>5.046987970872096</v>
       </c>
       <c r="O5" t="n">
-        <v>5.495667972870636</v>
+        <v>5.495667972870685</v>
       </c>
       <c r="P5" t="n">
-        <v>5.539241419381816</v>
+        <v>5.53924141938187</v>
       </c>
       <c r="Q5" t="n">
-        <v>5.017556578378351</v>
+        <v>5.017556578378416</v>
       </c>
       <c r="R5" t="n">
-        <v>6.157167680354444</v>
+        <v>6.15716768035459</v>
       </c>
       <c r="S5" t="n">
-        <v>6.718027414677699</v>
+        <v>6.71802741467791</v>
       </c>
       <c r="T5" t="n">
-        <v>6.279125711852221</v>
+        <v>6.279125711852335</v>
       </c>
       <c r="U5" t="n">
-        <v>5.522969819116264</v>
+        <v>5.522969819116393</v>
       </c>
       <c r="V5" t="n">
-        <v>6.003157566238402</v>
+        <v>6.003157566238477</v>
       </c>
       <c r="W5" t="n">
-        <v>6.500554547202904</v>
+        <v>6.500554547202973</v>
       </c>
       <c r="X5" t="n">
-        <v>4.499417391141494</v>
+        <v>4.499417391141555</v>
       </c>
       <c r="Y5" t="n">
-        <v>8.699551066760575</v>
+        <v>8.699551066760687</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.765138009755523</v>
+        <v>4.765138009755485</v>
       </c>
       <c r="AA5" t="n">
-        <v>6.399579726628535</v>
+        <v>6.399579726628623</v>
       </c>
       <c r="AB5" t="n">
-        <v>9.105472896561524</v>
+        <v>9.105472896561521</v>
       </c>
     </row>
     <row r="6">
@@ -2726,85 +2726,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>80.7781066578185</v>
+        <v>80.77810665781854</v>
       </c>
       <c r="C6" t="n">
-        <v>102.7167878466587</v>
+        <v>102.7167878466588</v>
       </c>
       <c r="D6" t="n">
-        <v>102.8966290026606</v>
+        <v>102.8966290026607</v>
       </c>
       <c r="E6" t="n">
-        <v>97.44669652919004</v>
+        <v>97.44669652919012</v>
       </c>
       <c r="F6" t="n">
         <v>52.1589703335116</v>
       </c>
       <c r="G6" t="n">
-        <v>103.7427793754386</v>
+        <v>103.7427793754389</v>
       </c>
       <c r="H6" t="n">
         <v>102.4264542706705</v>
       </c>
       <c r="I6" t="n">
-        <v>104.0372583457416</v>
+        <v>104.0372583457417</v>
       </c>
       <c r="J6" t="n">
-        <v>103.2278373466889</v>
+        <v>103.227837346689</v>
       </c>
       <c r="K6" t="n">
         <v>103.0485346087152</v>
       </c>
       <c r="L6" t="n">
-        <v>102.5010505034277</v>
+        <v>102.5010505034278</v>
       </c>
       <c r="M6" t="n">
-        <v>103.5635894793102</v>
+        <v>103.5635894793103</v>
       </c>
       <c r="N6" t="n">
-        <v>10.87359888260973</v>
+        <v>102.8091185322174</v>
       </c>
       <c r="O6" t="n">
-        <v>110.1244450229229</v>
+        <v>110.124445022923</v>
       </c>
       <c r="P6" t="n">
-        <v>111.8401499955882</v>
+        <v>111.8401499955883</v>
       </c>
       <c r="Q6" t="n">
         <v>103.5439913634943</v>
       </c>
       <c r="R6" t="n">
-        <v>102.5132095364701</v>
+        <v>102.5132095364702</v>
       </c>
       <c r="S6" t="n">
-        <v>103.0740692707934</v>
+        <v>103.0740692707935</v>
       </c>
       <c r="T6" t="n">
         <v>102.6351675679677</v>
       </c>
       <c r="U6" t="n">
-        <v>102.7773834746269</v>
+        <v>102.777383474627</v>
       </c>
       <c r="V6" t="n">
-        <v>128.1255217375783</v>
+        <v>128.1255217375784</v>
       </c>
       <c r="W6" t="n">
-        <v>102.8562399215589</v>
+        <v>102.856239921559</v>
       </c>
       <c r="X6" t="n">
-        <v>102.8596026259739</v>
+        <v>102.859602625974</v>
       </c>
       <c r="Y6" t="n">
-        <v>103.2743363270562</v>
+        <v>103.2743363270563</v>
       </c>
       <c r="Z6" t="n">
-        <v>89.77337095361887</v>
+        <v>89.77337095361892</v>
       </c>
       <c r="AA6" t="n">
-        <v>102.7556215827441</v>
+        <v>102.7556215827442</v>
       </c>
       <c r="AB6" t="n">
-        <v>103.5667273564931</v>
+        <v>103.5667273564932</v>
       </c>
     </row>
   </sheetData>
@@ -2970,85 +2970,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.624225025941864</v>
+        <v>2.624225025941829</v>
       </c>
       <c r="C2" t="n">
-        <v>2.860397404555666</v>
+        <v>2.860397404555663</v>
       </c>
       <c r="D2" t="n">
-        <v>2.634502045743111</v>
+        <v>2.634502045743079</v>
       </c>
       <c r="E2" t="n">
-        <v>2.588068434377328</v>
+        <v>2.588068434377292</v>
       </c>
       <c r="F2" t="n">
-        <v>2.63931808613867</v>
+        <v>2.639318086138635</v>
       </c>
       <c r="G2" t="n">
-        <v>2.711580456204347</v>
+        <v>2.711580456204309</v>
       </c>
       <c r="H2" t="n">
-        <v>2.603549694586669</v>
+        <v>2.603549694586631</v>
       </c>
       <c r="I2" t="n">
-        <v>2.696665086155867</v>
+        <v>2.696665086155832</v>
       </c>
       <c r="J2" t="n">
-        <v>2.670158609974469</v>
+        <v>2.670158609974435</v>
       </c>
       <c r="K2" t="n">
-        <v>2.660542181682997</v>
+        <v>2.660542181682963</v>
       </c>
       <c r="L2" t="n">
-        <v>2.619581387210966</v>
+        <v>2.61958138721093</v>
       </c>
       <c r="M2" t="n">
-        <v>2.691632131174349</v>
+        <v>2.691632131174345</v>
       </c>
       <c r="N2" t="n">
-        <v>2.632566002170901</v>
+        <v>2.632566002170816</v>
       </c>
       <c r="O2" t="n">
-        <v>5.227341239579926</v>
+        <v>5.227341239579871</v>
       </c>
       <c r="P2" t="n">
-        <v>2.654300172730656</v>
+        <v>2.65430017273062</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.664129818984115</v>
+        <v>2.664129818984081</v>
       </c>
       <c r="R2" t="n">
-        <v>2.66347374724265</v>
+        <v>2.663473747242612</v>
       </c>
       <c r="S2" t="n">
-        <v>2.664040195116336</v>
+        <v>2.664040195116272</v>
       </c>
       <c r="T2" t="n">
-        <v>2.644222141417583</v>
+        <v>2.644222141417552</v>
       </c>
       <c r="U2" t="n">
-        <v>3.509893580658912</v>
+        <v>3.50989358065888</v>
       </c>
       <c r="V2" t="n">
-        <v>2.647938410047483</v>
+        <v>2.647938410047447</v>
       </c>
       <c r="W2" t="n">
-        <v>3.739751588442446</v>
+        <v>3.739751588442412</v>
       </c>
       <c r="X2" t="n">
-        <v>2.652874296946371</v>
+        <v>2.652874296946338</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.724785681622197</v>
+        <v>2.724785681622162</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.893745594073696</v>
+        <v>2.893745594073659</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.636651771100211</v>
+        <v>2.636651771100177</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.700875133405155</v>
+        <v>2.70087513340515</v>
       </c>
     </row>
     <row r="3">
@@ -3058,85 +3058,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.495568682642043</v>
+        <v>2.918389732723182</v>
       </c>
       <c r="C3" t="n">
-        <v>3.339513849609383</v>
+        <v>3.038450489693747</v>
       </c>
       <c r="D3" t="n">
-        <v>3.746190562581678</v>
+        <v>3.011447727185588</v>
       </c>
       <c r="E3" t="n">
-        <v>2.58699911456583</v>
+        <v>2.573699707266601</v>
       </c>
       <c r="F3" t="n">
-        <v>3.863380511672085</v>
+        <v>3.053976426804219</v>
       </c>
       <c r="G3" t="n">
-        <v>5.507101060043523</v>
+        <v>3.590078267100523</v>
       </c>
       <c r="H3" t="n">
-        <v>3.026221511952861</v>
+        <v>2.766388496827039</v>
       </c>
       <c r="I3" t="n">
-        <v>5.201431523908361</v>
+        <v>3.52138553843664</v>
       </c>
       <c r="J3" t="n">
-        <v>4.563309943765772</v>
+        <v>3.28185193851108</v>
       </c>
       <c r="K3" t="n">
-        <v>4.350204641774226</v>
+        <v>3.207372430815377</v>
       </c>
       <c r="L3" t="n">
-        <v>3.392581390313523</v>
+        <v>2.88697905815205</v>
       </c>
       <c r="M3" t="n">
-        <v>5.106459086365285</v>
+        <v>3.480881319978208</v>
       </c>
       <c r="N3" t="n">
-        <v>3.697975597032381</v>
+        <v>2.997166724468245</v>
       </c>
       <c r="O3" t="n">
-        <v>6.354154097895998</v>
+        <v>5.597953767159231</v>
       </c>
       <c r="P3" t="n">
-        <v>4.185329078465895</v>
+        <v>3.148603925905383</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.433174674921647</v>
+        <v>3.242731712399811</v>
       </c>
       <c r="R3" t="n">
-        <v>4.429271571626009</v>
+        <v>3.259257812219122</v>
       </c>
       <c r="S3" t="n">
-        <v>4.416555184381536</v>
+        <v>3.229796244446524</v>
       </c>
       <c r="T3" t="n">
-        <v>3.974481607561963</v>
+        <v>3.09639691996668</v>
       </c>
       <c r="U3" t="n">
-        <v>4.39686083519204</v>
+        <v>3.810923842361081</v>
       </c>
       <c r="V3" t="n">
-        <v>4.041930816648852</v>
+        <v>3.097995265407871</v>
       </c>
       <c r="W3" t="n">
-        <v>5.042469948352369</v>
+        <v>4.177340982361105</v>
       </c>
       <c r="X3" t="n">
-        <v>4.173503709053087</v>
+        <v>3.157176372063105</v>
       </c>
       <c r="Y3" t="n">
-        <v>5.838495385370917</v>
+        <v>3.737564519559015</v>
       </c>
       <c r="Z3" t="n">
-        <v>4.379027971173668</v>
+        <v>3.364861470663477</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.790600137857848</v>
+        <v>3.02770662755692</v>
       </c>
       <c r="AB3" t="n">
-        <v>5.301218275398792</v>
+        <v>3.572281107980876</v>
       </c>
     </row>
     <row r="4">
@@ -3146,49 +3146,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8.354328753969767</v>
+        <v>8.354328753969781</v>
       </c>
       <c r="C4" t="n">
-        <v>5.425586477541867</v>
+        <v>5.425586477541911</v>
       </c>
       <c r="D4" t="n">
-        <v>11.13056849443726</v>
+        <v>11.13056849443733</v>
       </c>
       <c r="E4" t="n">
-        <v>2.000751142991114</v>
+        <v>2.000751142991066</v>
       </c>
       <c r="F4" t="n">
-        <v>12.35836883384908</v>
+        <v>12.35836883384911</v>
       </c>
       <c r="G4" t="n">
-        <v>24.00662781504916</v>
+        <v>24.00662781504883</v>
       </c>
       <c r="H4" t="n">
-        <v>5.11453220763418</v>
+        <v>5.114532207634155</v>
       </c>
       <c r="I4" t="n">
-        <v>24.40948576456633</v>
+        <v>24.40948576456637</v>
       </c>
       <c r="J4" t="n">
-        <v>17.26794196477661</v>
+        <v>17.26794196477656</v>
       </c>
       <c r="K4" t="n">
-        <v>15.49660818132448</v>
+        <v>15.49660818132443</v>
       </c>
       <c r="L4" t="n">
-        <v>7.808835685967365</v>
+        <v>7.808835685967362</v>
       </c>
       <c r="M4" t="n">
         <v>23.13586690106007</v>
       </c>
       <c r="N4" t="n">
-        <v>10.83050639163246</v>
+        <v>10.83050639163251</v>
       </c>
       <c r="O4" t="n">
-        <v>10.3416233019176</v>
+        <v>10.34162330191755</v>
       </c>
       <c r="P4" t="n">
-        <v>13.67672326305254</v>
+        <v>13.67672326305252</v>
       </c>
       <c r="Q4" t="n">
         <v>16.66847863809734</v>
@@ -3197,34 +3197,34 @@
         <v>18.00328595182098</v>
       </c>
       <c r="S4" t="n">
-        <v>15.84046370477231</v>
+        <v>15.84046370477228</v>
       </c>
       <c r="T4" t="n">
-        <v>13.56093169206002</v>
+        <v>13.56093169206004</v>
       </c>
       <c r="U4" t="n">
-        <v>8.666516449532564</v>
+        <v>8.666516449532555</v>
       </c>
       <c r="V4" t="n">
-        <v>12.40975639362037</v>
+        <v>12.40975639362051</v>
       </c>
       <c r="W4" t="n">
-        <v>12.81169834271118</v>
+        <v>12.81169834271108</v>
       </c>
       <c r="X4" t="n">
-        <v>14.71992438111992</v>
+        <v>14.71992438111988</v>
       </c>
       <c r="Y4" t="n">
-        <v>29.46117411541087</v>
+        <v>29.46117411541083</v>
       </c>
       <c r="Z4" t="n">
-        <v>12.69705125250782</v>
+        <v>12.69705125250778</v>
       </c>
       <c r="AA4" t="n">
-        <v>11.50514012813352</v>
+        <v>11.50514012813351</v>
       </c>
       <c r="AB4" t="n">
-        <v>26.38717626251987</v>
+        <v>26.38717626251996</v>
       </c>
     </row>
     <row r="5">
@@ -3234,85 +3234,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.893726193320814</v>
+        <v>4.89372619332083</v>
       </c>
       <c r="C5" t="n">
-        <v>6.644294352343303</v>
+        <v>6.644294352343299</v>
       </c>
       <c r="D5" t="n">
-        <v>6.964178198507099</v>
+        <v>6.964178198507093</v>
       </c>
       <c r="E5" t="n">
-        <v>5.399045708782155</v>
+        <v>5.39904570878213</v>
       </c>
       <c r="F5" t="n">
-        <v>5.368676996719419</v>
+        <v>5.368676996719406</v>
       </c>
       <c r="G5" t="n">
-        <v>8.240065308664986</v>
+        <v>8.240065308665001</v>
       </c>
       <c r="H5" t="n">
-        <v>6.614557153410064</v>
+        <v>6.614557153410008</v>
       </c>
       <c r="I5" t="n">
         <v>7.666338336380603</v>
       </c>
       <c r="J5" t="n">
-        <v>7.365790948167057</v>
+        <v>7.365790948167063</v>
       </c>
       <c r="K5" t="n">
-        <v>7.258313513002483</v>
+        <v>7.25831351300245</v>
       </c>
       <c r="L5" t="n">
-        <v>6.795642496544484</v>
+        <v>6.795642496544456</v>
       </c>
       <c r="M5" t="n">
-        <v>7.619571334115075</v>
+        <v>7.619571334115146</v>
       </c>
       <c r="N5" t="n">
-        <v>10.83050639163246</v>
+        <v>5.427347272878326</v>
       </c>
       <c r="O5" t="n">
-        <v>5.881096661182562</v>
+        <v>5.881096661182569</v>
       </c>
       <c r="P5" t="n">
-        <v>5.987118278320507</v>
+        <v>5.987118278320462</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.960391204753702</v>
+        <v>4.960391204753646</v>
       </c>
       <c r="R5" t="n">
-        <v>7.291426894585496</v>
+        <v>7.291426894585456</v>
       </c>
       <c r="S5" t="n">
-        <v>7.297825183897388</v>
+        <v>7.297825183897375</v>
       </c>
       <c r="T5" t="n">
-        <v>7.073971150615239</v>
+        <v>7.073971150615296</v>
       </c>
       <c r="U5" t="n">
-        <v>5.904637275012391</v>
+        <v>5.904637275012424</v>
       </c>
       <c r="V5" t="n">
-        <v>6.579455881938554</v>
+        <v>6.579455881938505</v>
       </c>
       <c r="W5" t="n">
-        <v>7.064947957114775</v>
+        <v>7.064947957114777</v>
       </c>
       <c r="X5" t="n">
-        <v>5.012376643338492</v>
+        <v>5.012376643338522</v>
       </c>
       <c r="Y5" t="n">
-        <v>9.934550260659256</v>
+        <v>9.934550260659259</v>
       </c>
       <c r="Z5" t="n">
-        <v>5.172477740615602</v>
+        <v>5.172477740615546</v>
       </c>
       <c r="AA5" t="n">
-        <v>6.988460335338089</v>
+        <v>6.988460335338137</v>
       </c>
       <c r="AB5" t="n">
-        <v>9.75695284707229</v>
+        <v>9.756952847072235</v>
       </c>
     </row>
     <row r="6">
@@ -3322,49 +3322,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>81.01562922457957</v>
+        <v>81.01562922457951</v>
       </c>
       <c r="C6" t="n">
-        <v>102.7143729995563</v>
+        <v>102.7143729995562</v>
       </c>
       <c r="D6" t="n">
-        <v>103.0342568457201</v>
+        <v>103.03425684572</v>
       </c>
       <c r="E6" t="n">
         <v>97.45475046135468</v>
       </c>
       <c r="F6" t="n">
-        <v>52.59731393336075</v>
+        <v>52.59731393336071</v>
       </c>
       <c r="G6" t="n">
-        <v>103.9048934989074</v>
+        <v>103.9048934989073</v>
       </c>
       <c r="H6" t="n">
         <v>102.6846358006231</v>
       </c>
       <c r="I6" t="n">
-        <v>103.7364169835937</v>
+        <v>103.7364169835936</v>
       </c>
       <c r="J6" t="n">
         <v>103.4358695953802</v>
       </c>
       <c r="K6" t="n">
-        <v>103.3283921602153</v>
+        <v>103.3283921602154</v>
       </c>
       <c r="L6" t="n">
-        <v>102.8657211437575</v>
+        <v>102.8657211437574</v>
       </c>
       <c r="M6" t="n">
         <v>103.6896499813518</v>
       </c>
       <c r="N6" t="n">
-        <v>10.83050639163246</v>
+        <v>103.0123883429474</v>
       </c>
       <c r="O6" t="n">
-        <v>110.3082880254091</v>
+        <v>110.3082880254092</v>
       </c>
       <c r="P6" t="n">
-        <v>112.094954600995</v>
+        <v>112.0949546009949</v>
       </c>
       <c r="Q6" t="n">
         <v>103.3689167231334</v>
@@ -3373,16 +3373,16 @@
         <v>103.3615055417984</v>
       </c>
       <c r="S6" t="n">
-        <v>103.3679038311105</v>
+        <v>103.3679038311104</v>
       </c>
       <c r="T6" t="n">
         <v>103.1440497978283</v>
       </c>
       <c r="U6" t="n">
-        <v>102.9242954806644</v>
+        <v>102.9242954806643</v>
       </c>
       <c r="V6" t="n">
-        <v>128.453997883289</v>
+        <v>128.4539978832889</v>
       </c>
       <c r="W6" t="n">
         <v>103.1346425211869</v>
@@ -3391,13 +3391,13 @@
         <v>103.2417798747142</v>
       </c>
       <c r="Y6" t="n">
-        <v>104.0540520454989</v>
+        <v>104.0540520454988</v>
       </c>
       <c r="Z6" t="n">
         <v>90.02794198489076</v>
       </c>
       <c r="AA6" t="n">
-        <v>103.0585389825512</v>
+        <v>103.0585389825511</v>
       </c>
       <c r="AB6" t="n">
         <v>103.7855303486827</v>
@@ -3566,85 +3566,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.46801203306059</v>
+        <v>2.468012033060581</v>
       </c>
       <c r="C2" t="n">
-        <v>2.727788715105695</v>
+        <v>2.727788715105646</v>
       </c>
       <c r="D2" t="n">
-        <v>2.449965102443537</v>
+        <v>2.449965102443536</v>
       </c>
       <c r="E2" t="n">
-        <v>2.619827979225561</v>
+        <v>2.619827979225555</v>
       </c>
       <c r="F2" t="n">
-        <v>2.540641095793258</v>
+        <v>2.54064109579323</v>
       </c>
       <c r="G2" t="n">
-        <v>2.487998365600232</v>
+        <v>2.487998365600227</v>
       </c>
       <c r="H2" t="n">
-        <v>2.47110050290873</v>
+        <v>2.47110050290872</v>
       </c>
       <c r="I2" t="n">
-        <v>2.532486017215212</v>
+        <v>2.532486017215223</v>
       </c>
       <c r="J2" t="n">
-        <v>2.493746652002185</v>
+        <v>2.493746652002209</v>
       </c>
       <c r="K2" t="n">
-        <v>2.540531406389108</v>
+        <v>2.540531406389099</v>
       </c>
       <c r="L2" t="n">
-        <v>2.641546948816785</v>
+        <v>2.641546948816836</v>
       </c>
       <c r="M2" t="n">
-        <v>2.496834065715542</v>
+        <v>2.496834065715527</v>
       </c>
       <c r="N2" t="n">
-        <v>2.487754795549578</v>
+        <v>2.48775479554957</v>
       </c>
       <c r="O2" t="n">
-        <v>4.977572165007548</v>
+        <v>4.977572165007567</v>
       </c>
       <c r="P2" t="n">
-        <v>2.466270651884447</v>
+        <v>2.466270651884428</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.525463128747153</v>
+        <v>2.525463128747121</v>
       </c>
       <c r="R2" t="n">
-        <v>2.541312075397336</v>
+        <v>2.541312075397372</v>
       </c>
       <c r="S2" t="n">
-        <v>2.569943724849089</v>
+        <v>2.569943724849053</v>
       </c>
       <c r="T2" t="n">
-        <v>2.471517568177283</v>
+        <v>2.471517568177227</v>
       </c>
       <c r="U2" t="n">
-        <v>3.123400692636091</v>
+        <v>3.123400692636087</v>
       </c>
       <c r="V2" t="n">
-        <v>2.473698212007935</v>
+        <v>2.473698212007879</v>
       </c>
       <c r="W2" t="n">
-        <v>3.329357451091864</v>
+        <v>3.329357451091792</v>
       </c>
       <c r="X2" t="n">
-        <v>2.52563986486319</v>
+        <v>2.525639864863225</v>
       </c>
       <c r="Y2" t="n">
         <v>2.460935268609963</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.641404139920504</v>
+        <v>2.64140413992046</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.453475256600063</v>
+        <v>2.453475256600058</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.467498178887833</v>
+        <v>2.467498178887849</v>
       </c>
     </row>
     <row r="3">
@@ -3654,85 +3654,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.458086539990092</v>
+        <v>2.785597395158422</v>
       </c>
       <c r="C3" t="n">
-        <v>4.09772490445943</v>
+        <v>3.173256997502095</v>
       </c>
       <c r="D3" t="n">
-        <v>3.050051396792463</v>
+        <v>2.654594186702729</v>
       </c>
       <c r="E3" t="n">
-        <v>6.9868000758824</v>
+        <v>4.021514669554906</v>
       </c>
       <c r="F3" t="n">
-        <v>5.176269196395161</v>
+        <v>3.389412965929338</v>
       </c>
       <c r="G3" t="n">
-        <v>3.917847201874958</v>
+        <v>2.933084304563409</v>
       </c>
       <c r="H3" t="n">
-        <v>3.549621894819195</v>
+        <v>2.833302164306922</v>
       </c>
       <c r="I3" t="n">
-        <v>4.98031797042403</v>
+        <v>3.328995444359479</v>
       </c>
       <c r="J3" t="n">
-        <v>4.058224752733827</v>
+        <v>2.987746320487961</v>
       </c>
       <c r="K3" t="n">
-        <v>5.157272476044549</v>
+        <v>3.359989089371243</v>
       </c>
       <c r="L3" t="n">
-        <v>7.473867249720646</v>
+        <v>4.109252182281318</v>
       </c>
       <c r="M3" t="n">
-        <v>4.172089312008344</v>
+        <v>3.029865838823612</v>
       </c>
       <c r="N3" t="n">
-        <v>3.926446685933669</v>
+        <v>2.95257214942778</v>
       </c>
       <c r="O3" t="n">
-        <v>5.568318697011366</v>
+        <v>5.172560997163067</v>
       </c>
       <c r="P3" t="n">
-        <v>3.416834587539062</v>
+        <v>2.773532718159319</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.805519791239112</v>
+        <v>3.249611027867083</v>
       </c>
       <c r="R3" t="n">
-        <v>5.192086153152606</v>
+        <v>3.410218992156521</v>
       </c>
       <c r="S3" t="n">
-        <v>5.807634898395369</v>
+        <v>3.539351060980469</v>
       </c>
       <c r="T3" t="n">
-        <v>3.55313321418399</v>
+        <v>2.825818461495508</v>
       </c>
       <c r="U3" t="n">
-        <v>3.956405539863564</v>
+        <v>3.395966906426079</v>
       </c>
       <c r="V3" t="n">
-        <v>3.589347384891963</v>
+        <v>2.828439255251096</v>
       </c>
       <c r="W3" t="n">
-        <v>4.444839987453291</v>
+        <v>3.694648791834535</v>
       </c>
       <c r="X3" t="n">
-        <v>4.814146677697583</v>
+        <v>3.264302159779056</v>
       </c>
       <c r="Y3" t="n">
-        <v>3.301936188590516</v>
+        <v>2.738931320028489</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.961323048549291</v>
+        <v>3.056413320161019</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.128384072729194</v>
+        <v>2.679663223995701</v>
       </c>
       <c r="AB3" t="n">
-        <v>3.482930211762829</v>
+        <v>2.807923394417997</v>
       </c>
     </row>
     <row r="4">
@@ -3742,85 +3742,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9.971222434939046</v>
+        <v>9.97122243493904</v>
       </c>
       <c r="C4" t="n">
-        <v>14.38981424628215</v>
+        <v>14.38981424628219</v>
       </c>
       <c r="D4" t="n">
-        <v>7.070960615451747</v>
+        <v>7.070960615451827</v>
       </c>
       <c r="E4" t="n">
-        <v>43.01055115187626</v>
+        <v>43.01055115187622</v>
       </c>
       <c r="F4" t="n">
-        <v>27.11826126545103</v>
+        <v>27.11826126545104</v>
       </c>
       <c r="G4" t="n">
         <v>13.34610066741704</v>
       </c>
       <c r="H4" t="n">
-        <v>12.2804998147098</v>
+        <v>12.28049981470977</v>
       </c>
       <c r="I4" t="n">
-        <v>25.73759401277866</v>
+        <v>25.73759401277875</v>
       </c>
       <c r="J4" t="n">
         <v>15.19748427978878</v>
       </c>
       <c r="K4" t="n">
-        <v>25.03477541581864</v>
+        <v>25.03477541581865</v>
       </c>
       <c r="L4" t="n">
-        <v>42.38374831756393</v>
+        <v>42.38374831756392</v>
       </c>
       <c r="M4" t="n">
-        <v>16.77038196867709</v>
+        <v>16.77038196867712</v>
       </c>
       <c r="N4" t="n">
-        <v>14.83775949594703</v>
+        <v>14.83775949594707</v>
       </c>
       <c r="O4" t="n">
-        <v>6.39853418540438</v>
+        <v>6.39853418540441</v>
       </c>
       <c r="P4" t="n">
-        <v>9.736589397038403</v>
+        <v>9.736589397038424</v>
       </c>
       <c r="Q4" t="n">
-        <v>22.55855417740201</v>
+        <v>22.55855417740197</v>
       </c>
       <c r="R4" t="n">
-        <v>28.39013248581423</v>
+        <v>28.39013248581425</v>
       </c>
       <c r="S4" t="n">
-        <v>27.28933094307293</v>
+        <v>27.28933094307295</v>
       </c>
       <c r="T4" t="n">
-        <v>11.58876435060948</v>
+        <v>11.58876435060949</v>
       </c>
       <c r="U4" t="n">
-        <v>8.845975399369651</v>
+        <v>8.845975399369697</v>
       </c>
       <c r="V4" t="n">
-        <v>10.98939585068676</v>
+        <v>10.98939585068668</v>
       </c>
       <c r="W4" t="n">
-        <v>11.85925730441437</v>
+        <v>11.85925730441447</v>
       </c>
       <c r="X4" t="n">
-        <v>23.55965378434558</v>
+        <v>23.55965378434567</v>
       </c>
       <c r="Y4" t="n">
-        <v>9.171543082142636</v>
+        <v>9.171543082142678</v>
       </c>
       <c r="Z4" t="n">
-        <v>12.64445335571963</v>
+        <v>12.64445335571962</v>
       </c>
       <c r="AA4" t="n">
-        <v>7.60669524796023</v>
+        <v>7.606695247960222</v>
       </c>
       <c r="AB4" t="n">
-        <v>11.45998585602307</v>
+        <v>11.45998585602308</v>
       </c>
     </row>
     <row r="5">
@@ -3830,85 +3830,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.96740748571616</v>
+        <v>4.967407485716119</v>
       </c>
       <c r="C5" t="n">
-        <v>7.161287166008752</v>
+        <v>7.161287166008747</v>
       </c>
       <c r="D5" t="n">
-        <v>6.771304772870491</v>
+        <v>6.771304772870492</v>
       </c>
       <c r="E5" t="n">
-        <v>7.620918763271233</v>
+        <v>7.620918763271212</v>
       </c>
       <c r="F5" t="n">
-        <v>6.100569470214156</v>
+        <v>6.100569470214175</v>
       </c>
       <c r="G5" t="n">
-        <v>7.617227120149332</v>
+        <v>7.617227120149354</v>
       </c>
       <c r="H5" t="n">
-        <v>7.010038843889427</v>
+        <v>7.01003884388936</v>
       </c>
       <c r="I5" t="n">
-        <v>7.70341646671306</v>
+        <v>7.703416466712966</v>
       </c>
       <c r="J5" t="n">
-        <v>7.264914356704947</v>
+        <v>7.264914356704893</v>
       </c>
       <c r="K5" t="n">
-        <v>7.794292838493848</v>
+        <v>7.794292838493823</v>
       </c>
       <c r="L5" t="n">
-        <v>8.935309859660485</v>
+        <v>8.935309859660503</v>
       </c>
       <c r="M5" t="n">
-        <v>7.313353336489278</v>
+        <v>7.313353336489305</v>
       </c>
       <c r="N5" t="n">
-        <v>14.83775949594703</v>
+        <v>5.641817956332193</v>
       </c>
       <c r="O5" t="n">
-        <v>5.641925880388097</v>
+        <v>5.641925880388091</v>
       </c>
       <c r="P5" t="n">
-        <v>5.722001600307697</v>
+        <v>5.722001600307678</v>
       </c>
       <c r="Q5" t="n">
-        <v>5.221776192860441</v>
+        <v>5.221776192860462</v>
       </c>
       <c r="R5" t="n">
-        <v>7.803110854067843</v>
+        <v>7.803110854067884</v>
       </c>
       <c r="S5" t="n">
-        <v>8.12651850583404</v>
+        <v>8.126518505834007</v>
       </c>
       <c r="T5" t="n">
-        <v>7.014749787956682</v>
+        <v>7.014749787956661</v>
       </c>
       <c r="U5" t="n">
-        <v>5.910579358061399</v>
+        <v>5.910579358061361</v>
       </c>
       <c r="V5" t="n">
-        <v>6.482667335833532</v>
+        <v>6.482667335833521</v>
       </c>
       <c r="W5" t="n">
-        <v>7.035774883940167</v>
+        <v>7.035774883940142</v>
       </c>
       <c r="X5" t="n">
-        <v>5.407786385810713</v>
+        <v>5.407786385810666</v>
       </c>
       <c r="Y5" t="n">
-        <v>8.887767238234382</v>
+        <v>8.887767238234401</v>
       </c>
       <c r="Z5" t="n">
-        <v>5.098970045945689</v>
+        <v>5.098970045945697</v>
       </c>
       <c r="AA5" t="n">
-        <v>6.810953578819238</v>
+        <v>6.810953578819245</v>
       </c>
       <c r="AB5" t="n">
-        <v>9.078410333779596</v>
+        <v>9.078410333779511</v>
       </c>
     </row>
     <row r="6">
@@ -3918,19 +3918,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>86.81732714828409</v>
+        <v>86.81732714828404</v>
       </c>
       <c r="C6" t="n">
-        <v>110.5133497795434</v>
+        <v>110.5133497795433</v>
       </c>
       <c r="D6" t="n">
         <v>110.1233673864052</v>
       </c>
       <c r="E6" t="n">
-        <v>106.6160608102511</v>
+        <v>106.616060810251</v>
       </c>
       <c r="F6" t="n">
-        <v>56.95088388550233</v>
+        <v>56.9508838855024</v>
       </c>
       <c r="G6" t="n">
         <v>110.5529712250616</v>
@@ -3939,22 +3939,22 @@
         <v>110.3621014574241</v>
       </c>
       <c r="I6" t="n">
-        <v>111.0554790802477</v>
+        <v>111.0554790802476</v>
       </c>
       <c r="J6" t="n">
         <v>110.6169769702396</v>
       </c>
       <c r="K6" t="n">
-        <v>111.1463554520283</v>
+        <v>111.1463554520284</v>
       </c>
       <c r="L6" t="n">
         <v>112.2873724731952</v>
       </c>
       <c r="M6" t="n">
-        <v>110.6654159500402</v>
+        <v>110.6654159500401</v>
       </c>
       <c r="N6" t="n">
-        <v>14.83775949594703</v>
+        <v>110.5502193541553</v>
       </c>
       <c r="O6" t="n">
         <v>117.9137790205118</v>
@@ -3963,25 +3963,25 @@
         <v>119.7931339131294</v>
       </c>
       <c r="Q6" t="n">
-        <v>110.9761529594479</v>
+        <v>110.9761529594481</v>
       </c>
       <c r="R6" t="n">
-        <v>111.1551734676022</v>
+        <v>111.1551734676023</v>
       </c>
       <c r="S6" t="n">
-        <v>111.4785811193687</v>
+        <v>111.4785811193688</v>
       </c>
       <c r="T6" t="n">
-        <v>110.3668124014912</v>
+        <v>110.3668124014913</v>
       </c>
       <c r="U6" t="n">
         <v>110.2447624421554</v>
       </c>
       <c r="V6" t="n">
-        <v>137.5157801946277</v>
+        <v>137.5157801946278</v>
       </c>
       <c r="W6" t="n">
-        <v>110.3874429226911</v>
+        <v>110.387442922691</v>
       </c>
       <c r="X6" t="n">
         <v>110.9781486400459</v>
@@ -3990,13 +3990,13 @@
         <v>110.2472804597806</v>
       </c>
       <c r="Z6" t="n">
-        <v>96.32170123043903</v>
+        <v>96.32170123043913</v>
       </c>
       <c r="AA6" t="n">
-        <v>110.1630161923537</v>
+        <v>110.1630161923538</v>
       </c>
       <c r="AB6" t="n">
-        <v>110.3332147141035</v>
+        <v>110.3332147141034</v>
       </c>
     </row>
   </sheetData>
@@ -4162,85 +4162,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.032053663854784</v>
+        <v>3.03205366385478</v>
       </c>
       <c r="C2" t="n">
-        <v>3.230147467090329</v>
+        <v>3.230147467090318</v>
       </c>
       <c r="D2" t="n">
-        <v>2.831832061046186</v>
+        <v>2.831832061046182</v>
       </c>
       <c r="E2" t="n">
         <v>3.210938212272278</v>
       </c>
       <c r="F2" t="n">
-        <v>3.068833602710842</v>
+        <v>3.068833602710845</v>
       </c>
       <c r="G2" t="n">
-        <v>2.860855207287277</v>
+        <v>2.860855207287273</v>
       </c>
       <c r="H2" t="n">
-        <v>2.869460709605483</v>
+        <v>2.86946070960548</v>
       </c>
       <c r="I2" t="n">
         <v>2.995834342311716</v>
       </c>
       <c r="J2" t="n">
-        <v>2.915214904270049</v>
+        <v>2.915214904270051</v>
       </c>
       <c r="K2" t="n">
-        <v>2.916828394301783</v>
+        <v>2.916828394301779</v>
       </c>
       <c r="L2" t="n">
-        <v>2.997122340267318</v>
+        <v>2.997122340267316</v>
       </c>
       <c r="M2" t="n">
-        <v>2.855942416981291</v>
+        <v>2.855942416981294</v>
       </c>
       <c r="N2" t="n">
-        <v>2.939978342837275</v>
+        <v>2.939978342837274</v>
       </c>
       <c r="O2" t="n">
-        <v>5.780571281669885</v>
+        <v>5.78057128166989</v>
       </c>
       <c r="P2" t="n">
-        <v>2.854575872635599</v>
+        <v>2.854575872635602</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.929802497627133</v>
+        <v>2.929802497627132</v>
       </c>
       <c r="R2" t="n">
-        <v>3.087931873729718</v>
+        <v>3.087931873729716</v>
       </c>
       <c r="S2" t="n">
-        <v>2.958272348504186</v>
+        <v>2.958272348504183</v>
       </c>
       <c r="T2" t="n">
-        <v>2.888675618010109</v>
+        <v>2.888675618010108</v>
       </c>
       <c r="U2" t="n">
-        <v>3.883195011566138</v>
+        <v>3.88319501156613</v>
       </c>
       <c r="V2" t="n">
-        <v>2.895274731583907</v>
+        <v>2.895274731583905</v>
       </c>
       <c r="W2" t="n">
-        <v>4.193108661498729</v>
+        <v>4.193108661498716</v>
       </c>
       <c r="X2" t="n">
-        <v>2.917861077988706</v>
+        <v>2.917861077988702</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.862968468789649</v>
+        <v>2.862968468789646</v>
       </c>
       <c r="Z2" t="n">
         <v>3.458539673838071</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.847015085160673</v>
+        <v>2.847015085160671</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.855687367121357</v>
+        <v>2.855687367121356</v>
       </c>
     </row>
     <row r="3">
@@ -4250,85 +4250,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8.008344906006988</v>
+        <v>4.588823187970422</v>
       </c>
       <c r="C3" t="n">
-        <v>5.935384302754167</v>
+        <v>4.098298765409547</v>
       </c>
       <c r="D3" t="n">
-        <v>3.404888246212755</v>
+        <v>3.039131083211717</v>
       </c>
       <c r="E3" t="n">
-        <v>12.1262115843208</v>
+        <v>6.007745696573136</v>
       </c>
       <c r="F3" t="n">
-        <v>8.956181610643759</v>
+        <v>4.93978119784909</v>
       </c>
       <c r="G3" t="n">
-        <v>4.06602007915367</v>
+        <v>3.249641806632932</v>
       </c>
       <c r="H3" t="n">
-        <v>4.291293998866816</v>
+        <v>3.352959689093778</v>
       </c>
       <c r="I3" t="n">
-        <v>7.238147367821987</v>
+        <v>4.363221331971237</v>
       </c>
       <c r="J3" t="n">
-        <v>5.331067396443386</v>
+        <v>3.680274583225039</v>
       </c>
       <c r="K3" t="n">
-        <v>5.381886907754541</v>
+        <v>3.696190203494706</v>
       </c>
       <c r="L3" t="n">
-        <v>7.215941666811356</v>
+        <v>4.251911768337185</v>
       </c>
       <c r="M3" t="n">
-        <v>4.037957220608316</v>
+        <v>3.244468745358278</v>
       </c>
       <c r="N3" t="n">
-        <v>5.916321009963286</v>
+        <v>3.891911376838411</v>
       </c>
       <c r="O3" t="n">
-        <v>8.728096207448381</v>
+        <v>6.698284930114145</v>
       </c>
       <c r="P3" t="n">
-        <v>3.920484741431428</v>
+        <v>3.208637301070097</v>
       </c>
       <c r="Q3" t="n">
-        <v>5.680075632816448</v>
+        <v>3.786675661356466</v>
       </c>
       <c r="R3" t="n">
-        <v>9.403128301596128</v>
+        <v>5.126417440665378</v>
       </c>
       <c r="S3" t="n">
-        <v>6.312809161722368</v>
+        <v>3.979412830922284</v>
       </c>
       <c r="T3" t="n">
-        <v>4.731047942797308</v>
+        <v>3.488868708840562</v>
       </c>
       <c r="U3" t="n">
-        <v>4.749488388663621</v>
+        <v>4.172819307693318</v>
       </c>
       <c r="V3" t="n">
-        <v>4.859110950211183</v>
+        <v>3.515361864691777</v>
       </c>
       <c r="W3" t="n">
-        <v>6.644914098806439</v>
+        <v>4.976948652167986</v>
       </c>
       <c r="X3" t="n">
-        <v>5.40838462077938</v>
+        <v>3.716497112585555</v>
       </c>
       <c r="Y3" t="n">
-        <v>4.125599676353276</v>
+        <v>3.286985874231521</v>
       </c>
       <c r="Z3" t="n">
-        <v>7.202146107568701</v>
+        <v>4.613415190827754</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.754570873904295</v>
+        <v>3.158879958556813</v>
       </c>
       <c r="AB3" t="n">
-        <v>4.021628636247571</v>
+        <v>3.251827415757631</v>
       </c>
     </row>
     <row r="4">
@@ -4338,85 +4338,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>42.91153549279133</v>
+        <v>42.91153549279144</v>
       </c>
       <c r="C4" t="n">
-        <v>24.86531174285749</v>
+        <v>24.8653117428575</v>
       </c>
       <c r="D4" t="n">
-        <v>6.333052560447052</v>
+        <v>6.333052560447123</v>
       </c>
       <c r="E4" t="n">
-        <v>81.08260982382382</v>
+        <v>81.08260982382401</v>
       </c>
       <c r="F4" t="n">
-        <v>53.98974470963307</v>
+        <v>53.98974470963313</v>
       </c>
       <c r="G4" t="n">
-        <v>10.68245834417816</v>
+        <v>10.68245834417827</v>
       </c>
       <c r="H4" t="n">
-        <v>14.71359836316715</v>
+        <v>14.71359836316723</v>
       </c>
       <c r="I4" t="n">
-        <v>39.92728023492218</v>
+        <v>39.92728023492216</v>
       </c>
       <c r="J4" t="n">
-        <v>21.26304469108331</v>
+        <v>21.26304469108339</v>
       </c>
       <c r="K4" t="n">
-        <v>21.77134287618566</v>
+        <v>21.77134287618574</v>
       </c>
       <c r="L4" t="n">
-        <v>31.97970509031282</v>
+        <v>31.97970509031281</v>
       </c>
       <c r="M4" t="n">
-        <v>11.14600215505909</v>
+        <v>11.14600215505916</v>
       </c>
       <c r="N4" t="n">
-        <v>27.12432858592441</v>
+        <v>27.12432858592453</v>
       </c>
       <c r="O4" t="n">
-        <v>24.79616063589717</v>
+        <v>24.79616063589715</v>
       </c>
       <c r="P4" t="n">
-        <v>10.05461522028177</v>
+        <v>10.05461522028186</v>
       </c>
       <c r="Q4" t="n">
-        <v>23.46505776786233</v>
+        <v>23.46505776786234</v>
       </c>
       <c r="R4" t="n">
-        <v>60.11135078813269</v>
+        <v>60.11135078813266</v>
       </c>
       <c r="S4" t="n">
-        <v>26.81832839512393</v>
+        <v>26.81832839512396</v>
       </c>
       <c r="T4" t="n">
-        <v>17.35422057248863</v>
+        <v>17.35422057248875</v>
       </c>
       <c r="U4" t="n">
-        <v>8.219726926187038</v>
+        <v>8.21972692618715</v>
       </c>
       <c r="V4" t="n">
-        <v>16.91433200394363</v>
+        <v>16.9143320039437</v>
       </c>
       <c r="W4" t="n">
-        <v>22.12444257817192</v>
+        <v>22.12444257817204</v>
       </c>
       <c r="X4" t="n">
-        <v>22.79470768326996</v>
+        <v>22.79470768327017</v>
       </c>
       <c r="Y4" t="n">
-        <v>12.48147890085057</v>
+        <v>12.4814789008506</v>
       </c>
       <c r="Z4" t="n">
         <v>31.0121366731477</v>
       </c>
       <c r="AA4" t="n">
-        <v>9.258121185129564</v>
+        <v>9.258121185129838</v>
       </c>
       <c r="AB4" t="n">
-        <v>11.84096257599786</v>
+        <v>11.84096257599789</v>
       </c>
     </row>
     <row r="5">
@@ -4426,85 +4426,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7.36082324635508</v>
+        <v>7.360823246355136</v>
       </c>
       <c r="C5" t="n">
-        <v>8.316457651546219</v>
+        <v>8.316457651546193</v>
       </c>
       <c r="D5" t="n">
-        <v>7.236015387971171</v>
+        <v>7.236015387971113</v>
       </c>
       <c r="E5" t="n">
-        <v>10.38041758483421</v>
+        <v>10.38041758483425</v>
       </c>
       <c r="F5" t="n">
-        <v>8.109156055189366</v>
+        <v>8.109156055189359</v>
       </c>
       <c r="G5" t="n">
-        <v>8.006921932102182</v>
+        <v>8.006921932102198</v>
       </c>
       <c r="H5" t="n">
-        <v>7.661048283481997</v>
+        <v>7.661048283481936</v>
       </c>
       <c r="I5" t="n">
-        <v>9.088496599642054</v>
+        <v>9.088496599642042</v>
       </c>
       <c r="J5" t="n">
-        <v>8.176749797956669</v>
+        <v>8.176749797956695</v>
       </c>
       <c r="K5" t="n">
-        <v>8.196088072338252</v>
+        <v>8.196088072338142</v>
       </c>
       <c r="L5" t="n">
-        <v>9.103045129058978</v>
+        <v>9.103045129058897</v>
       </c>
       <c r="M5" t="n">
-        <v>7.543097694955048</v>
+        <v>7.543097694955079</v>
       </c>
       <c r="N5" t="n">
-        <v>27.12432858592441</v>
+        <v>6.801209791812036</v>
       </c>
       <c r="O5" t="n">
-        <v>7.258308693697078</v>
+        <v>7.258308693697096</v>
       </c>
       <c r="P5" t="n">
-        <v>6.180157153643724</v>
+        <v>6.180157153643779</v>
       </c>
       <c r="Q5" t="n">
-        <v>5.785921823295334</v>
+        <v>5.785921823295274</v>
       </c>
       <c r="R5" t="n">
-        <v>10.12878058396596</v>
+        <v>10.12878058396598</v>
       </c>
       <c r="S5" t="n">
-        <v>8.664216600215108</v>
+        <v>8.664216600215143</v>
       </c>
       <c r="T5" t="n">
-        <v>7.878089513206811</v>
+        <v>7.878089513206768</v>
       </c>
       <c r="U5" t="n">
-        <v>6.330402752089975</v>
+        <v>6.330402752089997</v>
       </c>
       <c r="V5" t="n">
-        <v>7.345490991971402</v>
+        <v>7.34549099197145</v>
       </c>
       <c r="W5" t="n">
-        <v>8.195221413010048</v>
+        <v>8.195221413010083</v>
       </c>
       <c r="X5" t="n">
-        <v>5.846878788019307</v>
+        <v>5.846878788019377</v>
       </c>
       <c r="Y5" t="n">
-        <v>9.686727664837532</v>
+        <v>9.686727664837635</v>
       </c>
       <c r="Z5" t="n">
-        <v>6.688780906445682</v>
+        <v>6.688780906445659</v>
       </c>
       <c r="AA5" t="n">
-        <v>7.407514629880429</v>
+        <v>7.407514629880431</v>
       </c>
       <c r="AB5" t="n">
-        <v>9.768054880806096</v>
+        <v>9.768054880806121</v>
       </c>
     </row>
     <row r="6">
@@ -4514,85 +4514,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>83.52986685770955</v>
+        <v>83.52986685770964</v>
       </c>
       <c r="C6" t="n">
-        <v>104.3436927403424</v>
+        <v>104.3436927403425</v>
       </c>
       <c r="D6" t="n">
-        <v>103.2632504767672</v>
+        <v>103.2632504767674</v>
       </c>
       <c r="E6" t="n">
-        <v>102.4690784175718</v>
+        <v>102.4690784175719</v>
       </c>
       <c r="F6" t="n">
-        <v>55.23586135051892</v>
+        <v>55.235861350519</v>
       </c>
       <c r="G6" t="n">
-        <v>103.5910814870295</v>
+        <v>103.5910814870296</v>
       </c>
       <c r="H6" t="n">
-        <v>103.6882833722781</v>
+        <v>103.6882833722783</v>
       </c>
       <c r="I6" t="n">
-        <v>105.1157316884383</v>
+        <v>105.1157316884384</v>
       </c>
       <c r="J6" t="n">
-        <v>104.203984886753</v>
+        <v>104.2039848867531</v>
       </c>
       <c r="K6" t="n">
         <v>104.2233231611345</v>
       </c>
       <c r="L6" t="n">
-        <v>105.1302802178551</v>
+        <v>105.1302802178552</v>
       </c>
       <c r="M6" t="n">
-        <v>103.5703327837501</v>
+        <v>103.5703327837502</v>
       </c>
       <c r="N6" t="n">
-        <v>27.12432858592441</v>
+        <v>104.4848124793454</v>
       </c>
       <c r="O6" t="n">
         <v>111.7758359651136</v>
       </c>
       <c r="P6" t="n">
-        <v>112.3945169028242</v>
+        <v>112.3945169028243</v>
       </c>
       <c r="Q6" t="n">
-        <v>104.3698728487387</v>
+        <v>104.3698728487389</v>
       </c>
       <c r="R6" t="n">
-        <v>106.1560156727622</v>
+        <v>106.1560156727624</v>
       </c>
       <c r="S6" t="n">
         <v>104.6914516890116</v>
       </c>
       <c r="T6" t="n">
-        <v>103.9053246020029</v>
+        <v>103.9053246020031</v>
       </c>
       <c r="U6" t="n">
-        <v>103.4155085808341</v>
+        <v>103.4155085808343</v>
       </c>
       <c r="V6" t="n">
-        <v>129.3549534938587</v>
+        <v>129.3549534938589</v>
       </c>
       <c r="W6" t="n">
-        <v>104.2220365693999</v>
+        <v>104.2220365694</v>
       </c>
       <c r="X6" t="n">
-        <v>104.2349877984362</v>
+        <v>104.2349877984363</v>
       </c>
       <c r="Y6" t="n">
-        <v>103.6149505256852</v>
+        <v>103.6149505256851</v>
       </c>
       <c r="Z6" t="n">
         <v>91.63147934795279</v>
       </c>
       <c r="AA6" t="n">
-        <v>103.4347497186766</v>
+        <v>103.4347497186768</v>
       </c>
       <c r="AB6" t="n">
-        <v>103.5632370170011</v>
+        <v>103.5632370170012</v>
       </c>
     </row>
   </sheetData>
@@ -4758,85 +4758,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.289717205110781</v>
+        <v>3.289717205110759</v>
       </c>
       <c r="C2" t="n">
-        <v>3.452833086364672</v>
+        <v>3.452833086364665</v>
       </c>
       <c r="D2" t="n">
-        <v>3.071776491331266</v>
+        <v>3.071776491331241</v>
       </c>
       <c r="E2" t="n">
-        <v>3.320744564775205</v>
+        <v>3.320744564775183</v>
       </c>
       <c r="F2" t="n">
-        <v>3.147561436439791</v>
+        <v>3.147561436439775</v>
       </c>
       <c r="G2" t="n">
-        <v>3.011139727644736</v>
+        <v>3.011139727644716</v>
       </c>
       <c r="H2" t="n">
-        <v>2.984352829577851</v>
+        <v>2.984352829577828</v>
       </c>
       <c r="I2" t="n">
-        <v>3.041401879416993</v>
+        <v>3.041401879416975</v>
       </c>
       <c r="J2" t="n">
-        <v>3.049464253972532</v>
+        <v>3.049464253972553</v>
       </c>
       <c r="K2" t="n">
-        <v>3.012644953319946</v>
+        <v>3.012644953319924</v>
       </c>
       <c r="L2" t="n">
-        <v>3.102428559899563</v>
+        <v>3.102428559899537</v>
       </c>
       <c r="M2" t="n">
-        <v>2.978473653760986</v>
+        <v>2.978473653760979</v>
       </c>
       <c r="N2" t="n">
-        <v>3.037322726020575</v>
+        <v>3.037322726020564</v>
       </c>
       <c r="O2" t="n">
-        <v>6.043936008986233</v>
+        <v>6.043936008986205</v>
       </c>
       <c r="P2" t="n">
-        <v>3.008163221724052</v>
+        <v>3.008163221724062</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.081611066061636</v>
+        <v>3.081611066061613</v>
       </c>
       <c r="R2" t="n">
-        <v>3.272028140796392</v>
+        <v>3.272028140796363</v>
       </c>
       <c r="S2" t="n">
-        <v>3.07735810181115</v>
+        <v>3.077358101811114</v>
       </c>
       <c r="T2" t="n">
-        <v>2.994955834638801</v>
+        <v>2.994955834638787</v>
       </c>
       <c r="U2" t="n">
         <v>4.194003425772697</v>
       </c>
       <c r="V2" t="n">
-        <v>3.042384385776157</v>
+        <v>3.042384385776161</v>
       </c>
       <c r="W2" t="n">
-        <v>4.545934196652235</v>
+        <v>4.545934196652238</v>
       </c>
       <c r="X2" t="n">
-        <v>3.050905523920088</v>
+        <v>3.050905523920066</v>
       </c>
       <c r="Y2" t="n">
-        <v>3.016254973668942</v>
+        <v>3.016254973668929</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.65049938928389</v>
+        <v>3.650499389283868</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.988111646959978</v>
+        <v>2.988111646959947</v>
       </c>
       <c r="AB2" t="n">
-        <v>3.009527721494167</v>
+        <v>3.009527721494159</v>
       </c>
     </row>
     <row r="3">
@@ -4846,85 +4846,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>11.00076421616085</v>
+        <v>5.689433104848465</v>
       </c>
       <c r="C3" t="n">
-        <v>7.216124895777975</v>
+        <v>4.665549898751836</v>
       </c>
       <c r="D3" t="n">
-        <v>6.022299484131875</v>
+        <v>4.034250928011147</v>
       </c>
       <c r="E3" t="n">
-        <v>11.66337846601929</v>
+        <v>5.859287804034495</v>
       </c>
       <c r="F3" t="n">
-        <v>7.810312178261738</v>
+        <v>4.661361910866312</v>
       </c>
       <c r="G3" t="n">
-        <v>4.587842471894658</v>
+        <v>3.527620750153194</v>
       </c>
       <c r="H3" t="n">
-        <v>3.988883160330287</v>
+        <v>3.344002668140144</v>
       </c>
       <c r="I3" t="n">
-        <v>5.318390681127191</v>
+        <v>3.8022502371047</v>
       </c>
       <c r="J3" t="n">
-        <v>5.484092406721985</v>
+        <v>3.83578371225264</v>
       </c>
       <c r="K3" t="n">
-        <v>4.640634178065714</v>
+        <v>3.556072386129177</v>
       </c>
       <c r="L3" t="n">
-        <v>6.703382976615654</v>
+        <v>4.214990427218665</v>
       </c>
       <c r="M3" t="n">
-        <v>3.922052499575067</v>
+        <v>3.312763292892853</v>
       </c>
       <c r="N3" t="n">
-        <v>5.211559517332503</v>
+        <v>3.756832286258492</v>
       </c>
       <c r="O3" t="n">
-        <v>9.041458745635149</v>
+        <v>6.990071537522246</v>
       </c>
       <c r="P3" t="n">
-        <v>4.516687121330082</v>
+        <v>3.505704216832665</v>
       </c>
       <c r="Q3" t="n">
-        <v>6.243103932181698</v>
+        <v>4.094098574593619</v>
       </c>
       <c r="R3" t="n">
-        <v>10.72400672756869</v>
+        <v>5.695508638238766</v>
       </c>
       <c r="S3" t="n">
-        <v>6.118209631811309</v>
+        <v>4.036809504439058</v>
       </c>
       <c r="T3" t="n">
-        <v>4.231327622357562</v>
+        <v>3.422820092451728</v>
       </c>
       <c r="U3" t="n">
-        <v>5.119258433708418</v>
+        <v>4.514704160106137</v>
       </c>
       <c r="V3" t="n">
-        <v>5.308099274828567</v>
+        <v>3.769954096931474</v>
       </c>
       <c r="W3" t="n">
-        <v>7.495555914987873</v>
+        <v>5.500376587540105</v>
       </c>
       <c r="X3" t="n">
-        <v>5.531926897397694</v>
+        <v>3.853993321699015</v>
       </c>
       <c r="Y3" t="n">
-        <v>4.720131551060167</v>
+        <v>3.592662297149758</v>
       </c>
       <c r="Z3" t="n">
-        <v>7.172751901191312</v>
+        <v>4.742663983812142</v>
       </c>
       <c r="AA3" t="n">
-        <v>4.065674587831221</v>
+        <v>3.365014856936215</v>
       </c>
       <c r="AB3" t="n">
-        <v>4.627905974216962</v>
+        <v>3.566710718887575</v>
       </c>
     </row>
     <row r="4">
@@ -4934,85 +4934,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>65.11182915584183</v>
+        <v>65.11182915584176</v>
       </c>
       <c r="C4" t="n">
-        <v>34.32422296420152</v>
+        <v>34.32422296420155</v>
       </c>
       <c r="D4" t="n">
-        <v>27.40299803876713</v>
+        <v>27.40299803876709</v>
       </c>
       <c r="E4" t="n">
-        <v>71.89584881445388</v>
+        <v>71.89584881445386</v>
       </c>
       <c r="F4" t="n">
-        <v>43.94032344743574</v>
+        <v>43.94032344743578</v>
       </c>
       <c r="G4" t="n">
-        <v>13.8454311004566</v>
+        <v>13.84543110045696</v>
       </c>
       <c r="H4" t="n">
-        <v>10.54101739316688</v>
+        <v>10.54101739316687</v>
       </c>
       <c r="I4" t="n">
-        <v>22.0732534158841</v>
+        <v>22.07325341588407</v>
       </c>
       <c r="J4" t="n">
-        <v>21.60854095645576</v>
+        <v>21.60854095645569</v>
       </c>
       <c r="K4" t="n">
-        <v>15.23712862669239</v>
+        <v>15.23712862669233</v>
       </c>
       <c r="L4" t="n">
-        <v>29.18966246128466</v>
+        <v>29.18966246128469</v>
       </c>
       <c r="M4" t="n">
-        <v>9.534501493285788</v>
+        <v>9.534501493285791</v>
       </c>
       <c r="N4" t="n">
-        <v>20.40478683821671</v>
+        <v>20.4047868382167</v>
       </c>
       <c r="O4" t="n">
-        <v>25.23063903783618</v>
+        <v>25.23063903783616</v>
       </c>
       <c r="P4" t="n">
-        <v>13.38222417616195</v>
+        <v>13.38222417616192</v>
       </c>
       <c r="Q4" t="n">
-        <v>28.09933153881805</v>
+        <v>28.09933153881807</v>
       </c>
       <c r="R4" t="n">
-        <v>71.42199535956276</v>
+        <v>71.42199535956256</v>
       </c>
       <c r="S4" t="n">
-        <v>25.70361853201445</v>
+        <v>25.70361853201449</v>
       </c>
       <c r="T4" t="n">
-        <v>12.25881342984606</v>
+        <v>12.258813429846</v>
       </c>
       <c r="U4" t="n">
-        <v>8.724416309908136</v>
+        <v>8.72441630990817</v>
       </c>
       <c r="V4" t="n">
-        <v>19.57793099534464</v>
+        <v>19.5779309953446</v>
       </c>
       <c r="W4" t="n">
-        <v>26.66388433238845</v>
+        <v>26.66388433238844</v>
       </c>
       <c r="X4" t="n">
-        <v>22.33095704427163</v>
+        <v>22.33095704427156</v>
       </c>
       <c r="Y4" t="n">
-        <v>16.49125321305127</v>
+        <v>16.49125321305135</v>
       </c>
       <c r="Z4" t="n">
-        <v>28.63134284440377</v>
+        <v>28.63134284440384</v>
       </c>
       <c r="AA4" t="n">
-        <v>10.6919946103679</v>
+        <v>10.69199461036791</v>
       </c>
       <c r="AB4" t="n">
-        <v>16.33113218792016</v>
+        <v>16.33113218792014</v>
       </c>
     </row>
     <row r="5">
@@ -5022,85 +5022,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8.988928278444684</v>
+        <v>8.988928278444725</v>
       </c>
       <c r="C5" t="n">
-        <v>9.187148725604615</v>
+        <v>9.187148725604629</v>
       </c>
       <c r="D5" t="n">
-        <v>8.773921212453189</v>
+        <v>8.773921212453152</v>
       </c>
       <c r="E5" t="n">
-        <v>10.38981079197588</v>
+        <v>10.38981079197593</v>
       </c>
       <c r="F5" t="n">
-        <v>7.733228305000733</v>
+        <v>7.733228305000742</v>
       </c>
       <c r="G5" t="n">
-        <v>8.554875910190223</v>
+        <v>8.554875910190264</v>
       </c>
       <c r="H5" t="n">
-        <v>7.786430736077001</v>
+        <v>7.786430736077</v>
       </c>
       <c r="I5" t="n">
-        <v>8.430825997869707</v>
+        <v>8.430825997869764</v>
       </c>
       <c r="J5" t="n">
-        <v>8.52080095414359</v>
+        <v>8.520800954143589</v>
       </c>
       <c r="K5" t="n">
-        <v>8.106003288763945</v>
+        <v>8.106003288763928</v>
       </c>
       <c r="L5" t="n">
-        <v>9.120150427580265</v>
+        <v>9.120150427580215</v>
       </c>
       <c r="M5" t="n">
-        <v>7.757219039541289</v>
+        <v>7.757219039541281</v>
       </c>
       <c r="N5" t="n">
-        <v>20.40478683821671</v>
+        <v>6.643155706989568</v>
       </c>
       <c r="O5" t="n">
-        <v>7.556868766053175</v>
+        <v>7.55686876605317</v>
       </c>
       <c r="P5" t="n">
-        <v>6.6750732325009</v>
+        <v>6.67507323250078</v>
       </c>
       <c r="Q5" t="n">
-        <v>6.196739284325878</v>
+        <v>6.196739284325941</v>
       </c>
       <c r="R5" t="n">
-        <v>11.0358557134717</v>
+        <v>11.03585571347175</v>
       </c>
       <c r="S5" t="n">
-        <v>8.836968070491025</v>
+        <v>8.836968070490977</v>
       </c>
       <c r="T5" t="n">
-        <v>7.906196555863885</v>
+        <v>7.906196555863874</v>
       </c>
       <c r="U5" t="n">
-        <v>6.635087757327246</v>
+        <v>6.635087757327168</v>
       </c>
       <c r="V5" t="n">
-        <v>7.797733835660489</v>
+        <v>7.797733835660476</v>
       </c>
       <c r="W5" t="n">
-        <v>8.783358774093404</v>
+        <v>8.783358774093257</v>
       </c>
       <c r="X5" t="n">
-        <v>6.055823649621646</v>
+        <v>6.055823649621639</v>
       </c>
       <c r="Y5" t="n">
-        <v>10.34394574749275</v>
+        <v>10.34394574749263</v>
       </c>
       <c r="Z5" t="n">
-        <v>6.798626793109003</v>
+        <v>6.798626793109017</v>
       </c>
       <c r="AA5" t="n">
-        <v>7.828888307549501</v>
+        <v>7.828888307549366</v>
       </c>
       <c r="AB5" t="n">
-        <v>10.44623933999178</v>
+        <v>10.44623933999181</v>
       </c>
     </row>
     <row r="6">
@@ -5110,58 +5110,58 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>85.00767314614959</v>
+        <v>85.00767314614946</v>
       </c>
       <c r="C6" t="n">
-        <v>104.9604273252747</v>
+        <v>104.9604273252745</v>
       </c>
       <c r="D6" t="n">
-        <v>104.5471998121235</v>
+        <v>104.5471998121232</v>
       </c>
       <c r="E6" t="n">
-        <v>102.2816069876304</v>
+        <v>102.2816069876303</v>
       </c>
       <c r="F6" t="n">
-        <v>54.68429811860022</v>
+        <v>54.68429811860021</v>
       </c>
       <c r="G6" t="n">
-        <v>103.8622809759569</v>
+        <v>103.8622809759568</v>
       </c>
       <c r="H6" t="n">
         <v>103.559709335747</v>
       </c>
       <c r="I6" t="n">
-        <v>104.2041045975398</v>
+        <v>104.2041045975396</v>
       </c>
       <c r="J6" t="n">
-        <v>104.2940795538136</v>
+        <v>104.2940795538137</v>
       </c>
       <c r="K6" t="n">
         <v>103.8792818884341</v>
       </c>
       <c r="L6" t="n">
-        <v>104.8934290272505</v>
+        <v>104.8934290272504</v>
       </c>
       <c r="M6" t="n">
-        <v>103.5304976391994</v>
+        <v>103.5304976391993</v>
       </c>
       <c r="N6" t="n">
-        <v>20.40478683821671</v>
+        <v>104.1580286834241</v>
       </c>
       <c r="O6" t="n">
-        <v>111.8843293968027</v>
+        <v>111.8843293968026</v>
       </c>
       <c r="P6" t="n">
-        <v>112.7055606525112</v>
+        <v>112.7055606525111</v>
       </c>
       <c r="Q6" t="n">
-        <v>104.6582871617931</v>
+        <v>104.658287161793</v>
       </c>
       <c r="R6" t="n">
-        <v>106.8091343131419</v>
+        <v>106.8091343131417</v>
       </c>
       <c r="S6" t="n">
-        <v>104.6102466701611</v>
+        <v>104.610246670161</v>
       </c>
       <c r="T6" t="n">
         <v>103.6794751555338</v>
@@ -5179,16 +5179,16 @@
         <v>104.3114526340947</v>
       </c>
       <c r="Y6" t="n">
-        <v>103.9200587289675</v>
+        <v>103.9200587289674</v>
       </c>
       <c r="Z6" t="n">
-        <v>91.59556594846055</v>
+        <v>91.59556594846049</v>
       </c>
       <c r="AA6" t="n">
-        <v>103.6021669072197</v>
+        <v>103.6021669072196</v>
       </c>
       <c r="AB6" t="n">
-        <v>103.8726168824138</v>
+        <v>103.8726168824136</v>
       </c>
     </row>
   </sheetData>
@@ -5354,85 +5354,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.296974047046354</v>
+        <v>2.29697404704634</v>
       </c>
       <c r="C2" t="n">
-        <v>2.348894663363266</v>
+        <v>2.348894663363313</v>
       </c>
       <c r="D2" t="n">
-        <v>2.262336912219024</v>
+        <v>2.262336912219027</v>
       </c>
       <c r="E2" t="n">
-        <v>2.350843158358754</v>
+        <v>2.350843158358733</v>
       </c>
       <c r="F2" t="n">
-        <v>2.333742958719907</v>
+        <v>2.333742958719894</v>
       </c>
       <c r="G2" t="n">
-        <v>2.367977575825389</v>
+        <v>2.367977575825379</v>
       </c>
       <c r="H2" t="n">
-        <v>2.267355694162637</v>
+        <v>2.267355694162645</v>
       </c>
       <c r="I2" t="n">
-        <v>2.364311013827886</v>
+        <v>2.364311013827876</v>
       </c>
       <c r="J2" t="n">
-        <v>2.328580766836534</v>
+        <v>2.328580766836498</v>
       </c>
       <c r="K2" t="n">
-        <v>2.371923535264068</v>
+        <v>2.371923535264038</v>
       </c>
       <c r="L2" t="n">
-        <v>2.324545505482343</v>
+        <v>2.324545505482351</v>
       </c>
       <c r="M2" t="n">
-        <v>2.391976740341229</v>
+        <v>2.391976740341211</v>
       </c>
       <c r="N2" t="n">
-        <v>2.299583070746568</v>
+        <v>2.299583070746607</v>
       </c>
       <c r="O2" t="n">
-        <v>4.245885709121361</v>
+        <v>4.245885709121347</v>
       </c>
       <c r="P2" t="n">
-        <v>2.297933541402513</v>
+        <v>2.297933541402533</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.333936224417918</v>
+        <v>2.333936224417936</v>
       </c>
       <c r="R2" t="n">
-        <v>2.334870188047439</v>
+        <v>2.334870188047393</v>
       </c>
       <c r="S2" t="n">
-        <v>2.355348922853039</v>
+        <v>2.355348922852998</v>
       </c>
       <c r="T2" t="n">
-        <v>2.294379641524242</v>
+        <v>2.294379641524262</v>
       </c>
       <c r="U2" t="n">
-        <v>2.677755071062318</v>
+        <v>2.677755071062313</v>
       </c>
       <c r="V2" t="n">
-        <v>2.287220301859935</v>
+        <v>2.287220301859914</v>
       </c>
       <c r="W2" t="n">
-        <v>2.801052559733568</v>
+        <v>2.801052559733532</v>
       </c>
       <c r="X2" t="n">
-        <v>2.336793714404096</v>
+        <v>2.336793714404104</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.293661830048268</v>
+        <v>2.293661830048228</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.217088971164566</v>
+        <v>2.217088971164579</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.280756173812279</v>
+        <v>2.280756173812267</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.345661968121438</v>
+        <v>2.34566196812144</v>
       </c>
     </row>
     <row r="3">
@@ -5442,85 +5442,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.524208178965106</v>
+        <v>2.661085415773461</v>
       </c>
       <c r="C3" t="n">
-        <v>3.50110651248649</v>
+        <v>2.700232305129886</v>
       </c>
       <c r="D3" t="n">
-        <v>2.732945174707914</v>
+        <v>2.400098590564847</v>
       </c>
       <c r="E3" t="n">
-        <v>4.840710061444338</v>
+        <v>3.173073833485024</v>
       </c>
       <c r="F3" t="n">
-        <v>4.407666331888235</v>
+        <v>2.98094503515303</v>
       </c>
       <c r="G3" t="n">
-        <v>5.159494563422944</v>
+        <v>3.207215184819939</v>
       </c>
       <c r="H3" t="n">
-        <v>2.853459889967716</v>
+        <v>2.444615256363269</v>
       </c>
       <c r="I3" t="n">
-        <v>5.117857518666098</v>
+        <v>3.232926853007128</v>
       </c>
       <c r="J3" t="n">
-        <v>4.261482578633082</v>
+        <v>2.912656526034994</v>
       </c>
       <c r="K3" t="n">
-        <v>5.282974969746079</v>
+        <v>3.253914391657523</v>
       </c>
       <c r="L3" t="n">
-        <v>4.169293985297891</v>
+        <v>2.88577222668035</v>
       </c>
       <c r="M3" t="n">
-        <v>5.763468891178212</v>
+        <v>3.427310257271114</v>
       </c>
       <c r="N3" t="n">
-        <v>3.597643756194074</v>
+        <v>2.698580290042759</v>
       </c>
       <c r="O3" t="n">
-        <v>5.079388948179722</v>
+        <v>4.488032639546115</v>
       </c>
       <c r="P3" t="n">
-        <v>3.5448026936076</v>
+        <v>2.67140977099712</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.398702800558048</v>
+        <v>2.97056971012914</v>
       </c>
       <c r="R3" t="n">
-        <v>4.433812988846792</v>
+        <v>2.999783293566413</v>
       </c>
       <c r="S3" t="n">
-        <v>4.872953341304942</v>
+        <v>3.104746331877594</v>
       </c>
       <c r="T3" t="n">
-        <v>3.48162090066891</v>
+        <v>2.661529776216129</v>
       </c>
       <c r="U3" t="n">
-        <v>3.764614071467386</v>
+        <v>3.004406068439432</v>
       </c>
       <c r="V3" t="n">
-        <v>3.299811707546595</v>
+        <v>2.584282219882159</v>
       </c>
       <c r="W3" t="n">
-        <v>3.542623348431743</v>
+        <v>3.022274816510594</v>
       </c>
       <c r="X3" t="n">
-        <v>4.469027573682415</v>
+        <v>3.002406105715203</v>
       </c>
       <c r="Y3" t="n">
-        <v>3.457871035553237</v>
+        <v>2.646842083674286</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.970177591560462</v>
+        <v>2.436581084967448</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.15779063883629</v>
+        <v>2.544621174115338</v>
       </c>
       <c r="AB3" t="n">
-        <v>4.679111292953519</v>
+        <v>3.093847190683104</v>
       </c>
     </row>
     <row r="4">
@@ -5530,85 +5530,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>12.25166952336326</v>
+        <v>12.25166952336334</v>
       </c>
       <c r="C4" t="n">
-        <v>12.4996606537708</v>
+        <v>12.49966065377087</v>
       </c>
       <c r="D4" t="n">
-        <v>6.00006006837621</v>
+        <v>6.000060068376199</v>
       </c>
       <c r="E4" t="n">
-        <v>24.70831037029449</v>
+        <v>24.70831037029464</v>
       </c>
       <c r="F4" t="n">
-        <v>21.94635106933217</v>
+        <v>21.94635106933218</v>
       </c>
       <c r="G4" t="n">
-        <v>25.858700006303</v>
+        <v>25.85870000630266</v>
       </c>
       <c r="H4" t="n">
-        <v>7.386143088670275</v>
+        <v>7.386143088670023</v>
       </c>
       <c r="I4" t="n">
-        <v>29.02723807378223</v>
+        <v>29.02723807378229</v>
       </c>
       <c r="J4" t="n">
-        <v>18.91116043633937</v>
+        <v>18.91116043633923</v>
       </c>
       <c r="K4" t="n">
-        <v>27.7563843935336</v>
+        <v>27.75638439353326</v>
       </c>
       <c r="L4" t="n">
-        <v>18.44137290719106</v>
+        <v>18.44137290719161</v>
       </c>
       <c r="M4" t="n">
-        <v>32.99561224001829</v>
+        <v>32.99561224001792</v>
       </c>
       <c r="N4" t="n">
-        <v>14.00383852928711</v>
+        <v>14.00383852928707</v>
       </c>
       <c r="O4" t="n">
-        <v>8.644814835465382</v>
+        <v>8.644814835465368</v>
       </c>
       <c r="P4" t="n">
-        <v>12.65329723047193</v>
+        <v>12.65329723047185</v>
       </c>
       <c r="Q4" t="n">
-        <v>21.13823707174777</v>
+        <v>21.13823707174762</v>
       </c>
       <c r="R4" t="n">
-        <v>22.90549902930865</v>
+        <v>22.90549902930846</v>
       </c>
       <c r="S4" t="n">
-        <v>23.04137269386015</v>
+        <v>23.04137269386014</v>
       </c>
       <c r="T4" t="n">
-        <v>13.21767314571185</v>
+        <v>13.21767314571192</v>
       </c>
       <c r="U4" t="n">
-        <v>11.4724758901878</v>
+        <v>11.47247589019173</v>
       </c>
       <c r="V4" t="n">
-        <v>10.2447526028864</v>
+        <v>10.24475260288591</v>
       </c>
       <c r="W4" t="n">
-        <v>8.431178319390803</v>
+        <v>8.431178319391043</v>
       </c>
       <c r="X4" t="n">
-        <v>22.39914241025919</v>
+        <v>22.3991424102589</v>
       </c>
       <c r="Y4" t="n">
-        <v>12.42180600694493</v>
+        <v>12.42180600694497</v>
       </c>
       <c r="Z4" t="n">
-        <v>8.094324325905601</v>
+        <v>8.094324325905598</v>
       </c>
       <c r="AA4" t="n">
-        <v>9.737170070372882</v>
+        <v>9.737170070372922</v>
       </c>
       <c r="AB4" t="n">
-        <v>25.80252544859551</v>
+        <v>25.80252544859533</v>
       </c>
     </row>
     <row r="5">
@@ -5618,85 +5618,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.604381100905806</v>
+        <v>4.604381100905857</v>
       </c>
       <c r="C5" t="n">
-        <v>6.346762708136782</v>
+        <v>6.34676270813681</v>
       </c>
       <c r="D5" t="n">
-        <v>6.001280896877213</v>
+        <v>6.001280896877185</v>
       </c>
       <c r="E5" t="n">
-        <v>6.048866705234067</v>
+        <v>6.048866705234058</v>
       </c>
       <c r="F5" t="n">
-        <v>5.298274523713603</v>
+        <v>5.298274523713575</v>
       </c>
       <c r="G5" t="n">
-        <v>7.565323716430175</v>
+        <v>7.565323716430163</v>
       </c>
       <c r="H5" t="n">
-        <v>6.057970347684044</v>
+        <v>6.057970347684057</v>
       </c>
       <c r="I5" t="n">
-        <v>7.153125284953553</v>
+        <v>7.153125284953463</v>
       </c>
       <c r="J5" t="n">
-        <v>6.748444773462099</v>
+        <v>6.748444773462075</v>
       </c>
       <c r="K5" t="n">
-        <v>7.239112216507817</v>
+        <v>7.239112216507758</v>
       </c>
       <c r="L5" t="n">
-        <v>6.703955575152939</v>
+        <v>6.703955575153058</v>
       </c>
       <c r="M5" t="n">
-        <v>7.464475175146222</v>
+        <v>7.464475175146263</v>
       </c>
       <c r="N5" t="n">
-        <v>14.00383852928711</v>
+        <v>5.035884061144744</v>
       </c>
       <c r="O5" t="n">
-        <v>5.185820845724415</v>
+        <v>5.185820845724399</v>
       </c>
       <c r="P5" t="n">
-        <v>5.304795305593876</v>
+        <v>5.304795305593921</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.670475150290824</v>
+        <v>4.670475150290839</v>
       </c>
       <c r="R5" t="n">
-        <v>6.820577614313672</v>
+        <v>6.820577614313795</v>
       </c>
       <c r="S5" t="n">
-        <v>7.05189434462677</v>
+        <v>7.051894344626691</v>
       </c>
       <c r="T5" t="n">
-        <v>6.363218264763507</v>
+        <v>6.363218264763454</v>
       </c>
       <c r="U5" t="n">
-        <v>5.432668721585812</v>
+        <v>5.432668721586042</v>
       </c>
       <c r="V5" t="n">
-        <v>5.773222033094324</v>
+        <v>5.773222033094318</v>
       </c>
       <c r="W5" t="n">
-        <v>6.141017760451651</v>
+        <v>6.141017760451656</v>
       </c>
       <c r="X5" t="n">
-        <v>4.866638595096385</v>
+        <v>4.866638595096565</v>
       </c>
       <c r="Y5" t="n">
-        <v>8.111850460820285</v>
+        <v>8.111850460820222</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.327580949092266</v>
+        <v>4.32758094909221</v>
       </c>
       <c r="AA5" t="n">
         <v>6.209334929851672</v>
       </c>
       <c r="AB5" t="n">
-        <v>8.809674417793843</v>
+        <v>8.809674417793866</v>
       </c>
     </row>
     <row r="6">
@@ -5706,49 +5706,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>86.65696519725402</v>
+        <v>86.65696519725411</v>
       </c>
       <c r="C6" t="n">
-        <v>110.0815582769805</v>
+        <v>110.0815582769806</v>
       </c>
       <c r="D6" t="n">
-        <v>109.7360764657208</v>
+        <v>109.7360764657209</v>
       </c>
       <c r="E6" t="n">
         <v>105.318933566583</v>
       </c>
       <c r="F6" t="n">
-        <v>56.43706942443469</v>
+        <v>56.43706942443485</v>
       </c>
       <c r="G6" t="n">
-        <v>110.9293366470819</v>
+        <v>110.9293366470818</v>
       </c>
       <c r="H6" t="n">
-        <v>109.7927659165279</v>
+        <v>109.7927659165281</v>
       </c>
       <c r="I6" t="n">
-        <v>110.8879208537973</v>
+        <v>110.8879208537974</v>
       </c>
       <c r="J6" t="n">
-        <v>110.4832403423059</v>
+        <v>110.483240342306</v>
       </c>
       <c r="K6" t="n">
-        <v>110.9739077853518</v>
+        <v>110.9739077853517</v>
       </c>
       <c r="L6" t="n">
-        <v>110.4387511439974</v>
+        <v>110.4387511439972</v>
       </c>
       <c r="M6" t="n">
-        <v>111.1992707439983</v>
+        <v>111.1992707439984</v>
       </c>
       <c r="N6" t="n">
-        <v>14.00383852928711</v>
+        <v>110.1567889603694</v>
       </c>
       <c r="O6" t="n">
-        <v>117.7038557162718</v>
+        <v>117.7038557162719</v>
       </c>
       <c r="P6" t="n">
-        <v>119.6077928597866</v>
+        <v>119.6077928597867</v>
       </c>
       <c r="Q6" t="n">
         <v>110.544823923139</v>
@@ -5760,28 +5760,28 @@
         <v>110.7866899134706</v>
       </c>
       <c r="T6" t="n">
-        <v>110.0980138336076</v>
+        <v>110.0980138336074</v>
       </c>
       <c r="U6" t="n">
-        <v>110.052606930968</v>
+        <v>110.0526069309683</v>
       </c>
       <c r="V6" t="n">
         <v>137.0946825765068</v>
       </c>
       <c r="W6" t="n">
-        <v>109.8754619111942</v>
+        <v>109.8754619111943</v>
       </c>
       <c r="X6" t="n">
         <v>110.5771002982225</v>
       </c>
       <c r="Y6" t="n">
-        <v>110.0899058227761</v>
+        <v>110.0899058227762</v>
       </c>
       <c r="Z6" t="n">
-        <v>95.7331982790873</v>
+        <v>95.73319827908735</v>
       </c>
       <c r="AA6" t="n">
-        <v>109.9441304986956</v>
+        <v>109.9441304986957</v>
       </c>
       <c r="AB6" t="n">
         <v>110.6766059733571</v>
@@ -5950,85 +5950,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.685194862619011</v>
+        <v>2.685194862619021</v>
       </c>
       <c r="C2" t="n">
-        <v>2.973924393219727</v>
+        <v>2.973924393219726</v>
       </c>
       <c r="D2" t="n">
-        <v>2.63676508967943</v>
+        <v>2.636765089679428</v>
       </c>
       <c r="E2" t="n">
-        <v>2.773495957116592</v>
+        <v>2.773495957116591</v>
       </c>
       <c r="F2" t="n">
-        <v>2.77816684732028</v>
+        <v>2.778166847320283</v>
       </c>
       <c r="G2" t="n">
-        <v>2.686852345035739</v>
+        <v>2.686852345035743</v>
       </c>
       <c r="H2" t="n">
-        <v>2.595027360888654</v>
+        <v>2.595027360888661</v>
       </c>
       <c r="I2" t="n">
-        <v>2.71892351697795</v>
+        <v>2.718923516977947</v>
       </c>
       <c r="J2" t="n">
-        <v>2.670821355591099</v>
+        <v>2.670821355591101</v>
       </c>
       <c r="K2" t="n">
-        <v>2.705800576556019</v>
+        <v>2.705800576556023</v>
       </c>
       <c r="L2" t="n">
-        <v>2.789994437735349</v>
+        <v>2.789994437735351</v>
       </c>
       <c r="M2" t="n">
-        <v>2.637816505163726</v>
+        <v>2.637816505163722</v>
       </c>
       <c r="N2" t="n">
-        <v>2.634621703553862</v>
+        <v>2.634621703553867</v>
       </c>
       <c r="O2" t="n">
-        <v>5.158742267825038</v>
+        <v>5.158742267825061</v>
       </c>
       <c r="P2" t="n">
-        <v>2.628421504678214</v>
+        <v>2.628421504678215</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.720820988170413</v>
+        <v>2.720820988170412</v>
       </c>
       <c r="R2" t="n">
-        <v>2.787486030753163</v>
+        <v>2.78748603075316</v>
       </c>
       <c r="S2" t="n">
-        <v>2.736733996487071</v>
+        <v>2.736733996487079</v>
       </c>
       <c r="T2" t="n">
-        <v>2.665857743226747</v>
+        <v>2.665857743226748</v>
       </c>
       <c r="U2" t="n">
-        <v>3.400841047859711</v>
+        <v>3.400841047859704</v>
       </c>
       <c r="V2" t="n">
-        <v>2.623853867053727</v>
+        <v>2.623853867053734</v>
       </c>
       <c r="W2" t="n">
-        <v>3.658524646153365</v>
+        <v>3.65852464615337</v>
       </c>
       <c r="X2" t="n">
-        <v>2.67657489256569</v>
+        <v>2.676574892565697</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.67229155038638</v>
+        <v>2.672291550386384</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.827436974069596</v>
+        <v>2.827436974069594</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.621688924945451</v>
+        <v>2.621688924945454</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.674363403205632</v>
+        <v>2.674363403205644</v>
       </c>
     </row>
     <row r="3">
@@ -6038,85 +6038,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.243070051830728</v>
+        <v>3.485396392471998</v>
       </c>
       <c r="C3" t="n">
-        <v>6.125952433929981</v>
+        <v>3.967401860720049</v>
       </c>
       <c r="D3" t="n">
-        <v>4.147794841120525</v>
+        <v>3.127547515182063</v>
       </c>
       <c r="E3" t="n">
-        <v>7.284788403513936</v>
+        <v>4.202753153248501</v>
       </c>
       <c r="F3" t="n">
-        <v>7.46502785035176</v>
+        <v>4.267031197283156</v>
       </c>
       <c r="G3" t="n">
-        <v>5.280088372809751</v>
+        <v>3.480986660440421</v>
       </c>
       <c r="H3" t="n">
-        <v>3.177169449228342</v>
+        <v>2.796097958272037</v>
       </c>
       <c r="I3" t="n">
-        <v>6.071780848514746</v>
+        <v>3.805442647414515</v>
       </c>
       <c r="J3" t="n">
-        <v>4.923935831978881</v>
+        <v>3.375876773686056</v>
       </c>
       <c r="K3" t="n">
-        <v>5.750275883591653</v>
+        <v>3.645226700192975</v>
       </c>
       <c r="L3" t="n">
-        <v>7.67820428972011</v>
+        <v>4.287535473761682</v>
       </c>
       <c r="M3" t="n">
-        <v>4.215131099143459</v>
+        <v>3.14010215698277</v>
       </c>
       <c r="N3" t="n">
-        <v>4.093161771964357</v>
+        <v>3.110001120202293</v>
       </c>
       <c r="O3" t="n">
-        <v>5.891160878364319</v>
+        <v>5.395699455203269</v>
       </c>
       <c r="P3" t="n">
-        <v>3.933796038560765</v>
+        <v>3.042489450860496</v>
       </c>
       <c r="Q3" t="n">
-        <v>6.097456872237239</v>
+        <v>3.766544133474373</v>
       </c>
       <c r="R3" t="n">
-        <v>7.684377223082214</v>
+        <v>4.377843712951352</v>
       </c>
       <c r="S3" t="n">
-        <v>6.435792211229582</v>
+        <v>3.865053951162438</v>
       </c>
       <c r="T3" t="n">
-        <v>4.828338403812897</v>
+        <v>3.366996438785035</v>
       </c>
       <c r="U3" t="n">
-        <v>4.301577054645687</v>
+        <v>3.691289323642417</v>
       </c>
       <c r="V3" t="n">
-        <v>3.830569689748411</v>
+        <v>3.004133405404632</v>
       </c>
       <c r="W3" t="n">
-        <v>5.658186294259246</v>
+        <v>4.30230136137899</v>
       </c>
       <c r="X3" t="n">
-        <v>5.074203971456577</v>
+        <v>3.442633585626246</v>
       </c>
       <c r="Y3" t="n">
-        <v>4.965264468686768</v>
+        <v>3.405375353377732</v>
       </c>
       <c r="Z3" t="n">
-        <v>4.302066364754892</v>
+        <v>3.287147279310231</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.789807556861085</v>
+        <v>3.002824182915568</v>
       </c>
       <c r="AB3" t="n">
-        <v>5.04490151558991</v>
+        <v>3.452694476706222</v>
       </c>
     </row>
     <row r="4">
@@ -6126,85 +6126,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>22.67458405196268</v>
+        <v>22.67458405196266</v>
       </c>
       <c r="C4" t="n">
-        <v>28.79747250653989</v>
+        <v>28.79747250653995</v>
       </c>
       <c r="D4" t="n">
-        <v>14.95659854188482</v>
+        <v>14.95659854188479</v>
       </c>
       <c r="E4" t="n">
-        <v>41.85709505105167</v>
+        <v>41.85709505105186</v>
       </c>
       <c r="F4" t="n">
-        <v>43.75684489003846</v>
+        <v>43.75684489003857</v>
       </c>
       <c r="G4" t="n">
-        <v>21.80466959560284</v>
+        <v>21.80466959560294</v>
       </c>
       <c r="H4" t="n">
-        <v>6.775860663193045</v>
+        <v>6.775860663193098</v>
       </c>
       <c r="I4" t="n">
-        <v>32.77359667797541</v>
+        <v>32.7735966779755</v>
       </c>
       <c r="J4" t="n">
-        <v>20.14777453098132</v>
+        <v>20.14777453098138</v>
       </c>
       <c r="K4" t="n">
-        <v>26.41111987369256</v>
+        <v>26.41111987369261</v>
       </c>
       <c r="L4" t="n">
-        <v>41.16808887255242</v>
+        <v>41.16808887255246</v>
       </c>
       <c r="M4" t="n">
-        <v>14.95444018436244</v>
+        <v>14.95444018436255</v>
       </c>
       <c r="N4" t="n">
-        <v>14.50806095784716</v>
+        <v>14.50806095784715</v>
       </c>
       <c r="O4" t="n">
-        <v>7.21301932895606</v>
+        <v>7.213019328956142</v>
       </c>
       <c r="P4" t="n">
-        <v>12.07112091087379</v>
+        <v>12.071120910874</v>
       </c>
       <c r="Q4" t="n">
-        <v>29.49718959351142</v>
+        <v>29.49718959351132</v>
       </c>
       <c r="R4" t="n">
-        <v>48.08697007599771</v>
+        <v>48.08697007599764</v>
       </c>
       <c r="S4" t="n">
         <v>30.76693874323562</v>
       </c>
       <c r="T4" t="n">
-        <v>21.22617416031666</v>
+        <v>21.22617416031665</v>
       </c>
       <c r="U4" t="n">
-        <v>8.791831754516286</v>
+        <v>8.791831754516384</v>
       </c>
       <c r="V4" t="n">
-        <v>11.02069640650691</v>
+        <v>11.0206964065069</v>
       </c>
       <c r="W4" t="n">
-        <v>19.18713962009832</v>
+        <v>19.1871396200983</v>
       </c>
       <c r="X4" t="n">
-        <v>22.68674298699453</v>
+        <v>22.6867429869945</v>
       </c>
       <c r="Y4" t="n">
-        <v>21.64057702138259</v>
+        <v>21.64057702138253</v>
       </c>
       <c r="Z4" t="n">
         <v>13.08190210273063</v>
       </c>
       <c r="AA4" t="n">
-        <v>11.67233931446248</v>
+        <v>11.67233931446255</v>
       </c>
       <c r="AB4" t="n">
-        <v>23.90812806423034</v>
+        <v>23.90812806423047</v>
       </c>
     </row>
     <row r="5">
@@ -6214,82 +6214,82 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.68740030342162</v>
+        <v>5.687400303421691</v>
       </c>
       <c r="C5" t="n">
-        <v>7.920570245628289</v>
+        <v>7.920570245628275</v>
       </c>
       <c r="D5" t="n">
-        <v>7.088139544459701</v>
+        <v>7.088139544459821</v>
       </c>
       <c r="E5" t="n">
-        <v>7.595444432292239</v>
+        <v>7.595444432292276</v>
       </c>
       <c r="F5" t="n">
-        <v>7.041002345504747</v>
+        <v>7.041002345504705</v>
       </c>
       <c r="G5" t="n">
-        <v>8.057782136388941</v>
+        <v>8.057782136388978</v>
       </c>
       <c r="H5" t="n">
-        <v>6.616692697464294</v>
+        <v>6.616692697464244</v>
       </c>
       <c r="I5" t="n">
-        <v>8.016156775540429</v>
+        <v>8.016156775540409</v>
       </c>
       <c r="J5" t="n">
-        <v>7.471490919116984</v>
+        <v>7.471490919117136</v>
       </c>
       <c r="K5" t="n">
-        <v>7.867927126623969</v>
+        <v>7.867927126623955</v>
       </c>
       <c r="L5" t="n">
-        <v>8.818935519734126</v>
+        <v>8.818935519734094</v>
       </c>
       <c r="M5" t="n">
-        <v>7.119971745514903</v>
+        <v>7.119971745514883</v>
       </c>
       <c r="N5" t="n">
-        <v>14.50806095784716</v>
+        <v>5.554076905911562</v>
       </c>
       <c r="O5" t="n">
-        <v>5.604457608106025</v>
+        <v>5.604457608105985</v>
       </c>
       <c r="P5" t="n">
-        <v>5.797256241280968</v>
+        <v>5.797256241281099</v>
       </c>
       <c r="Q5" t="n">
-        <v>5.707031380485045</v>
+        <v>5.707031380485114</v>
       </c>
       <c r="R5" t="n">
-        <v>8.790601908945964</v>
+        <v>8.790601908946039</v>
       </c>
       <c r="S5" t="n">
-        <v>8.217334334821455</v>
+        <v>8.217334334821428</v>
       </c>
       <c r="T5" t="n">
-        <v>7.416754449558661</v>
+        <v>7.416754449558631</v>
       </c>
       <c r="U5" t="n">
-        <v>5.818124756428217</v>
+        <v>5.818124756428193</v>
       </c>
       <c r="V5" t="n">
-        <v>6.385523244217259</v>
+        <v>6.385523244217291</v>
       </c>
       <c r="W5" t="n">
-        <v>7.341797378720773</v>
+        <v>7.341797378720776</v>
       </c>
       <c r="X5" t="n">
-        <v>5.385768895625993</v>
+        <v>5.385768895625985</v>
       </c>
       <c r="Y5" t="n">
-        <v>9.400954404670443</v>
+        <v>9.400954404670593</v>
       </c>
       <c r="Z5" t="n">
-        <v>5.095515273286334</v>
+        <v>5.095515273286398</v>
       </c>
       <c r="AA5" t="n">
-        <v>6.917847328411166</v>
+        <v>6.917847328411143</v>
       </c>
       <c r="AB5" t="n">
         <v>9.556394825165921</v>
@@ -6302,49 +6302,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>81.93133926328167</v>
+        <v>81.93133926328166</v>
       </c>
       <c r="C6" t="n">
         <v>104.1501573447852</v>
       </c>
       <c r="D6" t="n">
-        <v>103.317726643617</v>
+        <v>103.3177266436169</v>
       </c>
       <c r="E6" t="n">
-        <v>99.80002051783165</v>
+        <v>99.80002051783167</v>
       </c>
       <c r="F6" t="n">
-        <v>54.35239511976601</v>
+        <v>54.35239511976604</v>
       </c>
       <c r="G6" t="n">
         <v>103.8834860255925</v>
       </c>
       <c r="H6" t="n">
-        <v>102.8462797966212</v>
+        <v>102.8462797966213</v>
       </c>
       <c r="I6" t="n">
-        <v>104.2457438746975</v>
+        <v>104.2457438746974</v>
       </c>
       <c r="J6" t="n">
         <v>103.7010780182741</v>
       </c>
       <c r="K6" t="n">
-        <v>104.0975142257809</v>
+        <v>104.0975142257808</v>
       </c>
       <c r="L6" t="n">
-        <v>105.0485226188913</v>
+        <v>105.0485226188912</v>
       </c>
       <c r="M6" t="n">
         <v>103.3495588446879</v>
       </c>
       <c r="N6" t="n">
-        <v>14.50806095784716</v>
+        <v>103.2935161113224</v>
       </c>
       <c r="O6" t="n">
         <v>110.1976853775308</v>
       </c>
       <c r="P6" t="n">
-        <v>112.0730103741142</v>
+        <v>112.0730103741141</v>
       </c>
       <c r="Q6" t="n">
         <v>104.2671774761465</v>
@@ -6353,13 +6353,13 @@
         <v>105.0201890081031</v>
       </c>
       <c r="S6" t="n">
-        <v>104.4469214339785</v>
+        <v>104.4469214339784</v>
       </c>
       <c r="T6" t="n">
-        <v>103.6463415487158</v>
+        <v>103.6463415487157</v>
       </c>
       <c r="U6" t="n">
-        <v>103.0130686827878</v>
+        <v>103.0130686827877</v>
       </c>
       <c r="V6" t="n">
         <v>128.4743579279231</v>
@@ -6368,19 +6368,19 @@
         <v>103.5710016900087</v>
       </c>
       <c r="X6" t="n">
-        <v>103.7673966806315</v>
+        <v>103.7673966806314</v>
       </c>
       <c r="Y6" t="n">
         <v>103.7190143602812</v>
       </c>
       <c r="Z6" t="n">
-        <v>90.08515518454669</v>
+        <v>90.08515518454671</v>
       </c>
       <c r="AA6" t="n">
-        <v>103.1474344275682</v>
+        <v>103.1474344275681</v>
       </c>
       <c r="AB6" t="n">
-        <v>103.7513672310633</v>
+        <v>103.7513672310632</v>
       </c>
     </row>
   </sheetData>

--- a/Results/Phase 2/Ammonia/ammonia land use results.xlsx
+++ b/Results/Phase 2/Ammonia/ammonia land use results.xlsx
@@ -674,85 +674,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.072621053209123</v>
+        <v>2.017713400519353</v>
       </c>
       <c r="C3" t="n">
-        <v>2.081609215572528</v>
+        <v>2.027433477384787</v>
       </c>
       <c r="D3" t="n">
-        <v>1.993041315758438</v>
+        <v>1.958732342202527</v>
       </c>
       <c r="E3" t="n">
-        <v>1.707297153000729</v>
+        <v>1.790301480063536</v>
       </c>
       <c r="F3" t="n">
-        <v>1.905192586650006</v>
+        <v>1.898181296297209</v>
       </c>
       <c r="G3" t="n">
-        <v>2.655100355671532</v>
+        <v>2.429532207825124</v>
       </c>
       <c r="H3" t="n">
-        <v>2.073738261990507</v>
+        <v>2.012418455278357</v>
       </c>
       <c r="I3" t="n">
-        <v>2.13766985255559</v>
+        <v>2.057487558162321</v>
       </c>
       <c r="J3" t="n">
-        <v>2.359893765170397</v>
+        <v>2.21810697368091</v>
       </c>
       <c r="K3" t="n">
-        <v>2.505149685343644</v>
+        <v>2.311670926893081</v>
       </c>
       <c r="L3" t="n">
-        <v>2.002484940818968</v>
+        <v>1.966552435482346</v>
       </c>
       <c r="M3" t="n">
-        <v>2.902636444667987</v>
+        <v>2.581084072129643</v>
       </c>
       <c r="N3" t="n">
-        <v>2.197639941893498</v>
+        <v>2.10120277131263</v>
       </c>
       <c r="O3" t="n">
-        <v>4.048200019511947</v>
+        <v>3.926846785049326</v>
       </c>
       <c r="P3" t="n">
-        <v>2.280974540905717</v>
+        <v>2.165568898399578</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.036514324851906</v>
+        <v>1.989187264055345</v>
       </c>
       <c r="R3" t="n">
-        <v>2.20470585499455</v>
+        <v>2.102493033621832</v>
       </c>
       <c r="S3" t="n">
-        <v>2.37572177598781</v>
+        <v>2.231271906308448</v>
       </c>
       <c r="T3" t="n">
-        <v>2.149240678494027</v>
+        <v>2.06583370205714</v>
       </c>
       <c r="U3" t="n">
-        <v>2.37169204398644</v>
+        <v>2.239419214126677</v>
       </c>
       <c r="V3" t="n">
-        <v>2.278598463461917</v>
+        <v>2.164219942961261</v>
       </c>
       <c r="W3" t="n">
-        <v>2.282141099503435</v>
+        <v>2.204745613458229</v>
       </c>
       <c r="X3" t="n">
-        <v>2.060053962103164</v>
+        <v>2.005150516451681</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.159160156970789</v>
+        <v>2.075382007116321</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.911901351311014</v>
+        <v>1.843664135203383</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.371422625535363</v>
+        <v>2.222956386920679</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.868626140798887</v>
+        <v>2.551300119612881</v>
       </c>
     </row>
     <row r="4">
@@ -1270,85 +1270,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.599777737320917</v>
+        <v>3.359097922808645</v>
       </c>
       <c r="C3" t="n">
-        <v>4.170517019768881</v>
+        <v>3.841745129758328</v>
       </c>
       <c r="D3" t="n">
-        <v>3.524533390321</v>
+        <v>3.291287593091146</v>
       </c>
       <c r="E3" t="n">
-        <v>3.453302540127194</v>
+        <v>3.225909280099835</v>
       </c>
       <c r="F3" t="n">
-        <v>4.363337517766804</v>
+        <v>3.869678322806434</v>
       </c>
       <c r="G3" t="n">
-        <v>3.190166103139096</v>
+        <v>3.066587971265393</v>
       </c>
       <c r="H3" t="n">
-        <v>3.014926830480474</v>
+        <v>2.930495648229835</v>
       </c>
       <c r="I3" t="n">
-        <v>3.644100642460891</v>
+        <v>3.367849910394878</v>
       </c>
       <c r="J3" t="n">
-        <v>3.412795278655226</v>
+        <v>3.219002746244638</v>
       </c>
       <c r="K3" t="n">
-        <v>3.569464100243326</v>
+        <v>3.334802834843978</v>
       </c>
       <c r="L3" t="n">
-        <v>4.16089495244537</v>
+        <v>3.762338395325582</v>
       </c>
       <c r="M3" t="n">
-        <v>3.188366255359542</v>
+        <v>3.053417911812701</v>
       </c>
       <c r="N3" t="n">
-        <v>3.29257302918606</v>
+        <v>3.125965716816395</v>
       </c>
       <c r="O3" t="n">
-        <v>5.781347669386791</v>
+        <v>5.697346206179899</v>
       </c>
       <c r="P3" t="n">
-        <v>3.158351391713428</v>
+        <v>3.043331041743581</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.740143385374397</v>
+        <v>3.449151522820961</v>
       </c>
       <c r="R3" t="n">
-        <v>5.491595897590482</v>
+        <v>4.628034145342871</v>
       </c>
       <c r="S3" t="n">
-        <v>3.878985660162715</v>
+        <v>3.562631622353753</v>
       </c>
       <c r="T3" t="n">
-        <v>3.307461596665085</v>
+        <v>3.134099937795734</v>
       </c>
       <c r="U3" t="n">
-        <v>4.104370397274807</v>
+        <v>4.003536646473574</v>
       </c>
       <c r="V3" t="n">
-        <v>3.332123312939177</v>
+        <v>3.168561979264517</v>
       </c>
       <c r="W3" t="n">
-        <v>4.73320382684487</v>
+        <v>4.507130449745653</v>
       </c>
       <c r="X3" t="n">
-        <v>3.499259477040387</v>
+        <v>3.276087081977743</v>
       </c>
       <c r="Y3" t="n">
-        <v>3.358392368103983</v>
+        <v>3.172911848328221</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.758289497676686</v>
+        <v>3.587414352964592</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.284900608046271</v>
+        <v>3.122373617984495</v>
       </c>
       <c r="AB3" t="n">
-        <v>3.4062870459818</v>
+        <v>3.197573016099884</v>
       </c>
     </row>
     <row r="4">
@@ -1866,85 +1866,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.310246958649935</v>
+        <v>2.254879526278935</v>
       </c>
       <c r="C3" t="n">
-        <v>2.381646076767074</v>
+        <v>2.315130029193705</v>
       </c>
       <c r="D3" t="n">
-        <v>2.398292386136929</v>
+        <v>2.310976662741708</v>
       </c>
       <c r="E3" t="n">
-        <v>2.126732813261405</v>
+        <v>2.14403554116809</v>
       </c>
       <c r="F3" t="n">
-        <v>2.11616603161831</v>
+        <v>2.116640173011408</v>
       </c>
       <c r="G3" t="n">
-        <v>3.098796218562608</v>
+        <v>2.814288418616706</v>
       </c>
       <c r="H3" t="n">
-        <v>2.229579261290259</v>
+        <v>2.193986715107497</v>
       </c>
       <c r="I3" t="n">
-        <v>2.484293334595829</v>
+        <v>2.369173572155105</v>
       </c>
       <c r="J3" t="n">
-        <v>2.716175262304382</v>
+        <v>2.539573985563599</v>
       </c>
       <c r="K3" t="n">
-        <v>2.652881038931255</v>
+        <v>2.493033155588467</v>
       </c>
       <c r="L3" t="n">
-        <v>2.250050911495745</v>
+        <v>2.210589234802415</v>
       </c>
       <c r="M3" t="n">
-        <v>3.057308807657052</v>
+        <v>2.762126836720379</v>
       </c>
       <c r="N3" t="n">
-        <v>2.439368841246363</v>
+        <v>2.341135534030442</v>
       </c>
       <c r="O3" t="n">
-        <v>4.423463372427768</v>
+        <v>4.308113592114604</v>
       </c>
       <c r="P3" t="n">
-        <v>2.605300332088122</v>
+        <v>2.464471440940341</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.340868267357719</v>
+        <v>2.272585395735396</v>
       </c>
       <c r="R3" t="n">
-        <v>2.334882094730485</v>
+        <v>2.266306302723139</v>
       </c>
       <c r="S3" t="n">
-        <v>2.655876706074814</v>
+        <v>2.499343601015704</v>
       </c>
       <c r="T3" t="n">
-        <v>2.419619058003049</v>
+        <v>2.325602461347092</v>
       </c>
       <c r="U3" t="n">
-        <v>2.8728212765994</v>
+        <v>2.731269580334881</v>
       </c>
       <c r="V3" t="n">
-        <v>2.528829340491017</v>
+        <v>2.412571547089764</v>
       </c>
       <c r="W3" t="n">
-        <v>2.869830594204347</v>
+        <v>2.765123880388692</v>
       </c>
       <c r="X3" t="n">
-        <v>2.444299238779087</v>
+        <v>2.343644367858395</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.531543109402734</v>
+        <v>2.407121015751216</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.309686734004697</v>
+        <v>2.214570066287366</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.470592918359408</v>
+        <v>2.364107138190481</v>
       </c>
       <c r="AB3" t="n">
-        <v>3.103075030306191</v>
+        <v>2.785899360533604</v>
       </c>
     </row>
     <row r="4">
@@ -2462,85 +2462,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.698135662515218</v>
+        <v>2.620526764456512</v>
       </c>
       <c r="C3" t="n">
-        <v>2.91042237678143</v>
+        <v>2.81638734546684</v>
       </c>
       <c r="D3" t="n">
-        <v>2.875799159684057</v>
+        <v>2.737343276166856</v>
       </c>
       <c r="E3" t="n">
-        <v>2.585059053932982</v>
+        <v>2.536387953485714</v>
       </c>
       <c r="F3" t="n">
-        <v>2.671887880472695</v>
+        <v>2.596526463920697</v>
       </c>
       <c r="G3" t="n">
-        <v>3.44114859838785</v>
+        <v>3.150795659795592</v>
       </c>
       <c r="H3" t="n">
-        <v>2.539116694304716</v>
+        <v>2.504309090555615</v>
       </c>
       <c r="I3" t="n">
-        <v>3.705329445805729</v>
+        <v>3.304507031053392</v>
       </c>
       <c r="J3" t="n">
-        <v>3.095183388549368</v>
+        <v>2.899329416847219</v>
       </c>
       <c r="K3" t="n">
-        <v>2.966777937279722</v>
+        <v>2.810275596690674</v>
       </c>
       <c r="L3" t="n">
-        <v>2.587791028995821</v>
+        <v>2.540585178134152</v>
       </c>
       <c r="M3" t="n">
-        <v>3.362188086537846</v>
+        <v>3.068692955544275</v>
       </c>
       <c r="N3" t="n">
-        <v>2.809723890274045</v>
+        <v>2.693453837200765</v>
       </c>
       <c r="O3" t="n">
-        <v>5.146690151053741</v>
+        <v>5.032794499847432</v>
       </c>
       <c r="P3" t="n">
-        <v>2.935240036678071</v>
+        <v>2.790189177476361</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.328920684182589</v>
+        <v>3.056765506004586</v>
       </c>
       <c r="R3" t="n">
-        <v>2.601501719442382</v>
+        <v>2.54734698599643</v>
       </c>
       <c r="S3" t="n">
-        <v>2.982234990015366</v>
+        <v>2.822303749849557</v>
       </c>
       <c r="T3" t="n">
-        <v>2.688279442602208</v>
+        <v>2.607708750553734</v>
       </c>
       <c r="U3" t="n">
-        <v>3.418477305160851</v>
+        <v>3.315175392308404</v>
       </c>
       <c r="V3" t="n">
-        <v>2.838989221059754</v>
+        <v>2.723888607185447</v>
       </c>
       <c r="W3" t="n">
-        <v>3.657846493253714</v>
+        <v>3.533873513608115</v>
       </c>
       <c r="X3" t="n">
-        <v>2.847087289778041</v>
+        <v>2.718685470248138</v>
       </c>
       <c r="Y3" t="n">
-        <v>3.135438745868365</v>
+        <v>2.922971942053955</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.96132479865585</v>
+        <v>2.829039442772717</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.769244501349066</v>
+        <v>2.666624084447367</v>
       </c>
       <c r="AB3" t="n">
-        <v>3.379020043746556</v>
+        <v>3.072561395412773</v>
       </c>
     </row>
     <row r="4">
@@ -3058,85 +3058,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.918389732723182</v>
+        <v>2.834775023679825</v>
       </c>
       <c r="C3" t="n">
-        <v>3.038450489693747</v>
+        <v>2.989693335977464</v>
       </c>
       <c r="D3" t="n">
-        <v>3.011447727185588</v>
+        <v>2.893804207897184</v>
       </c>
       <c r="E3" t="n">
-        <v>2.573699707266601</v>
+        <v>2.566135851492259</v>
       </c>
       <c r="F3" t="n">
-        <v>3.053976426804219</v>
+        <v>2.921322721242475</v>
       </c>
       <c r="G3" t="n">
-        <v>3.590078267100523</v>
+        <v>3.318860950951044</v>
       </c>
       <c r="H3" t="n">
-        <v>2.766388496827039</v>
+        <v>2.721229960996341</v>
       </c>
       <c r="I3" t="n">
-        <v>3.52138553843664</v>
+        <v>3.242859698704553</v>
       </c>
       <c r="J3" t="n">
-        <v>3.28185193851108</v>
+        <v>3.090836365954193</v>
       </c>
       <c r="K3" t="n">
-        <v>3.207372430815377</v>
+        <v>3.037640967300475</v>
       </c>
       <c r="L3" t="n">
-        <v>2.88697905815205</v>
+        <v>2.809671347369495</v>
       </c>
       <c r="M3" t="n">
-        <v>3.480881319978208</v>
+        <v>3.218049412489965</v>
       </c>
       <c r="N3" t="n">
-        <v>2.997166724468245</v>
+        <v>2.883081867515059</v>
       </c>
       <c r="O3" t="n">
-        <v>5.597953767159231</v>
+        <v>5.490601456253962</v>
       </c>
       <c r="P3" t="n">
-        <v>3.148603925905383</v>
+        <v>3.001250574523367</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.242731712399811</v>
+        <v>3.058528025316343</v>
       </c>
       <c r="R3" t="n">
-        <v>3.259257812219122</v>
+        <v>3.057884425872245</v>
       </c>
       <c r="S3" t="n">
-        <v>3.229796244446524</v>
+        <v>3.056171603644613</v>
       </c>
       <c r="T3" t="n">
-        <v>3.09639691996668</v>
+        <v>2.949068584320215</v>
       </c>
       <c r="U3" t="n">
-        <v>3.810923842361081</v>
+        <v>3.723393934008016</v>
       </c>
       <c r="V3" t="n">
-        <v>3.097995265407871</v>
+        <v>2.965838946556107</v>
       </c>
       <c r="W3" t="n">
-        <v>4.177340982361105</v>
+        <v>4.039476527908358</v>
       </c>
       <c r="X3" t="n">
-        <v>3.157176372063105</v>
+        <v>2.996272327682565</v>
       </c>
       <c r="Y3" t="n">
-        <v>3.737564519559015</v>
+        <v>3.398480503325669</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.364861470663477</v>
+        <v>3.229724696300479</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.02770662755692</v>
+        <v>2.90558219268033</v>
       </c>
       <c r="AB3" t="n">
-        <v>3.572281107980876</v>
+        <v>3.269084841601675</v>
       </c>
     </row>
     <row r="4">
@@ -3654,85 +3654,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.785597395158422</v>
+        <v>2.68828899288661</v>
       </c>
       <c r="C3" t="n">
-        <v>3.173256997502095</v>
+        <v>3.025499117541907</v>
       </c>
       <c r="D3" t="n">
-        <v>2.654594186702729</v>
+        <v>2.589426128378987</v>
       </c>
       <c r="E3" t="n">
-        <v>4.021514669554906</v>
+        <v>3.550828758217883</v>
       </c>
       <c r="F3" t="n">
-        <v>3.389412965929338</v>
+        <v>3.097496249555556</v>
       </c>
       <c r="G3" t="n">
-        <v>2.933084304563409</v>
+        <v>2.798239407239379</v>
       </c>
       <c r="H3" t="n">
-        <v>2.833302164306922</v>
+        <v>2.708883775756592</v>
       </c>
       <c r="I3" t="n">
-        <v>3.328995444359479</v>
+        <v>3.052437834396988</v>
       </c>
       <c r="J3" t="n">
-        <v>2.987746320487961</v>
+        <v>2.831596485934088</v>
       </c>
       <c r="K3" t="n">
-        <v>3.359989089371243</v>
+        <v>3.092892057279727</v>
       </c>
       <c r="L3" t="n">
-        <v>4.109252182281318</v>
+        <v>3.648961751243867</v>
       </c>
       <c r="M3" t="n">
-        <v>3.029865838823612</v>
+        <v>2.855544967667021</v>
       </c>
       <c r="N3" t="n">
-        <v>2.95257214942778</v>
+        <v>2.799914385270435</v>
       </c>
       <c r="O3" t="n">
-        <v>5.172560997163067</v>
+        <v>5.115399269278121</v>
       </c>
       <c r="P3" t="n">
-        <v>2.773532718159319</v>
+        <v>2.678786606772409</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.249611027867083</v>
+        <v>3.010000958358602</v>
       </c>
       <c r="R3" t="n">
-        <v>3.410218992156521</v>
+        <v>3.103232336759458</v>
       </c>
       <c r="S3" t="n">
-        <v>3.539351060980469</v>
+        <v>3.249340501589856</v>
       </c>
       <c r="T3" t="n">
-        <v>2.825818461495508</v>
+        <v>2.709701480585286</v>
       </c>
       <c r="U3" t="n">
-        <v>3.395966906426079</v>
+        <v>3.311088255464824</v>
       </c>
       <c r="V3" t="n">
-        <v>2.828439255251096</v>
+        <v>2.719693668109442</v>
       </c>
       <c r="W3" t="n">
-        <v>3.694648791834535</v>
+        <v>3.57555353451614</v>
       </c>
       <c r="X3" t="n">
-        <v>3.264302159779056</v>
+        <v>3.012783114077088</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.738931320028489</v>
+        <v>2.650202025389648</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.056413320161019</v>
+        <v>2.929253626125365</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.679663223995701</v>
+        <v>2.608581988976007</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.807923394417997</v>
+        <v>2.692940936811794</v>
       </c>
     </row>
     <row r="4">
@@ -4250,85 +4250,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.588823187970422</v>
+        <v>4.091038093934913</v>
       </c>
       <c r="C3" t="n">
-        <v>4.098298765409547</v>
+        <v>3.816252252698082</v>
       </c>
       <c r="D3" t="n">
-        <v>3.039131083211717</v>
+        <v>2.980328827532111</v>
       </c>
       <c r="E3" t="n">
-        <v>6.007745696573136</v>
+        <v>5.047522246873423</v>
       </c>
       <c r="F3" t="n">
-        <v>4.93978119784909</v>
+        <v>4.305597665193879</v>
       </c>
       <c r="G3" t="n">
-        <v>3.249641806632932</v>
+        <v>3.139395409095937</v>
       </c>
       <c r="H3" t="n">
-        <v>3.352959689093778</v>
+        <v>3.192390231951013</v>
       </c>
       <c r="I3" t="n">
-        <v>4.363221331971237</v>
+        <v>3.898377536952855</v>
       </c>
       <c r="J3" t="n">
-        <v>3.680274583225039</v>
+        <v>3.44252124979815</v>
       </c>
       <c r="K3" t="n">
-        <v>3.696190203494706</v>
+        <v>3.452182077658812</v>
       </c>
       <c r="L3" t="n">
-        <v>4.251911768337185</v>
+        <v>3.888919739944052</v>
       </c>
       <c r="M3" t="n">
-        <v>3.244468745358278</v>
+        <v>3.128027276547499</v>
       </c>
       <c r="N3" t="n">
-        <v>3.891911376838411</v>
+        <v>3.582772649736567</v>
       </c>
       <c r="O3" t="n">
-        <v>6.698284930114145</v>
+        <v>6.418952702482327</v>
       </c>
       <c r="P3" t="n">
-        <v>3.208637301070097</v>
+        <v>3.10551498176244</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.786675661356466</v>
+        <v>3.522876128073677</v>
       </c>
       <c r="R3" t="n">
-        <v>5.126417440665378</v>
+        <v>4.416685653226271</v>
       </c>
       <c r="S3" t="n">
-        <v>3.979412830922284</v>
+        <v>3.676831805096743</v>
       </c>
       <c r="T3" t="n">
-        <v>3.488868708840562</v>
+        <v>3.297296718399235</v>
       </c>
       <c r="U3" t="n">
-        <v>4.172819307693318</v>
+        <v>4.091830338073151</v>
       </c>
       <c r="V3" t="n">
-        <v>3.515361864691777</v>
+        <v>3.330285379706669</v>
       </c>
       <c r="W3" t="n">
-        <v>4.976948652167986</v>
+        <v>4.728407204374157</v>
       </c>
       <c r="X3" t="n">
-        <v>3.716497112585555</v>
+        <v>3.459547282525253</v>
       </c>
       <c r="Y3" t="n">
-        <v>3.286985874231521</v>
+        <v>3.154031691553236</v>
       </c>
       <c r="Z3" t="n">
-        <v>4.613415190827754</v>
+        <v>4.259758576968762</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.158879958556813</v>
+        <v>3.064853946296341</v>
       </c>
       <c r="AB3" t="n">
-        <v>3.251827415757631</v>
+        <v>3.12640521945333</v>
       </c>
     </row>
     <row r="4">
@@ -4846,85 +4846,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.689433104848465</v>
+        <v>4.926274341536826</v>
       </c>
       <c r="C3" t="n">
-        <v>4.665549898751836</v>
+        <v>4.270022626955521</v>
       </c>
       <c r="D3" t="n">
-        <v>4.034250928011147</v>
+        <v>3.721974188456113</v>
       </c>
       <c r="E3" t="n">
-        <v>5.859287804034495</v>
+        <v>5.013830825032595</v>
       </c>
       <c r="F3" t="n">
-        <v>4.661361910866312</v>
+        <v>4.148489434332188</v>
       </c>
       <c r="G3" t="n">
-        <v>3.527620750153194</v>
+        <v>3.380011362075588</v>
       </c>
       <c r="H3" t="n">
-        <v>3.344002668140144</v>
+        <v>3.234792966250581</v>
       </c>
       <c r="I3" t="n">
-        <v>3.8022502371047</v>
+        <v>3.553762892511329</v>
       </c>
       <c r="J3" t="n">
-        <v>3.83578371225264</v>
+        <v>3.594391948628245</v>
       </c>
       <c r="K3" t="n">
-        <v>3.556072386129177</v>
+        <v>3.390877847204076</v>
       </c>
       <c r="L3" t="n">
-        <v>4.214990427218665</v>
+        <v>3.884287589729416</v>
       </c>
       <c r="M3" t="n">
-        <v>3.312763292892853</v>
+        <v>3.216055300812756</v>
       </c>
       <c r="N3" t="n">
-        <v>3.756832286258492</v>
+        <v>3.529098620206699</v>
       </c>
       <c r="O3" t="n">
-        <v>6.990071537522246</v>
+        <v>6.706171314468961</v>
       </c>
       <c r="P3" t="n">
-        <v>3.505704216832665</v>
+        <v>3.363590106990862</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.094098574593619</v>
+        <v>3.774335328978363</v>
       </c>
       <c r="R3" t="n">
-        <v>5.695508638238766</v>
+        <v>4.849074079564453</v>
       </c>
       <c r="S3" t="n">
-        <v>4.036809504439058</v>
+        <v>3.747077785050744</v>
       </c>
       <c r="T3" t="n">
-        <v>3.422820092451728</v>
+        <v>3.293168331712715</v>
       </c>
       <c r="U3" t="n">
-        <v>4.514704160106137</v>
+        <v>4.428306724279715</v>
       </c>
       <c r="V3" t="n">
-        <v>3.769954096931474</v>
+        <v>3.553446396139253</v>
       </c>
       <c r="W3" t="n">
-        <v>5.500376587540105</v>
+        <v>5.197669694007589</v>
       </c>
       <c r="X3" t="n">
-        <v>3.853993321699015</v>
+        <v>3.603582623076353</v>
       </c>
       <c r="Y3" t="n">
-        <v>3.592662297149758</v>
+        <v>3.411946571101399</v>
       </c>
       <c r="Z3" t="n">
-        <v>4.742663983812142</v>
+        <v>4.418680338910294</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.365014856936215</v>
+        <v>3.254416967914232</v>
       </c>
       <c r="AB3" t="n">
-        <v>3.566710718887575</v>
+        <v>3.387436388862418</v>
       </c>
     </row>
     <row r="4">
@@ -5442,85 +5442,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.661085415773461</v>
+        <v>2.536387381001675</v>
       </c>
       <c r="C3" t="n">
-        <v>2.700232305129886</v>
+        <v>2.572032848708908</v>
       </c>
       <c r="D3" t="n">
-        <v>2.400098590564847</v>
+        <v>2.345254166218993</v>
       </c>
       <c r="E3" t="n">
-        <v>3.173073833485024</v>
+        <v>2.907149651570773</v>
       </c>
       <c r="F3" t="n">
-        <v>2.98094503515303</v>
+        <v>2.745640143600208</v>
       </c>
       <c r="G3" t="n">
-        <v>3.207215184819939</v>
+        <v>2.929885689552447</v>
       </c>
       <c r="H3" t="n">
-        <v>2.444615256363269</v>
+        <v>2.373924906465889</v>
       </c>
       <c r="I3" t="n">
-        <v>3.232926853007128</v>
+        <v>2.917335787582878</v>
       </c>
       <c r="J3" t="n">
-        <v>2.912656526034994</v>
+        <v>2.712822057747371</v>
       </c>
       <c r="K3" t="n">
-        <v>3.253914391657523</v>
+        <v>2.954496411325165</v>
       </c>
       <c r="L3" t="n">
-        <v>2.88577222668035</v>
+        <v>2.691007171877431</v>
       </c>
       <c r="M3" t="n">
-        <v>3.427310257271114</v>
+        <v>3.068128688817338</v>
       </c>
       <c r="N3" t="n">
-        <v>2.698580290042759</v>
+        <v>2.553348262272535</v>
       </c>
       <c r="O3" t="n">
-        <v>4.488032639546115</v>
+        <v>4.403925195704691</v>
       </c>
       <c r="P3" t="n">
-        <v>2.67140977099712</v>
+        <v>2.54205365313073</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.97056971012914</v>
+        <v>2.744923287361383</v>
       </c>
       <c r="R3" t="n">
-        <v>2.999783293566413</v>
+        <v>2.753197447979874</v>
       </c>
       <c r="S3" t="n">
-        <v>3.104746331877594</v>
+        <v>2.859298135629211</v>
       </c>
       <c r="T3" t="n">
-        <v>2.661529776216129</v>
+        <v>2.524967996385216</v>
       </c>
       <c r="U3" t="n">
-        <v>3.004406068439432</v>
+        <v>2.888105219609903</v>
       </c>
       <c r="V3" t="n">
-        <v>2.584282219882159</v>
+        <v>2.48211223698593</v>
       </c>
       <c r="W3" t="n">
-        <v>3.022274816510594</v>
+        <v>2.940113705628779</v>
       </c>
       <c r="X3" t="n">
-        <v>3.002406105715203</v>
+        <v>2.762114841152558</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.646842083674286</v>
+        <v>2.519670128482451</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.436581084967448</v>
+        <v>2.358533765354915</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.544621174115338</v>
+        <v>2.447711586046849</v>
       </c>
       <c r="AB3" t="n">
-        <v>3.093847190683104</v>
+        <v>2.814174815868145</v>
       </c>
     </row>
     <row r="4">
@@ -6038,85 +6038,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.485396392471998</v>
+        <v>3.228881905180359</v>
       </c>
       <c r="C3" t="n">
-        <v>3.967401860720049</v>
+        <v>3.636213940403544</v>
       </c>
       <c r="D3" t="n">
-        <v>3.127547515182063</v>
+        <v>2.962764059512669</v>
       </c>
       <c r="E3" t="n">
-        <v>4.202753153248501</v>
+        <v>3.713614104177741</v>
       </c>
       <c r="F3" t="n">
-        <v>4.267031197283156</v>
+        <v>3.754265387230537</v>
       </c>
       <c r="G3" t="n">
-        <v>3.480986660440421</v>
+        <v>3.235839642351702</v>
       </c>
       <c r="H3" t="n">
-        <v>2.796097958272037</v>
+        <v>2.729932025157326</v>
       </c>
       <c r="I3" t="n">
-        <v>3.805442647414515</v>
+        <v>3.424614752836583</v>
       </c>
       <c r="J3" t="n">
-        <v>3.375876773686056</v>
+        <v>3.149591456119892</v>
       </c>
       <c r="K3" t="n">
-        <v>3.645226700192975</v>
+        <v>3.34389167421802</v>
       </c>
       <c r="L3" t="n">
-        <v>4.287535473761682</v>
+        <v>3.809594113192686</v>
       </c>
       <c r="M3" t="n">
-        <v>3.14010215698277</v>
+        <v>2.975753509736739</v>
       </c>
       <c r="N3" t="n">
-        <v>3.110001120202293</v>
+        <v>2.950645671132183</v>
       </c>
       <c r="O3" t="n">
-        <v>5.395699455203269</v>
+        <v>5.324999230229623</v>
       </c>
       <c r="P3" t="n">
-        <v>3.042489450860496</v>
+        <v>2.913411546093156</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.766544133474373</v>
+        <v>3.427902323043062</v>
       </c>
       <c r="R3" t="n">
-        <v>4.377843712951352</v>
+        <v>3.811033335657203</v>
       </c>
       <c r="S3" t="n">
-        <v>3.865053951162438</v>
+        <v>3.512468766028667</v>
       </c>
       <c r="T3" t="n">
-        <v>3.366996438785035</v>
+        <v>3.126216004309838</v>
       </c>
       <c r="U3" t="n">
-        <v>3.691289323642417</v>
+        <v>3.601468586593725</v>
       </c>
       <c r="V3" t="n">
-        <v>3.004133405404632</v>
+        <v>2.887727210420411</v>
       </c>
       <c r="W3" t="n">
-        <v>4.30230136137899</v>
+        <v>4.086640578470751</v>
       </c>
       <c r="X3" t="n">
-        <v>3.442633585626246</v>
+        <v>3.184718044762875</v>
       </c>
       <c r="Y3" t="n">
-        <v>3.405375353377732</v>
+        <v>3.160223496066679</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.287147279310231</v>
+        <v>3.146234131193539</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.002824182915568</v>
+        <v>2.877874702992594</v>
       </c>
       <c r="AB3" t="n">
-        <v>3.452694476706222</v>
+        <v>3.178949885609193</v>
       </c>
     </row>
     <row r="4">
